--- a/Result/analyze_3.xlsx
+++ b/Result/analyze_3.xlsx
@@ -441,57 +441,57 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>2025-10-31</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
     </row>
@@ -562,13 +562,13 @@
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J3" t="n">
         <v>1</v>
       </c>
       <c r="K3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -587,16 +587,36 @@
       <c r="C4" t="n">
         <v>0</v>
       </c>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
+      <c r="D4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
@@ -645,41 +665,39 @@
           <t>IC/晶圓製造</t>
         </is>
       </c>
-      <c r="B6" t="n">
-        <v>0</v>
-      </c>
+      <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
         <v>2</v>
       </c>
       <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>3</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
         <v>2</v>
       </c>
-      <c r="E6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" t="n">
-        <v>3</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0</v>
-      </c>
       <c r="I6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J6" t="n">
         <v>1</v>
       </c>
       <c r="K6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -692,34 +710,34 @@
         <v>0</v>
       </c>
       <c r="C7" t="n">
+        <v>4</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
+        <v>4</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H7" t="n">
         <v>3</v>
       </c>
-      <c r="D7" t="n">
-        <v>4</v>
-      </c>
-      <c r="E7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" t="n">
-        <v>4</v>
-      </c>
-      <c r="H7" t="n">
-        <v>1</v>
-      </c>
       <c r="I7" t="n">
+        <v>2</v>
+      </c>
+      <c r="J7" t="n">
+        <v>5</v>
+      </c>
+      <c r="K7" t="n">
         <v>3</v>
       </c>
-      <c r="J7" t="n">
-        <v>2</v>
-      </c>
-      <c r="K7" t="n">
-        <v>5</v>
-      </c>
       <c r="L7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M7" t="n">
         <v>1</v>
@@ -731,9 +749,7 @@
           <t>IC模組</t>
         </is>
       </c>
-      <c r="B8" t="n">
-        <v>0</v>
-      </c>
+      <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
         <v>0</v>
       </c>
@@ -744,25 +760,25 @@
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H8" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I8" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="J8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K8" t="n">
         <v>2</v>
       </c>
       <c r="L8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -778,34 +794,34 @@
         <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F9" t="n">
+        <v>7</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H9" t="n">
+        <v>7</v>
+      </c>
+      <c r="I9" t="n">
+        <v>3</v>
+      </c>
+      <c r="J9" t="n">
         <v>2</v>
       </c>
-      <c r="E9" t="n">
-        <v>1</v>
-      </c>
-      <c r="F9" t="n">
-        <v>1</v>
-      </c>
-      <c r="G9" t="n">
-        <v>7</v>
-      </c>
-      <c r="H9" t="n">
-        <v>1</v>
-      </c>
-      <c r="I9" t="n">
-        <v>9</v>
-      </c>
-      <c r="J9" t="n">
-        <v>4</v>
-      </c>
       <c r="K9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
@@ -825,31 +841,31 @@
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H10" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I10" t="n">
         <v>3</v>
       </c>
       <c r="J10" t="n">
+        <v>2</v>
+      </c>
+      <c r="K10" t="n">
         <v>3</v>
       </c>
-      <c r="K10" t="n">
-        <v>2</v>
-      </c>
       <c r="L10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -860,7 +876,7 @@
       </c>
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
@@ -869,16 +885,16 @@
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G11" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -890,7 +906,7 @@
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12">
@@ -919,16 +935,16 @@
         <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
         <v>0</v>
@@ -966,10 +982,10 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
@@ -1109,10 +1125,10 @@
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F17" t="n">
         <v>0</v>
@@ -1121,16 +1137,16 @@
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
@@ -1212,13 +1228,13 @@
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -1253,10 +1269,10 @@
         <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
         <v>0</v>
@@ -1270,37 +1286,37 @@
       </c>
       <c r="B21" t="inlineStr"/>
       <c r="C21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H21" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -1326,16 +1342,16 @@
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J22" t="n">
         <v>1</v>
       </c>
       <c r="K22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
@@ -1350,7 +1366,9 @@
           <t>中藥材、西藥原料藥</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr"/>
+      <c r="B23" t="n">
+        <v>0</v>
+      </c>
       <c r="C23" t="n">
         <v>0</v>
       </c>
@@ -1364,10 +1382,10 @@
         <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I23" t="n">
         <v>0</v>
@@ -1379,10 +1397,10 @@
         <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -1414,13 +1432,13 @@
         <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K24" t="n">
         <v>1</v>
       </c>
       <c r="L24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
         <v>0</v>
@@ -1446,7 +1464,7 @@
         <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H25" t="n">
         <v>1</v>
@@ -1458,7 +1476,7 @@
         <v>1</v>
       </c>
       <c r="K25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
@@ -1525,16 +1543,16 @@
         <v>0</v>
       </c>
       <c r="F27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I27" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -1546,7 +1564,7 @@
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -1660,13 +1678,13 @@
         <v>0</v>
       </c>
       <c r="J30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L30" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
         <v>0</v>
@@ -1695,19 +1713,19 @@
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L31" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
         <v>0</v>
@@ -1724,34 +1742,34 @@
         <v>0</v>
       </c>
       <c r="D32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F32" t="n">
         <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H32" t="n">
         <v>1</v>
       </c>
       <c r="I32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33">
@@ -1762,10 +1780,10 @@
       </c>
       <c r="B33" t="inlineStr"/>
       <c r="C33" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D33" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E33" t="n">
         <v>0</v>
@@ -1774,19 +1792,19 @@
         <v>0</v>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J33" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L33" t="n">
         <v>0</v>
@@ -1806,7 +1824,7 @@
         <v>1</v>
       </c>
       <c r="D34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E34" t="n">
         <v>0</v>
@@ -1842,9 +1860,11 @@
           <t>保健食品代理銷售及通路</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr"/>
+      <c r="B35" t="n">
+        <v>0</v>
+      </c>
       <c r="C35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D35" t="n">
         <v>0</v>
@@ -1862,7 +1882,7 @@
         <v>1</v>
       </c>
       <c r="I35" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -1982,16 +2002,16 @@
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L38" t="n">
         <v>0</v>
@@ -2108,10 +2128,10 @@
         <v>0</v>
       </c>
       <c r="I41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K41" t="n">
         <v>0</v>
@@ -2146,10 +2166,10 @@
         <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I42" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J42" t="n">
         <v>1</v>
@@ -2158,7 +2178,7 @@
         <v>1</v>
       </c>
       <c r="L42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
         <v>0</v>
@@ -2187,10 +2207,10 @@
         <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -2213,7 +2233,7 @@
       </c>
       <c r="B44" t="inlineStr"/>
       <c r="C44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D44" t="n">
         <v>0</v>
@@ -2222,16 +2242,16 @@
         <v>0</v>
       </c>
       <c r="F44" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G44" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H44" t="n">
         <v>0</v>
       </c>
       <c r="I44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J44" t="n">
         <v>1</v>
@@ -2240,7 +2260,7 @@
         <v>1</v>
       </c>
       <c r="L44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
         <v>0</v>
@@ -2272,10 +2292,10 @@
         <v>0</v>
       </c>
       <c r="I45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K45" t="n">
         <v>0</v>
@@ -2313,13 +2333,13 @@
         <v>0</v>
       </c>
       <c r="I46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J46" t="n">
         <v>1</v>
       </c>
       <c r="K46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L46" t="n">
         <v>0</v>
@@ -2354,13 +2374,13 @@
         <v>0</v>
       </c>
       <c r="I47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J47" t="n">
         <v>1</v>
       </c>
       <c r="K47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L47" t="n">
         <v>0</v>
@@ -2416,39 +2436,41 @@
           <t>光通訊設備(如光纖電纜、光傳輸設備)</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr"/>
+      <c r="B49" t="n">
+        <v>0</v>
+      </c>
       <c r="C49" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D49" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F49" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G49" t="n">
+        <v>1</v>
+      </c>
+      <c r="H49" t="n">
         <v>2</v>
       </c>
-      <c r="H49" t="n">
-        <v>1</v>
-      </c>
       <c r="I49" t="n">
+        <v>1</v>
+      </c>
+      <c r="J49" t="n">
         <v>2</v>
-      </c>
-      <c r="J49" t="n">
-        <v>1</v>
       </c>
       <c r="K49" t="n">
         <v>2</v>
       </c>
       <c r="L49" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="50">
@@ -2500,34 +2522,34 @@
       </c>
       <c r="B51" t="inlineStr"/>
       <c r="C51" t="n">
+        <v>6</v>
+      </c>
+      <c r="D51" t="n">
+        <v>5</v>
+      </c>
+      <c r="E51" t="n">
         <v>3</v>
       </c>
-      <c r="D51" t="n">
+      <c r="F51" t="n">
+        <v>4</v>
+      </c>
+      <c r="G51" t="n">
+        <v>3</v>
+      </c>
+      <c r="H51" t="n">
+        <v>1</v>
+      </c>
+      <c r="I51" t="n">
+        <v>2</v>
+      </c>
+      <c r="J51" t="n">
+        <v>0</v>
+      </c>
+      <c r="K51" t="n">
         <v>6</v>
       </c>
-      <c r="E51" t="n">
-        <v>5</v>
-      </c>
-      <c r="F51" t="n">
-        <v>3</v>
-      </c>
-      <c r="G51" t="n">
-        <v>4</v>
-      </c>
-      <c r="H51" t="n">
-        <v>3</v>
-      </c>
-      <c r="I51" t="n">
-        <v>1</v>
-      </c>
-      <c r="J51" t="n">
-        <v>2</v>
-      </c>
-      <c r="K51" t="n">
-        <v>0</v>
-      </c>
       <c r="L51" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="M51" t="n">
         <v>1</v>
@@ -2594,22 +2616,22 @@
         <v>0</v>
       </c>
       <c r="G53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H53" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I53" t="n">
+        <v>1</v>
+      </c>
+      <c r="J53" t="n">
+        <v>1</v>
+      </c>
+      <c r="K53" t="n">
+        <v>3</v>
+      </c>
+      <c r="L53" t="n">
         <v>2</v>
-      </c>
-      <c r="J53" t="n">
-        <v>1</v>
-      </c>
-      <c r="K53" t="n">
-        <v>1</v>
-      </c>
-      <c r="L53" t="n">
-        <v>3</v>
       </c>
       <c r="M53" t="n">
         <v>2</v>
@@ -2621,41 +2643,39 @@
           <t>其他電子產品及電子服務產業</t>
         </is>
       </c>
-      <c r="B54" t="n">
-        <v>0</v>
-      </c>
+      <c r="B54" t="inlineStr"/>
       <c r="C54" t="n">
+        <v>6</v>
+      </c>
+      <c r="D54" t="n">
+        <v>0</v>
+      </c>
+      <c r="E54" t="n">
+        <v>2</v>
+      </c>
+      <c r="F54" t="n">
+        <v>5</v>
+      </c>
+      <c r="G54" t="n">
+        <v>1</v>
+      </c>
+      <c r="H54" t="n">
+        <v>1</v>
+      </c>
+      <c r="I54" t="n">
+        <v>1</v>
+      </c>
+      <c r="J54" t="n">
         <v>4</v>
-      </c>
-      <c r="D54" t="n">
-        <v>6</v>
-      </c>
-      <c r="E54" t="n">
-        <v>0</v>
-      </c>
-      <c r="F54" t="n">
-        <v>2</v>
-      </c>
-      <c r="G54" t="n">
-        <v>5</v>
-      </c>
-      <c r="H54" t="n">
-        <v>1</v>
-      </c>
-      <c r="I54" t="n">
-        <v>1</v>
-      </c>
-      <c r="J54" t="n">
-        <v>1</v>
       </c>
       <c r="K54" t="n">
         <v>4</v>
       </c>
       <c r="L54" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="55">
@@ -2664,39 +2684,41 @@
           <t>其他電腦及週邊設備</t>
         </is>
       </c>
-      <c r="B55" t="inlineStr"/>
+      <c r="B55" t="n">
+        <v>0</v>
+      </c>
       <c r="C55" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D55" t="n">
+        <v>1</v>
+      </c>
+      <c r="E55" t="n">
+        <v>1</v>
+      </c>
+      <c r="F55" t="n">
         <v>2</v>
       </c>
-      <c r="E55" t="n">
-        <v>1</v>
-      </c>
-      <c r="F55" t="n">
-        <v>1</v>
-      </c>
       <c r="G55" t="n">
+        <v>4</v>
+      </c>
+      <c r="H55" t="n">
+        <v>1</v>
+      </c>
+      <c r="I55" t="n">
         <v>2</v>
       </c>
-      <c r="H55" t="n">
+      <c r="J55" t="n">
         <v>4</v>
       </c>
-      <c r="I55" t="n">
-        <v>1</v>
-      </c>
-      <c r="J55" t="n">
+      <c r="K55" t="n">
         <v>2</v>
       </c>
-      <c r="K55" t="n">
-        <v>4</v>
-      </c>
       <c r="L55" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56">
@@ -2710,34 +2732,34 @@
         <v>2</v>
       </c>
       <c r="D56" t="n">
+        <v>0</v>
+      </c>
+      <c r="E56" t="n">
+        <v>0</v>
+      </c>
+      <c r="F56" t="n">
+        <v>4</v>
+      </c>
+      <c r="G56" t="n">
+        <v>3</v>
+      </c>
+      <c r="H56" t="n">
+        <v>5</v>
+      </c>
+      <c r="I56" t="n">
+        <v>3</v>
+      </c>
+      <c r="J56" t="n">
         <v>2</v>
       </c>
-      <c r="E56" t="n">
-        <v>0</v>
-      </c>
-      <c r="F56" t="n">
-        <v>0</v>
-      </c>
-      <c r="G56" t="n">
+      <c r="K56" t="n">
         <v>4</v>
       </c>
-      <c r="H56" t="n">
-        <v>3</v>
-      </c>
-      <c r="I56" t="n">
-        <v>5</v>
-      </c>
-      <c r="J56" t="n">
-        <v>3</v>
-      </c>
-      <c r="K56" t="n">
+      <c r="L56" t="n">
+        <v>1</v>
+      </c>
+      <c r="M56" t="n">
         <v>2</v>
-      </c>
-      <c r="L56" t="n">
-        <v>4</v>
-      </c>
-      <c r="M56" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="57">
@@ -2789,34 +2811,34 @@
       </c>
       <c r="B58" t="inlineStr"/>
       <c r="C58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
       </c>
       <c r="K58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M58" t="n">
         <v>0</v>
@@ -2830,10 +2852,10 @@
       </c>
       <c r="B59" t="inlineStr"/>
       <c r="C59" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E59" t="n">
         <v>0</v>
@@ -2842,10 +2864,10 @@
         <v>0</v>
       </c>
       <c r="G59" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I59" t="n">
         <v>0</v>
@@ -2854,10 +2876,10 @@
         <v>0</v>
       </c>
       <c r="K59" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M59" t="n">
         <v>0</v>
@@ -2877,10 +2899,10 @@
         <v>0</v>
       </c>
       <c r="E60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
@@ -2895,10 +2917,10 @@
         <v>0</v>
       </c>
       <c r="K60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M60" t="n">
         <v>0</v>
@@ -3009,7 +3031,7 @@
         <v>0</v>
       </c>
       <c r="H63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I63" t="n">
         <v>1</v>
@@ -3021,7 +3043,7 @@
         <v>1</v>
       </c>
       <c r="L63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M63" t="n">
         <v>0</v>
@@ -3035,10 +3057,10 @@
       </c>
       <c r="B64" t="inlineStr"/>
       <c r="C64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D64" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E64" t="n">
         <v>0</v>
@@ -3078,16 +3100,36 @@
       <c r="C65" t="n">
         <v>0</v>
       </c>
-      <c r="D65" t="inlineStr"/>
-      <c r="E65" t="inlineStr"/>
-      <c r="F65" t="inlineStr"/>
-      <c r="G65" t="inlineStr"/>
-      <c r="H65" t="inlineStr"/>
-      <c r="I65" t="inlineStr"/>
-      <c r="J65" t="inlineStr"/>
-      <c r="K65" t="inlineStr"/>
-      <c r="L65" t="inlineStr"/>
-      <c r="M65" t="inlineStr"/>
+      <c r="D65" t="n">
+        <v>0</v>
+      </c>
+      <c r="E65" t="n">
+        <v>0</v>
+      </c>
+      <c r="F65" t="n">
+        <v>0</v>
+      </c>
+      <c r="G65" t="n">
+        <v>0</v>
+      </c>
+      <c r="H65" t="n">
+        <v>0</v>
+      </c>
+      <c r="I65" t="n">
+        <v>0</v>
+      </c>
+      <c r="J65" t="n">
+        <v>0</v>
+      </c>
+      <c r="K65" t="n">
+        <v>0</v>
+      </c>
+      <c r="L65" t="n">
+        <v>0</v>
+      </c>
+      <c r="M65" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
@@ -3099,16 +3141,36 @@
       <c r="C66" t="n">
         <v>0</v>
       </c>
-      <c r="D66" t="inlineStr"/>
-      <c r="E66" t="inlineStr"/>
-      <c r="F66" t="inlineStr"/>
-      <c r="G66" t="inlineStr"/>
-      <c r="H66" t="inlineStr"/>
-      <c r="I66" t="inlineStr"/>
-      <c r="J66" t="inlineStr"/>
-      <c r="K66" t="inlineStr"/>
-      <c r="L66" t="inlineStr"/>
-      <c r="M66" t="inlineStr"/>
+      <c r="D66" t="n">
+        <v>0</v>
+      </c>
+      <c r="E66" t="n">
+        <v>0</v>
+      </c>
+      <c r="F66" t="n">
+        <v>0</v>
+      </c>
+      <c r="G66" t="n">
+        <v>0</v>
+      </c>
+      <c r="H66" t="n">
+        <v>0</v>
+      </c>
+      <c r="I66" t="n">
+        <v>0</v>
+      </c>
+      <c r="J66" t="n">
+        <v>0</v>
+      </c>
+      <c r="K66" t="n">
+        <v>0</v>
+      </c>
+      <c r="L66" t="n">
+        <v>0</v>
+      </c>
+      <c r="M66" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
@@ -3139,10 +3201,10 @@
         <v>0</v>
       </c>
       <c r="J67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L67" t="n">
         <v>0</v>
@@ -3180,10 +3242,10 @@
         <v>0</v>
       </c>
       <c r="J68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L68" t="n">
         <v>0</v>
@@ -3198,9 +3260,7 @@
           <t>加油站</t>
         </is>
       </c>
-      <c r="B69" t="n">
-        <v>0</v>
-      </c>
+      <c r="B69" t="inlineStr"/>
       <c r="C69" t="n">
         <v>0</v>
       </c>
@@ -3211,10 +3271,10 @@
         <v>0</v>
       </c>
       <c r="F69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H69" t="n">
         <v>0</v>
@@ -3290,10 +3350,10 @@
         <v>0</v>
       </c>
       <c r="E71" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
@@ -3308,13 +3368,13 @@
         <v>0</v>
       </c>
       <c r="K71" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L71" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M71" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="72">
@@ -3328,7 +3388,7 @@
         <v>1</v>
       </c>
       <c r="D72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E72" t="n">
         <v>0</v>
@@ -3349,13 +3409,13 @@
         <v>0</v>
       </c>
       <c r="K72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="73">
@@ -3448,7 +3508,7 @@
       </c>
       <c r="B75" t="inlineStr"/>
       <c r="C75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D75" t="n">
         <v>0</v>
@@ -3469,13 +3529,13 @@
         <v>0</v>
       </c>
       <c r="J75" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K75" t="n">
         <v>1</v>
       </c>
       <c r="L75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M75" t="n">
         <v>0</v>
@@ -3489,13 +3549,13 @@
       </c>
       <c r="B76" t="inlineStr"/>
       <c r="C76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D76" t="n">
         <v>1</v>
       </c>
       <c r="E76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F76" t="n">
         <v>0</v>
@@ -3507,13 +3567,13 @@
         <v>0</v>
       </c>
       <c r="I76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J76" t="n">
         <v>1</v>
       </c>
       <c r="K76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L76" t="n">
         <v>0</v>
@@ -3571,7 +3631,7 @@
       </c>
       <c r="B78" t="inlineStr"/>
       <c r="C78" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D78" t="n">
         <v>0</v>
@@ -3583,25 +3643,25 @@
         <v>0</v>
       </c>
       <c r="G78" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H78" t="n">
         <v>1</v>
       </c>
       <c r="I78" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
       </c>
       <c r="K78" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L78" t="n">
+        <v>1</v>
+      </c>
+      <c r="M78" t="n">
         <v>2</v>
-      </c>
-      <c r="M78" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="79">
@@ -3674,10 +3734,10 @@
         <v>0</v>
       </c>
       <c r="J80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K80" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L80" t="n">
         <v>0</v>
@@ -3759,10 +3819,10 @@
         <v>0</v>
       </c>
       <c r="K82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M82" t="n">
         <v>0</v>
@@ -3779,34 +3839,34 @@
         <v>2</v>
       </c>
       <c r="D83" t="n">
+        <v>0</v>
+      </c>
+      <c r="E83" t="n">
+        <v>1</v>
+      </c>
+      <c r="F83" t="n">
+        <v>1</v>
+      </c>
+      <c r="G83" t="n">
+        <v>0</v>
+      </c>
+      <c r="H83" t="n">
+        <v>1</v>
+      </c>
+      <c r="I83" t="n">
+        <v>0</v>
+      </c>
+      <c r="J83" t="n">
         <v>2</v>
       </c>
-      <c r="E83" t="n">
-        <v>0</v>
-      </c>
-      <c r="F83" t="n">
-        <v>1</v>
-      </c>
-      <c r="G83" t="n">
-        <v>1</v>
-      </c>
-      <c r="H83" t="n">
-        <v>0</v>
-      </c>
-      <c r="I83" t="n">
-        <v>1</v>
-      </c>
-      <c r="J83" t="n">
-        <v>0</v>
-      </c>
       <c r="K83" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L83" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M83" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="84">
@@ -3815,7 +3875,9 @@
           <t>基礎工程</t>
         </is>
       </c>
-      <c r="B84" t="inlineStr"/>
+      <c r="B84" t="n">
+        <v>0</v>
+      </c>
       <c r="C84" t="n">
         <v>0</v>
       </c>
@@ -3899,7 +3961,7 @@
       </c>
       <c r="B86" t="inlineStr"/>
       <c r="C86" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D86" t="n">
         <v>0</v>
@@ -3920,16 +3982,16 @@
         <v>0</v>
       </c>
       <c r="J86" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K86" t="n">
         <v>1</v>
       </c>
       <c r="L86" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M86" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="87">
@@ -3955,22 +4017,22 @@
         <v>0</v>
       </c>
       <c r="H87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
       </c>
       <c r="K87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="88">
@@ -4002,10 +4064,10 @@
         <v>0</v>
       </c>
       <c r="J88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L88" t="n">
         <v>0</v>
@@ -4020,9 +4082,7 @@
           <t>塑膠製品</t>
         </is>
       </c>
-      <c r="B89" t="n">
-        <v>0</v>
-      </c>
+      <c r="B89" t="inlineStr"/>
       <c r="C89" t="n">
         <v>1</v>
       </c>
@@ -4033,28 +4093,28 @@
         <v>1</v>
       </c>
       <c r="F89" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G89" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H89" t="n">
         <v>1</v>
       </c>
       <c r="I89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J89" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K89" t="n">
         <v>1</v>
       </c>
       <c r="L89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M89" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="90">
@@ -4124,13 +4184,13 @@
         <v>0</v>
       </c>
       <c r="I91" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J91" t="n">
         <v>1</v>
       </c>
       <c r="K91" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L91" t="n">
         <v>0</v>
@@ -4147,37 +4207,37 @@
       </c>
       <c r="B92" t="inlineStr"/>
       <c r="C92" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D92" t="n">
+        <v>0</v>
+      </c>
+      <c r="E92" t="n">
+        <v>2</v>
+      </c>
+      <c r="F92" t="n">
+        <v>1</v>
+      </c>
+      <c r="G92" t="n">
+        <v>1</v>
+      </c>
+      <c r="H92" t="n">
+        <v>1</v>
+      </c>
+      <c r="I92" t="n">
+        <v>0</v>
+      </c>
+      <c r="J92" t="n">
+        <v>0</v>
+      </c>
+      <c r="K92" t="n">
         <v>3</v>
       </c>
-      <c r="E92" t="n">
-        <v>0</v>
-      </c>
-      <c r="F92" t="n">
-        <v>2</v>
-      </c>
-      <c r="G92" t="n">
-        <v>1</v>
-      </c>
-      <c r="H92" t="n">
-        <v>1</v>
-      </c>
-      <c r="I92" t="n">
-        <v>1</v>
-      </c>
-      <c r="J92" t="n">
-        <v>0</v>
-      </c>
-      <c r="K92" t="n">
-        <v>0</v>
-      </c>
       <c r="L92" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M92" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="93">
@@ -4270,7 +4330,7 @@
       </c>
       <c r="B95" t="inlineStr"/>
       <c r="C95" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D95" t="n">
         <v>0</v>
@@ -4294,10 +4354,10 @@
         <v>0</v>
       </c>
       <c r="K95" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L95" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M95" t="n">
         <v>0</v>
@@ -4311,7 +4371,7 @@
       </c>
       <c r="B96" t="inlineStr"/>
       <c r="C96" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D96" t="n">
         <v>0</v>
@@ -4335,10 +4395,10 @@
         <v>0</v>
       </c>
       <c r="K96" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L96" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M96" t="n">
         <v>0</v>
@@ -4352,10 +4412,10 @@
       </c>
       <c r="B97" t="inlineStr"/>
       <c r="C97" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D97" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E97" t="n">
         <v>0</v>
@@ -4396,7 +4456,7 @@
         <v>1</v>
       </c>
       <c r="D98" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E98" t="n">
         <v>0</v>
@@ -4432,7 +4492,9 @@
           <t>娛樂服務業</t>
         </is>
       </c>
-      <c r="B99" t="inlineStr"/>
+      <c r="B99" t="n">
+        <v>0</v>
+      </c>
       <c r="C99" t="n">
         <v>0</v>
       </c>
@@ -4477,16 +4539,36 @@
       <c r="C100" t="n">
         <v>0</v>
       </c>
-      <c r="D100" t="inlineStr"/>
-      <c r="E100" t="inlineStr"/>
-      <c r="F100" t="inlineStr"/>
-      <c r="G100" t="inlineStr"/>
-      <c r="H100" t="inlineStr"/>
-      <c r="I100" t="inlineStr"/>
-      <c r="J100" t="inlineStr"/>
-      <c r="K100" t="inlineStr"/>
-      <c r="L100" t="inlineStr"/>
-      <c r="M100" t="inlineStr"/>
+      <c r="D100" t="n">
+        <v>0</v>
+      </c>
+      <c r="E100" t="n">
+        <v>0</v>
+      </c>
+      <c r="F100" t="n">
+        <v>0</v>
+      </c>
+      <c r="G100" t="n">
+        <v>0</v>
+      </c>
+      <c r="H100" t="n">
+        <v>0</v>
+      </c>
+      <c r="I100" t="n">
+        <v>0</v>
+      </c>
+      <c r="J100" t="n">
+        <v>0</v>
+      </c>
+      <c r="K100" t="n">
+        <v>0</v>
+      </c>
+      <c r="L100" t="n">
+        <v>0</v>
+      </c>
+      <c r="M100" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="1" t="inlineStr">
@@ -4517,16 +4599,16 @@
         <v>0</v>
       </c>
       <c r="J101" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K101" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L101" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M101" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="102">
@@ -4535,41 +4617,39 @@
           <t>安全監控系統</t>
         </is>
       </c>
-      <c r="B102" t="n">
-        <v>0</v>
-      </c>
+      <c r="B102" t="inlineStr"/>
       <c r="C102" t="n">
+        <v>1</v>
+      </c>
+      <c r="D102" t="n">
+        <v>0</v>
+      </c>
+      <c r="E102" t="n">
+        <v>1</v>
+      </c>
+      <c r="F102" t="n">
+        <v>1</v>
+      </c>
+      <c r="G102" t="n">
+        <v>1</v>
+      </c>
+      <c r="H102" t="n">
+        <v>1</v>
+      </c>
+      <c r="I102" t="n">
+        <v>3</v>
+      </c>
+      <c r="J102" t="n">
         <v>2</v>
       </c>
-      <c r="D102" t="n">
-        <v>1</v>
-      </c>
-      <c r="E102" t="n">
-        <v>0</v>
-      </c>
-      <c r="F102" t="n">
-        <v>1</v>
-      </c>
-      <c r="G102" t="n">
-        <v>1</v>
-      </c>
-      <c r="H102" t="n">
-        <v>1</v>
-      </c>
-      <c r="I102" t="n">
-        <v>1</v>
-      </c>
-      <c r="J102" t="n">
-        <v>3</v>
-      </c>
       <c r="K102" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L102" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M102" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="103">
@@ -4619,41 +4699,39 @@
           <t>封裝/模組</t>
         </is>
       </c>
-      <c r="B104" t="n">
-        <v>0</v>
-      </c>
+      <c r="B104" t="inlineStr"/>
       <c r="C104" t="n">
+        <v>0</v>
+      </c>
+      <c r="D104" t="n">
+        <v>0</v>
+      </c>
+      <c r="E104" t="n">
+        <v>0</v>
+      </c>
+      <c r="F104" t="n">
+        <v>0</v>
+      </c>
+      <c r="G104" t="n">
+        <v>0</v>
+      </c>
+      <c r="H104" t="n">
+        <v>0</v>
+      </c>
+      <c r="I104" t="n">
+        <v>0</v>
+      </c>
+      <c r="J104" t="n">
         <v>2</v>
       </c>
-      <c r="D104" t="n">
-        <v>0</v>
-      </c>
-      <c r="E104" t="n">
-        <v>0</v>
-      </c>
-      <c r="F104" t="n">
-        <v>0</v>
-      </c>
-      <c r="G104" t="n">
-        <v>0</v>
-      </c>
-      <c r="H104" t="n">
-        <v>0</v>
-      </c>
-      <c r="I104" t="n">
-        <v>0</v>
-      </c>
-      <c r="J104" t="n">
-        <v>0</v>
-      </c>
       <c r="K104" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L104" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M104" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="105">
@@ -4666,10 +4744,10 @@
         <v>0</v>
       </c>
       <c r="C105" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D105" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E105" t="n">
         <v>0</v>
@@ -4681,7 +4759,7 @@
         <v>0</v>
       </c>
       <c r="H105" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I105" t="n">
         <v>1</v>
@@ -4690,10 +4768,10 @@
         <v>1</v>
       </c>
       <c r="K105" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L105" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M105" t="n">
         <v>1</v>
@@ -4719,25 +4797,25 @@
         <v>0</v>
       </c>
       <c r="G106" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H106" t="n">
         <v>0</v>
       </c>
       <c r="I106" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J106" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K106" t="n">
         <v>1</v>
       </c>
       <c r="L106" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M106" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="107">
@@ -4889,10 +4967,10 @@
         <v>0</v>
       </c>
       <c r="I110" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J110" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K110" t="n">
         <v>0</v>
@@ -4910,9 +4988,7 @@
           <t>工業電腦</t>
         </is>
       </c>
-      <c r="B111" t="n">
-        <v>0</v>
-      </c>
+      <c r="B111" t="inlineStr"/>
       <c r="C111" t="n">
         <v>1</v>
       </c>
@@ -4920,31 +4996,31 @@
         <v>1</v>
       </c>
       <c r="E111" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F111" t="n">
+        <v>1</v>
+      </c>
+      <c r="G111" t="n">
         <v>2</v>
       </c>
-      <c r="G111" t="n">
-        <v>1</v>
-      </c>
       <c r="H111" t="n">
+        <v>0</v>
+      </c>
+      <c r="I111" t="n">
         <v>2</v>
       </c>
-      <c r="I111" t="n">
-        <v>0</v>
-      </c>
       <c r="J111" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K111" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L111" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M111" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="112">
@@ -4961,7 +5037,7 @@
         <v>1</v>
       </c>
       <c r="E112" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F112" t="n">
         <v>0</v>
@@ -4979,10 +5055,10 @@
         <v>0</v>
       </c>
       <c r="K112" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L112" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M112" t="n">
         <v>0</v>
@@ -4996,13 +5072,13 @@
       </c>
       <c r="B113" t="inlineStr"/>
       <c r="C113" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D113" t="n">
         <v>1</v>
       </c>
       <c r="E113" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F113" t="n">
         <v>0</v>
@@ -5020,10 +5096,10 @@
         <v>0</v>
       </c>
       <c r="K113" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L113" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M113" t="n">
         <v>0</v>
@@ -5162,16 +5238,36 @@
       <c r="C117" t="n">
         <v>0</v>
       </c>
-      <c r="D117" t="inlineStr"/>
-      <c r="E117" t="inlineStr"/>
-      <c r="F117" t="inlineStr"/>
-      <c r="G117" t="inlineStr"/>
-      <c r="H117" t="inlineStr"/>
-      <c r="I117" t="inlineStr"/>
-      <c r="J117" t="inlineStr"/>
-      <c r="K117" t="inlineStr"/>
-      <c r="L117" t="inlineStr"/>
-      <c r="M117" t="inlineStr"/>
+      <c r="D117" t="n">
+        <v>0</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" s="1" t="inlineStr">
@@ -5225,10 +5321,10 @@
         <v>0</v>
       </c>
       <c r="D119" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E119" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F119" t="n">
         <v>0</v>
@@ -5237,16 +5333,16 @@
         <v>0</v>
       </c>
       <c r="H119" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I119" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J119" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K119" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L119" t="n">
         <v>0</v>
@@ -5261,36 +5357,38 @@
           <t>建材原料</t>
         </is>
       </c>
-      <c r="B120" t="inlineStr"/>
+      <c r="B120" t="n">
+        <v>0</v>
+      </c>
       <c r="C120" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D120" t="n">
         <v>1</v>
       </c>
       <c r="E120" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F120" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G120" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H120" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I120" t="n">
         <v>1</v>
       </c>
       <c r="J120" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K120" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L120" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M120" t="n">
         <v>1</v>
@@ -5302,20 +5400,18 @@
           <t>建設業</t>
         </is>
       </c>
-      <c r="B121" t="n">
-        <v>0</v>
-      </c>
+      <c r="B121" t="inlineStr"/>
       <c r="C121" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D121" t="n">
         <v>0</v>
       </c>
       <c r="E121" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F121" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G121" t="n">
         <v>1</v>
@@ -5330,10 +5426,10 @@
         <v>0</v>
       </c>
       <c r="K121" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L121" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M121" t="n">
         <v>0</v>
@@ -5390,16 +5486,36 @@
       <c r="C123" t="n">
         <v>0</v>
       </c>
-      <c r="D123" t="inlineStr"/>
-      <c r="E123" t="inlineStr"/>
-      <c r="F123" t="inlineStr"/>
-      <c r="G123" t="inlineStr"/>
-      <c r="H123" t="inlineStr"/>
-      <c r="I123" t="inlineStr"/>
-      <c r="J123" t="inlineStr"/>
-      <c r="K123" t="inlineStr"/>
-      <c r="L123" t="inlineStr"/>
-      <c r="M123" t="inlineStr"/>
+      <c r="D123" t="n">
+        <v>0</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" s="1" t="inlineStr">
@@ -5424,7 +5540,7 @@
         <v>0</v>
       </c>
       <c r="H124" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I124" t="n">
         <v>0</v>
@@ -5433,10 +5549,10 @@
         <v>0</v>
       </c>
       <c r="K124" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L124" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M124" t="n">
         <v>0</v>
@@ -5500,19 +5616,19 @@
         <v>0</v>
       </c>
       <c r="F126" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G126" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H126" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I126" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J126" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K126" t="n">
         <v>0</v>
@@ -5550,10 +5666,10 @@
         <v>0</v>
       </c>
       <c r="I127" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J127" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K127" t="n">
         <v>0</v>
@@ -5581,7 +5697,7 @@
         <v>0</v>
       </c>
       <c r="E128" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F128" t="n">
         <v>0</v>
@@ -5590,22 +5706,22 @@
         <v>0</v>
       </c>
       <c r="H128" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I128" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J128" t="n">
         <v>2</v>
       </c>
       <c r="K128" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L128" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M128" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="129">
@@ -5631,7 +5747,7 @@
         <v>0</v>
       </c>
       <c r="H129" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I129" t="n">
         <v>1</v>
@@ -5643,7 +5759,7 @@
         <v>1</v>
       </c>
       <c r="L129" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M129" t="n">
         <v>0</v>
@@ -5678,10 +5794,10 @@
         <v>0</v>
       </c>
       <c r="J130" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K130" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L130" t="n">
         <v>0</v>
@@ -5710,10 +5826,10 @@
         <v>0</v>
       </c>
       <c r="G131" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H131" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I131" t="n">
         <v>0</v>
@@ -5722,7 +5838,7 @@
         <v>0</v>
       </c>
       <c r="K131" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L131" t="n">
         <v>1</v>
@@ -5739,19 +5855,19 @@
       </c>
       <c r="B132" t="inlineStr"/>
       <c r="C132" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D132" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E132" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F132" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G132" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H132" t="n">
         <v>0</v>
@@ -5766,10 +5882,10 @@
         <v>0</v>
       </c>
       <c r="L132" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M132" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="133">
@@ -5801,10 +5917,10 @@
         <v>0</v>
       </c>
       <c r="J133" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K133" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L133" t="n">
         <v>0</v>
@@ -5962,10 +6078,10 @@
         <v>0</v>
       </c>
       <c r="I137" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J137" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K137" t="n">
         <v>0</v>
@@ -5988,10 +6104,10 @@
         <v>0</v>
       </c>
       <c r="D138" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E138" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F138" t="n">
         <v>0</v>
@@ -6024,20 +6140,18 @@
           <t>散熱片、風扇馬達、散熱模組</t>
         </is>
       </c>
-      <c r="B139" t="n">
-        <v>0</v>
-      </c>
+      <c r="B139" t="inlineStr"/>
       <c r="C139" t="n">
         <v>1</v>
       </c>
       <c r="D139" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E139" t="n">
         <v>0</v>
       </c>
       <c r="F139" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G139" t="n">
         <v>1</v>
@@ -6052,7 +6166,7 @@
         <v>1</v>
       </c>
       <c r="K139" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L139" t="n">
         <v>0</v>
@@ -6067,7 +6181,9 @@
           <t>散裝航運</t>
         </is>
       </c>
-      <c r="B140" t="inlineStr"/>
+      <c r="B140" t="n">
+        <v>0</v>
+      </c>
       <c r="C140" t="n">
         <v>0</v>
       </c>
@@ -6131,7 +6247,7 @@
         <v>0</v>
       </c>
       <c r="J141" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K141" t="n">
         <v>1</v>
@@ -6140,7 +6256,7 @@
         <v>1</v>
       </c>
       <c r="M141" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="142">
@@ -6213,10 +6329,10 @@
         <v>0</v>
       </c>
       <c r="J143" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K143" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L143" t="n">
         <v>0</v>
@@ -6233,10 +6349,10 @@
       </c>
       <c r="B144" t="inlineStr"/>
       <c r="C144" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D144" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E144" t="n">
         <v>0</v>
@@ -6254,16 +6370,16 @@
         <v>0</v>
       </c>
       <c r="J144" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K144" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L144" t="n">
         <v>0</v>
       </c>
       <c r="M144" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="145">
@@ -6295,16 +6411,16 @@
         <v>0</v>
       </c>
       <c r="J145" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K145" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L145" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M145" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="146">
@@ -6333,10 +6449,10 @@
         <v>0</v>
       </c>
       <c r="I146" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J146" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K146" t="n">
         <v>0</v>
@@ -6377,16 +6493,16 @@
         <v>0</v>
       </c>
       <c r="J147" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K147" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L147" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M147" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="148">
@@ -6400,22 +6516,22 @@
         <v>0</v>
       </c>
       <c r="D148" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E148" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F148" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G148" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H148" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I148" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -6465,10 +6581,10 @@
         <v>0</v>
       </c>
       <c r="L149" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M149" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="150">
@@ -6485,13 +6601,13 @@
         <v>0</v>
       </c>
       <c r="E150" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F150" t="n">
         <v>1</v>
       </c>
       <c r="G150" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H150" t="n">
         <v>0</v>
@@ -6518,7 +6634,9 @@
           <t>旅館服務業</t>
         </is>
       </c>
-      <c r="B151" t="inlineStr"/>
+      <c r="B151" t="n">
+        <v>0</v>
+      </c>
       <c r="C151" t="n">
         <v>0</v>
       </c>
@@ -6526,10 +6644,10 @@
         <v>0</v>
       </c>
       <c r="E151" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F151" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G151" t="n">
         <v>0</v>
@@ -6538,19 +6656,19 @@
         <v>0</v>
       </c>
       <c r="I151" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J151" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K151" t="n">
         <v>0</v>
       </c>
       <c r="L151" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M151" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="152">
@@ -6579,13 +6697,13 @@
         <v>0</v>
       </c>
       <c r="I152" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J152" t="n">
         <v>1</v>
       </c>
       <c r="K152" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L152" t="n">
         <v>0</v>
@@ -6605,10 +6723,10 @@
         <v>0</v>
       </c>
       <c r="D153" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E153" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F153" t="n">
         <v>0</v>
@@ -6623,16 +6741,16 @@
         <v>0</v>
       </c>
       <c r="J153" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K153" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L153" t="n">
         <v>0</v>
       </c>
       <c r="M153" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="154">
@@ -6643,10 +6761,10 @@
       </c>
       <c r="B154" t="inlineStr"/>
       <c r="C154" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D154" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E154" t="n">
         <v>0</v>
@@ -6667,10 +6785,10 @@
         <v>0</v>
       </c>
       <c r="K154" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L154" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M154" t="n">
         <v>0</v>
@@ -6725,7 +6843,7 @@
       </c>
       <c r="B156" t="inlineStr"/>
       <c r="C156" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D156" t="n">
         <v>0</v>
@@ -6740,22 +6858,22 @@
         <v>0</v>
       </c>
       <c r="H156" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I156" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
       </c>
       <c r="K156" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L156" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M156" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="157">
@@ -6764,9 +6882,7 @@
           <t>染整</t>
         </is>
       </c>
-      <c r="B157" t="n">
-        <v>0</v>
-      </c>
+      <c r="B157" t="inlineStr"/>
       <c r="C157" t="n">
         <v>0</v>
       </c>
@@ -6777,10 +6893,10 @@
         <v>0</v>
       </c>
       <c r="F157" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G157" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H157" t="n">
         <v>0</v>
@@ -6789,13 +6905,13 @@
         <v>0</v>
       </c>
       <c r="J157" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K157" t="n">
         <v>2</v>
       </c>
       <c r="L157" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M157" t="n">
         <v>0</v>
@@ -6821,19 +6937,19 @@
         <v>0</v>
       </c>
       <c r="G158" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H158" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I158" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J158" t="n">
         <v>1</v>
       </c>
       <c r="K158" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L158" t="n">
         <v>0</v>
@@ -6912,10 +7028,10 @@
         <v>0</v>
       </c>
       <c r="J160" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K160" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L160" t="n">
         <v>0</v>
@@ -6953,10 +7069,10 @@
         <v>0</v>
       </c>
       <c r="J161" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K161" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L161" t="n">
         <v>0</v>
@@ -6994,13 +7110,13 @@
         <v>0</v>
       </c>
       <c r="J162" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K162" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L162" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M162" t="n">
         <v>1</v>
@@ -7035,13 +7151,13 @@
         <v>0</v>
       </c>
       <c r="J163" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K163" t="n">
         <v>1</v>
       </c>
       <c r="L163" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M163" t="n">
         <v>0</v>
@@ -7053,9 +7169,7 @@
           <t>機構樞紐</t>
         </is>
       </c>
-      <c r="B164" t="n">
-        <v>0</v>
-      </c>
+      <c r="B164" t="inlineStr"/>
       <c r="C164" t="n">
         <v>0</v>
       </c>
@@ -7075,13 +7189,13 @@
         <v>0</v>
       </c>
       <c r="I164" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J164" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K164" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L164" t="n">
         <v>0</v>
@@ -7100,7 +7214,7 @@
         <v>0</v>
       </c>
       <c r="C165" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D165" t="n">
         <v>0</v>
@@ -7115,22 +7229,22 @@
         <v>0</v>
       </c>
       <c r="H165" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I165" t="n">
         <v>1</v>
       </c>
       <c r="J165" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K165" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L165" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M165" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="166">
@@ -7147,7 +7261,7 @@
         <v>1</v>
       </c>
       <c r="E166" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F166" t="n">
         <v>0</v>
@@ -7165,10 +7279,10 @@
         <v>0</v>
       </c>
       <c r="K166" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L166" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M166" t="n">
         <v>0</v>
@@ -7182,34 +7296,34 @@
       </c>
       <c r="B167" t="inlineStr"/>
       <c r="C167" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D167" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E167" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F167" t="n">
         <v>1</v>
       </c>
       <c r="G167" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H167" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I167" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
       </c>
       <c r="K167" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L167" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M167" t="n">
         <v>0</v>
@@ -7396,10 +7510,10 @@
         <v>0</v>
       </c>
       <c r="F172" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G172" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H172" t="n">
         <v>0</v>
@@ -7411,10 +7525,10 @@
         <v>0</v>
       </c>
       <c r="K172" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L172" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M172" t="n">
         <v>0</v>
@@ -7428,13 +7542,13 @@
       </c>
       <c r="B173" t="inlineStr"/>
       <c r="C173" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D173" t="n">
         <v>1</v>
       </c>
       <c r="E173" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F173" t="n">
         <v>0</v>
@@ -7449,10 +7563,10 @@
         <v>0</v>
       </c>
       <c r="J173" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K173" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L173" t="n">
         <v>0</v>
@@ -7610,19 +7724,19 @@
         <v>0</v>
       </c>
       <c r="I177" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J177" t="n">
         <v>1</v>
       </c>
       <c r="K177" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L177" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M177" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="178">
@@ -7672,39 +7786,41 @@
           <t>無線通訊設備(如行動電話、衛星定位系統、衛星通訊設備、微波通訊設備、數位機上盒)</t>
         </is>
       </c>
-      <c r="B179" t="inlineStr"/>
+      <c r="B179" t="n">
+        <v>0</v>
+      </c>
       <c r="C179" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D179" t="n">
+        <v>1</v>
+      </c>
+      <c r="E179" t="n">
+        <v>1</v>
+      </c>
+      <c r="F179" t="n">
+        <v>1</v>
+      </c>
+      <c r="G179" t="n">
+        <v>1</v>
+      </c>
+      <c r="H179" t="n">
+        <v>3</v>
+      </c>
+      <c r="I179" t="n">
         <v>2</v>
       </c>
-      <c r="E179" t="n">
-        <v>1</v>
-      </c>
-      <c r="F179" t="n">
-        <v>1</v>
-      </c>
-      <c r="G179" t="n">
-        <v>1</v>
-      </c>
-      <c r="H179" t="n">
-        <v>1</v>
-      </c>
-      <c r="I179" t="n">
-        <v>3</v>
-      </c>
       <c r="J179" t="n">
+        <v>5</v>
+      </c>
+      <c r="K179" t="n">
+        <v>1</v>
+      </c>
+      <c r="L179" t="n">
+        <v>0</v>
+      </c>
+      <c r="M179" t="n">
         <v>2</v>
-      </c>
-      <c r="K179" t="n">
-        <v>5</v>
-      </c>
-      <c r="L179" t="n">
-        <v>1</v>
-      </c>
-      <c r="M179" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="180">
@@ -7739,10 +7855,10 @@
         <v>0</v>
       </c>
       <c r="K180" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L180" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M180" t="n">
         <v>0</v>
@@ -7758,7 +7874,7 @@
         <v>0</v>
       </c>
       <c r="C181" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D181" t="n">
         <v>0</v>
@@ -7767,28 +7883,28 @@
         <v>0</v>
       </c>
       <c r="F181" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G181" t="n">
         <v>1</v>
       </c>
       <c r="H181" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I181" t="n">
         <v>0</v>
       </c>
       <c r="J181" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K181" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L181" t="n">
         <v>2</v>
       </c>
       <c r="M181" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="182">
@@ -7799,13 +7915,13 @@
       </c>
       <c r="B182" t="inlineStr"/>
       <c r="C182" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D182" t="n">
         <v>1</v>
       </c>
       <c r="E182" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F182" t="n">
         <v>0</v>
@@ -7820,13 +7936,13 @@
         <v>0</v>
       </c>
       <c r="J182" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K182" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L182" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M182" t="n">
         <v>1</v>
@@ -7896,22 +8012,22 @@
         <v>0</v>
       </c>
       <c r="H184" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I184" t="n">
         <v>1</v>
       </c>
       <c r="J184" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K184" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L184" t="n">
         <v>1</v>
       </c>
       <c r="M184" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="185">
@@ -8066,13 +8182,13 @@
         <v>0</v>
       </c>
       <c r="J188" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K188" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L188" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M188" t="n">
         <v>1</v>
@@ -8148,10 +8264,10 @@
         <v>0</v>
       </c>
       <c r="J190" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K190" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L190" t="n">
         <v>0</v>
@@ -8177,10 +8293,10 @@
         <v>0</v>
       </c>
       <c r="F191" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G191" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H191" t="n">
         <v>0</v>
@@ -8209,7 +8325,7 @@
       </c>
       <c r="B192" t="inlineStr"/>
       <c r="C192" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D192" t="n">
         <v>0</v>
@@ -8227,19 +8343,19 @@
         <v>0</v>
       </c>
       <c r="I192" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J192" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K192" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L192" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M192" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="193">
@@ -8248,22 +8364,40 @@
           <t>理財投資</t>
         </is>
       </c>
-      <c r="B193" t="n">
-        <v>0</v>
-      </c>
+      <c r="B193" t="inlineStr"/>
       <c r="C193" t="n">
         <v>0</v>
       </c>
-      <c r="D193" t="inlineStr"/>
-      <c r="E193" t="inlineStr"/>
-      <c r="F193" t="inlineStr"/>
-      <c r="G193" t="inlineStr"/>
-      <c r="H193" t="inlineStr"/>
-      <c r="I193" t="inlineStr"/>
-      <c r="J193" t="inlineStr"/>
-      <c r="K193" t="inlineStr"/>
-      <c r="L193" t="inlineStr"/>
-      <c r="M193" t="inlineStr"/>
+      <c r="D193" t="n">
+        <v>0</v>
+      </c>
+      <c r="E193" t="n">
+        <v>0</v>
+      </c>
+      <c r="F193" t="n">
+        <v>0</v>
+      </c>
+      <c r="G193" t="n">
+        <v>0</v>
+      </c>
+      <c r="H193" t="n">
+        <v>0</v>
+      </c>
+      <c r="I193" t="n">
+        <v>0</v>
+      </c>
+      <c r="J193" t="n">
+        <v>0</v>
+      </c>
+      <c r="K193" t="n">
+        <v>0</v>
+      </c>
+      <c r="L193" t="n">
+        <v>0</v>
+      </c>
+      <c r="M193" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="194">
       <c r="A194" s="1" t="inlineStr">
@@ -8276,19 +8410,19 @@
         <v>1</v>
       </c>
       <c r="D194" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E194" t="n">
         <v>0</v>
       </c>
       <c r="F194" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G194" t="n">
         <v>1</v>
       </c>
       <c r="H194" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I194" t="n">
         <v>0</v>
@@ -8335,13 +8469,13 @@
         <v>0</v>
       </c>
       <c r="J195" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K195" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L195" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M195" t="n">
         <v>0</v>
@@ -8355,7 +8489,7 @@
       </c>
       <c r="B196" t="inlineStr"/>
       <c r="C196" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D196" t="n">
         <v>0</v>
@@ -8364,7 +8498,7 @@
         <v>0</v>
       </c>
       <c r="F196" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G196" t="n">
         <v>1</v>
@@ -8376,16 +8510,16 @@
         <v>1</v>
       </c>
       <c r="J196" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K196" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L196" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M196" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="197">
@@ -8394,39 +8528,41 @@
           <t>生產製程及檢測設備</t>
         </is>
       </c>
-      <c r="B197" t="inlineStr"/>
+      <c r="B197" t="n">
+        <v>0</v>
+      </c>
       <c r="C197" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D197" t="n">
+        <v>0</v>
+      </c>
+      <c r="E197" t="n">
+        <v>1</v>
+      </c>
+      <c r="F197" t="n">
         <v>4</v>
       </c>
-      <c r="E197" t="n">
-        <v>0</v>
-      </c>
-      <c r="F197" t="n">
-        <v>1</v>
-      </c>
       <c r="G197" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H197" t="n">
+        <v>3</v>
+      </c>
+      <c r="I197" t="n">
+        <v>5</v>
+      </c>
+      <c r="J197" t="n">
+        <v>1</v>
+      </c>
+      <c r="K197" t="n">
+        <v>6</v>
+      </c>
+      <c r="L197" t="n">
         <v>2</v>
       </c>
-      <c r="I197" t="n">
-        <v>3</v>
-      </c>
-      <c r="J197" t="n">
-        <v>5</v>
-      </c>
-      <c r="K197" t="n">
-        <v>1</v>
-      </c>
-      <c r="L197" t="n">
-        <v>6</v>
-      </c>
       <c r="M197" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="198">
@@ -8575,7 +8711,7 @@
         <v>0</v>
       </c>
       <c r="H201" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I201" t="n">
         <v>0</v>
@@ -8619,10 +8755,10 @@
         <v>0</v>
       </c>
       <c r="I202" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J202" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K202" t="n">
         <v>0</v>
@@ -8651,10 +8787,10 @@
         <v>0</v>
       </c>
       <c r="F203" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G203" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H203" t="n">
         <v>0</v>
@@ -8663,13 +8799,13 @@
         <v>0</v>
       </c>
       <c r="J203" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K203" t="n">
         <v>1</v>
       </c>
       <c r="L203" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M203" t="n">
         <v>0</v>
@@ -8686,7 +8822,7 @@
         <v>0</v>
       </c>
       <c r="D204" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E204" t="n">
         <v>1</v>
@@ -8695,7 +8831,7 @@
         <v>1</v>
       </c>
       <c r="G204" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H204" t="n">
         <v>0</v>
@@ -8707,13 +8843,13 @@
         <v>0</v>
       </c>
       <c r="K204" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L204" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M204" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="205">
@@ -8727,7 +8863,7 @@
         <v>0</v>
       </c>
       <c r="D205" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E205" t="n">
         <v>1</v>
@@ -8736,7 +8872,7 @@
         <v>1</v>
       </c>
       <c r="G205" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H205" t="n">
         <v>0</v>
@@ -8745,13 +8881,13 @@
         <v>0</v>
       </c>
       <c r="J205" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K205" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L205" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M205" t="n">
         <v>0</v>
@@ -8833,7 +8969,7 @@
         <v>0</v>
       </c>
       <c r="L207" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M207" t="n">
         <v>1</v>
@@ -8847,37 +8983,37 @@
       </c>
       <c r="B208" t="inlineStr"/>
       <c r="C208" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D208" t="n">
+        <v>1</v>
+      </c>
+      <c r="E208" t="n">
+        <v>0</v>
+      </c>
+      <c r="F208" t="n">
+        <v>2</v>
+      </c>
+      <c r="G208" t="n">
+        <v>1</v>
+      </c>
+      <c r="H208" t="n">
+        <v>3</v>
+      </c>
+      <c r="I208" t="n">
+        <v>2</v>
+      </c>
+      <c r="J208" t="n">
         <v>5</v>
-      </c>
-      <c r="E208" t="n">
-        <v>1</v>
-      </c>
-      <c r="F208" t="n">
-        <v>0</v>
-      </c>
-      <c r="G208" t="n">
-        <v>2</v>
-      </c>
-      <c r="H208" t="n">
-        <v>1</v>
-      </c>
-      <c r="I208" t="n">
-        <v>3</v>
-      </c>
-      <c r="J208" t="n">
-        <v>2</v>
       </c>
       <c r="K208" t="n">
         <v>5</v>
       </c>
       <c r="L208" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M208" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="209">
@@ -8906,13 +9042,13 @@
         <v>0</v>
       </c>
       <c r="I209" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J209" t="n">
         <v>1</v>
       </c>
       <c r="K209" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L209" t="n">
         <v>0</v>
@@ -8950,10 +9086,10 @@
         <v>0</v>
       </c>
       <c r="J210" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K210" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L210" t="n">
         <v>0</v>
@@ -8985,19 +9121,19 @@
         <v>0</v>
       </c>
       <c r="H211" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I211" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J211" t="n">
         <v>2</v>
       </c>
       <c r="K211" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L211" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M211" t="n">
         <v>0</v>
@@ -9196,10 +9332,10 @@
         <v>0</v>
       </c>
       <c r="J216" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K216" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L216" t="n">
         <v>0</v>
@@ -9231,19 +9367,19 @@
         <v>0</v>
       </c>
       <c r="H217" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I217" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J217" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K217" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L217" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M217" t="n">
         <v>1</v>
@@ -9269,25 +9405,25 @@
         <v>0</v>
       </c>
       <c r="G218" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H218" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I218" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J218" t="n">
         <v>1</v>
       </c>
       <c r="K218" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L218" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M218" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="219">
@@ -9316,19 +9452,19 @@
         <v>0</v>
       </c>
       <c r="I219" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J219" t="n">
         <v>1</v>
       </c>
       <c r="K219" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L219" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M219" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="220">
@@ -9348,28 +9484,28 @@
         <v>0</v>
       </c>
       <c r="F220" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G220" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H220" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I220" t="n">
+        <v>8</v>
+      </c>
+      <c r="J220" t="n">
+        <v>5</v>
+      </c>
+      <c r="K220" t="n">
         <v>3</v>
       </c>
-      <c r="J220" t="n">
-        <v>8</v>
-      </c>
-      <c r="K220" t="n">
-        <v>5</v>
-      </c>
       <c r="L220" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M220" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="221">
@@ -9382,37 +9518,37 @@
         <v>0</v>
       </c>
       <c r="C221" t="n">
+        <v>3</v>
+      </c>
+      <c r="D221" t="n">
+        <v>0</v>
+      </c>
+      <c r="E221" t="n">
+        <v>1</v>
+      </c>
+      <c r="F221" t="n">
+        <v>1</v>
+      </c>
+      <c r="G221" t="n">
+        <v>1</v>
+      </c>
+      <c r="H221" t="n">
         <v>2</v>
       </c>
-      <c r="D221" t="n">
-        <v>3</v>
-      </c>
-      <c r="E221" t="n">
-        <v>1</v>
-      </c>
-      <c r="F221" t="n">
-        <v>1</v>
-      </c>
-      <c r="G221" t="n">
-        <v>1</v>
-      </c>
-      <c r="H221" t="n">
-        <v>1</v>
-      </c>
       <c r="I221" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J221" t="n">
         <v>4</v>
       </c>
       <c r="K221" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L221" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M221" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="222">
@@ -9450,10 +9586,10 @@
         <v>0</v>
       </c>
       <c r="L222" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M222" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="223">
@@ -9462,9 +9598,7 @@
           <t>紡紗</t>
         </is>
       </c>
-      <c r="B223" t="n">
-        <v>0</v>
-      </c>
+      <c r="B223" t="inlineStr"/>
       <c r="C223" t="n">
         <v>0</v>
       </c>
@@ -9481,19 +9615,19 @@
         <v>0</v>
       </c>
       <c r="H223" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I223" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J223" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K223" t="n">
         <v>1</v>
       </c>
       <c r="L223" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M223" t="n">
         <v>0</v>
@@ -9604,7 +9738,7 @@
         <v>0</v>
       </c>
       <c r="H226" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I226" t="n">
         <v>0</v>
@@ -9613,10 +9747,10 @@
         <v>0</v>
       </c>
       <c r="K226" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L226" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M226" t="n">
         <v>0</v>
@@ -9648,13 +9782,13 @@
         <v>0</v>
       </c>
       <c r="I227" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J227" t="n">
         <v>1</v>
       </c>
       <c r="K227" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L227" t="n">
         <v>0</v>
@@ -9689,16 +9823,16 @@
         <v>0</v>
       </c>
       <c r="I228" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J228" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K228" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L228" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M228" t="n">
         <v>1</v>
@@ -9730,16 +9864,16 @@
         <v>0</v>
       </c>
       <c r="I229" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J229" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K229" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L229" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M229" t="n">
         <v>1</v>
@@ -9751,39 +9885,41 @@
           <t>網路設備(如數據機、網路卡、閘道器、路由器、網路電話)</t>
         </is>
       </c>
-      <c r="B230" t="inlineStr"/>
+      <c r="B230" t="n">
+        <v>0</v>
+      </c>
       <c r="C230" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D230" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E230" t="n">
         <v>1</v>
       </c>
       <c r="F230" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G230" t="n">
         <v>2</v>
       </c>
       <c r="H230" t="n">
+        <v>1</v>
+      </c>
+      <c r="I230" t="n">
         <v>2</v>
       </c>
-      <c r="I230" t="n">
-        <v>1</v>
-      </c>
       <c r="J230" t="n">
+        <v>6</v>
+      </c>
+      <c r="K230" t="n">
+        <v>1</v>
+      </c>
+      <c r="L230" t="n">
+        <v>1</v>
+      </c>
+      <c r="M230" t="n">
         <v>2</v>
-      </c>
-      <c r="K230" t="n">
-        <v>6</v>
-      </c>
-      <c r="L230" t="n">
-        <v>1</v>
-      </c>
-      <c r="M230" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="231">
@@ -9806,19 +9942,19 @@
         <v>0</v>
       </c>
       <c r="G231" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H231" t="n">
         <v>1</v>
       </c>
       <c r="I231" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J231" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K231" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L231" t="n">
         <v>1</v>
@@ -9865,7 +10001,7 @@
         <v>0</v>
       </c>
       <c r="M232" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="233">
@@ -9876,7 +10012,7 @@
       </c>
       <c r="B233" t="inlineStr"/>
       <c r="C233" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D233" t="n">
         <v>0</v>
@@ -9891,22 +10027,22 @@
         <v>0</v>
       </c>
       <c r="H233" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I233" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J233" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K233" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L233" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M233" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="234">
@@ -9956,9 +10092,7 @@
           <t>織布</t>
         </is>
       </c>
-      <c r="B235" t="n">
-        <v>0</v>
-      </c>
+      <c r="B235" t="inlineStr"/>
       <c r="C235" t="n">
         <v>0</v>
       </c>
@@ -9969,25 +10103,25 @@
         <v>0</v>
       </c>
       <c r="F235" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G235" t="n">
         <v>1</v>
       </c>
       <c r="H235" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I235" t="n">
         <v>0</v>
       </c>
       <c r="J235" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K235" t="n">
         <v>1</v>
       </c>
       <c r="L235" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M235" t="n">
         <v>0</v>
@@ -10025,10 +10159,10 @@
         <v>0</v>
       </c>
       <c r="K236" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L236" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M236" t="n">
         <v>0</v>
@@ -10081,7 +10215,9 @@
           <t>背光源(發光二極體、冷陰極管)</t>
         </is>
       </c>
-      <c r="B238" t="inlineStr"/>
+      <c r="B238" t="n">
+        <v>0</v>
+      </c>
       <c r="C238" t="n">
         <v>0</v>
       </c>
@@ -10101,19 +10237,19 @@
         <v>0</v>
       </c>
       <c r="I238" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J238" t="n">
         <v>1</v>
       </c>
       <c r="K238" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L238" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M238" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="239">
@@ -10127,7 +10263,7 @@
         <v>1</v>
       </c>
       <c r="D239" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E239" t="n">
         <v>0</v>
@@ -10145,16 +10281,16 @@
         <v>0</v>
       </c>
       <c r="J239" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K239" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L239" t="n">
         <v>0</v>
       </c>
       <c r="M239" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="240">
@@ -10189,10 +10325,10 @@
         <v>0</v>
       </c>
       <c r="K240" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L240" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M240" t="n">
         <v>0</v>
@@ -10385,16 +10521,16 @@
         <v>0</v>
       </c>
       <c r="H245" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I245" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J245" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K245" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L245" t="n">
         <v>0</v>
@@ -10432,16 +10568,16 @@
         <v>0</v>
       </c>
       <c r="J246" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K246" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L246" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M246" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="247">
@@ -10476,10 +10612,10 @@
         <v>0</v>
       </c>
       <c r="K247" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L247" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M247" t="n">
         <v>0</v>
@@ -10491,9 +10627,11 @@
           <t>藥品代理銷售及通路</t>
         </is>
       </c>
-      <c r="B248" t="inlineStr"/>
+      <c r="B248" t="n">
+        <v>0</v>
+      </c>
       <c r="C248" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D248" t="n">
         <v>0</v>
@@ -10505,13 +10643,13 @@
         <v>0</v>
       </c>
       <c r="G248" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H248" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I248" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J248" t="n">
         <v>0</v>
@@ -10543,19 +10681,19 @@
         <v>0</v>
       </c>
       <c r="F249" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G249" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H249" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I249" t="n">
         <v>1</v>
       </c>
       <c r="J249" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K249" t="n">
         <v>0</v>
@@ -10590,19 +10728,19 @@
         <v>0</v>
       </c>
       <c r="H250" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I250" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J250" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K250" t="n">
         <v>1</v>
       </c>
       <c r="L250" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M250" t="n">
         <v>0</v>
@@ -10678,16 +10816,16 @@
         <v>0</v>
       </c>
       <c r="J252" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K252" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L252" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M252" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="253">
@@ -10696,9 +10834,7 @@
           <t>行銷廣告服務</t>
         </is>
       </c>
-      <c r="B253" t="n">
-        <v>0</v>
-      </c>
+      <c r="B253" t="inlineStr"/>
       <c r="C253" t="n">
         <v>0</v>
       </c>
@@ -10812,7 +10948,7 @@
         <v>0</v>
       </c>
       <c r="M255" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="256">
@@ -10823,13 +10959,13 @@
       </c>
       <c r="B256" t="inlineStr"/>
       <c r="C256" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D256" t="n">
         <v>1</v>
       </c>
       <c r="E256" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F256" t="n">
         <v>0</v>
@@ -10838,10 +10974,10 @@
         <v>0</v>
       </c>
       <c r="H256" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I256" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J256" t="n">
         <v>0</v>
@@ -10967,13 +11103,13 @@
         <v>0</v>
       </c>
       <c r="J259" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K259" t="n">
         <v>1</v>
       </c>
       <c r="L259" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M259" t="n">
         <v>0</v>
@@ -10996,10 +11132,10 @@
         <v>0</v>
       </c>
       <c r="F260" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G260" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H260" t="n">
         <v>0</v>
@@ -11026,9 +11162,7 @@
           <t>觸控面板</t>
         </is>
       </c>
-      <c r="B261" t="n">
-        <v>0</v>
-      </c>
+      <c r="B261" t="inlineStr"/>
       <c r="C261" t="n">
         <v>0</v>
       </c>
@@ -11048,10 +11182,10 @@
         <v>0</v>
       </c>
       <c r="I261" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J261" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K261" t="n">
         <v>0</v>
@@ -11077,28 +11211,28 @@
         <v>0</v>
       </c>
       <c r="E262" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F262" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G262" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H262" t="n">
+        <v>8</v>
+      </c>
+      <c r="I262" t="n">
+        <v>2</v>
+      </c>
+      <c r="J262" t="n">
+        <v>4</v>
+      </c>
+      <c r="K262" t="n">
         <v>3</v>
       </c>
-      <c r="I262" t="n">
-        <v>9</v>
-      </c>
-      <c r="J262" t="n">
-        <v>2</v>
-      </c>
-      <c r="K262" t="n">
-        <v>4</v>
-      </c>
       <c r="L262" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M262" t="n">
         <v>0</v>
@@ -11127,7 +11261,7 @@
         <v>0</v>
       </c>
       <c r="H263" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I263" t="n">
         <v>1</v>
@@ -11136,10 +11270,10 @@
         <v>1</v>
       </c>
       <c r="K263" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L263" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M263" t="n">
         <v>0</v>
@@ -11168,22 +11302,22 @@
         <v>0</v>
       </c>
       <c r="H264" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I264" t="n">
         <v>1</v>
       </c>
       <c r="J264" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K264" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L264" t="n">
         <v>1</v>
       </c>
       <c r="M264" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="265">
@@ -11279,7 +11413,7 @@
         <v>1</v>
       </c>
       <c r="D267" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E267" t="n">
         <v>0</v>
@@ -11405,13 +11539,13 @@
         <v>1</v>
       </c>
       <c r="E270" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F270" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G270" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H270" t="n">
         <v>0</v>
@@ -11426,10 +11560,10 @@
         <v>0</v>
       </c>
       <c r="L270" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M270" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="271">
@@ -11442,16 +11576,36 @@
       <c r="C271" t="n">
         <v>0</v>
       </c>
-      <c r="D271" t="inlineStr"/>
-      <c r="E271" t="inlineStr"/>
-      <c r="F271" t="inlineStr"/>
-      <c r="G271" t="inlineStr"/>
-      <c r="H271" t="inlineStr"/>
-      <c r="I271" t="inlineStr"/>
-      <c r="J271" t="inlineStr"/>
-      <c r="K271" t="inlineStr"/>
-      <c r="L271" t="inlineStr"/>
-      <c r="M271" t="inlineStr"/>
+      <c r="D271" t="n">
+        <v>0</v>
+      </c>
+      <c r="E271" t="n">
+        <v>0</v>
+      </c>
+      <c r="F271" t="n">
+        <v>0</v>
+      </c>
+      <c r="G271" t="n">
+        <v>0</v>
+      </c>
+      <c r="H271" t="n">
+        <v>0</v>
+      </c>
+      <c r="I271" t="n">
+        <v>0</v>
+      </c>
+      <c r="J271" t="n">
+        <v>0</v>
+      </c>
+      <c r="K271" t="n">
+        <v>0</v>
+      </c>
+      <c r="L271" t="n">
+        <v>0</v>
+      </c>
+      <c r="M271" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="272">
       <c r="A272" s="1" t="inlineStr">
@@ -11482,13 +11636,13 @@
         <v>0</v>
       </c>
       <c r="J272" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K272" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L272" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M272" t="n">
         <v>1</v>
@@ -11520,19 +11674,19 @@
         <v>0</v>
       </c>
       <c r="I273" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J273" t="n">
         <v>1</v>
       </c>
       <c r="K273" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L273" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M273" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="274">
@@ -11561,16 +11715,16 @@
         <v>0</v>
       </c>
       <c r="I274" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J274" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K274" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L274" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M274" t="n">
         <v>1</v>
@@ -11599,22 +11753,22 @@
         <v>0</v>
       </c>
       <c r="H275" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I275" t="n">
         <v>1</v>
       </c>
       <c r="J275" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K275" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L275" t="n">
         <v>1</v>
       </c>
       <c r="M275" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="276">
@@ -11643,16 +11797,16 @@
         <v>0</v>
       </c>
       <c r="I276" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J276" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K276" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L276" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M276" t="n">
         <v>1</v>
@@ -11664,9 +11818,7 @@
           <t>資料分析處理服務</t>
         </is>
       </c>
-      <c r="B277" t="n">
-        <v>0</v>
-      </c>
+      <c r="B277" t="inlineStr"/>
       <c r="C277" t="n">
         <v>0</v>
       </c>
@@ -11721,10 +11873,10 @@
         <v>0</v>
       </c>
       <c r="G278" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H278" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I278" t="n">
         <v>1</v>
@@ -11739,7 +11891,7 @@
         <v>1</v>
       </c>
       <c r="M278" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="279">
@@ -11765,7 +11917,7 @@
         <v>0</v>
       </c>
       <c r="H279" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I279" t="n">
         <v>1</v>
@@ -11777,7 +11929,7 @@
         <v>1</v>
       </c>
       <c r="L279" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M279" t="n">
         <v>0</v>
@@ -11850,16 +12002,16 @@
         <v>0</v>
       </c>
       <c r="I281" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J281" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K281" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L281" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M281" t="n">
         <v>1</v>
@@ -11994,9 +12146,7 @@
           <t>資訊系統建置服務</t>
         </is>
       </c>
-      <c r="B285" t="n">
-        <v>0</v>
-      </c>
+      <c r="B285" t="inlineStr"/>
       <c r="C285" t="n">
         <v>0</v>
       </c>
@@ -12037,9 +12187,7 @@
           <t>資訊聚合</t>
         </is>
       </c>
-      <c r="B286" t="n">
-        <v>0</v>
-      </c>
+      <c r="B286" t="inlineStr"/>
       <c r="C286" t="n">
         <v>0</v>
       </c>
@@ -12094,16 +12242,16 @@
         <v>0</v>
       </c>
       <c r="G287" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H287" t="n">
         <v>1</v>
       </c>
       <c r="I287" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J287" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K287" t="n">
         <v>1</v>
@@ -12112,7 +12260,7 @@
         <v>1</v>
       </c>
       <c r="M287" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="288">
@@ -12123,28 +12271,28 @@
       </c>
       <c r="B288" t="inlineStr"/>
       <c r="C288" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D288" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E288" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F288" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G288" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H288" t="n">
         <v>0</v>
       </c>
       <c r="I288" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J288" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K288" t="n">
         <v>0</v>
@@ -12167,25 +12315,25 @@
         <v>2</v>
       </c>
       <c r="D289" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E289" t="n">
         <v>1</v>
       </c>
       <c r="F289" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G289" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H289" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I289" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J289" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K289" t="n">
         <v>0</v>
@@ -12308,10 +12456,10 @@
         <v>0</v>
       </c>
       <c r="J292" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K292" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L292" t="n">
         <v>0</v>
@@ -12381,19 +12529,19 @@
         <v>0</v>
       </c>
       <c r="G294" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H294" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I294" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J294" t="n">
         <v>1</v>
       </c>
       <c r="K294" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L294" t="n">
         <v>0</v>
@@ -12410,7 +12558,7 @@
       </c>
       <c r="B295" t="inlineStr"/>
       <c r="C295" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D295" t="n">
         <v>0</v>
@@ -12475,10 +12623,10 @@
         <v>0</v>
       </c>
       <c r="K296" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L296" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M296" t="n">
         <v>0</v>
@@ -12576,16 +12724,36 @@
       <c r="C299" t="n">
         <v>0</v>
       </c>
-      <c r="D299" t="inlineStr"/>
-      <c r="E299" t="inlineStr"/>
-      <c r="F299" t="inlineStr"/>
-      <c r="G299" t="inlineStr"/>
-      <c r="H299" t="inlineStr"/>
-      <c r="I299" t="inlineStr"/>
-      <c r="J299" t="inlineStr"/>
-      <c r="K299" t="inlineStr"/>
-      <c r="L299" t="inlineStr"/>
-      <c r="M299" t="inlineStr"/>
+      <c r="D299" t="n">
+        <v>0</v>
+      </c>
+      <c r="E299" t="n">
+        <v>0</v>
+      </c>
+      <c r="F299" t="n">
+        <v>0</v>
+      </c>
+      <c r="G299" t="n">
+        <v>0</v>
+      </c>
+      <c r="H299" t="n">
+        <v>0</v>
+      </c>
+      <c r="I299" t="n">
+        <v>0</v>
+      </c>
+      <c r="J299" t="n">
+        <v>0</v>
+      </c>
+      <c r="K299" t="n">
+        <v>0</v>
+      </c>
+      <c r="L299" t="n">
+        <v>0</v>
+      </c>
+      <c r="M299" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="300">
       <c r="A300" s="1" t="inlineStr">
@@ -12634,14 +12802,12 @@
           <t>通路經銷</t>
         </is>
       </c>
-      <c r="B301" t="n">
-        <v>0</v>
-      </c>
+      <c r="B301" t="inlineStr"/>
       <c r="C301" t="n">
         <v>1</v>
       </c>
       <c r="D301" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E301" t="n">
         <v>0</v>
@@ -12656,19 +12822,19 @@
         <v>0</v>
       </c>
       <c r="I301" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J301" t="n">
         <v>1</v>
       </c>
       <c r="K301" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L301" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M301" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="302">
@@ -12681,37 +12847,37 @@
         <v>0</v>
       </c>
       <c r="C302" t="n">
+        <v>1</v>
+      </c>
+      <c r="D302" t="n">
+        <v>0</v>
+      </c>
+      <c r="E302" t="n">
+        <v>0</v>
+      </c>
+      <c r="F302" t="n">
+        <v>1</v>
+      </c>
+      <c r="G302" t="n">
+        <v>0</v>
+      </c>
+      <c r="H302" t="n">
+        <v>1</v>
+      </c>
+      <c r="I302" t="n">
+        <v>0</v>
+      </c>
+      <c r="J302" t="n">
+        <v>1</v>
+      </c>
+      <c r="K302" t="n">
         <v>2</v>
       </c>
-      <c r="D302" t="n">
-        <v>1</v>
-      </c>
-      <c r="E302" t="n">
-        <v>0</v>
-      </c>
-      <c r="F302" t="n">
-        <v>0</v>
-      </c>
-      <c r="G302" t="n">
-        <v>1</v>
-      </c>
-      <c r="H302" t="n">
-        <v>1</v>
-      </c>
-      <c r="I302" t="n">
+      <c r="L302" t="n">
+        <v>1</v>
+      </c>
+      <c r="M302" t="n">
         <v>2</v>
-      </c>
-      <c r="J302" t="n">
-        <v>0</v>
-      </c>
-      <c r="K302" t="n">
-        <v>1</v>
-      </c>
-      <c r="L302" t="n">
-        <v>2</v>
-      </c>
-      <c r="M302" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="303">
@@ -12722,7 +12888,7 @@
       </c>
       <c r="B303" t="inlineStr"/>
       <c r="C303" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D303" t="n">
         <v>0</v>
@@ -12737,19 +12903,19 @@
         <v>0</v>
       </c>
       <c r="H303" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I303" t="n">
         <v>1</v>
       </c>
       <c r="J303" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K303" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L303" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M303" t="n">
         <v>1</v>
@@ -12901,7 +13067,7 @@
         <v>0</v>
       </c>
       <c r="H307" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I307" t="n">
         <v>1</v>
@@ -12913,7 +13079,7 @@
         <v>1</v>
       </c>
       <c r="L307" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M307" t="n">
         <v>0</v>
@@ -12927,13 +13093,13 @@
       </c>
       <c r="B308" t="inlineStr"/>
       <c r="C308" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D308" t="n">
         <v>1</v>
       </c>
       <c r="E308" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F308" t="n">
         <v>0</v>
@@ -12945,10 +13111,10 @@
         <v>0</v>
       </c>
       <c r="I308" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J308" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K308" t="n">
         <v>0</v>
@@ -13012,7 +13178,7 @@
         <v>1</v>
       </c>
       <c r="D310" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E310" t="n">
         <v>0</v>
@@ -13033,10 +13199,10 @@
         <v>0</v>
       </c>
       <c r="K310" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L310" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M310" t="n">
         <v>0</v>
@@ -13050,10 +13216,10 @@
       </c>
       <c r="B311" t="inlineStr"/>
       <c r="C311" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D311" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E311" t="n">
         <v>0</v>
@@ -13112,13 +13278,13 @@
         <v>0</v>
       </c>
       <c r="J312" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K312" t="n">
         <v>1</v>
       </c>
       <c r="L312" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M312" t="n">
         <v>0</v>
@@ -13130,9 +13296,11 @@
           <t>醫療器材代理銷售及通路</t>
         </is>
       </c>
-      <c r="B313" t="inlineStr"/>
+      <c r="B313" t="n">
+        <v>0</v>
+      </c>
       <c r="C313" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D313" t="n">
         <v>0</v>
@@ -13147,7 +13315,7 @@
         <v>0</v>
       </c>
       <c r="H313" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I313" t="n">
         <v>1</v>
@@ -13159,7 +13327,7 @@
         <v>1</v>
       </c>
       <c r="L313" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M313" t="n">
         <v>0</v>
@@ -13175,37 +13343,37 @@
         <v>0</v>
       </c>
       <c r="C314" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D314" t="n">
         <v>1</v>
       </c>
       <c r="E314" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F314" t="n">
         <v>0</v>
       </c>
       <c r="G314" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H314" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I314" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J314" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K314" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L314" t="n">
         <v>0</v>
       </c>
       <c r="M314" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="315">
@@ -13269,25 +13437,25 @@
         <v>0</v>
       </c>
       <c r="G316" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H316" t="n">
+        <v>0</v>
+      </c>
+      <c r="I316" t="n">
+        <v>1</v>
+      </c>
+      <c r="J316" t="n">
         <v>2</v>
       </c>
-      <c r="I316" t="n">
-        <v>0</v>
-      </c>
-      <c r="J316" t="n">
-        <v>1</v>
-      </c>
       <c r="K316" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L316" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M316" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="317">
@@ -13296,24 +13464,26 @@
           <t>金屬加工用機械</t>
         </is>
       </c>
-      <c r="B317" t="inlineStr"/>
+      <c r="B317" t="n">
+        <v>0</v>
+      </c>
       <c r="C317" t="n">
         <v>0</v>
       </c>
       <c r="D317" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E317" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F317" t="n">
         <v>0</v>
       </c>
       <c r="G317" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H317" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I317" t="n">
         <v>0</v>
@@ -13339,25 +13509,25 @@
       </c>
       <c r="B318" t="inlineStr"/>
       <c r="C318" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D318" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E318" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F318" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G318" t="n">
         <v>0</v>
       </c>
       <c r="H318" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I318" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J318" t="n">
         <v>0</v>
@@ -13369,7 +13539,7 @@
         <v>0</v>
       </c>
       <c r="M318" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="319">
@@ -13436,10 +13606,10 @@
         <v>0</v>
       </c>
       <c r="H320" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I320" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J320" t="n">
         <v>0</v>
@@ -13506,10 +13676,10 @@
         <v>0</v>
       </c>
       <c r="D322" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E322" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F322" t="n">
         <v>0</v>
@@ -13626,25 +13796,25 @@
       </c>
       <c r="B325" t="inlineStr"/>
       <c r="C325" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D325" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E325" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F325" t="n">
         <v>1</v>
       </c>
       <c r="G325" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H325" t="n">
         <v>0</v>
       </c>
       <c r="I325" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J325" t="n">
         <v>1</v>
@@ -13653,7 +13823,7 @@
         <v>1</v>
       </c>
       <c r="L325" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M325" t="n">
         <v>0</v>
@@ -13667,16 +13837,16 @@
       </c>
       <c r="B326" t="inlineStr"/>
       <c r="C326" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D326" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E326" t="n">
         <v>1</v>
       </c>
       <c r="F326" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G326" t="n">
         <v>0</v>
@@ -13688,13 +13858,13 @@
         <v>0</v>
       </c>
       <c r="J326" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K326" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L326" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M326" t="n">
         <v>0</v>
@@ -13717,10 +13887,10 @@
         <v>0</v>
       </c>
       <c r="F327" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G327" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H327" t="n">
         <v>0</v>
@@ -13735,10 +13905,10 @@
         <v>0</v>
       </c>
       <c r="L327" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M327" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="328">
@@ -13790,10 +13960,10 @@
       </c>
       <c r="B329" t="inlineStr"/>
       <c r="C329" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D329" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E329" t="n">
         <v>0</v>
@@ -13814,13 +13984,13 @@
         <v>0</v>
       </c>
       <c r="K329" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L329" t="n">
         <v>1</v>
       </c>
       <c r="M329" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="330">
@@ -13937,10 +14107,10 @@
         <v>0</v>
       </c>
       <c r="K332" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L332" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M332" t="n">
         <v>0</v>
@@ -13995,10 +14165,10 @@
       </c>
       <c r="B334" t="inlineStr"/>
       <c r="C334" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D334" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E334" t="n">
         <v>0</v>
@@ -14025,7 +14195,7 @@
         <v>0</v>
       </c>
       <c r="M334" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="335">
@@ -14038,16 +14208,36 @@
       <c r="C335" t="n">
         <v>0</v>
       </c>
-      <c r="D335" t="inlineStr"/>
-      <c r="E335" t="inlineStr"/>
-      <c r="F335" t="inlineStr"/>
-      <c r="G335" t="inlineStr"/>
-      <c r="H335" t="inlineStr"/>
-      <c r="I335" t="inlineStr"/>
-      <c r="J335" t="inlineStr"/>
-      <c r="K335" t="inlineStr"/>
-      <c r="L335" t="inlineStr"/>
-      <c r="M335" t="inlineStr"/>
+      <c r="D335" t="n">
+        <v>0</v>
+      </c>
+      <c r="E335" t="n">
+        <v>0</v>
+      </c>
+      <c r="F335" t="n">
+        <v>0</v>
+      </c>
+      <c r="G335" t="n">
+        <v>0</v>
+      </c>
+      <c r="H335" t="n">
+        <v>0</v>
+      </c>
+      <c r="I335" t="n">
+        <v>0</v>
+      </c>
+      <c r="J335" t="n">
+        <v>0</v>
+      </c>
+      <c r="K335" t="n">
+        <v>0</v>
+      </c>
+      <c r="L335" t="n">
+        <v>0</v>
+      </c>
+      <c r="M335" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="336">
       <c r="A336" s="1" t="inlineStr">
@@ -14078,10 +14268,10 @@
         <v>0</v>
       </c>
       <c r="J336" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K336" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L336" t="n">
         <v>0</v>
@@ -14104,28 +14294,28 @@
         <v>0</v>
       </c>
       <c r="E337" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F337" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G337" t="n">
         <v>2</v>
       </c>
       <c r="H337" t="n">
+        <v>4</v>
+      </c>
+      <c r="I337" t="n">
         <v>2</v>
       </c>
-      <c r="I337" t="n">
-        <v>4</v>
-      </c>
       <c r="J337" t="n">
+        <v>3</v>
+      </c>
+      <c r="K337" t="n">
         <v>2</v>
       </c>
-      <c r="K337" t="n">
-        <v>3</v>
-      </c>
       <c r="L337" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M337" t="n">
         <v>0</v>
@@ -14154,7 +14344,7 @@
         <v>0</v>
       </c>
       <c r="H338" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I338" t="n">
         <v>1</v>
@@ -14166,7 +14356,7 @@
         <v>1</v>
       </c>
       <c r="L338" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M338" t="n">
         <v>0</v>
@@ -14192,19 +14382,19 @@
         <v>0</v>
       </c>
       <c r="G339" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H339" t="n">
         <v>1</v>
       </c>
       <c r="I339" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J339" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K339" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L339" t="n">
         <v>1</v>
@@ -14236,22 +14426,22 @@
         <v>0</v>
       </c>
       <c r="H340" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I340" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J340" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K340" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L340" t="n">
         <v>1</v>
       </c>
       <c r="M340" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="341">
@@ -14277,22 +14467,22 @@
         <v>0</v>
       </c>
       <c r="H341" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I341" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J341" t="n">
         <v>2</v>
       </c>
       <c r="K341" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L341" t="n">
         <v>1</v>
       </c>
       <c r="M341" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="342">
@@ -14303,19 +14493,19 @@
       </c>
       <c r="B342" t="inlineStr"/>
       <c r="C342" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D342" t="n">
         <v>1</v>
       </c>
       <c r="E342" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F342" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G342" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H342" t="n">
         <v>0</v>
@@ -14347,7 +14537,7 @@
         <v>1</v>
       </c>
       <c r="D343" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E343" t="n">
         <v>0</v>
@@ -14359,16 +14549,16 @@
         <v>0</v>
       </c>
       <c r="H343" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I343" t="n">
         <v>1</v>
       </c>
       <c r="J343" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K343" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L343" t="n">
         <v>0</v>
@@ -14409,10 +14599,10 @@
         <v>0</v>
       </c>
       <c r="K344" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L344" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M344" t="n">
         <v>0</v>
@@ -14426,10 +14616,10 @@
       </c>
       <c r="B345" t="inlineStr"/>
       <c r="C345" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D345" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E345" t="n">
         <v>0</v>
@@ -14473,10 +14663,10 @@
         <v>0</v>
       </c>
       <c r="E346" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F346" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G346" t="n">
         <v>0</v>
@@ -14491,10 +14681,10 @@
         <v>0</v>
       </c>
       <c r="K346" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L346" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M346" t="n">
         <v>0</v>
@@ -14576,10 +14766,10 @@
         <v>0</v>
       </c>
       <c r="L348" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M348" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="349">
@@ -14672,28 +14862,28 @@
       </c>
       <c r="B351" t="inlineStr"/>
       <c r="C351" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D351" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E351" t="n">
         <v>1</v>
       </c>
       <c r="F351" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G351" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H351" t="n">
         <v>1</v>
       </c>
       <c r="I351" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J351" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K351" t="n">
         <v>1</v>
@@ -14713,37 +14903,37 @@
       </c>
       <c r="B352" t="inlineStr"/>
       <c r="C352" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D352" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E352" t="n">
         <v>0</v>
       </c>
       <c r="F352" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G352" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H352" t="n">
         <v>0</v>
       </c>
       <c r="I352" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J352" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K352" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="L352" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="M352" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="353">
@@ -14754,10 +14944,10 @@
       </c>
       <c r="B353" t="inlineStr"/>
       <c r="C353" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D353" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E353" t="n">
         <v>0</v>
@@ -14772,16 +14962,16 @@
         <v>0</v>
       </c>
       <c r="I353" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J353" t="n">
         <v>1</v>
       </c>
       <c r="K353" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L353" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M353" t="n">
         <v>0</v>
@@ -14793,41 +14983,39 @@
           <t>電感器</t>
         </is>
       </c>
-      <c r="B354" t="n">
-        <v>0</v>
-      </c>
+      <c r="B354" t="inlineStr"/>
       <c r="C354" t="n">
         <v>1</v>
       </c>
       <c r="D354" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E354" t="n">
         <v>0</v>
       </c>
       <c r="F354" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G354" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H354" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I354" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J354" t="n">
+        <v>2</v>
+      </c>
+      <c r="K354" t="n">
         <v>3</v>
       </c>
-      <c r="K354" t="n">
+      <c r="L354" t="n">
         <v>2</v>
       </c>
-      <c r="L354" t="n">
-        <v>3</v>
-      </c>
       <c r="M354" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="355">
@@ -14856,19 +15044,19 @@
         <v>0</v>
       </c>
       <c r="I355" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J355" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K355" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L355" t="n">
         <v>1</v>
       </c>
       <c r="M355" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="356">
@@ -14879,34 +15067,34 @@
       </c>
       <c r="B356" t="inlineStr"/>
       <c r="C356" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D356" t="n">
+        <v>0</v>
+      </c>
+      <c r="E356" t="n">
         <v>2</v>
-      </c>
-      <c r="E356" t="n">
-        <v>0</v>
       </c>
       <c r="F356" t="n">
         <v>2</v>
       </c>
       <c r="G356" t="n">
+        <v>0</v>
+      </c>
+      <c r="H356" t="n">
+        <v>1</v>
+      </c>
+      <c r="I356" t="n">
+        <v>0</v>
+      </c>
+      <c r="J356" t="n">
         <v>2</v>
       </c>
-      <c r="H356" t="n">
-        <v>0</v>
-      </c>
-      <c r="I356" t="n">
-        <v>1</v>
-      </c>
-      <c r="J356" t="n">
-        <v>0</v>
-      </c>
       <c r="K356" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L356" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M356" t="n">
         <v>0</v>
@@ -14926,10 +15114,10 @@
         <v>0</v>
       </c>
       <c r="E357" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F357" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G357" t="n">
         <v>0</v>
@@ -14938,13 +15126,13 @@
         <v>0</v>
       </c>
       <c r="I357" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J357" t="n">
         <v>1</v>
       </c>
       <c r="K357" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L357" t="n">
         <v>0</v>
@@ -14967,10 +15155,10 @@
         <v>0</v>
       </c>
       <c r="E358" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F358" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G358" t="n">
         <v>0</v>
@@ -15046,34 +15234,34 @@
         <v>1</v>
       </c>
       <c r="D360" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E360" t="n">
+        <v>0</v>
+      </c>
+      <c r="F360" t="n">
+        <v>1</v>
+      </c>
+      <c r="G360" t="n">
+        <v>1</v>
+      </c>
+      <c r="H360" t="n">
         <v>2</v>
       </c>
-      <c r="F360" t="n">
-        <v>0</v>
-      </c>
-      <c r="G360" t="n">
-        <v>1</v>
-      </c>
-      <c r="H360" t="n">
-        <v>1</v>
-      </c>
       <c r="I360" t="n">
+        <v>1</v>
+      </c>
+      <c r="J360" t="n">
         <v>2</v>
       </c>
-      <c r="J360" t="n">
-        <v>1</v>
-      </c>
       <c r="K360" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L360" t="n">
         <v>1</v>
       </c>
       <c r="M360" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="361">
@@ -15087,7 +15275,7 @@
         <v>1</v>
       </c>
       <c r="D361" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E361" t="n">
         <v>0</v>
@@ -15190,10 +15378,10 @@
         <v>0</v>
       </c>
       <c r="K363" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L363" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M363" t="n">
         <v>0</v>
@@ -15216,13 +15404,13 @@
         <v>0</v>
       </c>
       <c r="F364" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G364" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H364" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I364" t="n">
         <v>1</v>
@@ -15231,13 +15419,13 @@
         <v>1</v>
       </c>
       <c r="K364" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L364" t="n">
         <v>0</v>
       </c>
       <c r="M364" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="365">
@@ -15248,34 +15436,34 @@
       </c>
       <c r="B365" t="inlineStr"/>
       <c r="C365" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D365" t="n">
         <v>1</v>
       </c>
       <c r="E365" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F365" t="n">
         <v>0</v>
       </c>
       <c r="G365" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H365" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I365" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J365" t="n">
+        <v>1</v>
+      </c>
+      <c r="K365" t="n">
         <v>2</v>
       </c>
-      <c r="K365" t="n">
-        <v>1</v>
-      </c>
       <c r="L365" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M365" t="n">
         <v>0</v>
@@ -15369,14 +15557,12 @@
           <t>電阻器</t>
         </is>
       </c>
-      <c r="B368" t="n">
-        <v>0</v>
-      </c>
+      <c r="B368" t="inlineStr"/>
       <c r="C368" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D368" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E368" t="n">
         <v>0</v>
@@ -15391,16 +15577,16 @@
         <v>0</v>
       </c>
       <c r="I368" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J368" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K368" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L368" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M368" t="n">
         <v>0</v>
@@ -15414,7 +15600,7 @@
       </c>
       <c r="B369" t="inlineStr"/>
       <c r="C369" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D369" t="n">
         <v>0</v>
@@ -15432,13 +15618,13 @@
         <v>0</v>
       </c>
       <c r="I369" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J369" t="n">
         <v>1</v>
       </c>
       <c r="K369" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L369" t="n">
         <v>0</v>
@@ -15453,9 +15639,7 @@
           <t>面板</t>
         </is>
       </c>
-      <c r="B370" t="n">
-        <v>0</v>
-      </c>
+      <c r="B370" t="inlineStr"/>
       <c r="C370" t="n">
         <v>0</v>
       </c>
@@ -15475,13 +15659,13 @@
         <v>0</v>
       </c>
       <c r="I370" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J370" t="n">
         <v>1</v>
       </c>
       <c r="K370" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L370" t="n">
         <v>0</v>
@@ -15496,7 +15680,9 @@
           <t>預拌混凝土</t>
         </is>
       </c>
-      <c r="B371" t="inlineStr"/>
+      <c r="B371" t="n">
+        <v>0</v>
+      </c>
       <c r="C371" t="n">
         <v>0</v>
       </c>
@@ -15541,16 +15727,36 @@
       <c r="C372" t="n">
         <v>0</v>
       </c>
-      <c r="D372" t="inlineStr"/>
-      <c r="E372" t="inlineStr"/>
-      <c r="F372" t="inlineStr"/>
-      <c r="G372" t="inlineStr"/>
-      <c r="H372" t="inlineStr"/>
-      <c r="I372" t="inlineStr"/>
-      <c r="J372" t="inlineStr"/>
-      <c r="K372" t="inlineStr"/>
-      <c r="L372" t="inlineStr"/>
-      <c r="M372" t="inlineStr"/>
+      <c r="D372" t="n">
+        <v>0</v>
+      </c>
+      <c r="E372" t="n">
+        <v>0</v>
+      </c>
+      <c r="F372" t="n">
+        <v>0</v>
+      </c>
+      <c r="G372" t="n">
+        <v>0</v>
+      </c>
+      <c r="H372" t="n">
+        <v>0</v>
+      </c>
+      <c r="I372" t="n">
+        <v>0</v>
+      </c>
+      <c r="J372" t="n">
+        <v>0</v>
+      </c>
+      <c r="K372" t="n">
+        <v>0</v>
+      </c>
+      <c r="L372" t="n">
+        <v>0</v>
+      </c>
+      <c r="M372" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="373">
       <c r="A373" s="1" t="inlineStr">
@@ -15569,22 +15775,22 @@
         <v>0</v>
       </c>
       <c r="F373" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G373" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H373" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I373" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J373" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K373" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L373" t="n">
         <v>1</v>
@@ -15610,13 +15816,13 @@
         <v>0</v>
       </c>
       <c r="F374" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G374" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H374" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I374" t="n">
         <v>1</v>
@@ -15625,7 +15831,7 @@
         <v>1</v>
       </c>
       <c r="K374" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L374" t="n">
         <v>0</v>
@@ -15648,10 +15854,10 @@
         <v>0</v>
       </c>
       <c r="E375" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F375" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G375" t="n">
         <v>0</v>
@@ -15666,10 +15872,10 @@
         <v>0</v>
       </c>
       <c r="K375" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L375" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M375" t="n">
         <v>0</v>
@@ -15698,22 +15904,22 @@
         <v>0</v>
       </c>
       <c r="H376" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I376" t="n">
+        <v>5</v>
+      </c>
+      <c r="J376" t="n">
+        <v>4</v>
+      </c>
+      <c r="K376" t="n">
+        <v>3</v>
+      </c>
+      <c r="L376" t="n">
         <v>2</v>
       </c>
-      <c r="J376" t="n">
-        <v>5</v>
-      </c>
-      <c r="K376" t="n">
-        <v>4</v>
-      </c>
-      <c r="L376" t="n">
-        <v>3</v>
-      </c>
       <c r="M376" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="377">
@@ -15736,19 +15942,19 @@
         <v>0</v>
       </c>
       <c r="G377" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H377" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I377" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J377" t="n">
         <v>1</v>
       </c>
       <c r="K377" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L377" t="n">
         <v>0</v>
@@ -15782,16 +15988,16 @@
         <v>0</v>
       </c>
       <c r="H378" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I378" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J378" t="n">
         <v>2</v>
       </c>
       <c r="K378" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L378" t="n">
         <v>0</v>
@@ -15972,19 +16178,19 @@
       </c>
       <c r="B383" t="inlineStr"/>
       <c r="C383" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D383" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E383" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F383" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G383" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H383" t="n">
         <v>0</v>
@@ -15993,16 +16199,16 @@
         <v>0</v>
       </c>
       <c r="J383" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K383" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L383" t="n">
         <v>0</v>
       </c>
       <c r="M383" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="384">
@@ -16057,7 +16263,7 @@
         <v>2</v>
       </c>
       <c r="D385" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E385" t="n">
         <v>0</v>
@@ -16075,13 +16281,13 @@
         <v>0</v>
       </c>
       <c r="J385" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K385" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L385" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M385" t="n">
         <v>0</v>

--- a/Result/analyze_3.xlsx
+++ b/Result/analyze_3.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M388"/>
+  <dimension ref="A1:M387"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -682,7 +682,7 @@
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I6" t="n">
         <v>1</v>
@@ -809,13 +809,13 @@
         <v>1</v>
       </c>
       <c r="H9" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I9" t="n">
+        <v>4</v>
+      </c>
+      <c r="J9" t="n">
         <v>3</v>
-      </c>
-      <c r="J9" t="n">
-        <v>2</v>
       </c>
       <c r="K9" t="n">
         <v>2</v>
@@ -833,7 +833,9 @@
           <t>IC通路</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
+      <c r="B10" t="n">
+        <v>0</v>
+      </c>
       <c r="C10" t="n">
         <v>0</v>
       </c>
@@ -853,7 +855,7 @@
         <v>4</v>
       </c>
       <c r="I10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J10" t="n">
         <v>2</v>
@@ -1298,10 +1300,10 @@
         <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
@@ -1366,9 +1368,7 @@
           <t>中藥材、西藥原料藥</t>
         </is>
       </c>
-      <c r="B23" t="n">
-        <v>0</v>
-      </c>
+      <c r="B23" t="inlineStr"/>
       <c r="C23" t="n">
         <v>0</v>
       </c>
@@ -1778,7 +1778,9 @@
           <t>伺服器</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr"/>
+      <c r="B33" t="n">
+        <v>0</v>
+      </c>
       <c r="C33" t="n">
         <v>2</v>
       </c>
@@ -1860,9 +1862,7 @@
           <t>保健食品代理銷售及通路</t>
         </is>
       </c>
-      <c r="B35" t="n">
-        <v>0</v>
-      </c>
+      <c r="B35" t="inlineStr"/>
       <c r="C35" t="n">
         <v>0</v>
       </c>
@@ -1876,10 +1876,10 @@
         <v>0</v>
       </c>
       <c r="G35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H35" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I35" t="n">
         <v>0</v>
@@ -2436,9 +2436,7 @@
           <t>光通訊設備(如光纖電纜、光傳輸設備)</t>
         </is>
       </c>
-      <c r="B49" t="n">
-        <v>0</v>
-      </c>
+      <c r="B49" t="inlineStr"/>
       <c r="C49" t="n">
         <v>3</v>
       </c>
@@ -2520,7 +2518,9 @@
           <t>其他</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr"/>
+      <c r="B51" t="n">
+        <v>0</v>
+      </c>
       <c r="C51" t="n">
         <v>6</v>
       </c>
@@ -2531,7 +2531,7 @@
         <v>3</v>
       </c>
       <c r="F51" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G51" t="n">
         <v>3</v>
@@ -2602,7 +2602,9 @@
           <t>其他零組件</t>
         </is>
       </c>
-      <c r="B53" t="inlineStr"/>
+      <c r="B53" t="n">
+        <v>0</v>
+      </c>
       <c r="C53" t="n">
         <v>0</v>
       </c>
@@ -2628,7 +2630,7 @@
         <v>1</v>
       </c>
       <c r="K53" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L53" t="n">
         <v>2</v>
@@ -2643,7 +2645,9 @@
           <t>其他電子產品及電子服務產業</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr"/>
+      <c r="B54" t="n">
+        <v>0</v>
+      </c>
       <c r="C54" t="n">
         <v>6</v>
       </c>
@@ -3014,7 +3018,9 @@
           <t>分析工具</t>
         </is>
       </c>
-      <c r="B63" t="inlineStr"/>
+      <c r="B63" t="n">
+        <v>0</v>
+      </c>
       <c r="C63" t="n">
         <v>0</v>
       </c>
@@ -3875,9 +3881,7 @@
           <t>基礎工程</t>
         </is>
       </c>
-      <c r="B84" t="n">
-        <v>0</v>
-      </c>
+      <c r="B84" t="inlineStr"/>
       <c r="C84" t="n">
         <v>0</v>
       </c>
@@ -4205,9 +4209,11 @@
           <t>大功率鋰電池芯/模組、電池管理系統、動力馬達等零組件</t>
         </is>
       </c>
-      <c r="B92" t="inlineStr"/>
+      <c r="B92" t="n">
+        <v>0</v>
+      </c>
       <c r="C92" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D92" t="n">
         <v>0</v>
@@ -4231,7 +4237,7 @@
         <v>0</v>
       </c>
       <c r="K92" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L92" t="n">
         <v>0</v>
@@ -4328,7 +4334,9 @@
           <t>太陽能發電設備/系統及系統工程</t>
         </is>
       </c>
-      <c r="B95" t="inlineStr"/>
+      <c r="B95" t="n">
+        <v>0</v>
+      </c>
       <c r="C95" t="n">
         <v>0</v>
       </c>
@@ -4451,7 +4459,9 @@
           <t>太陽能電池模組</t>
         </is>
       </c>
-      <c r="B98" t="inlineStr"/>
+      <c r="B98" t="n">
+        <v>0</v>
+      </c>
       <c r="C98" t="n">
         <v>1</v>
       </c>
@@ -4492,9 +4502,7 @@
           <t>娛樂服務業</t>
         </is>
       </c>
-      <c r="B99" t="n">
-        <v>0</v>
-      </c>
+      <c r="B99" t="inlineStr"/>
       <c r="C99" t="n">
         <v>0</v>
       </c>
@@ -4646,7 +4654,7 @@
         <v>1</v>
       </c>
       <c r="L102" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M102" t="n">
         <v>0</v>
@@ -4699,7 +4707,9 @@
           <t>封裝/模組</t>
         </is>
       </c>
-      <c r="B104" t="inlineStr"/>
+      <c r="B104" t="n">
+        <v>0</v>
+      </c>
       <c r="C104" t="n">
         <v>0</v>
       </c>
@@ -4740,9 +4750,7 @@
           <t>專用機械(如紡織成衣生產用機械、食品飲料生產用機械、農林用機械等)</t>
         </is>
       </c>
-      <c r="B105" t="n">
-        <v>0</v>
-      </c>
+      <c r="B105" t="inlineStr"/>
       <c r="C105" t="n">
         <v>1</v>
       </c>
@@ -4794,7 +4802,7 @@
         <v>0</v>
       </c>
       <c r="F106" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G106" t="n">
         <v>0</v>
@@ -4809,7 +4817,7 @@
         <v>1</v>
       </c>
       <c r="K106" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L106" t="n">
         <v>0</v>
@@ -5357,9 +5365,7 @@
           <t>建材原料</t>
         </is>
       </c>
-      <c r="B120" t="n">
-        <v>0</v>
-      </c>
+      <c r="B120" t="inlineStr"/>
       <c r="C120" t="n">
         <v>1</v>
       </c>
@@ -5694,7 +5700,7 @@
         <v>0</v>
       </c>
       <c r="D128" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E128" t="n">
         <v>0</v>
@@ -5730,7 +5736,9 @@
           <t>應用軟體</t>
         </is>
       </c>
-      <c r="B129" t="inlineStr"/>
+      <c r="B129" t="n">
+        <v>0</v>
+      </c>
       <c r="C129" t="n">
         <v>0</v>
       </c>
@@ -6181,9 +6189,7 @@
           <t>散裝航運</t>
         </is>
       </c>
-      <c r="B140" t="n">
-        <v>0</v>
-      </c>
+      <c r="B140" t="inlineStr"/>
       <c r="C140" t="n">
         <v>0</v>
       </c>
@@ -6634,9 +6640,7 @@
           <t>旅館服務業</t>
         </is>
       </c>
-      <c r="B151" t="n">
-        <v>0</v>
-      </c>
+      <c r="B151" t="inlineStr"/>
       <c r="C151" t="n">
         <v>0</v>
       </c>
@@ -6759,7 +6763,9 @@
           <t>有線通訊設備(如電話機、傳真機)</t>
         </is>
       </c>
-      <c r="B154" t="inlineStr"/>
+      <c r="B154" t="n">
+        <v>0</v>
+      </c>
       <c r="C154" t="n">
         <v>1</v>
       </c>
@@ -6923,7 +6929,9 @@
           <t>桌上型電腦</t>
         </is>
       </c>
-      <c r="B158" t="inlineStr"/>
+      <c r="B158" t="n">
+        <v>0</v>
+      </c>
       <c r="C158" t="n">
         <v>0</v>
       </c>
@@ -7087,7 +7095,9 @@
           <t>機器學習</t>
         </is>
       </c>
-      <c r="B162" t="inlineStr"/>
+      <c r="B162" t="n">
+        <v>0</v>
+      </c>
       <c r="C162" t="n">
         <v>0</v>
       </c>
@@ -7210,9 +7220,7 @@
           <t>機殼</t>
         </is>
       </c>
-      <c r="B165" t="n">
-        <v>0</v>
-      </c>
+      <c r="B165" t="inlineStr"/>
       <c r="C165" t="n">
         <v>0</v>
       </c>
@@ -7294,9 +7302,11 @@
           <t>機電系統工程</t>
         </is>
       </c>
-      <c r="B167" t="inlineStr"/>
+      <c r="B167" t="n">
+        <v>0</v>
+      </c>
       <c r="C167" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D167" t="n">
         <v>0</v>
@@ -7581,7 +7591,9 @@
           <t>海陸空大眾運輸</t>
         </is>
       </c>
-      <c r="B174" t="inlineStr"/>
+      <c r="B174" t="n">
+        <v>0</v>
+      </c>
       <c r="C174" t="n">
         <v>0</v>
       </c>
@@ -7786,9 +7798,7 @@
           <t>無線通訊設備(如行動電話、衛星定位系統、衛星通訊設備、微波通訊設備、數位機上盒)</t>
         </is>
       </c>
-      <c r="B179" t="n">
-        <v>0</v>
-      </c>
+      <c r="B179" t="inlineStr"/>
       <c r="C179" t="n">
         <v>2</v>
       </c>
@@ -7870,9 +7880,7 @@
           <t>燈具/應用</t>
         </is>
       </c>
-      <c r="B181" t="n">
-        <v>0</v>
-      </c>
+      <c r="B181" t="inlineStr"/>
       <c r="C181" t="n">
         <v>0</v>
       </c>
@@ -7995,7 +8003,9 @@
           <t>營運管理軟體</t>
         </is>
       </c>
-      <c r="B184" t="inlineStr"/>
+      <c r="B184" t="n">
+        <v>0</v>
+      </c>
       <c r="C184" t="n">
         <v>0</v>
       </c>
@@ -8405,7 +8415,9 @@
           <t>環保潔能服務產業</t>
         </is>
       </c>
-      <c r="B194" t="inlineStr"/>
+      <c r="B194" t="n">
+        <v>0</v>
+      </c>
       <c r="C194" t="n">
         <v>1</v>
       </c>
@@ -8487,7 +8499,9 @@
           <t>生產製程、檢測設備及原物料</t>
         </is>
       </c>
-      <c r="B196" t="inlineStr"/>
+      <c r="B196" t="n">
+        <v>0</v>
+      </c>
       <c r="C196" t="n">
         <v>0</v>
       </c>
@@ -9391,7 +9405,9 @@
           <t>筆記型電腦</t>
         </is>
       </c>
-      <c r="B218" t="inlineStr"/>
+      <c r="B218" t="n">
+        <v>0</v>
+      </c>
       <c r="C218" t="n">
         <v>0</v>
       </c>
@@ -9473,7 +9489,9 @@
           <t>系統整合</t>
         </is>
       </c>
-      <c r="B220" t="inlineStr"/>
+      <c r="B220" t="n">
+        <v>0</v>
+      </c>
       <c r="C220" t="n">
         <v>0</v>
       </c>
@@ -9521,7 +9539,7 @@
         <v>3</v>
       </c>
       <c r="D221" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E221" t="n">
         <v>1</v>
@@ -10215,9 +10233,7 @@
           <t>背光源(發光二極體、冷陰極管)</t>
         </is>
       </c>
-      <c r="B238" t="n">
-        <v>0</v>
-      </c>
+      <c r="B238" t="inlineStr"/>
       <c r="C238" t="n">
         <v>0</v>
       </c>
@@ -10340,7 +10356,9 @@
           <t>臨床實驗、移植技術、疾病治療</t>
         </is>
       </c>
-      <c r="B241" t="inlineStr"/>
+      <c r="B241" t="n">
+        <v>0</v>
+      </c>
       <c r="C241" t="n">
         <v>0</v>
       </c>
@@ -10545,7 +10563,9 @@
           <t>自然語言處理</t>
         </is>
       </c>
-      <c r="B246" t="inlineStr"/>
+      <c r="B246" t="n">
+        <v>0</v>
+      </c>
       <c r="C246" t="n">
         <v>0</v>
       </c>
@@ -10627,9 +10647,7 @@
           <t>藥品代理銷售及通路</t>
         </is>
       </c>
-      <c r="B248" t="n">
-        <v>0</v>
-      </c>
+      <c r="B248" t="inlineStr"/>
       <c r="C248" t="n">
         <v>0</v>
       </c>
@@ -10643,10 +10661,10 @@
         <v>0</v>
       </c>
       <c r="G248" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H248" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I248" t="n">
         <v>0</v>
@@ -10711,7 +10729,9 @@
           <t>虛擬化軟體</t>
         </is>
       </c>
-      <c r="B250" t="inlineStr"/>
+      <c r="B250" t="n">
+        <v>0</v>
+      </c>
       <c r="C250" t="n">
         <v>0</v>
       </c>
@@ -11220,7 +11240,7 @@
         <v>3</v>
       </c>
       <c r="H262" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I262" t="n">
         <v>2</v>
@@ -11244,7 +11264,9 @@
           <t>設備安裝服務</t>
         </is>
       </c>
-      <c r="B263" t="inlineStr"/>
+      <c r="B263" t="n">
+        <v>0</v>
+      </c>
       <c r="C263" t="n">
         <v>0</v>
       </c>
@@ -11285,7 +11307,9 @@
           <t>設備管理軟體</t>
         </is>
       </c>
-      <c r="B264" t="inlineStr"/>
+      <c r="B264" t="n">
+        <v>0</v>
+      </c>
       <c r="C264" t="n">
         <v>0</v>
       </c>
@@ -11323,7 +11347,7 @@
     <row r="265">
       <c r="A265" s="1" t="inlineStr">
         <is>
-          <t>設備維護</t>
+          <t>證券業</t>
         </is>
       </c>
       <c r="B265" t="inlineStr"/>
@@ -11364,53 +11388,33 @@
     <row r="266">
       <c r="A266" s="1" t="inlineStr">
         <is>
-          <t>證券業</t>
-        </is>
-      </c>
-      <c r="B266" t="inlineStr"/>
-      <c r="C266" t="n">
-        <v>0</v>
-      </c>
-      <c r="D266" t="n">
-        <v>0</v>
-      </c>
-      <c r="E266" t="n">
-        <v>0</v>
-      </c>
-      <c r="F266" t="n">
-        <v>0</v>
-      </c>
-      <c r="G266" t="n">
-        <v>0</v>
-      </c>
-      <c r="H266" t="n">
-        <v>0</v>
-      </c>
-      <c r="I266" t="n">
-        <v>0</v>
-      </c>
-      <c r="J266" t="n">
-        <v>0</v>
-      </c>
-      <c r="K266" t="n">
-        <v>0</v>
-      </c>
-      <c r="L266" t="n">
-        <v>0</v>
-      </c>
-      <c r="M266" t="n">
-        <v>0</v>
-      </c>
+          <t>變壓器</t>
+        </is>
+      </c>
+      <c r="B266" t="n">
+        <v>0</v>
+      </c>
+      <c r="C266" t="inlineStr"/>
+      <c r="D266" t="inlineStr"/>
+      <c r="E266" t="inlineStr"/>
+      <c r="F266" t="inlineStr"/>
+      <c r="G266" t="inlineStr"/>
+      <c r="H266" t="inlineStr"/>
+      <c r="I266" t="inlineStr"/>
+      <c r="J266" t="inlineStr"/>
+      <c r="K266" t="inlineStr"/>
+      <c r="L266" t="inlineStr"/>
+      <c r="M266" t="inlineStr"/>
     </row>
     <row r="267">
       <c r="A267" s="1" t="inlineStr">
         <is>
-          <t>變壓器</t>
+          <t>貨櫃航運</t>
         </is>
       </c>
       <c r="B267" t="inlineStr"/>
       <c r="C267" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D267" t="n">
         <v>0</v>
@@ -11446,7 +11450,7 @@
     <row r="268">
       <c r="A268" s="1" t="inlineStr">
         <is>
-          <t>貨櫃航運</t>
+          <t>貨櫃運輸集散及倉儲</t>
         </is>
       </c>
       <c r="B268" t="inlineStr"/>
@@ -11487,21 +11491,21 @@
     <row r="269">
       <c r="A269" s="1" t="inlineStr">
         <is>
-          <t>貨櫃運輸集散及倉儲</t>
+          <t>貿易商、代理商、經銷商</t>
         </is>
       </c>
       <c r="B269" t="inlineStr"/>
       <c r="C269" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D269" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E269" t="n">
         <v>0</v>
       </c>
       <c r="F269" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G269" t="n">
         <v>0</v>
@@ -11519,7 +11523,7 @@
         <v>0</v>
       </c>
       <c r="L269" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M269" t="n">
         <v>0</v>
@@ -11528,21 +11532,21 @@
     <row r="270">
       <c r="A270" s="1" t="inlineStr">
         <is>
-          <t>貿易商、代理商、經銷商</t>
+          <t>資安審計</t>
         </is>
       </c>
       <c r="B270" t="inlineStr"/>
       <c r="C270" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D270" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E270" t="n">
         <v>0</v>
       </c>
       <c r="F270" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G270" t="n">
         <v>0</v>
@@ -11560,7 +11564,7 @@
         <v>0</v>
       </c>
       <c r="L270" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M270" t="n">
         <v>0</v>
@@ -11569,7 +11573,7 @@
     <row r="271">
       <c r="A271" s="1" t="inlineStr">
         <is>
-          <t>資安審計</t>
+          <t>資安治理</t>
         </is>
       </c>
       <c r="B271" t="inlineStr"/>
@@ -11595,22 +11599,22 @@
         <v>0</v>
       </c>
       <c r="J271" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K271" t="n">
         <v>0</v>
       </c>
       <c r="L271" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M271" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" s="1" t="inlineStr">
         <is>
-          <t>資安治理</t>
+          <t>資安營運管理服務</t>
         </is>
       </c>
       <c r="B272" t="inlineStr"/>
@@ -11633,10 +11637,10 @@
         <v>0</v>
       </c>
       <c r="I272" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J272" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K272" t="n">
         <v>0</v>
@@ -11645,13 +11649,13 @@
         <v>1</v>
       </c>
       <c r="M272" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" s="1" t="inlineStr">
         <is>
-          <t>資安營運管理服務</t>
+          <t>資安防護能力分析與鑑識服務</t>
         </is>
       </c>
       <c r="B273" t="inlineStr"/>
@@ -11677,7 +11681,7 @@
         <v>1</v>
       </c>
       <c r="J273" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K273" t="n">
         <v>0</v>
@@ -11686,16 +11690,18 @@
         <v>1</v>
       </c>
       <c r="M273" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" s="1" t="inlineStr">
         <is>
-          <t>資安防護能力分析與鑑識服務</t>
-        </is>
-      </c>
-      <c r="B274" t="inlineStr"/>
+          <t>資安防護軟體</t>
+        </is>
+      </c>
+      <c r="B274" t="n">
+        <v>0</v>
+      </c>
       <c r="C274" t="n">
         <v>0</v>
       </c>
@@ -11712,7 +11718,7 @@
         <v>0</v>
       </c>
       <c r="H274" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I274" t="n">
         <v>1</v>
@@ -11721,19 +11727,19 @@
         <v>2</v>
       </c>
       <c r="K274" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L274" t="n">
         <v>1</v>
       </c>
       <c r="M274" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" s="1" t="inlineStr">
         <is>
-          <t>資安防護軟體</t>
+          <t>資安顧問服務</t>
         </is>
       </c>
       <c r="B275" t="inlineStr"/>
@@ -11753,7 +11759,7 @@
         <v>0</v>
       </c>
       <c r="H275" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I275" t="n">
         <v>1</v>
@@ -11762,19 +11768,19 @@
         <v>2</v>
       </c>
       <c r="K275" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L275" t="n">
         <v>1</v>
       </c>
       <c r="M275" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" s="1" t="inlineStr">
         <is>
-          <t>資安顧問服務</t>
+          <t>資料分析處理服務</t>
         </is>
       </c>
       <c r="B276" t="inlineStr"/>
@@ -11797,25 +11803,25 @@
         <v>0</v>
       </c>
       <c r="I276" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J276" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K276" t="n">
         <v>0</v>
       </c>
       <c r="L276" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M276" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" s="1" t="inlineStr">
         <is>
-          <t>資料分析處理服務</t>
+          <t>資料安全</t>
         </is>
       </c>
       <c r="B277" t="inlineStr"/>
@@ -11832,22 +11838,22 @@
         <v>0</v>
       </c>
       <c r="G277" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H277" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I277" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J277" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K277" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L277" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M277" t="n">
         <v>0</v>
@@ -11856,7 +11862,7 @@
     <row r="278">
       <c r="A278" s="1" t="inlineStr">
         <is>
-          <t>資料安全</t>
+          <t>資料庫</t>
         </is>
       </c>
       <c r="B278" t="inlineStr"/>
@@ -11873,7 +11879,7 @@
         <v>0</v>
       </c>
       <c r="G278" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H278" t="n">
         <v>2</v>
@@ -11888,7 +11894,7 @@
         <v>1</v>
       </c>
       <c r="L278" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M278" t="n">
         <v>0</v>
@@ -11897,7 +11903,7 @@
     <row r="279">
       <c r="A279" s="1" t="inlineStr">
         <is>
-          <t>資料庫</t>
+          <t>資料聚合</t>
         </is>
       </c>
       <c r="B279" t="inlineStr"/>
@@ -11917,16 +11923,16 @@
         <v>0</v>
       </c>
       <c r="H279" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I279" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J279" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K279" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L279" t="n">
         <v>0</v>
@@ -11938,10 +11944,12 @@
     <row r="280">
       <c r="A280" s="1" t="inlineStr">
         <is>
-          <t>資料聚合</t>
-        </is>
-      </c>
-      <c r="B280" t="inlineStr"/>
+          <t>資料處理</t>
+        </is>
+      </c>
+      <c r="B280" t="n">
+        <v>0</v>
+      </c>
       <c r="C280" t="n">
         <v>0</v>
       </c>
@@ -11961,28 +11969,30 @@
         <v>0</v>
       </c>
       <c r="I280" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J280" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K280" t="n">
         <v>0</v>
       </c>
       <c r="L280" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M280" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" s="1" t="inlineStr">
         <is>
-          <t>資料處理</t>
-        </is>
-      </c>
-      <c r="B281" t="inlineStr"/>
+          <t>資料處理服務</t>
+        </is>
+      </c>
+      <c r="B281" t="n">
+        <v>0</v>
+      </c>
       <c r="C281" t="n">
         <v>0</v>
       </c>
@@ -12002,28 +12012,30 @@
         <v>0</v>
       </c>
       <c r="I281" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J281" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K281" t="n">
         <v>0</v>
       </c>
       <c r="L281" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M281" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" s="1" t="inlineStr">
         <is>
-          <t>資料處理服務</t>
-        </is>
-      </c>
-      <c r="B282" t="inlineStr"/>
+          <t>資服</t>
+        </is>
+      </c>
+      <c r="B282" t="n">
+        <v>0</v>
+      </c>
       <c r="C282" t="n">
         <v>0</v>
       </c>
@@ -12061,7 +12073,7 @@
     <row r="283">
       <c r="A283" s="1" t="inlineStr">
         <is>
-          <t>資服</t>
+          <t>資訊收集設備</t>
         </is>
       </c>
       <c r="B283" t="inlineStr"/>
@@ -12102,7 +12114,7 @@
     <row r="284">
       <c r="A284" s="1" t="inlineStr">
         <is>
-          <t>資訊收集設備</t>
+          <t>資訊系統建置服務</t>
         </is>
       </c>
       <c r="B284" t="inlineStr"/>
@@ -12143,7 +12155,7 @@
     <row r="285">
       <c r="A285" s="1" t="inlineStr">
         <is>
-          <t>資訊系統建置服務</t>
+          <t>資訊聚合</t>
         </is>
       </c>
       <c r="B285" t="inlineStr"/>
@@ -12184,7 +12196,7 @@
     <row r="286">
       <c r="A286" s="1" t="inlineStr">
         <is>
-          <t>資訊聚合</t>
+          <t>身分認證與訪問管理</t>
         </is>
       </c>
       <c r="B286" t="inlineStr"/>
@@ -12201,22 +12213,22 @@
         <v>0</v>
       </c>
       <c r="G286" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H286" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I286" t="n">
         <v>0</v>
       </c>
       <c r="J286" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K286" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L286" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M286" t="n">
         <v>0</v>
@@ -12225,15 +12237,17 @@
     <row r="287">
       <c r="A287" s="1" t="inlineStr">
         <is>
-          <t>身分認證與訪問管理</t>
-        </is>
-      </c>
-      <c r="B287" t="inlineStr"/>
+          <t>車燈</t>
+        </is>
+      </c>
+      <c r="B287" t="n">
+        <v>0</v>
+      </c>
       <c r="C287" t="n">
         <v>0</v>
       </c>
       <c r="D287" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E287" t="n">
         <v>0</v>
@@ -12242,22 +12256,22 @@
         <v>0</v>
       </c>
       <c r="G287" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H287" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I287" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J287" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K287" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L287" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M287" t="n">
         <v>0</v>
@@ -12266,30 +12280,32 @@
     <row r="288">
       <c r="A288" s="1" t="inlineStr">
         <is>
-          <t>車燈</t>
-        </is>
-      </c>
-      <c r="B288" t="inlineStr"/>
+          <t>車用機械傳動設備及零配件</t>
+        </is>
+      </c>
+      <c r="B288" t="n">
+        <v>0</v>
+      </c>
       <c r="C288" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D288" t="n">
         <v>1</v>
       </c>
       <c r="E288" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F288" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G288" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H288" t="n">
         <v>0</v>
       </c>
       <c r="I288" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J288" t="n">
         <v>0</v>
@@ -12307,30 +12323,30 @@
     <row r="289">
       <c r="A289" s="1" t="inlineStr">
         <is>
-          <t>車用機械傳動設備及零配件</t>
+          <t>軟性電路板</t>
         </is>
       </c>
       <c r="B289" t="inlineStr"/>
       <c r="C289" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D289" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E289" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F289" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G289" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H289" t="n">
         <v>0</v>
       </c>
       <c r="I289" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J289" t="n">
         <v>0</v>
@@ -12348,7 +12364,7 @@
     <row r="290">
       <c r="A290" s="1" t="inlineStr">
         <is>
-          <t>軟性電路板</t>
+          <t>軟體開發</t>
         </is>
       </c>
       <c r="B290" t="inlineStr"/>
@@ -12389,7 +12405,7 @@
     <row r="291">
       <c r="A291" s="1" t="inlineStr">
         <is>
-          <t>軟體開發</t>
+          <t>軟體開發工具</t>
         </is>
       </c>
       <c r="B291" t="inlineStr"/>
@@ -12415,7 +12431,7 @@
         <v>0</v>
       </c>
       <c r="J291" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K291" t="n">
         <v>0</v>
@@ -12430,7 +12446,7 @@
     <row r="292">
       <c r="A292" s="1" t="inlineStr">
         <is>
-          <t>軟體開發工具</t>
+          <t>輪胎</t>
         </is>
       </c>
       <c r="B292" t="inlineStr"/>
@@ -12456,7 +12472,7 @@
         <v>0</v>
       </c>
       <c r="J292" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K292" t="n">
         <v>0</v>
@@ -12471,7 +12487,7 @@
     <row r="293">
       <c r="A293" s="1" t="inlineStr">
         <is>
-          <t>輪胎</t>
+          <t>輸出入模組/介面卡</t>
         </is>
       </c>
       <c r="B293" t="inlineStr"/>
@@ -12488,16 +12504,16 @@
         <v>0</v>
       </c>
       <c r="G293" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H293" t="n">
         <v>0</v>
       </c>
       <c r="I293" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J293" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K293" t="n">
         <v>0</v>
@@ -12512,7 +12528,7 @@
     <row r="294">
       <c r="A294" s="1" t="inlineStr">
         <is>
-          <t>輸出入模組/介面卡</t>
+          <t>輸送機械及零配件</t>
         </is>
       </c>
       <c r="B294" t="inlineStr"/>
@@ -12529,16 +12545,16 @@
         <v>0</v>
       </c>
       <c r="G294" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H294" t="n">
         <v>0</v>
       </c>
       <c r="I294" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J294" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K294" t="n">
         <v>0</v>
@@ -12553,7 +12569,7 @@
     <row r="295">
       <c r="A295" s="1" t="inlineStr">
         <is>
-          <t>輸送機械及零配件</t>
+          <t>農業科技業</t>
         </is>
       </c>
       <c r="B295" t="inlineStr"/>
@@ -12582,7 +12598,7 @@
         <v>0</v>
       </c>
       <c r="K295" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L295" t="n">
         <v>0</v>
@@ -12594,7 +12610,7 @@
     <row r="296">
       <c r="A296" s="1" t="inlineStr">
         <is>
-          <t>農業科技業</t>
+          <t>農藥</t>
         </is>
       </c>
       <c r="B296" t="inlineStr"/>
@@ -12623,7 +12639,7 @@
         <v>0</v>
       </c>
       <c r="K296" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L296" t="n">
         <v>0</v>
@@ -12635,7 +12651,7 @@
     <row r="297">
       <c r="A297" s="1" t="inlineStr">
         <is>
-          <t>農藥</t>
+          <t>近眼顯示(Dear-Eye Display)</t>
         </is>
       </c>
       <c r="B297" t="inlineStr"/>
@@ -12676,7 +12692,7 @@
     <row r="298">
       <c r="A298" s="1" t="inlineStr">
         <is>
-          <t>近眼顯示(Dear-Eye Display)</t>
+          <t>通訊</t>
         </is>
       </c>
       <c r="B298" t="inlineStr"/>
@@ -12717,7 +12733,7 @@
     <row r="299">
       <c r="A299" s="1" t="inlineStr">
         <is>
-          <t>通訊</t>
+          <t>通訊服務</t>
         </is>
       </c>
       <c r="B299" t="inlineStr"/>
@@ -12758,12 +12774,14 @@
     <row r="300">
       <c r="A300" s="1" t="inlineStr">
         <is>
-          <t>通訊服務</t>
-        </is>
-      </c>
-      <c r="B300" t="inlineStr"/>
+          <t>通路經銷</t>
+        </is>
+      </c>
+      <c r="B300" t="n">
+        <v>0</v>
+      </c>
       <c r="C300" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D300" t="n">
         <v>0</v>
@@ -12781,16 +12799,16 @@
         <v>0</v>
       </c>
       <c r="I300" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J300" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K300" t="n">
         <v>0</v>
       </c>
       <c r="L300" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M300" t="n">
         <v>0</v>
@@ -12799,7 +12817,7 @@
     <row r="301">
       <c r="A301" s="1" t="inlineStr">
         <is>
-          <t>通路經銷</t>
+          <t>連接器設計、組裝及製造</t>
         </is>
       </c>
       <c r="B301" t="inlineStr"/>
@@ -12813,41 +12831,39 @@
         <v>0</v>
       </c>
       <c r="F301" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G301" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H301" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I301" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J301" t="n">
         <v>1</v>
       </c>
       <c r="K301" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L301" t="n">
         <v>1</v>
       </c>
       <c r="M301" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" s="1" t="inlineStr">
         <is>
-          <t>連接器設計、組裝及製造</t>
-        </is>
-      </c>
-      <c r="B302" t="n">
-        <v>0</v>
-      </c>
+          <t>連接線</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr"/>
       <c r="C302" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D302" t="n">
         <v>0</v>
@@ -12856,7 +12872,7 @@
         <v>0</v>
       </c>
       <c r="F302" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G302" t="n">
         <v>0</v>
@@ -12865,25 +12881,25 @@
         <v>1</v>
       </c>
       <c r="I302" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J302" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K302" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L302" t="n">
         <v>1</v>
       </c>
       <c r="M302" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" s="1" t="inlineStr">
         <is>
-          <t>連接線</t>
+          <t>運動服務/顧問</t>
         </is>
       </c>
       <c r="B303" t="inlineStr"/>
@@ -12903,28 +12919,28 @@
         <v>0</v>
       </c>
       <c r="H303" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I303" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J303" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K303" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L303" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M303" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" s="1" t="inlineStr">
         <is>
-          <t>運動服務/顧問</t>
+          <t>運動用品</t>
         </is>
       </c>
       <c r="B304" t="inlineStr"/>
@@ -12965,7 +12981,7 @@
     <row r="305">
       <c r="A305" s="1" t="inlineStr">
         <is>
-          <t>運動用品</t>
+          <t>運動行銷/媒體</t>
         </is>
       </c>
       <c r="B305" t="inlineStr"/>
@@ -13006,7 +13022,7 @@
     <row r="306">
       <c r="A306" s="1" t="inlineStr">
         <is>
-          <t>運動行銷/媒體</t>
+          <t>運算元件與設備</t>
         </is>
       </c>
       <c r="B306" t="inlineStr"/>
@@ -13026,16 +13042,16 @@
         <v>0</v>
       </c>
       <c r="H306" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I306" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J306" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K306" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L306" t="n">
         <v>0</v>
@@ -13047,15 +13063,17 @@
     <row r="307">
       <c r="A307" s="1" t="inlineStr">
         <is>
-          <t>運算元件與設備</t>
-        </is>
-      </c>
-      <c r="B307" t="inlineStr"/>
+          <t>運算設備</t>
+        </is>
+      </c>
+      <c r="B307" t="n">
+        <v>0</v>
+      </c>
       <c r="C307" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D307" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E307" t="n">
         <v>0</v>
@@ -13067,16 +13085,16 @@
         <v>0</v>
       </c>
       <c r="H307" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I307" t="n">
         <v>1</v>
       </c>
       <c r="J307" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K307" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L307" t="n">
         <v>0</v>
@@ -13088,15 +13106,15 @@
     <row r="308">
       <c r="A308" s="1" t="inlineStr">
         <is>
-          <t>運算設備</t>
+          <t>運輸工具</t>
         </is>
       </c>
       <c r="B308" t="inlineStr"/>
       <c r="C308" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D308" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E308" t="n">
         <v>0</v>
@@ -13111,7 +13129,7 @@
         <v>0</v>
       </c>
       <c r="I308" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J308" t="n">
         <v>0</v>
@@ -13129,10 +13147,12 @@
     <row r="309">
       <c r="A309" s="1" t="inlineStr">
         <is>
-          <t>運輸工具</t>
-        </is>
-      </c>
-      <c r="B309" t="inlineStr"/>
+          <t>配電管理設施</t>
+        </is>
+      </c>
+      <c r="B309" t="n">
+        <v>0</v>
+      </c>
       <c r="C309" t="n">
         <v>0</v>
       </c>
@@ -13170,12 +13190,14 @@
     <row r="310">
       <c r="A310" s="1" t="inlineStr">
         <is>
-          <t>配電管理設施</t>
-        </is>
-      </c>
-      <c r="B310" t="inlineStr"/>
+          <t>配電系統</t>
+        </is>
+      </c>
+      <c r="B310" t="n">
+        <v>0</v>
+      </c>
       <c r="C310" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D310" t="n">
         <v>0</v>
@@ -13199,7 +13221,7 @@
         <v>0</v>
       </c>
       <c r="K310" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L310" t="n">
         <v>0</v>
@@ -13211,12 +13233,12 @@
     <row r="311">
       <c r="A311" s="1" t="inlineStr">
         <is>
-          <t>配電系統</t>
+          <t>酚醛樹脂</t>
         </is>
       </c>
       <c r="B311" t="inlineStr"/>
       <c r="C311" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D311" t="n">
         <v>0</v>
@@ -13237,10 +13259,10 @@
         <v>0</v>
       </c>
       <c r="J311" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K311" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L311" t="n">
         <v>0</v>
@@ -13252,7 +13274,7 @@
     <row r="312">
       <c r="A312" s="1" t="inlineStr">
         <is>
-          <t>酚醛樹脂</t>
+          <t>醫療器材代理銷售及通路</t>
         </is>
       </c>
       <c r="B312" t="inlineStr"/>
@@ -13269,13 +13291,13 @@
         <v>0</v>
       </c>
       <c r="G312" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H312" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I312" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J312" t="n">
         <v>1</v>
@@ -13293,17 +13315,17 @@
     <row r="313">
       <c r="A313" s="1" t="inlineStr">
         <is>
-          <t>醫療器材代理銷售及通路</t>
+          <t>醫療器材研發、設計、製造</t>
         </is>
       </c>
       <c r="B313" t="n">
         <v>0</v>
       </c>
       <c r="C313" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D313" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E313" t="n">
         <v>0</v>
@@ -13312,41 +13334,39 @@
         <v>0</v>
       </c>
       <c r="G313" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H313" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I313" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J313" t="n">
         <v>1</v>
       </c>
       <c r="K313" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L313" t="n">
         <v>0</v>
       </c>
       <c r="M313" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" s="1" t="inlineStr">
         <is>
-          <t>醫療器材研發、設計、製造</t>
-        </is>
-      </c>
-      <c r="B314" t="n">
-        <v>0</v>
-      </c>
+          <t>醫療院所</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr"/>
       <c r="C314" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D314" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E314" t="n">
         <v>0</v>
@@ -13355,16 +13375,16 @@
         <v>0</v>
       </c>
       <c r="G314" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H314" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I314" t="n">
         <v>0</v>
       </c>
       <c r="J314" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K314" t="n">
         <v>0</v>
@@ -13373,13 +13393,13 @@
         <v>0</v>
       </c>
       <c r="M314" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" s="1" t="inlineStr">
         <is>
-          <t>醫療院所</t>
+          <t>金屬、塑膠模具</t>
         </is>
       </c>
       <c r="B315" t="inlineStr"/>
@@ -13396,22 +13416,22 @@
         <v>0</v>
       </c>
       <c r="G315" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H315" t="n">
         <v>0</v>
       </c>
       <c r="I315" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J315" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K315" t="n">
         <v>0</v>
       </c>
       <c r="L315" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M315" t="n">
         <v>0</v>
@@ -13420,7 +13440,7 @@
     <row r="316">
       <c r="A316" s="1" t="inlineStr">
         <is>
-          <t>金屬、塑膠模具</t>
+          <t>金屬加工用機械</t>
         </is>
       </c>
       <c r="B316" t="inlineStr"/>
@@ -13428,7 +13448,7 @@
         <v>0</v>
       </c>
       <c r="D316" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E316" t="n">
         <v>0</v>
@@ -13437,22 +13457,22 @@
         <v>0</v>
       </c>
       <c r="G316" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H316" t="n">
         <v>0</v>
       </c>
       <c r="I316" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J316" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K316" t="n">
         <v>0</v>
       </c>
       <c r="L316" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M316" t="n">
         <v>0</v>
@@ -13461,29 +13481,27 @@
     <row r="317">
       <c r="A317" s="1" t="inlineStr">
         <is>
-          <t>金屬加工用機械</t>
-        </is>
-      </c>
-      <c r="B317" t="n">
-        <v>0</v>
-      </c>
+          <t>金屬加工處理</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr"/>
       <c r="C317" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D317" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E317" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F317" t="n">
         <v>0</v>
       </c>
       <c r="G317" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H317" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I317" t="n">
         <v>0</v>
@@ -13498,24 +13516,24 @@
         <v>0</v>
       </c>
       <c r="M317" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" s="1" t="inlineStr">
         <is>
-          <t>金屬加工處理</t>
+          <t>金屬材料</t>
         </is>
       </c>
       <c r="B318" t="inlineStr"/>
       <c r="C318" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D318" t="n">
         <v>0</v>
       </c>
       <c r="E318" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F318" t="n">
         <v>0</v>
@@ -13524,7 +13542,7 @@
         <v>0</v>
       </c>
       <c r="H318" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I318" t="n">
         <v>0</v>
@@ -13539,13 +13557,13 @@
         <v>0</v>
       </c>
       <c r="M318" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" s="1" t="inlineStr">
         <is>
-          <t>金屬材料</t>
+          <t>金屬製品</t>
         </is>
       </c>
       <c r="B319" t="inlineStr"/>
@@ -13565,7 +13583,7 @@
         <v>0</v>
       </c>
       <c r="H319" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I319" t="n">
         <v>0</v>
@@ -13586,7 +13604,7 @@
     <row r="320">
       <c r="A320" s="1" t="inlineStr">
         <is>
-          <t>金屬製品</t>
+          <t>金控業/銀行業/保險業</t>
         </is>
       </c>
       <c r="B320" t="inlineStr"/>
@@ -13606,7 +13624,7 @@
         <v>0</v>
       </c>
       <c r="H320" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I320" t="n">
         <v>0</v>
@@ -13627,7 +13645,7 @@
     <row r="321">
       <c r="A321" s="1" t="inlineStr">
         <is>
-          <t>金控業/銀行業/保險業</t>
+          <t>金流串接處理服務</t>
         </is>
       </c>
       <c r="B321" t="inlineStr"/>
@@ -13635,7 +13653,7 @@
         <v>0</v>
       </c>
       <c r="D321" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E321" t="n">
         <v>0</v>
@@ -13668,7 +13686,7 @@
     <row r="322">
       <c r="A322" s="1" t="inlineStr">
         <is>
-          <t>金流串接處理服務</t>
+          <t>金融提款機(ATM)</t>
         </is>
       </c>
       <c r="B322" t="inlineStr"/>
@@ -13676,7 +13694,7 @@
         <v>0</v>
       </c>
       <c r="D322" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E322" t="n">
         <v>0</v>
@@ -13709,7 +13727,7 @@
     <row r="323">
       <c r="A323" s="1" t="inlineStr">
         <is>
-          <t>金融提款機(ATM)</t>
+          <t>鈑金</t>
         </is>
       </c>
       <c r="B323" t="inlineStr"/>
@@ -13750,21 +13768,21 @@
     <row r="324">
       <c r="A324" s="1" t="inlineStr">
         <is>
-          <t>鈑金</t>
+          <t>銅箔</t>
         </is>
       </c>
       <c r="B324" t="inlineStr"/>
       <c r="C324" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D324" t="n">
         <v>0</v>
       </c>
       <c r="E324" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F324" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G324" t="n">
         <v>0</v>
@@ -13773,13 +13791,13 @@
         <v>0</v>
       </c>
       <c r="I324" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J324" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K324" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L324" t="n">
         <v>0</v>
@@ -13791,21 +13809,21 @@
     <row r="325">
       <c r="A325" s="1" t="inlineStr">
         <is>
-          <t>銅箔</t>
+          <t>銅箔基板</t>
         </is>
       </c>
       <c r="B325" t="inlineStr"/>
       <c r="C325" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D325" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E325" t="n">
         <v>1</v>
       </c>
       <c r="F325" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G325" t="n">
         <v>0</v>
@@ -13814,10 +13832,10 @@
         <v>0</v>
       </c>
       <c r="I325" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J325" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K325" t="n">
         <v>1</v>
@@ -13832,21 +13850,21 @@
     <row r="326">
       <c r="A326" s="1" t="inlineStr">
         <is>
-          <t>銅箔基板</t>
+          <t>銷售、進出口業務</t>
         </is>
       </c>
       <c r="B326" t="inlineStr"/>
       <c r="C326" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D326" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E326" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F326" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G326" t="n">
         <v>0</v>
@@ -13858,13 +13876,13 @@
         <v>0</v>
       </c>
       <c r="J326" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K326" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L326" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M326" t="n">
         <v>0</v>
@@ -13873,7 +13891,7 @@
     <row r="327">
       <c r="A327" s="1" t="inlineStr">
         <is>
-          <t>銷售、進出口業務</t>
+          <t>鋁合金鋼圈</t>
         </is>
       </c>
       <c r="B327" t="inlineStr"/>
@@ -13887,7 +13905,7 @@
         <v>0</v>
       </c>
       <c r="F327" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G327" t="n">
         <v>0</v>
@@ -13905,7 +13923,7 @@
         <v>0</v>
       </c>
       <c r="L327" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M327" t="n">
         <v>0</v>
@@ -13914,12 +13932,12 @@
     <row r="328">
       <c r="A328" s="1" t="inlineStr">
         <is>
-          <t>鋁合金鋼圈</t>
+          <t>鋰電池材料</t>
         </is>
       </c>
       <c r="B328" t="inlineStr"/>
       <c r="C328" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D328" t="n">
         <v>0</v>
@@ -13943,10 +13961,10 @@
         <v>0</v>
       </c>
       <c r="K328" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L328" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M328" t="n">
         <v>0</v>
@@ -13955,12 +13973,12 @@
     <row r="329">
       <c r="A329" s="1" t="inlineStr">
         <is>
-          <t>鋰電池材料</t>
+          <t>鋼材</t>
         </is>
       </c>
       <c r="B329" t="inlineStr"/>
       <c r="C329" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D329" t="n">
         <v>0</v>
@@ -13984,10 +14002,10 @@
         <v>0</v>
       </c>
       <c r="K329" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L329" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M329" t="n">
         <v>0</v>
@@ -13996,7 +14014,7 @@
     <row r="330">
       <c r="A330" s="1" t="inlineStr">
         <is>
-          <t>鋼材</t>
+          <t>鋼筋</t>
         </is>
       </c>
       <c r="B330" t="inlineStr"/>
@@ -14037,7 +14055,7 @@
     <row r="331">
       <c r="A331" s="1" t="inlineStr">
         <is>
-          <t>鋼筋</t>
+          <t>鋼線鋼纜</t>
         </is>
       </c>
       <c r="B331" t="inlineStr"/>
@@ -14066,7 +14084,7 @@
         <v>0</v>
       </c>
       <c r="K331" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L331" t="n">
         <v>0</v>
@@ -14078,7 +14096,7 @@
     <row r="332">
       <c r="A332" s="1" t="inlineStr">
         <is>
-          <t>鋼線鋼纜</t>
+          <t>鋼胚</t>
         </is>
       </c>
       <c r="B332" t="inlineStr"/>
@@ -14107,7 +14125,7 @@
         <v>0</v>
       </c>
       <c r="K332" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L332" t="n">
         <v>0</v>
@@ -14119,12 +14137,12 @@
     <row r="333">
       <c r="A333" s="1" t="inlineStr">
         <is>
-          <t>鋼胚</t>
+          <t>鋼鑄鐵元件</t>
         </is>
       </c>
       <c r="B333" t="inlineStr"/>
       <c r="C333" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D333" t="n">
         <v>0</v>
@@ -14154,18 +14172,18 @@
         <v>0</v>
       </c>
       <c r="M333" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="334">
       <c r="A334" s="1" t="inlineStr">
         <is>
-          <t>鋼鑄鐵元件</t>
+          <t>錢包/資產管理</t>
         </is>
       </c>
       <c r="B334" t="inlineStr"/>
       <c r="C334" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D334" t="n">
         <v>0</v>
@@ -14195,13 +14213,13 @@
         <v>0</v>
       </c>
       <c r="M334" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="335">
       <c r="A335" s="1" t="inlineStr">
         <is>
-          <t>錢包/資產管理</t>
+          <t>開發工具</t>
         </is>
       </c>
       <c r="B335" t="inlineStr"/>
@@ -14227,7 +14245,7 @@
         <v>0</v>
       </c>
       <c r="J335" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K335" t="n">
         <v>0</v>
@@ -14242,7 +14260,7 @@
     <row r="336">
       <c r="A336" s="1" t="inlineStr">
         <is>
-          <t>開發工具</t>
+          <t>隨身碟、記憶卡讀卡機</t>
         </is>
       </c>
       <c r="B336" t="inlineStr"/>
@@ -14253,25 +14271,25 @@
         <v>0</v>
       </c>
       <c r="E336" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F336" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G336" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H336" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I336" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J336" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K336" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L336" t="n">
         <v>0</v>
@@ -14283,10 +14301,12 @@
     <row r="337">
       <c r="A337" s="1" t="inlineStr">
         <is>
-          <t>隨身碟、記憶卡讀卡機</t>
-        </is>
-      </c>
-      <c r="B337" t="inlineStr"/>
+          <t>雲端作業系統</t>
+        </is>
+      </c>
+      <c r="B337" t="n">
+        <v>0</v>
+      </c>
       <c r="C337" t="n">
         <v>0</v>
       </c>
@@ -14294,25 +14314,25 @@
         <v>0</v>
       </c>
       <c r="E337" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F337" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G337" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H337" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I337" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J337" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K337" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L337" t="n">
         <v>0</v>
@@ -14324,7 +14344,7 @@
     <row r="338">
       <c r="A338" s="1" t="inlineStr">
         <is>
-          <t>雲端作業系統</t>
+          <t>雲端安全</t>
         </is>
       </c>
       <c r="B338" t="inlineStr"/>
@@ -14341,34 +14361,36 @@
         <v>0</v>
       </c>
       <c r="G338" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H338" t="n">
         <v>1</v>
       </c>
       <c r="I338" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J338" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K338" t="n">
         <v>1</v>
       </c>
       <c r="L338" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M338" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="339">
       <c r="A339" s="1" t="inlineStr">
         <is>
-          <t>雲端安全</t>
-        </is>
-      </c>
-      <c r="B339" t="inlineStr"/>
+          <t>雲端平台</t>
+        </is>
+      </c>
+      <c r="B339" t="n">
+        <v>0</v>
+      </c>
       <c r="C339" t="n">
         <v>0</v>
       </c>
@@ -14382,16 +14404,16 @@
         <v>0</v>
       </c>
       <c r="G339" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H339" t="n">
         <v>1</v>
       </c>
       <c r="I339" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J339" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K339" t="n">
         <v>1</v>
@@ -14400,16 +14422,18 @@
         <v>1</v>
       </c>
       <c r="M339" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="340">
       <c r="A340" s="1" t="inlineStr">
         <is>
-          <t>雲端平台</t>
-        </is>
-      </c>
-      <c r="B340" t="inlineStr"/>
+          <t>雲端應用服務</t>
+        </is>
+      </c>
+      <c r="B340" t="n">
+        <v>0</v>
+      </c>
       <c r="C340" t="n">
         <v>0</v>
       </c>
@@ -14432,7 +14456,7 @@
         <v>2</v>
       </c>
       <c r="J340" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K340" t="n">
         <v>1</v>
@@ -14447,39 +14471,39 @@
     <row r="341">
       <c r="A341" s="1" t="inlineStr">
         <is>
-          <t>雲端應用服務</t>
+          <t>零售通路</t>
         </is>
       </c>
       <c r="B341" t="inlineStr"/>
       <c r="C341" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D341" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E341" t="n">
         <v>0</v>
       </c>
       <c r="F341" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G341" t="n">
         <v>0</v>
       </c>
       <c r="H341" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I341" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J341" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K341" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L341" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M341" t="n">
         <v>0</v>
@@ -14488,7 +14512,7 @@
     <row r="342">
       <c r="A342" s="1" t="inlineStr">
         <is>
-          <t>零售通路</t>
+          <t>零組件/材料</t>
         </is>
       </c>
       <c r="B342" t="inlineStr"/>
@@ -14496,25 +14520,25 @@
         <v>1</v>
       </c>
       <c r="D342" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E342" t="n">
         <v>0</v>
       </c>
       <c r="F342" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G342" t="n">
         <v>0</v>
       </c>
       <c r="H342" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I342" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J342" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K342" t="n">
         <v>0</v>
@@ -14529,12 +14553,12 @@
     <row r="343">
       <c r="A343" s="1" t="inlineStr">
         <is>
-          <t>零組件/材料</t>
+          <t>電信服務業</t>
         </is>
       </c>
       <c r="B343" t="inlineStr"/>
       <c r="C343" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D343" t="n">
         <v>0</v>
@@ -14549,16 +14573,16 @@
         <v>0</v>
       </c>
       <c r="H343" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I343" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J343" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K343" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L343" t="n">
         <v>0</v>
@@ -14570,10 +14594,12 @@
     <row r="344">
       <c r="A344" s="1" t="inlineStr">
         <is>
-          <t>電信服務業</t>
-        </is>
-      </c>
-      <c r="B344" t="inlineStr"/>
+          <t>電力系統</t>
+        </is>
+      </c>
+      <c r="B344" t="n">
+        <v>0</v>
+      </c>
       <c r="C344" t="n">
         <v>0</v>
       </c>
@@ -14599,7 +14625,7 @@
         <v>0</v>
       </c>
       <c r="K344" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L344" t="n">
         <v>0</v>
@@ -14611,18 +14637,18 @@
     <row r="345">
       <c r="A345" s="1" t="inlineStr">
         <is>
-          <t>電力系統</t>
+          <t>電力設備</t>
         </is>
       </c>
       <c r="B345" t="inlineStr"/>
       <c r="C345" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D345" t="n">
         <v>0</v>
       </c>
       <c r="E345" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F345" t="n">
         <v>0</v>
@@ -14640,7 +14666,7 @@
         <v>0</v>
       </c>
       <c r="K345" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L345" t="n">
         <v>0</v>
@@ -14652,7 +14678,7 @@
     <row r="346">
       <c r="A346" s="1" t="inlineStr">
         <is>
-          <t>電力設備</t>
+          <t>電力零售業</t>
         </is>
       </c>
       <c r="B346" t="inlineStr"/>
@@ -14663,7 +14689,7 @@
         <v>0</v>
       </c>
       <c r="E346" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F346" t="n">
         <v>0</v>
@@ -14681,7 +14707,7 @@
         <v>0</v>
       </c>
       <c r="K346" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L346" t="n">
         <v>0</v>
@@ -14693,10 +14719,12 @@
     <row r="347">
       <c r="A347" s="1" t="inlineStr">
         <is>
-          <t>電力零售業</t>
-        </is>
-      </c>
-      <c r="B347" t="inlineStr"/>
+          <t>電動汽車、電動機車、電動自行車</t>
+        </is>
+      </c>
+      <c r="B347" t="n">
+        <v>0</v>
+      </c>
       <c r="C347" t="n">
         <v>0</v>
       </c>
@@ -14725,7 +14753,7 @@
         <v>0</v>
       </c>
       <c r="L347" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M347" t="n">
         <v>0</v>
@@ -14734,7 +14762,7 @@
     <row r="348">
       <c r="A348" s="1" t="inlineStr">
         <is>
-          <t>電動汽車、電動機車、電動自行車</t>
+          <t>電子書</t>
         </is>
       </c>
       <c r="B348" t="inlineStr"/>
@@ -14766,7 +14794,7 @@
         <v>0</v>
       </c>
       <c r="L348" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M348" t="n">
         <v>0</v>
@@ -14775,7 +14803,7 @@
     <row r="349">
       <c r="A349" s="1" t="inlineStr">
         <is>
-          <t>電子書</t>
+          <t>電子觸控白板</t>
         </is>
       </c>
       <c r="B349" t="inlineStr"/>
@@ -14816,89 +14844,91 @@
     <row r="350">
       <c r="A350" s="1" t="inlineStr">
         <is>
-          <t>電子觸控白板</t>
-        </is>
-      </c>
-      <c r="B350" t="inlineStr"/>
+          <t>電子零組件、塑膠零件、五金零件</t>
+        </is>
+      </c>
+      <c r="B350" t="n">
+        <v>0</v>
+      </c>
       <c r="C350" t="n">
         <v>0</v>
       </c>
       <c r="D350" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E350" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F350" t="n">
         <v>0</v>
       </c>
       <c r="G350" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H350" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I350" t="n">
         <v>0</v>
       </c>
       <c r="J350" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K350" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L350" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M350" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="351">
       <c r="A351" s="1" t="inlineStr">
         <is>
-          <t>電子零組件、塑膠零件、五金零件</t>
+          <t>電容器</t>
         </is>
       </c>
       <c r="B351" t="inlineStr"/>
       <c r="C351" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D351" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E351" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F351" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G351" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H351" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I351" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J351" t="n">
         <v>1</v>
       </c>
       <c r="K351" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="L351" t="n">
         <v>1</v>
       </c>
       <c r="M351" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="352">
       <c r="A352" s="1" t="inlineStr">
         <is>
-          <t>電容器</t>
+          <t>電容器材料(如電蝕／化成鋁箔、介面瓷粉)</t>
         </is>
       </c>
       <c r="B352" t="inlineStr"/>
@@ -14912,7 +14942,7 @@
         <v>0</v>
       </c>
       <c r="F352" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G352" t="n">
         <v>0</v>
@@ -14921,16 +14951,16 @@
         <v>0</v>
       </c>
       <c r="I352" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J352" t="n">
         <v>1</v>
       </c>
       <c r="K352" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="L352" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M352" t="n">
         <v>0</v>
@@ -14939,7 +14969,7 @@
     <row r="353">
       <c r="A353" s="1" t="inlineStr">
         <is>
-          <t>電容器材料(如電蝕／化成鋁箔、介面瓷粉)</t>
+          <t>電感器</t>
         </is>
       </c>
       <c r="B353" t="inlineStr"/>
@@ -14953,25 +14983,25 @@
         <v>0</v>
       </c>
       <c r="F353" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G353" t="n">
         <v>0</v>
       </c>
       <c r="H353" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I353" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J353" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K353" t="n">
+        <v>3</v>
+      </c>
+      <c r="L353" t="n">
         <v>2</v>
-      </c>
-      <c r="L353" t="n">
-        <v>0</v>
       </c>
       <c r="M353" t="n">
         <v>0</v>
@@ -14980,12 +15010,12 @@
     <row r="354">
       <c r="A354" s="1" t="inlineStr">
         <is>
-          <t>電感器</t>
+          <t>電感器材料(如鐵氧體、導電漿墨)</t>
         </is>
       </c>
       <c r="B354" t="inlineStr"/>
       <c r="C354" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D354" t="n">
         <v>0</v>
@@ -14994,25 +15024,25 @@
         <v>0</v>
       </c>
       <c r="F354" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G354" t="n">
         <v>0</v>
       </c>
       <c r="H354" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I354" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J354" t="n">
         <v>2</v>
       </c>
       <c r="K354" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L354" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M354" t="n">
         <v>0</v>
@@ -15021,30 +15051,32 @@
     <row r="355">
       <c r="A355" s="1" t="inlineStr">
         <is>
-          <t>電感器材料(如鐵氧體、導電漿墨)</t>
-        </is>
-      </c>
-      <c r="B355" t="inlineStr"/>
+          <t>電控元件</t>
+        </is>
+      </c>
+      <c r="B355" t="n">
+        <v>0</v>
+      </c>
       <c r="C355" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D355" t="n">
         <v>0</v>
       </c>
       <c r="E355" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F355" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G355" t="n">
         <v>0</v>
       </c>
       <c r="H355" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I355" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J355" t="n">
         <v>2</v>
@@ -15053,7 +15085,7 @@
         <v>1</v>
       </c>
       <c r="L355" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M355" t="n">
         <v>0</v>
@@ -15062,36 +15094,36 @@
     <row r="356">
       <c r="A356" s="1" t="inlineStr">
         <is>
-          <t>電控元件</t>
+          <t>電池</t>
         </is>
       </c>
       <c r="B356" t="inlineStr"/>
       <c r="C356" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D356" t="n">
         <v>0</v>
       </c>
       <c r="E356" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F356" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G356" t="n">
         <v>0</v>
       </c>
       <c r="H356" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I356" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J356" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K356" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L356" t="n">
         <v>0</v>
@@ -15103,10 +15135,12 @@
     <row r="357">
       <c r="A357" s="1" t="inlineStr">
         <is>
-          <t>電池</t>
-        </is>
-      </c>
-      <c r="B357" t="inlineStr"/>
+          <t>電池模組</t>
+        </is>
+      </c>
+      <c r="B357" t="n">
+        <v>0</v>
+      </c>
       <c r="C357" t="n">
         <v>0</v>
       </c>
@@ -15126,10 +15160,10 @@
         <v>0</v>
       </c>
       <c r="I357" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J357" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K357" t="n">
         <v>0</v>
@@ -15144,7 +15178,7 @@
     <row r="358">
       <c r="A358" s="1" t="inlineStr">
         <is>
-          <t>電池模組</t>
+          <t>電池芯</t>
         </is>
       </c>
       <c r="B358" t="inlineStr"/>
@@ -15155,7 +15189,7 @@
         <v>0</v>
       </c>
       <c r="E358" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F358" t="n">
         <v>0</v>
@@ -15185,39 +15219,41 @@
     <row r="359">
       <c r="A359" s="1" t="inlineStr">
         <is>
-          <t>電池芯</t>
-        </is>
-      </c>
-      <c r="B359" t="inlineStr"/>
+          <t>電源供應器</t>
+        </is>
+      </c>
+      <c r="B359" t="n">
+        <v>0</v>
+      </c>
       <c r="C359" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D359" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E359" t="n">
         <v>0</v>
       </c>
       <c r="F359" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G359" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H359" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I359" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J359" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K359" t="n">
         <v>0</v>
       </c>
       <c r="L359" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M359" t="n">
         <v>0</v>
@@ -15226,39 +15262,41 @@
     <row r="360">
       <c r="A360" s="1" t="inlineStr">
         <is>
-          <t>電源供應器</t>
-        </is>
-      </c>
-      <c r="B360" t="inlineStr"/>
+          <t>電網營造</t>
+        </is>
+      </c>
+      <c r="B360" t="n">
+        <v>0</v>
+      </c>
       <c r="C360" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D360" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E360" t="n">
         <v>0</v>
       </c>
       <c r="F360" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G360" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H360" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I360" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J360" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K360" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L360" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M360" t="n">
         <v>0</v>
@@ -15267,12 +15305,12 @@
     <row r="361">
       <c r="A361" s="1" t="inlineStr">
         <is>
-          <t>電網營造</t>
+          <t>電網維運</t>
         </is>
       </c>
       <c r="B361" t="inlineStr"/>
       <c r="C361" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D361" t="n">
         <v>0</v>
@@ -15308,7 +15346,7 @@
     <row r="362">
       <c r="A362" s="1" t="inlineStr">
         <is>
-          <t>電網維運</t>
+          <t>電纜</t>
         </is>
       </c>
       <c r="B362" t="inlineStr"/>
@@ -15337,7 +15375,7 @@
         <v>0</v>
       </c>
       <c r="K362" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L362" t="n">
         <v>0</v>
@@ -15349,7 +15387,7 @@
     <row r="363">
       <c r="A363" s="1" t="inlineStr">
         <is>
-          <t>電纜</t>
+          <t>電腦視覺</t>
         </is>
       </c>
       <c r="B363" t="inlineStr"/>
@@ -15363,83 +15401,83 @@
         <v>0</v>
       </c>
       <c r="F363" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G363" t="n">
         <v>0</v>
       </c>
       <c r="H363" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I363" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J363" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K363" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L363" t="n">
         <v>0</v>
       </c>
       <c r="M363" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="364">
       <c r="A364" s="1" t="inlineStr">
         <is>
-          <t>電腦視覺</t>
+          <t>電腦設備</t>
         </is>
       </c>
       <c r="B364" t="inlineStr"/>
       <c r="C364" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D364" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E364" t="n">
         <v>0</v>
       </c>
       <c r="F364" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G364" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H364" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I364" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J364" t="n">
         <v>1</v>
       </c>
       <c r="K364" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L364" t="n">
         <v>0</v>
       </c>
       <c r="M364" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="365">
       <c r="A365" s="1" t="inlineStr">
         <is>
-          <t>電腦設備</t>
+          <t>電視</t>
         </is>
       </c>
       <c r="B365" t="inlineStr"/>
       <c r="C365" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D365" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E365" t="n">
         <v>0</v>
@@ -15448,19 +15486,19 @@
         <v>0</v>
       </c>
       <c r="G365" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H365" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I365" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J365" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K365" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L365" t="n">
         <v>0</v>
@@ -15472,7 +15510,7 @@
     <row r="366">
       <c r="A366" s="1" t="inlineStr">
         <is>
-          <t>電視</t>
+          <t>電鍍材料</t>
         </is>
       </c>
       <c r="B366" t="inlineStr"/>
@@ -15513,12 +15551,12 @@
     <row r="367">
       <c r="A367" s="1" t="inlineStr">
         <is>
-          <t>電鍍材料</t>
+          <t>電阻器</t>
         </is>
       </c>
       <c r="B367" t="inlineStr"/>
       <c r="C367" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D367" t="n">
         <v>0</v>
@@ -15536,16 +15574,16 @@
         <v>0</v>
       </c>
       <c r="I367" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J367" t="n">
         <v>0</v>
       </c>
       <c r="K367" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L367" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M367" t="n">
         <v>0</v>
@@ -15554,12 +15592,12 @@
     <row r="368">
       <c r="A368" s="1" t="inlineStr">
         <is>
-          <t>電阻器</t>
+          <t>電阻器材料(氧化鋁陶瓷基板、導電漿墨)</t>
         </is>
       </c>
       <c r="B368" t="inlineStr"/>
       <c r="C368" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D368" t="n">
         <v>0</v>
@@ -15577,16 +15615,16 @@
         <v>0</v>
       </c>
       <c r="I368" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J368" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K368" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L368" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M368" t="n">
         <v>0</v>
@@ -15595,7 +15633,7 @@
     <row r="369">
       <c r="A369" s="1" t="inlineStr">
         <is>
-          <t>電阻器材料(氧化鋁陶瓷基板、導電漿墨)</t>
+          <t>面板</t>
         </is>
       </c>
       <c r="B369" t="inlineStr"/>
@@ -15636,7 +15674,7 @@
     <row r="370">
       <c r="A370" s="1" t="inlineStr">
         <is>
-          <t>面板</t>
+          <t>預拌混凝土</t>
         </is>
       </c>
       <c r="B370" t="inlineStr"/>
@@ -15659,10 +15697,10 @@
         <v>0</v>
       </c>
       <c r="I370" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J370" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K370" t="n">
         <v>0</v>
@@ -15677,12 +15715,10 @@
     <row r="371">
       <c r="A371" s="1" t="inlineStr">
         <is>
-          <t>預拌混凝土</t>
-        </is>
-      </c>
-      <c r="B371" t="n">
-        <v>0</v>
-      </c>
+          <t>領域方案</t>
+        </is>
+      </c>
+      <c r="B371" t="inlineStr"/>
       <c r="C371" t="n">
         <v>0</v>
       </c>
@@ -15720,10 +15756,12 @@
     <row r="372">
       <c r="A372" s="1" t="inlineStr">
         <is>
-          <t>領域方案</t>
-        </is>
-      </c>
-      <c r="B372" t="inlineStr"/>
+          <t>領域解決方案</t>
+        </is>
+      </c>
+      <c r="B372" t="n">
+        <v>0</v>
+      </c>
       <c r="C372" t="n">
         <v>0</v>
       </c>
@@ -15734,34 +15772,34 @@
         <v>0</v>
       </c>
       <c r="F372" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G372" t="n">
         <v>0</v>
       </c>
       <c r="H372" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I372" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J372" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K372" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L372" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M372" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="373">
       <c r="A373" s="1" t="inlineStr">
         <is>
-          <t>領域解決方案</t>
+          <t>頭顯裝置品牌廠</t>
         </is>
       </c>
       <c r="B373" t="inlineStr"/>
@@ -15781,28 +15819,28 @@
         <v>0</v>
       </c>
       <c r="H373" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I373" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J373" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K373" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L373" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M373" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="374">
       <c r="A374" s="1" t="inlineStr">
         <is>
-          <t>頭顯裝置品牌廠</t>
+          <t>顏染料</t>
         </is>
       </c>
       <c r="B374" t="inlineStr"/>
@@ -15813,25 +15851,25 @@
         <v>0</v>
       </c>
       <c r="E374" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F374" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G374" t="n">
         <v>0</v>
       </c>
       <c r="H374" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I374" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J374" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K374" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L374" t="n">
         <v>0</v>
@@ -15843,10 +15881,12 @@
     <row r="375">
       <c r="A375" s="1" t="inlineStr">
         <is>
-          <t>顏染料</t>
-        </is>
-      </c>
-      <c r="B375" t="inlineStr"/>
+          <t>顧問諮詢</t>
+        </is>
+      </c>
+      <c r="B375" t="n">
+        <v>0</v>
+      </c>
       <c r="C375" t="n">
         <v>0</v>
       </c>
@@ -15854,7 +15894,7 @@
         <v>0</v>
       </c>
       <c r="E375" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F375" t="n">
         <v>0</v>
@@ -15863,19 +15903,19 @@
         <v>0</v>
       </c>
       <c r="H375" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I375" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J375" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K375" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L375" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M375" t="n">
         <v>0</v>
@@ -15884,7 +15924,7 @@
     <row r="376">
       <c r="A376" s="1" t="inlineStr">
         <is>
-          <t>顧問諮詢</t>
+          <t>顯示卡</t>
         </is>
       </c>
       <c r="B376" t="inlineStr"/>
@@ -15901,22 +15941,22 @@
         <v>0</v>
       </c>
       <c r="G376" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H376" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I376" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J376" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K376" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L376" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M376" t="n">
         <v>0</v>
@@ -15925,7 +15965,7 @@
     <row r="377">
       <c r="A377" s="1" t="inlineStr">
         <is>
-          <t>顯示卡</t>
+          <t>顯示器模組</t>
         </is>
       </c>
       <c r="B377" t="inlineStr"/>
@@ -15942,16 +15982,16 @@
         <v>0</v>
       </c>
       <c r="G377" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H377" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I377" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J377" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K377" t="n">
         <v>0</v>
@@ -15966,12 +16006,10 @@
     <row r="378">
       <c r="A378" s="1" t="inlineStr">
         <is>
-          <t>顯示器模組</t>
-        </is>
-      </c>
-      <c r="B378" t="n">
-        <v>0</v>
-      </c>
+          <t>風場營造</t>
+        </is>
+      </c>
+      <c r="B378" t="inlineStr"/>
       <c r="C378" t="n">
         <v>0</v>
       </c>
@@ -15988,13 +16026,13 @@
         <v>0</v>
       </c>
       <c r="H378" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I378" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J378" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K378" t="n">
         <v>0</v>
@@ -16009,7 +16047,7 @@
     <row r="379">
       <c r="A379" s="1" t="inlineStr">
         <is>
-          <t>風場營造</t>
+          <t>風場規劃</t>
         </is>
       </c>
       <c r="B379" t="inlineStr"/>
@@ -16050,7 +16088,7 @@
     <row r="380">
       <c r="A380" s="1" t="inlineStr">
         <is>
-          <t>風場規劃</t>
+          <t>風場開發</t>
         </is>
       </c>
       <c r="B380" t="inlineStr"/>
@@ -16091,7 +16129,7 @@
     <row r="381">
       <c r="A381" s="1" t="inlineStr">
         <is>
-          <t>風場開發</t>
+          <t>風機維護</t>
         </is>
       </c>
       <c r="B381" t="inlineStr"/>
@@ -16132,21 +16170,21 @@
     <row r="382">
       <c r="A382" s="1" t="inlineStr">
         <is>
-          <t>風機維護</t>
+          <t>餐飲連鎖</t>
         </is>
       </c>
       <c r="B382" t="inlineStr"/>
       <c r="C382" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D382" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E382" t="n">
         <v>0</v>
       </c>
       <c r="F382" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G382" t="n">
         <v>0</v>
@@ -16158,7 +16196,7 @@
         <v>0</v>
       </c>
       <c r="J382" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K382" t="n">
         <v>0</v>
@@ -16167,18 +16205,18 @@
         <v>0</v>
       </c>
       <c r="M382" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="383">
       <c r="A383" s="1" t="inlineStr">
         <is>
-          <t>餐飲連鎖</t>
+          <t>驅動IC</t>
         </is>
       </c>
       <c r="B383" t="inlineStr"/>
       <c r="C383" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D383" t="n">
         <v>0</v>
@@ -16187,7 +16225,7 @@
         <v>0</v>
       </c>
       <c r="F383" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G383" t="n">
         <v>0</v>
@@ -16199,7 +16237,7 @@
         <v>0</v>
       </c>
       <c r="J383" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K383" t="n">
         <v>0</v>
@@ -16208,18 +16246,20 @@
         <v>0</v>
       </c>
       <c r="M383" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="384">
       <c r="A384" s="1" t="inlineStr">
         <is>
-          <t>驅動IC</t>
-        </is>
-      </c>
-      <c r="B384" t="inlineStr"/>
+          <t>高/低壓輸電設施</t>
+        </is>
+      </c>
+      <c r="B384" t="n">
+        <v>0</v>
+      </c>
       <c r="C384" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D384" t="n">
         <v>0</v>
@@ -16240,10 +16280,10 @@
         <v>0</v>
       </c>
       <c r="J384" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K384" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L384" t="n">
         <v>0</v>
@@ -16255,12 +16295,12 @@
     <row r="385">
       <c r="A385" s="1" t="inlineStr">
         <is>
-          <t>高/低壓輸電設施</t>
+          <t>高壓AMI</t>
         </is>
       </c>
       <c r="B385" t="inlineStr"/>
       <c r="C385" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D385" t="n">
         <v>0</v>
@@ -16281,10 +16321,10 @@
         <v>0</v>
       </c>
       <c r="J385" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K385" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L385" t="n">
         <v>0</v>
@@ -16296,7 +16336,7 @@
     <row r="386">
       <c r="A386" s="1" t="inlineStr">
         <is>
-          <t>高壓AMI</t>
+          <t>高爾夫球具業</t>
         </is>
       </c>
       <c r="B386" t="inlineStr"/>
@@ -16337,7 +16377,7 @@
     <row r="387">
       <c r="A387" s="1" t="inlineStr">
         <is>
-          <t>高爾夫球具業</t>
+          <t>齒輪箱</t>
         </is>
       </c>
       <c r="B387" t="inlineStr"/>
@@ -16372,47 +16412,6 @@
         <v>0</v>
       </c>
       <c r="M387" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="388">
-      <c r="A388" s="1" t="inlineStr">
-        <is>
-          <t>齒輪箱</t>
-        </is>
-      </c>
-      <c r="B388" t="inlineStr"/>
-      <c r="C388" t="n">
-        <v>0</v>
-      </c>
-      <c r="D388" t="n">
-        <v>0</v>
-      </c>
-      <c r="E388" t="n">
-        <v>0</v>
-      </c>
-      <c r="F388" t="n">
-        <v>0</v>
-      </c>
-      <c r="G388" t="n">
-        <v>0</v>
-      </c>
-      <c r="H388" t="n">
-        <v>0</v>
-      </c>
-      <c r="I388" t="n">
-        <v>0</v>
-      </c>
-      <c r="J388" t="n">
-        <v>0</v>
-      </c>
-      <c r="K388" t="n">
-        <v>0</v>
-      </c>
-      <c r="L388" t="n">
-        <v>0</v>
-      </c>
-      <c r="M388" t="n">
         <v>0</v>
       </c>
     </row>

--- a/Result/analyze_3.xlsx
+++ b/Result/analyze_3.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M387"/>
+  <dimension ref="A1:M388"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,57 +441,57 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
     </row>
@@ -559,13 +559,13 @@
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I3" t="n">
         <v>1</v>
       </c>
       <c r="J3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
@@ -667,37 +667,37 @@
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="n">
+        <v>3</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
+        <v>3</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
         <v>2</v>
       </c>
-      <c r="D6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" t="n">
-        <v>3</v>
-      </c>
-      <c r="G6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" t="n">
-        <v>3</v>
-      </c>
-      <c r="I6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J6" t="n">
-        <v>1</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>1</v>
-      </c>
       <c r="M6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -710,37 +710,37 @@
         <v>0</v>
       </c>
       <c r="C7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" t="n">
         <v>4</v>
       </c>
-      <c r="D7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E7" t="n">
-        <v>0</v>
-      </c>
       <c r="F7" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H7" t="n">
+        <v>2</v>
+      </c>
+      <c r="I7" t="n">
+        <v>5</v>
+      </c>
+      <c r="J7" t="n">
         <v>3</v>
       </c>
-      <c r="I7" t="n">
-        <v>2</v>
-      </c>
-      <c r="J7" t="n">
-        <v>5</v>
-      </c>
       <c r="K7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L7" t="n">
         <v>1</v>
       </c>
       <c r="M7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -757,25 +757,25 @@
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G8" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H8" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="I8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J8" t="n">
         <v>2</v>
       </c>
       <c r="K8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -794,37 +794,37 @@
         <v>0</v>
       </c>
       <c r="C9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E9" t="n">
+        <v>7</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" t="n">
+        <v>9</v>
+      </c>
+      <c r="H9" t="n">
+        <v>4</v>
+      </c>
+      <c r="I9" t="n">
+        <v>3</v>
+      </c>
+      <c r="J9" t="n">
         <v>2</v>
       </c>
-      <c r="D9" t="n">
-        <v>1</v>
-      </c>
-      <c r="E9" t="n">
-        <v>1</v>
-      </c>
-      <c r="F9" t="n">
-        <v>7</v>
-      </c>
-      <c r="G9" t="n">
-        <v>1</v>
-      </c>
-      <c r="H9" t="n">
-        <v>9</v>
-      </c>
-      <c r="I9" t="n">
-        <v>4</v>
-      </c>
-      <c r="J9" t="n">
-        <v>3</v>
-      </c>
       <c r="K9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -833,38 +833,36 @@
           <t>IC通路</t>
         </is>
       </c>
-      <c r="B10" t="n">
-        <v>0</v>
-      </c>
+      <c r="B10" t="inlineStr"/>
       <c r="C10" t="n">
         <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I10" t="n">
         <v>2</v>
       </c>
       <c r="J10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -884,16 +882,16 @@
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F11" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -905,10 +903,10 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -934,16 +932,16 @@
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
@@ -981,10 +979,10 @@
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -1124,10 +1122,10 @@
       </c>
       <c r="B17" t="inlineStr"/>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -1136,16 +1134,16 @@
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
@@ -1227,16 +1225,16 @@
         <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1268,10 +1266,10 @@
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
@@ -1286,39 +1284,41 @@
           <t>中、西藥製劑</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr"/>
+      <c r="B21" t="n">
+        <v>0</v>
+      </c>
       <c r="C21" t="n">
         <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G21" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -1350,7 +1350,7 @@
         <v>1</v>
       </c>
       <c r="J22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
@@ -1379,10 +1379,10 @@
         <v>0</v>
       </c>
       <c r="F23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H23" t="n">
         <v>0</v>
@@ -1394,10 +1394,10 @@
         <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
         <v>0</v>
@@ -1409,7 +1409,9 @@
           <t>主/被動元件</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr"/>
+      <c r="B24" t="n">
+        <v>0</v>
+      </c>
       <c r="C24" t="n">
         <v>0</v>
       </c>
@@ -1429,13 +1431,13 @@
         <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J24" t="n">
         <v>1</v>
       </c>
       <c r="K24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
@@ -1461,7 +1463,7 @@
         <v>0</v>
       </c>
       <c r="F25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G25" t="n">
         <v>1</v>
@@ -1473,7 +1475,7 @@
         <v>1</v>
       </c>
       <c r="J25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K25" t="n">
         <v>0</v>
@@ -1540,16 +1542,16 @@
         <v>0</v>
       </c>
       <c r="E27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H27" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I27" t="n">
         <v>0</v>
@@ -1561,10 +1563,10 @@
         <v>0</v>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -1675,13 +1677,13 @@
         <v>0</v>
       </c>
       <c r="I30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K30" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L30" t="n">
         <v>0</v>
@@ -1710,19 +1712,19 @@
         <v>0</v>
       </c>
       <c r="G31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K31" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
@@ -1737,12 +1739,14 @@
           <t>休閒車業</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr"/>
+      <c r="B32" t="n">
+        <v>0</v>
+      </c>
       <c r="C32" t="n">
         <v>0</v>
       </c>
       <c r="D32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E32" t="n">
         <v>0</v>
@@ -1754,22 +1758,22 @@
         <v>1</v>
       </c>
       <c r="H32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I32" t="n">
         <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33">
@@ -1778,11 +1782,9 @@
           <t>伺服器</t>
         </is>
       </c>
-      <c r="B33" t="n">
-        <v>0</v>
-      </c>
+      <c r="B33" t="inlineStr"/>
       <c r="C33" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D33" t="n">
         <v>0</v>
@@ -1791,19 +1793,19 @@
         <v>0</v>
       </c>
       <c r="F33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I33" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K33" t="n">
         <v>0</v>
@@ -1823,7 +1825,7 @@
       </c>
       <c r="B34" t="inlineStr"/>
       <c r="C34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D34" t="n">
         <v>0</v>
@@ -1873,13 +1875,13 @@
         <v>0</v>
       </c>
       <c r="F35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G35" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H35" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I35" t="n">
         <v>0</v>
@@ -1999,16 +2001,16 @@
         <v>0</v>
       </c>
       <c r="G38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K38" t="n">
         <v>0</v>
@@ -2125,10 +2127,10 @@
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -2163,10 +2165,10 @@
         <v>0</v>
       </c>
       <c r="G42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H42" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I42" t="n">
         <v>1</v>
@@ -2175,7 +2177,7 @@
         <v>1</v>
       </c>
       <c r="K42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L42" t="n">
         <v>0</v>
@@ -2204,10 +2206,10 @@
         <v>0</v>
       </c>
       <c r="G43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I43" t="n">
         <v>0</v>
@@ -2231,7 +2233,9 @@
           <t>光學鏡片、鏡頭</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr"/>
+      <c r="B44" t="n">
+        <v>0</v>
+      </c>
       <c r="C44" t="n">
         <v>0</v>
       </c>
@@ -2239,16 +2243,16 @@
         <v>0</v>
       </c>
       <c r="E44" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F44" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I44" t="n">
         <v>1</v>
@@ -2257,7 +2261,7 @@
         <v>1</v>
       </c>
       <c r="K44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L44" t="n">
         <v>0</v>
@@ -2289,10 +2293,10 @@
         <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -2330,13 +2334,13 @@
         <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I46" t="n">
         <v>1</v>
       </c>
       <c r="J46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K46" t="n">
         <v>0</v>
@@ -2371,13 +2375,13 @@
         <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I47" t="n">
         <v>1</v>
       </c>
       <c r="J47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K47" t="n">
         <v>0</v>
@@ -2438,37 +2442,37 @@
       </c>
       <c r="B49" t="inlineStr"/>
       <c r="C49" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F49" t="n">
+        <v>1</v>
+      </c>
+      <c r="G49" t="n">
         <v>2</v>
       </c>
-      <c r="G49" t="n">
-        <v>1</v>
-      </c>
       <c r="H49" t="n">
+        <v>1</v>
+      </c>
+      <c r="I49" t="n">
         <v>2</v>
-      </c>
-      <c r="I49" t="n">
-        <v>1</v>
       </c>
       <c r="J49" t="n">
         <v>2</v>
       </c>
       <c r="K49" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L49" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M49" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50">
@@ -2522,31 +2526,31 @@
         <v>0</v>
       </c>
       <c r="C51" t="n">
+        <v>4</v>
+      </c>
+      <c r="D51" t="n">
+        <v>3</v>
+      </c>
+      <c r="E51" t="n">
+        <v>4</v>
+      </c>
+      <c r="F51" t="n">
+        <v>2</v>
+      </c>
+      <c r="G51" t="n">
+        <v>1</v>
+      </c>
+      <c r="H51" t="n">
+        <v>2</v>
+      </c>
+      <c r="I51" t="n">
+        <v>0</v>
+      </c>
+      <c r="J51" t="n">
         <v>6</v>
       </c>
-      <c r="D51" t="n">
-        <v>5</v>
-      </c>
-      <c r="E51" t="n">
-        <v>3</v>
-      </c>
-      <c r="F51" t="n">
-        <v>3</v>
-      </c>
-      <c r="G51" t="n">
-        <v>3</v>
-      </c>
-      <c r="H51" t="n">
-        <v>1</v>
-      </c>
-      <c r="I51" t="n">
-        <v>2</v>
-      </c>
-      <c r="J51" t="n">
-        <v>0</v>
-      </c>
       <c r="K51" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="L51" t="n">
         <v>1</v>
@@ -2602,9 +2606,7 @@
           <t>其他零組件</t>
         </is>
       </c>
-      <c r="B53" t="n">
-        <v>0</v>
-      </c>
+      <c r="B53" t="inlineStr"/>
       <c r="C53" t="n">
         <v>0</v>
       </c>
@@ -2615,19 +2617,19 @@
         <v>0</v>
       </c>
       <c r="F53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G53" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H53" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I53" t="n">
         <v>1</v>
       </c>
       <c r="J53" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K53" t="n">
         <v>2</v>
@@ -2636,7 +2638,7 @@
         <v>2</v>
       </c>
       <c r="M53" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -2645,20 +2647,18 @@
           <t>其他電子產品及電子服務產業</t>
         </is>
       </c>
-      <c r="B54" t="n">
-        <v>0</v>
-      </c>
+      <c r="B54" t="inlineStr"/>
       <c r="C54" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D54" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E54" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F54" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G54" t="n">
         <v>1</v>
@@ -2667,16 +2667,16 @@
         <v>1</v>
       </c>
       <c r="I54" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J54" t="n">
         <v>4</v>
       </c>
       <c r="K54" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M54" t="n">
         <v>1</v>
@@ -2692,34 +2692,34 @@
         <v>0</v>
       </c>
       <c r="C55" t="n">
+        <v>0</v>
+      </c>
+      <c r="D55" t="n">
+        <v>1</v>
+      </c>
+      <c r="E55" t="n">
         <v>2</v>
       </c>
-      <c r="D55" t="n">
-        <v>1</v>
-      </c>
-      <c r="E55" t="n">
-        <v>1</v>
-      </c>
       <c r="F55" t="n">
+        <v>3</v>
+      </c>
+      <c r="G55" t="n">
+        <v>1</v>
+      </c>
+      <c r="H55" t="n">
         <v>2</v>
       </c>
-      <c r="G55" t="n">
+      <c r="I55" t="n">
         <v>4</v>
       </c>
-      <c r="H55" t="n">
-        <v>1</v>
-      </c>
-      <c r="I55" t="n">
+      <c r="J55" t="n">
         <v>2</v>
       </c>
-      <c r="J55" t="n">
-        <v>4</v>
-      </c>
       <c r="K55" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M55" t="n">
         <v>0</v>
@@ -2733,37 +2733,37 @@
       </c>
       <c r="B56" t="inlineStr"/>
       <c r="C56" t="n">
+        <v>0</v>
+      </c>
+      <c r="D56" t="n">
+        <v>0</v>
+      </c>
+      <c r="E56" t="n">
+        <v>4</v>
+      </c>
+      <c r="F56" t="n">
+        <v>3</v>
+      </c>
+      <c r="G56" t="n">
+        <v>5</v>
+      </c>
+      <c r="H56" t="n">
+        <v>3</v>
+      </c>
+      <c r="I56" t="n">
         <v>2</v>
       </c>
-      <c r="D56" t="n">
-        <v>0</v>
-      </c>
-      <c r="E56" t="n">
-        <v>0</v>
-      </c>
-      <c r="F56" t="n">
+      <c r="J56" t="n">
         <v>4</v>
       </c>
-      <c r="G56" t="n">
-        <v>3</v>
-      </c>
-      <c r="H56" t="n">
-        <v>5</v>
-      </c>
-      <c r="I56" t="n">
-        <v>3</v>
-      </c>
-      <c r="J56" t="n">
+      <c r="K56" t="n">
+        <v>1</v>
+      </c>
+      <c r="L56" t="n">
         <v>2</v>
       </c>
-      <c r="K56" t="n">
-        <v>4</v>
-      </c>
-      <c r="L56" t="n">
-        <v>1</v>
-      </c>
       <c r="M56" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -2815,31 +2815,31 @@
       </c>
       <c r="B58" t="inlineStr"/>
       <c r="C58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I58" t="n">
         <v>0</v>
       </c>
       <c r="J58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L58" t="n">
         <v>0</v>
@@ -2856,7 +2856,7 @@
       </c>
       <c r="B59" t="inlineStr"/>
       <c r="C59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D59" t="n">
         <v>0</v>
@@ -2865,10 +2865,10 @@
         <v>0</v>
       </c>
       <c r="F59" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H59" t="n">
         <v>0</v>
@@ -2877,10 +2877,10 @@
         <v>0</v>
       </c>
       <c r="J59" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L59" t="n">
         <v>0</v>
@@ -2900,10 +2900,10 @@
         <v>0</v>
       </c>
       <c r="D60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F60" t="n">
         <v>0</v>
@@ -2918,10 +2918,10 @@
         <v>0</v>
       </c>
       <c r="J60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L60" t="n">
         <v>0</v>
@@ -3018,9 +3018,7 @@
           <t>分析工具</t>
         </is>
       </c>
-      <c r="B63" t="n">
-        <v>0</v>
-      </c>
+      <c r="B63" t="inlineStr"/>
       <c r="C63" t="n">
         <v>0</v>
       </c>
@@ -3034,7 +3032,7 @@
         <v>0</v>
       </c>
       <c r="G63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H63" t="n">
         <v>1</v>
@@ -3046,7 +3044,7 @@
         <v>1</v>
       </c>
       <c r="K63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L63" t="n">
         <v>0</v>
@@ -3063,7 +3061,7 @@
       </c>
       <c r="B64" t="inlineStr"/>
       <c r="C64" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D64" t="n">
         <v>0</v>
@@ -3204,10 +3202,10 @@
         <v>0</v>
       </c>
       <c r="I67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K67" t="n">
         <v>0</v>
@@ -3245,10 +3243,10 @@
         <v>0</v>
       </c>
       <c r="I68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K68" t="n">
         <v>0</v>
@@ -3274,10 +3272,10 @@
         <v>0</v>
       </c>
       <c r="E69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
@@ -3353,10 +3351,10 @@
         <v>0</v>
       </c>
       <c r="D71" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F71" t="n">
         <v>0</v>
@@ -3371,16 +3369,16 @@
         <v>0</v>
       </c>
       <c r="J71" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K71" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L71" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="72">
@@ -3391,7 +3389,7 @@
       </c>
       <c r="B72" t="inlineStr"/>
       <c r="C72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D72" t="n">
         <v>0</v>
@@ -3412,16 +3410,16 @@
         <v>0</v>
       </c>
       <c r="J72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="73">
@@ -3532,13 +3530,13 @@
         <v>0</v>
       </c>
       <c r="I75" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J75" t="n">
         <v>1</v>
       </c>
       <c r="K75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L75" t="n">
         <v>0</v>
@@ -3558,7 +3556,7 @@
         <v>1</v>
       </c>
       <c r="D76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E76" t="n">
         <v>0</v>
@@ -3570,13 +3568,13 @@
         <v>0</v>
       </c>
       <c r="H76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I76" t="n">
         <v>1</v>
       </c>
       <c r="J76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K76" t="n">
         <v>0</v>
@@ -3635,7 +3633,9 @@
           <t>原材料</t>
         </is>
       </c>
-      <c r="B78" t="inlineStr"/>
+      <c r="B78" t="n">
+        <v>0</v>
+      </c>
       <c r="C78" t="n">
         <v>0</v>
       </c>
@@ -3646,25 +3646,25 @@
         <v>0</v>
       </c>
       <c r="F78" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G78" t="n">
         <v>1</v>
       </c>
       <c r="H78" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I78" t="n">
         <v>0</v>
       </c>
       <c r="J78" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K78" t="n">
+        <v>1</v>
+      </c>
+      <c r="L78" t="n">
         <v>2</v>
-      </c>
-      <c r="L78" t="n">
-        <v>1</v>
       </c>
       <c r="M78" t="n">
         <v>2</v>
@@ -3737,10 +3737,10 @@
         <v>0</v>
       </c>
       <c r="I80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J80" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K80" t="n">
         <v>0</v>
@@ -3822,10 +3822,10 @@
         <v>0</v>
       </c>
       <c r="J82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L82" t="n">
         <v>0</v>
@@ -3842,37 +3842,37 @@
       </c>
       <c r="B83" t="inlineStr"/>
       <c r="C83" t="n">
+        <v>0</v>
+      </c>
+      <c r="D83" t="n">
+        <v>1</v>
+      </c>
+      <c r="E83" t="n">
+        <v>1</v>
+      </c>
+      <c r="F83" t="n">
+        <v>0</v>
+      </c>
+      <c r="G83" t="n">
+        <v>1</v>
+      </c>
+      <c r="H83" t="n">
+        <v>0</v>
+      </c>
+      <c r="I83" t="n">
         <v>2</v>
       </c>
-      <c r="D83" t="n">
-        <v>0</v>
-      </c>
-      <c r="E83" t="n">
-        <v>1</v>
-      </c>
-      <c r="F83" t="n">
-        <v>1</v>
-      </c>
-      <c r="G83" t="n">
-        <v>0</v>
-      </c>
-      <c r="H83" t="n">
-        <v>1</v>
-      </c>
-      <c r="I83" t="n">
-        <v>0</v>
-      </c>
       <c r="J83" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K83" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L83" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M83" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="84">
@@ -3983,16 +3983,16 @@
         <v>0</v>
       </c>
       <c r="I86" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J86" t="n">
         <v>1</v>
       </c>
       <c r="K86" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L86" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M86" t="n">
         <v>0</v>
@@ -4018,25 +4018,25 @@
         <v>0</v>
       </c>
       <c r="G87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I87" t="n">
         <v>0</v>
       </c>
       <c r="J87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="88">
@@ -4065,10 +4065,10 @@
         <v>0</v>
       </c>
       <c r="I88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K88" t="n">
         <v>0</v>
@@ -4086,7 +4086,9 @@
           <t>塑膠製品</t>
         </is>
       </c>
-      <c r="B89" t="inlineStr"/>
+      <c r="B89" t="n">
+        <v>0</v>
+      </c>
       <c r="C89" t="n">
         <v>1</v>
       </c>
@@ -4097,28 +4099,28 @@
         <v>1</v>
       </c>
       <c r="F89" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G89" t="n">
         <v>1</v>
       </c>
       <c r="H89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I89" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J89" t="n">
         <v>1</v>
       </c>
       <c r="K89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L89" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="90">
@@ -4185,13 +4187,13 @@
         <v>0</v>
       </c>
       <c r="H91" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I91" t="n">
         <v>1</v>
       </c>
       <c r="J91" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K91" t="n">
         <v>0</v>
@@ -4213,13 +4215,13 @@
         <v>0</v>
       </c>
       <c r="C92" t="n">
+        <v>0</v>
+      </c>
+      <c r="D92" t="n">
         <v>2</v>
       </c>
-      <c r="D92" t="n">
-        <v>0</v>
-      </c>
       <c r="E92" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F92" t="n">
         <v>1</v>
@@ -4228,19 +4230,19 @@
         <v>1</v>
       </c>
       <c r="H92" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I92" t="n">
         <v>0</v>
       </c>
       <c r="J92" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K92" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L92" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M92" t="n">
         <v>1</v>
@@ -4252,7 +4254,9 @@
           <t>天然瓦斯供應</t>
         </is>
       </c>
-      <c r="B93" t="inlineStr"/>
+      <c r="B93" t="n">
+        <v>0</v>
+      </c>
       <c r="C93" t="n">
         <v>0</v>
       </c>
@@ -4334,9 +4338,7 @@
           <t>太陽能發電設備/系統及系統工程</t>
         </is>
       </c>
-      <c r="B95" t="n">
-        <v>0</v>
-      </c>
+      <c r="B95" t="inlineStr"/>
       <c r="C95" t="n">
         <v>0</v>
       </c>
@@ -4359,10 +4361,10 @@
         <v>0</v>
       </c>
       <c r="J95" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K95" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L95" t="n">
         <v>0</v>
@@ -4400,10 +4402,10 @@
         <v>0</v>
       </c>
       <c r="J96" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K96" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L96" t="n">
         <v>0</v>
@@ -4420,7 +4422,7 @@
       </c>
       <c r="B97" t="inlineStr"/>
       <c r="C97" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D97" t="n">
         <v>0</v>
@@ -4459,11 +4461,9 @@
           <t>太陽能電池模組</t>
         </is>
       </c>
-      <c r="B98" t="n">
-        <v>0</v>
-      </c>
+      <c r="B98" t="inlineStr"/>
       <c r="C98" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D98" t="n">
         <v>0</v>
@@ -4604,16 +4604,16 @@
         <v>0</v>
       </c>
       <c r="I101" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J101" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K101" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L101" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M101" t="n">
         <v>0</v>
@@ -4627,10 +4627,10 @@
       </c>
       <c r="B102" t="inlineStr"/>
       <c r="C102" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D102" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E102" t="n">
         <v>1</v>
@@ -4642,19 +4642,19 @@
         <v>1</v>
       </c>
       <c r="H102" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I102" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J102" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K102" t="n">
         <v>1</v>
       </c>
       <c r="L102" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M102" t="n">
         <v>0</v>
@@ -4707,9 +4707,7 @@
           <t>封裝/模組</t>
         </is>
       </c>
-      <c r="B104" t="n">
-        <v>0</v>
-      </c>
+      <c r="B104" t="inlineStr"/>
       <c r="C104" t="n">
         <v>0</v>
       </c>
@@ -4729,16 +4727,16 @@
         <v>0</v>
       </c>
       <c r="I104" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J104" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K104" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L104" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M104" t="n">
         <v>0</v>
@@ -4752,7 +4750,7 @@
       </c>
       <c r="B105" t="inlineStr"/>
       <c r="C105" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D105" t="n">
         <v>0</v>
@@ -4764,25 +4762,25 @@
         <v>0</v>
       </c>
       <c r="G105" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H105" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I105" t="n">
         <v>1</v>
       </c>
       <c r="J105" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K105" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L105" t="n">
         <v>1</v>
       </c>
       <c r="M105" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="106">
@@ -4799,31 +4797,31 @@
         <v>0</v>
       </c>
       <c r="E106" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F106" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G106" t="n">
         <v>0</v>
       </c>
       <c r="H106" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I106" t="n">
+        <v>1</v>
+      </c>
+      <c r="J106" t="n">
         <v>2</v>
       </c>
-      <c r="J106" t="n">
-        <v>1</v>
-      </c>
       <c r="K106" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L106" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M106" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="107">
@@ -4914,7 +4912,9 @@
           <t>工業用紙</t>
         </is>
       </c>
-      <c r="B109" t="inlineStr"/>
+      <c r="B109" t="n">
+        <v>0</v>
+      </c>
       <c r="C109" t="n">
         <v>0</v>
       </c>
@@ -4955,7 +4955,9 @@
           <t>工業用設備</t>
         </is>
       </c>
-      <c r="B110" t="inlineStr"/>
+      <c r="B110" t="n">
+        <v>0</v>
+      </c>
       <c r="C110" t="n">
         <v>0</v>
       </c>
@@ -4972,10 +4974,10 @@
         <v>0</v>
       </c>
       <c r="H110" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I110" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -4996,36 +4998,38 @@
           <t>工業電腦</t>
         </is>
       </c>
-      <c r="B111" t="inlineStr"/>
+      <c r="B111" t="n">
+        <v>0</v>
+      </c>
       <c r="C111" t="n">
         <v>1</v>
       </c>
       <c r="D111" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E111" t="n">
+        <v>1</v>
+      </c>
+      <c r="F111" t="n">
         <v>2</v>
       </c>
-      <c r="F111" t="n">
-        <v>1</v>
-      </c>
       <c r="G111" t="n">
+        <v>0</v>
+      </c>
+      <c r="H111" t="n">
         <v>2</v>
       </c>
-      <c r="H111" t="n">
-        <v>0</v>
-      </c>
       <c r="I111" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J111" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K111" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L111" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M111" t="n">
         <v>0</v>
@@ -5042,7 +5046,7 @@
         <v>1</v>
       </c>
       <c r="D112" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E112" t="n">
         <v>0</v>
@@ -5060,10 +5064,10 @@
         <v>0</v>
       </c>
       <c r="J112" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K112" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L112" t="n">
         <v>0</v>
@@ -5083,7 +5087,7 @@
         <v>1</v>
       </c>
       <c r="D113" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E113" t="n">
         <v>0</v>
@@ -5101,10 +5105,10 @@
         <v>0</v>
       </c>
       <c r="J113" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K113" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L113" t="n">
         <v>0</v>
@@ -5326,10 +5330,10 @@
       </c>
       <c r="B119" t="inlineStr"/>
       <c r="C119" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D119" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E119" t="n">
         <v>0</v>
@@ -5338,16 +5342,16 @@
         <v>0</v>
       </c>
       <c r="G119" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H119" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I119" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J119" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K119" t="n">
         <v>0</v>
@@ -5370,34 +5374,34 @@
         <v>1</v>
       </c>
       <c r="D120" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E120" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F120" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G120" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H120" t="n">
         <v>1</v>
       </c>
       <c r="I120" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J120" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K120" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L120" t="n">
         <v>1</v>
       </c>
       <c r="M120" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="121">
@@ -5406,21 +5410,23 @@
           <t>建設業</t>
         </is>
       </c>
-      <c r="B121" t="inlineStr"/>
+      <c r="B121" t="n">
+        <v>0</v>
+      </c>
       <c r="C121" t="n">
         <v>0</v>
       </c>
       <c r="D121" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E121" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F121" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G121" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H121" t="n">
         <v>0</v>
@@ -5429,10 +5435,10 @@
         <v>0</v>
       </c>
       <c r="J121" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K121" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L121" t="n">
         <v>0</v>
@@ -5546,16 +5552,16 @@
         <v>0</v>
       </c>
       <c r="H124" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I124" t="n">
         <v>0</v>
       </c>
       <c r="J124" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K124" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L124" t="n">
         <v>0</v>
@@ -5619,19 +5625,19 @@
         <v>0</v>
       </c>
       <c r="E126" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F126" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G126" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H126" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I126" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -5669,10 +5675,10 @@
         <v>0</v>
       </c>
       <c r="H127" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I127" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -5697,10 +5703,10 @@
         <v>0</v>
       </c>
       <c r="C128" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D128" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E128" t="n">
         <v>0</v>
@@ -5709,7 +5715,7 @@
         <v>0</v>
       </c>
       <c r="G128" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H128" t="n">
         <v>2</v>
@@ -5718,16 +5724,16 @@
         <v>2</v>
       </c>
       <c r="J128" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K128" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L128" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M128" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="129">
@@ -5736,9 +5742,7 @@
           <t>應用軟體</t>
         </is>
       </c>
-      <c r="B129" t="n">
-        <v>0</v>
-      </c>
+      <c r="B129" t="inlineStr"/>
       <c r="C129" t="n">
         <v>0</v>
       </c>
@@ -5752,7 +5756,7 @@
         <v>0</v>
       </c>
       <c r="G129" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H129" t="n">
         <v>1</v>
@@ -5764,7 +5768,7 @@
         <v>1</v>
       </c>
       <c r="K129" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L129" t="n">
         <v>0</v>
@@ -5799,10 +5803,10 @@
         <v>0</v>
       </c>
       <c r="I130" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J130" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K130" t="n">
         <v>0</v>
@@ -5820,7 +5824,9 @@
           <t>成衣及其它家居紡織類品</t>
         </is>
       </c>
-      <c r="B131" t="inlineStr"/>
+      <c r="B131" t="n">
+        <v>0</v>
+      </c>
       <c r="C131" t="n">
         <v>0</v>
       </c>
@@ -5831,10 +5837,10 @@
         <v>0</v>
       </c>
       <c r="F131" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G131" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H131" t="n">
         <v>0</v>
@@ -5843,7 +5849,7 @@
         <v>0</v>
       </c>
       <c r="J131" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K131" t="n">
         <v>1</v>
@@ -5852,7 +5858,7 @@
         <v>1</v>
       </c>
       <c r="M131" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="132">
@@ -5863,16 +5869,16 @@
       </c>
       <c r="B132" t="inlineStr"/>
       <c r="C132" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D132" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E132" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F132" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G132" t="n">
         <v>0</v>
@@ -5887,10 +5893,10 @@
         <v>0</v>
       </c>
       <c r="K132" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L132" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M132" t="n">
         <v>0</v>
@@ -5922,10 +5928,10 @@
         <v>0</v>
       </c>
       <c r="I133" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J133" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K133" t="n">
         <v>0</v>
@@ -6083,10 +6089,10 @@
         <v>0</v>
       </c>
       <c r="H137" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I137" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -6109,10 +6115,10 @@
       </c>
       <c r="B138" t="inlineStr"/>
       <c r="C138" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D138" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E138" t="n">
         <v>0</v>
@@ -6150,13 +6156,13 @@
       </c>
       <c r="B139" t="inlineStr"/>
       <c r="C139" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D139" t="n">
         <v>0</v>
       </c>
       <c r="E139" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F139" t="n">
         <v>1</v>
@@ -6171,7 +6177,7 @@
         <v>1</v>
       </c>
       <c r="J139" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K139" t="n">
         <v>0</v>
@@ -6250,7 +6256,7 @@
         <v>0</v>
       </c>
       <c r="I141" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J141" t="n">
         <v>1</v>
@@ -6259,7 +6265,7 @@
         <v>1</v>
       </c>
       <c r="L141" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M141" t="n">
         <v>0</v>
@@ -6332,10 +6338,10 @@
         <v>0</v>
       </c>
       <c r="I143" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J143" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K143" t="n">
         <v>0</v>
@@ -6355,7 +6361,7 @@
       </c>
       <c r="B144" t="inlineStr"/>
       <c r="C144" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D144" t="n">
         <v>0</v>
@@ -6373,19 +6379,19 @@
         <v>0</v>
       </c>
       <c r="I144" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J144" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K144" t="n">
         <v>0</v>
       </c>
       <c r="L144" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M144" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="145">
@@ -6414,16 +6420,16 @@
         <v>0</v>
       </c>
       <c r="I145" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J145" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K145" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L145" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M145" t="n">
         <v>0</v>
@@ -6452,10 +6458,10 @@
         <v>0</v>
       </c>
       <c r="H146" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I146" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -6496,16 +6502,16 @@
         <v>0</v>
       </c>
       <c r="I147" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J147" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K147" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L147" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M147" t="n">
         <v>0</v>
@@ -6519,22 +6525,22 @@
       </c>
       <c r="B148" t="inlineStr"/>
       <c r="C148" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D148" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E148" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F148" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G148" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H148" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I148" t="n">
         <v>0</v>
@@ -6558,7 +6564,9 @@
           <t>文化用紙</t>
         </is>
       </c>
-      <c r="B149" t="inlineStr"/>
+      <c r="B149" t="n">
+        <v>0</v>
+      </c>
       <c r="C149" t="n">
         <v>0</v>
       </c>
@@ -6584,10 +6592,10 @@
         <v>0</v>
       </c>
       <c r="K149" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L149" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M149" t="n">
         <v>0</v>
@@ -6604,13 +6612,13 @@
         <v>0</v>
       </c>
       <c r="D150" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E150" t="n">
         <v>1</v>
       </c>
       <c r="F150" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G150" t="n">
         <v>0</v>
@@ -6645,10 +6653,10 @@
         <v>0</v>
       </c>
       <c r="D151" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E151" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F151" t="n">
         <v>0</v>
@@ -6657,19 +6665,19 @@
         <v>0</v>
       </c>
       <c r="H151" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I151" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
       </c>
       <c r="K151" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L151" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M151" t="n">
         <v>0</v>
@@ -6681,7 +6689,9 @@
           <t>晶片組</t>
         </is>
       </c>
-      <c r="B152" t="inlineStr"/>
+      <c r="B152" t="n">
+        <v>0</v>
+      </c>
       <c r="C152" t="n">
         <v>0</v>
       </c>
@@ -6698,13 +6708,13 @@
         <v>0</v>
       </c>
       <c r="H152" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I152" t="n">
         <v>1</v>
       </c>
       <c r="J152" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K152" t="n">
         <v>0</v>
@@ -6724,10 +6734,10 @@
       </c>
       <c r="B153" t="inlineStr"/>
       <c r="C153" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D153" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E153" t="n">
         <v>0</v>
@@ -6742,19 +6752,19 @@
         <v>0</v>
       </c>
       <c r="I153" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J153" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K153" t="n">
         <v>0</v>
       </c>
       <c r="L153" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M153" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="154">
@@ -6763,11 +6773,9 @@
           <t>有線通訊設備(如電話機、傳真機)</t>
         </is>
       </c>
-      <c r="B154" t="n">
-        <v>0</v>
-      </c>
+      <c r="B154" t="inlineStr"/>
       <c r="C154" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D154" t="n">
         <v>0</v>
@@ -6788,10 +6796,10 @@
         <v>0</v>
       </c>
       <c r="J154" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K154" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L154" t="n">
         <v>0</v>
@@ -6861,25 +6869,25 @@
         <v>0</v>
       </c>
       <c r="G156" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H156" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I156" t="n">
         <v>0</v>
       </c>
       <c r="J156" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K156" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L156" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M156" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="157">
@@ -6896,10 +6904,10 @@
         <v>0</v>
       </c>
       <c r="E157" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F157" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G157" t="n">
         <v>0</v>
@@ -6908,13 +6916,13 @@
         <v>0</v>
       </c>
       <c r="I157" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J157" t="n">
         <v>2</v>
       </c>
       <c r="K157" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L157" t="n">
         <v>0</v>
@@ -6929,9 +6937,7 @@
           <t>桌上型電腦</t>
         </is>
       </c>
-      <c r="B158" t="n">
-        <v>0</v>
-      </c>
+      <c r="B158" t="inlineStr"/>
       <c r="C158" t="n">
         <v>0</v>
       </c>
@@ -6942,19 +6948,19 @@
         <v>0</v>
       </c>
       <c r="F158" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G158" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H158" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I158" t="n">
         <v>1</v>
       </c>
       <c r="J158" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K158" t="n">
         <v>0</v>
@@ -7033,10 +7039,10 @@
         <v>0</v>
       </c>
       <c r="I160" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J160" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K160" t="n">
         <v>0</v>
@@ -7074,10 +7080,10 @@
         <v>0</v>
       </c>
       <c r="I161" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J161" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K161" t="n">
         <v>0</v>
@@ -7095,9 +7101,7 @@
           <t>機器學習</t>
         </is>
       </c>
-      <c r="B162" t="n">
-        <v>0</v>
-      </c>
+      <c r="B162" t="inlineStr"/>
       <c r="C162" t="n">
         <v>0</v>
       </c>
@@ -7117,19 +7121,19 @@
         <v>0</v>
       </c>
       <c r="I162" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J162" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K162" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L162" t="n">
         <v>1</v>
       </c>
       <c r="M162" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="163">
@@ -7158,13 +7162,13 @@
         <v>0</v>
       </c>
       <c r="I163" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J163" t="n">
         <v>1</v>
       </c>
       <c r="K163" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L163" t="n">
         <v>0</v>
@@ -7196,13 +7200,13 @@
         <v>0</v>
       </c>
       <c r="H164" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I164" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J164" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K164" t="n">
         <v>0</v>
@@ -7234,22 +7238,22 @@
         <v>0</v>
       </c>
       <c r="G165" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H165" t="n">
         <v>1</v>
       </c>
       <c r="I165" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J165" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K165" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L165" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M165" t="n">
         <v>0</v>
@@ -7266,7 +7270,7 @@
         <v>1</v>
       </c>
       <c r="D166" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E166" t="n">
         <v>0</v>
@@ -7284,10 +7288,10 @@
         <v>0</v>
       </c>
       <c r="J166" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K166" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L166" t="n">
         <v>0</v>
@@ -7302,35 +7306,33 @@
           <t>機電系統工程</t>
         </is>
       </c>
-      <c r="B167" t="n">
-        <v>0</v>
-      </c>
+      <c r="B167" t="inlineStr"/>
       <c r="C167" t="n">
         <v>0</v>
       </c>
       <c r="D167" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E167" t="n">
         <v>1</v>
       </c>
       <c r="F167" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G167" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H167" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I167" t="n">
         <v>0</v>
       </c>
       <c r="J167" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K167" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L167" t="n">
         <v>0</v>
@@ -7517,10 +7519,10 @@
         <v>0</v>
       </c>
       <c r="E172" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F172" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G172" t="n">
         <v>0</v>
@@ -7532,10 +7534,10 @@
         <v>0</v>
       </c>
       <c r="J172" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K172" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L172" t="n">
         <v>0</v>
@@ -7555,7 +7557,7 @@
         <v>1</v>
       </c>
       <c r="D173" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E173" t="n">
         <v>0</v>
@@ -7570,10 +7572,10 @@
         <v>0</v>
       </c>
       <c r="I173" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J173" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K173" t="n">
         <v>0</v>
@@ -7591,9 +7593,7 @@
           <t>海陸空大眾運輸</t>
         </is>
       </c>
-      <c r="B174" t="n">
-        <v>0</v>
-      </c>
+      <c r="B174" t="inlineStr"/>
       <c r="C174" t="n">
         <v>0</v>
       </c>
@@ -7675,7 +7675,9 @@
           <t>清潔用品</t>
         </is>
       </c>
-      <c r="B176" t="inlineStr"/>
+      <c r="B176" t="n">
+        <v>0</v>
+      </c>
       <c r="C176" t="n">
         <v>0</v>
       </c>
@@ -7716,7 +7718,9 @@
           <t>濾波器、振盪器</t>
         </is>
       </c>
-      <c r="B177" t="inlineStr"/>
+      <c r="B177" t="n">
+        <v>0</v>
+      </c>
       <c r="C177" t="n">
         <v>0</v>
       </c>
@@ -7733,7 +7737,7 @@
         <v>0</v>
       </c>
       <c r="H177" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I177" t="n">
         <v>1</v>
@@ -7742,10 +7746,10 @@
         <v>1</v>
       </c>
       <c r="K177" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L177" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M177" t="n">
         <v>0</v>
@@ -7800,37 +7804,37 @@
       </c>
       <c r="B179" t="inlineStr"/>
       <c r="C179" t="n">
+        <v>1</v>
+      </c>
+      <c r="D179" t="n">
+        <v>1</v>
+      </c>
+      <c r="E179" t="n">
+        <v>1</v>
+      </c>
+      <c r="F179" t="n">
+        <v>1</v>
+      </c>
+      <c r="G179" t="n">
+        <v>3</v>
+      </c>
+      <c r="H179" t="n">
         <v>2</v>
       </c>
-      <c r="D179" t="n">
-        <v>1</v>
-      </c>
-      <c r="E179" t="n">
-        <v>1</v>
-      </c>
-      <c r="F179" t="n">
-        <v>1</v>
-      </c>
-      <c r="G179" t="n">
-        <v>1</v>
-      </c>
-      <c r="H179" t="n">
-        <v>3</v>
-      </c>
       <c r="I179" t="n">
+        <v>5</v>
+      </c>
+      <c r="J179" t="n">
+        <v>1</v>
+      </c>
+      <c r="K179" t="n">
+        <v>0</v>
+      </c>
+      <c r="L179" t="n">
         <v>2</v>
       </c>
-      <c r="J179" t="n">
-        <v>5</v>
-      </c>
-      <c r="K179" t="n">
-        <v>1</v>
-      </c>
-      <c r="L179" t="n">
-        <v>0</v>
-      </c>
       <c r="M179" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="180">
@@ -7862,10 +7866,10 @@
         <v>0</v>
       </c>
       <c r="J180" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K180" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L180" t="n">
         <v>0</v>
@@ -7888,28 +7892,28 @@
         <v>0</v>
       </c>
       <c r="E181" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F181" t="n">
         <v>1</v>
       </c>
       <c r="G181" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H181" t="n">
         <v>0</v>
       </c>
       <c r="I181" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J181" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K181" t="n">
         <v>2</v>
       </c>
       <c r="L181" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M181" t="n">
         <v>0</v>
@@ -7926,7 +7930,7 @@
         <v>1</v>
       </c>
       <c r="D182" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E182" t="n">
         <v>0</v>
@@ -7941,19 +7945,19 @@
         <v>0</v>
       </c>
       <c r="I182" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J182" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K182" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L182" t="n">
         <v>1</v>
       </c>
       <c r="M182" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="183">
@@ -8003,9 +8007,7 @@
           <t>營運管理軟體</t>
         </is>
       </c>
-      <c r="B184" t="n">
-        <v>0</v>
-      </c>
+      <c r="B184" t="inlineStr"/>
       <c r="C184" t="n">
         <v>0</v>
       </c>
@@ -8019,22 +8021,22 @@
         <v>0</v>
       </c>
       <c r="G184" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H184" t="n">
         <v>1</v>
       </c>
       <c r="I184" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J184" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K184" t="n">
         <v>1</v>
       </c>
       <c r="L184" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M184" t="n">
         <v>0</v>
@@ -8189,19 +8191,19 @@
         <v>0</v>
       </c>
       <c r="I188" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J188" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K188" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L188" t="n">
         <v>1</v>
       </c>
       <c r="M188" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="189">
@@ -8271,10 +8273,10 @@
         <v>0</v>
       </c>
       <c r="I190" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J190" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K190" t="n">
         <v>0</v>
@@ -8300,10 +8302,10 @@
         <v>0</v>
       </c>
       <c r="E191" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F191" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G191" t="n">
         <v>0</v>
@@ -8350,19 +8352,19 @@
         <v>0</v>
       </c>
       <c r="H192" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I192" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J192" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K192" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L192" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M192" t="n">
         <v>0</v>
@@ -8419,19 +8421,19 @@
         <v>0</v>
       </c>
       <c r="C194" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D194" t="n">
         <v>0</v>
       </c>
       <c r="E194" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F194" t="n">
         <v>1</v>
       </c>
       <c r="G194" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H194" t="n">
         <v>0</v>
@@ -8478,13 +8480,13 @@
         <v>0</v>
       </c>
       <c r="I195" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J195" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K195" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L195" t="n">
         <v>0</v>
@@ -8499,9 +8501,7 @@
           <t>生產製程、檢測設備及原物料</t>
         </is>
       </c>
-      <c r="B196" t="n">
-        <v>0</v>
-      </c>
+      <c r="B196" t="inlineStr"/>
       <c r="C196" t="n">
         <v>0</v>
       </c>
@@ -8509,7 +8509,7 @@
         <v>0</v>
       </c>
       <c r="E196" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F196" t="n">
         <v>1</v>
@@ -8521,19 +8521,19 @@
         <v>1</v>
       </c>
       <c r="I196" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J196" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K196" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L196" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M196" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="197">
@@ -8542,38 +8542,36 @@
           <t>生產製程及檢測設備</t>
         </is>
       </c>
-      <c r="B197" t="n">
-        <v>0</v>
-      </c>
+      <c r="B197" t="inlineStr"/>
       <c r="C197" t="n">
+        <v>0</v>
+      </c>
+      <c r="D197" t="n">
+        <v>1</v>
+      </c>
+      <c r="E197" t="n">
         <v>4</v>
       </c>
-      <c r="D197" t="n">
-        <v>0</v>
-      </c>
-      <c r="E197" t="n">
-        <v>1</v>
-      </c>
       <c r="F197" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G197" t="n">
+        <v>3</v>
+      </c>
+      <c r="H197" t="n">
+        <v>5</v>
+      </c>
+      <c r="I197" t="n">
+        <v>1</v>
+      </c>
+      <c r="J197" t="n">
+        <v>6</v>
+      </c>
+      <c r="K197" t="n">
         <v>2</v>
       </c>
-      <c r="H197" t="n">
-        <v>3</v>
-      </c>
-      <c r="I197" t="n">
-        <v>5</v>
-      </c>
-      <c r="J197" t="n">
-        <v>1</v>
-      </c>
-      <c r="K197" t="n">
-        <v>6</v>
-      </c>
       <c r="L197" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M197" t="n">
         <v>1</v>
@@ -8722,10 +8720,10 @@
         <v>0</v>
       </c>
       <c r="G201" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H201" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I201" t="n">
         <v>0</v>
@@ -8766,10 +8764,10 @@
         <v>0</v>
       </c>
       <c r="H202" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I202" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J202" t="n">
         <v>0</v>
@@ -8798,10 +8796,10 @@
         <v>0</v>
       </c>
       <c r="E203" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F203" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G203" t="n">
         <v>0</v>
@@ -8810,13 +8808,13 @@
         <v>0</v>
       </c>
       <c r="I203" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J203" t="n">
         <v>1</v>
       </c>
       <c r="K203" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L203" t="n">
         <v>0</v>
@@ -8833,7 +8831,7 @@
       </c>
       <c r="B204" t="inlineStr"/>
       <c r="C204" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D204" t="n">
         <v>1</v>
@@ -8842,7 +8840,7 @@
         <v>1</v>
       </c>
       <c r="F204" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G204" t="n">
         <v>0</v>
@@ -8854,16 +8852,16 @@
         <v>0</v>
       </c>
       <c r="J204" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K204" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L204" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M204" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="205">
@@ -8874,7 +8872,7 @@
       </c>
       <c r="B205" t="inlineStr"/>
       <c r="C205" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D205" t="n">
         <v>1</v>
@@ -8883,7 +8881,7 @@
         <v>1</v>
       </c>
       <c r="F205" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G205" t="n">
         <v>0</v>
@@ -8892,13 +8890,13 @@
         <v>0</v>
       </c>
       <c r="I205" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J205" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K205" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L205" t="n">
         <v>0</v>
@@ -8983,10 +8981,10 @@
         <v>0</v>
       </c>
       <c r="L207" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M207" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="208">
@@ -8997,37 +8995,37 @@
       </c>
       <c r="B208" t="inlineStr"/>
       <c r="C208" t="n">
+        <v>1</v>
+      </c>
+      <c r="D208" t="n">
+        <v>0</v>
+      </c>
+      <c r="E208" t="n">
+        <v>2</v>
+      </c>
+      <c r="F208" t="n">
+        <v>1</v>
+      </c>
+      <c r="G208" t="n">
+        <v>3</v>
+      </c>
+      <c r="H208" t="n">
+        <v>2</v>
+      </c>
+      <c r="I208" t="n">
         <v>5</v>
-      </c>
-      <c r="D208" t="n">
-        <v>1</v>
-      </c>
-      <c r="E208" t="n">
-        <v>0</v>
-      </c>
-      <c r="F208" t="n">
-        <v>2</v>
-      </c>
-      <c r="G208" t="n">
-        <v>1</v>
-      </c>
-      <c r="H208" t="n">
-        <v>3</v>
-      </c>
-      <c r="I208" t="n">
-        <v>2</v>
       </c>
       <c r="J208" t="n">
         <v>5</v>
       </c>
       <c r="K208" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L208" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M208" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="209">
@@ -9053,13 +9051,13 @@
         <v>0</v>
       </c>
       <c r="H209" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I209" t="n">
         <v>1</v>
       </c>
       <c r="J209" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K209" t="n">
         <v>0</v>
@@ -9097,10 +9095,10 @@
         <v>0</v>
       </c>
       <c r="I210" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J210" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K210" t="n">
         <v>0</v>
@@ -9132,19 +9130,19 @@
         <v>0</v>
       </c>
       <c r="G211" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H211" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I211" t="n">
         <v>2</v>
       </c>
       <c r="J211" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K211" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L211" t="n">
         <v>0</v>
@@ -9343,10 +9341,10 @@
         <v>0</v>
       </c>
       <c r="I216" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J216" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K216" t="n">
         <v>0</v>
@@ -9378,25 +9376,25 @@
         <v>0</v>
       </c>
       <c r="G217" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H217" t="n">
         <v>1</v>
       </c>
       <c r="I217" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J217" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K217" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L217" t="n">
         <v>1</v>
       </c>
       <c r="M217" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="218">
@@ -9405,9 +9403,7 @@
           <t>筆記型電腦</t>
         </is>
       </c>
-      <c r="B218" t="n">
-        <v>0</v>
-      </c>
+      <c r="B218" t="inlineStr"/>
       <c r="C218" t="n">
         <v>0</v>
       </c>
@@ -9418,25 +9414,25 @@
         <v>0</v>
       </c>
       <c r="F218" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G218" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H218" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I218" t="n">
         <v>1</v>
       </c>
       <c r="J218" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K218" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L218" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M218" t="n">
         <v>0</v>
@@ -9465,19 +9461,19 @@
         <v>0</v>
       </c>
       <c r="H219" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I219" t="n">
         <v>1</v>
       </c>
       <c r="J219" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K219" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L219" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M219" t="n">
         <v>0</v>
@@ -9489,9 +9485,7 @@
           <t>系統整合</t>
         </is>
       </c>
-      <c r="B220" t="n">
-        <v>0</v>
-      </c>
+      <c r="B220" t="inlineStr"/>
       <c r="C220" t="n">
         <v>0</v>
       </c>
@@ -9499,31 +9493,31 @@
         <v>0</v>
       </c>
       <c r="E220" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F220" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G220" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H220" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I220" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="J220" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K220" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L220" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M220" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="221">
@@ -9532,11 +9526,9 @@
           <t>系統整合服務</t>
         </is>
       </c>
-      <c r="B221" t="n">
-        <v>0</v>
-      </c>
+      <c r="B221" t="inlineStr"/>
       <c r="C221" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D221" t="n">
         <v>1</v>
@@ -9548,25 +9540,25 @@
         <v>1</v>
       </c>
       <c r="G221" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H221" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I221" t="n">
         <v>4</v>
       </c>
       <c r="J221" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K221" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L221" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M221" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="222">
@@ -9601,10 +9593,10 @@
         <v>0</v>
       </c>
       <c r="K222" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L222" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M222" t="n">
         <v>0</v>
@@ -9630,19 +9622,19 @@
         <v>0</v>
       </c>
       <c r="G223" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H223" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I223" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J223" t="n">
         <v>1</v>
       </c>
       <c r="K223" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L223" t="n">
         <v>0</v>
@@ -9756,16 +9748,16 @@
         <v>0</v>
       </c>
       <c r="H226" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I226" t="n">
         <v>0</v>
       </c>
       <c r="J226" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K226" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L226" t="n">
         <v>0</v>
@@ -9797,13 +9789,13 @@
         <v>0</v>
       </c>
       <c r="H227" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I227" t="n">
         <v>1</v>
       </c>
       <c r="J227" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K227" t="n">
         <v>0</v>
@@ -9838,22 +9830,22 @@
         <v>0</v>
       </c>
       <c r="H228" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I228" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J228" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K228" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L228" t="n">
         <v>1</v>
       </c>
       <c r="M228" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="229">
@@ -9879,22 +9871,22 @@
         <v>0</v>
       </c>
       <c r="H229" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I229" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J229" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K229" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L229" t="n">
         <v>1</v>
       </c>
       <c r="M229" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="230">
@@ -9903,41 +9895,39 @@
           <t>網路設備(如數據機、網路卡、閘道器、路由器、網路電話)</t>
         </is>
       </c>
-      <c r="B230" t="n">
-        <v>0</v>
-      </c>
+      <c r="B230" t="inlineStr"/>
       <c r="C230" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D230" t="n">
         <v>1</v>
       </c>
       <c r="E230" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F230" t="n">
         <v>2</v>
       </c>
       <c r="G230" t="n">
+        <v>1</v>
+      </c>
+      <c r="H230" t="n">
         <v>2</v>
       </c>
-      <c r="H230" t="n">
-        <v>1</v>
-      </c>
       <c r="I230" t="n">
+        <v>6</v>
+      </c>
+      <c r="J230" t="n">
+        <v>1</v>
+      </c>
+      <c r="K230" t="n">
+        <v>1</v>
+      </c>
+      <c r="L230" t="n">
         <v>2</v>
       </c>
-      <c r="J230" t="n">
-        <v>6</v>
-      </c>
-      <c r="K230" t="n">
-        <v>1</v>
-      </c>
-      <c r="L230" t="n">
-        <v>1</v>
-      </c>
       <c r="M230" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="231">
@@ -9957,19 +9947,19 @@
         <v>0</v>
       </c>
       <c r="F231" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G231" t="n">
         <v>1</v>
       </c>
       <c r="H231" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I231" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J231" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K231" t="n">
         <v>1</v>
@@ -9978,7 +9968,7 @@
         <v>1</v>
       </c>
       <c r="M231" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="232">
@@ -10016,10 +10006,10 @@
         <v>0</v>
       </c>
       <c r="L232" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M232" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="233">
@@ -10042,25 +10032,25 @@
         <v>0</v>
       </c>
       <c r="G233" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H233" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I233" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J233" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K233" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L233" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M233" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="234">
@@ -10118,25 +10108,25 @@
         <v>0</v>
       </c>
       <c r="E235" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F235" t="n">
         <v>1</v>
       </c>
       <c r="G235" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H235" t="n">
         <v>0</v>
       </c>
       <c r="I235" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J235" t="n">
         <v>1</v>
       </c>
       <c r="K235" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L235" t="n">
         <v>0</v>
@@ -10174,10 +10164,10 @@
         <v>0</v>
       </c>
       <c r="J236" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K236" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L236" t="n">
         <v>0</v>
@@ -10250,22 +10240,22 @@
         <v>0</v>
       </c>
       <c r="H238" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I238" t="n">
         <v>1</v>
       </c>
       <c r="J238" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K238" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L238" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M238" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="239">
@@ -10276,7 +10266,7 @@
       </c>
       <c r="B239" t="inlineStr"/>
       <c r="C239" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D239" t="n">
         <v>0</v>
@@ -10294,19 +10284,19 @@
         <v>0</v>
       </c>
       <c r="I239" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J239" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K239" t="n">
         <v>0</v>
       </c>
       <c r="L239" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M239" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="240">
@@ -10338,10 +10328,10 @@
         <v>0</v>
       </c>
       <c r="J240" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K240" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L240" t="n">
         <v>0</v>
@@ -10356,9 +10346,7 @@
           <t>臨床實驗、移植技術、疾病治療</t>
         </is>
       </c>
-      <c r="B241" t="n">
-        <v>0</v>
-      </c>
+      <c r="B241" t="inlineStr"/>
       <c r="C241" t="n">
         <v>0</v>
       </c>
@@ -10536,16 +10524,16 @@
         <v>0</v>
       </c>
       <c r="G245" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H245" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I245" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J245" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K245" t="n">
         <v>0</v>
@@ -10563,9 +10551,7 @@
           <t>自然語言處理</t>
         </is>
       </c>
-      <c r="B246" t="n">
-        <v>0</v>
-      </c>
+      <c r="B246" t="inlineStr"/>
       <c r="C246" t="n">
         <v>0</v>
       </c>
@@ -10585,16 +10571,16 @@
         <v>0</v>
       </c>
       <c r="I246" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J246" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K246" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L246" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M246" t="n">
         <v>0</v>
@@ -10629,10 +10615,10 @@
         <v>0</v>
       </c>
       <c r="J247" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K247" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L247" t="n">
         <v>0</v>
@@ -10658,13 +10644,13 @@
         <v>0</v>
       </c>
       <c r="F248" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G248" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H248" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I248" t="n">
         <v>0</v>
@@ -10696,19 +10682,19 @@
         <v>0</v>
       </c>
       <c r="E249" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F249" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G249" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H249" t="n">
         <v>1</v>
       </c>
       <c r="I249" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J249" t="n">
         <v>0</v>
@@ -10729,9 +10715,7 @@
           <t>虛擬化軟體</t>
         </is>
       </c>
-      <c r="B250" t="n">
-        <v>0</v>
-      </c>
+      <c r="B250" t="inlineStr"/>
       <c r="C250" t="n">
         <v>0</v>
       </c>
@@ -10745,19 +10729,19 @@
         <v>0</v>
       </c>
       <c r="G250" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H250" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I250" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J250" t="n">
         <v>1</v>
       </c>
       <c r="K250" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L250" t="n">
         <v>0</v>
@@ -10833,16 +10817,16 @@
         <v>0</v>
       </c>
       <c r="I252" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J252" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K252" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L252" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M252" t="n">
         <v>0</v>
@@ -10965,10 +10949,10 @@
         <v>0</v>
       </c>
       <c r="L255" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M255" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="256">
@@ -10982,7 +10966,7 @@
         <v>1</v>
       </c>
       <c r="D256" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E256" t="n">
         <v>0</v>
@@ -10991,10 +10975,10 @@
         <v>0</v>
       </c>
       <c r="G256" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H256" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I256" t="n">
         <v>0</v>
@@ -11120,13 +11104,13 @@
         <v>0</v>
       </c>
       <c r="I259" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J259" t="n">
         <v>1</v>
       </c>
       <c r="K259" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L259" t="n">
         <v>0</v>
@@ -11149,10 +11133,10 @@
         <v>0</v>
       </c>
       <c r="E260" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F260" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G260" t="n">
         <v>0</v>
@@ -11199,10 +11183,10 @@
         <v>0</v>
       </c>
       <c r="H261" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I261" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J261" t="n">
         <v>0</v>
@@ -11228,31 +11212,31 @@
         <v>0</v>
       </c>
       <c r="D262" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E262" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F262" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G262" t="n">
+        <v>9</v>
+      </c>
+      <c r="H262" t="n">
+        <v>2</v>
+      </c>
+      <c r="I262" t="n">
+        <v>4</v>
+      </c>
+      <c r="J262" t="n">
         <v>3</v>
       </c>
-      <c r="H262" t="n">
-        <v>10</v>
-      </c>
-      <c r="I262" t="n">
+      <c r="K262" t="n">
+        <v>0</v>
+      </c>
+      <c r="L262" t="n">
         <v>2</v>
-      </c>
-      <c r="J262" t="n">
-        <v>4</v>
-      </c>
-      <c r="K262" t="n">
-        <v>3</v>
-      </c>
-      <c r="L262" t="n">
-        <v>0</v>
       </c>
       <c r="M262" t="n">
         <v>0</v>
@@ -11264,9 +11248,7 @@
           <t>設備安裝服務</t>
         </is>
       </c>
-      <c r="B263" t="n">
-        <v>0</v>
-      </c>
+      <c r="B263" t="inlineStr"/>
       <c r="C263" t="n">
         <v>0</v>
       </c>
@@ -11280,7 +11262,7 @@
         <v>0</v>
       </c>
       <c r="G263" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H263" t="n">
         <v>1</v>
@@ -11289,10 +11271,10 @@
         <v>1</v>
       </c>
       <c r="J263" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K263" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L263" t="n">
         <v>0</v>
@@ -11307,9 +11289,7 @@
           <t>設備管理軟體</t>
         </is>
       </c>
-      <c r="B264" t="n">
-        <v>0</v>
-      </c>
+      <c r="B264" t="inlineStr"/>
       <c r="C264" t="n">
         <v>0</v>
       </c>
@@ -11323,22 +11303,22 @@
         <v>0</v>
       </c>
       <c r="G264" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H264" t="n">
         <v>1</v>
       </c>
       <c r="I264" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J264" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K264" t="n">
         <v>1</v>
       </c>
       <c r="L264" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M264" t="n">
         <v>0</v>
@@ -11347,7 +11327,7 @@
     <row r="265">
       <c r="A265" s="1" t="inlineStr">
         <is>
-          <t>證券業</t>
+          <t>設備維護</t>
         </is>
       </c>
       <c r="B265" t="inlineStr"/>
@@ -11388,28 +11368,50 @@
     <row r="266">
       <c r="A266" s="1" t="inlineStr">
         <is>
-          <t>變壓器</t>
+          <t>證券業</t>
         </is>
       </c>
       <c r="B266" t="n">
         <v>0</v>
       </c>
-      <c r="C266" t="inlineStr"/>
-      <c r="D266" t="inlineStr"/>
-      <c r="E266" t="inlineStr"/>
-      <c r="F266" t="inlineStr"/>
-      <c r="G266" t="inlineStr"/>
-      <c r="H266" t="inlineStr"/>
-      <c r="I266" t="inlineStr"/>
-      <c r="J266" t="inlineStr"/>
-      <c r="K266" t="inlineStr"/>
-      <c r="L266" t="inlineStr"/>
-      <c r="M266" t="inlineStr"/>
+      <c r="C266" t="n">
+        <v>0</v>
+      </c>
+      <c r="D266" t="n">
+        <v>0</v>
+      </c>
+      <c r="E266" t="n">
+        <v>0</v>
+      </c>
+      <c r="F266" t="n">
+        <v>0</v>
+      </c>
+      <c r="G266" t="n">
+        <v>0</v>
+      </c>
+      <c r="H266" t="n">
+        <v>0</v>
+      </c>
+      <c r="I266" t="n">
+        <v>0</v>
+      </c>
+      <c r="J266" t="n">
+        <v>0</v>
+      </c>
+      <c r="K266" t="n">
+        <v>0</v>
+      </c>
+      <c r="L266" t="n">
+        <v>0</v>
+      </c>
+      <c r="M266" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="267">
       <c r="A267" s="1" t="inlineStr">
         <is>
-          <t>貨櫃航運</t>
+          <t>變壓器</t>
         </is>
       </c>
       <c r="B267" t="inlineStr"/>
@@ -11450,7 +11452,7 @@
     <row r="268">
       <c r="A268" s="1" t="inlineStr">
         <is>
-          <t>貨櫃運輸集散及倉儲</t>
+          <t>貨櫃航運</t>
         </is>
       </c>
       <c r="B268" t="inlineStr"/>
@@ -11491,21 +11493,23 @@
     <row r="269">
       <c r="A269" s="1" t="inlineStr">
         <is>
-          <t>貿易商、代理商、經銷商</t>
-        </is>
-      </c>
-      <c r="B269" t="inlineStr"/>
+          <t>貨櫃運輸集散及倉儲</t>
+        </is>
+      </c>
+      <c r="B269" t="n">
+        <v>0</v>
+      </c>
       <c r="C269" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D269" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E269" t="n">
         <v>0</v>
       </c>
       <c r="F269" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G269" t="n">
         <v>0</v>
@@ -11523,7 +11527,7 @@
         <v>0</v>
       </c>
       <c r="L269" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M269" t="n">
         <v>0</v>
@@ -11532,18 +11536,18 @@
     <row r="270">
       <c r="A270" s="1" t="inlineStr">
         <is>
-          <t>資安審計</t>
+          <t>貿易商、代理商、經銷商</t>
         </is>
       </c>
       <c r="B270" t="inlineStr"/>
       <c r="C270" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D270" t="n">
         <v>0</v>
       </c>
       <c r="E270" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F270" t="n">
         <v>0</v>
@@ -11561,7 +11565,7 @@
         <v>0</v>
       </c>
       <c r="K270" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L270" t="n">
         <v>0</v>
@@ -11573,7 +11577,7 @@
     <row r="271">
       <c r="A271" s="1" t="inlineStr">
         <is>
-          <t>資安治理</t>
+          <t>資安審計</t>
         </is>
       </c>
       <c r="B271" t="inlineStr"/>
@@ -11599,22 +11603,22 @@
         <v>0</v>
       </c>
       <c r="J271" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K271" t="n">
         <v>0</v>
       </c>
       <c r="L271" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M271" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" s="1" t="inlineStr">
         <is>
-          <t>資安營運管理服務</t>
+          <t>資安治理</t>
         </is>
       </c>
       <c r="B272" t="inlineStr"/>
@@ -11637,13 +11641,13 @@
         <v>0</v>
       </c>
       <c r="I272" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J272" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K272" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L272" t="n">
         <v>1</v>
@@ -11655,7 +11659,7 @@
     <row r="273">
       <c r="A273" s="1" t="inlineStr">
         <is>
-          <t>資安防護能力分析與鑑識服務</t>
+          <t>資安營運管理服務</t>
         </is>
       </c>
       <c r="B273" t="inlineStr"/>
@@ -11675,33 +11679,31 @@
         <v>0</v>
       </c>
       <c r="H273" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I273" t="n">
         <v>1</v>
       </c>
       <c r="J273" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K273" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L273" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M273" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" s="1" t="inlineStr">
         <is>
-          <t>資安防護軟體</t>
-        </is>
-      </c>
-      <c r="B274" t="n">
-        <v>0</v>
-      </c>
+          <t>資安防護能力分析與鑑識服務</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr"/>
       <c r="C274" t="n">
         <v>0</v>
       </c>
@@ -11721,10 +11723,10 @@
         <v>1</v>
       </c>
       <c r="I274" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J274" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K274" t="n">
         <v>1</v>
@@ -11739,7 +11741,7 @@
     <row r="275">
       <c r="A275" s="1" t="inlineStr">
         <is>
-          <t>資安顧問服務</t>
+          <t>資安防護軟體</t>
         </is>
       </c>
       <c r="B275" t="inlineStr"/>
@@ -11756,31 +11758,31 @@
         <v>0</v>
       </c>
       <c r="G275" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H275" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I275" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J275" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K275" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L275" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M275" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" s="1" t="inlineStr">
         <is>
-          <t>資料分析處理服務</t>
+          <t>資安顧問服務</t>
         </is>
       </c>
       <c r="B276" t="inlineStr"/>
@@ -11800,19 +11802,19 @@
         <v>0</v>
       </c>
       <c r="H276" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I276" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J276" t="n">
         <v>0</v>
       </c>
       <c r="K276" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L276" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M276" t="n">
         <v>0</v>
@@ -11821,7 +11823,7 @@
     <row r="277">
       <c r="A277" s="1" t="inlineStr">
         <is>
-          <t>資料安全</t>
+          <t>資料分析處理服務</t>
         </is>
       </c>
       <c r="B277" t="inlineStr"/>
@@ -11838,22 +11840,22 @@
         <v>0</v>
       </c>
       <c r="G277" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H277" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I277" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J277" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K277" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L277" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M277" t="n">
         <v>0</v>
@@ -11862,7 +11864,7 @@
     <row r="278">
       <c r="A278" s="1" t="inlineStr">
         <is>
-          <t>資料庫</t>
+          <t>資料安全</t>
         </is>
       </c>
       <c r="B278" t="inlineStr"/>
@@ -11876,13 +11878,13 @@
         <v>0</v>
       </c>
       <c r="F278" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G278" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H278" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I278" t="n">
         <v>1</v>
@@ -11903,7 +11905,7 @@
     <row r="279">
       <c r="A279" s="1" t="inlineStr">
         <is>
-          <t>資料聚合</t>
+          <t>資料庫</t>
         </is>
       </c>
       <c r="B279" t="inlineStr"/>
@@ -11920,16 +11922,16 @@
         <v>0</v>
       </c>
       <c r="G279" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H279" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I279" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J279" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K279" t="n">
         <v>0</v>
@@ -11944,12 +11946,10 @@
     <row r="280">
       <c r="A280" s="1" t="inlineStr">
         <is>
-          <t>資料處理</t>
-        </is>
-      </c>
-      <c r="B280" t="n">
-        <v>0</v>
-      </c>
+          <t>資料聚合</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr"/>
       <c r="C280" t="n">
         <v>0</v>
       </c>
@@ -11969,30 +11969,28 @@
         <v>0</v>
       </c>
       <c r="I280" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J280" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K280" t="n">
         <v>0</v>
       </c>
       <c r="L280" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M280" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" s="1" t="inlineStr">
         <is>
-          <t>資料處理服務</t>
-        </is>
-      </c>
-      <c r="B281" t="n">
-        <v>0</v>
-      </c>
+          <t>資料處理</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr"/>
       <c r="C281" t="n">
         <v>0</v>
       </c>
@@ -12009,19 +12007,19 @@
         <v>0</v>
       </c>
       <c r="H281" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I281" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J281" t="n">
         <v>0</v>
       </c>
       <c r="K281" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L281" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M281" t="n">
         <v>0</v>
@@ -12030,12 +12028,10 @@
     <row r="282">
       <c r="A282" s="1" t="inlineStr">
         <is>
-          <t>資服</t>
-        </is>
-      </c>
-      <c r="B282" t="n">
-        <v>0</v>
-      </c>
+          <t>資料處理服務</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr"/>
       <c r="C282" t="n">
         <v>0</v>
       </c>
@@ -12073,7 +12069,7 @@
     <row r="283">
       <c r="A283" s="1" t="inlineStr">
         <is>
-          <t>資訊收集設備</t>
+          <t>資服</t>
         </is>
       </c>
       <c r="B283" t="inlineStr"/>
@@ -12114,48 +12110,28 @@
     <row r="284">
       <c r="A284" s="1" t="inlineStr">
         <is>
-          <t>資訊系統建置服務</t>
-        </is>
-      </c>
-      <c r="B284" t="inlineStr"/>
-      <c r="C284" t="n">
-        <v>0</v>
-      </c>
-      <c r="D284" t="n">
-        <v>0</v>
-      </c>
-      <c r="E284" t="n">
-        <v>0</v>
-      </c>
-      <c r="F284" t="n">
-        <v>0</v>
-      </c>
-      <c r="G284" t="n">
-        <v>0</v>
-      </c>
-      <c r="H284" t="n">
-        <v>0</v>
-      </c>
-      <c r="I284" t="n">
-        <v>0</v>
-      </c>
-      <c r="J284" t="n">
-        <v>0</v>
-      </c>
-      <c r="K284" t="n">
-        <v>0</v>
-      </c>
-      <c r="L284" t="n">
-        <v>0</v>
-      </c>
-      <c r="M284" t="n">
-        <v>0</v>
-      </c>
+          <t>資訊收集設備</t>
+        </is>
+      </c>
+      <c r="B284" t="n">
+        <v>0</v>
+      </c>
+      <c r="C284" t="inlineStr"/>
+      <c r="D284" t="inlineStr"/>
+      <c r="E284" t="inlineStr"/>
+      <c r="F284" t="inlineStr"/>
+      <c r="G284" t="inlineStr"/>
+      <c r="H284" t="inlineStr"/>
+      <c r="I284" t="inlineStr"/>
+      <c r="J284" t="inlineStr"/>
+      <c r="K284" t="inlineStr"/>
+      <c r="L284" t="inlineStr"/>
+      <c r="M284" t="inlineStr"/>
     </row>
     <row r="285">
       <c r="A285" s="1" t="inlineStr">
         <is>
-          <t>資訊聚合</t>
+          <t>資訊系統建置服務</t>
         </is>
       </c>
       <c r="B285" t="inlineStr"/>
@@ -12196,7 +12172,7 @@
     <row r="286">
       <c r="A286" s="1" t="inlineStr">
         <is>
-          <t>身分認證與訪問管理</t>
+          <t>資訊聚合</t>
         </is>
       </c>
       <c r="B286" t="inlineStr"/>
@@ -12213,22 +12189,22 @@
         <v>0</v>
       </c>
       <c r="G286" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H286" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I286" t="n">
         <v>0</v>
       </c>
       <c r="J286" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K286" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L286" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M286" t="n">
         <v>0</v>
@@ -12237,38 +12213,36 @@
     <row r="287">
       <c r="A287" s="1" t="inlineStr">
         <is>
-          <t>車燈</t>
-        </is>
-      </c>
-      <c r="B287" t="n">
-        <v>0</v>
-      </c>
+          <t>身分認證與訪問管理</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr"/>
       <c r="C287" t="n">
         <v>0</v>
       </c>
       <c r="D287" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E287" t="n">
         <v>0</v>
       </c>
       <c r="F287" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G287" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H287" t="n">
         <v>0</v>
       </c>
       <c r="I287" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J287" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K287" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L287" t="n">
         <v>0</v>
@@ -12280,32 +12254,30 @@
     <row r="288">
       <c r="A288" s="1" t="inlineStr">
         <is>
-          <t>車用機械傳動設備及零配件</t>
-        </is>
-      </c>
-      <c r="B288" t="n">
-        <v>0</v>
-      </c>
+          <t>車燈</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr"/>
       <c r="C288" t="n">
+        <v>1</v>
+      </c>
+      <c r="D288" t="n">
+        <v>0</v>
+      </c>
+      <c r="E288" t="n">
+        <v>1</v>
+      </c>
+      <c r="F288" t="n">
+        <v>0</v>
+      </c>
+      <c r="G288" t="n">
+        <v>0</v>
+      </c>
+      <c r="H288" t="n">
         <v>2</v>
       </c>
-      <c r="D288" t="n">
-        <v>1</v>
-      </c>
-      <c r="E288" t="n">
-        <v>1</v>
-      </c>
-      <c r="F288" t="n">
-        <v>2</v>
-      </c>
-      <c r="G288" t="n">
-        <v>1</v>
-      </c>
-      <c r="H288" t="n">
-        <v>0</v>
-      </c>
       <c r="I288" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J288" t="n">
         <v>0</v>
@@ -12323,27 +12295,27 @@
     <row r="289">
       <c r="A289" s="1" t="inlineStr">
         <is>
-          <t>軟性電路板</t>
+          <t>車用機械傳動設備及零配件</t>
         </is>
       </c>
       <c r="B289" t="inlineStr"/>
       <c r="C289" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D289" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E289" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F289" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G289" t="n">
         <v>0</v>
       </c>
       <c r="H289" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I289" t="n">
         <v>0</v>
@@ -12364,7 +12336,7 @@
     <row r="290">
       <c r="A290" s="1" t="inlineStr">
         <is>
-          <t>軟體開發</t>
+          <t>軟性電路板</t>
         </is>
       </c>
       <c r="B290" t="inlineStr"/>
@@ -12405,7 +12377,7 @@
     <row r="291">
       <c r="A291" s="1" t="inlineStr">
         <is>
-          <t>軟體開發工具</t>
+          <t>軟體開發</t>
         </is>
       </c>
       <c r="B291" t="inlineStr"/>
@@ -12431,7 +12403,7 @@
         <v>0</v>
       </c>
       <c r="J291" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K291" t="n">
         <v>0</v>
@@ -12446,7 +12418,7 @@
     <row r="292">
       <c r="A292" s="1" t="inlineStr">
         <is>
-          <t>輪胎</t>
+          <t>軟體開發工具</t>
         </is>
       </c>
       <c r="B292" t="inlineStr"/>
@@ -12469,7 +12441,7 @@
         <v>0</v>
       </c>
       <c r="I292" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J292" t="n">
         <v>0</v>
@@ -12487,7 +12459,7 @@
     <row r="293">
       <c r="A293" s="1" t="inlineStr">
         <is>
-          <t>輸出入模組/介面卡</t>
+          <t>輪胎</t>
         </is>
       </c>
       <c r="B293" t="inlineStr"/>
@@ -12504,16 +12476,16 @@
         <v>0</v>
       </c>
       <c r="G293" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H293" t="n">
         <v>0</v>
       </c>
       <c r="I293" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J293" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K293" t="n">
         <v>0</v>
@@ -12528,7 +12500,7 @@
     <row r="294">
       <c r="A294" s="1" t="inlineStr">
         <is>
-          <t>輸送機械及零配件</t>
+          <t>輸出入模組/介面卡</t>
         </is>
       </c>
       <c r="B294" t="inlineStr"/>
@@ -12542,16 +12514,16 @@
         <v>0</v>
       </c>
       <c r="F294" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G294" t="n">
         <v>0</v>
       </c>
       <c r="H294" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I294" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J294" t="n">
         <v>0</v>
@@ -12569,7 +12541,7 @@
     <row r="295">
       <c r="A295" s="1" t="inlineStr">
         <is>
-          <t>農業科技業</t>
+          <t>輸送機械及零配件</t>
         </is>
       </c>
       <c r="B295" t="inlineStr"/>
@@ -12598,7 +12570,7 @@
         <v>0</v>
       </c>
       <c r="K295" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L295" t="n">
         <v>0</v>
@@ -12610,7 +12582,7 @@
     <row r="296">
       <c r="A296" s="1" t="inlineStr">
         <is>
-          <t>農藥</t>
+          <t>農業科技業</t>
         </is>
       </c>
       <c r="B296" t="inlineStr"/>
@@ -12636,7 +12608,7 @@
         <v>0</v>
       </c>
       <c r="J296" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K296" t="n">
         <v>0</v>
@@ -12651,10 +12623,12 @@
     <row r="297">
       <c r="A297" s="1" t="inlineStr">
         <is>
-          <t>近眼顯示(Dear-Eye Display)</t>
-        </is>
-      </c>
-      <c r="B297" t="inlineStr"/>
+          <t>農藥</t>
+        </is>
+      </c>
+      <c r="B297" t="n">
+        <v>0</v>
+      </c>
       <c r="C297" t="n">
         <v>0</v>
       </c>
@@ -12692,7 +12666,7 @@
     <row r="298">
       <c r="A298" s="1" t="inlineStr">
         <is>
-          <t>通訊</t>
+          <t>近眼顯示(Dear-Eye Display)</t>
         </is>
       </c>
       <c r="B298" t="inlineStr"/>
@@ -12733,7 +12707,7 @@
     <row r="299">
       <c r="A299" s="1" t="inlineStr">
         <is>
-          <t>通訊服務</t>
+          <t>通訊</t>
         </is>
       </c>
       <c r="B299" t="inlineStr"/>
@@ -12774,14 +12748,12 @@
     <row r="300">
       <c r="A300" s="1" t="inlineStr">
         <is>
-          <t>通路經銷</t>
-        </is>
-      </c>
-      <c r="B300" t="n">
-        <v>0</v>
-      </c>
+          <t>通訊服務</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr"/>
       <c r="C300" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D300" t="n">
         <v>0</v>
@@ -12799,16 +12771,16 @@
         <v>0</v>
       </c>
       <c r="I300" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J300" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K300" t="n">
         <v>0</v>
       </c>
       <c r="L300" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M300" t="n">
         <v>0</v>
@@ -12817,12 +12789,12 @@
     <row r="301">
       <c r="A301" s="1" t="inlineStr">
         <is>
-          <t>連接器設計、組裝及製造</t>
+          <t>通路經銷</t>
         </is>
       </c>
       <c r="B301" t="inlineStr"/>
       <c r="C301" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D301" t="n">
         <v>0</v>
@@ -12831,34 +12803,34 @@
         <v>0</v>
       </c>
       <c r="F301" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G301" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H301" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I301" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J301" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K301" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L301" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M301" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" s="1" t="inlineStr">
         <is>
-          <t>連接線</t>
+          <t>連接器設計、組裝及製造</t>
         </is>
       </c>
       <c r="B302" t="inlineStr"/>
@@ -12869,40 +12841,42 @@
         <v>0</v>
       </c>
       <c r="E302" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F302" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G302" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H302" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I302" t="n">
         <v>1</v>
       </c>
       <c r="J302" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K302" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L302" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M302" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" s="1" t="inlineStr">
         <is>
-          <t>運動服務/顧問</t>
-        </is>
-      </c>
-      <c r="B303" t="inlineStr"/>
+          <t>連接線</t>
+        </is>
+      </c>
+      <c r="B303" t="n">
+        <v>0</v>
+      </c>
       <c r="C303" t="n">
         <v>0</v>
       </c>
@@ -12916,22 +12890,22 @@
         <v>0</v>
       </c>
       <c r="G303" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H303" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I303" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J303" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K303" t="n">
         <v>0</v>
       </c>
       <c r="L303" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M303" t="n">
         <v>0</v>
@@ -12940,7 +12914,7 @@
     <row r="304">
       <c r="A304" s="1" t="inlineStr">
         <is>
-          <t>運動用品</t>
+          <t>運動服務/顧問</t>
         </is>
       </c>
       <c r="B304" t="inlineStr"/>
@@ -12981,7 +12955,7 @@
     <row r="305">
       <c r="A305" s="1" t="inlineStr">
         <is>
-          <t>運動行銷/媒體</t>
+          <t>運動用品</t>
         </is>
       </c>
       <c r="B305" t="inlineStr"/>
@@ -13022,7 +12996,7 @@
     <row r="306">
       <c r="A306" s="1" t="inlineStr">
         <is>
-          <t>運算元件與設備</t>
+          <t>運動行銷/媒體</t>
         </is>
       </c>
       <c r="B306" t="inlineStr"/>
@@ -13042,16 +13016,16 @@
         <v>0</v>
       </c>
       <c r="H306" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I306" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J306" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K306" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L306" t="n">
         <v>0</v>
@@ -13063,17 +13037,15 @@
     <row r="307">
       <c r="A307" s="1" t="inlineStr">
         <is>
-          <t>運算設備</t>
-        </is>
-      </c>
-      <c r="B307" t="n">
-        <v>0</v>
-      </c>
+          <t>運算元件與設備</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr"/>
       <c r="C307" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D307" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E307" t="n">
         <v>0</v>
@@ -13082,16 +13054,16 @@
         <v>0</v>
       </c>
       <c r="G307" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H307" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I307" t="n">
         <v>1</v>
       </c>
       <c r="J307" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K307" t="n">
         <v>0</v>
@@ -13106,12 +13078,12 @@
     <row r="308">
       <c r="A308" s="1" t="inlineStr">
         <is>
-          <t>運輸工具</t>
+          <t>運算設備</t>
         </is>
       </c>
       <c r="B308" t="inlineStr"/>
       <c r="C308" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D308" t="n">
         <v>0</v>
@@ -13126,7 +13098,7 @@
         <v>0</v>
       </c>
       <c r="H308" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I308" t="n">
         <v>0</v>
@@ -13147,12 +13119,10 @@
     <row r="309">
       <c r="A309" s="1" t="inlineStr">
         <is>
-          <t>配電管理設施</t>
-        </is>
-      </c>
-      <c r="B309" t="n">
-        <v>0</v>
-      </c>
+          <t>運輸工具</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr"/>
       <c r="C309" t="n">
         <v>0</v>
       </c>
@@ -13190,12 +13160,10 @@
     <row r="310">
       <c r="A310" s="1" t="inlineStr">
         <is>
-          <t>配電系統</t>
-        </is>
-      </c>
-      <c r="B310" t="n">
-        <v>0</v>
-      </c>
+          <t>配電管理設施</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr"/>
       <c r="C310" t="n">
         <v>0</v>
       </c>
@@ -13218,7 +13186,7 @@
         <v>0</v>
       </c>
       <c r="J310" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K310" t="n">
         <v>0</v>
@@ -13233,7 +13201,7 @@
     <row r="311">
       <c r="A311" s="1" t="inlineStr">
         <is>
-          <t>酚醛樹脂</t>
+          <t>配電系統</t>
         </is>
       </c>
       <c r="B311" t="inlineStr"/>
@@ -13259,10 +13227,10 @@
         <v>0</v>
       </c>
       <c r="J311" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K311" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L311" t="n">
         <v>0</v>
@@ -13274,7 +13242,7 @@
     <row r="312">
       <c r="A312" s="1" t="inlineStr">
         <is>
-          <t>醫療器材代理銷售及通路</t>
+          <t>酚醛樹脂</t>
         </is>
       </c>
       <c r="B312" t="inlineStr"/>
@@ -13291,10 +13259,10 @@
         <v>0</v>
       </c>
       <c r="G312" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H312" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I312" t="n">
         <v>1</v>
@@ -13303,7 +13271,7 @@
         <v>1</v>
       </c>
       <c r="K312" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L312" t="n">
         <v>0</v>
@@ -13315,32 +13283,30 @@
     <row r="313">
       <c r="A313" s="1" t="inlineStr">
         <is>
-          <t>醫療器材研發、設計、製造</t>
-        </is>
-      </c>
-      <c r="B313" t="n">
-        <v>0</v>
-      </c>
+          <t>醫療器材代理銷售及通路</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr"/>
       <c r="C313" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D313" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E313" t="n">
         <v>0</v>
       </c>
       <c r="F313" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G313" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H313" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I313" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J313" t="n">
         <v>1</v>
@@ -13352,18 +13318,20 @@
         <v>0</v>
       </c>
       <c r="M313" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" s="1" t="inlineStr">
         <is>
-          <t>醫療院所</t>
-        </is>
-      </c>
-      <c r="B314" t="inlineStr"/>
+          <t>醫療器材研發、設計、製造</t>
+        </is>
+      </c>
+      <c r="B314" t="n">
+        <v>0</v>
+      </c>
       <c r="C314" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D314" t="n">
         <v>0</v>
@@ -13372,16 +13340,16 @@
         <v>0</v>
       </c>
       <c r="F314" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G314" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H314" t="n">
         <v>0</v>
       </c>
       <c r="I314" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J314" t="n">
         <v>0</v>
@@ -13390,7 +13358,7 @@
         <v>0</v>
       </c>
       <c r="L314" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M314" t="n">
         <v>0</v>
@@ -13399,7 +13367,7 @@
     <row r="315">
       <c r="A315" s="1" t="inlineStr">
         <is>
-          <t>金屬、塑膠模具</t>
+          <t>醫療院所</t>
         </is>
       </c>
       <c r="B315" t="inlineStr"/>
@@ -13416,22 +13384,22 @@
         <v>0</v>
       </c>
       <c r="G315" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H315" t="n">
         <v>0</v>
       </c>
       <c r="I315" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J315" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K315" t="n">
         <v>0</v>
       </c>
       <c r="L315" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M315" t="n">
         <v>0</v>
@@ -13440,7 +13408,7 @@
     <row r="316">
       <c r="A316" s="1" t="inlineStr">
         <is>
-          <t>金屬加工用機械</t>
+          <t>金屬、塑膠模具</t>
         </is>
       </c>
       <c r="B316" t="inlineStr"/>
@@ -13448,28 +13416,28 @@
         <v>0</v>
       </c>
       <c r="D316" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E316" t="n">
         <v>0</v>
       </c>
       <c r="F316" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G316" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H316" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I316" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J316" t="n">
         <v>0</v>
       </c>
       <c r="K316" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L316" t="n">
         <v>0</v>
@@ -13481,18 +13449,18 @@
     <row r="317">
       <c r="A317" s="1" t="inlineStr">
         <is>
-          <t>金屬加工處理</t>
+          <t>金屬加工用機械</t>
         </is>
       </c>
       <c r="B317" t="inlineStr"/>
       <c r="C317" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D317" t="n">
         <v>0</v>
       </c>
       <c r="E317" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F317" t="n">
         <v>0</v>
@@ -13501,7 +13469,7 @@
         <v>0</v>
       </c>
       <c r="H317" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I317" t="n">
         <v>0</v>
@@ -13516,13 +13484,13 @@
         <v>0</v>
       </c>
       <c r="M317" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" s="1" t="inlineStr">
         <is>
-          <t>金屬材料</t>
+          <t>金屬加工處理</t>
         </is>
       </c>
       <c r="B318" t="inlineStr"/>
@@ -13530,7 +13498,7 @@
         <v>0</v>
       </c>
       <c r="D318" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E318" t="n">
         <v>0</v>
@@ -13539,7 +13507,7 @@
         <v>0</v>
       </c>
       <c r="G318" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H318" t="n">
         <v>0</v>
@@ -13554,7 +13522,7 @@
         <v>0</v>
       </c>
       <c r="L318" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M318" t="n">
         <v>0</v>
@@ -13563,7 +13531,7 @@
     <row r="319">
       <c r="A319" s="1" t="inlineStr">
         <is>
-          <t>金屬製品</t>
+          <t>金屬材料</t>
         </is>
       </c>
       <c r="B319" t="inlineStr"/>
@@ -13583,7 +13551,7 @@
         <v>0</v>
       </c>
       <c r="H319" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I319" t="n">
         <v>0</v>
@@ -13604,7 +13572,7 @@
     <row r="320">
       <c r="A320" s="1" t="inlineStr">
         <is>
-          <t>金控業/銀行業/保險業</t>
+          <t>金屬製品</t>
         </is>
       </c>
       <c r="B320" t="inlineStr"/>
@@ -13621,7 +13589,7 @@
         <v>0</v>
       </c>
       <c r="G320" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H320" t="n">
         <v>0</v>
@@ -13645,7 +13613,7 @@
     <row r="321">
       <c r="A321" s="1" t="inlineStr">
         <is>
-          <t>金流串接處理服務</t>
+          <t>金控業/銀行業/保險業</t>
         </is>
       </c>
       <c r="B321" t="inlineStr"/>
@@ -13653,7 +13621,7 @@
         <v>0</v>
       </c>
       <c r="D321" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E321" t="n">
         <v>0</v>
@@ -13686,12 +13654,12 @@
     <row r="322">
       <c r="A322" s="1" t="inlineStr">
         <is>
-          <t>金融提款機(ATM)</t>
+          <t>金流串接處理服務</t>
         </is>
       </c>
       <c r="B322" t="inlineStr"/>
       <c r="C322" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D322" t="n">
         <v>0</v>
@@ -13727,7 +13695,7 @@
     <row r="323">
       <c r="A323" s="1" t="inlineStr">
         <is>
-          <t>鈑金</t>
+          <t>金融提款機(ATM)</t>
         </is>
       </c>
       <c r="B323" t="inlineStr"/>
@@ -13768,21 +13736,21 @@
     <row r="324">
       <c r="A324" s="1" t="inlineStr">
         <is>
-          <t>銅箔</t>
+          <t>鈑金</t>
         </is>
       </c>
       <c r="B324" t="inlineStr"/>
       <c r="C324" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D324" t="n">
         <v>0</v>
       </c>
       <c r="E324" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F324" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G324" t="n">
         <v>0</v>
@@ -13791,13 +13759,13 @@
         <v>0</v>
       </c>
       <c r="I324" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J324" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K324" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L324" t="n">
         <v>0</v>
@@ -13809,12 +13777,12 @@
     <row r="325">
       <c r="A325" s="1" t="inlineStr">
         <is>
-          <t>銅箔基板</t>
+          <t>銅箔</t>
         </is>
       </c>
       <c r="B325" t="inlineStr"/>
       <c r="C325" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D325" t="n">
         <v>1</v>
@@ -13829,16 +13797,16 @@
         <v>0</v>
       </c>
       <c r="H325" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I325" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J325" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K325" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L325" t="n">
         <v>0</v>
@@ -13850,21 +13818,23 @@
     <row r="326">
       <c r="A326" s="1" t="inlineStr">
         <is>
-          <t>銷售、進出口業務</t>
-        </is>
-      </c>
-      <c r="B326" t="inlineStr"/>
+          <t>銅箔基板</t>
+        </is>
+      </c>
+      <c r="B326" t="n">
+        <v>0</v>
+      </c>
       <c r="C326" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D326" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E326" t="n">
         <v>0</v>
       </c>
       <c r="F326" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G326" t="n">
         <v>0</v>
@@ -13873,16 +13843,16 @@
         <v>0</v>
       </c>
       <c r="I326" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J326" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K326" t="n">
         <v>0</v>
       </c>
       <c r="L326" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M326" t="n">
         <v>0</v>
@@ -13891,7 +13861,7 @@
     <row r="327">
       <c r="A327" s="1" t="inlineStr">
         <is>
-          <t>鋁合金鋼圈</t>
+          <t>銷售、進出口業務</t>
         </is>
       </c>
       <c r="B327" t="inlineStr"/>
@@ -13902,7 +13872,7 @@
         <v>0</v>
       </c>
       <c r="E327" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F327" t="n">
         <v>0</v>
@@ -13920,7 +13890,7 @@
         <v>0</v>
       </c>
       <c r="K327" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L327" t="n">
         <v>0</v>
@@ -13932,12 +13902,12 @@
     <row r="328">
       <c r="A328" s="1" t="inlineStr">
         <is>
-          <t>鋰電池材料</t>
+          <t>鋁合金鋼圈</t>
         </is>
       </c>
       <c r="B328" t="inlineStr"/>
       <c r="C328" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D328" t="n">
         <v>0</v>
@@ -13961,10 +13931,10 @@
         <v>0</v>
       </c>
       <c r="K328" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L328" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M328" t="n">
         <v>0</v>
@@ -13973,7 +13943,7 @@
     <row r="329">
       <c r="A329" s="1" t="inlineStr">
         <is>
-          <t>鋼材</t>
+          <t>鋰電池材料</t>
         </is>
       </c>
       <c r="B329" t="inlineStr"/>
@@ -13999,22 +13969,22 @@
         <v>0</v>
       </c>
       <c r="J329" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K329" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L329" t="n">
         <v>0</v>
       </c>
       <c r="M329" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" s="1" t="inlineStr">
         <is>
-          <t>鋼筋</t>
+          <t>鋼材</t>
         </is>
       </c>
       <c r="B330" t="inlineStr"/>
@@ -14055,7 +14025,7 @@
     <row r="331">
       <c r="A331" s="1" t="inlineStr">
         <is>
-          <t>鋼線鋼纜</t>
+          <t>鋼筋</t>
         </is>
       </c>
       <c r="B331" t="inlineStr"/>
@@ -14084,7 +14054,7 @@
         <v>0</v>
       </c>
       <c r="K331" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L331" t="n">
         <v>0</v>
@@ -14096,7 +14066,7 @@
     <row r="332">
       <c r="A332" s="1" t="inlineStr">
         <is>
-          <t>鋼胚</t>
+          <t>鋼線鋼纜</t>
         </is>
       </c>
       <c r="B332" t="inlineStr"/>
@@ -14122,7 +14092,7 @@
         <v>0</v>
       </c>
       <c r="J332" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K332" t="n">
         <v>0</v>
@@ -14137,12 +14107,12 @@
     <row r="333">
       <c r="A333" s="1" t="inlineStr">
         <is>
-          <t>鋼鑄鐵元件</t>
+          <t>鋼胚</t>
         </is>
       </c>
       <c r="B333" t="inlineStr"/>
       <c r="C333" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D333" t="n">
         <v>0</v>
@@ -14172,13 +14142,13 @@
         <v>0</v>
       </c>
       <c r="M333" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="334">
       <c r="A334" s="1" t="inlineStr">
         <is>
-          <t>錢包/資產管理</t>
+          <t>鋼鑄鐵元件</t>
         </is>
       </c>
       <c r="B334" t="inlineStr"/>
@@ -14210,7 +14180,7 @@
         <v>0</v>
       </c>
       <c r="L334" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M334" t="n">
         <v>0</v>
@@ -14219,7 +14189,7 @@
     <row r="335">
       <c r="A335" s="1" t="inlineStr">
         <is>
-          <t>開發工具</t>
+          <t>錢包/資產管理</t>
         </is>
       </c>
       <c r="B335" t="inlineStr"/>
@@ -14245,7 +14215,7 @@
         <v>0</v>
       </c>
       <c r="J335" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K335" t="n">
         <v>0</v>
@@ -14260,7 +14230,7 @@
     <row r="336">
       <c r="A336" s="1" t="inlineStr">
         <is>
-          <t>隨身碟、記憶卡讀卡機</t>
+          <t>開發工具</t>
         </is>
       </c>
       <c r="B336" t="inlineStr"/>
@@ -14271,25 +14241,25 @@
         <v>0</v>
       </c>
       <c r="E336" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F336" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G336" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H336" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I336" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J336" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K336" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L336" t="n">
         <v>0</v>
@@ -14301,38 +14271,36 @@
     <row r="337">
       <c r="A337" s="1" t="inlineStr">
         <is>
-          <t>雲端作業系統</t>
-        </is>
-      </c>
-      <c r="B337" t="n">
-        <v>0</v>
-      </c>
+          <t>隨身碟、記憶卡讀卡機</t>
+        </is>
+      </c>
+      <c r="B337" t="inlineStr"/>
       <c r="C337" t="n">
         <v>0</v>
       </c>
       <c r="D337" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E337" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F337" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G337" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H337" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I337" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J337" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K337" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L337" t="n">
         <v>0</v>
@@ -14344,7 +14312,7 @@
     <row r="338">
       <c r="A338" s="1" t="inlineStr">
         <is>
-          <t>雲端安全</t>
+          <t>雲端作業系統</t>
         </is>
       </c>
       <c r="B338" t="inlineStr"/>
@@ -14367,30 +14335,28 @@
         <v>1</v>
       </c>
       <c r="I338" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J338" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K338" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L338" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M338" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="339">
       <c r="A339" s="1" t="inlineStr">
         <is>
-          <t>雲端平台</t>
-        </is>
-      </c>
-      <c r="B339" t="n">
-        <v>0</v>
-      </c>
+          <t>雲端安全</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr"/>
       <c r="C339" t="n">
         <v>0</v>
       </c>
@@ -14401,19 +14367,19 @@
         <v>0</v>
       </c>
       <c r="F339" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G339" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H339" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I339" t="n">
         <v>2</v>
       </c>
       <c r="J339" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K339" t="n">
         <v>1</v>
@@ -14428,12 +14394,10 @@
     <row r="340">
       <c r="A340" s="1" t="inlineStr">
         <is>
-          <t>雲端應用服務</t>
-        </is>
-      </c>
-      <c r="B340" t="n">
-        <v>0</v>
-      </c>
+          <t>雲端平台</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr"/>
       <c r="C340" t="n">
         <v>0</v>
       </c>
@@ -14447,22 +14411,22 @@
         <v>0</v>
       </c>
       <c r="G340" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H340" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I340" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J340" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K340" t="n">
         <v>1</v>
       </c>
       <c r="L340" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M340" t="n">
         <v>0</v>
@@ -14471,36 +14435,36 @@
     <row r="341">
       <c r="A341" s="1" t="inlineStr">
         <is>
-          <t>零售通路</t>
+          <t>雲端應用服務</t>
         </is>
       </c>
       <c r="B341" t="inlineStr"/>
       <c r="C341" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D341" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E341" t="n">
         <v>0</v>
       </c>
       <c r="F341" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G341" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H341" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I341" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J341" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K341" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L341" t="n">
         <v>0</v>
@@ -14512,7 +14476,7 @@
     <row r="342">
       <c r="A342" s="1" t="inlineStr">
         <is>
-          <t>零組件/材料</t>
+          <t>零售通路</t>
         </is>
       </c>
       <c r="B342" t="inlineStr"/>
@@ -14523,7 +14487,7 @@
         <v>0</v>
       </c>
       <c r="E342" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F342" t="n">
         <v>0</v>
@@ -14532,13 +14496,13 @@
         <v>0</v>
       </c>
       <c r="H342" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I342" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J342" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K342" t="n">
         <v>0</v>
@@ -14547,13 +14511,13 @@
         <v>0</v>
       </c>
       <c r="M342" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="343">
       <c r="A343" s="1" t="inlineStr">
         <is>
-          <t>電信服務業</t>
+          <t>零組件/材料</t>
         </is>
       </c>
       <c r="B343" t="inlineStr"/>
@@ -14570,19 +14534,19 @@
         <v>0</v>
       </c>
       <c r="G343" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H343" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I343" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J343" t="n">
         <v>0</v>
       </c>
       <c r="K343" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L343" t="n">
         <v>0</v>
@@ -14594,12 +14558,10 @@
     <row r="344">
       <c r="A344" s="1" t="inlineStr">
         <is>
-          <t>電力系統</t>
-        </is>
-      </c>
-      <c r="B344" t="n">
-        <v>0</v>
-      </c>
+          <t>電信服務業</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr"/>
       <c r="C344" t="n">
         <v>0</v>
       </c>
@@ -14622,7 +14584,7 @@
         <v>0</v>
       </c>
       <c r="J344" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K344" t="n">
         <v>0</v>
@@ -14637,7 +14599,7 @@
     <row r="345">
       <c r="A345" s="1" t="inlineStr">
         <is>
-          <t>電力設備</t>
+          <t>電力系統</t>
         </is>
       </c>
       <c r="B345" t="inlineStr"/>
@@ -14648,7 +14610,7 @@
         <v>0</v>
       </c>
       <c r="E345" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F345" t="n">
         <v>0</v>
@@ -14666,7 +14628,7 @@
         <v>0</v>
       </c>
       <c r="K345" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L345" t="n">
         <v>0</v>
@@ -14678,7 +14640,7 @@
     <row r="346">
       <c r="A346" s="1" t="inlineStr">
         <is>
-          <t>電力零售業</t>
+          <t>電力設備</t>
         </is>
       </c>
       <c r="B346" t="inlineStr"/>
@@ -14686,7 +14648,7 @@
         <v>0</v>
       </c>
       <c r="D346" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E346" t="n">
         <v>0</v>
@@ -14704,7 +14666,7 @@
         <v>0</v>
       </c>
       <c r="J346" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K346" t="n">
         <v>0</v>
@@ -14719,12 +14681,10 @@
     <row r="347">
       <c r="A347" s="1" t="inlineStr">
         <is>
-          <t>電動汽車、電動機車、電動自行車</t>
-        </is>
-      </c>
-      <c r="B347" t="n">
-        <v>0</v>
-      </c>
+          <t>電力零售業</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr"/>
       <c r="C347" t="n">
         <v>0</v>
       </c>
@@ -14753,7 +14713,7 @@
         <v>0</v>
       </c>
       <c r="L347" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M347" t="n">
         <v>0</v>
@@ -14762,10 +14722,12 @@
     <row r="348">
       <c r="A348" s="1" t="inlineStr">
         <is>
-          <t>電子書</t>
-        </is>
-      </c>
-      <c r="B348" t="inlineStr"/>
+          <t>電動汽車、電動機車、電動自行車</t>
+        </is>
+      </c>
+      <c r="B348" t="n">
+        <v>0</v>
+      </c>
       <c r="C348" t="n">
         <v>0</v>
       </c>
@@ -14791,7 +14753,7 @@
         <v>0</v>
       </c>
       <c r="K348" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L348" t="n">
         <v>0</v>
@@ -14803,7 +14765,7 @@
     <row r="349">
       <c r="A349" s="1" t="inlineStr">
         <is>
-          <t>電子觸控白板</t>
+          <t>電子書</t>
         </is>
       </c>
       <c r="B349" t="inlineStr"/>
@@ -14844,79 +14806,77 @@
     <row r="350">
       <c r="A350" s="1" t="inlineStr">
         <is>
-          <t>電子零組件、塑膠零件、五金零件</t>
-        </is>
-      </c>
-      <c r="B350" t="n">
-        <v>0</v>
-      </c>
+          <t>電子觸控白板</t>
+        </is>
+      </c>
+      <c r="B350" t="inlineStr"/>
       <c r="C350" t="n">
         <v>0</v>
       </c>
       <c r="D350" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E350" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F350" t="n">
         <v>0</v>
       </c>
       <c r="G350" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H350" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I350" t="n">
         <v>0</v>
       </c>
       <c r="J350" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K350" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L350" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M350" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="351">
       <c r="A351" s="1" t="inlineStr">
         <is>
-          <t>電容器</t>
+          <t>電子零組件、塑膠零件、五金零件</t>
         </is>
       </c>
       <c r="B351" t="inlineStr"/>
       <c r="C351" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D351" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E351" t="n">
         <v>0</v>
       </c>
       <c r="F351" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G351" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H351" t="n">
         <v>0</v>
       </c>
       <c r="I351" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J351" t="n">
         <v>1</v>
       </c>
       <c r="K351" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="L351" t="n">
         <v>1</v>
@@ -14928,18 +14888,20 @@
     <row r="352">
       <c r="A352" s="1" t="inlineStr">
         <is>
-          <t>電容器材料(如電蝕／化成鋁箔、介面瓷粉)</t>
-        </is>
-      </c>
-      <c r="B352" t="inlineStr"/>
+          <t>電容器</t>
+        </is>
+      </c>
+      <c r="B352" t="n">
+        <v>0</v>
+      </c>
       <c r="C352" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D352" t="n">
         <v>0</v>
       </c>
       <c r="E352" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F352" t="n">
         <v>0</v>
@@ -14948,33 +14910,35 @@
         <v>0</v>
       </c>
       <c r="H352" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I352" t="n">
         <v>1</v>
       </c>
       <c r="J352" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="K352" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L352" t="n">
         <v>0</v>
       </c>
       <c r="M352" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="353">
       <c r="A353" s="1" t="inlineStr">
         <is>
-          <t>電感器</t>
-        </is>
-      </c>
-      <c r="B353" t="inlineStr"/>
+          <t>電容器材料(如電蝕／化成鋁箔、介面瓷粉)</t>
+        </is>
+      </c>
+      <c r="B353" t="n">
+        <v>0</v>
+      </c>
       <c r="C353" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D353" t="n">
         <v>0</v>
@@ -14983,7 +14947,7 @@
         <v>0</v>
       </c>
       <c r="F353" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G353" t="n">
         <v>0</v>
@@ -14992,16 +14956,16 @@
         <v>1</v>
       </c>
       <c r="I353" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J353" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K353" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L353" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M353" t="n">
         <v>0</v>
@@ -15010,10 +14974,12 @@
     <row r="354">
       <c r="A354" s="1" t="inlineStr">
         <is>
-          <t>電感器材料(如鐵氧體、導電漿墨)</t>
-        </is>
-      </c>
-      <c r="B354" t="inlineStr"/>
+          <t>電感器</t>
+        </is>
+      </c>
+      <c r="B354" t="n">
+        <v>0</v>
+      </c>
       <c r="C354" t="n">
         <v>0</v>
       </c>
@@ -15021,28 +14987,28 @@
         <v>0</v>
       </c>
       <c r="E354" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F354" t="n">
         <v>0</v>
       </c>
       <c r="G354" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H354" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I354" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J354" t="n">
         <v>2</v>
       </c>
       <c r="K354" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L354" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M354" t="n">
         <v>0</v>
@@ -15051,35 +15017,33 @@
     <row r="355">
       <c r="A355" s="1" t="inlineStr">
         <is>
-          <t>電控元件</t>
-        </is>
-      </c>
-      <c r="B355" t="n">
-        <v>0</v>
-      </c>
+          <t>電感器材料(如鐵氧體、導電漿墨)</t>
+        </is>
+      </c>
+      <c r="B355" t="inlineStr"/>
       <c r="C355" t="n">
+        <v>0</v>
+      </c>
+      <c r="D355" t="n">
+        <v>0</v>
+      </c>
+      <c r="E355" t="n">
+        <v>0</v>
+      </c>
+      <c r="F355" t="n">
+        <v>0</v>
+      </c>
+      <c r="G355" t="n">
+        <v>0</v>
+      </c>
+      <c r="H355" t="n">
+        <v>1</v>
+      </c>
+      <c r="I355" t="n">
         <v>2</v>
       </c>
-      <c r="D355" t="n">
-        <v>0</v>
-      </c>
-      <c r="E355" t="n">
-        <v>2</v>
-      </c>
-      <c r="F355" t="n">
-        <v>2</v>
-      </c>
-      <c r="G355" t="n">
-        <v>0</v>
-      </c>
-      <c r="H355" t="n">
-        <v>1</v>
-      </c>
-      <c r="I355" t="n">
-        <v>0</v>
-      </c>
       <c r="J355" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K355" t="n">
         <v>1</v>
@@ -15094,7 +15058,7 @@
     <row r="356">
       <c r="A356" s="1" t="inlineStr">
         <is>
-          <t>電池</t>
+          <t>電控元件</t>
         </is>
       </c>
       <c r="B356" t="inlineStr"/>
@@ -15102,22 +15066,22 @@
         <v>0</v>
       </c>
       <c r="D356" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E356" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F356" t="n">
         <v>0</v>
       </c>
       <c r="G356" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H356" t="n">
         <v>0</v>
       </c>
       <c r="I356" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J356" t="n">
         <v>1</v>
@@ -15135,20 +15099,18 @@
     <row r="357">
       <c r="A357" s="1" t="inlineStr">
         <is>
-          <t>電池模組</t>
-        </is>
-      </c>
-      <c r="B357" t="n">
-        <v>0</v>
-      </c>
+          <t>電池</t>
+        </is>
+      </c>
+      <c r="B357" t="inlineStr"/>
       <c r="C357" t="n">
         <v>0</v>
       </c>
       <c r="D357" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E357" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F357" t="n">
         <v>0</v>
@@ -15157,10 +15119,10 @@
         <v>0</v>
       </c>
       <c r="H357" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I357" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J357" t="n">
         <v>0</v>
@@ -15178,15 +15140,17 @@
     <row r="358">
       <c r="A358" s="1" t="inlineStr">
         <is>
-          <t>電池芯</t>
-        </is>
-      </c>
-      <c r="B358" t="inlineStr"/>
+          <t>電池模組</t>
+        </is>
+      </c>
+      <c r="B358" t="n">
+        <v>0</v>
+      </c>
       <c r="C358" t="n">
         <v>0</v>
       </c>
       <c r="D358" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E358" t="n">
         <v>0</v>
@@ -15213,87 +15177,85 @@
         <v>0</v>
       </c>
       <c r="M358" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="359">
       <c r="A359" s="1" t="inlineStr">
         <is>
-          <t>電源供應器</t>
+          <t>電池芯</t>
         </is>
       </c>
       <c r="B359" t="n">
         <v>0</v>
       </c>
       <c r="C359" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D359" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E359" t="n">
         <v>0</v>
       </c>
       <c r="F359" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G359" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H359" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I359" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J359" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K359" t="n">
         <v>0</v>
       </c>
       <c r="L359" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M359" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="360">
       <c r="A360" s="1" t="inlineStr">
         <is>
-          <t>電網營造</t>
-        </is>
-      </c>
-      <c r="B360" t="n">
-        <v>0</v>
-      </c>
+          <t>電源供應器</t>
+        </is>
+      </c>
+      <c r="B360" t="inlineStr"/>
       <c r="C360" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D360" t="n">
         <v>0</v>
       </c>
       <c r="E360" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F360" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G360" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H360" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I360" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J360" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K360" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L360" t="n">
         <v>0</v>
@@ -15305,7 +15267,7 @@
     <row r="361">
       <c r="A361" s="1" t="inlineStr">
         <is>
-          <t>電網維運</t>
+          <t>電網營造</t>
         </is>
       </c>
       <c r="B361" t="inlineStr"/>
@@ -15346,7 +15308,7 @@
     <row r="362">
       <c r="A362" s="1" t="inlineStr">
         <is>
-          <t>電纜</t>
+          <t>電網維運</t>
         </is>
       </c>
       <c r="B362" t="inlineStr"/>
@@ -15375,7 +15337,7 @@
         <v>0</v>
       </c>
       <c r="K362" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L362" t="n">
         <v>0</v>
@@ -15387,7 +15349,7 @@
     <row r="363">
       <c r="A363" s="1" t="inlineStr">
         <is>
-          <t>電腦視覺</t>
+          <t>電纜</t>
         </is>
       </c>
       <c r="B363" t="inlineStr"/>
@@ -15401,19 +15363,19 @@
         <v>0</v>
       </c>
       <c r="F363" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G363" t="n">
         <v>0</v>
       </c>
       <c r="H363" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I363" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J363" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K363" t="n">
         <v>0</v>
@@ -15422,24 +15384,24 @@
         <v>0</v>
       </c>
       <c r="M363" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="364">
       <c r="A364" s="1" t="inlineStr">
         <is>
-          <t>電腦設備</t>
+          <t>電腦視覺</t>
         </is>
       </c>
       <c r="B364" t="inlineStr"/>
       <c r="C364" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D364" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E364" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F364" t="n">
         <v>0</v>
@@ -15448,19 +15410,19 @@
         <v>1</v>
       </c>
       <c r="H364" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I364" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J364" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K364" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L364" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M364" t="n">
         <v>0</v>
@@ -15469,12 +15431,12 @@
     <row r="365">
       <c r="A365" s="1" t="inlineStr">
         <is>
-          <t>電視</t>
+          <t>電腦設備</t>
         </is>
       </c>
       <c r="B365" t="inlineStr"/>
       <c r="C365" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D365" t="n">
         <v>0</v>
@@ -15483,19 +15445,19 @@
         <v>0</v>
       </c>
       <c r="F365" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G365" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H365" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I365" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J365" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K365" t="n">
         <v>0</v>
@@ -15510,7 +15472,7 @@
     <row r="366">
       <c r="A366" s="1" t="inlineStr">
         <is>
-          <t>電鍍材料</t>
+          <t>電視</t>
         </is>
       </c>
       <c r="B366" t="inlineStr"/>
@@ -15551,12 +15513,12 @@
     <row r="367">
       <c r="A367" s="1" t="inlineStr">
         <is>
-          <t>電阻器</t>
+          <t>電鍍材料</t>
         </is>
       </c>
       <c r="B367" t="inlineStr"/>
       <c r="C367" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D367" t="n">
         <v>0</v>
@@ -15574,16 +15536,16 @@
         <v>0</v>
       </c>
       <c r="I367" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J367" t="n">
         <v>0</v>
       </c>
       <c r="K367" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L367" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M367" t="n">
         <v>0</v>
@@ -15592,10 +15554,12 @@
     <row r="368">
       <c r="A368" s="1" t="inlineStr">
         <is>
-          <t>電阻器材料(氧化鋁陶瓷基板、導電漿墨)</t>
-        </is>
-      </c>
-      <c r="B368" t="inlineStr"/>
+          <t>電阻器</t>
+        </is>
+      </c>
+      <c r="B368" t="n">
+        <v>0</v>
+      </c>
       <c r="C368" t="n">
         <v>0</v>
       </c>
@@ -15612,16 +15576,16 @@
         <v>0</v>
       </c>
       <c r="H368" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I368" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J368" t="n">
         <v>1</v>
       </c>
       <c r="K368" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L368" t="n">
         <v>0</v>
@@ -15633,7 +15597,7 @@
     <row r="369">
       <c r="A369" s="1" t="inlineStr">
         <is>
-          <t>面板</t>
+          <t>電阻器材料(氧化鋁陶瓷基板、導電漿墨)</t>
         </is>
       </c>
       <c r="B369" t="inlineStr"/>
@@ -15653,13 +15617,13 @@
         <v>0</v>
       </c>
       <c r="H369" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I369" t="n">
         <v>1</v>
       </c>
       <c r="J369" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K369" t="n">
         <v>0</v>
@@ -15674,7 +15638,7 @@
     <row r="370">
       <c r="A370" s="1" t="inlineStr">
         <is>
-          <t>預拌混凝土</t>
+          <t>面板</t>
         </is>
       </c>
       <c r="B370" t="inlineStr"/>
@@ -15694,10 +15658,10 @@
         <v>0</v>
       </c>
       <c r="H370" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I370" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J370" t="n">
         <v>0</v>
@@ -15715,7 +15679,7 @@
     <row r="371">
       <c r="A371" s="1" t="inlineStr">
         <is>
-          <t>領域方案</t>
+          <t>預拌混凝土</t>
         </is>
       </c>
       <c r="B371" t="inlineStr"/>
@@ -15756,12 +15720,10 @@
     <row r="372">
       <c r="A372" s="1" t="inlineStr">
         <is>
-          <t>領域解決方案</t>
-        </is>
-      </c>
-      <c r="B372" t="n">
-        <v>0</v>
-      </c>
+          <t>領域方案</t>
+        </is>
+      </c>
+      <c r="B372" t="inlineStr"/>
       <c r="C372" t="n">
         <v>0</v>
       </c>
@@ -15772,34 +15734,34 @@
         <v>0</v>
       </c>
       <c r="F372" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G372" t="n">
         <v>0</v>
       </c>
       <c r="H372" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I372" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J372" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K372" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L372" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M372" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="373">
       <c r="A373" s="1" t="inlineStr">
         <is>
-          <t>頭顯裝置品牌廠</t>
+          <t>領域解決方案</t>
         </is>
       </c>
       <c r="B373" t="inlineStr"/>
@@ -15810,28 +15772,28 @@
         <v>0</v>
       </c>
       <c r="E373" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F373" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G373" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H373" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I373" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J373" t="n">
         <v>1</v>
       </c>
       <c r="K373" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L373" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M373" t="n">
         <v>0</v>
@@ -15840,7 +15802,7 @@
     <row r="374">
       <c r="A374" s="1" t="inlineStr">
         <is>
-          <t>顏染料</t>
+          <t>頭顯裝置品牌廠</t>
         </is>
       </c>
       <c r="B374" t="inlineStr"/>
@@ -15857,19 +15819,19 @@
         <v>0</v>
       </c>
       <c r="G374" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H374" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I374" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J374" t="n">
         <v>0</v>
       </c>
       <c r="K374" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L374" t="n">
         <v>0</v>
@@ -15881,7 +15843,7 @@
     <row r="375">
       <c r="A375" s="1" t="inlineStr">
         <is>
-          <t>顧問諮詢</t>
+          <t>顏染料</t>
         </is>
       </c>
       <c r="B375" t="n">
@@ -15891,7 +15853,7 @@
         <v>0</v>
       </c>
       <c r="D375" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E375" t="n">
         <v>0</v>
@@ -15903,19 +15865,19 @@
         <v>0</v>
       </c>
       <c r="H375" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I375" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J375" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K375" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L375" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M375" t="n">
         <v>0</v>
@@ -15924,7 +15886,7 @@
     <row r="376">
       <c r="A376" s="1" t="inlineStr">
         <is>
-          <t>顯示卡</t>
+          <t>顧問諮詢</t>
         </is>
       </c>
       <c r="B376" t="inlineStr"/>
@@ -15941,19 +15903,19 @@
         <v>0</v>
       </c>
       <c r="G376" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H376" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I376" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J376" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K376" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L376" t="n">
         <v>0</v>
@@ -15965,7 +15927,7 @@
     <row r="377">
       <c r="A377" s="1" t="inlineStr">
         <is>
-          <t>顯示器模組</t>
+          <t>顯示卡</t>
         </is>
       </c>
       <c r="B377" t="inlineStr"/>
@@ -15979,7 +15941,7 @@
         <v>0</v>
       </c>
       <c r="F377" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G377" t="n">
         <v>0</v>
@@ -15988,10 +15950,10 @@
         <v>1</v>
       </c>
       <c r="I377" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J377" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K377" t="n">
         <v>0</v>
@@ -16006,7 +15968,7 @@
     <row r="378">
       <c r="A378" s="1" t="inlineStr">
         <is>
-          <t>風場營造</t>
+          <t>顯示器模組</t>
         </is>
       </c>
       <c r="B378" t="inlineStr"/>
@@ -16023,13 +15985,13 @@
         <v>0</v>
       </c>
       <c r="G378" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H378" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I378" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J378" t="n">
         <v>0</v>
@@ -16047,7 +16009,7 @@
     <row r="379">
       <c r="A379" s="1" t="inlineStr">
         <is>
-          <t>風場規劃</t>
+          <t>風場營造</t>
         </is>
       </c>
       <c r="B379" t="inlineStr"/>
@@ -16088,7 +16050,7 @@
     <row r="380">
       <c r="A380" s="1" t="inlineStr">
         <is>
-          <t>風場開發</t>
+          <t>風場規劃</t>
         </is>
       </c>
       <c r="B380" t="inlineStr"/>
@@ -16129,7 +16091,7 @@
     <row r="381">
       <c r="A381" s="1" t="inlineStr">
         <is>
-          <t>風機維護</t>
+          <t>風場開發</t>
         </is>
       </c>
       <c r="B381" t="inlineStr"/>
@@ -16170,21 +16132,21 @@
     <row r="382">
       <c r="A382" s="1" t="inlineStr">
         <is>
-          <t>餐飲連鎖</t>
+          <t>風機維護</t>
         </is>
       </c>
       <c r="B382" t="inlineStr"/>
       <c r="C382" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D382" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E382" t="n">
         <v>0</v>
       </c>
       <c r="F382" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G382" t="n">
         <v>0</v>
@@ -16196,7 +16158,7 @@
         <v>0</v>
       </c>
       <c r="J382" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K382" t="n">
         <v>0</v>
@@ -16205,24 +16167,24 @@
         <v>0</v>
       </c>
       <c r="M382" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="383">
       <c r="A383" s="1" t="inlineStr">
         <is>
-          <t>驅動IC</t>
+          <t>餐飲連鎖</t>
         </is>
       </c>
       <c r="B383" t="inlineStr"/>
       <c r="C383" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D383" t="n">
         <v>0</v>
       </c>
       <c r="E383" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F383" t="n">
         <v>0</v>
@@ -16234,7 +16196,7 @@
         <v>0</v>
       </c>
       <c r="I383" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J383" t="n">
         <v>0</v>
@@ -16243,7 +16205,7 @@
         <v>0</v>
       </c>
       <c r="L383" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M383" t="n">
         <v>0</v>
@@ -16252,14 +16214,12 @@
     <row r="384">
       <c r="A384" s="1" t="inlineStr">
         <is>
-          <t>高/低壓輸電設施</t>
-        </is>
-      </c>
-      <c r="B384" t="n">
-        <v>0</v>
-      </c>
+          <t>驅動IC</t>
+        </is>
+      </c>
+      <c r="B384" t="inlineStr"/>
       <c r="C384" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D384" t="n">
         <v>0</v>
@@ -16280,10 +16240,10 @@
         <v>0</v>
       </c>
       <c r="J384" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K384" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L384" t="n">
         <v>0</v>
@@ -16295,7 +16255,7 @@
     <row r="385">
       <c r="A385" s="1" t="inlineStr">
         <is>
-          <t>高壓AMI</t>
+          <t>高/低壓輸電設施</t>
         </is>
       </c>
       <c r="B385" t="inlineStr"/>
@@ -16318,10 +16278,10 @@
         <v>0</v>
       </c>
       <c r="I385" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J385" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K385" t="n">
         <v>0</v>
@@ -16336,7 +16296,7 @@
     <row r="386">
       <c r="A386" s="1" t="inlineStr">
         <is>
-          <t>高爾夫球具業</t>
+          <t>高壓AMI</t>
         </is>
       </c>
       <c r="B386" t="inlineStr"/>
@@ -16377,41 +16337,84 @@
     <row r="387">
       <c r="A387" s="1" t="inlineStr">
         <is>
+          <t>高爾夫球具業</t>
+        </is>
+      </c>
+      <c r="B387" t="n">
+        <v>0</v>
+      </c>
+      <c r="C387" t="n">
+        <v>0</v>
+      </c>
+      <c r="D387" t="n">
+        <v>0</v>
+      </c>
+      <c r="E387" t="n">
+        <v>0</v>
+      </c>
+      <c r="F387" t="n">
+        <v>0</v>
+      </c>
+      <c r="G387" t="n">
+        <v>0</v>
+      </c>
+      <c r="H387" t="n">
+        <v>0</v>
+      </c>
+      <c r="I387" t="n">
+        <v>0</v>
+      </c>
+      <c r="J387" t="n">
+        <v>0</v>
+      </c>
+      <c r="K387" t="n">
+        <v>0</v>
+      </c>
+      <c r="L387" t="n">
+        <v>0</v>
+      </c>
+      <c r="M387" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" s="1" t="inlineStr">
+        <is>
           <t>齒輪箱</t>
         </is>
       </c>
-      <c r="B387" t="inlineStr"/>
-      <c r="C387" t="n">
-        <v>0</v>
-      </c>
-      <c r="D387" t="n">
-        <v>0</v>
-      </c>
-      <c r="E387" t="n">
-        <v>0</v>
-      </c>
-      <c r="F387" t="n">
-        <v>0</v>
-      </c>
-      <c r="G387" t="n">
-        <v>0</v>
-      </c>
-      <c r="H387" t="n">
-        <v>0</v>
-      </c>
-      <c r="I387" t="n">
-        <v>0</v>
-      </c>
-      <c r="J387" t="n">
-        <v>0</v>
-      </c>
-      <c r="K387" t="n">
-        <v>0</v>
-      </c>
-      <c r="L387" t="n">
-        <v>0</v>
-      </c>
-      <c r="M387" t="n">
+      <c r="B388" t="inlineStr"/>
+      <c r="C388" t="n">
+        <v>0</v>
+      </c>
+      <c r="D388" t="n">
+        <v>0</v>
+      </c>
+      <c r="E388" t="n">
+        <v>0</v>
+      </c>
+      <c r="F388" t="n">
+        <v>0</v>
+      </c>
+      <c r="G388" t="n">
+        <v>0</v>
+      </c>
+      <c r="H388" t="n">
+        <v>0</v>
+      </c>
+      <c r="I388" t="n">
+        <v>0</v>
+      </c>
+      <c r="J388" t="n">
+        <v>0</v>
+      </c>
+      <c r="K388" t="n">
+        <v>0</v>
+      </c>
+      <c r="L388" t="n">
+        <v>0</v>
+      </c>
+      <c r="M388" t="n">
         <v>0</v>
       </c>
     </row>

--- a/Result/analyze_3.xlsx
+++ b/Result/analyze_3.xlsx
@@ -441,57 +441,57 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
     </row>
@@ -556,13 +556,13 @@
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H3" t="n">
         <v>1</v>
       </c>
       <c r="I3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -670,31 +670,31 @@
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
         <v>3</v>
       </c>
-      <c r="F6" t="n">
-        <v>0</v>
-      </c>
       <c r="G6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K6" t="n">
         <v>3</v>
       </c>
-      <c r="H6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
       <c r="L6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
@@ -706,38 +706,36 @@
           <t>IC封裝測試</t>
         </is>
       </c>
-      <c r="B7" t="n">
-        <v>0</v>
-      </c>
+      <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E7" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G7" t="n">
+        <v>2</v>
+      </c>
+      <c r="H7" t="n">
+        <v>5</v>
+      </c>
+      <c r="I7" t="n">
         <v>3</v>
       </c>
-      <c r="H7" t="n">
-        <v>2</v>
-      </c>
-      <c r="I7" t="n">
-        <v>5</v>
-      </c>
       <c r="J7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K7" t="n">
         <v>1</v>
       </c>
       <c r="L7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -754,25 +752,25 @@
         <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E8" t="n">
         <v>3</v>
       </c>
       <c r="F8" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G8" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I8" t="n">
         <v>2</v>
       </c>
       <c r="J8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
@@ -790,41 +788,39 @@
           <t>IC設計</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>0</v>
-      </c>
+      <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E9" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="F9" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="G9" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="H9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L9" t="n">
         <v>1</v>
       </c>
       <c r="M9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -835,31 +831,31 @@
       </c>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G10" t="n">
         <v>3</v>
       </c>
       <c r="H10" t="n">
+        <v>2</v>
+      </c>
+      <c r="I10" t="n">
         <v>3</v>
       </c>
-      <c r="I10" t="n">
-        <v>2</v>
-      </c>
       <c r="J10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -874,21 +870,23 @@
           <t>IP設計/IC設計代工服務</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr"/>
+      <c r="B11" t="n">
+        <v>0</v>
+      </c>
       <c r="C11" t="n">
         <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E11" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -900,10 +898,10 @@
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
@@ -929,16 +927,16 @@
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
@@ -976,10 +974,10 @@
         <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
@@ -1120,9 +1118,11 @@
           <t>一般零售</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr"/>
+      <c r="B17" t="n">
+        <v>0</v>
+      </c>
       <c r="C17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
         <v>0</v>
@@ -1131,16 +1131,16 @@
         <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1222,16 +1222,16 @@
         <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
         <v>0</v>
@@ -1263,10 +1263,10 @@
         <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
         <v>0</v>
@@ -1288,34 +1288,34 @@
         <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F21" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H21" t="n">
         <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
         <v>0</v>
@@ -1338,16 +1338,16 @@
         <v>0</v>
       </c>
       <c r="F22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H22" t="n">
         <v>1</v>
       </c>
       <c r="I22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -1376,10 +1376,10 @@
         <v>0</v>
       </c>
       <c r="E23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
@@ -1428,13 +1428,13 @@
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I24" t="n">
         <v>1</v>
       </c>
       <c r="J24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
@@ -1460,7 +1460,7 @@
         <v>0</v>
       </c>
       <c r="E25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F25" t="n">
         <v>1</v>
@@ -1472,7 +1472,7 @@
         <v>1</v>
       </c>
       <c r="I25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -1539,16 +1539,16 @@
         <v>0</v>
       </c>
       <c r="D27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F27" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G27" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H27" t="n">
         <v>0</v>
@@ -1560,10 +1560,10 @@
         <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
         <v>0</v>
@@ -1674,13 +1674,13 @@
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J30" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K30" t="n">
         <v>0</v>
@@ -1709,19 +1709,19 @@
         <v>0</v>
       </c>
       <c r="F31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J31" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K31" t="n">
         <v>0</v>
@@ -1739,9 +1739,7 @@
           <t>休閒車業</t>
         </is>
       </c>
-      <c r="B32" t="n">
-        <v>0</v>
-      </c>
+      <c r="B32" t="inlineStr"/>
       <c r="C32" t="n">
         <v>0</v>
       </c>
@@ -1749,28 +1747,28 @@
         <v>0</v>
       </c>
       <c r="E32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H32" t="n">
         <v>0</v>
       </c>
       <c r="I32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
         <v>0</v>
@@ -1782,7 +1780,9 @@
           <t>伺服器</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr"/>
+      <c r="B33" t="n">
+        <v>0</v>
+      </c>
       <c r="C33" t="n">
         <v>0</v>
       </c>
@@ -1790,19 +1790,19 @@
         <v>0</v>
       </c>
       <c r="E33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H33" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -1864,7 +1864,9 @@
           <t>保健食品代理銷售及通路</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr"/>
+      <c r="B35" t="n">
+        <v>0</v>
+      </c>
       <c r="C35" t="n">
         <v>0</v>
       </c>
@@ -1872,13 +1874,13 @@
         <v>0</v>
       </c>
       <c r="E35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F35" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G35" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H35" t="n">
         <v>0</v>
@@ -1998,16 +2000,16 @@
         <v>0</v>
       </c>
       <c r="F38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -2124,10 +2126,10 @@
         <v>0</v>
       </c>
       <c r="G41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I41" t="n">
         <v>0</v>
@@ -2162,10 +2164,10 @@
         <v>0</v>
       </c>
       <c r="F42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G42" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H42" t="n">
         <v>1</v>
@@ -2174,7 +2176,7 @@
         <v>1</v>
       </c>
       <c r="J42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K42" t="n">
         <v>0</v>
@@ -2203,10 +2205,10 @@
         <v>0</v>
       </c>
       <c r="F43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H43" t="n">
         <v>0</v>
@@ -2233,23 +2235,21 @@
           <t>光學鏡片、鏡頭</t>
         </is>
       </c>
-      <c r="B44" t="n">
-        <v>0</v>
-      </c>
+      <c r="B44" t="inlineStr"/>
       <c r="C44" t="n">
         <v>0</v>
       </c>
       <c r="D44" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E44" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F44" t="n">
         <v>0</v>
       </c>
       <c r="G44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H44" t="n">
         <v>1</v>
@@ -2258,7 +2258,7 @@
         <v>1</v>
       </c>
       <c r="J44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K44" t="n">
         <v>0</v>
@@ -2267,7 +2267,7 @@
         <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="45">
@@ -2290,10 +2290,10 @@
         <v>0</v>
       </c>
       <c r="G45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I45" t="n">
         <v>0</v>
@@ -2331,13 +2331,13 @@
         <v>0</v>
       </c>
       <c r="G46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H46" t="n">
         <v>1</v>
       </c>
       <c r="I46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -2372,13 +2372,13 @@
         <v>0</v>
       </c>
       <c r="G47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H47" t="n">
         <v>1</v>
       </c>
       <c r="I47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -2440,39 +2440,41 @@
           <t>光通訊設備(如光纖電纜、光傳輸設備)</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr"/>
+      <c r="B49" t="n">
+        <v>0</v>
+      </c>
       <c r="C49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D49" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E49" t="n">
+        <v>1</v>
+      </c>
+      <c r="F49" t="n">
         <v>2</v>
       </c>
-      <c r="F49" t="n">
-        <v>1</v>
-      </c>
       <c r="G49" t="n">
+        <v>1</v>
+      </c>
+      <c r="H49" t="n">
         <v>2</v>
-      </c>
-      <c r="H49" t="n">
-        <v>1</v>
       </c>
       <c r="I49" t="n">
         <v>2</v>
       </c>
       <c r="J49" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K49" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L49" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="50">
@@ -2526,28 +2528,28 @@
         <v>0</v>
       </c>
       <c r="C51" t="n">
+        <v>3</v>
+      </c>
+      <c r="D51" t="n">
         <v>4</v>
       </c>
-      <c r="D51" t="n">
+      <c r="E51" t="n">
         <v>3</v>
       </c>
-      <c r="E51" t="n">
-        <v>4</v>
-      </c>
       <c r="F51" t="n">
+        <v>1</v>
+      </c>
+      <c r="G51" t="n">
         <v>2</v>
       </c>
-      <c r="G51" t="n">
-        <v>1</v>
-      </c>
       <c r="H51" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I51" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J51" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="K51" t="n">
         <v>1</v>
@@ -2614,28 +2616,28 @@
         <v>0</v>
       </c>
       <c r="E53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F53" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G53" t="n">
+        <v>1</v>
+      </c>
+      <c r="H53" t="n">
+        <v>1</v>
+      </c>
+      <c r="I53" t="n">
+        <v>3</v>
+      </c>
+      <c r="J53" t="n">
         <v>2</v>
-      </c>
-      <c r="H53" t="n">
-        <v>1</v>
-      </c>
-      <c r="I53" t="n">
-        <v>1</v>
-      </c>
-      <c r="J53" t="n">
-        <v>3</v>
       </c>
       <c r="K53" t="n">
         <v>2</v>
       </c>
       <c r="L53" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M53" t="n">
         <v>0</v>
@@ -2647,33 +2649,35 @@
           <t>其他電子產品及電子服務產業</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr"/>
+      <c r="B54" t="n">
+        <v>0</v>
+      </c>
       <c r="C54" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D54" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E54" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G54" t="n">
         <v>1</v>
       </c>
       <c r="H54" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I54" t="n">
         <v>4</v>
       </c>
       <c r="J54" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L54" t="n">
         <v>1</v>
@@ -2692,37 +2696,37 @@
         <v>0</v>
       </c>
       <c r="C55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D55" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E55" t="n">
+        <v>4</v>
+      </c>
+      <c r="F55" t="n">
+        <v>1</v>
+      </c>
+      <c r="G55" t="n">
         <v>2</v>
       </c>
-      <c r="F55" t="n">
-        <v>3</v>
-      </c>
-      <c r="G55" t="n">
-        <v>1</v>
-      </c>
       <c r="H55" t="n">
+        <v>4</v>
+      </c>
+      <c r="I55" t="n">
         <v>2</v>
       </c>
-      <c r="I55" t="n">
-        <v>4</v>
-      </c>
       <c r="J55" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L55" t="n">
         <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="56">
@@ -2736,31 +2740,31 @@
         <v>0</v>
       </c>
       <c r="D56" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E56" t="n">
+        <v>3</v>
+      </c>
+      <c r="F56" t="n">
+        <v>5</v>
+      </c>
+      <c r="G56" t="n">
+        <v>3</v>
+      </c>
+      <c r="H56" t="n">
+        <v>2</v>
+      </c>
+      <c r="I56" t="n">
         <v>4</v>
       </c>
-      <c r="F56" t="n">
-        <v>3</v>
-      </c>
-      <c r="G56" t="n">
-        <v>5</v>
-      </c>
-      <c r="H56" t="n">
-        <v>3</v>
-      </c>
-      <c r="I56" t="n">
+      <c r="J56" t="n">
+        <v>1</v>
+      </c>
+      <c r="K56" t="n">
         <v>2</v>
       </c>
-      <c r="J56" t="n">
-        <v>4</v>
-      </c>
-      <c r="K56" t="n">
-        <v>1</v>
-      </c>
       <c r="L56" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M56" t="n">
         <v>0</v>
@@ -2815,28 +2819,28 @@
       </c>
       <c r="B58" t="inlineStr"/>
       <c r="C58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H58" t="n">
         <v>0</v>
       </c>
       <c r="I58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K58" t="n">
         <v>0</v>
@@ -2845,7 +2849,7 @@
         <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="59">
@@ -2862,10 +2866,10 @@
         <v>0</v>
       </c>
       <c r="E59" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
@@ -2874,10 +2878,10 @@
         <v>0</v>
       </c>
       <c r="I59" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K59" t="n">
         <v>0</v>
@@ -2886,7 +2890,7 @@
         <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="60">
@@ -2897,10 +2901,10 @@
       </c>
       <c r="B60" t="inlineStr"/>
       <c r="C60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E60" t="n">
         <v>0</v>
@@ -2915,10 +2919,10 @@
         <v>0</v>
       </c>
       <c r="I60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K60" t="n">
         <v>0</v>
@@ -3029,7 +3033,7 @@
         <v>0</v>
       </c>
       <c r="F63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G63" t="n">
         <v>1</v>
@@ -3041,7 +3045,7 @@
         <v>1</v>
       </c>
       <c r="J63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K63" t="n">
         <v>0</v>
@@ -3182,7 +3186,9 @@
           <t>加工製成品</t>
         </is>
       </c>
-      <c r="B67" t="inlineStr"/>
+      <c r="B67" t="n">
+        <v>0</v>
+      </c>
       <c r="C67" t="n">
         <v>0</v>
       </c>
@@ -3199,10 +3205,10 @@
         <v>0</v>
       </c>
       <c r="H67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -3240,10 +3246,10 @@
         <v>0</v>
       </c>
       <c r="H68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -3269,10 +3275,10 @@
         <v>0</v>
       </c>
       <c r="D69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F69" t="n">
         <v>0</v>
@@ -3305,7 +3311,9 @@
           <t>化妝品</t>
         </is>
       </c>
-      <c r="B70" t="inlineStr"/>
+      <c r="B70" t="n">
+        <v>0</v>
+      </c>
       <c r="C70" t="n">
         <v>0</v>
       </c>
@@ -3348,10 +3356,10 @@
       </c>
       <c r="B71" t="inlineStr"/>
       <c r="C71" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E71" t="n">
         <v>0</v>
@@ -3366,16 +3374,16 @@
         <v>0</v>
       </c>
       <c r="I71" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J71" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K71" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M71" t="n">
         <v>0</v>
@@ -3407,16 +3415,16 @@
         <v>0</v>
       </c>
       <c r="I72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M72" t="n">
         <v>0</v>
@@ -3527,13 +3535,13 @@
         <v>0</v>
       </c>
       <c r="H75" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I75" t="n">
         <v>1</v>
       </c>
       <c r="J75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K75" t="n">
         <v>0</v>
@@ -3553,7 +3561,7 @@
       </c>
       <c r="B76" t="inlineStr"/>
       <c r="C76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D76" t="n">
         <v>0</v>
@@ -3565,13 +3573,13 @@
         <v>0</v>
       </c>
       <c r="G76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H76" t="n">
         <v>1</v>
       </c>
       <c r="I76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -3633,9 +3641,7 @@
           <t>原材料</t>
         </is>
       </c>
-      <c r="B78" t="n">
-        <v>0</v>
-      </c>
+      <c r="B78" t="inlineStr"/>
       <c r="C78" t="n">
         <v>0</v>
       </c>
@@ -3643,31 +3649,31 @@
         <v>0</v>
       </c>
       <c r="E78" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F78" t="n">
         <v>1</v>
       </c>
       <c r="G78" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H78" t="n">
         <v>0</v>
       </c>
       <c r="I78" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J78" t="n">
+        <v>1</v>
+      </c>
+      <c r="K78" t="n">
         <v>2</v>
-      </c>
-      <c r="K78" t="n">
-        <v>1</v>
       </c>
       <c r="L78" t="n">
         <v>2</v>
       </c>
       <c r="M78" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="79">
@@ -3676,7 +3682,9 @@
           <t>原物料</t>
         </is>
       </c>
-      <c r="B79" t="inlineStr"/>
+      <c r="B79" t="n">
+        <v>0</v>
+      </c>
       <c r="C79" t="n">
         <v>0</v>
       </c>
@@ -3734,10 +3742,10 @@
         <v>0</v>
       </c>
       <c r="H80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I80" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -3819,10 +3827,10 @@
         <v>0</v>
       </c>
       <c r="I82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K82" t="n">
         <v>0</v>
@@ -3842,34 +3850,34 @@
       </c>
       <c r="B83" t="inlineStr"/>
       <c r="C83" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D83" t="n">
         <v>1</v>
       </c>
       <c r="E83" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F83" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G83" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H83" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I83" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J83" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K83" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L83" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M83" t="n">
         <v>0</v>
@@ -3980,16 +3988,16 @@
         <v>0</v>
       </c>
       <c r="H86" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I86" t="n">
         <v>1</v>
       </c>
       <c r="J86" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K86" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L86" t="n">
         <v>0</v>
@@ -4015,25 +4023,25 @@
         <v>0</v>
       </c>
       <c r="F87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H87" t="n">
         <v>0</v>
       </c>
       <c r="I87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M87" t="n">
         <v>0</v>
@@ -4062,10 +4070,10 @@
         <v>0</v>
       </c>
       <c r="H88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -4086,14 +4094,12 @@
           <t>塑膠製品</t>
         </is>
       </c>
-      <c r="B89" t="n">
-        <v>0</v>
-      </c>
+      <c r="B89" t="inlineStr"/>
       <c r="C89" t="n">
         <v>1</v>
       </c>
       <c r="D89" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E89" t="n">
         <v>1</v>
@@ -4102,22 +4108,22 @@
         <v>1</v>
       </c>
       <c r="G89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H89" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I89" t="n">
         <v>1</v>
       </c>
       <c r="J89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K89" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M89" t="n">
         <v>0</v>
@@ -4184,13 +4190,13 @@
         <v>0</v>
       </c>
       <c r="G91" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H91" t="n">
         <v>1</v>
       </c>
       <c r="I91" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -4211,14 +4217,12 @@
           <t>大功率鋰電池芯/模組、電池管理系統、動力馬達等零組件</t>
         </is>
       </c>
-      <c r="B92" t="n">
-        <v>0</v>
-      </c>
+      <c r="B92" t="inlineStr"/>
       <c r="C92" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D92" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E92" t="n">
         <v>1</v>
@@ -4227,19 +4231,19 @@
         <v>1</v>
       </c>
       <c r="G92" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H92" t="n">
         <v>0</v>
       </c>
       <c r="I92" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J92" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K92" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L92" t="n">
         <v>1</v>
@@ -4254,9 +4258,7 @@
           <t>天然瓦斯供應</t>
         </is>
       </c>
-      <c r="B93" t="n">
-        <v>0</v>
-      </c>
+      <c r="B93" t="inlineStr"/>
       <c r="C93" t="n">
         <v>0</v>
       </c>
@@ -4358,10 +4360,10 @@
         <v>0</v>
       </c>
       <c r="I95" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J95" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K95" t="n">
         <v>0</v>
@@ -4370,7 +4372,7 @@
         <v>0</v>
       </c>
       <c r="M95" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="96">
@@ -4399,10 +4401,10 @@
         <v>0</v>
       </c>
       <c r="I96" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J96" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K96" t="n">
         <v>0</v>
@@ -4601,16 +4603,16 @@
         <v>0</v>
       </c>
       <c r="H101" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I101" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J101" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K101" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L101" t="n">
         <v>0</v>
@@ -4627,7 +4629,7 @@
       </c>
       <c r="B102" t="inlineStr"/>
       <c r="C102" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D102" t="n">
         <v>1</v>
@@ -4639,19 +4641,19 @@
         <v>1</v>
       </c>
       <c r="G102" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H102" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I102" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J102" t="n">
         <v>1</v>
       </c>
       <c r="K102" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L102" t="n">
         <v>0</v>
@@ -4724,16 +4726,16 @@
         <v>0</v>
       </c>
       <c r="H104" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I104" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J104" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K104" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L104" t="n">
         <v>0</v>
@@ -4759,25 +4761,25 @@
         <v>0</v>
       </c>
       <c r="F105" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G105" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H105" t="n">
         <v>1</v>
       </c>
       <c r="I105" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J105" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K105" t="n">
         <v>1</v>
       </c>
       <c r="L105" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M105" t="n">
         <v>0</v>
@@ -4794,31 +4796,31 @@
         <v>0</v>
       </c>
       <c r="D106" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E106" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F106" t="n">
         <v>0</v>
       </c>
       <c r="G106" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H106" t="n">
+        <v>1</v>
+      </c>
+      <c r="I106" t="n">
         <v>2</v>
       </c>
-      <c r="I106" t="n">
-        <v>1</v>
-      </c>
       <c r="J106" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K106" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L106" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M106" t="n">
         <v>0</v>
@@ -4912,9 +4914,7 @@
           <t>工業用紙</t>
         </is>
       </c>
-      <c r="B109" t="n">
-        <v>0</v>
-      </c>
+      <c r="B109" t="inlineStr"/>
       <c r="C109" t="n">
         <v>0</v>
       </c>
@@ -4955,9 +4955,7 @@
           <t>工業用設備</t>
         </is>
       </c>
-      <c r="B110" t="n">
-        <v>0</v>
-      </c>
+      <c r="B110" t="inlineStr"/>
       <c r="C110" t="n">
         <v>0</v>
       </c>
@@ -4971,10 +4969,10 @@
         <v>0</v>
       </c>
       <c r="G110" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H110" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I110" t="n">
         <v>0</v>
@@ -5002,31 +5000,31 @@
         <v>0</v>
       </c>
       <c r="C111" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D111" t="n">
+        <v>1</v>
+      </c>
+      <c r="E111" t="n">
         <v>2</v>
       </c>
-      <c r="E111" t="n">
-        <v>1</v>
-      </c>
       <c r="F111" t="n">
+        <v>0</v>
+      </c>
+      <c r="G111" t="n">
         <v>2</v>
       </c>
-      <c r="G111" t="n">
-        <v>0</v>
-      </c>
       <c r="H111" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I111" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J111" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K111" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L111" t="n">
         <v>0</v>
@@ -5043,7 +5041,7 @@
       </c>
       <c r="B112" t="inlineStr"/>
       <c r="C112" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D112" t="n">
         <v>0</v>
@@ -5061,10 +5059,10 @@
         <v>0</v>
       </c>
       <c r="I112" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J112" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K112" t="n">
         <v>0</v>
@@ -5073,7 +5071,7 @@
         <v>0</v>
       </c>
       <c r="M112" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="113">
@@ -5084,7 +5082,7 @@
       </c>
       <c r="B113" t="inlineStr"/>
       <c r="C113" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D113" t="n">
         <v>0</v>
@@ -5102,10 +5100,10 @@
         <v>0</v>
       </c>
       <c r="I113" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J113" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K113" t="n">
         <v>0</v>
@@ -5114,7 +5112,7 @@
         <v>0</v>
       </c>
       <c r="M113" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="114">
@@ -5330,7 +5328,7 @@
       </c>
       <c r="B119" t="inlineStr"/>
       <c r="C119" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D119" t="n">
         <v>0</v>
@@ -5339,16 +5337,16 @@
         <v>0</v>
       </c>
       <c r="F119" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G119" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H119" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I119" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -5371,34 +5369,34 @@
       </c>
       <c r="B120" t="inlineStr"/>
       <c r="C120" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D120" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E120" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F120" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G120" t="n">
         <v>1</v>
       </c>
       <c r="H120" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I120" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J120" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K120" t="n">
         <v>1</v>
       </c>
       <c r="L120" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M120" t="n">
         <v>0</v>
@@ -5414,16 +5412,16 @@
         <v>0</v>
       </c>
       <c r="C121" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D121" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E121" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F121" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G121" t="n">
         <v>0</v>
@@ -5432,10 +5430,10 @@
         <v>0</v>
       </c>
       <c r="I121" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J121" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K121" t="n">
         <v>0</v>
@@ -5546,7 +5544,7 @@
         <v>0</v>
       </c>
       <c r="F124" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G124" t="n">
         <v>0</v>
@@ -5555,10 +5553,10 @@
         <v>0</v>
       </c>
       <c r="I124" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J124" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K124" t="n">
         <v>0</v>
@@ -5622,19 +5620,19 @@
         <v>0</v>
       </c>
       <c r="D126" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E126" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F126" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G126" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H126" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I126" t="n">
         <v>0</v>
@@ -5672,10 +5670,10 @@
         <v>0</v>
       </c>
       <c r="G127" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H127" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I127" t="n">
         <v>0</v>
@@ -5699,11 +5697,9 @@
           <t>應用/系統軟體設計開發</t>
         </is>
       </c>
-      <c r="B128" t="n">
-        <v>0</v>
-      </c>
+      <c r="B128" t="inlineStr"/>
       <c r="C128" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D128" t="n">
         <v>0</v>
@@ -5712,7 +5708,7 @@
         <v>0</v>
       </c>
       <c r="F128" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G128" t="n">
         <v>2</v>
@@ -5721,19 +5717,19 @@
         <v>2</v>
       </c>
       <c r="I128" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J128" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K128" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L128" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M128" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="129">
@@ -5753,7 +5749,7 @@
         <v>0</v>
       </c>
       <c r="F129" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G129" t="n">
         <v>1</v>
@@ -5765,7 +5761,7 @@
         <v>1</v>
       </c>
       <c r="J129" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K129" t="n">
         <v>0</v>
@@ -5800,10 +5796,10 @@
         <v>0</v>
       </c>
       <c r="H130" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I130" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -5834,10 +5830,10 @@
         <v>0</v>
       </c>
       <c r="E131" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F131" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G131" t="n">
         <v>0</v>
@@ -5846,7 +5842,7 @@
         <v>0</v>
       </c>
       <c r="I131" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J131" t="n">
         <v>1</v>
@@ -5855,10 +5851,10 @@
         <v>1</v>
       </c>
       <c r="L131" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M131" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="132">
@@ -5869,13 +5865,13 @@
       </c>
       <c r="B132" t="inlineStr"/>
       <c r="C132" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D132" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E132" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F132" t="n">
         <v>0</v>
@@ -5890,10 +5886,10 @@
         <v>0</v>
       </c>
       <c r="J132" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K132" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L132" t="n">
         <v>0</v>
@@ -5925,10 +5921,10 @@
         <v>0</v>
       </c>
       <c r="H133" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I133" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -6086,10 +6082,10 @@
         <v>0</v>
       </c>
       <c r="G137" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H137" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I137" t="n">
         <v>0</v>
@@ -6115,7 +6111,7 @@
       </c>
       <c r="B138" t="inlineStr"/>
       <c r="C138" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D138" t="n">
         <v>0</v>
@@ -6159,7 +6155,7 @@
         <v>0</v>
       </c>
       <c r="D139" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E139" t="n">
         <v>1</v>
@@ -6174,7 +6170,7 @@
         <v>1</v>
       </c>
       <c r="I139" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -6253,7 +6249,7 @@
         <v>0</v>
       </c>
       <c r="H141" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I141" t="n">
         <v>1</v>
@@ -6262,7 +6258,7 @@
         <v>1</v>
       </c>
       <c r="K141" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L141" t="n">
         <v>0</v>
@@ -6335,10 +6331,10 @@
         <v>0</v>
       </c>
       <c r="H143" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I143" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -6376,19 +6372,19 @@
         <v>0</v>
       </c>
       <c r="H144" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I144" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
       </c>
       <c r="K144" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L144" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M144" t="n">
         <v>0</v>
@@ -6417,16 +6413,16 @@
         <v>0</v>
       </c>
       <c r="H145" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I145" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J145" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K145" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L145" t="n">
         <v>0</v>
@@ -6455,10 +6451,10 @@
         <v>0</v>
       </c>
       <c r="G146" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H146" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I146" t="n">
         <v>0</v>
@@ -6499,16 +6495,16 @@
         <v>0</v>
       </c>
       <c r="H147" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I147" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J147" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K147" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L147" t="n">
         <v>0</v>
@@ -6525,19 +6521,19 @@
       </c>
       <c r="B148" t="inlineStr"/>
       <c r="C148" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D148" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E148" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F148" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G148" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H148" t="n">
         <v>0</v>
@@ -6564,9 +6560,7 @@
           <t>文化用紙</t>
         </is>
       </c>
-      <c r="B149" t="n">
-        <v>0</v>
-      </c>
+      <c r="B149" t="inlineStr"/>
       <c r="C149" t="n">
         <v>0</v>
       </c>
@@ -6589,10 +6583,10 @@
         <v>0</v>
       </c>
       <c r="J149" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K149" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L149" t="n">
         <v>0</v>
@@ -6609,13 +6603,13 @@
       </c>
       <c r="B150" t="inlineStr"/>
       <c r="C150" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D150" t="n">
         <v>1</v>
       </c>
       <c r="E150" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F150" t="n">
         <v>0</v>
@@ -6650,10 +6644,10 @@
       </c>
       <c r="B151" t="inlineStr"/>
       <c r="C151" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D151" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E151" t="n">
         <v>0</v>
@@ -6662,25 +6656,25 @@
         <v>0</v>
       </c>
       <c r="G151" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H151" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I151" t="n">
         <v>0</v>
       </c>
       <c r="J151" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K151" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L151" t="n">
         <v>0</v>
       </c>
       <c r="M151" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="152">
@@ -6689,9 +6683,7 @@
           <t>晶片組</t>
         </is>
       </c>
-      <c r="B152" t="n">
-        <v>0</v>
-      </c>
+      <c r="B152" t="inlineStr"/>
       <c r="C152" t="n">
         <v>0</v>
       </c>
@@ -6705,13 +6697,13 @@
         <v>0</v>
       </c>
       <c r="G152" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H152" t="n">
         <v>1</v>
       </c>
       <c r="I152" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -6734,7 +6726,7 @@
       </c>
       <c r="B153" t="inlineStr"/>
       <c r="C153" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D153" t="n">
         <v>0</v>
@@ -6749,19 +6741,19 @@
         <v>0</v>
       </c>
       <c r="H153" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I153" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
       </c>
       <c r="K153" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L153" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M153" t="n">
         <v>0</v>
@@ -6793,10 +6785,10 @@
         <v>0</v>
       </c>
       <c r="I154" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J154" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K154" t="n">
         <v>0</v>
@@ -6866,25 +6858,25 @@
         <v>0</v>
       </c>
       <c r="F156" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G156" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H156" t="n">
         <v>0</v>
       </c>
       <c r="I156" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J156" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K156" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L156" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M156" t="n">
         <v>0</v>
@@ -6901,10 +6893,10 @@
         <v>0</v>
       </c>
       <c r="D157" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E157" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F157" t="n">
         <v>0</v>
@@ -6913,13 +6905,13 @@
         <v>0</v>
       </c>
       <c r="H157" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I157" t="n">
         <v>2</v>
       </c>
       <c r="J157" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K157" t="n">
         <v>0</v>
@@ -6945,19 +6937,19 @@
         <v>0</v>
       </c>
       <c r="E158" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F158" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G158" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H158" t="n">
         <v>1</v>
       </c>
       <c r="I158" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -7036,10 +7028,10 @@
         <v>0</v>
       </c>
       <c r="H160" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I160" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -7077,10 +7069,10 @@
         <v>0</v>
       </c>
       <c r="H161" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I161" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -7118,19 +7110,19 @@
         <v>0</v>
       </c>
       <c r="H162" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I162" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J162" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K162" t="n">
         <v>1</v>
       </c>
       <c r="L162" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M162" t="n">
         <v>0</v>
@@ -7159,13 +7151,13 @@
         <v>0</v>
       </c>
       <c r="H163" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I163" t="n">
         <v>1</v>
       </c>
       <c r="J163" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K163" t="n">
         <v>0</v>
@@ -7197,13 +7189,13 @@
         <v>0</v>
       </c>
       <c r="G164" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H164" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I164" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -7235,22 +7227,22 @@
         <v>0</v>
       </c>
       <c r="F165" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G165" t="n">
         <v>1</v>
       </c>
       <c r="H165" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I165" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J165" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K165" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L165" t="n">
         <v>0</v>
@@ -7267,7 +7259,7 @@
       </c>
       <c r="B166" t="inlineStr"/>
       <c r="C166" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D166" t="n">
         <v>0</v>
@@ -7285,10 +7277,10 @@
         <v>0</v>
       </c>
       <c r="I166" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J166" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K166" t="n">
         <v>0</v>
@@ -7297,7 +7289,7 @@
         <v>0</v>
       </c>
       <c r="M166" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="167">
@@ -7308,28 +7300,28 @@
       </c>
       <c r="B167" t="inlineStr"/>
       <c r="C167" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D167" t="n">
         <v>1</v>
       </c>
       <c r="E167" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F167" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G167" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H167" t="n">
         <v>0</v>
       </c>
       <c r="I167" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J167" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K167" t="n">
         <v>0</v>
@@ -7338,7 +7330,7 @@
         <v>0</v>
       </c>
       <c r="M167" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="168">
@@ -7516,10 +7508,10 @@
         <v>0</v>
       </c>
       <c r="D172" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E172" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F172" t="n">
         <v>0</v>
@@ -7531,10 +7523,10 @@
         <v>0</v>
       </c>
       <c r="I172" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J172" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K172" t="n">
         <v>0</v>
@@ -7552,9 +7544,11 @@
           <t>流行音樂及文化內容產業</t>
         </is>
       </c>
-      <c r="B173" t="inlineStr"/>
+      <c r="B173" t="n">
+        <v>0</v>
+      </c>
       <c r="C173" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D173" t="n">
         <v>0</v>
@@ -7569,10 +7563,10 @@
         <v>0</v>
       </c>
       <c r="H173" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I173" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -7675,9 +7669,7 @@
           <t>清潔用品</t>
         </is>
       </c>
-      <c r="B176" t="n">
-        <v>0</v>
-      </c>
+      <c r="B176" t="inlineStr"/>
       <c r="C176" t="n">
         <v>0</v>
       </c>
@@ -7718,9 +7710,7 @@
           <t>濾波器、振盪器</t>
         </is>
       </c>
-      <c r="B177" t="n">
-        <v>0</v>
-      </c>
+      <c r="B177" t="inlineStr"/>
       <c r="C177" t="n">
         <v>0</v>
       </c>
@@ -7734,19 +7724,19 @@
         <v>0</v>
       </c>
       <c r="G177" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H177" t="n">
         <v>1</v>
       </c>
       <c r="I177" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J177" t="n">
         <v>1</v>
       </c>
       <c r="K177" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L177" t="n">
         <v>0</v>
@@ -7802,7 +7792,9 @@
           <t>無線通訊設備(如行動電話、衛星定位系統、衛星通訊設備、微波通訊設備、數位機上盒)</t>
         </is>
       </c>
-      <c r="B179" t="inlineStr"/>
+      <c r="B179" t="n">
+        <v>0</v>
+      </c>
       <c r="C179" t="n">
         <v>1</v>
       </c>
@@ -7813,25 +7805,25 @@
         <v>1</v>
       </c>
       <c r="F179" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G179" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H179" t="n">
+        <v>5</v>
+      </c>
+      <c r="I179" t="n">
+        <v>1</v>
+      </c>
+      <c r="J179" t="n">
+        <v>0</v>
+      </c>
+      <c r="K179" t="n">
         <v>2</v>
       </c>
-      <c r="I179" t="n">
-        <v>5</v>
-      </c>
-      <c r="J179" t="n">
-        <v>1</v>
-      </c>
-      <c r="K179" t="n">
-        <v>0</v>
-      </c>
       <c r="L179" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M179" t="n">
         <v>0</v>
@@ -7863,10 +7855,10 @@
         <v>0</v>
       </c>
       <c r="I180" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J180" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K180" t="n">
         <v>0</v>
@@ -7889,28 +7881,28 @@
         <v>0</v>
       </c>
       <c r="D181" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E181" t="n">
         <v>1</v>
       </c>
       <c r="F181" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G181" t="n">
         <v>0</v>
       </c>
       <c r="H181" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I181" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J181" t="n">
         <v>2</v>
       </c>
       <c r="K181" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L181" t="n">
         <v>0</v>
@@ -7927,7 +7919,7 @@
       </c>
       <c r="B182" t="inlineStr"/>
       <c r="C182" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D182" t="n">
         <v>0</v>
@@ -7942,19 +7934,19 @@
         <v>0</v>
       </c>
       <c r="H182" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I182" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J182" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K182" t="n">
         <v>1</v>
       </c>
       <c r="L182" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M182" t="n">
         <v>0</v>
@@ -8018,22 +8010,22 @@
         <v>0</v>
       </c>
       <c r="F184" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G184" t="n">
         <v>1</v>
       </c>
       <c r="H184" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I184" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J184" t="n">
         <v>1</v>
       </c>
       <c r="K184" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L184" t="n">
         <v>0</v>
@@ -8048,7 +8040,9 @@
           <t>營養食品</t>
         </is>
       </c>
-      <c r="B185" t="inlineStr"/>
+      <c r="B185" t="n">
+        <v>0</v>
+      </c>
       <c r="C185" t="n">
         <v>0</v>
       </c>
@@ -8188,19 +8182,19 @@
         <v>0</v>
       </c>
       <c r="H188" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I188" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J188" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K188" t="n">
         <v>1</v>
       </c>
       <c r="L188" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M188" t="n">
         <v>0</v>
@@ -8270,10 +8264,10 @@
         <v>0</v>
       </c>
       <c r="H190" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I190" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -8299,10 +8293,10 @@
         <v>0</v>
       </c>
       <c r="D191" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E191" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F191" t="n">
         <v>0</v>
@@ -8349,19 +8343,19 @@
         <v>0</v>
       </c>
       <c r="G192" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H192" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I192" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J192" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K192" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L192" t="n">
         <v>0</v>
@@ -8417,20 +8411,18 @@
           <t>環保潔能服務產業</t>
         </is>
       </c>
-      <c r="B194" t="n">
-        <v>0</v>
-      </c>
+      <c r="B194" t="inlineStr"/>
       <c r="C194" t="n">
         <v>0</v>
       </c>
       <c r="D194" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E194" t="n">
         <v>1</v>
       </c>
       <c r="F194" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G194" t="n">
         <v>0</v>
@@ -8477,13 +8469,13 @@
         <v>0</v>
       </c>
       <c r="H195" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I195" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J195" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K195" t="n">
         <v>0</v>
@@ -8506,7 +8498,7 @@
         <v>0</v>
       </c>
       <c r="D196" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E196" t="n">
         <v>1</v>
@@ -8518,22 +8510,22 @@
         <v>1</v>
       </c>
       <c r="H196" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I196" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J196" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K196" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L196" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M196" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="197">
@@ -8542,39 +8534,41 @@
           <t>生產製程及檢測設備</t>
         </is>
       </c>
-      <c r="B197" t="inlineStr"/>
+      <c r="B197" t="n">
+        <v>0</v>
+      </c>
       <c r="C197" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D197" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E197" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F197" t="n">
+        <v>3</v>
+      </c>
+      <c r="G197" t="n">
+        <v>5</v>
+      </c>
+      <c r="H197" t="n">
+        <v>1</v>
+      </c>
+      <c r="I197" t="n">
+        <v>6</v>
+      </c>
+      <c r="J197" t="n">
         <v>2</v>
       </c>
-      <c r="G197" t="n">
+      <c r="K197" t="n">
+        <v>1</v>
+      </c>
+      <c r="L197" t="n">
+        <v>1</v>
+      </c>
+      <c r="M197" t="n">
         <v>3</v>
-      </c>
-      <c r="H197" t="n">
-        <v>5</v>
-      </c>
-      <c r="I197" t="n">
-        <v>1</v>
-      </c>
-      <c r="J197" t="n">
-        <v>6</v>
-      </c>
-      <c r="K197" t="n">
-        <v>2</v>
-      </c>
-      <c r="L197" t="n">
-        <v>1</v>
-      </c>
-      <c r="M197" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="198">
@@ -8717,10 +8711,10 @@
         <v>0</v>
       </c>
       <c r="F201" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G201" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H201" t="n">
         <v>0</v>
@@ -8761,10 +8755,10 @@
         <v>0</v>
       </c>
       <c r="G202" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H202" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I202" t="n">
         <v>0</v>
@@ -8793,10 +8787,10 @@
         <v>0</v>
       </c>
       <c r="D203" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E203" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F203" t="n">
         <v>0</v>
@@ -8805,13 +8799,13 @@
         <v>0</v>
       </c>
       <c r="H203" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I203" t="n">
         <v>1</v>
       </c>
       <c r="J203" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K203" t="n">
         <v>0</v>
@@ -8837,7 +8831,7 @@
         <v>1</v>
       </c>
       <c r="E204" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F204" t="n">
         <v>0</v>
@@ -8849,19 +8843,19 @@
         <v>0</v>
       </c>
       <c r="I204" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J204" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K204" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L204" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M204" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="205">
@@ -8878,7 +8872,7 @@
         <v>1</v>
       </c>
       <c r="E205" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F205" t="n">
         <v>0</v>
@@ -8887,13 +8881,13 @@
         <v>0</v>
       </c>
       <c r="H205" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I205" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J205" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K205" t="n">
         <v>0</v>
@@ -8975,10 +8969,10 @@
         <v>0</v>
       </c>
       <c r="J207" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K207" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L207" t="n">
         <v>0</v>
@@ -8995,37 +8989,37 @@
       </c>
       <c r="B208" t="inlineStr"/>
       <c r="C208" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D208" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E208" t="n">
+        <v>1</v>
+      </c>
+      <c r="F208" t="n">
+        <v>3</v>
+      </c>
+      <c r="G208" t="n">
         <v>2</v>
       </c>
-      <c r="F208" t="n">
-        <v>1</v>
-      </c>
-      <c r="G208" t="n">
-        <v>3</v>
-      </c>
       <c r="H208" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I208" t="n">
         <v>5</v>
       </c>
       <c r="J208" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K208" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L208" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M208" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="209">
@@ -9048,13 +9042,13 @@
         <v>0</v>
       </c>
       <c r="G209" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H209" t="n">
         <v>1</v>
       </c>
       <c r="I209" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J209" t="n">
         <v>0</v>
@@ -9092,10 +9086,10 @@
         <v>0</v>
       </c>
       <c r="H210" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I210" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J210" t="n">
         <v>0</v>
@@ -9127,19 +9121,19 @@
         <v>0</v>
       </c>
       <c r="F211" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G211" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H211" t="n">
         <v>2</v>
       </c>
       <c r="I211" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J211" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K211" t="n">
         <v>0</v>
@@ -9338,10 +9332,10 @@
         <v>0</v>
       </c>
       <c r="H216" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I216" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J216" t="n">
         <v>0</v>
@@ -9373,25 +9367,25 @@
         <v>0</v>
       </c>
       <c r="F217" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G217" t="n">
         <v>1</v>
       </c>
       <c r="H217" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I217" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J217" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K217" t="n">
         <v>1</v>
       </c>
       <c r="L217" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M217" t="n">
         <v>0</v>
@@ -9411,25 +9405,25 @@
         <v>0</v>
       </c>
       <c r="E218" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F218" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G218" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H218" t="n">
         <v>1</v>
       </c>
       <c r="I218" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J218" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K218" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L218" t="n">
         <v>0</v>
@@ -9458,19 +9452,19 @@
         <v>0</v>
       </c>
       <c r="G219" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H219" t="n">
         <v>1</v>
       </c>
       <c r="I219" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J219" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K219" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L219" t="n">
         <v>0</v>
@@ -9490,34 +9484,34 @@
         <v>0</v>
       </c>
       <c r="D220" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E220" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F220" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G220" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H220" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="I220" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J220" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K220" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L220" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M220" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="221">
@@ -9537,28 +9531,28 @@
         <v>1</v>
       </c>
       <c r="F221" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G221" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H221" t="n">
         <v>4</v>
       </c>
       <c r="I221" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J221" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K221" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L221" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M221" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="222">
@@ -9590,10 +9584,10 @@
         <v>0</v>
       </c>
       <c r="J222" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K222" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L222" t="n">
         <v>0</v>
@@ -9619,19 +9613,19 @@
         <v>0</v>
       </c>
       <c r="F223" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G223" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H223" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I223" t="n">
         <v>1</v>
       </c>
       <c r="J223" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K223" t="n">
         <v>0</v>
@@ -9742,7 +9736,7 @@
         <v>0</v>
       </c>
       <c r="F226" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G226" t="n">
         <v>0</v>
@@ -9751,10 +9745,10 @@
         <v>0</v>
       </c>
       <c r="I226" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J226" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K226" t="n">
         <v>0</v>
@@ -9786,13 +9780,13 @@
         <v>0</v>
       </c>
       <c r="G227" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H227" t="n">
         <v>1</v>
       </c>
       <c r="I227" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J227" t="n">
         <v>0</v>
@@ -9827,22 +9821,22 @@
         <v>0</v>
       </c>
       <c r="G228" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H228" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I228" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J228" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K228" t="n">
         <v>1</v>
       </c>
       <c r="L228" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M228" t="n">
         <v>0</v>
@@ -9868,22 +9862,22 @@
         <v>0</v>
       </c>
       <c r="G229" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H229" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I229" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J229" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K229" t="n">
         <v>1</v>
       </c>
       <c r="L229" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M229" t="n">
         <v>0</v>
@@ -9895,36 +9889,38 @@
           <t>網路設備(如數據機、網路卡、閘道器、路由器、網路電話)</t>
         </is>
       </c>
-      <c r="B230" t="inlineStr"/>
+      <c r="B230" t="n">
+        <v>0</v>
+      </c>
       <c r="C230" t="n">
         <v>1</v>
       </c>
       <c r="D230" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E230" t="n">
         <v>2</v>
       </c>
       <c r="F230" t="n">
+        <v>1</v>
+      </c>
+      <c r="G230" t="n">
         <v>2</v>
       </c>
-      <c r="G230" t="n">
-        <v>1</v>
-      </c>
       <c r="H230" t="n">
+        <v>6</v>
+      </c>
+      <c r="I230" t="n">
+        <v>1</v>
+      </c>
+      <c r="J230" t="n">
+        <v>1</v>
+      </c>
+      <c r="K230" t="n">
         <v>2</v>
       </c>
-      <c r="I230" t="n">
-        <v>6</v>
-      </c>
-      <c r="J230" t="n">
-        <v>1</v>
-      </c>
-      <c r="K230" t="n">
-        <v>1</v>
-      </c>
       <c r="L230" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M230" t="n">
         <v>0</v>
@@ -9944,19 +9940,19 @@
         <v>0</v>
       </c>
       <c r="E231" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F231" t="n">
         <v>1</v>
       </c>
       <c r="G231" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H231" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I231" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J231" t="n">
         <v>1</v>
@@ -9965,7 +9961,7 @@
         <v>1</v>
       </c>
       <c r="L231" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M231" t="n">
         <v>0</v>
@@ -10003,13 +9999,13 @@
         <v>0</v>
       </c>
       <c r="K232" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L232" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M232" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="233">
@@ -10029,25 +10025,25 @@
         <v>0</v>
       </c>
       <c r="F233" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G233" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H233" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I233" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J233" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K233" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L233" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M233" t="n">
         <v>0</v>
@@ -10105,25 +10101,25 @@
         <v>0</v>
       </c>
       <c r="D235" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E235" t="n">
         <v>1</v>
       </c>
       <c r="F235" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G235" t="n">
         <v>0</v>
       </c>
       <c r="H235" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I235" t="n">
         <v>1</v>
       </c>
       <c r="J235" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K235" t="n">
         <v>0</v>
@@ -10161,10 +10157,10 @@
         <v>0</v>
       </c>
       <c r="I236" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J236" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K236" t="n">
         <v>0</v>
@@ -10237,22 +10233,22 @@
         <v>0</v>
       </c>
       <c r="G238" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H238" t="n">
         <v>1</v>
       </c>
       <c r="I238" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J238" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K238" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L238" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M238" t="n">
         <v>0</v>
@@ -10281,19 +10277,19 @@
         <v>0</v>
       </c>
       <c r="H239" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I239" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J239" t="n">
         <v>0</v>
       </c>
       <c r="K239" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L239" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M239" t="n">
         <v>0</v>
@@ -10325,10 +10321,10 @@
         <v>0</v>
       </c>
       <c r="I240" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J240" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K240" t="n">
         <v>0</v>
@@ -10521,16 +10517,16 @@
         <v>0</v>
       </c>
       <c r="F245" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G245" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H245" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I245" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J245" t="n">
         <v>0</v>
@@ -10568,16 +10564,16 @@
         <v>0</v>
       </c>
       <c r="H246" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I246" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J246" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K246" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L246" t="n">
         <v>0</v>
@@ -10612,10 +10608,10 @@
         <v>0</v>
       </c>
       <c r="I247" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J247" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K247" t="n">
         <v>0</v>
@@ -10633,7 +10629,9 @@
           <t>藥品代理銷售及通路</t>
         </is>
       </c>
-      <c r="B248" t="inlineStr"/>
+      <c r="B248" t="n">
+        <v>0</v>
+      </c>
       <c r="C248" t="n">
         <v>0</v>
       </c>
@@ -10641,13 +10639,13 @@
         <v>0</v>
       </c>
       <c r="E248" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F248" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G248" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H248" t="n">
         <v>0</v>
@@ -10679,19 +10677,19 @@
         <v>0</v>
       </c>
       <c r="D249" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E249" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F249" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G249" t="n">
         <v>1</v>
       </c>
       <c r="H249" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I249" t="n">
         <v>0</v>
@@ -10726,19 +10724,19 @@
         <v>0</v>
       </c>
       <c r="F250" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G250" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H250" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I250" t="n">
         <v>1</v>
       </c>
       <c r="J250" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K250" t="n">
         <v>0</v>
@@ -10814,16 +10812,16 @@
         <v>0</v>
       </c>
       <c r="H252" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I252" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J252" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K252" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L252" t="n">
         <v>0</v>
@@ -10946,10 +10944,10 @@
         <v>0</v>
       </c>
       <c r="K255" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L255" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M255" t="n">
         <v>0</v>
@@ -10963,7 +10961,7 @@
       </c>
       <c r="B256" t="inlineStr"/>
       <c r="C256" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D256" t="n">
         <v>0</v>
@@ -10972,10 +10970,10 @@
         <v>0</v>
       </c>
       <c r="F256" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G256" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H256" t="n">
         <v>0</v>
@@ -11101,13 +11099,13 @@
         <v>0</v>
       </c>
       <c r="H259" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I259" t="n">
         <v>1</v>
       </c>
       <c r="J259" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K259" t="n">
         <v>0</v>
@@ -11130,10 +11128,10 @@
         <v>0</v>
       </c>
       <c r="D260" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E260" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F260" t="n">
         <v>0</v>
@@ -11180,10 +11178,10 @@
         <v>0</v>
       </c>
       <c r="G261" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H261" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I261" t="n">
         <v>0</v>
@@ -11209,34 +11207,34 @@
       </c>
       <c r="B262" t="inlineStr"/>
       <c r="C262" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D262" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E262" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F262" t="n">
+        <v>10</v>
+      </c>
+      <c r="G262" t="n">
+        <v>2</v>
+      </c>
+      <c r="H262" t="n">
+        <v>4</v>
+      </c>
+      <c r="I262" t="n">
         <v>3</v>
       </c>
-      <c r="G262" t="n">
-        <v>9</v>
-      </c>
-      <c r="H262" t="n">
+      <c r="J262" t="n">
+        <v>0</v>
+      </c>
+      <c r="K262" t="n">
         <v>2</v>
       </c>
-      <c r="I262" t="n">
-        <v>4</v>
-      </c>
-      <c r="J262" t="n">
-        <v>3</v>
-      </c>
-      <c r="K262" t="n">
-        <v>0</v>
-      </c>
       <c r="L262" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M262" t="n">
         <v>0</v>
@@ -11259,7 +11257,7 @@
         <v>0</v>
       </c>
       <c r="F263" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G263" t="n">
         <v>1</v>
@@ -11268,10 +11266,10 @@
         <v>1</v>
       </c>
       <c r="I263" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J263" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K263" t="n">
         <v>0</v>
@@ -11280,7 +11278,7 @@
         <v>0</v>
       </c>
       <c r="M263" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="264">
@@ -11300,22 +11298,22 @@
         <v>0</v>
       </c>
       <c r="F264" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G264" t="n">
         <v>1</v>
       </c>
       <c r="H264" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I264" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J264" t="n">
         <v>1</v>
       </c>
       <c r="K264" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L264" t="n">
         <v>0</v>
@@ -11446,7 +11444,7 @@
         <v>0</v>
       </c>
       <c r="M267" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="268">
@@ -11496,9 +11494,7 @@
           <t>貨櫃運輸集散及倉儲</t>
         </is>
       </c>
-      <c r="B269" t="n">
-        <v>0</v>
-      </c>
+      <c r="B269" t="inlineStr"/>
       <c r="C269" t="n">
         <v>0</v>
       </c>
@@ -11541,13 +11537,13 @@
       </c>
       <c r="B270" t="inlineStr"/>
       <c r="C270" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D270" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E270" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F270" t="n">
         <v>0</v>
@@ -11562,10 +11558,10 @@
         <v>0</v>
       </c>
       <c r="J270" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K270" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L270" t="n">
         <v>0</v>
@@ -11638,19 +11634,19 @@
         <v>0</v>
       </c>
       <c r="H272" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I272" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J272" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K272" t="n">
         <v>1</v>
       </c>
       <c r="L272" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M272" t="n">
         <v>0</v>
@@ -11676,19 +11672,19 @@
         <v>0</v>
       </c>
       <c r="G273" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H273" t="n">
         <v>1</v>
       </c>
       <c r="I273" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J273" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K273" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L273" t="n">
         <v>0</v>
@@ -11717,22 +11713,22 @@
         <v>0</v>
       </c>
       <c r="G274" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H274" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I274" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J274" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K274" t="n">
         <v>1</v>
       </c>
       <c r="L274" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M274" t="n">
         <v>0</v>
@@ -11755,22 +11751,22 @@
         <v>0</v>
       </c>
       <c r="F275" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G275" t="n">
         <v>1</v>
       </c>
       <c r="H275" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I275" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J275" t="n">
         <v>1</v>
       </c>
       <c r="K275" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L275" t="n">
         <v>0</v>
@@ -11799,22 +11795,22 @@
         <v>0</v>
       </c>
       <c r="G276" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H276" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I276" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J276" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K276" t="n">
         <v>1</v>
       </c>
       <c r="L276" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M276" t="n">
         <v>0</v>
@@ -11875,13 +11871,13 @@
         <v>0</v>
       </c>
       <c r="E278" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F278" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G278" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H278" t="n">
         <v>1</v>
@@ -11893,7 +11889,7 @@
         <v>1</v>
       </c>
       <c r="K278" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L278" t="n">
         <v>0</v>
@@ -11919,10 +11915,10 @@
         <v>0</v>
       </c>
       <c r="F279" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G279" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H279" t="n">
         <v>1</v>
@@ -11931,7 +11927,7 @@
         <v>1</v>
       </c>
       <c r="J279" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K279" t="n">
         <v>0</v>
@@ -12004,22 +12000,22 @@
         <v>0</v>
       </c>
       <c r="G281" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H281" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I281" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J281" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K281" t="n">
         <v>1</v>
       </c>
       <c r="L281" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M281" t="n">
         <v>0</v>
@@ -12113,20 +12109,40 @@
           <t>資訊收集設備</t>
         </is>
       </c>
-      <c r="B284" t="n">
-        <v>0</v>
-      </c>
-      <c r="C284" t="inlineStr"/>
-      <c r="D284" t="inlineStr"/>
-      <c r="E284" t="inlineStr"/>
-      <c r="F284" t="inlineStr"/>
-      <c r="G284" t="inlineStr"/>
-      <c r="H284" t="inlineStr"/>
-      <c r="I284" t="inlineStr"/>
-      <c r="J284" t="inlineStr"/>
-      <c r="K284" t="inlineStr"/>
-      <c r="L284" t="inlineStr"/>
-      <c r="M284" t="inlineStr"/>
+      <c r="B284" t="inlineStr"/>
+      <c r="C284" t="n">
+        <v>0</v>
+      </c>
+      <c r="D284" t="n">
+        <v>0</v>
+      </c>
+      <c r="E284" t="n">
+        <v>0</v>
+      </c>
+      <c r="F284" t="n">
+        <v>0</v>
+      </c>
+      <c r="G284" t="n">
+        <v>0</v>
+      </c>
+      <c r="H284" t="n">
+        <v>0</v>
+      </c>
+      <c r="I284" t="n">
+        <v>0</v>
+      </c>
+      <c r="J284" t="n">
+        <v>0</v>
+      </c>
+      <c r="K284" t="n">
+        <v>0</v>
+      </c>
+      <c r="L284" t="n">
+        <v>0</v>
+      </c>
+      <c r="M284" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="285">
       <c r="A285" s="1" t="inlineStr">
@@ -12224,16 +12240,16 @@
         <v>0</v>
       </c>
       <c r="E287" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F287" t="n">
         <v>1</v>
       </c>
       <c r="G287" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H287" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I287" t="n">
         <v>1</v>
@@ -12242,7 +12258,7 @@
         <v>1</v>
       </c>
       <c r="K287" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L287" t="n">
         <v>0</v>
@@ -12259,22 +12275,22 @@
       </c>
       <c r="B288" t="inlineStr"/>
       <c r="C288" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D288" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E288" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F288" t="n">
         <v>0</v>
       </c>
       <c r="G288" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H288" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I288" t="n">
         <v>0</v>
@@ -12303,19 +12319,19 @@
         <v>1</v>
       </c>
       <c r="D289" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E289" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F289" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G289" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H289" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I289" t="n">
         <v>0</v>
@@ -12438,10 +12454,10 @@
         <v>0</v>
       </c>
       <c r="H292" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I292" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J292" t="n">
         <v>0</v>
@@ -12511,19 +12527,19 @@
         <v>0</v>
       </c>
       <c r="E294" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F294" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G294" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H294" t="n">
         <v>1</v>
       </c>
       <c r="I294" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J294" t="n">
         <v>0</v>
@@ -12605,10 +12621,10 @@
         <v>0</v>
       </c>
       <c r="I296" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J296" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K296" t="n">
         <v>0</v>
@@ -12626,9 +12642,7 @@
           <t>農藥</t>
         </is>
       </c>
-      <c r="B297" t="n">
-        <v>0</v>
-      </c>
+      <c r="B297" t="inlineStr"/>
       <c r="C297" t="n">
         <v>0</v>
       </c>
@@ -12806,19 +12820,19 @@
         <v>0</v>
       </c>
       <c r="G301" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H301" t="n">
         <v>1</v>
       </c>
       <c r="I301" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J301" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K301" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L301" t="n">
         <v>0</v>
@@ -12838,31 +12852,31 @@
         <v>0</v>
       </c>
       <c r="D302" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E302" t="n">
         <v>1</v>
       </c>
       <c r="F302" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G302" t="n">
+        <v>0</v>
+      </c>
+      <c r="H302" t="n">
+        <v>1</v>
+      </c>
+      <c r="I302" t="n">
         <v>2</v>
       </c>
-      <c r="H302" t="n">
-        <v>0</v>
-      </c>
-      <c r="I302" t="n">
-        <v>1</v>
-      </c>
       <c r="J302" t="n">
+        <v>1</v>
+      </c>
+      <c r="K302" t="n">
         <v>2</v>
       </c>
-      <c r="K302" t="n">
-        <v>1</v>
-      </c>
       <c r="L302" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M302" t="n">
         <v>0</v>
@@ -12874,9 +12888,7 @@
           <t>連接線</t>
         </is>
       </c>
-      <c r="B303" t="n">
-        <v>0</v>
-      </c>
+      <c r="B303" t="inlineStr"/>
       <c r="C303" t="n">
         <v>0</v>
       </c>
@@ -12887,25 +12899,25 @@
         <v>0</v>
       </c>
       <c r="F303" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G303" t="n">
         <v>1</v>
       </c>
       <c r="H303" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I303" t="n">
         <v>3</v>
       </c>
       <c r="J303" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K303" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L303" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M303" t="n">
         <v>0</v>
@@ -13051,7 +13063,7 @@
         <v>0</v>
       </c>
       <c r="F307" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G307" t="n">
         <v>1</v>
@@ -13063,7 +13075,7 @@
         <v>1</v>
       </c>
       <c r="J307" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K307" t="n">
         <v>0</v>
@@ -13081,9 +13093,11 @@
           <t>運算設備</t>
         </is>
       </c>
-      <c r="B308" t="inlineStr"/>
+      <c r="B308" t="n">
+        <v>0</v>
+      </c>
       <c r="C308" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D308" t="n">
         <v>0</v>
@@ -13095,10 +13109,10 @@
         <v>0</v>
       </c>
       <c r="G308" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H308" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I308" t="n">
         <v>0</v>
@@ -13183,10 +13197,10 @@
         <v>0</v>
       </c>
       <c r="I310" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J310" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K310" t="n">
         <v>0</v>
@@ -13195,7 +13209,7 @@
         <v>0</v>
       </c>
       <c r="M310" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="311">
@@ -13236,7 +13250,7 @@
         <v>0</v>
       </c>
       <c r="M311" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="312">
@@ -13262,13 +13276,13 @@
         <v>0</v>
       </c>
       <c r="H312" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I312" t="n">
         <v>1</v>
       </c>
       <c r="J312" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K312" t="n">
         <v>0</v>
@@ -13294,7 +13308,7 @@
         <v>0</v>
       </c>
       <c r="E313" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F313" t="n">
         <v>1</v>
@@ -13309,7 +13323,7 @@
         <v>1</v>
       </c>
       <c r="J313" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K313" t="n">
         <v>0</v>
@@ -13331,34 +13345,34 @@
         <v>0</v>
       </c>
       <c r="C314" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D314" t="n">
         <v>0</v>
       </c>
       <c r="E314" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F314" t="n">
         <v>2</v>
       </c>
       <c r="G314" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H314" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I314" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J314" t="n">
         <v>0</v>
       </c>
       <c r="K314" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L314" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M314" t="n">
         <v>0</v>
@@ -13419,25 +13433,25 @@
         <v>0</v>
       </c>
       <c r="E316" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F316" t="n">
+        <v>0</v>
+      </c>
+      <c r="G316" t="n">
+        <v>1</v>
+      </c>
+      <c r="H316" t="n">
         <v>2</v>
       </c>
-      <c r="G316" t="n">
-        <v>0</v>
-      </c>
-      <c r="H316" t="n">
-        <v>1</v>
-      </c>
       <c r="I316" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J316" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K316" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L316" t="n">
         <v>0</v>
@@ -13460,7 +13474,7 @@
         <v>0</v>
       </c>
       <c r="E317" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F317" t="n">
         <v>0</v>
@@ -13495,19 +13509,19 @@
       </c>
       <c r="B318" t="inlineStr"/>
       <c r="C318" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D318" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E318" t="n">
         <v>0</v>
       </c>
       <c r="F318" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G318" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H318" t="n">
         <v>0</v>
@@ -13519,10 +13533,10 @@
         <v>0</v>
       </c>
       <c r="K318" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L318" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M318" t="n">
         <v>0</v>
@@ -13586,10 +13600,10 @@
         <v>0</v>
       </c>
       <c r="F320" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G320" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H320" t="n">
         <v>0</v>
@@ -13616,7 +13630,9 @@
           <t>金控業/銀行業/保險業</t>
         </is>
       </c>
-      <c r="B321" t="inlineStr"/>
+      <c r="B321" t="n">
+        <v>0</v>
+      </c>
       <c r="C321" t="n">
         <v>0</v>
       </c>
@@ -13659,7 +13675,7 @@
       </c>
       <c r="B322" t="inlineStr"/>
       <c r="C322" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D322" t="n">
         <v>0</v>
@@ -13782,19 +13798,19 @@
       </c>
       <c r="B325" t="inlineStr"/>
       <c r="C325" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D325" t="n">
         <v>1</v>
       </c>
       <c r="E325" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F325" t="n">
         <v>0</v>
       </c>
       <c r="G325" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H325" t="n">
         <v>1</v>
@@ -13803,7 +13819,7 @@
         <v>1</v>
       </c>
       <c r="J325" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K325" t="n">
         <v>0</v>
@@ -13821,14 +13837,12 @@
           <t>銅箔基板</t>
         </is>
       </c>
-      <c r="B326" t="n">
-        <v>0</v>
-      </c>
+      <c r="B326" t="inlineStr"/>
       <c r="C326" t="n">
         <v>1</v>
       </c>
       <c r="D326" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E326" t="n">
         <v>0</v>
@@ -13840,13 +13854,13 @@
         <v>0</v>
       </c>
       <c r="H326" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I326" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J326" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K326" t="n">
         <v>0</v>
@@ -13869,10 +13883,10 @@
         <v>0</v>
       </c>
       <c r="D327" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E327" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F327" t="n">
         <v>0</v>
@@ -13887,10 +13901,10 @@
         <v>0</v>
       </c>
       <c r="J327" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K327" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L327" t="n">
         <v>0</v>
@@ -13966,19 +13980,19 @@
         <v>0</v>
       </c>
       <c r="I329" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J329" t="n">
         <v>1</v>
       </c>
       <c r="K329" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L329" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M329" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="330">
@@ -14089,10 +14103,10 @@
         <v>0</v>
       </c>
       <c r="I332" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J332" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K332" t="n">
         <v>0</v>
@@ -14177,10 +14191,10 @@
         <v>0</v>
       </c>
       <c r="K334" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L334" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M334" t="n">
         <v>0</v>
@@ -14250,10 +14264,10 @@
         <v>0</v>
       </c>
       <c r="H336" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I336" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J336" t="n">
         <v>0</v>
@@ -14276,28 +14290,28 @@
       </c>
       <c r="B337" t="inlineStr"/>
       <c r="C337" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D337" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E337" t="n">
         <v>2</v>
       </c>
       <c r="F337" t="n">
+        <v>4</v>
+      </c>
+      <c r="G337" t="n">
         <v>2</v>
       </c>
-      <c r="G337" t="n">
-        <v>4</v>
-      </c>
       <c r="H337" t="n">
+        <v>3</v>
+      </c>
+      <c r="I337" t="n">
         <v>2</v>
       </c>
-      <c r="I337" t="n">
-        <v>3</v>
-      </c>
       <c r="J337" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K337" t="n">
         <v>0</v>
@@ -14326,7 +14340,7 @@
         <v>0</v>
       </c>
       <c r="F338" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G338" t="n">
         <v>1</v>
@@ -14338,7 +14352,7 @@
         <v>1</v>
       </c>
       <c r="J338" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K338" t="n">
         <v>0</v>
@@ -14364,19 +14378,19 @@
         <v>0</v>
       </c>
       <c r="E339" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F339" t="n">
         <v>1</v>
       </c>
       <c r="G339" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H339" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I339" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J339" t="n">
         <v>1</v>
@@ -14385,7 +14399,7 @@
         <v>1</v>
       </c>
       <c r="L339" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M339" t="n">
         <v>0</v>
@@ -14408,22 +14422,22 @@
         <v>0</v>
       </c>
       <c r="F340" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G340" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H340" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I340" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J340" t="n">
         <v>1</v>
       </c>
       <c r="K340" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L340" t="n">
         <v>0</v>
@@ -14449,22 +14463,22 @@
         <v>0</v>
       </c>
       <c r="F341" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G341" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H341" t="n">
         <v>2</v>
       </c>
       <c r="I341" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J341" t="n">
         <v>1</v>
       </c>
       <c r="K341" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L341" t="n">
         <v>0</v>
@@ -14481,13 +14495,13 @@
       </c>
       <c r="B342" t="inlineStr"/>
       <c r="C342" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D342" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E342" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F342" t="n">
         <v>0</v>
@@ -14508,10 +14522,10 @@
         <v>0</v>
       </c>
       <c r="L342" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M342" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="343">
@@ -14531,16 +14545,16 @@
         <v>0</v>
       </c>
       <c r="F343" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G343" t="n">
         <v>1</v>
       </c>
       <c r="H343" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I343" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J343" t="n">
         <v>0</v>
@@ -14581,10 +14595,10 @@
         <v>0</v>
       </c>
       <c r="I344" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J344" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K344" t="n">
         <v>0</v>
@@ -14634,7 +14648,7 @@
         <v>0</v>
       </c>
       <c r="M345" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="346">
@@ -14645,10 +14659,10 @@
       </c>
       <c r="B346" t="inlineStr"/>
       <c r="C346" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D346" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E346" t="n">
         <v>0</v>
@@ -14663,10 +14677,10 @@
         <v>0</v>
       </c>
       <c r="I346" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J346" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K346" t="n">
         <v>0</v>
@@ -14675,7 +14689,7 @@
         <v>0</v>
       </c>
       <c r="M346" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="347">
@@ -14725,9 +14739,7 @@
           <t>電動汽車、電動機車、電動自行車</t>
         </is>
       </c>
-      <c r="B348" t="n">
-        <v>0</v>
-      </c>
+      <c r="B348" t="inlineStr"/>
       <c r="C348" t="n">
         <v>0</v>
       </c>
@@ -14750,10 +14762,10 @@
         <v>0</v>
       </c>
       <c r="J348" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K348" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L348" t="n">
         <v>0</v>
@@ -14852,22 +14864,22 @@
       </c>
       <c r="B351" t="inlineStr"/>
       <c r="C351" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D351" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E351" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F351" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G351" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H351" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I351" t="n">
         <v>1</v>
@@ -14879,7 +14891,7 @@
         <v>1</v>
       </c>
       <c r="L351" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M351" t="n">
         <v>0</v>
@@ -14891,41 +14903,39 @@
           <t>電容器</t>
         </is>
       </c>
-      <c r="B352" t="n">
-        <v>0</v>
-      </c>
+      <c r="B352" t="inlineStr"/>
       <c r="C352" t="n">
         <v>0</v>
       </c>
       <c r="D352" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E352" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F352" t="n">
         <v>0</v>
       </c>
       <c r="G352" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H352" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I352" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="J352" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="K352" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L352" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M352" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="353">
@@ -14934,9 +14944,7 @@
           <t>電容器材料(如電蝕／化成鋁箔、介面瓷粉)</t>
         </is>
       </c>
-      <c r="B353" t="n">
-        <v>0</v>
-      </c>
+      <c r="B353" t="inlineStr"/>
       <c r="C353" t="n">
         <v>0</v>
       </c>
@@ -14950,16 +14958,16 @@
         <v>0</v>
       </c>
       <c r="G353" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H353" t="n">
         <v>1</v>
       </c>
       <c r="I353" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J353" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K353" t="n">
         <v>0</v>
@@ -14968,7 +14976,7 @@
         <v>0</v>
       </c>
       <c r="M353" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="354">
@@ -14984,34 +14992,34 @@
         <v>0</v>
       </c>
       <c r="D354" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E354" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F354" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G354" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H354" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I354" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J354" t="n">
         <v>2</v>
       </c>
       <c r="K354" t="n">
+        <v>0</v>
+      </c>
+      <c r="L354" t="n">
+        <v>0</v>
+      </c>
+      <c r="M354" t="n">
         <v>2</v>
-      </c>
-      <c r="L354" t="n">
-        <v>0</v>
-      </c>
-      <c r="M354" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="355">
@@ -15034,19 +15042,19 @@
         <v>0</v>
       </c>
       <c r="G355" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H355" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I355" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J355" t="n">
         <v>1</v>
       </c>
       <c r="K355" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L355" t="n">
         <v>0</v>
@@ -15063,28 +15071,28 @@
       </c>
       <c r="B356" t="inlineStr"/>
       <c r="C356" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D356" t="n">
         <v>2</v>
       </c>
       <c r="E356" t="n">
+        <v>0</v>
+      </c>
+      <c r="F356" t="n">
+        <v>1</v>
+      </c>
+      <c r="G356" t="n">
+        <v>0</v>
+      </c>
+      <c r="H356" t="n">
         <v>2</v>
       </c>
-      <c r="F356" t="n">
-        <v>0</v>
-      </c>
-      <c r="G356" t="n">
-        <v>1</v>
-      </c>
-      <c r="H356" t="n">
-        <v>0</v>
-      </c>
       <c r="I356" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J356" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K356" t="n">
         <v>0</v>
@@ -15104,10 +15112,10 @@
       </c>
       <c r="B357" t="inlineStr"/>
       <c r="C357" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D357" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E357" t="n">
         <v>0</v>
@@ -15116,13 +15124,13 @@
         <v>0</v>
       </c>
       <c r="G357" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H357" t="n">
         <v>1</v>
       </c>
       <c r="I357" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J357" t="n">
         <v>0</v>
@@ -15143,14 +15151,12 @@
           <t>電池模組</t>
         </is>
       </c>
-      <c r="B358" t="n">
-        <v>0</v>
-      </c>
+      <c r="B358" t="inlineStr"/>
       <c r="C358" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D358" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E358" t="n">
         <v>0</v>
@@ -15174,10 +15180,10 @@
         <v>0</v>
       </c>
       <c r="L358" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M358" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="359">
@@ -15186,9 +15192,7 @@
           <t>電池芯</t>
         </is>
       </c>
-      <c r="B359" t="n">
-        <v>0</v>
-      </c>
+      <c r="B359" t="inlineStr"/>
       <c r="C359" t="n">
         <v>0</v>
       </c>
@@ -15217,10 +15221,10 @@
         <v>0</v>
       </c>
       <c r="L359" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M359" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="360">
@@ -15231,37 +15235,37 @@
       </c>
       <c r="B360" t="inlineStr"/>
       <c r="C360" t="n">
+        <v>0</v>
+      </c>
+      <c r="D360" t="n">
+        <v>1</v>
+      </c>
+      <c r="E360" t="n">
+        <v>1</v>
+      </c>
+      <c r="F360" t="n">
         <v>2</v>
       </c>
-      <c r="D360" t="n">
-        <v>0</v>
-      </c>
-      <c r="E360" t="n">
-        <v>1</v>
-      </c>
-      <c r="F360" t="n">
-        <v>1</v>
-      </c>
       <c r="G360" t="n">
+        <v>1</v>
+      </c>
+      <c r="H360" t="n">
         <v>2</v>
       </c>
-      <c r="H360" t="n">
-        <v>1</v>
-      </c>
       <c r="I360" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J360" t="n">
         <v>1</v>
       </c>
       <c r="K360" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L360" t="n">
         <v>0</v>
       </c>
       <c r="M360" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="361">
@@ -15302,7 +15306,7 @@
         <v>0</v>
       </c>
       <c r="M361" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="362">
@@ -15372,10 +15376,10 @@
         <v>0</v>
       </c>
       <c r="I363" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J363" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K363" t="n">
         <v>0</v>
@@ -15398,13 +15402,13 @@
         <v>0</v>
       </c>
       <c r="D364" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E364" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F364" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G364" t="n">
         <v>1</v>
@@ -15413,16 +15417,16 @@
         <v>1</v>
       </c>
       <c r="I364" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J364" t="n">
         <v>0</v>
       </c>
       <c r="K364" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L364" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M364" t="n">
         <v>0</v>
@@ -15434,30 +15438,32 @@
           <t>電腦設備</t>
         </is>
       </c>
-      <c r="B365" t="inlineStr"/>
+      <c r="B365" t="n">
+        <v>0</v>
+      </c>
       <c r="C365" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D365" t="n">
         <v>0</v>
       </c>
       <c r="E365" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F365" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G365" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H365" t="n">
+        <v>1</v>
+      </c>
+      <c r="I365" t="n">
         <v>2</v>
       </c>
-      <c r="I365" t="n">
-        <v>1</v>
-      </c>
       <c r="J365" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K365" t="n">
         <v>0</v>
@@ -15557,9 +15563,7 @@
           <t>電阻器</t>
         </is>
       </c>
-      <c r="B368" t="n">
-        <v>0</v>
-      </c>
+      <c r="B368" t="inlineStr"/>
       <c r="C368" t="n">
         <v>0</v>
       </c>
@@ -15573,25 +15577,25 @@
         <v>0</v>
       </c>
       <c r="G368" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H368" t="n">
+        <v>0</v>
+      </c>
+      <c r="I368" t="n">
         <v>2</v>
       </c>
-      <c r="I368" t="n">
-        <v>0</v>
-      </c>
       <c r="J368" t="n">
         <v>1</v>
       </c>
       <c r="K368" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L368" t="n">
         <v>0</v>
       </c>
       <c r="M368" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="369">
@@ -15614,13 +15618,13 @@
         <v>0</v>
       </c>
       <c r="G369" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H369" t="n">
         <v>1</v>
       </c>
       <c r="I369" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J369" t="n">
         <v>0</v>
@@ -15655,13 +15659,13 @@
         <v>0</v>
       </c>
       <c r="G370" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H370" t="n">
         <v>1</v>
       </c>
       <c r="I370" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J370" t="n">
         <v>0</v>
@@ -15769,22 +15773,22 @@
         <v>0</v>
       </c>
       <c r="D373" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E373" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F373" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G373" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H373" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I373" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J373" t="n">
         <v>1</v>
@@ -15793,7 +15797,7 @@
         <v>1</v>
       </c>
       <c r="L373" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M373" t="n">
         <v>0</v>
@@ -15810,13 +15814,13 @@
         <v>0</v>
       </c>
       <c r="D374" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E374" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F374" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G374" t="n">
         <v>1</v>
@@ -15825,7 +15829,7 @@
         <v>1</v>
       </c>
       <c r="I374" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J374" t="n">
         <v>0</v>
@@ -15846,14 +15850,12 @@
           <t>顏染料</t>
         </is>
       </c>
-      <c r="B375" t="n">
-        <v>0</v>
-      </c>
+      <c r="B375" t="inlineStr"/>
       <c r="C375" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D375" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E375" t="n">
         <v>0</v>
@@ -15868,10 +15870,10 @@
         <v>0</v>
       </c>
       <c r="I375" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J375" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K375" t="n">
         <v>0</v>
@@ -15900,28 +15902,28 @@
         <v>0</v>
       </c>
       <c r="F376" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G376" t="n">
+        <v>5</v>
+      </c>
+      <c r="H376" t="n">
+        <v>4</v>
+      </c>
+      <c r="I376" t="n">
+        <v>3</v>
+      </c>
+      <c r="J376" t="n">
         <v>2</v>
       </c>
-      <c r="H376" t="n">
-        <v>5</v>
-      </c>
-      <c r="I376" t="n">
-        <v>4</v>
-      </c>
-      <c r="J376" t="n">
-        <v>3</v>
-      </c>
       <c r="K376" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L376" t="n">
         <v>0</v>
       </c>
       <c r="M376" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="377">
@@ -15938,19 +15940,19 @@
         <v>0</v>
       </c>
       <c r="E377" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F377" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G377" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H377" t="n">
         <v>1</v>
       </c>
       <c r="I377" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J377" t="n">
         <v>0</v>
@@ -15982,16 +15984,16 @@
         <v>0</v>
       </c>
       <c r="F378" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G378" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H378" t="n">
         <v>2</v>
       </c>
       <c r="I378" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J378" t="n">
         <v>0</v>
@@ -16178,13 +16180,13 @@
       </c>
       <c r="B383" t="inlineStr"/>
       <c r="C383" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D383" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E383" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F383" t="n">
         <v>0</v>
@@ -16193,19 +16195,19 @@
         <v>0</v>
       </c>
       <c r="H383" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I383" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J383" t="n">
         <v>0</v>
       </c>
       <c r="K383" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L383" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M383" t="n">
         <v>0</v>
@@ -16275,13 +16277,13 @@
         <v>0</v>
       </c>
       <c r="H385" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I385" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J385" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K385" t="n">
         <v>0</v>
@@ -16290,7 +16292,7 @@
         <v>0</v>
       </c>
       <c r="M385" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="386">
@@ -16340,9 +16342,7 @@
           <t>高爾夫球具業</t>
         </is>
       </c>
-      <c r="B387" t="n">
-        <v>0</v>
-      </c>
+      <c r="B387" t="inlineStr"/>
       <c r="C387" t="n">
         <v>0</v>
       </c>

--- a/Result/analyze_3.xlsx
+++ b/Result/analyze_3.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M388"/>
+  <dimension ref="A1:M387"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,57 +441,57 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
     </row>
@@ -553,13 +553,13 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G3" t="n">
         <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
@@ -667,37 +667,37 @@
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="n">
         <v>3</v>
       </c>
-      <c r="E6" t="n">
-        <v>0</v>
-      </c>
       <c r="F6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J6" t="n">
         <v>3</v>
       </c>
-      <c r="G6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" t="n">
-        <v>1</v>
-      </c>
       <c r="K6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -708,37 +708,37 @@
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D7" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F7" t="n">
+        <v>2</v>
+      </c>
+      <c r="G7" t="n">
+        <v>5</v>
+      </c>
+      <c r="H7" t="n">
         <v>3</v>
       </c>
-      <c r="G7" t="n">
+      <c r="I7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
         <v>2</v>
-      </c>
-      <c r="H7" t="n">
-        <v>5</v>
-      </c>
-      <c r="I7" t="n">
-        <v>3</v>
-      </c>
-      <c r="J7" t="n">
-        <v>1</v>
-      </c>
-      <c r="K7" t="n">
-        <v>1</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -747,39 +747,41 @@
           <t>IC模組</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr"/>
+      <c r="B8" t="n">
+        <v>0</v>
+      </c>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E8" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F8" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H8" t="n">
         <v>2</v>
       </c>
       <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
         <v>2</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -788,39 +790,41 @@
           <t>IC設計</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr"/>
+      <c r="B9" t="n">
+        <v>0</v>
+      </c>
       <c r="C9" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D9" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E9" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="F9" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="G9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H9" t="n">
+        <v>2</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
         <v>3</v>
-      </c>
-      <c r="I9" t="n">
-        <v>2</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" t="n">
-        <v>1</v>
-      </c>
-      <c r="L9" t="n">
-        <v>1</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -831,37 +835,37 @@
       </c>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H10" t="n">
         <v>3</v>
       </c>
-      <c r="H10" t="n">
-        <v>2</v>
-      </c>
       <c r="I10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
         <v>3</v>
-      </c>
-      <c r="J10" t="n">
-        <v>1</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -874,16 +878,16 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D11" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -895,16 +899,16 @@
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -924,16 +928,16 @@
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -971,10 +975,10 @@
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1118,9 +1122,7 @@
           <t>一般零售</t>
         </is>
       </c>
-      <c r="B17" t="n">
-        <v>0</v>
-      </c>
+      <c r="B17" t="inlineStr"/>
       <c r="C17" t="n">
         <v>0</v>
       </c>
@@ -1128,16 +1130,16 @@
         <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
@@ -1222,13 +1224,13 @@
         <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
@@ -1263,7 +1265,7 @@
         <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -1284,41 +1286,39 @@
           <t>中、西藥製劑</t>
         </is>
       </c>
-      <c r="B21" t="n">
-        <v>0</v>
-      </c>
+      <c r="B21" t="inlineStr"/>
       <c r="C21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E21" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -1335,7 +1335,7 @@
         <v>0</v>
       </c>
       <c r="E22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F22" t="n">
         <v>1</v>
@@ -1344,7 +1344,7 @@
         <v>1</v>
       </c>
       <c r="H22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I22" t="n">
         <v>0</v>
@@ -1373,10 +1373,10 @@
         <v>0</v>
       </c>
       <c r="D23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F23" t="n">
         <v>0</v>
@@ -1388,10 +1388,10 @@
         <v>0</v>
       </c>
       <c r="I23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
@@ -1400,7 +1400,7 @@
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -1409,9 +1409,7 @@
           <t>主/被動元件</t>
         </is>
       </c>
-      <c r="B24" t="n">
-        <v>0</v>
-      </c>
+      <c r="B24" t="inlineStr"/>
       <c r="C24" t="n">
         <v>0</v>
       </c>
@@ -1425,13 +1423,13 @@
         <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H24" t="n">
         <v>1</v>
       </c>
       <c r="I24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -1443,7 +1441,7 @@
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25">
@@ -1457,7 +1455,7 @@
         <v>0</v>
       </c>
       <c r="D25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E25" t="n">
         <v>1</v>
@@ -1469,7 +1467,7 @@
         <v>1</v>
       </c>
       <c r="H25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I25" t="n">
         <v>0</v>
@@ -1536,16 +1534,16 @@
       </c>
       <c r="B27" t="inlineStr"/>
       <c r="C27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E27" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F27" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
@@ -1557,10 +1555,10 @@
         <v>0</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
@@ -1671,13 +1669,13 @@
         <v>0</v>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I30" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -1706,19 +1704,19 @@
         <v>0</v>
       </c>
       <c r="E31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I31" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -1744,34 +1742,34 @@
         <v>0</v>
       </c>
       <c r="D32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E32" t="n">
         <v>1</v>
       </c>
       <c r="F32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33">
@@ -1780,26 +1778,24 @@
           <t>伺服器</t>
         </is>
       </c>
-      <c r="B33" t="n">
-        <v>0</v>
-      </c>
+      <c r="B33" t="inlineStr"/>
       <c r="C33" t="n">
         <v>0</v>
       </c>
       <c r="D33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F33" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G33" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I33" t="n">
         <v>0</v>
@@ -1864,20 +1860,18 @@
           <t>保健食品代理銷售及通路</t>
         </is>
       </c>
-      <c r="B35" t="n">
-        <v>0</v>
-      </c>
+      <c r="B35" t="inlineStr"/>
       <c r="C35" t="n">
         <v>0</v>
       </c>
       <c r="D35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F35" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
@@ -2000,13 +1994,13 @@
         <v>0</v>
       </c>
       <c r="F38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I38" t="n">
         <v>0</v>
@@ -2123,10 +2117,10 @@
         <v>0</v>
       </c>
       <c r="F41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H41" t="n">
         <v>0</v>
@@ -2144,7 +2138,7 @@
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="42">
@@ -2161,10 +2155,10 @@
         <v>0</v>
       </c>
       <c r="E42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F42" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G42" t="n">
         <v>1</v>
@@ -2173,7 +2167,7 @@
         <v>1</v>
       </c>
       <c r="I42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -2185,7 +2179,7 @@
         <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="43">
@@ -2202,10 +2196,10 @@
         <v>0</v>
       </c>
       <c r="E43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
@@ -2237,16 +2231,16 @@
       </c>
       <c r="B44" t="inlineStr"/>
       <c r="C44" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D44" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E44" t="n">
         <v>0</v>
       </c>
       <c r="F44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G44" t="n">
         <v>1</v>
@@ -2255,7 +2249,7 @@
         <v>1</v>
       </c>
       <c r="I44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -2264,10 +2258,10 @@
         <v>0</v>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -2287,10 +2281,10 @@
         <v>0</v>
       </c>
       <c r="F45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H45" t="n">
         <v>0</v>
@@ -2328,13 +2322,13 @@
         <v>0</v>
       </c>
       <c r="F46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G46" t="n">
         <v>1</v>
       </c>
       <c r="H46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I46" t="n">
         <v>0</v>
@@ -2369,13 +2363,13 @@
         <v>0</v>
       </c>
       <c r="F47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G47" t="n">
         <v>1</v>
       </c>
       <c r="H47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I47" t="n">
         <v>0</v>
@@ -2444,37 +2438,37 @@
         <v>0</v>
       </c>
       <c r="C49" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D49" t="n">
+        <v>0</v>
+      </c>
+      <c r="E49" t="n">
         <v>2</v>
       </c>
-      <c r="E49" t="n">
-        <v>1</v>
-      </c>
       <c r="F49" t="n">
+        <v>1</v>
+      </c>
+      <c r="G49" t="n">
         <v>2</v>
-      </c>
-      <c r="G49" t="n">
-        <v>1</v>
       </c>
       <c r="H49" t="n">
         <v>2</v>
       </c>
       <c r="I49" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J49" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K49" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M49" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="50">
@@ -2528,37 +2522,37 @@
         <v>0</v>
       </c>
       <c r="C51" t="n">
+        <v>4</v>
+      </c>
+      <c r="D51" t="n">
         <v>3</v>
       </c>
-      <c r="D51" t="n">
-        <v>4</v>
-      </c>
       <c r="E51" t="n">
+        <v>0</v>
+      </c>
+      <c r="F51" t="n">
+        <v>2</v>
+      </c>
+      <c r="G51" t="n">
+        <v>0</v>
+      </c>
+      <c r="H51" t="n">
+        <v>6</v>
+      </c>
+      <c r="I51" t="n">
+        <v>1</v>
+      </c>
+      <c r="J51" t="n">
+        <v>1</v>
+      </c>
+      <c r="K51" t="n">
+        <v>1</v>
+      </c>
+      <c r="L51" t="n">
+        <v>1</v>
+      </c>
+      <c r="M51" t="n">
         <v>3</v>
-      </c>
-      <c r="F51" t="n">
-        <v>1</v>
-      </c>
-      <c r="G51" t="n">
-        <v>2</v>
-      </c>
-      <c r="H51" t="n">
-        <v>0</v>
-      </c>
-      <c r="I51" t="n">
-        <v>6</v>
-      </c>
-      <c r="J51" t="n">
-        <v>1</v>
-      </c>
-      <c r="K51" t="n">
-        <v>1</v>
-      </c>
-      <c r="L51" t="n">
-        <v>1</v>
-      </c>
-      <c r="M51" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="52">
@@ -2608,39 +2602,41 @@
           <t>其他零組件</t>
         </is>
       </c>
-      <c r="B53" t="inlineStr"/>
+      <c r="B53" t="n">
+        <v>0</v>
+      </c>
       <c r="C53" t="n">
         <v>0</v>
       </c>
       <c r="D53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F53" t="n">
+        <v>1</v>
+      </c>
+      <c r="G53" t="n">
+        <v>1</v>
+      </c>
+      <c r="H53" t="n">
+        <v>3</v>
+      </c>
+      <c r="I53" t="n">
         <v>2</v>
-      </c>
-      <c r="G53" t="n">
-        <v>1</v>
-      </c>
-      <c r="H53" t="n">
-        <v>1</v>
-      </c>
-      <c r="I53" t="n">
-        <v>3</v>
       </c>
       <c r="J53" t="n">
         <v>2</v>
       </c>
       <c r="K53" t="n">
+        <v>0</v>
+      </c>
+      <c r="L53" t="n">
+        <v>0</v>
+      </c>
+      <c r="M53" t="n">
         <v>2</v>
-      </c>
-      <c r="L53" t="n">
-        <v>0</v>
-      </c>
-      <c r="M53" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -2653,37 +2649,37 @@
         <v>0</v>
       </c>
       <c r="C54" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D54" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E54" t="n">
         <v>1</v>
       </c>
       <c r="F54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G54" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H54" t="n">
         <v>4</v>
       </c>
       <c r="I54" t="n">
+        <v>0</v>
+      </c>
+      <c r="J54" t="n">
+        <v>1</v>
+      </c>
+      <c r="K54" t="n">
+        <v>1</v>
+      </c>
+      <c r="L54" t="n">
+        <v>1</v>
+      </c>
+      <c r="M54" t="n">
         <v>4</v>
-      </c>
-      <c r="J54" t="n">
-        <v>0</v>
-      </c>
-      <c r="K54" t="n">
-        <v>1</v>
-      </c>
-      <c r="L54" t="n">
-        <v>1</v>
-      </c>
-      <c r="M54" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="55">
@@ -2692,41 +2688,39 @@
           <t>其他電腦及週邊設備</t>
         </is>
       </c>
-      <c r="B55" t="n">
-        <v>0</v>
-      </c>
+      <c r="B55" t="inlineStr"/>
       <c r="C55" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D55" t="n">
+        <v>4</v>
+      </c>
+      <c r="E55" t="n">
+        <v>1</v>
+      </c>
+      <c r="F55" t="n">
         <v>2</v>
       </c>
-      <c r="E55" t="n">
+      <c r="G55" t="n">
         <v>4</v>
       </c>
-      <c r="F55" t="n">
-        <v>1</v>
-      </c>
-      <c r="G55" t="n">
+      <c r="H55" t="n">
         <v>2</v>
       </c>
-      <c r="H55" t="n">
-        <v>4</v>
-      </c>
       <c r="I55" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K55" t="n">
         <v>0</v>
       </c>
       <c r="L55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56">
@@ -2737,37 +2731,37 @@
       </c>
       <c r="B56" t="inlineStr"/>
       <c r="C56" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D56" t="n">
+        <v>3</v>
+      </c>
+      <c r="E56" t="n">
+        <v>5</v>
+      </c>
+      <c r="F56" t="n">
+        <v>3</v>
+      </c>
+      <c r="G56" t="n">
+        <v>2</v>
+      </c>
+      <c r="H56" t="n">
         <v>4</v>
       </c>
-      <c r="E56" t="n">
-        <v>3</v>
-      </c>
-      <c r="F56" t="n">
-        <v>5</v>
-      </c>
-      <c r="G56" t="n">
-        <v>3</v>
-      </c>
-      <c r="H56" t="n">
+      <c r="I56" t="n">
+        <v>1</v>
+      </c>
+      <c r="J56" t="n">
         <v>2</v>
       </c>
-      <c r="I56" t="n">
-        <v>4</v>
-      </c>
-      <c r="J56" t="n">
-        <v>1</v>
-      </c>
       <c r="K56" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L56" t="n">
         <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="57">
@@ -2819,25 +2813,25 @@
       </c>
       <c r="B58" t="inlineStr"/>
       <c r="C58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
       </c>
       <c r="H58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -2846,10 +2840,10 @@
         <v>0</v>
       </c>
       <c r="L58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59">
@@ -2863,10 +2857,10 @@
         <v>0</v>
       </c>
       <c r="D59" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F59" t="n">
         <v>0</v>
@@ -2875,10 +2869,10 @@
         <v>0</v>
       </c>
       <c r="H59" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -2887,10 +2881,10 @@
         <v>0</v>
       </c>
       <c r="L59" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M59" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="60">
@@ -2901,7 +2895,7 @@
       </c>
       <c r="B60" t="inlineStr"/>
       <c r="C60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D60" t="n">
         <v>0</v>
@@ -2919,7 +2913,7 @@
         <v>0</v>
       </c>
       <c r="I60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -3030,7 +3024,7 @@
         <v>0</v>
       </c>
       <c r="E63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F63" t="n">
         <v>1</v>
@@ -3042,7 +3036,7 @@
         <v>1</v>
       </c>
       <c r="I63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -3186,9 +3180,7 @@
           <t>加工製成品</t>
         </is>
       </c>
-      <c r="B67" t="n">
-        <v>0</v>
-      </c>
+      <c r="B67" t="inlineStr"/>
       <c r="C67" t="n">
         <v>0</v>
       </c>
@@ -3202,10 +3194,10 @@
         <v>0</v>
       </c>
       <c r="G67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I67" t="n">
         <v>0</v>
@@ -3243,10 +3235,10 @@
         <v>0</v>
       </c>
       <c r="G68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I68" t="n">
         <v>0</v>
@@ -3272,10 +3264,10 @@
       </c>
       <c r="B69" t="inlineStr"/>
       <c r="C69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E69" t="n">
         <v>0</v>
@@ -3311,9 +3303,7 @@
           <t>化妝品</t>
         </is>
       </c>
-      <c r="B70" t="n">
-        <v>0</v>
-      </c>
+      <c r="B70" t="inlineStr"/>
       <c r="C70" t="n">
         <v>0</v>
       </c>
@@ -3356,7 +3346,7 @@
       </c>
       <c r="B71" t="inlineStr"/>
       <c r="C71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D71" t="n">
         <v>0</v>
@@ -3371,16 +3361,16 @@
         <v>0</v>
       </c>
       <c r="H71" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I71" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J71" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L71" t="n">
         <v>0</v>
@@ -3412,22 +3402,22 @@
         <v>0</v>
       </c>
       <c r="H72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L72" t="n">
         <v>0</v>
       </c>
       <c r="M72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="73">
@@ -3468,7 +3458,7 @@
         <v>0</v>
       </c>
       <c r="M73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="74">
@@ -3532,13 +3522,13 @@
         <v>0</v>
       </c>
       <c r="G75" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H75" t="n">
         <v>1</v>
       </c>
       <c r="I75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -3570,13 +3560,13 @@
         <v>0</v>
       </c>
       <c r="F76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G76" t="n">
         <v>1</v>
       </c>
       <c r="H76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I76" t="n">
         <v>0</v>
@@ -3646,34 +3636,34 @@
         <v>0</v>
       </c>
       <c r="D78" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E78" t="n">
         <v>1</v>
       </c>
       <c r="F78" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G78" t="n">
         <v>0</v>
       </c>
       <c r="H78" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I78" t="n">
+        <v>1</v>
+      </c>
+      <c r="J78" t="n">
         <v>2</v>
-      </c>
-      <c r="J78" t="n">
-        <v>1</v>
       </c>
       <c r="K78" t="n">
         <v>2</v>
       </c>
       <c r="L78" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M78" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="79">
@@ -3682,9 +3672,7 @@
           <t>原物料</t>
         </is>
       </c>
-      <c r="B79" t="n">
-        <v>0</v>
-      </c>
+      <c r="B79" t="inlineStr"/>
       <c r="C79" t="n">
         <v>0</v>
       </c>
@@ -3739,10 +3727,10 @@
         <v>0</v>
       </c>
       <c r="G80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H80" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I80" t="n">
         <v>0</v>
@@ -3824,10 +3812,10 @@
         <v>0</v>
       </c>
       <c r="H82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -3853,34 +3841,34 @@
         <v>1</v>
       </c>
       <c r="D83" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E83" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F83" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G83" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H83" t="n">
+        <v>1</v>
+      </c>
+      <c r="I83" t="n">
+        <v>0</v>
+      </c>
+      <c r="J83" t="n">
+        <v>1</v>
+      </c>
+      <c r="K83" t="n">
+        <v>0</v>
+      </c>
+      <c r="L83" t="n">
+        <v>0</v>
+      </c>
+      <c r="M83" t="n">
         <v>2</v>
-      </c>
-      <c r="I83" t="n">
-        <v>1</v>
-      </c>
-      <c r="J83" t="n">
-        <v>0</v>
-      </c>
-      <c r="K83" t="n">
-        <v>1</v>
-      </c>
-      <c r="L83" t="n">
-        <v>0</v>
-      </c>
-      <c r="M83" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="84">
@@ -3985,16 +3973,16 @@
         <v>0</v>
       </c>
       <c r="G86" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H86" t="n">
         <v>1</v>
       </c>
       <c r="I86" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J86" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K86" t="n">
         <v>0</v>
@@ -4020,25 +4008,25 @@
         <v>0</v>
       </c>
       <c r="E87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G87" t="n">
         <v>0</v>
       </c>
       <c r="H87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L87" t="n">
         <v>0</v>
@@ -4067,10 +4055,10 @@
         <v>0</v>
       </c>
       <c r="G88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I88" t="n">
         <v>0</v>
@@ -4085,7 +4073,7 @@
         <v>0</v>
       </c>
       <c r="M88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="89">
@@ -4094,39 +4082,41 @@
           <t>塑膠製品</t>
         </is>
       </c>
-      <c r="B89" t="inlineStr"/>
+      <c r="B89" t="n">
+        <v>0</v>
+      </c>
       <c r="C89" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D89" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E89" t="n">
         <v>1</v>
       </c>
       <c r="F89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G89" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H89" t="n">
         <v>1</v>
       </c>
       <c r="I89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J89" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L89" t="n">
         <v>0</v>
       </c>
       <c r="M89" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="90">
@@ -4187,13 +4177,13 @@
         <v>0</v>
       </c>
       <c r="F91" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G91" t="n">
         <v>1</v>
       </c>
       <c r="H91" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I91" t="n">
         <v>0</v>
@@ -4217,30 +4207,32 @@
           <t>大功率鋰電池芯/模組、電池管理系統、動力馬達等零組件</t>
         </is>
       </c>
-      <c r="B92" t="inlineStr"/>
+      <c r="B92" t="n">
+        <v>0</v>
+      </c>
       <c r="C92" t="n">
+        <v>1</v>
+      </c>
+      <c r="D92" t="n">
+        <v>1</v>
+      </c>
+      <c r="E92" t="n">
+        <v>1</v>
+      </c>
+      <c r="F92" t="n">
+        <v>0</v>
+      </c>
+      <c r="G92" t="n">
+        <v>0</v>
+      </c>
+      <c r="H92" t="n">
         <v>2</v>
       </c>
-      <c r="D92" t="n">
-        <v>1</v>
-      </c>
-      <c r="E92" t="n">
-        <v>1</v>
-      </c>
-      <c r="F92" t="n">
-        <v>1</v>
-      </c>
-      <c r="G92" t="n">
-        <v>0</v>
-      </c>
-      <c r="H92" t="n">
-        <v>0</v>
-      </c>
       <c r="I92" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J92" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K92" t="n">
         <v>1</v>
@@ -4249,7 +4241,7 @@
         <v>1</v>
       </c>
       <c r="M92" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="93">
@@ -4357,10 +4349,10 @@
         <v>0</v>
       </c>
       <c r="H95" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I95" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -4369,7 +4361,7 @@
         <v>0</v>
       </c>
       <c r="L95" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M95" t="n">
         <v>1</v>
@@ -4381,7 +4373,9 @@
           <t>太陽能電廠</t>
         </is>
       </c>
-      <c r="B96" t="inlineStr"/>
+      <c r="B96" t="n">
+        <v>0</v>
+      </c>
       <c r="C96" t="n">
         <v>0</v>
       </c>
@@ -4398,10 +4392,10 @@
         <v>0</v>
       </c>
       <c r="H96" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I96" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -4413,7 +4407,7 @@
         <v>0</v>
       </c>
       <c r="M96" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="97">
@@ -4600,16 +4594,16 @@
         <v>0</v>
       </c>
       <c r="G101" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H101" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I101" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J101" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K101" t="n">
         <v>0</v>
@@ -4638,28 +4632,28 @@
         <v>1</v>
       </c>
       <c r="F102" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G102" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H102" t="n">
+        <v>1</v>
+      </c>
+      <c r="I102" t="n">
+        <v>1</v>
+      </c>
+      <c r="J102" t="n">
+        <v>0</v>
+      </c>
+      <c r="K102" t="n">
+        <v>0</v>
+      </c>
+      <c r="L102" t="n">
+        <v>0</v>
+      </c>
+      <c r="M102" t="n">
         <v>2</v>
-      </c>
-      <c r="I102" t="n">
-        <v>1</v>
-      </c>
-      <c r="J102" t="n">
-        <v>1</v>
-      </c>
-      <c r="K102" t="n">
-        <v>0</v>
-      </c>
-      <c r="L102" t="n">
-        <v>0</v>
-      </c>
-      <c r="M102" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="103">
@@ -4723,16 +4717,16 @@
         <v>0</v>
       </c>
       <c r="G104" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H104" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I104" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J104" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K104" t="n">
         <v>0</v>
@@ -4741,7 +4735,7 @@
         <v>0</v>
       </c>
       <c r="M104" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="105">
@@ -4758,31 +4752,31 @@
         <v>0</v>
       </c>
       <c r="E105" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F105" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G105" t="n">
         <v>1</v>
       </c>
       <c r="H105" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I105" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J105" t="n">
         <v>1</v>
       </c>
       <c r="K105" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L105" t="n">
         <v>0</v>
       </c>
       <c r="M105" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="106">
@@ -4793,37 +4787,37 @@
       </c>
       <c r="B106" t="inlineStr"/>
       <c r="C106" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D106" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E106" t="n">
         <v>0</v>
       </c>
       <c r="F106" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G106" t="n">
+        <v>1</v>
+      </c>
+      <c r="H106" t="n">
         <v>2</v>
       </c>
-      <c r="H106" t="n">
-        <v>1</v>
-      </c>
       <c r="I106" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J106" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K106" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L106" t="n">
         <v>0</v>
       </c>
       <c r="M106" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="107">
@@ -4955,7 +4949,9 @@
           <t>工業用設備</t>
         </is>
       </c>
-      <c r="B110" t="inlineStr"/>
+      <c r="B110" t="n">
+        <v>0</v>
+      </c>
       <c r="C110" t="n">
         <v>0</v>
       </c>
@@ -4966,10 +4962,10 @@
         <v>0</v>
       </c>
       <c r="F110" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G110" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H110" t="n">
         <v>0</v>
@@ -4987,7 +4983,7 @@
         <v>0</v>
       </c>
       <c r="M110" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="111">
@@ -4996,32 +4992,30 @@
           <t>工業電腦</t>
         </is>
       </c>
-      <c r="B111" t="n">
-        <v>0</v>
-      </c>
+      <c r="B111" t="inlineStr"/>
       <c r="C111" t="n">
+        <v>1</v>
+      </c>
+      <c r="D111" t="n">
         <v>2</v>
       </c>
-      <c r="D111" t="n">
-        <v>1</v>
-      </c>
       <c r="E111" t="n">
+        <v>0</v>
+      </c>
+      <c r="F111" t="n">
         <v>2</v>
       </c>
-      <c r="F111" t="n">
-        <v>0</v>
-      </c>
       <c r="G111" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H111" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I111" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J111" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K111" t="n">
         <v>0</v>
@@ -5056,10 +5050,10 @@
         <v>0</v>
       </c>
       <c r="H112" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I112" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -5068,10 +5062,10 @@
         <v>0</v>
       </c>
       <c r="L112" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M112" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="113">
@@ -5097,10 +5091,10 @@
         <v>0</v>
       </c>
       <c r="H113" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I113" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -5109,10 +5103,10 @@
         <v>0</v>
       </c>
       <c r="L113" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M113" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="114">
@@ -5334,16 +5328,16 @@
         <v>0</v>
       </c>
       <c r="E119" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F119" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G119" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H119" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I119" t="n">
         <v>0</v>
@@ -5369,37 +5363,37 @@
       </c>
       <c r="B120" t="inlineStr"/>
       <c r="C120" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D120" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E120" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F120" t="n">
         <v>1</v>
       </c>
       <c r="G120" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H120" t="n">
+        <v>0</v>
+      </c>
+      <c r="I120" t="n">
+        <v>1</v>
+      </c>
+      <c r="J120" t="n">
+        <v>1</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0</v>
+      </c>
+      <c r="M120" t="n">
         <v>2</v>
-      </c>
-      <c r="I120" t="n">
-        <v>0</v>
-      </c>
-      <c r="J120" t="n">
-        <v>1</v>
-      </c>
-      <c r="K120" t="n">
-        <v>1</v>
-      </c>
-      <c r="L120" t="n">
-        <v>0</v>
-      </c>
-      <c r="M120" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="121">
@@ -5412,13 +5406,13 @@
         <v>0</v>
       </c>
       <c r="C121" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D121" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E121" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F121" t="n">
         <v>0</v>
@@ -5430,7 +5424,7 @@
         <v>0</v>
       </c>
       <c r="I121" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -5442,7 +5436,7 @@
         <v>0</v>
       </c>
       <c r="M121" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="122">
@@ -5541,19 +5535,19 @@
         <v>0</v>
       </c>
       <c r="E124" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F124" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G124" t="n">
         <v>0</v>
       </c>
       <c r="H124" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I124" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -5617,19 +5611,19 @@
       </c>
       <c r="B126" t="inlineStr"/>
       <c r="C126" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D126" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E126" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F126" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G126" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H126" t="n">
         <v>0</v>
@@ -5656,7 +5650,9 @@
           <t>感測裝置</t>
         </is>
       </c>
-      <c r="B127" t="inlineStr"/>
+      <c r="B127" t="n">
+        <v>0</v>
+      </c>
       <c r="C127" t="n">
         <v>0</v>
       </c>
@@ -5667,10 +5663,10 @@
         <v>0</v>
       </c>
       <c r="F127" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G127" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H127" t="n">
         <v>0</v>
@@ -5697,7 +5693,9 @@
           <t>應用/系統軟體設計開發</t>
         </is>
       </c>
-      <c r="B128" t="inlineStr"/>
+      <c r="B128" t="n">
+        <v>0</v>
+      </c>
       <c r="C128" t="n">
         <v>0</v>
       </c>
@@ -5705,7 +5703,7 @@
         <v>0</v>
       </c>
       <c r="E128" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F128" t="n">
         <v>2</v>
@@ -5714,19 +5712,19 @@
         <v>2</v>
       </c>
       <c r="H128" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I128" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J128" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K128" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L128" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M128" t="n">
         <v>1</v>
@@ -5746,7 +5744,7 @@
         <v>0</v>
       </c>
       <c r="E129" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F129" t="n">
         <v>1</v>
@@ -5758,7 +5756,7 @@
         <v>1</v>
       </c>
       <c r="I129" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -5793,10 +5791,10 @@
         <v>0</v>
       </c>
       <c r="G130" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H130" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I130" t="n">
         <v>0</v>
@@ -5820,17 +5818,15 @@
           <t>成衣及其它家居紡織類品</t>
         </is>
       </c>
-      <c r="B131" t="n">
-        <v>0</v>
-      </c>
+      <c r="B131" t="inlineStr"/>
       <c r="C131" t="n">
         <v>0</v>
       </c>
       <c r="D131" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E131" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F131" t="n">
         <v>0</v>
@@ -5839,7 +5835,7 @@
         <v>0</v>
       </c>
       <c r="H131" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I131" t="n">
         <v>1</v>
@@ -5848,13 +5844,13 @@
         <v>1</v>
       </c>
       <c r="K131" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L131" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M131" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="132">
@@ -5865,10 +5861,10 @@
       </c>
       <c r="B132" t="inlineStr"/>
       <c r="C132" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D132" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E132" t="n">
         <v>0</v>
@@ -5883,10 +5879,10 @@
         <v>0</v>
       </c>
       <c r="I132" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J132" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K132" t="n">
         <v>0</v>
@@ -5918,10 +5914,10 @@
         <v>0</v>
       </c>
       <c r="G133" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H133" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I133" t="n">
         <v>0</v>
@@ -6079,10 +6075,10 @@
         <v>0</v>
       </c>
       <c r="F137" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G137" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H137" t="n">
         <v>0</v>
@@ -6152,7 +6148,7 @@
       </c>
       <c r="B139" t="inlineStr"/>
       <c r="C139" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D139" t="n">
         <v>1</v>
@@ -6167,7 +6163,7 @@
         <v>1</v>
       </c>
       <c r="H139" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I139" t="n">
         <v>0</v>
@@ -6182,7 +6178,7 @@
         <v>0</v>
       </c>
       <c r="M139" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="140">
@@ -6246,7 +6242,7 @@
         <v>0</v>
       </c>
       <c r="G141" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H141" t="n">
         <v>1</v>
@@ -6255,7 +6251,7 @@
         <v>1</v>
       </c>
       <c r="J141" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K141" t="n">
         <v>0</v>
@@ -6328,10 +6324,10 @@
         <v>0</v>
       </c>
       <c r="G143" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H143" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I143" t="n">
         <v>0</v>
@@ -6369,19 +6365,19 @@
         <v>0</v>
       </c>
       <c r="G144" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H144" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I144" t="n">
         <v>0</v>
       </c>
       <c r="J144" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K144" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L144" t="n">
         <v>0</v>
@@ -6410,16 +6406,16 @@
         <v>0</v>
       </c>
       <c r="G145" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H145" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I145" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J145" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K145" t="n">
         <v>0</v>
@@ -6448,10 +6444,10 @@
         <v>0</v>
       </c>
       <c r="F146" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G146" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H146" t="n">
         <v>0</v>
@@ -6492,16 +6488,16 @@
         <v>0</v>
       </c>
       <c r="G147" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H147" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I147" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J147" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K147" t="n">
         <v>0</v>
@@ -6521,16 +6517,16 @@
       </c>
       <c r="B148" t="inlineStr"/>
       <c r="C148" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D148" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E148" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F148" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G148" t="n">
         <v>0</v>
@@ -6580,10 +6576,10 @@
         <v>0</v>
       </c>
       <c r="I149" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J149" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K149" t="n">
         <v>0</v>
@@ -6606,7 +6602,7 @@
         <v>1</v>
       </c>
       <c r="D150" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E150" t="n">
         <v>0</v>
@@ -6633,7 +6629,7 @@
         <v>0</v>
       </c>
       <c r="M150" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="151">
@@ -6644,7 +6640,7 @@
       </c>
       <c r="B151" t="inlineStr"/>
       <c r="C151" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D151" t="n">
         <v>0</v>
@@ -6653,28 +6649,28 @@
         <v>0</v>
       </c>
       <c r="F151" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G151" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H151" t="n">
         <v>0</v>
       </c>
       <c r="I151" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J151" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K151" t="n">
         <v>0</v>
       </c>
       <c r="L151" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M151" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="152">
@@ -6694,13 +6690,13 @@
         <v>0</v>
       </c>
       <c r="F152" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G152" t="n">
         <v>1</v>
       </c>
       <c r="H152" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I152" t="n">
         <v>0</v>
@@ -6738,25 +6734,25 @@
         <v>0</v>
       </c>
       <c r="G153" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H153" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I153" t="n">
         <v>0</v>
       </c>
       <c r="J153" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K153" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L153" t="n">
         <v>0</v>
       </c>
       <c r="M153" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="154">
@@ -6782,10 +6778,10 @@
         <v>0</v>
       </c>
       <c r="H154" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I154" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -6797,7 +6793,7 @@
         <v>0</v>
       </c>
       <c r="M154" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="155">
@@ -6855,25 +6851,25 @@
         <v>0</v>
       </c>
       <c r="E156" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F156" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G156" t="n">
         <v>0</v>
       </c>
       <c r="H156" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I156" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J156" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K156" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L156" t="n">
         <v>0</v>
@@ -6890,10 +6886,10 @@
       </c>
       <c r="B157" t="inlineStr"/>
       <c r="C157" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D157" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E157" t="n">
         <v>0</v>
@@ -6902,13 +6898,13 @@
         <v>0</v>
       </c>
       <c r="G157" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H157" t="n">
         <v>2</v>
       </c>
       <c r="I157" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -6934,19 +6930,19 @@
         <v>0</v>
       </c>
       <c r="D158" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E158" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F158" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G158" t="n">
         <v>1</v>
       </c>
       <c r="H158" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I158" t="n">
         <v>0</v>
@@ -6961,7 +6957,7 @@
         <v>0</v>
       </c>
       <c r="M158" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="159">
@@ -7025,10 +7021,10 @@
         <v>0</v>
       </c>
       <c r="G160" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H160" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I160" t="n">
         <v>0</v>
@@ -7043,7 +7039,7 @@
         <v>0</v>
       </c>
       <c r="M160" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="161">
@@ -7066,10 +7062,10 @@
         <v>0</v>
       </c>
       <c r="G161" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H161" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I161" t="n">
         <v>0</v>
@@ -7107,25 +7103,25 @@
         <v>0</v>
       </c>
       <c r="G162" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H162" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I162" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J162" t="n">
         <v>1</v>
       </c>
       <c r="K162" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L162" t="n">
         <v>0</v>
       </c>
       <c r="M162" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="163">
@@ -7148,13 +7144,13 @@
         <v>0</v>
       </c>
       <c r="G163" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H163" t="n">
         <v>1</v>
       </c>
       <c r="I163" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -7186,13 +7182,13 @@
         <v>0</v>
       </c>
       <c r="F164" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G164" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H164" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I164" t="n">
         <v>0</v>
@@ -7224,22 +7220,22 @@
         <v>0</v>
       </c>
       <c r="E165" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F165" t="n">
         <v>1</v>
       </c>
       <c r="G165" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H165" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I165" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J165" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K165" t="n">
         <v>0</v>
@@ -7274,10 +7270,10 @@
         <v>0</v>
       </c>
       <c r="H166" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I166" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -7286,7 +7282,7 @@
         <v>0</v>
       </c>
       <c r="L166" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M166" t="n">
         <v>1</v>
@@ -7298,27 +7294,29 @@
           <t>機電系統工程</t>
         </is>
       </c>
-      <c r="B167" t="inlineStr"/>
+      <c r="B167" t="n">
+        <v>0</v>
+      </c>
       <c r="C167" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D167" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E167" t="n">
         <v>0</v>
       </c>
       <c r="F167" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G167" t="n">
         <v>0</v>
       </c>
       <c r="H167" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I167" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -7327,10 +7325,10 @@
         <v>0</v>
       </c>
       <c r="L167" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M167" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="168">
@@ -7505,10 +7503,10 @@
       </c>
       <c r="B172" t="inlineStr"/>
       <c r="C172" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D172" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E172" t="n">
         <v>0</v>
@@ -7520,10 +7518,10 @@
         <v>0</v>
       </c>
       <c r="H172" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I172" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -7544,9 +7542,7 @@
           <t>流行音樂及文化內容產業</t>
         </is>
       </c>
-      <c r="B173" t="n">
-        <v>0</v>
-      </c>
+      <c r="B173" t="inlineStr"/>
       <c r="C173" t="n">
         <v>0</v>
       </c>
@@ -7560,10 +7556,10 @@
         <v>0</v>
       </c>
       <c r="G173" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H173" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I173" t="n">
         <v>0</v>
@@ -7721,19 +7717,19 @@
         <v>0</v>
       </c>
       <c r="F177" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G177" t="n">
         <v>1</v>
       </c>
       <c r="H177" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I177" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J177" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K177" t="n">
         <v>0</v>
@@ -7742,7 +7738,7 @@
         <v>0</v>
       </c>
       <c r="M177" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="178">
@@ -7799,48 +7795,50 @@
         <v>1</v>
       </c>
       <c r="D179" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E179" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F179" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G179" t="n">
+        <v>5</v>
+      </c>
+      <c r="H179" t="n">
+        <v>1</v>
+      </c>
+      <c r="I179" t="n">
+        <v>0</v>
+      </c>
+      <c r="J179" t="n">
         <v>2</v>
       </c>
-      <c r="H179" t="n">
-        <v>5</v>
-      </c>
-      <c r="I179" t="n">
-        <v>1</v>
-      </c>
-      <c r="J179" t="n">
-        <v>0</v>
-      </c>
       <c r="K179" t="n">
+        <v>0</v>
+      </c>
+      <c r="L179" t="n">
+        <v>0</v>
+      </c>
+      <c r="M179" t="n">
         <v>2</v>
-      </c>
-      <c r="L179" t="n">
-        <v>0</v>
-      </c>
-      <c r="M179" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="1" t="inlineStr">
         <is>
-          <t>煤、鐵礦砂、鎳鐵、鉻鐵、廢鋼</t>
-        </is>
-      </c>
-      <c r="B180" t="inlineStr"/>
+          <t>燈具/應用</t>
+        </is>
+      </c>
+      <c r="B180" t="n">
+        <v>0</v>
+      </c>
       <c r="C180" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D180" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E180" t="n">
         <v>0</v>
@@ -7849,13 +7847,13 @@
         <v>0</v>
       </c>
       <c r="G180" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H180" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I180" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -7867,13 +7865,13 @@
         <v>0</v>
       </c>
       <c r="M180" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="1" t="inlineStr">
         <is>
-          <t>燈具/應用</t>
+          <t>營造業</t>
         </is>
       </c>
       <c r="B181" t="inlineStr"/>
@@ -7881,25 +7879,25 @@
         <v>0</v>
       </c>
       <c r="D181" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E181" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F181" t="n">
         <v>0</v>
       </c>
       <c r="G181" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H181" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I181" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J181" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K181" t="n">
         <v>0</v>
@@ -7914,7 +7912,7 @@
     <row r="182">
       <c r="A182" s="1" t="inlineStr">
         <is>
-          <t>營造業</t>
+          <t>營造設置</t>
         </is>
       </c>
       <c r="B182" t="inlineStr"/>
@@ -7934,16 +7932,16 @@
         <v>0</v>
       </c>
       <c r="H182" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I182" t="n">
         <v>0</v>
       </c>
       <c r="J182" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K182" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L182" t="n">
         <v>0</v>
@@ -7955,7 +7953,7 @@
     <row r="183">
       <c r="A183" s="1" t="inlineStr">
         <is>
-          <t>營造設置</t>
+          <t>營運管理軟體</t>
         </is>
       </c>
       <c r="B183" t="inlineStr"/>
@@ -7966,19 +7964,19 @@
         <v>0</v>
       </c>
       <c r="E183" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F183" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G183" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H183" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I183" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -7996,7 +7994,7 @@
     <row r="184">
       <c r="A184" s="1" t="inlineStr">
         <is>
-          <t>營運管理軟體</t>
+          <t>營養食品</t>
         </is>
       </c>
       <c r="B184" t="inlineStr"/>
@@ -8010,19 +8008,19 @@
         <v>0</v>
       </c>
       <c r="F184" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G184" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H184" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I184" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J184" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K184" t="n">
         <v>0</v>
@@ -8037,12 +8035,10 @@
     <row r="185">
       <c r="A185" s="1" t="inlineStr">
         <is>
-          <t>營養食品</t>
-        </is>
-      </c>
-      <c r="B185" t="n">
-        <v>0</v>
-      </c>
+          <t>物業管理</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr"/>
       <c r="C185" t="n">
         <v>0</v>
       </c>
@@ -8080,7 +8076,7 @@
     <row r="186">
       <c r="A186" s="1" t="inlineStr">
         <is>
-          <t>物業管理</t>
+          <t>物流倉儲服務</t>
         </is>
       </c>
       <c r="B186" t="inlineStr"/>
@@ -8121,7 +8117,7 @@
     <row r="187">
       <c r="A187" s="1" t="inlineStr">
         <is>
-          <t>物流倉儲服務</t>
+          <t>物聯網安全</t>
         </is>
       </c>
       <c r="B187" t="inlineStr"/>
@@ -8138,16 +8134,16 @@
         <v>0</v>
       </c>
       <c r="G187" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H187" t="n">
         <v>0</v>
       </c>
       <c r="I187" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J187" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K187" t="n">
         <v>0</v>
@@ -8162,7 +8158,7 @@
     <row r="188">
       <c r="A188" s="1" t="inlineStr">
         <is>
-          <t>物聯網安全</t>
+          <t>特殊照明業</t>
         </is>
       </c>
       <c r="B188" t="inlineStr"/>
@@ -8182,28 +8178,28 @@
         <v>0</v>
       </c>
       <c r="H188" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I188" t="n">
         <v>0</v>
       </c>
       <c r="J188" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K188" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L188" t="n">
         <v>0</v>
       </c>
       <c r="M188" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="1" t="inlineStr">
         <is>
-          <t>特殊照明業</t>
+          <t>玻/碳纖</t>
         </is>
       </c>
       <c r="B189" t="inlineStr"/>
@@ -8220,7 +8216,7 @@
         <v>0</v>
       </c>
       <c r="G189" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H189" t="n">
         <v>0</v>
@@ -8244,12 +8240,12 @@
     <row r="190">
       <c r="A190" s="1" t="inlineStr">
         <is>
-          <t>玻/碳纖</t>
+          <t>玻璃基板</t>
         </is>
       </c>
       <c r="B190" t="inlineStr"/>
       <c r="C190" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D190" t="n">
         <v>0</v>
@@ -8264,7 +8260,7 @@
         <v>0</v>
       </c>
       <c r="H190" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I190" t="n">
         <v>0</v>
@@ -8285,7 +8281,7 @@
     <row r="191">
       <c r="A191" s="1" t="inlineStr">
         <is>
-          <t>玻璃基板</t>
+          <t>玻璃纖維/玻纖布</t>
         </is>
       </c>
       <c r="B191" t="inlineStr"/>
@@ -8293,22 +8289,22 @@
         <v>0</v>
       </c>
       <c r="D191" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E191" t="n">
         <v>0</v>
       </c>
       <c r="F191" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G191" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H191" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I191" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -8320,13 +8316,13 @@
         <v>0</v>
       </c>
       <c r="M191" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="1" t="inlineStr">
         <is>
-          <t>玻璃纖維/玻纖布</t>
+          <t>理財投資</t>
         </is>
       </c>
       <c r="B192" t="inlineStr"/>
@@ -8343,16 +8339,16 @@
         <v>0</v>
       </c>
       <c r="G192" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H192" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I192" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J192" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K192" t="n">
         <v>0</v>
@@ -8367,15 +8363,15 @@
     <row r="193">
       <c r="A193" s="1" t="inlineStr">
         <is>
-          <t>理財投資</t>
+          <t>環保潔能服務產業</t>
         </is>
       </c>
       <c r="B193" t="inlineStr"/>
       <c r="C193" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D193" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E193" t="n">
         <v>0</v>
@@ -8402,13 +8398,13 @@
         <v>0</v>
       </c>
       <c r="M193" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="1" t="inlineStr">
         <is>
-          <t>環保潔能服務產業</t>
+          <t>環氧樹脂</t>
         </is>
       </c>
       <c r="B194" t="inlineStr"/>
@@ -8416,19 +8412,19 @@
         <v>0</v>
       </c>
       <c r="D194" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E194" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F194" t="n">
         <v>0</v>
       </c>
       <c r="G194" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H194" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I194" t="n">
         <v>0</v>
@@ -8449,132 +8445,132 @@
     <row r="195">
       <c r="A195" s="1" t="inlineStr">
         <is>
-          <t>環氧樹脂</t>
+          <t>生產製程、檢測設備及原物料</t>
         </is>
       </c>
       <c r="B195" t="inlineStr"/>
       <c r="C195" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D195" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E195" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F195" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G195" t="n">
         <v>0</v>
       </c>
       <c r="H195" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I195" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J195" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K195" t="n">
         <v>0</v>
       </c>
       <c r="L195" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M195" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="1" t="inlineStr">
         <is>
-          <t>生產製程、檢測設備及原物料</t>
-        </is>
-      </c>
-      <c r="B196" t="inlineStr"/>
+          <t>生產製程及檢測設備</t>
+        </is>
+      </c>
+      <c r="B196" t="n">
+        <v>0</v>
+      </c>
       <c r="C196" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D196" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E196" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F196" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G196" t="n">
         <v>1</v>
       </c>
       <c r="H196" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I196" t="n">
+        <v>2</v>
+      </c>
+      <c r="J196" t="n">
+        <v>1</v>
+      </c>
+      <c r="K196" t="n">
+        <v>1</v>
+      </c>
+      <c r="L196" t="n">
         <v>3</v>
       </c>
-      <c r="J196" t="n">
-        <v>0</v>
-      </c>
-      <c r="K196" t="n">
-        <v>1</v>
-      </c>
-      <c r="L196" t="n">
-        <v>0</v>
-      </c>
       <c r="M196" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="1" t="inlineStr">
         <is>
-          <t>生產製程及檢測設備</t>
-        </is>
-      </c>
-      <c r="B197" t="n">
-        <v>0</v>
-      </c>
+          <t>發電營運</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr"/>
       <c r="C197" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D197" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E197" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F197" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G197" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H197" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I197" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="J197" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K197" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L197" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M197" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="1" t="inlineStr">
         <is>
-          <t>發電營運</t>
+          <t>監控管理</t>
         </is>
       </c>
       <c r="B198" t="inlineStr"/>
@@ -8615,7 +8611,7 @@
     <row r="199">
       <c r="A199" s="1" t="inlineStr">
         <is>
-          <t>監控管理</t>
+          <t>監控系統</t>
         </is>
       </c>
       <c r="B199" t="inlineStr"/>
@@ -8650,13 +8646,13 @@
         <v>0</v>
       </c>
       <c r="M199" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="1" t="inlineStr">
         <is>
-          <t>監控系統</t>
+          <t>監理法遵</t>
         </is>
       </c>
       <c r="B200" t="inlineStr"/>
@@ -8667,7 +8663,7 @@
         <v>0</v>
       </c>
       <c r="E200" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F200" t="n">
         <v>0</v>
@@ -8697,10 +8693,12 @@
     <row r="201">
       <c r="A201" s="1" t="inlineStr">
         <is>
-          <t>監理法遵</t>
-        </is>
-      </c>
-      <c r="B201" t="inlineStr"/>
+          <t>監視器/顯示器</t>
+        </is>
+      </c>
+      <c r="B201" t="n">
+        <v>0</v>
+      </c>
       <c r="C201" t="n">
         <v>0</v>
       </c>
@@ -8738,12 +8736,12 @@
     <row r="202">
       <c r="A202" s="1" t="inlineStr">
         <is>
-          <t>監視器/顯示器</t>
+          <t>石化上游原料及相關鑽探設備</t>
         </is>
       </c>
       <c r="B202" t="inlineStr"/>
       <c r="C202" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D202" t="n">
         <v>0</v>
@@ -8758,7 +8756,7 @@
         <v>1</v>
       </c>
       <c r="H202" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I202" t="n">
         <v>0</v>
@@ -8779,15 +8777,15 @@
     <row r="203">
       <c r="A203" s="1" t="inlineStr">
         <is>
-          <t>石化上游原料及相關鑽探設備</t>
+          <t>石化中間原料(例如乙烯、丙烯、丁二烯、苯、酚等)</t>
         </is>
       </c>
       <c r="B203" t="inlineStr"/>
       <c r="C203" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D203" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E203" t="n">
         <v>0</v>
@@ -8799,19 +8797,19 @@
         <v>0</v>
       </c>
       <c r="H203" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I203" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J203" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K203" t="n">
         <v>0</v>
       </c>
       <c r="L203" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M203" t="n">
         <v>0</v>
@@ -8820,7 +8818,7 @@
     <row r="204">
       <c r="A204" s="1" t="inlineStr">
         <is>
-          <t>石化中間原料(例如乙烯、丙烯、丁二烯、苯、酚等)</t>
+          <t>石化原料(例如純對苯二甲酸、乙二醇、己內醯胺、丙烯腈等)</t>
         </is>
       </c>
       <c r="B204" t="inlineStr"/>
@@ -8828,7 +8826,7 @@
         <v>1</v>
       </c>
       <c r="D204" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E204" t="n">
         <v>0</v>
@@ -8837,39 +8835,39 @@
         <v>0</v>
       </c>
       <c r="G204" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H204" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I204" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J204" t="n">
         <v>0</v>
       </c>
       <c r="K204" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L204" t="n">
         <v>0</v>
       </c>
       <c r="M204" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="1" t="inlineStr">
         <is>
-          <t>石化原料(例如純對苯二甲酸、乙二醇、己內醯胺、丙烯腈等)</t>
+          <t>石灰石</t>
         </is>
       </c>
       <c r="B205" t="inlineStr"/>
       <c r="C205" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D205" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E205" t="n">
         <v>0</v>
@@ -8881,10 +8879,10 @@
         <v>0</v>
       </c>
       <c r="H205" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I205" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J205" t="n">
         <v>0</v>
@@ -8902,7 +8900,7 @@
     <row r="206">
       <c r="A206" s="1" t="inlineStr">
         <is>
-          <t>石灰石</t>
+          <t>矽晶圓/矽晶片</t>
         </is>
       </c>
       <c r="B206" t="inlineStr"/>
@@ -8925,10 +8923,10 @@
         <v>0</v>
       </c>
       <c r="I206" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J206" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K206" t="n">
         <v>0</v>
@@ -8943,33 +8941,35 @@
     <row r="207">
       <c r="A207" s="1" t="inlineStr">
         <is>
-          <t>矽晶圓/矽晶片</t>
-        </is>
-      </c>
-      <c r="B207" t="inlineStr"/>
+          <t>硬板、軟板、IC載板製造</t>
+        </is>
+      </c>
+      <c r="B207" t="n">
+        <v>0</v>
+      </c>
       <c r="C207" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D207" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E207" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F207" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G207" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H207" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I207" t="n">
         <v>0</v>
       </c>
       <c r="J207" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K207" t="n">
         <v>1</v>
@@ -8978,13 +8978,13 @@
         <v>0</v>
       </c>
       <c r="M207" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="1" t="inlineStr">
         <is>
-          <t>硬板、軟板、IC載板製造</t>
+          <t>硬碟機</t>
         </is>
       </c>
       <c r="B208" t="inlineStr"/>
@@ -8992,31 +8992,31 @@
         <v>0</v>
       </c>
       <c r="D208" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E208" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F208" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G208" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H208" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I208" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J208" t="n">
         <v>0</v>
       </c>
       <c r="K208" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L208" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M208" t="n">
         <v>0</v>
@@ -9025,7 +9025,7 @@
     <row r="209">
       <c r="A209" s="1" t="inlineStr">
         <is>
-          <t>硬碟機</t>
+          <t>硬體開發工具</t>
         </is>
       </c>
       <c r="B209" t="inlineStr"/>
@@ -9045,7 +9045,7 @@
         <v>1</v>
       </c>
       <c r="H209" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I209" t="n">
         <v>0</v>
@@ -9066,7 +9066,7 @@
     <row r="210">
       <c r="A210" s="1" t="inlineStr">
         <is>
-          <t>硬體開發工具</t>
+          <t>磁碟儲存系統</t>
         </is>
       </c>
       <c r="B210" t="inlineStr"/>
@@ -9077,13 +9077,13 @@
         <v>0</v>
       </c>
       <c r="E210" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F210" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G210" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H210" t="n">
         <v>1</v>
@@ -9107,7 +9107,7 @@
     <row r="211">
       <c r="A211" s="1" t="inlineStr">
         <is>
-          <t>磁碟儲存系統</t>
+          <t>票券銷售</t>
         </is>
       </c>
       <c r="B211" t="inlineStr"/>
@@ -9121,16 +9121,16 @@
         <v>0</v>
       </c>
       <c r="F211" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G211" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H211" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I211" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J211" t="n">
         <v>0</v>
@@ -9148,7 +9148,7 @@
     <row r="212">
       <c r="A212" s="1" t="inlineStr">
         <is>
-          <t>票券銷售</t>
+          <t>租賃業</t>
         </is>
       </c>
       <c r="B212" t="inlineStr"/>
@@ -9189,7 +9189,7 @@
     <row r="213">
       <c r="A213" s="1" t="inlineStr">
         <is>
-          <t>租賃業</t>
+          <t>移動控制</t>
         </is>
       </c>
       <c r="B213" t="inlineStr"/>
@@ -9230,7 +9230,7 @@
     <row r="214">
       <c r="A214" s="1" t="inlineStr">
         <is>
-          <t>移動控制</t>
+          <t>稜鏡片</t>
         </is>
       </c>
       <c r="B214" t="inlineStr"/>
@@ -9271,7 +9271,7 @@
     <row r="215">
       <c r="A215" s="1" t="inlineStr">
         <is>
-          <t>稜鏡片</t>
+          <t>穿戴式裝置</t>
         </is>
       </c>
       <c r="B215" t="inlineStr"/>
@@ -9288,7 +9288,7 @@
         <v>0</v>
       </c>
       <c r="G215" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H215" t="n">
         <v>0</v>
@@ -9312,7 +9312,7 @@
     <row r="216">
       <c r="A216" s="1" t="inlineStr">
         <is>
-          <t>穿戴式裝置</t>
+          <t>端點安全防護</t>
         </is>
       </c>
       <c r="B216" t="inlineStr"/>
@@ -9323,22 +9323,22 @@
         <v>0</v>
       </c>
       <c r="E216" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F216" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G216" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H216" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I216" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J216" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K216" t="n">
         <v>0</v>
@@ -9353,7 +9353,7 @@
     <row r="217">
       <c r="A217" s="1" t="inlineStr">
         <is>
-          <t>端點安全防護</t>
+          <t>筆記型電腦</t>
         </is>
       </c>
       <c r="B217" t="inlineStr"/>
@@ -9361,7 +9361,7 @@
         <v>0</v>
       </c>
       <c r="D217" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E217" t="n">
         <v>0</v>
@@ -9373,28 +9373,28 @@
         <v>1</v>
       </c>
       <c r="H217" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I217" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J217" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K217" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L217" t="n">
         <v>0</v>
       </c>
       <c r="M217" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" s="1" t="inlineStr">
         <is>
-          <t>筆記型電腦</t>
+          <t>精簡型電腦</t>
         </is>
       </c>
       <c r="B218" t="inlineStr"/>
@@ -9405,22 +9405,22 @@
         <v>0</v>
       </c>
       <c r="E218" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F218" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G218" t="n">
         <v>1</v>
       </c>
       <c r="H218" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I218" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J218" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K218" t="n">
         <v>0</v>
@@ -9429,36 +9429,36 @@
         <v>0</v>
       </c>
       <c r="M218" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" s="1" t="inlineStr">
         <is>
-          <t>精簡型電腦</t>
+          <t>系統整合</t>
         </is>
       </c>
       <c r="B219" t="inlineStr"/>
       <c r="C219" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D219" t="n">
         <v>0</v>
       </c>
       <c r="E219" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F219" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G219" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H219" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I219" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J219" t="n">
         <v>1</v>
@@ -9467,48 +9467,50 @@
         <v>0</v>
       </c>
       <c r="L219" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M219" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" s="1" t="inlineStr">
         <is>
-          <t>系統整合</t>
-        </is>
-      </c>
-      <c r="B220" t="inlineStr"/>
+          <t>系統整合服務</t>
+        </is>
+      </c>
+      <c r="B220" t="n">
+        <v>0</v>
+      </c>
       <c r="C220" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D220" t="n">
         <v>1</v>
       </c>
       <c r="E220" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F220" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G220" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="H220" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I220" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J220" t="n">
         <v>2</v>
       </c>
       <c r="K220" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L220" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M220" t="n">
         <v>1</v>
@@ -9517,48 +9519,48 @@
     <row r="221">
       <c r="A221" s="1" t="inlineStr">
         <is>
-          <t>系統整合服務</t>
+          <t>紙漿、紙類原料</t>
         </is>
       </c>
       <c r="B221" t="inlineStr"/>
       <c r="C221" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D221" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E221" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F221" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G221" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H221" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I221" t="n">
         <v>1</v>
       </c>
       <c r="J221" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K221" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L221" t="n">
         <v>0</v>
       </c>
       <c r="M221" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" s="1" t="inlineStr">
         <is>
-          <t>紙漿、紙類原料</t>
+          <t>紡紗</t>
         </is>
       </c>
       <c r="B222" t="inlineStr"/>
@@ -9569,22 +9571,22 @@
         <v>0</v>
       </c>
       <c r="E222" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F222" t="n">
         <v>0</v>
       </c>
       <c r="G222" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H222" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I222" t="n">
         <v>0</v>
       </c>
       <c r="J222" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K222" t="n">
         <v>0</v>
@@ -9599,7 +9601,7 @@
     <row r="223">
       <c r="A223" s="1" t="inlineStr">
         <is>
-          <t>紡紗</t>
+          <t>組裝廠</t>
         </is>
       </c>
       <c r="B223" t="inlineStr"/>
@@ -9613,16 +9615,16 @@
         <v>0</v>
       </c>
       <c r="F223" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G223" t="n">
         <v>0</v>
       </c>
       <c r="H223" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I223" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J223" t="n">
         <v>0</v>
@@ -9640,7 +9642,7 @@
     <row r="224">
       <c r="A224" s="1" t="inlineStr">
         <is>
-          <t>組裝廠</t>
+          <t>結構工程</t>
         </is>
       </c>
       <c r="B224" t="inlineStr"/>
@@ -9681,7 +9683,7 @@
     <row r="225">
       <c r="A225" s="1" t="inlineStr">
         <is>
-          <t>結構工程</t>
+          <t>網路IC</t>
         </is>
       </c>
       <c r="B225" t="inlineStr"/>
@@ -9692,7 +9694,7 @@
         <v>0</v>
       </c>
       <c r="E225" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F225" t="n">
         <v>0</v>
@@ -9701,7 +9703,7 @@
         <v>0</v>
       </c>
       <c r="H225" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I225" t="n">
         <v>0</v>
@@ -9722,7 +9724,7 @@
     <row r="226">
       <c r="A226" s="1" t="inlineStr">
         <is>
-          <t>網路IC</t>
+          <t>網路卡</t>
         </is>
       </c>
       <c r="B226" t="inlineStr"/>
@@ -9739,13 +9741,13 @@
         <v>1</v>
       </c>
       <c r="G226" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H226" t="n">
         <v>0</v>
       </c>
       <c r="I226" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J226" t="n">
         <v>0</v>
@@ -9763,7 +9765,7 @@
     <row r="227">
       <c r="A227" s="1" t="inlineStr">
         <is>
-          <t>網路卡</t>
+          <t>網路基礎設施</t>
         </is>
       </c>
       <c r="B227" t="inlineStr"/>
@@ -9777,19 +9779,19 @@
         <v>0</v>
       </c>
       <c r="F227" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G227" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H227" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I227" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J227" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K227" t="n">
         <v>0</v>
@@ -9804,7 +9806,7 @@
     <row r="228">
       <c r="A228" s="1" t="inlineStr">
         <is>
-          <t>網路基礎設施</t>
+          <t>網路安全防護</t>
         </is>
       </c>
       <c r="B228" t="inlineStr"/>
@@ -9818,22 +9820,22 @@
         <v>0</v>
       </c>
       <c r="F228" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G228" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H228" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I228" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J228" t="n">
         <v>1</v>
       </c>
       <c r="K228" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L228" t="n">
         <v>0</v>
@@ -9845,70 +9847,70 @@
     <row r="229">
       <c r="A229" s="1" t="inlineStr">
         <is>
-          <t>網路安全防護</t>
-        </is>
-      </c>
-      <c r="B229" t="inlineStr"/>
+          <t>網路設備(如數據機、網路卡、閘道器、路由器、網路電話)</t>
+        </is>
+      </c>
+      <c r="B229" t="n">
+        <v>0</v>
+      </c>
       <c r="C229" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D229" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E229" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F229" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G229" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H229" t="n">
+        <v>1</v>
+      </c>
+      <c r="I229" t="n">
+        <v>1</v>
+      </c>
+      <c r="J229" t="n">
         <v>2</v>
       </c>
-      <c r="I229" t="n">
-        <v>0</v>
-      </c>
-      <c r="J229" t="n">
-        <v>1</v>
-      </c>
       <c r="K229" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L229" t="n">
         <v>0</v>
       </c>
       <c r="M229" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="1" t="inlineStr">
         <is>
-          <t>網路設備(如數據機、網路卡、閘道器、路由器、網路電話)</t>
-        </is>
-      </c>
-      <c r="B230" t="n">
-        <v>0</v>
-      </c>
+          <t>網頁內容安全</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr"/>
       <c r="C230" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D230" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E230" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F230" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G230" t="n">
         <v>2</v>
       </c>
       <c r="H230" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="I230" t="n">
         <v>1</v>
@@ -9917,7 +9919,7 @@
         <v>1</v>
       </c>
       <c r="K230" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L230" t="n">
         <v>0</v>
@@ -9929,7 +9931,7 @@
     <row r="231">
       <c r="A231" s="1" t="inlineStr">
         <is>
-          <t>網頁內容安全</t>
+          <t>線上遊戲業</t>
         </is>
       </c>
       <c r="B231" t="inlineStr"/>
@@ -9940,28 +9942,28 @@
         <v>0</v>
       </c>
       <c r="E231" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F231" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G231" t="n">
         <v>0</v>
       </c>
       <c r="H231" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I231" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J231" t="n">
         <v>1</v>
       </c>
       <c r="K231" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L231" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M231" t="n">
         <v>0</v>
@@ -9970,7 +9972,7 @@
     <row r="232">
       <c r="A232" s="1" t="inlineStr">
         <is>
-          <t>線上遊戲業</t>
+          <t>線材</t>
         </is>
       </c>
       <c r="B232" t="inlineStr"/>
@@ -9981,25 +9983,25 @@
         <v>0</v>
       </c>
       <c r="E232" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F232" t="n">
         <v>0</v>
       </c>
       <c r="G232" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H232" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I232" t="n">
         <v>0</v>
       </c>
       <c r="J232" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K232" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L232" t="n">
         <v>0</v>
@@ -10011,7 +10013,7 @@
     <row r="233">
       <c r="A233" s="1" t="inlineStr">
         <is>
-          <t>線材</t>
+          <t>線材盤元</t>
         </is>
       </c>
       <c r="B233" t="inlineStr"/>
@@ -10025,22 +10027,22 @@
         <v>0</v>
       </c>
       <c r="F233" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G233" t="n">
         <v>0</v>
       </c>
       <c r="H233" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I233" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J233" t="n">
         <v>0</v>
       </c>
       <c r="K233" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L233" t="n">
         <v>0</v>
@@ -10052,15 +10054,15 @@
     <row r="234">
       <c r="A234" s="1" t="inlineStr">
         <is>
-          <t>線材盤元</t>
+          <t>織布</t>
         </is>
       </c>
       <c r="B234" t="inlineStr"/>
       <c r="C234" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D234" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E234" t="n">
         <v>0</v>
@@ -10069,10 +10071,10 @@
         <v>0</v>
       </c>
       <c r="G234" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H234" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I234" t="n">
         <v>0</v>
@@ -10093,7 +10095,7 @@
     <row r="235">
       <c r="A235" s="1" t="inlineStr">
         <is>
-          <t>織布</t>
+          <t>聚亞醯胺樹脂</t>
         </is>
       </c>
       <c r="B235" t="inlineStr"/>
@@ -10101,10 +10103,10 @@
         <v>0</v>
       </c>
       <c r="D235" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E235" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F235" t="n">
         <v>0</v>
@@ -10116,7 +10118,7 @@
         <v>1</v>
       </c>
       <c r="I235" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J235" t="n">
         <v>0</v>
@@ -10134,7 +10136,7 @@
     <row r="236">
       <c r="A236" s="1" t="inlineStr">
         <is>
-          <t>聚亞醯胺樹脂</t>
+          <t>背光模組</t>
         </is>
       </c>
       <c r="B236" t="inlineStr"/>
@@ -10157,7 +10159,7 @@
         <v>0</v>
       </c>
       <c r="I236" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J236" t="n">
         <v>0</v>
@@ -10175,7 +10177,7 @@
     <row r="237">
       <c r="A237" s="1" t="inlineStr">
         <is>
-          <t>背光模組</t>
+          <t>背光源(發光二極體、冷陰極管)</t>
         </is>
       </c>
       <c r="B237" t="inlineStr"/>
@@ -10189,19 +10191,19 @@
         <v>0</v>
       </c>
       <c r="F237" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G237" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H237" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I237" t="n">
         <v>0</v>
       </c>
       <c r="J237" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K237" t="n">
         <v>0</v>
@@ -10216,7 +10218,7 @@
     <row r="238">
       <c r="A238" s="1" t="inlineStr">
         <is>
-          <t>背光源(發光二極體、冷陰極管)</t>
+          <t>能源管理服務</t>
         </is>
       </c>
       <c r="B238" t="inlineStr"/>
@@ -10236,28 +10238,28 @@
         <v>1</v>
       </c>
       <c r="H238" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I238" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J238" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K238" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L238" t="n">
         <v>0</v>
       </c>
       <c r="M238" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" s="1" t="inlineStr">
         <is>
-          <t>能源管理服務</t>
+          <t>膠材</t>
         </is>
       </c>
       <c r="B239" t="inlineStr"/>
@@ -10286,7 +10288,7 @@
         <v>0</v>
       </c>
       <c r="K239" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L239" t="n">
         <v>0</v>
@@ -10298,7 +10300,7 @@
     <row r="240">
       <c r="A240" s="1" t="inlineStr">
         <is>
-          <t>膠材</t>
+          <t>臨床實驗、移植技術、疾病治療</t>
         </is>
       </c>
       <c r="B240" t="inlineStr"/>
@@ -10321,7 +10323,7 @@
         <v>0</v>
       </c>
       <c r="I240" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J240" t="n">
         <v>0</v>
@@ -10339,7 +10341,7 @@
     <row r="241">
       <c r="A241" s="1" t="inlineStr">
         <is>
-          <t>臨床實驗、移植技術、疾病治療</t>
+          <t>自動化機台</t>
         </is>
       </c>
       <c r="B241" t="inlineStr"/>
@@ -10374,13 +10376,13 @@
         <v>0</v>
       </c>
       <c r="M241" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" s="1" t="inlineStr">
         <is>
-          <t>自動化機台</t>
+          <t>自動售票機</t>
         </is>
       </c>
       <c r="B242" t="inlineStr"/>
@@ -10421,7 +10423,7 @@
     <row r="243">
       <c r="A243" s="1" t="inlineStr">
         <is>
-          <t>自動售票機</t>
+          <t>自動販賣機</t>
         </is>
       </c>
       <c r="B243" t="inlineStr"/>
@@ -10462,7 +10464,7 @@
     <row r="244">
       <c r="A244" s="1" t="inlineStr">
         <is>
-          <t>自動販賣機</t>
+          <t>自有產品(服務)銷售</t>
         </is>
       </c>
       <c r="B244" t="inlineStr"/>
@@ -10473,13 +10475,13 @@
         <v>0</v>
       </c>
       <c r="E244" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F244" t="n">
         <v>0</v>
       </c>
       <c r="G244" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H244" t="n">
         <v>0</v>
@@ -10503,7 +10505,7 @@
     <row r="245">
       <c r="A245" s="1" t="inlineStr">
         <is>
-          <t>自有產品(服務)銷售</t>
+          <t>自然語言處理</t>
         </is>
       </c>
       <c r="B245" t="inlineStr"/>
@@ -10517,16 +10519,16 @@
         <v>0</v>
       </c>
       <c r="F245" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G245" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H245" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I245" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J245" t="n">
         <v>0</v>
@@ -10544,7 +10546,7 @@
     <row r="246">
       <c r="A246" s="1" t="inlineStr">
         <is>
-          <t>自然語言處理</t>
+          <t>藍寶石晶圓/晶片</t>
         </is>
       </c>
       <c r="B246" t="inlineStr"/>
@@ -10570,7 +10572,7 @@
         <v>0</v>
       </c>
       <c r="J246" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K246" t="n">
         <v>0</v>
@@ -10585,18 +10587,20 @@
     <row r="247">
       <c r="A247" s="1" t="inlineStr">
         <is>
-          <t>藍寶石晶圓/晶片</t>
-        </is>
-      </c>
-      <c r="B247" t="inlineStr"/>
+          <t>藥品代理銷售及通路</t>
+        </is>
+      </c>
+      <c r="B247" t="n">
+        <v>0</v>
+      </c>
       <c r="C247" t="n">
         <v>0</v>
       </c>
       <c r="D247" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E247" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F247" t="n">
         <v>0</v>
@@ -10608,7 +10612,7 @@
         <v>0</v>
       </c>
       <c r="I247" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J247" t="n">
         <v>0</v>
@@ -10626,23 +10630,21 @@
     <row r="248">
       <c r="A248" s="1" t="inlineStr">
         <is>
-          <t>藥品代理銷售及通路</t>
-        </is>
-      </c>
-      <c r="B248" t="n">
-        <v>0</v>
-      </c>
+          <t>處理器/IC</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr"/>
       <c r="C248" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D248" t="n">
         <v>0</v>
       </c>
       <c r="E248" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F248" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G248" t="n">
         <v>0</v>
@@ -10669,7 +10671,7 @@
     <row r="249">
       <c r="A249" s="1" t="inlineStr">
         <is>
-          <t>處理器/IC</t>
+          <t>虛擬化軟體</t>
         </is>
       </c>
       <c r="B249" t="inlineStr"/>
@@ -10677,19 +10679,19 @@
         <v>0</v>
       </c>
       <c r="D249" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E249" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F249" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G249" t="n">
         <v>1</v>
       </c>
       <c r="H249" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I249" t="n">
         <v>0</v>
@@ -10710,7 +10712,7 @@
     <row r="250">
       <c r="A250" s="1" t="inlineStr">
         <is>
-          <t>虛擬化軟體</t>
+          <t>螺絲螺帽</t>
         </is>
       </c>
       <c r="B250" t="inlineStr"/>
@@ -10724,16 +10726,16 @@
         <v>0</v>
       </c>
       <c r="F250" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G250" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H250" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I250" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J250" t="n">
         <v>0</v>
@@ -10751,7 +10753,7 @@
     <row r="251">
       <c r="A251" s="1" t="inlineStr">
         <is>
-          <t>螺絲螺帽</t>
+          <t>行動安全</t>
         </is>
       </c>
       <c r="B251" t="inlineStr"/>
@@ -10768,13 +10770,13 @@
         <v>0</v>
       </c>
       <c r="G251" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H251" t="n">
         <v>0</v>
       </c>
       <c r="I251" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J251" t="n">
         <v>0</v>
@@ -10792,7 +10794,7 @@
     <row r="252">
       <c r="A252" s="1" t="inlineStr">
         <is>
-          <t>行動安全</t>
+          <t>行銷廣告服務</t>
         </is>
       </c>
       <c r="B252" t="inlineStr"/>
@@ -10812,13 +10814,13 @@
         <v>0</v>
       </c>
       <c r="H252" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I252" t="n">
         <v>0</v>
       </c>
       <c r="J252" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K252" t="n">
         <v>0</v>
@@ -10833,7 +10835,7 @@
     <row r="253">
       <c r="A253" s="1" t="inlineStr">
         <is>
-          <t>行銷廣告服務</t>
+          <t>衛星定位系統</t>
         </is>
       </c>
       <c r="B253" t="inlineStr"/>
@@ -10874,7 +10876,7 @@
     <row r="254">
       <c r="A254" s="1" t="inlineStr">
         <is>
-          <t>衛星定位系統</t>
+          <t>裁剪加工</t>
         </is>
       </c>
       <c r="B254" t="inlineStr"/>
@@ -10900,7 +10902,7 @@
         <v>0</v>
       </c>
       <c r="J254" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K254" t="n">
         <v>0</v>
@@ -10915,7 +10917,7 @@
     <row r="255">
       <c r="A255" s="1" t="inlineStr">
         <is>
-          <t>裁剪加工</t>
+          <t>裝潢業</t>
         </is>
       </c>
       <c r="B255" t="inlineStr"/>
@@ -10926,7 +10928,7 @@
         <v>0</v>
       </c>
       <c r="E255" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F255" t="n">
         <v>0</v>
@@ -10944,7 +10946,7 @@
         <v>0</v>
       </c>
       <c r="K255" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L255" t="n">
         <v>0</v>
@@ -10956,7 +10958,7 @@
     <row r="256">
       <c r="A256" s="1" t="inlineStr">
         <is>
-          <t>裝潢業</t>
+          <t>裝置/器材零組件</t>
         </is>
       </c>
       <c r="B256" t="inlineStr"/>
@@ -10970,7 +10972,7 @@
         <v>0</v>
       </c>
       <c r="F256" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G256" t="n">
         <v>0</v>
@@ -10997,7 +10999,7 @@
     <row r="257">
       <c r="A257" s="1" t="inlineStr">
         <is>
-          <t>裝置/器材零組件</t>
+          <t>裝置/器材顯示器</t>
         </is>
       </c>
       <c r="B257" t="inlineStr"/>
@@ -11038,7 +11040,7 @@
     <row r="258">
       <c r="A258" s="1" t="inlineStr">
         <is>
-          <t>裝置/器材顯示器</t>
+          <t>製管</t>
         </is>
       </c>
       <c r="B258" t="inlineStr"/>
@@ -11055,7 +11057,7 @@
         <v>0</v>
       </c>
       <c r="G258" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H258" t="n">
         <v>0</v>
@@ -11079,12 +11081,12 @@
     <row r="259">
       <c r="A259" s="1" t="inlineStr">
         <is>
-          <t>製管</t>
+          <t>製造商</t>
         </is>
       </c>
       <c r="B259" t="inlineStr"/>
       <c r="C259" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D259" t="n">
         <v>0</v>
@@ -11099,10 +11101,10 @@
         <v>0</v>
       </c>
       <c r="H259" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I259" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J259" t="n">
         <v>0</v>
@@ -11120,7 +11122,7 @@
     <row r="260">
       <c r="A260" s="1" t="inlineStr">
         <is>
-          <t>製造商</t>
+          <t>觸控面板</t>
         </is>
       </c>
       <c r="B260" t="inlineStr"/>
@@ -11128,13 +11130,13 @@
         <v>0</v>
       </c>
       <c r="D260" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E260" t="n">
         <v>0</v>
       </c>
       <c r="F260" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G260" t="n">
         <v>0</v>
@@ -11161,33 +11163,33 @@
     <row r="261">
       <c r="A261" s="1" t="inlineStr">
         <is>
-          <t>觸控面板</t>
+          <t>記憶體</t>
         </is>
       </c>
       <c r="B261" t="inlineStr"/>
       <c r="C261" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D261" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E261" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F261" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G261" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H261" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I261" t="n">
         <v>0</v>
       </c>
       <c r="J261" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K261" t="n">
         <v>0</v>
@@ -11202,48 +11204,48 @@
     <row r="262">
       <c r="A262" s="1" t="inlineStr">
         <is>
-          <t>記憶體</t>
+          <t>設備安裝服務</t>
         </is>
       </c>
       <c r="B262" t="inlineStr"/>
       <c r="C262" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D262" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E262" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F262" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="G262" t="n">
+        <v>1</v>
+      </c>
+      <c r="H262" t="n">
         <v>2</v>
       </c>
-      <c r="H262" t="n">
-        <v>4</v>
-      </c>
       <c r="I262" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J262" t="n">
         <v>0</v>
       </c>
       <c r="K262" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L262" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M262" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" s="1" t="inlineStr">
         <is>
-          <t>設備安裝服務</t>
+          <t>設備管理軟體</t>
         </is>
       </c>
       <c r="B263" t="inlineStr"/>
@@ -11254,19 +11256,19 @@
         <v>0</v>
       </c>
       <c r="E263" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F263" t="n">
         <v>1</v>
       </c>
       <c r="G263" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H263" t="n">
         <v>1</v>
       </c>
       <c r="I263" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J263" t="n">
         <v>0</v>
@@ -11284,7 +11286,7 @@
     <row r="264">
       <c r="A264" s="1" t="inlineStr">
         <is>
-          <t>設備管理軟體</t>
+          <t>設備維護</t>
         </is>
       </c>
       <c r="B264" t="inlineStr"/>
@@ -11298,19 +11300,19 @@
         <v>0</v>
       </c>
       <c r="F264" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G264" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H264" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I264" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J264" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K264" t="n">
         <v>0</v>
@@ -11325,10 +11327,12 @@
     <row r="265">
       <c r="A265" s="1" t="inlineStr">
         <is>
-          <t>設備維護</t>
-        </is>
-      </c>
-      <c r="B265" t="inlineStr"/>
+          <t>證券業</t>
+        </is>
+      </c>
+      <c r="B265" t="n">
+        <v>0</v>
+      </c>
       <c r="C265" t="n">
         <v>0</v>
       </c>
@@ -11366,12 +11370,10 @@
     <row r="266">
       <c r="A266" s="1" t="inlineStr">
         <is>
-          <t>證券業</t>
-        </is>
-      </c>
-      <c r="B266" t="n">
-        <v>0</v>
-      </c>
+          <t>變壓器</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr"/>
       <c r="C266" t="n">
         <v>0</v>
       </c>
@@ -11400,7 +11402,7 @@
         <v>0</v>
       </c>
       <c r="L266" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M266" t="n">
         <v>0</v>
@@ -11409,10 +11411,12 @@
     <row r="267">
       <c r="A267" s="1" t="inlineStr">
         <is>
-          <t>變壓器</t>
-        </is>
-      </c>
-      <c r="B267" t="inlineStr"/>
+          <t>貨櫃航運</t>
+        </is>
+      </c>
+      <c r="B267" t="n">
+        <v>0</v>
+      </c>
       <c r="C267" t="n">
         <v>0</v>
       </c>
@@ -11444,16 +11448,18 @@
         <v>0</v>
       </c>
       <c r="M267" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" s="1" t="inlineStr">
         <is>
-          <t>貨櫃航運</t>
-        </is>
-      </c>
-      <c r="B268" t="inlineStr"/>
+          <t>貨櫃運輸集散及倉儲</t>
+        </is>
+      </c>
+      <c r="B268" t="n">
+        <v>0</v>
+      </c>
       <c r="C268" t="n">
         <v>0</v>
       </c>
@@ -11491,12 +11497,12 @@
     <row r="269">
       <c r="A269" s="1" t="inlineStr">
         <is>
-          <t>貨櫃運輸集散及倉儲</t>
+          <t>貿易商、代理商、經銷商</t>
         </is>
       </c>
       <c r="B269" t="inlineStr"/>
       <c r="C269" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D269" t="n">
         <v>0</v>
@@ -11514,7 +11520,7 @@
         <v>0</v>
       </c>
       <c r="I269" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J269" t="n">
         <v>0</v>
@@ -11526,13 +11532,13 @@
         <v>0</v>
       </c>
       <c r="M269" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" s="1" t="inlineStr">
         <is>
-          <t>貿易商、代理商、經銷商</t>
+          <t>資安審計</t>
         </is>
       </c>
       <c r="B270" t="inlineStr"/>
@@ -11540,7 +11546,7 @@
         <v>0</v>
       </c>
       <c r="D270" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E270" t="n">
         <v>0</v>
@@ -11558,7 +11564,7 @@
         <v>0</v>
       </c>
       <c r="J270" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K270" t="n">
         <v>0</v>
@@ -11573,7 +11579,7 @@
     <row r="271">
       <c r="A271" s="1" t="inlineStr">
         <is>
-          <t>資安審計</t>
+          <t>資安治理</t>
         </is>
       </c>
       <c r="B271" t="inlineStr"/>
@@ -11590,16 +11596,16 @@
         <v>0</v>
       </c>
       <c r="G271" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H271" t="n">
         <v>0</v>
       </c>
       <c r="I271" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J271" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K271" t="n">
         <v>0</v>
@@ -11614,7 +11620,7 @@
     <row r="272">
       <c r="A272" s="1" t="inlineStr">
         <is>
-          <t>資安治理</t>
+          <t>資安營運管理服務</t>
         </is>
       </c>
       <c r="B272" t="inlineStr"/>
@@ -11628,22 +11634,22 @@
         <v>0</v>
       </c>
       <c r="F272" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G272" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H272" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I272" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J272" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K272" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L272" t="n">
         <v>0</v>
@@ -11655,7 +11661,7 @@
     <row r="273">
       <c r="A273" s="1" t="inlineStr">
         <is>
-          <t>資安營運管理服務</t>
+          <t>資安防護能力分析與鑑識服務</t>
         </is>
       </c>
       <c r="B273" t="inlineStr"/>
@@ -11669,16 +11675,16 @@
         <v>0</v>
       </c>
       <c r="F273" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G273" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H273" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I273" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J273" t="n">
         <v>1</v>
@@ -11696,7 +11702,7 @@
     <row r="274">
       <c r="A274" s="1" t="inlineStr">
         <is>
-          <t>資安防護能力分析與鑑識服務</t>
+          <t>資安防護軟體</t>
         </is>
       </c>
       <c r="B274" t="inlineStr"/>
@@ -11707,25 +11713,25 @@
         <v>0</v>
       </c>
       <c r="E274" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F274" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G274" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H274" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I274" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J274" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K274" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L274" t="n">
         <v>0</v>
@@ -11737,7 +11743,7 @@
     <row r="275">
       <c r="A275" s="1" t="inlineStr">
         <is>
-          <t>資安防護軟體</t>
+          <t>資安顧問服務</t>
         </is>
       </c>
       <c r="B275" t="inlineStr"/>
@@ -11754,10 +11760,10 @@
         <v>1</v>
       </c>
       <c r="G275" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H275" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I275" t="n">
         <v>1</v>
@@ -11778,7 +11784,7 @@
     <row r="276">
       <c r="A276" s="1" t="inlineStr">
         <is>
-          <t>資安顧問服務</t>
+          <t>資料分析處理服務</t>
         </is>
       </c>
       <c r="B276" t="inlineStr"/>
@@ -11795,19 +11801,19 @@
         <v>0</v>
       </c>
       <c r="G276" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H276" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I276" t="n">
         <v>0</v>
       </c>
       <c r="J276" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K276" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L276" t="n">
         <v>0</v>
@@ -11819,7 +11825,7 @@
     <row r="277">
       <c r="A277" s="1" t="inlineStr">
         <is>
-          <t>資料分析處理服務</t>
+          <t>資料安全</t>
         </is>
       </c>
       <c r="B277" t="inlineStr"/>
@@ -11827,22 +11833,22 @@
         <v>0</v>
       </c>
       <c r="D277" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E277" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F277" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G277" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H277" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I277" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J277" t="n">
         <v>0</v>
@@ -11860,7 +11866,7 @@
     <row r="278">
       <c r="A278" s="1" t="inlineStr">
         <is>
-          <t>資料安全</t>
+          <t>資料庫</t>
         </is>
       </c>
       <c r="B278" t="inlineStr"/>
@@ -11871,10 +11877,10 @@
         <v>0</v>
       </c>
       <c r="E278" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F278" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G278" t="n">
         <v>1</v>
@@ -11883,10 +11889,10 @@
         <v>1</v>
       </c>
       <c r="I278" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J278" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K278" t="n">
         <v>0</v>
@@ -11901,7 +11907,7 @@
     <row r="279">
       <c r="A279" s="1" t="inlineStr">
         <is>
-          <t>資料庫</t>
+          <t>資料聚合</t>
         </is>
       </c>
       <c r="B279" t="inlineStr"/>
@@ -11915,16 +11921,16 @@
         <v>0</v>
       </c>
       <c r="F279" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G279" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H279" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I279" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J279" t="n">
         <v>0</v>
@@ -11942,7 +11948,7 @@
     <row r="280">
       <c r="A280" s="1" t="inlineStr">
         <is>
-          <t>資料聚合</t>
+          <t>資料處理</t>
         </is>
       </c>
       <c r="B280" t="inlineStr"/>
@@ -11956,19 +11962,19 @@
         <v>0</v>
       </c>
       <c r="F280" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G280" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H280" t="n">
         <v>0</v>
       </c>
       <c r="I280" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J280" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K280" t="n">
         <v>0</v>
@@ -11983,10 +11989,12 @@
     <row r="281">
       <c r="A281" s="1" t="inlineStr">
         <is>
-          <t>資料處理</t>
-        </is>
-      </c>
-      <c r="B281" t="inlineStr"/>
+          <t>資料處理服務</t>
+        </is>
+      </c>
+      <c r="B281" t="n">
+        <v>0</v>
+      </c>
       <c r="C281" t="n">
         <v>0</v>
       </c>
@@ -12000,19 +12008,19 @@
         <v>0</v>
       </c>
       <c r="G281" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H281" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I281" t="n">
         <v>0</v>
       </c>
       <c r="J281" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K281" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L281" t="n">
         <v>0</v>
@@ -12024,7 +12032,7 @@
     <row r="282">
       <c r="A282" s="1" t="inlineStr">
         <is>
-          <t>資料處理服務</t>
+          <t>資服</t>
         </is>
       </c>
       <c r="B282" t="inlineStr"/>
@@ -12065,7 +12073,7 @@
     <row r="283">
       <c r="A283" s="1" t="inlineStr">
         <is>
-          <t>資服</t>
+          <t>資訊收集設備</t>
         </is>
       </c>
       <c r="B283" t="inlineStr"/>
@@ -12106,7 +12114,7 @@
     <row r="284">
       <c r="A284" s="1" t="inlineStr">
         <is>
-          <t>資訊收集設備</t>
+          <t>資訊系統建置服務</t>
         </is>
       </c>
       <c r="B284" t="inlineStr"/>
@@ -12147,7 +12155,7 @@
     <row r="285">
       <c r="A285" s="1" t="inlineStr">
         <is>
-          <t>資訊系統建置服務</t>
+          <t>資訊聚合</t>
         </is>
       </c>
       <c r="B285" t="inlineStr"/>
@@ -12188,7 +12196,7 @@
     <row r="286">
       <c r="A286" s="1" t="inlineStr">
         <is>
-          <t>資訊聚合</t>
+          <t>身分認證與訪問管理</t>
         </is>
       </c>
       <c r="B286" t="inlineStr"/>
@@ -12196,22 +12204,22 @@
         <v>0</v>
       </c>
       <c r="D286" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E286" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F286" t="n">
         <v>0</v>
       </c>
       <c r="G286" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H286" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I286" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J286" t="n">
         <v>0</v>
@@ -12229,33 +12237,33 @@
     <row r="287">
       <c r="A287" s="1" t="inlineStr">
         <is>
-          <t>身分認證與訪問管理</t>
+          <t>車燈</t>
         </is>
       </c>
       <c r="B287" t="inlineStr"/>
       <c r="C287" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D287" t="n">
         <v>0</v>
       </c>
       <c r="E287" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F287" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G287" t="n">
         <v>0</v>
       </c>
       <c r="H287" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I287" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J287" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K287" t="n">
         <v>0</v>
@@ -12270,12 +12278,12 @@
     <row r="288">
       <c r="A288" s="1" t="inlineStr">
         <is>
-          <t>車燈</t>
+          <t>車用機械傳動設備及零配件</t>
         </is>
       </c>
       <c r="B288" t="inlineStr"/>
       <c r="C288" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D288" t="n">
         <v>1</v>
@@ -12284,10 +12292,10 @@
         <v>0</v>
       </c>
       <c r="F288" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G288" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H288" t="n">
         <v>0</v>
@@ -12305,30 +12313,30 @@
         <v>0</v>
       </c>
       <c r="M288" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" s="1" t="inlineStr">
         <is>
-          <t>車用機械傳動設備及零配件</t>
+          <t>軟性電路板</t>
         </is>
       </c>
       <c r="B289" t="inlineStr"/>
       <c r="C289" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D289" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E289" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F289" t="n">
         <v>0</v>
       </c>
       <c r="G289" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H289" t="n">
         <v>0</v>
@@ -12352,7 +12360,7 @@
     <row r="290">
       <c r="A290" s="1" t="inlineStr">
         <is>
-          <t>軟性電路板</t>
+          <t>軟體開發</t>
         </is>
       </c>
       <c r="B290" t="inlineStr"/>
@@ -12393,7 +12401,7 @@
     <row r="291">
       <c r="A291" s="1" t="inlineStr">
         <is>
-          <t>軟體開發</t>
+          <t>軟體開發工具</t>
         </is>
       </c>
       <c r="B291" t="inlineStr"/>
@@ -12410,7 +12418,7 @@
         <v>0</v>
       </c>
       <c r="G291" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H291" t="n">
         <v>0</v>
@@ -12434,7 +12442,7 @@
     <row r="292">
       <c r="A292" s="1" t="inlineStr">
         <is>
-          <t>軟體開發工具</t>
+          <t>輪胎</t>
         </is>
       </c>
       <c r="B292" t="inlineStr"/>
@@ -12454,7 +12462,7 @@
         <v>0</v>
       </c>
       <c r="H292" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I292" t="n">
         <v>0</v>
@@ -12475,7 +12483,7 @@
     <row r="293">
       <c r="A293" s="1" t="inlineStr">
         <is>
-          <t>輪胎</t>
+          <t>輸出入模組/介面卡</t>
         </is>
       </c>
       <c r="B293" t="inlineStr"/>
@@ -12483,16 +12491,16 @@
         <v>0</v>
       </c>
       <c r="D293" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E293" t="n">
         <v>0</v>
       </c>
       <c r="F293" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G293" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H293" t="n">
         <v>0</v>
@@ -12516,7 +12524,7 @@
     <row r="294">
       <c r="A294" s="1" t="inlineStr">
         <is>
-          <t>輸出入模組/介面卡</t>
+          <t>輸送機械及零配件</t>
         </is>
       </c>
       <c r="B294" t="inlineStr"/>
@@ -12527,16 +12535,16 @@
         <v>0</v>
       </c>
       <c r="E294" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F294" t="n">
         <v>0</v>
       </c>
       <c r="G294" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H294" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I294" t="n">
         <v>0</v>
@@ -12551,13 +12559,13 @@
         <v>0</v>
       </c>
       <c r="M294" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" s="1" t="inlineStr">
         <is>
-          <t>輸送機械及零配件</t>
+          <t>農業科技業</t>
         </is>
       </c>
       <c r="B295" t="inlineStr"/>
@@ -12577,7 +12585,7 @@
         <v>0</v>
       </c>
       <c r="H295" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I295" t="n">
         <v>0</v>
@@ -12598,7 +12606,7 @@
     <row r="296">
       <c r="A296" s="1" t="inlineStr">
         <is>
-          <t>農業科技業</t>
+          <t>農藥</t>
         </is>
       </c>
       <c r="B296" t="inlineStr"/>
@@ -12621,7 +12629,7 @@
         <v>0</v>
       </c>
       <c r="I296" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J296" t="n">
         <v>0</v>
@@ -12639,7 +12647,7 @@
     <row r="297">
       <c r="A297" s="1" t="inlineStr">
         <is>
-          <t>農藥</t>
+          <t>近眼顯示(Dear-Eye Display)</t>
         </is>
       </c>
       <c r="B297" t="inlineStr"/>
@@ -12680,7 +12688,7 @@
     <row r="298">
       <c r="A298" s="1" t="inlineStr">
         <is>
-          <t>近眼顯示(Dear-Eye Display)</t>
+          <t>通訊</t>
         </is>
       </c>
       <c r="B298" t="inlineStr"/>
@@ -12721,7 +12729,7 @@
     <row r="299">
       <c r="A299" s="1" t="inlineStr">
         <is>
-          <t>通訊</t>
+          <t>通訊服務</t>
         </is>
       </c>
       <c r="B299" t="inlineStr"/>
@@ -12762,10 +12770,12 @@
     <row r="300">
       <c r="A300" s="1" t="inlineStr">
         <is>
-          <t>通訊服務</t>
-        </is>
-      </c>
-      <c r="B300" t="inlineStr"/>
+          <t>通路經銷</t>
+        </is>
+      </c>
+      <c r="B300" t="n">
+        <v>0</v>
+      </c>
       <c r="C300" t="n">
         <v>0</v>
       </c>
@@ -12776,16 +12786,16 @@
         <v>0</v>
       </c>
       <c r="F300" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G300" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H300" t="n">
         <v>0</v>
       </c>
       <c r="I300" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J300" t="n">
         <v>0</v>
@@ -12803,18 +12813,20 @@
     <row r="301">
       <c r="A301" s="1" t="inlineStr">
         <is>
-          <t>通路經銷</t>
-        </is>
-      </c>
-      <c r="B301" t="inlineStr"/>
+          <t>連接器設計、組裝及製造</t>
+        </is>
+      </c>
+      <c r="B301" t="n">
+        <v>0</v>
+      </c>
       <c r="C301" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D301" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E301" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F301" t="n">
         <v>0</v>
@@ -12823,13 +12835,13 @@
         <v>1</v>
       </c>
       <c r="H301" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I301" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J301" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K301" t="n">
         <v>0</v>
@@ -12838,13 +12850,13 @@
         <v>0</v>
       </c>
       <c r="M301" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" s="1" t="inlineStr">
         <is>
-          <t>連接器設計、組裝及製造</t>
+          <t>連接線</t>
         </is>
       </c>
       <c r="B302" t="inlineStr"/>
@@ -12852,40 +12864,40 @@
         <v>0</v>
       </c>
       <c r="D302" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E302" t="n">
         <v>1</v>
       </c>
       <c r="F302" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G302" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H302" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I302" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J302" t="n">
         <v>1</v>
       </c>
       <c r="K302" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L302" t="n">
         <v>0</v>
       </c>
       <c r="M302" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" s="1" t="inlineStr">
         <is>
-          <t>連接線</t>
+          <t>運動服務/顧問</t>
         </is>
       </c>
       <c r="B303" t="inlineStr"/>
@@ -12899,22 +12911,22 @@
         <v>0</v>
       </c>
       <c r="F303" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G303" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H303" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I303" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J303" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K303" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L303" t="n">
         <v>0</v>
@@ -12926,7 +12938,7 @@
     <row r="304">
       <c r="A304" s="1" t="inlineStr">
         <is>
-          <t>運動服務/顧問</t>
+          <t>運動用品</t>
         </is>
       </c>
       <c r="B304" t="inlineStr"/>
@@ -12967,7 +12979,7 @@
     <row r="305">
       <c r="A305" s="1" t="inlineStr">
         <is>
-          <t>運動用品</t>
+          <t>運動行銷/媒體</t>
         </is>
       </c>
       <c r="B305" t="inlineStr"/>
@@ -13008,7 +13020,7 @@
     <row r="306">
       <c r="A306" s="1" t="inlineStr">
         <is>
-          <t>運動行銷/媒體</t>
+          <t>運算元件與設備</t>
         </is>
       </c>
       <c r="B306" t="inlineStr"/>
@@ -13019,16 +13031,16 @@
         <v>0</v>
       </c>
       <c r="E306" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F306" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G306" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H306" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I306" t="n">
         <v>0</v>
@@ -13043,13 +13055,13 @@
         <v>0</v>
       </c>
       <c r="M306" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" s="1" t="inlineStr">
         <is>
-          <t>運算元件與設備</t>
+          <t>運算設備</t>
         </is>
       </c>
       <c r="B307" t="inlineStr"/>
@@ -13066,13 +13078,13 @@
         <v>1</v>
       </c>
       <c r="G307" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H307" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I307" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J307" t="n">
         <v>0</v>
@@ -13084,18 +13096,16 @@
         <v>0</v>
       </c>
       <c r="M307" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" s="1" t="inlineStr">
         <is>
-          <t>運算設備</t>
-        </is>
-      </c>
-      <c r="B308" t="n">
-        <v>0</v>
-      </c>
+          <t>運輸工具</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr"/>
       <c r="C308" t="n">
         <v>0</v>
       </c>
@@ -13109,7 +13119,7 @@
         <v>0</v>
       </c>
       <c r="G308" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H308" t="n">
         <v>0</v>
@@ -13133,7 +13143,7 @@
     <row r="309">
       <c r="A309" s="1" t="inlineStr">
         <is>
-          <t>運輸工具</t>
+          <t>配電管理設施</t>
         </is>
       </c>
       <c r="B309" t="inlineStr"/>
@@ -13153,7 +13163,7 @@
         <v>0</v>
       </c>
       <c r="H309" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I309" t="n">
         <v>0</v>
@@ -13165,16 +13175,16 @@
         <v>0</v>
       </c>
       <c r="L309" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M309" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" s="1" t="inlineStr">
         <is>
-          <t>配電管理設施</t>
+          <t>配電系統</t>
         </is>
       </c>
       <c r="B310" t="inlineStr"/>
@@ -13197,7 +13207,7 @@
         <v>0</v>
       </c>
       <c r="I310" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J310" t="n">
         <v>0</v>
@@ -13206,16 +13216,16 @@
         <v>0</v>
       </c>
       <c r="L310" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M310" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" s="1" t="inlineStr">
         <is>
-          <t>配電系統</t>
+          <t>酚醛樹脂</t>
         </is>
       </c>
       <c r="B311" t="inlineStr"/>
@@ -13232,10 +13242,10 @@
         <v>0</v>
       </c>
       <c r="G311" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H311" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I311" t="n">
         <v>0</v>
@@ -13250,36 +13260,38 @@
         <v>0</v>
       </c>
       <c r="M311" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" s="1" t="inlineStr">
         <is>
-          <t>酚醛樹脂</t>
-        </is>
-      </c>
-      <c r="B312" t="inlineStr"/>
+          <t>醫療器材代理銷售及通路</t>
+        </is>
+      </c>
+      <c r="B312" t="n">
+        <v>0</v>
+      </c>
       <c r="C312" t="n">
         <v>0</v>
       </c>
       <c r="D312" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E312" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F312" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G312" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H312" t="n">
         <v>1</v>
       </c>
       <c r="I312" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J312" t="n">
         <v>0</v>
@@ -13291,39 +13303,41 @@
         <v>0</v>
       </c>
       <c r="M312" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" s="1" t="inlineStr">
         <is>
-          <t>醫療器材代理銷售及通路</t>
-        </is>
-      </c>
-      <c r="B313" t="inlineStr"/>
+          <t>醫療器材研發、設計、製造</t>
+        </is>
+      </c>
+      <c r="B313" t="n">
+        <v>0</v>
+      </c>
       <c r="C313" t="n">
         <v>0</v>
       </c>
       <c r="D313" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E313" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F313" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G313" t="n">
         <v>1</v>
       </c>
       <c r="H313" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I313" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J313" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K313" t="n">
         <v>0</v>
@@ -13332,18 +13346,16 @@
         <v>0</v>
       </c>
       <c r="M313" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" s="1" t="inlineStr">
         <is>
-          <t>醫療器材研發、設計、製造</t>
-        </is>
-      </c>
-      <c r="B314" t="n">
-        <v>0</v>
-      </c>
+          <t>醫療院所</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr"/>
       <c r="C314" t="n">
         <v>0</v>
       </c>
@@ -13351,16 +13363,16 @@
         <v>0</v>
       </c>
       <c r="E314" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F314" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G314" t="n">
         <v>0</v>
       </c>
       <c r="H314" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I314" t="n">
         <v>0</v>
@@ -13369,7 +13381,7 @@
         <v>0</v>
       </c>
       <c r="K314" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L314" t="n">
         <v>0</v>
@@ -13381,7 +13393,7 @@
     <row r="315">
       <c r="A315" s="1" t="inlineStr">
         <is>
-          <t>醫療院所</t>
+          <t>金屬、塑膠模具</t>
         </is>
       </c>
       <c r="B315" t="inlineStr"/>
@@ -13389,22 +13401,22 @@
         <v>0</v>
       </c>
       <c r="D315" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E315" t="n">
         <v>0</v>
       </c>
       <c r="F315" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G315" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H315" t="n">
         <v>0</v>
       </c>
       <c r="I315" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J315" t="n">
         <v>0</v>
@@ -13422,33 +13434,35 @@
     <row r="316">
       <c r="A316" s="1" t="inlineStr">
         <is>
-          <t>金屬、塑膠模具</t>
-        </is>
-      </c>
-      <c r="B316" t="inlineStr"/>
+          <t>金屬加工用機械</t>
+        </is>
+      </c>
+      <c r="B316" t="n">
+        <v>0</v>
+      </c>
       <c r="C316" t="n">
         <v>0</v>
       </c>
       <c r="D316" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E316" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F316" t="n">
         <v>0</v>
       </c>
       <c r="G316" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H316" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I316" t="n">
         <v>0</v>
       </c>
       <c r="J316" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K316" t="n">
         <v>0</v>
@@ -13463,7 +13477,7 @@
     <row r="317">
       <c r="A317" s="1" t="inlineStr">
         <is>
-          <t>金屬加工用機械</t>
+          <t>金屬加工處理</t>
         </is>
       </c>
       <c r="B317" t="inlineStr"/>
@@ -13489,7 +13503,7 @@
         <v>0</v>
       </c>
       <c r="J317" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K317" t="n">
         <v>0</v>
@@ -13504,12 +13518,12 @@
     <row r="318">
       <c r="A318" s="1" t="inlineStr">
         <is>
-          <t>金屬加工處理</t>
+          <t>金屬材料</t>
         </is>
       </c>
       <c r="B318" t="inlineStr"/>
       <c r="C318" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D318" t="n">
         <v>0</v>
@@ -13518,7 +13532,7 @@
         <v>0</v>
       </c>
       <c r="F318" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G318" t="n">
         <v>0</v>
@@ -13533,7 +13547,7 @@
         <v>0</v>
       </c>
       <c r="K318" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L318" t="n">
         <v>0</v>
@@ -13545,7 +13559,7 @@
     <row r="319">
       <c r="A319" s="1" t="inlineStr">
         <is>
-          <t>金屬材料</t>
+          <t>金屬製品</t>
         </is>
       </c>
       <c r="B319" t="inlineStr"/>
@@ -13556,7 +13570,7 @@
         <v>0</v>
       </c>
       <c r="E319" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F319" t="n">
         <v>0</v>
@@ -13586,10 +13600,12 @@
     <row r="320">
       <c r="A320" s="1" t="inlineStr">
         <is>
-          <t>金屬製品</t>
-        </is>
-      </c>
-      <c r="B320" t="inlineStr"/>
+          <t>金控業/銀行業/保險業</t>
+        </is>
+      </c>
+      <c r="B320" t="n">
+        <v>0</v>
+      </c>
       <c r="C320" t="n">
         <v>0</v>
       </c>
@@ -13600,7 +13616,7 @@
         <v>0</v>
       </c>
       <c r="F320" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G320" t="n">
         <v>0</v>
@@ -13627,12 +13643,10 @@
     <row r="321">
       <c r="A321" s="1" t="inlineStr">
         <is>
-          <t>金控業/銀行業/保險業</t>
-        </is>
-      </c>
-      <c r="B321" t="n">
-        <v>0</v>
-      </c>
+          <t>金流串接處理服務</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr"/>
       <c r="C321" t="n">
         <v>0</v>
       </c>
@@ -13670,7 +13684,7 @@
     <row r="322">
       <c r="A322" s="1" t="inlineStr">
         <is>
-          <t>金流串接處理服務</t>
+          <t>金融提款機(ATM)</t>
         </is>
       </c>
       <c r="B322" t="inlineStr"/>
@@ -13711,7 +13725,7 @@
     <row r="323">
       <c r="A323" s="1" t="inlineStr">
         <is>
-          <t>金融提款機(ATM)</t>
+          <t>鈑金</t>
         </is>
       </c>
       <c r="B323" t="inlineStr"/>
@@ -13752,12 +13766,12 @@
     <row r="324">
       <c r="A324" s="1" t="inlineStr">
         <is>
-          <t>鈑金</t>
+          <t>銅箔</t>
         </is>
       </c>
       <c r="B324" t="inlineStr"/>
       <c r="C324" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D324" t="n">
         <v>0</v>
@@ -13766,13 +13780,13 @@
         <v>0</v>
       </c>
       <c r="F324" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G324" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H324" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I324" t="n">
         <v>0</v>
@@ -13787,21 +13801,21 @@
         <v>0</v>
       </c>
       <c r="M324" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" s="1" t="inlineStr">
         <is>
-          <t>銅箔</t>
+          <t>銅箔基板</t>
         </is>
       </c>
       <c r="B325" t="inlineStr"/>
       <c r="C325" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D325" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E325" t="n">
         <v>0</v>
@@ -13810,13 +13824,13 @@
         <v>0</v>
       </c>
       <c r="G325" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H325" t="n">
         <v>1</v>
       </c>
       <c r="I325" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J325" t="n">
         <v>0</v>
@@ -13828,13 +13842,13 @@
         <v>0</v>
       </c>
       <c r="M325" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" s="1" t="inlineStr">
         <is>
-          <t>銅箔基板</t>
+          <t>銷售、進出口業務</t>
         </is>
       </c>
       <c r="B326" t="inlineStr"/>
@@ -13854,7 +13868,7 @@
         <v>0</v>
       </c>
       <c r="H326" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I326" t="n">
         <v>1</v>
@@ -13875,7 +13889,7 @@
     <row r="327">
       <c r="A327" s="1" t="inlineStr">
         <is>
-          <t>銷售、進出口業務</t>
+          <t>鋁合金鋼圈</t>
         </is>
       </c>
       <c r="B327" t="inlineStr"/>
@@ -13883,7 +13897,7 @@
         <v>0</v>
       </c>
       <c r="D327" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E327" t="n">
         <v>0</v>
@@ -13901,7 +13915,7 @@
         <v>0</v>
       </c>
       <c r="J327" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K327" t="n">
         <v>0</v>
@@ -13916,7 +13930,7 @@
     <row r="328">
       <c r="A328" s="1" t="inlineStr">
         <is>
-          <t>鋁合金鋼圈</t>
+          <t>鋰電池材料</t>
         </is>
       </c>
       <c r="B328" t="inlineStr"/>
@@ -13939,25 +13953,25 @@
         <v>0</v>
       </c>
       <c r="I328" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J328" t="n">
         <v>0</v>
       </c>
       <c r="K328" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L328" t="n">
         <v>0</v>
       </c>
       <c r="M328" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="329">
       <c r="A329" s="1" t="inlineStr">
         <is>
-          <t>鋰電池材料</t>
+          <t>鋼材</t>
         </is>
       </c>
       <c r="B329" t="inlineStr"/>
@@ -13980,16 +13994,16 @@
         <v>0</v>
       </c>
       <c r="I329" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J329" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K329" t="n">
         <v>0</v>
       </c>
       <c r="L329" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M329" t="n">
         <v>0</v>
@@ -13998,7 +14012,7 @@
     <row r="330">
       <c r="A330" s="1" t="inlineStr">
         <is>
-          <t>鋼材</t>
+          <t>鋼筋</t>
         </is>
       </c>
       <c r="B330" t="inlineStr"/>
@@ -14039,10 +14053,12 @@
     <row r="331">
       <c r="A331" s="1" t="inlineStr">
         <is>
-          <t>鋼筋</t>
-        </is>
-      </c>
-      <c r="B331" t="inlineStr"/>
+          <t>鋼線鋼纜</t>
+        </is>
+      </c>
+      <c r="B331" t="n">
+        <v>0</v>
+      </c>
       <c r="C331" t="n">
         <v>0</v>
       </c>
@@ -14080,7 +14096,7 @@
     <row r="332">
       <c r="A332" s="1" t="inlineStr">
         <is>
-          <t>鋼線鋼纜</t>
+          <t>鋼胚</t>
         </is>
       </c>
       <c r="B332" t="inlineStr"/>
@@ -14103,7 +14119,7 @@
         <v>0</v>
       </c>
       <c r="I332" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J332" t="n">
         <v>0</v>
@@ -14121,7 +14137,7 @@
     <row r="333">
       <c r="A333" s="1" t="inlineStr">
         <is>
-          <t>鋼胚</t>
+          <t>鋼鑄鐵元件</t>
         </is>
       </c>
       <c r="B333" t="inlineStr"/>
@@ -14147,7 +14163,7 @@
         <v>0</v>
       </c>
       <c r="J333" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K333" t="n">
         <v>0</v>
@@ -14162,7 +14178,7 @@
     <row r="334">
       <c r="A334" s="1" t="inlineStr">
         <is>
-          <t>鋼鑄鐵元件</t>
+          <t>錢包/資產管理</t>
         </is>
       </c>
       <c r="B334" t="inlineStr"/>
@@ -14191,7 +14207,7 @@
         <v>0</v>
       </c>
       <c r="K334" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L334" t="n">
         <v>0</v>
@@ -14203,7 +14219,7 @@
     <row r="335">
       <c r="A335" s="1" t="inlineStr">
         <is>
-          <t>錢包/資產管理</t>
+          <t>開發工具</t>
         </is>
       </c>
       <c r="B335" t="inlineStr"/>
@@ -14220,7 +14236,7 @@
         <v>0</v>
       </c>
       <c r="G335" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H335" t="n">
         <v>0</v>
@@ -14244,27 +14260,27 @@
     <row r="336">
       <c r="A336" s="1" t="inlineStr">
         <is>
-          <t>開發工具</t>
+          <t>隨身碟、記憶卡讀卡機</t>
         </is>
       </c>
       <c r="B336" t="inlineStr"/>
       <c r="C336" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D336" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E336" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F336" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G336" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H336" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I336" t="n">
         <v>0</v>
@@ -14285,30 +14301,30 @@
     <row r="337">
       <c r="A337" s="1" t="inlineStr">
         <is>
-          <t>隨身碟、記憶卡讀卡機</t>
+          <t>雲端作業系統</t>
         </is>
       </c>
       <c r="B337" t="inlineStr"/>
       <c r="C337" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D337" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E337" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F337" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G337" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H337" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I337" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J337" t="n">
         <v>0</v>
@@ -14326,7 +14342,7 @@
     <row r="338">
       <c r="A338" s="1" t="inlineStr">
         <is>
-          <t>雲端作業系統</t>
+          <t>雲端安全</t>
         </is>
       </c>
       <c r="B338" t="inlineStr"/>
@@ -14334,16 +14350,16 @@
         <v>0</v>
       </c>
       <c r="D338" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E338" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F338" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G338" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H338" t="n">
         <v>1</v>
@@ -14352,7 +14368,7 @@
         <v>1</v>
       </c>
       <c r="J338" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K338" t="n">
         <v>0</v>
@@ -14367,7 +14383,7 @@
     <row r="339">
       <c r="A339" s="1" t="inlineStr">
         <is>
-          <t>雲端安全</t>
+          <t>雲端平台</t>
         </is>
       </c>
       <c r="B339" t="inlineStr"/>
@@ -14381,22 +14397,22 @@
         <v>1</v>
       </c>
       <c r="F339" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G339" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H339" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I339" t="n">
         <v>1</v>
       </c>
       <c r="J339" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K339" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L339" t="n">
         <v>0</v>
@@ -14408,7 +14424,7 @@
     <row r="340">
       <c r="A340" s="1" t="inlineStr">
         <is>
-          <t>雲端平台</t>
+          <t>雲端應用服務</t>
         </is>
       </c>
       <c r="B340" t="inlineStr"/>
@@ -14419,22 +14435,22 @@
         <v>0</v>
       </c>
       <c r="E340" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F340" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G340" t="n">
         <v>2</v>
       </c>
       <c r="H340" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I340" t="n">
         <v>1</v>
       </c>
       <c r="J340" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K340" t="n">
         <v>0</v>
@@ -14443,18 +14459,20 @@
         <v>0</v>
       </c>
       <c r="M340" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="341">
       <c r="A341" s="1" t="inlineStr">
         <is>
-          <t>雲端應用服務</t>
-        </is>
-      </c>
-      <c r="B341" t="inlineStr"/>
+          <t>零售通路</t>
+        </is>
+      </c>
+      <c r="B341" t="n">
+        <v>0</v>
+      </c>
       <c r="C341" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D341" t="n">
         <v>0</v>
@@ -14463,34 +14481,34 @@
         <v>0</v>
       </c>
       <c r="F341" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G341" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H341" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I341" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J341" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K341" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L341" t="n">
         <v>0</v>
       </c>
       <c r="M341" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="342">
       <c r="A342" s="1" t="inlineStr">
         <is>
-          <t>零售通路</t>
+          <t>零組件/材料</t>
         </is>
       </c>
       <c r="B342" t="inlineStr"/>
@@ -14498,16 +14516,16 @@
         <v>0</v>
       </c>
       <c r="D342" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E342" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F342" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G342" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H342" t="n">
         <v>0</v>
@@ -14522,16 +14540,16 @@
         <v>0</v>
       </c>
       <c r="L342" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M342" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="343">
       <c r="A343" s="1" t="inlineStr">
         <is>
-          <t>零組件/材料</t>
+          <t>電信服務業</t>
         </is>
       </c>
       <c r="B343" t="inlineStr"/>
@@ -14545,13 +14563,13 @@
         <v>0</v>
       </c>
       <c r="F343" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G343" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H343" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I343" t="n">
         <v>0</v>
@@ -14572,7 +14590,7 @@
     <row r="344">
       <c r="A344" s="1" t="inlineStr">
         <is>
-          <t>電信服務業</t>
+          <t>電力系統</t>
         </is>
       </c>
       <c r="B344" t="inlineStr"/>
@@ -14595,7 +14613,7 @@
         <v>0</v>
       </c>
       <c r="I344" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J344" t="n">
         <v>0</v>
@@ -14604,16 +14622,16 @@
         <v>0</v>
       </c>
       <c r="L344" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M344" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="345">
       <c r="A345" s="1" t="inlineStr">
         <is>
-          <t>電力系統</t>
+          <t>電力設備</t>
         </is>
       </c>
       <c r="B345" t="inlineStr"/>
@@ -14633,7 +14651,7 @@
         <v>0</v>
       </c>
       <c r="H345" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I345" t="n">
         <v>0</v>
@@ -14645,7 +14663,7 @@
         <v>0</v>
       </c>
       <c r="L345" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M345" t="n">
         <v>1</v>
@@ -14654,12 +14672,12 @@
     <row r="346">
       <c r="A346" s="1" t="inlineStr">
         <is>
-          <t>電力設備</t>
+          <t>電力零售業</t>
         </is>
       </c>
       <c r="B346" t="inlineStr"/>
       <c r="C346" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D346" t="n">
         <v>0</v>
@@ -14677,7 +14695,7 @@
         <v>0</v>
       </c>
       <c r="I346" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J346" t="n">
         <v>0</v>
@@ -14689,13 +14707,13 @@
         <v>0</v>
       </c>
       <c r="M346" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="347">
       <c r="A347" s="1" t="inlineStr">
         <is>
-          <t>電力零售業</t>
+          <t>電動汽車、電動機車、電動自行車</t>
         </is>
       </c>
       <c r="B347" t="inlineStr"/>
@@ -14718,7 +14736,7 @@
         <v>0</v>
       </c>
       <c r="I347" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J347" t="n">
         <v>0</v>
@@ -14730,13 +14748,13 @@
         <v>0</v>
       </c>
       <c r="M347" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="348">
       <c r="A348" s="1" t="inlineStr">
         <is>
-          <t>電動汽車、電動機車、電動自行車</t>
+          <t>電子書</t>
         </is>
       </c>
       <c r="B348" t="inlineStr"/>
@@ -14762,7 +14780,7 @@
         <v>0</v>
       </c>
       <c r="J348" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K348" t="n">
         <v>0</v>
@@ -14771,13 +14789,13 @@
         <v>0</v>
       </c>
       <c r="M348" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="349">
       <c r="A349" s="1" t="inlineStr">
         <is>
-          <t>電子書</t>
+          <t>電子觸控白板</t>
         </is>
       </c>
       <c r="B349" t="inlineStr"/>
@@ -14818,7 +14836,7 @@
     <row r="350">
       <c r="A350" s="1" t="inlineStr">
         <is>
-          <t>電子觸控白板</t>
+          <t>電子零組件、塑膠零件、五金零件</t>
         </is>
       </c>
       <c r="B350" t="inlineStr"/>
@@ -14826,25 +14844,25 @@
         <v>0</v>
       </c>
       <c r="D350" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E350" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F350" t="n">
         <v>0</v>
       </c>
       <c r="G350" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H350" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I350" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J350" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K350" t="n">
         <v>0</v>
@@ -14853,13 +14871,13 @@
         <v>0</v>
       </c>
       <c r="M350" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="351">
       <c r="A351" s="1" t="inlineStr">
         <is>
-          <t>電子零組件、塑膠零件、五金零件</t>
+          <t>電容器</t>
         </is>
       </c>
       <c r="B351" t="inlineStr"/>
@@ -14870,37 +14888,37 @@
         <v>0</v>
       </c>
       <c r="E351" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F351" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G351" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H351" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="I351" t="n">
         <v>1</v>
       </c>
       <c r="J351" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K351" t="n">
         <v>1</v>
       </c>
       <c r="L351" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M351" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="352">
       <c r="A352" s="1" t="inlineStr">
         <is>
-          <t>電容器</t>
+          <t>電容器材料(如電蝕／化成鋁箔、介面瓷粉)</t>
         </is>
       </c>
       <c r="B352" t="inlineStr"/>
@@ -14908,25 +14926,25 @@
         <v>0</v>
       </c>
       <c r="D352" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E352" t="n">
         <v>0</v>
       </c>
       <c r="F352" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G352" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H352" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I352" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J352" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K352" t="n">
         <v>0</v>
@@ -14935,33 +14953,33 @@
         <v>1</v>
       </c>
       <c r="M352" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="353">
       <c r="A353" s="1" t="inlineStr">
         <is>
-          <t>電容器材料(如電蝕／化成鋁箔、介面瓷粉)</t>
+          <t>電感器</t>
         </is>
       </c>
       <c r="B353" t="inlineStr"/>
       <c r="C353" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D353" t="n">
         <v>0</v>
       </c>
       <c r="E353" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F353" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G353" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H353" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I353" t="n">
         <v>2</v>
@@ -14973,7 +14991,7 @@
         <v>0</v>
       </c>
       <c r="L353" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M353" t="n">
         <v>1</v>
@@ -14982,17 +15000,15 @@
     <row r="354">
       <c r="A354" s="1" t="inlineStr">
         <is>
-          <t>電感器</t>
-        </is>
-      </c>
-      <c r="B354" t="n">
-        <v>0</v>
-      </c>
+          <t>電感器材料(如鐵氧體、導電漿墨)</t>
+        </is>
+      </c>
+      <c r="B354" t="inlineStr"/>
       <c r="C354" t="n">
         <v>0</v>
       </c>
       <c r="D354" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E354" t="n">
         <v>0</v>
@@ -15001,16 +15017,16 @@
         <v>1</v>
       </c>
       <c r="G354" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H354" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I354" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J354" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K354" t="n">
         <v>0</v>
@@ -15019,18 +15035,20 @@
         <v>0</v>
       </c>
       <c r="M354" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="355">
       <c r="A355" s="1" t="inlineStr">
         <is>
-          <t>電感器材料(如鐵氧體、導電漿墨)</t>
-        </is>
-      </c>
-      <c r="B355" t="inlineStr"/>
+          <t>電控元件</t>
+        </is>
+      </c>
+      <c r="B355" t="n">
+        <v>0</v>
+      </c>
       <c r="C355" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D355" t="n">
         <v>0</v>
@@ -15042,39 +15060,39 @@
         <v>0</v>
       </c>
       <c r="G355" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H355" t="n">
+        <v>1</v>
+      </c>
+      <c r="I355" t="n">
+        <v>0</v>
+      </c>
+      <c r="J355" t="n">
+        <v>0</v>
+      </c>
+      <c r="K355" t="n">
+        <v>0</v>
+      </c>
+      <c r="L355" t="n">
+        <v>0</v>
+      </c>
+      <c r="M355" t="n">
         <v>2</v>
-      </c>
-      <c r="I355" t="n">
-        <v>1</v>
-      </c>
-      <c r="J355" t="n">
-        <v>1</v>
-      </c>
-      <c r="K355" t="n">
-        <v>0</v>
-      </c>
-      <c r="L355" t="n">
-        <v>0</v>
-      </c>
-      <c r="M355" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="356">
       <c r="A356" s="1" t="inlineStr">
         <is>
-          <t>電控元件</t>
+          <t>電池</t>
         </is>
       </c>
       <c r="B356" t="inlineStr"/>
       <c r="C356" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D356" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E356" t="n">
         <v>0</v>
@@ -15083,13 +15101,13 @@
         <v>1</v>
       </c>
       <c r="G356" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H356" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I356" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J356" t="n">
         <v>0</v>
@@ -15101,18 +15119,20 @@
         <v>0</v>
       </c>
       <c r="M356" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="357">
       <c r="A357" s="1" t="inlineStr">
         <is>
-          <t>電池</t>
-        </is>
-      </c>
-      <c r="B357" t="inlineStr"/>
+          <t>電池模組</t>
+        </is>
+      </c>
+      <c r="B357" t="n">
+        <v>0</v>
+      </c>
       <c r="C357" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D357" t="n">
         <v>0</v>
@@ -15124,10 +15144,10 @@
         <v>0</v>
       </c>
       <c r="G357" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H357" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I357" t="n">
         <v>0</v>
@@ -15136,24 +15156,24 @@
         <v>0</v>
       </c>
       <c r="K357" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L357" t="n">
         <v>0</v>
       </c>
       <c r="M357" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="358">
       <c r="A358" s="1" t="inlineStr">
         <is>
-          <t>電池模組</t>
+          <t>電池芯</t>
         </is>
       </c>
       <c r="B358" t="inlineStr"/>
       <c r="C358" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D358" t="n">
         <v>0</v>
@@ -15177,42 +15197,42 @@
         <v>0</v>
       </c>
       <c r="K358" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L358" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M358" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="359">
       <c r="A359" s="1" t="inlineStr">
         <is>
-          <t>電池芯</t>
+          <t>電源供應器</t>
         </is>
       </c>
       <c r="B359" t="inlineStr"/>
       <c r="C359" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D359" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E359" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F359" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G359" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H359" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I359" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J359" t="n">
         <v>0</v>
@@ -15224,13 +15244,13 @@
         <v>1</v>
       </c>
       <c r="M359" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="360">
       <c r="A360" s="1" t="inlineStr">
         <is>
-          <t>電源供應器</t>
+          <t>電網營造</t>
         </is>
       </c>
       <c r="B360" t="inlineStr"/>
@@ -15238,40 +15258,40 @@
         <v>0</v>
       </c>
       <c r="D360" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E360" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F360" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G360" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H360" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I360" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J360" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K360" t="n">
         <v>0</v>
       </c>
       <c r="L360" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M360" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="361">
       <c r="A361" s="1" t="inlineStr">
         <is>
-          <t>電網營造</t>
+          <t>電網維運</t>
         </is>
       </c>
       <c r="B361" t="inlineStr"/>
@@ -15306,13 +15326,13 @@
         <v>0</v>
       </c>
       <c r="M361" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="362">
       <c r="A362" s="1" t="inlineStr">
         <is>
-          <t>電網維運</t>
+          <t>電纜</t>
         </is>
       </c>
       <c r="B362" t="inlineStr"/>
@@ -15332,7 +15352,7 @@
         <v>0</v>
       </c>
       <c r="H362" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I362" t="n">
         <v>0</v>
@@ -15353,33 +15373,33 @@
     <row r="363">
       <c r="A363" s="1" t="inlineStr">
         <is>
-          <t>電纜</t>
+          <t>電腦視覺</t>
         </is>
       </c>
       <c r="B363" t="inlineStr"/>
       <c r="C363" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D363" t="n">
         <v>0</v>
       </c>
       <c r="E363" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F363" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G363" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H363" t="n">
         <v>0</v>
       </c>
       <c r="I363" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J363" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K363" t="n">
         <v>0</v>
@@ -15388,13 +15408,13 @@
         <v>0</v>
       </c>
       <c r="M363" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="364">
       <c r="A364" s="1" t="inlineStr">
         <is>
-          <t>電腦視覺</t>
+          <t>電腦設備</t>
         </is>
       </c>
       <c r="B364" t="inlineStr"/>
@@ -15405,16 +15425,16 @@
         <v>1</v>
       </c>
       <c r="E364" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F364" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G364" t="n">
         <v>1</v>
       </c>
       <c r="H364" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I364" t="n">
         <v>0</v>
@@ -15423,24 +15443,22 @@
         <v>0</v>
       </c>
       <c r="K364" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L364" t="n">
         <v>0</v>
       </c>
       <c r="M364" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="365">
       <c r="A365" s="1" t="inlineStr">
         <is>
-          <t>電腦設備</t>
-        </is>
-      </c>
-      <c r="B365" t="n">
-        <v>0</v>
-      </c>
+          <t>電視</t>
+        </is>
+      </c>
+      <c r="B365" t="inlineStr"/>
       <c r="C365" t="n">
         <v>0</v>
       </c>
@@ -15448,19 +15466,19 @@
         <v>0</v>
       </c>
       <c r="E365" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F365" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G365" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H365" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I365" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J365" t="n">
         <v>0</v>
@@ -15478,7 +15496,7 @@
     <row r="366">
       <c r="A366" s="1" t="inlineStr">
         <is>
-          <t>電視</t>
+          <t>電鍍材料</t>
         </is>
       </c>
       <c r="B366" t="inlineStr"/>
@@ -15519,7 +15537,7 @@
     <row r="367">
       <c r="A367" s="1" t="inlineStr">
         <is>
-          <t>電鍍材料</t>
+          <t>電阻器</t>
         </is>
       </c>
       <c r="B367" t="inlineStr"/>
@@ -15533,16 +15551,16 @@
         <v>0</v>
       </c>
       <c r="F367" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G367" t="n">
         <v>0</v>
       </c>
       <c r="H367" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I367" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J367" t="n">
         <v>0</v>
@@ -15551,16 +15569,16 @@
         <v>0</v>
       </c>
       <c r="L367" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M367" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="368">
       <c r="A368" s="1" t="inlineStr">
         <is>
-          <t>電阻器</t>
+          <t>電阻器材料(氧化鋁陶瓷基板、導電漿墨)</t>
         </is>
       </c>
       <c r="B368" t="inlineStr"/>
@@ -15574,19 +15592,19 @@
         <v>0</v>
       </c>
       <c r="F368" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G368" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H368" t="n">
         <v>0</v>
       </c>
       <c r="I368" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J368" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K368" t="n">
         <v>0</v>
@@ -15595,13 +15613,13 @@
         <v>0</v>
       </c>
       <c r="M368" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="369">
       <c r="A369" s="1" t="inlineStr">
         <is>
-          <t>電阻器材料(氧化鋁陶瓷基板、導電漿墨)</t>
+          <t>面板</t>
         </is>
       </c>
       <c r="B369" t="inlineStr"/>
@@ -15615,13 +15633,13 @@
         <v>0</v>
       </c>
       <c r="F369" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G369" t="n">
         <v>1</v>
       </c>
       <c r="H369" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I369" t="n">
         <v>0</v>
@@ -15636,13 +15654,13 @@
         <v>0</v>
       </c>
       <c r="M369" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="370">
       <c r="A370" s="1" t="inlineStr">
         <is>
-          <t>面板</t>
+          <t>預拌混凝土</t>
         </is>
       </c>
       <c r="B370" t="inlineStr"/>
@@ -15659,10 +15677,10 @@
         <v>0</v>
       </c>
       <c r="G370" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H370" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I370" t="n">
         <v>0</v>
@@ -15683,7 +15701,7 @@
     <row r="371">
       <c r="A371" s="1" t="inlineStr">
         <is>
-          <t>預拌混凝土</t>
+          <t>領域方案</t>
         </is>
       </c>
       <c r="B371" t="inlineStr"/>
@@ -15724,33 +15742,33 @@
     <row r="372">
       <c r="A372" s="1" t="inlineStr">
         <is>
-          <t>領域方案</t>
+          <t>領域解決方案</t>
         </is>
       </c>
       <c r="B372" t="inlineStr"/>
       <c r="C372" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D372" t="n">
         <v>0</v>
       </c>
       <c r="E372" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F372" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G372" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H372" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I372" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J372" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K372" t="n">
         <v>0</v>
@@ -15759,42 +15777,42 @@
         <v>0</v>
       </c>
       <c r="M372" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="373">
       <c r="A373" s="1" t="inlineStr">
         <is>
-          <t>領域解決方案</t>
+          <t>頭顯裝置品牌廠</t>
         </is>
       </c>
       <c r="B373" t="inlineStr"/>
       <c r="C373" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D373" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E373" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F373" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G373" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H373" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I373" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J373" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K373" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L373" t="n">
         <v>0</v>
@@ -15806,7 +15824,7 @@
     <row r="374">
       <c r="A374" s="1" t="inlineStr">
         <is>
-          <t>頭顯裝置品牌廠</t>
+          <t>顏染料</t>
         </is>
       </c>
       <c r="B374" t="inlineStr"/>
@@ -15814,16 +15832,16 @@
         <v>0</v>
       </c>
       <c r="D374" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E374" t="n">
         <v>0</v>
       </c>
       <c r="F374" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G374" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H374" t="n">
         <v>1</v>
@@ -15847,30 +15865,30 @@
     <row r="375">
       <c r="A375" s="1" t="inlineStr">
         <is>
-          <t>顏染料</t>
+          <t>顧問諮詢</t>
         </is>
       </c>
       <c r="B375" t="inlineStr"/>
       <c r="C375" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D375" t="n">
         <v>0</v>
       </c>
       <c r="E375" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F375" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G375" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H375" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I375" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J375" t="n">
         <v>0</v>
@@ -15879,16 +15897,16 @@
         <v>0</v>
       </c>
       <c r="L375" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M375" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="376">
       <c r="A376" s="1" t="inlineStr">
         <is>
-          <t>顧問諮詢</t>
+          <t>顯示卡</t>
         </is>
       </c>
       <c r="B376" t="inlineStr"/>
@@ -15896,25 +15914,25 @@
         <v>0</v>
       </c>
       <c r="D376" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E376" t="n">
         <v>0</v>
       </c>
       <c r="F376" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G376" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H376" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I376" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J376" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K376" t="n">
         <v>0</v>
@@ -15923,13 +15941,13 @@
         <v>0</v>
       </c>
       <c r="M376" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="377">
       <c r="A377" s="1" t="inlineStr">
         <is>
-          <t>顯示卡</t>
+          <t>顯示器模組</t>
         </is>
       </c>
       <c r="B377" t="inlineStr"/>
@@ -15943,13 +15961,13 @@
         <v>1</v>
       </c>
       <c r="F377" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G377" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H377" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I377" t="n">
         <v>0</v>
@@ -15970,7 +15988,7 @@
     <row r="378">
       <c r="A378" s="1" t="inlineStr">
         <is>
-          <t>顯示器模組</t>
+          <t>風場營造</t>
         </is>
       </c>
       <c r="B378" t="inlineStr"/>
@@ -15984,13 +16002,13 @@
         <v>0</v>
       </c>
       <c r="F378" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G378" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H378" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I378" t="n">
         <v>0</v>
@@ -16011,7 +16029,7 @@
     <row r="379">
       <c r="A379" s="1" t="inlineStr">
         <is>
-          <t>風場營造</t>
+          <t>風場規劃</t>
         </is>
       </c>
       <c r="B379" t="inlineStr"/>
@@ -16052,7 +16070,7 @@
     <row r="380">
       <c r="A380" s="1" t="inlineStr">
         <is>
-          <t>風場規劃</t>
+          <t>風場開發</t>
         </is>
       </c>
       <c r="B380" t="inlineStr"/>
@@ -16093,7 +16111,7 @@
     <row r="381">
       <c r="A381" s="1" t="inlineStr">
         <is>
-          <t>風場開發</t>
+          <t>風機維護</t>
         </is>
       </c>
       <c r="B381" t="inlineStr"/>
@@ -16134,12 +16152,12 @@
     <row r="382">
       <c r="A382" s="1" t="inlineStr">
         <is>
-          <t>風機維護</t>
+          <t>餐飲連鎖</t>
         </is>
       </c>
       <c r="B382" t="inlineStr"/>
       <c r="C382" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D382" t="n">
         <v>0</v>
@@ -16151,7 +16169,7 @@
         <v>0</v>
       </c>
       <c r="G382" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H382" t="n">
         <v>0</v>
@@ -16160,7 +16178,7 @@
         <v>0</v>
       </c>
       <c r="J382" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K382" t="n">
         <v>0</v>
@@ -16175,7 +16193,7 @@
     <row r="383">
       <c r="A383" s="1" t="inlineStr">
         <is>
-          <t>餐飲連鎖</t>
+          <t>驅動IC</t>
         </is>
       </c>
       <c r="B383" t="inlineStr"/>
@@ -16183,7 +16201,7 @@
         <v>0</v>
       </c>
       <c r="D383" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E383" t="n">
         <v>0</v>
@@ -16195,7 +16213,7 @@
         <v>0</v>
       </c>
       <c r="H383" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I383" t="n">
         <v>0</v>
@@ -16204,7 +16222,7 @@
         <v>0</v>
       </c>
       <c r="K383" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L383" t="n">
         <v>0</v>
@@ -16216,7 +16234,7 @@
     <row r="384">
       <c r="A384" s="1" t="inlineStr">
         <is>
-          <t>驅動IC</t>
+          <t>高/低壓輸電設施</t>
         </is>
       </c>
       <c r="B384" t="inlineStr"/>
@@ -16233,10 +16251,10 @@
         <v>0</v>
       </c>
       <c r="G384" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H384" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I384" t="n">
         <v>0</v>
@@ -16248,16 +16266,16 @@
         <v>0</v>
       </c>
       <c r="L384" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M384" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="385">
       <c r="A385" s="1" t="inlineStr">
         <is>
-          <t>高/低壓輸電設施</t>
+          <t>高壓AMI</t>
         </is>
       </c>
       <c r="B385" t="inlineStr"/>
@@ -16277,10 +16295,10 @@
         <v>0</v>
       </c>
       <c r="H385" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I385" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J385" t="n">
         <v>0</v>
@@ -16292,13 +16310,13 @@
         <v>0</v>
       </c>
       <c r="M385" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="386">
       <c r="A386" s="1" t="inlineStr">
         <is>
-          <t>高壓AMI</t>
+          <t>高爾夫球具業</t>
         </is>
       </c>
       <c r="B386" t="inlineStr"/>
@@ -16339,7 +16357,7 @@
     <row r="387">
       <c r="A387" s="1" t="inlineStr">
         <is>
-          <t>高爾夫球具業</t>
+          <t>齒輪箱</t>
         </is>
       </c>
       <c r="B387" t="inlineStr"/>
@@ -16374,47 +16392,6 @@
         <v>0</v>
       </c>
       <c r="M387" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="388">
-      <c r="A388" s="1" t="inlineStr">
-        <is>
-          <t>齒輪箱</t>
-        </is>
-      </c>
-      <c r="B388" t="inlineStr"/>
-      <c r="C388" t="n">
-        <v>0</v>
-      </c>
-      <c r="D388" t="n">
-        <v>0</v>
-      </c>
-      <c r="E388" t="n">
-        <v>0</v>
-      </c>
-      <c r="F388" t="n">
-        <v>0</v>
-      </c>
-      <c r="G388" t="n">
-        <v>0</v>
-      </c>
-      <c r="H388" t="n">
-        <v>0</v>
-      </c>
-      <c r="I388" t="n">
-        <v>0</v>
-      </c>
-      <c r="J388" t="n">
-        <v>0</v>
-      </c>
-      <c r="K388" t="n">
-        <v>0</v>
-      </c>
-      <c r="L388" t="n">
-        <v>0</v>
-      </c>
-      <c r="M388" t="n">
         <v>0</v>
       </c>
     </row>

--- a/Result/analyze_3.xlsx
+++ b/Result/analyze_3.xlsx
@@ -441,57 +441,57 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
     </row>
@@ -550,13 +550,13 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F3" t="n">
         <v>1</v>
       </c>
       <c r="G3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -665,39 +665,41 @@
           <t>IC/晶圓製造</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr"/>
+      <c r="B6" t="n">
+        <v>0</v>
+      </c>
       <c r="C6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" t="n">
         <v>3</v>
       </c>
-      <c r="D6" t="n">
-        <v>0</v>
-      </c>
       <c r="E6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I6" t="n">
         <v>3</v>
       </c>
-      <c r="F6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" t="n">
-        <v>1</v>
-      </c>
       <c r="J6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -708,37 +710,37 @@
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E7" t="n">
+        <v>2</v>
+      </c>
+      <c r="F7" t="n">
+        <v>5</v>
+      </c>
+      <c r="G7" t="n">
         <v>3</v>
       </c>
-      <c r="F7" t="n">
+      <c r="H7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
         <v>2</v>
       </c>
-      <c r="G7" t="n">
-        <v>5</v>
-      </c>
-      <c r="H7" t="n">
-        <v>3</v>
-      </c>
-      <c r="I7" t="n">
-        <v>1</v>
-      </c>
-      <c r="J7" t="n">
-        <v>1</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
       <c r="M7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -747,41 +749,39 @@
           <t>IC模組</t>
         </is>
       </c>
-      <c r="B8" t="n">
-        <v>0</v>
-      </c>
+      <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D8" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E8" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G8" t="n">
         <v>2</v>
       </c>
       <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
         <v>2</v>
       </c>
-      <c r="I8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
       <c r="M8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -794,37 +794,37 @@
         <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E9" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="F9" t="n">
         <v>3</v>
       </c>
       <c r="G9" t="n">
+        <v>2</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
         <v>3</v>
       </c>
-      <c r="H9" t="n">
-        <v>2</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" t="n">
-        <v>1</v>
-      </c>
-      <c r="K9" t="n">
-        <v>1</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
       <c r="M9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -835,37 +835,37 @@
       </c>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="n">
+        <v>1</v>
+      </c>
+      <c r="D10" t="n">
+        <v>4</v>
+      </c>
+      <c r="E10" t="n">
+        <v>3</v>
+      </c>
+      <c r="F10" t="n">
         <v>2</v>
       </c>
-      <c r="D10" t="n">
-        <v>1</v>
-      </c>
-      <c r="E10" t="n">
-        <v>4</v>
-      </c>
-      <c r="F10" t="n">
+      <c r="G10" t="n">
         <v>3</v>
       </c>
-      <c r="G10" t="n">
-        <v>1</v>
-      </c>
       <c r="H10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
         <v>3</v>
       </c>
-      <c r="I10" t="n">
-        <v>1</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
       <c r="M10" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -874,17 +874,15 @@
           <t>IP設計/IC設計代工服務</t>
         </is>
       </c>
-      <c r="B11" t="n">
-        <v>0</v>
-      </c>
+      <c r="B11" t="inlineStr"/>
       <c r="C11" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
@@ -896,19 +894,19 @@
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -925,16 +923,16 @@
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -972,10 +970,10 @@
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
@@ -1127,16 +1125,16 @@
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -1218,16 +1216,16 @@
         <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
@@ -1259,7 +1257,7 @@
         <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
@@ -1288,37 +1286,37 @@
       </c>
       <c r="B21" t="inlineStr"/>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D21" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F21" t="n">
         <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -1332,7 +1330,7 @@
         <v>0</v>
       </c>
       <c r="D22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E22" t="n">
         <v>1</v>
@@ -1341,7 +1339,7 @@
         <v>1</v>
       </c>
       <c r="G22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H22" t="n">
         <v>0</v>
@@ -1370,10 +1368,10 @@
       </c>
       <c r="B23" t="inlineStr"/>
       <c r="C23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -1385,10 +1383,10 @@
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -1397,10 +1395,10 @@
         <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -1420,13 +1418,13 @@
         <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G24" t="n">
         <v>1</v>
       </c>
       <c r="H24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I24" t="n">
         <v>0</v>
@@ -1438,10 +1436,10 @@
         <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M24" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -1450,9 +1448,11 @@
           <t>主機板</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr"/>
+      <c r="B25" t="n">
+        <v>0</v>
+      </c>
       <c r="C25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D25" t="n">
         <v>1</v>
@@ -1464,7 +1464,7 @@
         <v>1</v>
       </c>
       <c r="G25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H25" t="n">
         <v>0</v>
@@ -1534,13 +1534,13 @@
       </c>
       <c r="B27" t="inlineStr"/>
       <c r="C27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D27" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F27" t="n">
         <v>0</v>
@@ -1552,10 +1552,10 @@
         <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K27" t="n">
         <v>0</v>
@@ -1666,13 +1666,13 @@
         <v>0</v>
       </c>
       <c r="F30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H30" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I30" t="n">
         <v>0</v>
@@ -1701,19 +1701,19 @@
         <v>0</v>
       </c>
       <c r="D31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H31" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I31" t="n">
         <v>0</v>
@@ -1739,37 +1739,37 @@
       </c>
       <c r="B32" t="inlineStr"/>
       <c r="C32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D32" t="n">
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F32" t="n">
         <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K32" t="n">
         <v>0</v>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33">
@@ -1780,19 +1780,19 @@
       </c>
       <c r="B33" t="inlineStr"/>
       <c r="C33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E33" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F33" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H33" t="n">
         <v>0</v>
@@ -1862,13 +1862,13 @@
       </c>
       <c r="B35" t="inlineStr"/>
       <c r="C35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D35" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E35" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F35" t="n">
         <v>0</v>
@@ -1988,16 +1988,16 @@
         <v>0</v>
       </c>
       <c r="D38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E38" t="n">
         <v>0</v>
       </c>
       <c r="F38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H38" t="n">
         <v>0</v>
@@ -2114,10 +2114,10 @@
         <v>0</v>
       </c>
       <c r="E41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
@@ -2135,10 +2135,10 @@
         <v>0</v>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -2152,10 +2152,10 @@
         <v>0</v>
       </c>
       <c r="D42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E42" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F42" t="n">
         <v>1</v>
@@ -2164,7 +2164,7 @@
         <v>1</v>
       </c>
       <c r="H42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I42" t="n">
         <v>0</v>
@@ -2176,10 +2176,10 @@
         <v>0</v>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -2193,10 +2193,10 @@
         <v>0</v>
       </c>
       <c r="D43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F43" t="n">
         <v>0</v>
@@ -2231,13 +2231,13 @@
       </c>
       <c r="B44" t="inlineStr"/>
       <c r="C44" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D44" t="n">
         <v>0</v>
       </c>
       <c r="E44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F44" t="n">
         <v>1</v>
@@ -2246,7 +2246,7 @@
         <v>1</v>
       </c>
       <c r="H44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I44" t="n">
         <v>0</v>
@@ -2255,10 +2255,10 @@
         <v>0</v>
       </c>
       <c r="K44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
         <v>0</v>
@@ -2278,10 +2278,10 @@
         <v>0</v>
       </c>
       <c r="E45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
@@ -2319,13 +2319,13 @@
         <v>0</v>
       </c>
       <c r="E46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F46" t="n">
         <v>1</v>
       </c>
       <c r="G46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H46" t="n">
         <v>0</v>
@@ -2360,13 +2360,13 @@
         <v>0</v>
       </c>
       <c r="E47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F47" t="n">
         <v>1</v>
       </c>
       <c r="G47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H47" t="n">
         <v>0</v>
@@ -2434,41 +2434,39 @@
           <t>光通訊設備(如光纖電纜、光傳輸設備)</t>
         </is>
       </c>
-      <c r="B49" t="n">
-        <v>0</v>
-      </c>
+      <c r="B49" t="inlineStr"/>
       <c r="C49" t="n">
+        <v>1</v>
+      </c>
+      <c r="D49" t="n">
         <v>2</v>
       </c>
-      <c r="D49" t="n">
-        <v>0</v>
-      </c>
       <c r="E49" t="n">
+        <v>1</v>
+      </c>
+      <c r="F49" t="n">
         <v>2</v>
-      </c>
-      <c r="F49" t="n">
-        <v>1</v>
       </c>
       <c r="G49" t="n">
         <v>2</v>
       </c>
       <c r="H49" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I49" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J49" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L49" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M49" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="50">
@@ -2522,37 +2520,37 @@
         <v>0</v>
       </c>
       <c r="C51" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D51" t="n">
+        <v>1</v>
+      </c>
+      <c r="E51" t="n">
+        <v>2</v>
+      </c>
+      <c r="F51" t="n">
+        <v>0</v>
+      </c>
+      <c r="G51" t="n">
+        <v>6</v>
+      </c>
+      <c r="H51" t="n">
+        <v>1</v>
+      </c>
+      <c r="I51" t="n">
+        <v>1</v>
+      </c>
+      <c r="J51" t="n">
+        <v>1</v>
+      </c>
+      <c r="K51" t="n">
+        <v>1</v>
+      </c>
+      <c r="L51" t="n">
         <v>3</v>
       </c>
-      <c r="E51" t="n">
-        <v>0</v>
-      </c>
-      <c r="F51" t="n">
-        <v>2</v>
-      </c>
-      <c r="G51" t="n">
-        <v>0</v>
-      </c>
-      <c r="H51" t="n">
-        <v>6</v>
-      </c>
-      <c r="I51" t="n">
-        <v>1</v>
-      </c>
-      <c r="J51" t="n">
-        <v>1</v>
-      </c>
-      <c r="K51" t="n">
-        <v>1</v>
-      </c>
-      <c r="L51" t="n">
-        <v>1</v>
-      </c>
       <c r="M51" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="52">
@@ -2606,37 +2604,37 @@
         <v>0</v>
       </c>
       <c r="C53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D53" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E53" t="n">
+        <v>1</v>
+      </c>
+      <c r="F53" t="n">
+        <v>1</v>
+      </c>
+      <c r="G53" t="n">
+        <v>3</v>
+      </c>
+      <c r="H53" t="n">
         <v>2</v>
-      </c>
-      <c r="F53" t="n">
-        <v>1</v>
-      </c>
-      <c r="G53" t="n">
-        <v>1</v>
-      </c>
-      <c r="H53" t="n">
-        <v>3</v>
       </c>
       <c r="I53" t="n">
         <v>2</v>
       </c>
       <c r="J53" t="n">
+        <v>0</v>
+      </c>
+      <c r="K53" t="n">
+        <v>0</v>
+      </c>
+      <c r="L53" t="n">
         <v>2</v>
       </c>
-      <c r="K53" t="n">
-        <v>0</v>
-      </c>
-      <c r="L53" t="n">
-        <v>0</v>
-      </c>
       <c r="M53" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -2649,7 +2647,7 @@
         <v>0</v>
       </c>
       <c r="C54" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D54" t="n">
         <v>1</v>
@@ -2658,28 +2656,28 @@
         <v>1</v>
       </c>
       <c r="F54" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G54" t="n">
         <v>4</v>
       </c>
       <c r="H54" t="n">
+        <v>0</v>
+      </c>
+      <c r="I54" t="n">
+        <v>1</v>
+      </c>
+      <c r="J54" t="n">
+        <v>1</v>
+      </c>
+      <c r="K54" t="n">
+        <v>1</v>
+      </c>
+      <c r="L54" t="n">
         <v>4</v>
       </c>
-      <c r="I54" t="n">
-        <v>0</v>
-      </c>
-      <c r="J54" t="n">
-        <v>1</v>
-      </c>
-      <c r="K54" t="n">
-        <v>1</v>
-      </c>
-      <c r="L54" t="n">
-        <v>1</v>
-      </c>
       <c r="M54" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -2690,37 +2688,37 @@
       </c>
       <c r="B55" t="inlineStr"/>
       <c r="C55" t="n">
+        <v>4</v>
+      </c>
+      <c r="D55" t="n">
+        <v>1</v>
+      </c>
+      <c r="E55" t="n">
         <v>2</v>
       </c>
-      <c r="D55" t="n">
+      <c r="F55" t="n">
         <v>4</v>
       </c>
-      <c r="E55" t="n">
-        <v>1</v>
-      </c>
-      <c r="F55" t="n">
+      <c r="G55" t="n">
         <v>2</v>
       </c>
-      <c r="G55" t="n">
-        <v>4</v>
-      </c>
       <c r="H55" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
       </c>
       <c r="K55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L55" t="n">
         <v>1</v>
       </c>
       <c r="M55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="56">
@@ -2729,39 +2727,41 @@
           <t>其他電腦及週邊設備之零組件</t>
         </is>
       </c>
-      <c r="B56" t="inlineStr"/>
+      <c r="B56" t="n">
+        <v>0</v>
+      </c>
       <c r="C56" t="n">
+        <v>3</v>
+      </c>
+      <c r="D56" t="n">
+        <v>5</v>
+      </c>
+      <c r="E56" t="n">
+        <v>3</v>
+      </c>
+      <c r="F56" t="n">
+        <v>2</v>
+      </c>
+      <c r="G56" t="n">
         <v>4</v>
       </c>
-      <c r="D56" t="n">
-        <v>3</v>
-      </c>
-      <c r="E56" t="n">
-        <v>5</v>
-      </c>
-      <c r="F56" t="n">
-        <v>3</v>
-      </c>
-      <c r="G56" t="n">
+      <c r="H56" t="n">
+        <v>0</v>
+      </c>
+      <c r="I56" t="n">
         <v>2</v>
       </c>
-      <c r="H56" t="n">
-        <v>4</v>
-      </c>
-      <c r="I56" t="n">
-        <v>1</v>
-      </c>
       <c r="J56" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K56" t="n">
         <v>0</v>
       </c>
       <c r="L56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -2813,22 +2813,22 @@
       </c>
       <c r="B58" t="inlineStr"/>
       <c r="C58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F58" t="n">
         <v>0</v>
       </c>
       <c r="G58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I58" t="n">
         <v>0</v>
@@ -2837,10 +2837,10 @@
         <v>0</v>
       </c>
       <c r="K58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M58" t="n">
         <v>0</v>
@@ -2854,10 +2854,10 @@
       </c>
       <c r="B59" t="inlineStr"/>
       <c r="C59" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E59" t="n">
         <v>0</v>
@@ -2866,10 +2866,10 @@
         <v>0</v>
       </c>
       <c r="G59" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I59" t="n">
         <v>0</v>
@@ -2878,13 +2878,13 @@
         <v>0</v>
       </c>
       <c r="K59" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L59" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M59" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60">
@@ -2907,7 +2907,7 @@
         <v>0</v>
       </c>
       <c r="G60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H60" t="n">
         <v>0</v>
@@ -3021,7 +3021,7 @@
         <v>0</v>
       </c>
       <c r="D63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E63" t="n">
         <v>1</v>
@@ -3033,7 +3033,7 @@
         <v>1</v>
       </c>
       <c r="H63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I63" t="n">
         <v>0</v>
@@ -3191,10 +3191,10 @@
         <v>0</v>
       </c>
       <c r="F67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H67" t="n">
         <v>0</v>
@@ -3232,10 +3232,10 @@
         <v>0</v>
       </c>
       <c r="F68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H68" t="n">
         <v>0</v>
@@ -3264,7 +3264,7 @@
       </c>
       <c r="B69" t="inlineStr"/>
       <c r="C69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D69" t="n">
         <v>0</v>
@@ -3358,16 +3358,16 @@
         <v>0</v>
       </c>
       <c r="G71" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H71" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I71" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K71" t="n">
         <v>0</v>
@@ -3399,25 +3399,25 @@
         <v>0</v>
       </c>
       <c r="G72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K72" t="n">
         <v>0</v>
       </c>
       <c r="L72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="73">
@@ -3455,10 +3455,10 @@
         <v>0</v>
       </c>
       <c r="L73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M73" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74">
@@ -3519,13 +3519,13 @@
         <v>0</v>
       </c>
       <c r="F75" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G75" t="n">
         <v>1</v>
       </c>
       <c r="H75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I75" t="n">
         <v>0</v>
@@ -3549,7 +3549,9 @@
           <t>印表機、傳真機、掃瞄器、多功能事務機、投影機</t>
         </is>
       </c>
-      <c r="B76" t="inlineStr"/>
+      <c r="B76" t="n">
+        <v>0</v>
+      </c>
       <c r="C76" t="n">
         <v>0</v>
       </c>
@@ -3557,13 +3559,13 @@
         <v>0</v>
       </c>
       <c r="E76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F76" t="n">
         <v>1</v>
       </c>
       <c r="G76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H76" t="n">
         <v>0</v>
@@ -3631,36 +3633,38 @@
           <t>原材料</t>
         </is>
       </c>
-      <c r="B78" t="inlineStr"/>
+      <c r="B78" t="n">
+        <v>0</v>
+      </c>
       <c r="C78" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D78" t="n">
         <v>1</v>
       </c>
       <c r="E78" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F78" t="n">
         <v>0</v>
       </c>
       <c r="G78" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H78" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I78" t="n">
         <v>1</v>
       </c>
       <c r="J78" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K78" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L78" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M78" t="n">
         <v>0</v>
@@ -3724,10 +3728,10 @@
         <v>0</v>
       </c>
       <c r="F80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G80" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H80" t="n">
         <v>0</v>
@@ -3809,10 +3813,10 @@
         <v>0</v>
       </c>
       <c r="G82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I82" t="n">
         <v>0</v>
@@ -3838,37 +3842,37 @@
       </c>
       <c r="B83" t="inlineStr"/>
       <c r="C83" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D83" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E83" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F83" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G83" t="n">
+        <v>1</v>
+      </c>
+      <c r="H83" t="n">
+        <v>0</v>
+      </c>
+      <c r="I83" t="n">
+        <v>1</v>
+      </c>
+      <c r="J83" t="n">
+        <v>0</v>
+      </c>
+      <c r="K83" t="n">
+        <v>0</v>
+      </c>
+      <c r="L83" t="n">
         <v>2</v>
       </c>
-      <c r="H83" t="n">
-        <v>1</v>
-      </c>
-      <c r="I83" t="n">
-        <v>0</v>
-      </c>
-      <c r="J83" t="n">
-        <v>1</v>
-      </c>
-      <c r="K83" t="n">
-        <v>0</v>
-      </c>
-      <c r="L83" t="n">
-        <v>0</v>
-      </c>
       <c r="M83" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="84">
@@ -3970,16 +3974,16 @@
         <v>0</v>
       </c>
       <c r="F86" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G86" t="n">
         <v>1</v>
       </c>
       <c r="H86" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I86" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -4005,25 +4009,25 @@
         <v>0</v>
       </c>
       <c r="D87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F87" t="n">
         <v>0</v>
       </c>
       <c r="G87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K87" t="n">
         <v>0</v>
@@ -4041,7 +4045,9 @@
           <t>塑膠框</t>
         </is>
       </c>
-      <c r="B88" t="inlineStr"/>
+      <c r="B88" t="n">
+        <v>0</v>
+      </c>
       <c r="C88" t="n">
         <v>0</v>
       </c>
@@ -4052,10 +4058,10 @@
         <v>0</v>
       </c>
       <c r="F88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H88" t="n">
         <v>0</v>
@@ -4070,10 +4076,10 @@
         <v>0</v>
       </c>
       <c r="L88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="89">
@@ -4086,37 +4092,37 @@
         <v>0</v>
       </c>
       <c r="C89" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D89" t="n">
         <v>1</v>
       </c>
       <c r="E89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F89" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G89" t="n">
         <v>1</v>
       </c>
       <c r="H89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I89" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K89" t="n">
         <v>0</v>
       </c>
       <c r="L89" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="90">
@@ -4174,13 +4180,13 @@
         <v>0</v>
       </c>
       <c r="E91" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F91" t="n">
         <v>1</v>
       </c>
       <c r="G91" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H91" t="n">
         <v>0</v>
@@ -4207,9 +4213,7 @@
           <t>大功率鋰電池芯/模組、電池管理系統、動力馬達等零組件</t>
         </is>
       </c>
-      <c r="B92" t="n">
-        <v>0</v>
-      </c>
+      <c r="B92" t="inlineStr"/>
       <c r="C92" t="n">
         <v>1</v>
       </c>
@@ -4217,31 +4221,31 @@
         <v>1</v>
       </c>
       <c r="E92" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F92" t="n">
         <v>0</v>
       </c>
       <c r="G92" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H92" t="n">
+        <v>0</v>
+      </c>
+      <c r="I92" t="n">
+        <v>1</v>
+      </c>
+      <c r="J92" t="n">
+        <v>1</v>
+      </c>
+      <c r="K92" t="n">
+        <v>1</v>
+      </c>
+      <c r="L92" t="n">
         <v>2</v>
       </c>
-      <c r="I92" t="n">
-        <v>0</v>
-      </c>
-      <c r="J92" t="n">
-        <v>1</v>
-      </c>
-      <c r="K92" t="n">
-        <v>1</v>
-      </c>
-      <c r="L92" t="n">
-        <v>1</v>
-      </c>
       <c r="M92" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="93">
@@ -4346,10 +4350,10 @@
         <v>0</v>
       </c>
       <c r="G95" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H95" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I95" t="n">
         <v>0</v>
@@ -4358,13 +4362,13 @@
         <v>0</v>
       </c>
       <c r="K95" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L95" t="n">
         <v>1</v>
       </c>
       <c r="M95" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="96">
@@ -4373,9 +4377,7 @@
           <t>太陽能電廠</t>
         </is>
       </c>
-      <c r="B96" t="n">
-        <v>0</v>
-      </c>
+      <c r="B96" t="inlineStr"/>
       <c r="C96" t="n">
         <v>0</v>
       </c>
@@ -4389,10 +4391,10 @@
         <v>0</v>
       </c>
       <c r="G96" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H96" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I96" t="n">
         <v>0</v>
@@ -4404,10 +4406,10 @@
         <v>0</v>
       </c>
       <c r="L96" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M96" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="97">
@@ -4457,7 +4459,9 @@
           <t>太陽能電池模組</t>
         </is>
       </c>
-      <c r="B98" t="inlineStr"/>
+      <c r="B98" t="n">
+        <v>0</v>
+      </c>
       <c r="C98" t="n">
         <v>0</v>
       </c>
@@ -4530,7 +4534,7 @@
         <v>0</v>
       </c>
       <c r="M99" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="100">
@@ -4591,16 +4595,16 @@
         <v>0</v>
       </c>
       <c r="F101" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G101" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H101" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I101" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -4629,31 +4633,31 @@
         <v>1</v>
       </c>
       <c r="E102" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F102" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G102" t="n">
+        <v>1</v>
+      </c>
+      <c r="H102" t="n">
+        <v>1</v>
+      </c>
+      <c r="I102" t="n">
+        <v>0</v>
+      </c>
+      <c r="J102" t="n">
+        <v>0</v>
+      </c>
+      <c r="K102" t="n">
+        <v>0</v>
+      </c>
+      <c r="L102" t="n">
         <v>2</v>
       </c>
-      <c r="H102" t="n">
-        <v>1</v>
-      </c>
-      <c r="I102" t="n">
-        <v>1</v>
-      </c>
-      <c r="J102" t="n">
-        <v>0</v>
-      </c>
-      <c r="K102" t="n">
-        <v>0</v>
-      </c>
-      <c r="L102" t="n">
-        <v>0</v>
-      </c>
       <c r="M102" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="103">
@@ -4714,16 +4718,16 @@
         <v>0</v>
       </c>
       <c r="F104" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G104" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H104" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I104" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -4732,10 +4736,10 @@
         <v>0</v>
       </c>
       <c r="L104" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M104" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="105">
@@ -4749,34 +4753,34 @@
         <v>0</v>
       </c>
       <c r="D105" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E105" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F105" t="n">
         <v>1</v>
       </c>
       <c r="G105" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H105" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I105" t="n">
         <v>1</v>
       </c>
       <c r="J105" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K105" t="n">
         <v>0</v>
       </c>
       <c r="L105" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M105" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="106">
@@ -4787,37 +4791,37 @@
       </c>
       <c r="B106" t="inlineStr"/>
       <c r="C106" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D106" t="n">
         <v>0</v>
       </c>
       <c r="E106" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F106" t="n">
+        <v>1</v>
+      </c>
+      <c r="G106" t="n">
         <v>2</v>
       </c>
-      <c r="G106" t="n">
-        <v>1</v>
-      </c>
       <c r="H106" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I106" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J106" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K106" t="n">
         <v>0</v>
       </c>
       <c r="L106" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M106" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="107">
@@ -4949,9 +4953,7 @@
           <t>工業用設備</t>
         </is>
       </c>
-      <c r="B110" t="n">
-        <v>0</v>
-      </c>
+      <c r="B110" t="inlineStr"/>
       <c r="C110" t="n">
         <v>0</v>
       </c>
@@ -4959,10 +4961,10 @@
         <v>0</v>
       </c>
       <c r="E110" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F110" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G110" t="n">
         <v>0</v>
@@ -4980,10 +4982,10 @@
         <v>0</v>
       </c>
       <c r="L110" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M110" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="111">
@@ -4994,25 +4996,25 @@
       </c>
       <c r="B111" t="inlineStr"/>
       <c r="C111" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D111" t="n">
+        <v>0</v>
+      </c>
+      <c r="E111" t="n">
         <v>2</v>
       </c>
-      <c r="E111" t="n">
-        <v>0</v>
-      </c>
       <c r="F111" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G111" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H111" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I111" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -5047,10 +5049,10 @@
         <v>0</v>
       </c>
       <c r="G112" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H112" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I112" t="n">
         <v>0</v>
@@ -5059,10 +5061,10 @@
         <v>0</v>
       </c>
       <c r="K112" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L112" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M112" t="n">
         <v>0</v>
@@ -5088,10 +5090,10 @@
         <v>0</v>
       </c>
       <c r="G113" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H113" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I113" t="n">
         <v>0</v>
@@ -5100,10 +5102,10 @@
         <v>0</v>
       </c>
       <c r="K113" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L113" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M113" t="n">
         <v>0</v>
@@ -5325,16 +5327,16 @@
         <v>0</v>
       </c>
       <c r="D119" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E119" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F119" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G119" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H119" t="n">
         <v>0</v>
@@ -5363,37 +5365,37 @@
       </c>
       <c r="B120" t="inlineStr"/>
       <c r="C120" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D120" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E120" t="n">
         <v>1</v>
       </c>
       <c r="F120" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G120" t="n">
+        <v>0</v>
+      </c>
+      <c r="H120" t="n">
+        <v>1</v>
+      </c>
+      <c r="I120" t="n">
+        <v>1</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0</v>
+      </c>
+      <c r="L120" t="n">
         <v>2</v>
       </c>
-      <c r="H120" t="n">
-        <v>0</v>
-      </c>
-      <c r="I120" t="n">
-        <v>1</v>
-      </c>
-      <c r="J120" t="n">
-        <v>1</v>
-      </c>
-      <c r="K120" t="n">
-        <v>0</v>
-      </c>
-      <c r="L120" t="n">
-        <v>0</v>
-      </c>
       <c r="M120" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="121">
@@ -5406,10 +5408,10 @@
         <v>0</v>
       </c>
       <c r="C121" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D121" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E121" t="n">
         <v>0</v>
@@ -5418,7 +5420,7 @@
         <v>0</v>
       </c>
       <c r="G121" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H121" t="n">
         <v>0</v>
@@ -5433,10 +5435,10 @@
         <v>0</v>
       </c>
       <c r="L121" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M121" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="122">
@@ -5532,19 +5534,19 @@
         <v>0</v>
       </c>
       <c r="D124" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E124" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F124" t="n">
         <v>0</v>
       </c>
       <c r="G124" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H124" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I124" t="n">
         <v>0</v>
@@ -5609,9 +5611,11 @@
           <t>感測器/模組</t>
         </is>
       </c>
-      <c r="B126" t="inlineStr"/>
+      <c r="B126" t="n">
+        <v>0</v>
+      </c>
       <c r="C126" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D126" t="n">
         <v>0</v>
@@ -5620,7 +5624,7 @@
         <v>1</v>
       </c>
       <c r="F126" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G126" t="n">
         <v>0</v>
@@ -5650,9 +5654,7 @@
           <t>感測裝置</t>
         </is>
       </c>
-      <c r="B127" t="n">
-        <v>0</v>
-      </c>
+      <c r="B127" t="inlineStr"/>
       <c r="C127" t="n">
         <v>0</v>
       </c>
@@ -5660,10 +5662,10 @@
         <v>0</v>
       </c>
       <c r="E127" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F127" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G127" t="n">
         <v>0</v>
@@ -5693,14 +5695,12 @@
           <t>應用/系統軟體設計開發</t>
         </is>
       </c>
-      <c r="B128" t="n">
-        <v>0</v>
-      </c>
+      <c r="B128" t="inlineStr"/>
       <c r="C128" t="n">
         <v>0</v>
       </c>
       <c r="D128" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E128" t="n">
         <v>2</v>
@@ -5709,25 +5709,25 @@
         <v>2</v>
       </c>
       <c r="G128" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H128" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I128" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J128" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K128" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L128" t="n">
         <v>1</v>
       </c>
       <c r="M128" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="129">
@@ -5741,7 +5741,7 @@
         <v>0</v>
       </c>
       <c r="D129" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E129" t="n">
         <v>1</v>
@@ -5753,7 +5753,7 @@
         <v>1</v>
       </c>
       <c r="H129" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I129" t="n">
         <v>0</v>
@@ -5788,10 +5788,10 @@
         <v>0</v>
       </c>
       <c r="F130" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G130" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H130" t="n">
         <v>0</v>
@@ -5818,12 +5818,14 @@
           <t>成衣及其它家居紡織類品</t>
         </is>
       </c>
-      <c r="B131" t="inlineStr"/>
+      <c r="B131" t="n">
+        <v>0</v>
+      </c>
       <c r="C131" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D131" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E131" t="n">
         <v>0</v>
@@ -5832,7 +5834,7 @@
         <v>0</v>
       </c>
       <c r="G131" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H131" t="n">
         <v>1</v>
@@ -5841,13 +5843,13 @@
         <v>1</v>
       </c>
       <c r="J131" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K131" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L131" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M131" t="n">
         <v>0</v>
@@ -5861,7 +5863,7 @@
       </c>
       <c r="B132" t="inlineStr"/>
       <c r="C132" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D132" t="n">
         <v>0</v>
@@ -5876,10 +5878,10 @@
         <v>0</v>
       </c>
       <c r="H132" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I132" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -5911,10 +5913,10 @@
         <v>0</v>
       </c>
       <c r="F133" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G133" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H133" t="n">
         <v>0</v>
@@ -5941,7 +5943,9 @@
           <t>接著劑(合成樹脂)</t>
         </is>
       </c>
-      <c r="B134" t="inlineStr"/>
+      <c r="B134" t="n">
+        <v>0</v>
+      </c>
       <c r="C134" t="n">
         <v>0</v>
       </c>
@@ -6064,7 +6068,9 @@
           <t>擴散膜、增亮膜、導光板</t>
         </is>
       </c>
-      <c r="B137" t="inlineStr"/>
+      <c r="B137" t="n">
+        <v>0</v>
+      </c>
       <c r="C137" t="n">
         <v>0</v>
       </c>
@@ -6072,10 +6078,10 @@
         <v>0</v>
       </c>
       <c r="E137" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F137" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G137" t="n">
         <v>0</v>
@@ -6160,7 +6166,7 @@
         <v>1</v>
       </c>
       <c r="G139" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H139" t="n">
         <v>0</v>
@@ -6175,10 +6181,10 @@
         <v>0</v>
       </c>
       <c r="L139" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M139" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="140">
@@ -6239,7 +6245,7 @@
         <v>0</v>
       </c>
       <c r="F141" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G141" t="n">
         <v>1</v>
@@ -6248,7 +6254,7 @@
         <v>1</v>
       </c>
       <c r="I141" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -6321,10 +6327,10 @@
         <v>0</v>
       </c>
       <c r="F143" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G143" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H143" t="n">
         <v>0</v>
@@ -6362,19 +6368,19 @@
         <v>0</v>
       </c>
       <c r="F144" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G144" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H144" t="n">
         <v>0</v>
       </c>
       <c r="I144" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J144" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K144" t="n">
         <v>0</v>
@@ -6403,16 +6409,16 @@
         <v>0</v>
       </c>
       <c r="F145" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G145" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H145" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I145" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -6441,10 +6447,10 @@
         <v>0</v>
       </c>
       <c r="E146" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F146" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G146" t="n">
         <v>0</v>
@@ -6485,16 +6491,16 @@
         <v>0</v>
       </c>
       <c r="F147" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G147" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H147" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I147" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -6517,13 +6523,13 @@
       </c>
       <c r="B148" t="inlineStr"/>
       <c r="C148" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D148" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E148" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F148" t="n">
         <v>0</v>
@@ -6573,10 +6579,10 @@
         <v>0</v>
       </c>
       <c r="H149" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I149" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -6599,7 +6605,7 @@
       </c>
       <c r="B150" t="inlineStr"/>
       <c r="C150" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D150" t="n">
         <v>0</v>
@@ -6626,10 +6632,10 @@
         <v>0</v>
       </c>
       <c r="L150" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M150" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="151">
@@ -6638,7 +6644,9 @@
           <t>旅館服務業</t>
         </is>
       </c>
-      <c r="B151" t="inlineStr"/>
+      <c r="B151" t="n">
+        <v>0</v>
+      </c>
       <c r="C151" t="n">
         <v>0</v>
       </c>
@@ -6646,10 +6654,10 @@
         <v>0</v>
       </c>
       <c r="E151" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F151" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G151" t="n">
         <v>0</v>
@@ -6658,16 +6666,16 @@
         <v>0</v>
       </c>
       <c r="I151" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
       </c>
       <c r="K151" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L151" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M151" t="n">
         <v>0</v>
@@ -6687,13 +6695,13 @@
         <v>0</v>
       </c>
       <c r="E152" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F152" t="n">
         <v>1</v>
       </c>
       <c r="G152" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H152" t="n">
         <v>0</v>
@@ -6731,28 +6739,28 @@
         <v>0</v>
       </c>
       <c r="F153" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G153" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H153" t="n">
         <v>0</v>
       </c>
       <c r="I153" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J153" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K153" t="n">
         <v>0</v>
       </c>
       <c r="L153" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M153" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="154">
@@ -6775,10 +6783,10 @@
         <v>0</v>
       </c>
       <c r="G154" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H154" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I154" t="n">
         <v>0</v>
@@ -6790,10 +6798,10 @@
         <v>0</v>
       </c>
       <c r="L154" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M154" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="155">
@@ -6848,25 +6856,25 @@
         <v>0</v>
       </c>
       <c r="D156" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E156" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F156" t="n">
         <v>0</v>
       </c>
       <c r="G156" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H156" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I156" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J156" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K156" t="n">
         <v>0</v>
@@ -6886,7 +6894,7 @@
       </c>
       <c r="B157" t="inlineStr"/>
       <c r="C157" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D157" t="n">
         <v>0</v>
@@ -6895,13 +6903,13 @@
         <v>0</v>
       </c>
       <c r="F157" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G157" t="n">
         <v>2</v>
       </c>
       <c r="H157" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I157" t="n">
         <v>0</v>
@@ -6916,7 +6924,7 @@
         <v>0</v>
       </c>
       <c r="M157" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="158">
@@ -6927,19 +6935,19 @@
       </c>
       <c r="B158" t="inlineStr"/>
       <c r="C158" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D158" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E158" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F158" t="n">
         <v>1</v>
       </c>
       <c r="G158" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H158" t="n">
         <v>0</v>
@@ -6954,10 +6962,10 @@
         <v>0</v>
       </c>
       <c r="L158" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M158" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="159">
@@ -7018,10 +7026,10 @@
         <v>0</v>
       </c>
       <c r="F160" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G160" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H160" t="n">
         <v>0</v>
@@ -7036,10 +7044,10 @@
         <v>0</v>
       </c>
       <c r="L160" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M160" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="161">
@@ -7059,10 +7067,10 @@
         <v>0</v>
       </c>
       <c r="F161" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G161" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H161" t="n">
         <v>0</v>
@@ -7100,28 +7108,28 @@
         <v>0</v>
       </c>
       <c r="F162" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G162" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H162" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I162" t="n">
         <v>1</v>
       </c>
       <c r="J162" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K162" t="n">
         <v>0</v>
       </c>
       <c r="L162" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M162" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="163">
@@ -7141,13 +7149,13 @@
         <v>0</v>
       </c>
       <c r="F163" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G163" t="n">
         <v>1</v>
       </c>
       <c r="H163" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I163" t="n">
         <v>0</v>
@@ -7179,13 +7187,13 @@
         <v>0</v>
       </c>
       <c r="E164" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F164" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G164" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H164" t="n">
         <v>0</v>
@@ -7212,27 +7220,29 @@
           <t>機殼</t>
         </is>
       </c>
-      <c r="B165" t="inlineStr"/>
+      <c r="B165" t="n">
+        <v>0</v>
+      </c>
       <c r="C165" t="n">
         <v>0</v>
       </c>
       <c r="D165" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E165" t="n">
         <v>1</v>
       </c>
       <c r="F165" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G165" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H165" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I165" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -7267,10 +7277,10 @@
         <v>0</v>
       </c>
       <c r="G166" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H166" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I166" t="n">
         <v>0</v>
@@ -7279,13 +7289,13 @@
         <v>0</v>
       </c>
       <c r="K166" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L166" t="n">
         <v>1</v>
       </c>
       <c r="M166" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="167">
@@ -7294,14 +7304,12 @@
           <t>機電系統工程</t>
         </is>
       </c>
-      <c r="B167" t="n">
-        <v>0</v>
-      </c>
+      <c r="B167" t="inlineStr"/>
       <c r="C167" t="n">
         <v>0</v>
       </c>
       <c r="D167" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E167" t="n">
         <v>0</v>
@@ -7310,10 +7318,10 @@
         <v>0</v>
       </c>
       <c r="G167" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H167" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I167" t="n">
         <v>0</v>
@@ -7322,10 +7330,10 @@
         <v>0</v>
       </c>
       <c r="K167" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L167" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M167" t="n">
         <v>0</v>
@@ -7337,7 +7345,9 @@
           <t>橡膠製品</t>
         </is>
       </c>
-      <c r="B168" t="inlineStr"/>
+      <c r="B168" t="n">
+        <v>0</v>
+      </c>
       <c r="C168" t="n">
         <v>0</v>
       </c>
@@ -7503,7 +7513,7 @@
       </c>
       <c r="B172" t="inlineStr"/>
       <c r="C172" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D172" t="n">
         <v>0</v>
@@ -7515,10 +7525,10 @@
         <v>0</v>
       </c>
       <c r="G172" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H172" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I172" t="n">
         <v>0</v>
@@ -7553,10 +7563,10 @@
         <v>0</v>
       </c>
       <c r="F173" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G173" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H173" t="n">
         <v>0</v>
@@ -7624,7 +7634,9 @@
           <t>海陸空貨運承攬</t>
         </is>
       </c>
-      <c r="B175" t="inlineStr"/>
+      <c r="B175" t="n">
+        <v>0</v>
+      </c>
       <c r="C175" t="n">
         <v>0</v>
       </c>
@@ -7706,7 +7718,9 @@
           <t>濾波器、振盪器</t>
         </is>
       </c>
-      <c r="B177" t="inlineStr"/>
+      <c r="B177" t="n">
+        <v>0</v>
+      </c>
       <c r="C177" t="n">
         <v>0</v>
       </c>
@@ -7714,7 +7728,7 @@
         <v>0</v>
       </c>
       <c r="E177" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F177" t="n">
         <v>1</v>
@@ -7723,10 +7737,10 @@
         <v>1</v>
       </c>
       <c r="H177" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I177" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -7735,10 +7749,10 @@
         <v>0</v>
       </c>
       <c r="L177" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M177" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="178">
@@ -7795,50 +7809,48 @@
         <v>1</v>
       </c>
       <c r="D179" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E179" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F179" t="n">
+        <v>5</v>
+      </c>
+      <c r="G179" t="n">
+        <v>1</v>
+      </c>
+      <c r="H179" t="n">
+        <v>0</v>
+      </c>
+      <c r="I179" t="n">
         <v>2</v>
       </c>
-      <c r="G179" t="n">
-        <v>5</v>
-      </c>
-      <c r="H179" t="n">
-        <v>1</v>
-      </c>
-      <c r="I179" t="n">
-        <v>0</v>
-      </c>
       <c r="J179" t="n">
+        <v>0</v>
+      </c>
+      <c r="K179" t="n">
+        <v>0</v>
+      </c>
+      <c r="L179" t="n">
         <v>2</v>
       </c>
-      <c r="K179" t="n">
-        <v>0</v>
-      </c>
-      <c r="L179" t="n">
-        <v>0</v>
-      </c>
       <c r="M179" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="1" t="inlineStr">
         <is>
-          <t>燈具/應用</t>
-        </is>
-      </c>
-      <c r="B180" t="n">
-        <v>0</v>
-      </c>
+          <t>煤、鐵礦砂、鎳鐵、鉻鐵、廢鋼</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr"/>
       <c r="C180" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D180" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E180" t="n">
         <v>0</v>
@@ -7847,13 +7859,13 @@
         <v>0</v>
       </c>
       <c r="G180" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H180" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I180" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -7865,18 +7877,18 @@
         <v>0</v>
       </c>
       <c r="M180" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="1" t="inlineStr">
         <is>
-          <t>營造業</t>
+          <t>燈具/應用</t>
         </is>
       </c>
       <c r="B181" t="inlineStr"/>
       <c r="C181" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D181" t="n">
         <v>0</v>
@@ -7885,25 +7897,25 @@
         <v>0</v>
       </c>
       <c r="F181" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G181" t="n">
         <v>2</v>
       </c>
       <c r="H181" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I181" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J181" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K181" t="n">
         <v>0</v>
       </c>
       <c r="L181" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M181" t="n">
         <v>0</v>
@@ -7912,10 +7924,12 @@
     <row r="182">
       <c r="A182" s="1" t="inlineStr">
         <is>
-          <t>營造設置</t>
-        </is>
-      </c>
-      <c r="B182" t="inlineStr"/>
+          <t>營造業</t>
+        </is>
+      </c>
+      <c r="B182" t="n">
+        <v>0</v>
+      </c>
       <c r="C182" t="n">
         <v>0</v>
       </c>
@@ -7926,16 +7940,16 @@
         <v>0</v>
       </c>
       <c r="F182" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G182" t="n">
         <v>0</v>
       </c>
       <c r="H182" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I182" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -7953,7 +7967,7 @@
     <row r="183">
       <c r="A183" s="1" t="inlineStr">
         <is>
-          <t>營運管理軟體</t>
+          <t>營造設置</t>
         </is>
       </c>
       <c r="B183" t="inlineStr"/>
@@ -7964,19 +7978,19 @@
         <v>0</v>
       </c>
       <c r="E183" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F183" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G183" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H183" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I183" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -7994,7 +8008,7 @@
     <row r="184">
       <c r="A184" s="1" t="inlineStr">
         <is>
-          <t>營養食品</t>
+          <t>營運管理軟體</t>
         </is>
       </c>
       <c r="B184" t="inlineStr"/>
@@ -8002,19 +8016,19 @@
         <v>0</v>
       </c>
       <c r="D184" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E184" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F184" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G184" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H184" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I184" t="n">
         <v>0</v>
@@ -8035,7 +8049,7 @@
     <row r="185">
       <c r="A185" s="1" t="inlineStr">
         <is>
-          <t>物業管理</t>
+          <t>營養食品</t>
         </is>
       </c>
       <c r="B185" t="inlineStr"/>
@@ -8076,7 +8090,7 @@
     <row r="186">
       <c r="A186" s="1" t="inlineStr">
         <is>
-          <t>物流倉儲服務</t>
+          <t>物業管理</t>
         </is>
       </c>
       <c r="B186" t="inlineStr"/>
@@ -8117,7 +8131,7 @@
     <row r="187">
       <c r="A187" s="1" t="inlineStr">
         <is>
-          <t>物聯網安全</t>
+          <t>物流倉儲服務</t>
         </is>
       </c>
       <c r="B187" t="inlineStr"/>
@@ -8134,16 +8148,16 @@
         <v>0</v>
       </c>
       <c r="G187" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H187" t="n">
         <v>0</v>
       </c>
       <c r="I187" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J187" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K187" t="n">
         <v>0</v>
@@ -8158,7 +8172,7 @@
     <row r="188">
       <c r="A188" s="1" t="inlineStr">
         <is>
-          <t>特殊照明業</t>
+          <t>物聯網安全</t>
         </is>
       </c>
       <c r="B188" t="inlineStr"/>
@@ -8172,16 +8186,16 @@
         <v>0</v>
       </c>
       <c r="F188" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G188" t="n">
         <v>0</v>
       </c>
       <c r="H188" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I188" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -8193,13 +8207,13 @@
         <v>0</v>
       </c>
       <c r="M188" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="1" t="inlineStr">
         <is>
-          <t>玻/碳纖</t>
+          <t>特殊照明業</t>
         </is>
       </c>
       <c r="B189" t="inlineStr"/>
@@ -8216,7 +8230,7 @@
         <v>0</v>
       </c>
       <c r="G189" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H189" t="n">
         <v>0</v>
@@ -8231,7 +8245,7 @@
         <v>0</v>
       </c>
       <c r="L189" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M189" t="n">
         <v>0</v>
@@ -8240,12 +8254,12 @@
     <row r="190">
       <c r="A190" s="1" t="inlineStr">
         <is>
-          <t>玻璃基板</t>
+          <t>玻/碳纖</t>
         </is>
       </c>
       <c r="B190" t="inlineStr"/>
       <c r="C190" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D190" t="n">
         <v>0</v>
@@ -8254,7 +8268,7 @@
         <v>0</v>
       </c>
       <c r="F190" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G190" t="n">
         <v>0</v>
@@ -8281,7 +8295,7 @@
     <row r="191">
       <c r="A191" s="1" t="inlineStr">
         <is>
-          <t>玻璃纖維/玻纖布</t>
+          <t>玻璃基板</t>
         </is>
       </c>
       <c r="B191" t="inlineStr"/>
@@ -8295,16 +8309,16 @@
         <v>0</v>
       </c>
       <c r="F191" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G191" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H191" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I191" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -8316,13 +8330,13 @@
         <v>0</v>
       </c>
       <c r="M191" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="1" t="inlineStr">
         <is>
-          <t>理財投資</t>
+          <t>玻璃纖維/玻纖布</t>
         </is>
       </c>
       <c r="B192" t="inlineStr"/>
@@ -8333,16 +8347,16 @@
         <v>0</v>
       </c>
       <c r="E192" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F192" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G192" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H192" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I192" t="n">
         <v>0</v>
@@ -8354,7 +8368,7 @@
         <v>0</v>
       </c>
       <c r="L192" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M192" t="n">
         <v>0</v>
@@ -8363,15 +8377,15 @@
     <row r="193">
       <c r="A193" s="1" t="inlineStr">
         <is>
-          <t>環保潔能服務產業</t>
+          <t>理財投資</t>
         </is>
       </c>
       <c r="B193" t="inlineStr"/>
       <c r="C193" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D193" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E193" t="n">
         <v>0</v>
@@ -8398,18 +8412,18 @@
         <v>0</v>
       </c>
       <c r="M193" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="1" t="inlineStr">
         <is>
-          <t>環氧樹脂</t>
+          <t>環保潔能服務產業</t>
         </is>
       </c>
       <c r="B194" t="inlineStr"/>
       <c r="C194" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D194" t="n">
         <v>0</v>
@@ -8421,22 +8435,22 @@
         <v>0</v>
       </c>
       <c r="G194" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H194" t="n">
+        <v>0</v>
+      </c>
+      <c r="I194" t="n">
+        <v>0</v>
+      </c>
+      <c r="J194" t="n">
+        <v>0</v>
+      </c>
+      <c r="K194" t="n">
+        <v>0</v>
+      </c>
+      <c r="L194" t="n">
         <v>2</v>
-      </c>
-      <c r="I194" t="n">
-        <v>0</v>
-      </c>
-      <c r="J194" t="n">
-        <v>0</v>
-      </c>
-      <c r="K194" t="n">
-        <v>0</v>
-      </c>
-      <c r="L194" t="n">
-        <v>0</v>
       </c>
       <c r="M194" t="n">
         <v>0</v>
@@ -8445,123 +8459,121 @@
     <row r="195">
       <c r="A195" s="1" t="inlineStr">
         <is>
-          <t>生產製程、檢測設備及原物料</t>
+          <t>環氧樹脂</t>
         </is>
       </c>
       <c r="B195" t="inlineStr"/>
       <c r="C195" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D195" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E195" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F195" t="n">
         <v>1</v>
       </c>
       <c r="G195" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H195" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I195" t="n">
         <v>0</v>
       </c>
       <c r="J195" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K195" t="n">
         <v>0</v>
       </c>
       <c r="L195" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M195" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="1" t="inlineStr">
         <is>
-          <t>生產製程及檢測設備</t>
-        </is>
-      </c>
-      <c r="B196" t="n">
-        <v>0</v>
-      </c>
+          <t>生產製程、檢測設備及原物料</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr"/>
       <c r="C196" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D196" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E196" t="n">
+        <v>1</v>
+      </c>
+      <c r="F196" t="n">
+        <v>0</v>
+      </c>
+      <c r="G196" t="n">
         <v>3</v>
       </c>
-      <c r="F196" t="n">
-        <v>5</v>
-      </c>
-      <c r="G196" t="n">
-        <v>1</v>
-      </c>
       <c r="H196" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I196" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J196" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K196" t="n">
         <v>1</v>
       </c>
       <c r="L196" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M196" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="1" t="inlineStr">
         <is>
-          <t>發電營運</t>
+          <t>生產製程及檢測設備</t>
         </is>
       </c>
       <c r="B197" t="inlineStr"/>
       <c r="C197" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D197" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E197" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F197" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G197" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H197" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I197" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J197" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K197" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L197" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M197" t="n">
         <v>0</v>
@@ -8570,7 +8582,7 @@
     <row r="198">
       <c r="A198" s="1" t="inlineStr">
         <is>
-          <t>監控管理</t>
+          <t>發電營運</t>
         </is>
       </c>
       <c r="B198" t="inlineStr"/>
@@ -8611,7 +8623,7 @@
     <row r="199">
       <c r="A199" s="1" t="inlineStr">
         <is>
-          <t>監控系統</t>
+          <t>監控管理</t>
         </is>
       </c>
       <c r="B199" t="inlineStr"/>
@@ -8646,13 +8658,13 @@
         <v>0</v>
       </c>
       <c r="M199" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="1" t="inlineStr">
         <is>
-          <t>監理法遵</t>
+          <t>監控系統</t>
         </is>
       </c>
       <c r="B200" t="inlineStr"/>
@@ -8663,7 +8675,7 @@
         <v>0</v>
       </c>
       <c r="E200" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F200" t="n">
         <v>0</v>
@@ -8684,7 +8696,7 @@
         <v>0</v>
       </c>
       <c r="L200" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M200" t="n">
         <v>0</v>
@@ -8693,23 +8705,21 @@
     <row r="201">
       <c r="A201" s="1" t="inlineStr">
         <is>
-          <t>監視器/顯示器</t>
-        </is>
-      </c>
-      <c r="B201" t="n">
-        <v>0</v>
-      </c>
+          <t>監理法遵</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr"/>
       <c r="C201" t="n">
         <v>0</v>
       </c>
       <c r="D201" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E201" t="n">
         <v>0</v>
       </c>
       <c r="F201" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G201" t="n">
         <v>0</v>
@@ -8736,27 +8746,29 @@
     <row r="202">
       <c r="A202" s="1" t="inlineStr">
         <is>
-          <t>石化上游原料及相關鑽探設備</t>
-        </is>
-      </c>
-      <c r="B202" t="inlineStr"/>
+          <t>監視器/顯示器</t>
+        </is>
+      </c>
+      <c r="B202" t="n">
+        <v>0</v>
+      </c>
       <c r="C202" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D202" t="n">
         <v>0</v>
       </c>
       <c r="E202" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F202" t="n">
         <v>0</v>
       </c>
       <c r="G202" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H202" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I202" t="n">
         <v>0</v>
@@ -8777,12 +8789,12 @@
     <row r="203">
       <c r="A203" s="1" t="inlineStr">
         <is>
-          <t>石化中間原料(例如乙烯、丙烯、丁二烯、苯、酚等)</t>
+          <t>石化上游原料及相關鑽探設備</t>
         </is>
       </c>
       <c r="B203" t="inlineStr"/>
       <c r="C203" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D203" t="n">
         <v>0</v>
@@ -8791,25 +8803,25 @@
         <v>0</v>
       </c>
       <c r="F203" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G203" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H203" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I203" t="n">
         <v>0</v>
       </c>
       <c r="J203" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K203" t="n">
         <v>0</v>
       </c>
       <c r="L203" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M203" t="n">
         <v>0</v>
@@ -8818,12 +8830,14 @@
     <row r="204">
       <c r="A204" s="1" t="inlineStr">
         <is>
-          <t>石化原料(例如純對苯二甲酸、乙二醇、己內醯胺、丙烯腈等)</t>
-        </is>
-      </c>
-      <c r="B204" t="inlineStr"/>
+          <t>石化中間原料(例如乙烯、丙烯、丁二烯、苯、酚等)</t>
+        </is>
+      </c>
+      <c r="B204" t="n">
+        <v>0</v>
+      </c>
       <c r="C204" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D204" t="n">
         <v>0</v>
@@ -8835,19 +8849,19 @@
         <v>0</v>
       </c>
       <c r="G204" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H204" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I204" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J204" t="n">
         <v>0</v>
       </c>
       <c r="K204" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L204" t="n">
         <v>0</v>
@@ -8859,7 +8873,7 @@
     <row r="205">
       <c r="A205" s="1" t="inlineStr">
         <is>
-          <t>石灰石</t>
+          <t>石化原料(例如純對苯二甲酸、乙二醇、己內醯胺、丙烯腈等)</t>
         </is>
       </c>
       <c r="B205" t="inlineStr"/>
@@ -8873,10 +8887,10 @@
         <v>0</v>
       </c>
       <c r="F205" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G205" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H205" t="n">
         <v>0</v>
@@ -8900,7 +8914,7 @@
     <row r="206">
       <c r="A206" s="1" t="inlineStr">
         <is>
-          <t>矽晶圓/矽晶片</t>
+          <t>石灰石</t>
         </is>
       </c>
       <c r="B206" t="inlineStr"/>
@@ -8923,10 +8937,10 @@
         <v>0</v>
       </c>
       <c r="I206" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J206" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K206" t="n">
         <v>0</v>
@@ -8941,82 +8955,80 @@
     <row r="207">
       <c r="A207" s="1" t="inlineStr">
         <is>
-          <t>硬板、軟板、IC載板製造</t>
-        </is>
-      </c>
-      <c r="B207" t="n">
-        <v>0</v>
-      </c>
+          <t>矽晶圓/矽晶片</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr"/>
       <c r="C207" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D207" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E207" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F207" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G207" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H207" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I207" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J207" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K207" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L207" t="n">
         <v>0</v>
       </c>
       <c r="M207" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="1" t="inlineStr">
         <is>
-          <t>硬碟機</t>
+          <t>硬板、軟板、IC載板製造</t>
         </is>
       </c>
       <c r="B208" t="inlineStr"/>
       <c r="C208" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D208" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E208" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F208" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G208" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H208" t="n">
         <v>0</v>
       </c>
       <c r="I208" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J208" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K208" t="n">
         <v>0</v>
       </c>
       <c r="L208" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="M208" t="n">
         <v>0</v>
@@ -9025,10 +9037,12 @@
     <row r="209">
       <c r="A209" s="1" t="inlineStr">
         <is>
-          <t>硬體開發工具</t>
-        </is>
-      </c>
-      <c r="B209" t="inlineStr"/>
+          <t>硬碟機</t>
+        </is>
+      </c>
+      <c r="B209" t="n">
+        <v>0</v>
+      </c>
       <c r="C209" t="n">
         <v>0</v>
       </c>
@@ -9036,13 +9050,13 @@
         <v>0</v>
       </c>
       <c r="E209" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F209" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G209" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H209" t="n">
         <v>0</v>
@@ -9066,7 +9080,7 @@
     <row r="210">
       <c r="A210" s="1" t="inlineStr">
         <is>
-          <t>磁碟儲存系統</t>
+          <t>硬體開發工具</t>
         </is>
       </c>
       <c r="B210" t="inlineStr"/>
@@ -9077,16 +9091,16 @@
         <v>0</v>
       </c>
       <c r="E210" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F210" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G210" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H210" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I210" t="n">
         <v>0</v>
@@ -9107,7 +9121,7 @@
     <row r="211">
       <c r="A211" s="1" t="inlineStr">
         <is>
-          <t>票券銷售</t>
+          <t>磁碟儲存系統</t>
         </is>
       </c>
       <c r="B211" t="inlineStr"/>
@@ -9115,16 +9129,16 @@
         <v>0</v>
       </c>
       <c r="D211" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E211" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F211" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G211" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H211" t="n">
         <v>0</v>
@@ -9148,7 +9162,7 @@
     <row r="212">
       <c r="A212" s="1" t="inlineStr">
         <is>
-          <t>租賃業</t>
+          <t>票券銷售</t>
         </is>
       </c>
       <c r="B212" t="inlineStr"/>
@@ -9189,7 +9203,7 @@
     <row r="213">
       <c r="A213" s="1" t="inlineStr">
         <is>
-          <t>移動控制</t>
+          <t>租賃業</t>
         </is>
       </c>
       <c r="B213" t="inlineStr"/>
@@ -9230,7 +9244,7 @@
     <row r="214">
       <c r="A214" s="1" t="inlineStr">
         <is>
-          <t>稜鏡片</t>
+          <t>移動控制</t>
         </is>
       </c>
       <c r="B214" t="inlineStr"/>
@@ -9271,7 +9285,7 @@
     <row r="215">
       <c r="A215" s="1" t="inlineStr">
         <is>
-          <t>穿戴式裝置</t>
+          <t>稜鏡片</t>
         </is>
       </c>
       <c r="B215" t="inlineStr"/>
@@ -9288,7 +9302,7 @@
         <v>0</v>
       </c>
       <c r="G215" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H215" t="n">
         <v>0</v>
@@ -9312,7 +9326,7 @@
     <row r="216">
       <c r="A216" s="1" t="inlineStr">
         <is>
-          <t>端點安全防護</t>
+          <t>穿戴式裝置</t>
         </is>
       </c>
       <c r="B216" t="inlineStr"/>
@@ -9323,22 +9337,22 @@
         <v>0</v>
       </c>
       <c r="E216" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F216" t="n">
         <v>1</v>
       </c>
       <c r="G216" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H216" t="n">
         <v>0</v>
       </c>
       <c r="I216" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J216" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K216" t="n">
         <v>0</v>
@@ -9353,7 +9367,7 @@
     <row r="217">
       <c r="A217" s="1" t="inlineStr">
         <is>
-          <t>筆記型電腦</t>
+          <t>端點安全防護</t>
         </is>
       </c>
       <c r="B217" t="inlineStr"/>
@@ -9364,16 +9378,16 @@
         <v>1</v>
       </c>
       <c r="E217" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F217" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G217" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H217" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I217" t="n">
         <v>1</v>
@@ -9388,36 +9402,36 @@
         <v>0</v>
       </c>
       <c r="M217" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" s="1" t="inlineStr">
         <is>
-          <t>精簡型電腦</t>
+          <t>筆記型電腦</t>
         </is>
       </c>
       <c r="B218" t="inlineStr"/>
       <c r="C218" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D218" t="n">
         <v>0</v>
       </c>
       <c r="E218" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F218" t="n">
         <v>1</v>
       </c>
       <c r="G218" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H218" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I218" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J218" t="n">
         <v>0</v>
@@ -9426,42 +9440,42 @@
         <v>0</v>
       </c>
       <c r="L218" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M218" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" s="1" t="inlineStr">
         <is>
-          <t>系統整合</t>
+          <t>精簡型電腦</t>
         </is>
       </c>
       <c r="B219" t="inlineStr"/>
       <c r="C219" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D219" t="n">
         <v>0</v>
       </c>
       <c r="E219" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F219" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="G219" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H219" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I219" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J219" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K219" t="n">
         <v>0</v>
@@ -9470,88 +9484,88 @@
         <v>1</v>
       </c>
       <c r="M219" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" s="1" t="inlineStr">
         <is>
-          <t>系統整合服務</t>
+          <t>系統整合</t>
         </is>
       </c>
       <c r="B220" t="n">
         <v>0</v>
       </c>
       <c r="C220" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D220" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E220" t="n">
+        <v>7</v>
+      </c>
+      <c r="F220" t="n">
+        <v>5</v>
+      </c>
+      <c r="G220" t="n">
+        <v>3</v>
+      </c>
+      <c r="H220" t="n">
         <v>2</v>
       </c>
-      <c r="F220" t="n">
-        <v>4</v>
-      </c>
-      <c r="G220" t="n">
-        <v>4</v>
-      </c>
-      <c r="H220" t="n">
-        <v>1</v>
-      </c>
       <c r="I220" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J220" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K220" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L220" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M220" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" s="1" t="inlineStr">
         <is>
-          <t>紙漿、紙類原料</t>
+          <t>系統整合服務</t>
         </is>
       </c>
       <c r="B221" t="inlineStr"/>
       <c r="C221" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D221" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E221" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F221" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G221" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H221" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I221" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J221" t="n">
         <v>0</v>
       </c>
       <c r="K221" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L221" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M221" t="n">
         <v>0</v>
@@ -9560,7 +9574,7 @@
     <row r="222">
       <c r="A222" s="1" t="inlineStr">
         <is>
-          <t>紡紗</t>
+          <t>紙漿、紙類原料</t>
         </is>
       </c>
       <c r="B222" t="inlineStr"/>
@@ -9571,13 +9585,13 @@
         <v>0</v>
       </c>
       <c r="E222" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F222" t="n">
         <v>0</v>
       </c>
       <c r="G222" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H222" t="n">
         <v>1</v>
@@ -9601,7 +9615,7 @@
     <row r="223">
       <c r="A223" s="1" t="inlineStr">
         <is>
-          <t>組裝廠</t>
+          <t>紡紗</t>
         </is>
       </c>
       <c r="B223" t="inlineStr"/>
@@ -9609,16 +9623,16 @@
         <v>0</v>
       </c>
       <c r="D223" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E223" t="n">
         <v>0</v>
       </c>
       <c r="F223" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G223" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H223" t="n">
         <v>0</v>
@@ -9642,7 +9656,7 @@
     <row r="224">
       <c r="A224" s="1" t="inlineStr">
         <is>
-          <t>結構工程</t>
+          <t>組裝廠</t>
         </is>
       </c>
       <c r="B224" t="inlineStr"/>
@@ -9683,7 +9697,7 @@
     <row r="225">
       <c r="A225" s="1" t="inlineStr">
         <is>
-          <t>網路IC</t>
+          <t>結構工程</t>
         </is>
       </c>
       <c r="B225" t="inlineStr"/>
@@ -9694,7 +9708,7 @@
         <v>0</v>
       </c>
       <c r="E225" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F225" t="n">
         <v>0</v>
@@ -9703,7 +9717,7 @@
         <v>0</v>
       </c>
       <c r="H225" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I225" t="n">
         <v>0</v>
@@ -9724,7 +9738,7 @@
     <row r="226">
       <c r="A226" s="1" t="inlineStr">
         <is>
-          <t>網路卡</t>
+          <t>網路IC</t>
         </is>
       </c>
       <c r="B226" t="inlineStr"/>
@@ -9732,13 +9746,13 @@
         <v>0</v>
       </c>
       <c r="D226" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E226" t="n">
         <v>0</v>
       </c>
       <c r="F226" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G226" t="n">
         <v>1</v>
@@ -9765,7 +9779,7 @@
     <row r="227">
       <c r="A227" s="1" t="inlineStr">
         <is>
-          <t>網路基礎設施</t>
+          <t>網路卡</t>
         </is>
       </c>
       <c r="B227" t="inlineStr"/>
@@ -9776,22 +9790,22 @@
         <v>0</v>
       </c>
       <c r="E227" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F227" t="n">
         <v>1</v>
       </c>
       <c r="G227" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H227" t="n">
         <v>0</v>
       </c>
       <c r="I227" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J227" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K227" t="n">
         <v>0</v>
@@ -9806,7 +9820,7 @@
     <row r="228">
       <c r="A228" s="1" t="inlineStr">
         <is>
-          <t>網路安全防護</t>
+          <t>網路基礎設施</t>
         </is>
       </c>
       <c r="B228" t="inlineStr"/>
@@ -9817,22 +9831,22 @@
         <v>0</v>
       </c>
       <c r="E228" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F228" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G228" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H228" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I228" t="n">
         <v>1</v>
       </c>
       <c r="J228" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K228" t="n">
         <v>0</v>
@@ -9847,26 +9861,24 @@
     <row r="229">
       <c r="A229" s="1" t="inlineStr">
         <is>
-          <t>網路設備(如數據機、網路卡、閘道器、路由器、網路電話)</t>
-        </is>
-      </c>
-      <c r="B229" t="n">
-        <v>0</v>
-      </c>
+          <t>網路安全防護</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr"/>
       <c r="C229" t="n">
+        <v>0</v>
+      </c>
+      <c r="D229" t="n">
+        <v>0</v>
+      </c>
+      <c r="E229" t="n">
+        <v>1</v>
+      </c>
+      <c r="F229" t="n">
         <v>2</v>
       </c>
-      <c r="D229" t="n">
-        <v>1</v>
-      </c>
-      <c r="E229" t="n">
-        <v>1</v>
-      </c>
-      <c r="F229" t="n">
-        <v>1</v>
-      </c>
       <c r="G229" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H229" t="n">
         <v>1</v>
@@ -9875,7 +9887,7 @@
         <v>1</v>
       </c>
       <c r="J229" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K229" t="n">
         <v>0</v>
@@ -9884,86 +9896,86 @@
         <v>0</v>
       </c>
       <c r="M229" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="1" t="inlineStr">
         <is>
-          <t>網頁內容安全</t>
+          <t>網路設備(如數據機、網路卡、閘道器、路由器、網路電話)</t>
         </is>
       </c>
       <c r="B230" t="inlineStr"/>
       <c r="C230" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D230" t="n">
         <v>1</v>
       </c>
       <c r="E230" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F230" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G230" t="n">
+        <v>1</v>
+      </c>
+      <c r="H230" t="n">
+        <v>1</v>
+      </c>
+      <c r="I230" t="n">
         <v>2</v>
       </c>
-      <c r="H230" t="n">
-        <v>1</v>
-      </c>
-      <c r="I230" t="n">
-        <v>1</v>
-      </c>
       <c r="J230" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K230" t="n">
         <v>0</v>
       </c>
       <c r="L230" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M230" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" s="1" t="inlineStr">
         <is>
-          <t>線上遊戲業</t>
+          <t>網頁內容安全</t>
         </is>
       </c>
       <c r="B231" t="inlineStr"/>
       <c r="C231" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D231" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E231" t="n">
         <v>0</v>
       </c>
       <c r="F231" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G231" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H231" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I231" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J231" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K231" t="n">
         <v>0</v>
       </c>
       <c r="L231" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M231" t="n">
         <v>0</v>
@@ -9972,7 +9984,7 @@
     <row r="232">
       <c r="A232" s="1" t="inlineStr">
         <is>
-          <t>線材</t>
+          <t>線上遊戲業</t>
         </is>
       </c>
       <c r="B232" t="inlineStr"/>
@@ -9983,37 +9995,37 @@
         <v>0</v>
       </c>
       <c r="E232" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F232" t="n">
         <v>0</v>
       </c>
       <c r="G232" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H232" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I232" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J232" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K232" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L232" t="n">
         <v>0</v>
       </c>
       <c r="M232" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" s="1" t="inlineStr">
         <is>
-          <t>線材盤元</t>
+          <t>線材</t>
         </is>
       </c>
       <c r="B233" t="inlineStr"/>
@@ -10021,22 +10033,22 @@
         <v>0</v>
       </c>
       <c r="D233" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E233" t="n">
         <v>0</v>
       </c>
       <c r="F233" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G233" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H233" t="n">
         <v>0</v>
       </c>
       <c r="I233" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J233" t="n">
         <v>0</v>
@@ -10045,7 +10057,7 @@
         <v>0</v>
       </c>
       <c r="L233" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M233" t="n">
         <v>0</v>
@@ -10054,15 +10066,15 @@
     <row r="234">
       <c r="A234" s="1" t="inlineStr">
         <is>
-          <t>織布</t>
+          <t>線材盤元</t>
         </is>
       </c>
       <c r="B234" t="inlineStr"/>
       <c r="C234" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D234" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E234" t="n">
         <v>0</v>
@@ -10071,10 +10083,10 @@
         <v>0</v>
       </c>
       <c r="G234" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H234" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I234" t="n">
         <v>0</v>
@@ -10095,12 +10107,12 @@
     <row r="235">
       <c r="A235" s="1" t="inlineStr">
         <is>
-          <t>聚亞醯胺樹脂</t>
+          <t>織布</t>
         </is>
       </c>
       <c r="B235" t="inlineStr"/>
       <c r="C235" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D235" t="n">
         <v>0</v>
@@ -10109,13 +10121,13 @@
         <v>0</v>
       </c>
       <c r="F235" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G235" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H235" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I235" t="n">
         <v>0</v>
@@ -10136,7 +10148,7 @@
     <row r="236">
       <c r="A236" s="1" t="inlineStr">
         <is>
-          <t>背光模組</t>
+          <t>聚亞醯胺樹脂</t>
         </is>
       </c>
       <c r="B236" t="inlineStr"/>
@@ -10153,7 +10165,7 @@
         <v>0</v>
       </c>
       <c r="G236" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H236" t="n">
         <v>0</v>
@@ -10177,10 +10189,12 @@
     <row r="237">
       <c r="A237" s="1" t="inlineStr">
         <is>
-          <t>背光源(發光二極體、冷陰極管)</t>
-        </is>
-      </c>
-      <c r="B237" t="inlineStr"/>
+          <t>背光模組</t>
+        </is>
+      </c>
+      <c r="B237" t="n">
+        <v>0</v>
+      </c>
       <c r="C237" t="n">
         <v>0</v>
       </c>
@@ -10191,19 +10205,19 @@
         <v>0</v>
       </c>
       <c r="F237" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G237" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H237" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I237" t="n">
         <v>0</v>
       </c>
       <c r="J237" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K237" t="n">
         <v>0</v>
@@ -10218,7 +10232,7 @@
     <row r="238">
       <c r="A238" s="1" t="inlineStr">
         <is>
-          <t>能源管理服務</t>
+          <t>背光源(發光二極體、冷陰極管)</t>
         </is>
       </c>
       <c r="B238" t="inlineStr"/>
@@ -10229,22 +10243,22 @@
         <v>0</v>
       </c>
       <c r="E238" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F238" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G238" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H238" t="n">
         <v>0</v>
       </c>
       <c r="I238" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J238" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K238" t="n">
         <v>0</v>
@@ -10253,13 +10267,13 @@
         <v>0</v>
       </c>
       <c r="M238" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" s="1" t="inlineStr">
         <is>
-          <t>膠材</t>
+          <t>能源管理服務</t>
         </is>
       </c>
       <c r="B239" t="inlineStr"/>
@@ -10273,16 +10287,16 @@
         <v>0</v>
       </c>
       <c r="F239" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G239" t="n">
         <v>0</v>
       </c>
       <c r="H239" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I239" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J239" t="n">
         <v>0</v>
@@ -10291,7 +10305,7 @@
         <v>0</v>
       </c>
       <c r="L239" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M239" t="n">
         <v>0</v>
@@ -10300,7 +10314,7 @@
     <row r="240">
       <c r="A240" s="1" t="inlineStr">
         <is>
-          <t>臨床實驗、移植技術、疾病治療</t>
+          <t>膠材</t>
         </is>
       </c>
       <c r="B240" t="inlineStr"/>
@@ -10317,7 +10331,7 @@
         <v>0</v>
       </c>
       <c r="G240" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H240" t="n">
         <v>0</v>
@@ -10341,7 +10355,7 @@
     <row r="241">
       <c r="A241" s="1" t="inlineStr">
         <is>
-          <t>自動化機台</t>
+          <t>臨床實驗、移植技術、疾病治療</t>
         </is>
       </c>
       <c r="B241" t="inlineStr"/>
@@ -10376,13 +10390,13 @@
         <v>0</v>
       </c>
       <c r="M241" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" s="1" t="inlineStr">
         <is>
-          <t>自動售票機</t>
+          <t>自動化機台</t>
         </is>
       </c>
       <c r="B242" t="inlineStr"/>
@@ -10414,7 +10428,7 @@
         <v>0</v>
       </c>
       <c r="L242" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M242" t="n">
         <v>0</v>
@@ -10423,7 +10437,7 @@
     <row r="243">
       <c r="A243" s="1" t="inlineStr">
         <is>
-          <t>自動販賣機</t>
+          <t>自動售票機</t>
         </is>
       </c>
       <c r="B243" t="inlineStr"/>
@@ -10464,7 +10478,7 @@
     <row r="244">
       <c r="A244" s="1" t="inlineStr">
         <is>
-          <t>自有產品(服務)銷售</t>
+          <t>自動販賣機</t>
         </is>
       </c>
       <c r="B244" t="inlineStr"/>
@@ -10475,13 +10489,13 @@
         <v>0</v>
       </c>
       <c r="E244" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F244" t="n">
         <v>0</v>
       </c>
       <c r="G244" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H244" t="n">
         <v>0</v>
@@ -10505,7 +10519,7 @@
     <row r="245">
       <c r="A245" s="1" t="inlineStr">
         <is>
-          <t>自然語言處理</t>
+          <t>自有產品(服務)銷售</t>
         </is>
       </c>
       <c r="B245" t="inlineStr"/>
@@ -10513,22 +10527,22 @@
         <v>0</v>
       </c>
       <c r="D245" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E245" t="n">
         <v>0</v>
       </c>
       <c r="F245" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G245" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H245" t="n">
         <v>0</v>
       </c>
       <c r="I245" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J245" t="n">
         <v>0</v>
@@ -10546,7 +10560,7 @@
     <row r="246">
       <c r="A246" s="1" t="inlineStr">
         <is>
-          <t>藍寶石晶圓/晶片</t>
+          <t>自然語言處理</t>
         </is>
       </c>
       <c r="B246" t="inlineStr"/>
@@ -10560,7 +10574,7 @@
         <v>0</v>
       </c>
       <c r="F246" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G246" t="n">
         <v>0</v>
@@ -10587,26 +10601,24 @@
     <row r="247">
       <c r="A247" s="1" t="inlineStr">
         <is>
-          <t>藥品代理銷售及通路</t>
-        </is>
-      </c>
-      <c r="B247" t="n">
-        <v>0</v>
-      </c>
+          <t>藍寶石晶圓/晶片</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr"/>
       <c r="C247" t="n">
         <v>0</v>
       </c>
       <c r="D247" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E247" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F247" t="n">
         <v>0</v>
       </c>
       <c r="G247" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H247" t="n">
         <v>0</v>
@@ -10630,21 +10642,21 @@
     <row r="248">
       <c r="A248" s="1" t="inlineStr">
         <is>
-          <t>處理器/IC</t>
+          <t>藥品代理銷售及通路</t>
         </is>
       </c>
       <c r="B248" t="inlineStr"/>
       <c r="C248" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D248" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E248" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F248" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G248" t="n">
         <v>0</v>
@@ -10671,10 +10683,12 @@
     <row r="249">
       <c r="A249" s="1" t="inlineStr">
         <is>
-          <t>虛擬化軟體</t>
-        </is>
-      </c>
-      <c r="B249" t="inlineStr"/>
+          <t>處理器/IC</t>
+        </is>
+      </c>
+      <c r="B249" t="n">
+        <v>0</v>
+      </c>
       <c r="C249" t="n">
         <v>0</v>
       </c>
@@ -10682,16 +10696,16 @@
         <v>0</v>
       </c>
       <c r="E249" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F249" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G249" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H249" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I249" t="n">
         <v>0</v>
@@ -10712,7 +10726,7 @@
     <row r="250">
       <c r="A250" s="1" t="inlineStr">
         <is>
-          <t>螺絲螺帽</t>
+          <t>虛擬化軟體</t>
         </is>
       </c>
       <c r="B250" t="inlineStr"/>
@@ -10720,16 +10734,16 @@
         <v>0</v>
       </c>
       <c r="D250" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E250" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F250" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G250" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H250" t="n">
         <v>0</v>
@@ -10753,7 +10767,7 @@
     <row r="251">
       <c r="A251" s="1" t="inlineStr">
         <is>
-          <t>行動安全</t>
+          <t>螺絲螺帽</t>
         </is>
       </c>
       <c r="B251" t="inlineStr"/>
@@ -10770,13 +10784,13 @@
         <v>0</v>
       </c>
       <c r="G251" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H251" t="n">
         <v>0</v>
       </c>
       <c r="I251" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J251" t="n">
         <v>0</v>
@@ -10794,7 +10808,7 @@
     <row r="252">
       <c r="A252" s="1" t="inlineStr">
         <is>
-          <t>行銷廣告服務</t>
+          <t>行動安全</t>
         </is>
       </c>
       <c r="B252" t="inlineStr"/>
@@ -10808,13 +10822,13 @@
         <v>0</v>
       </c>
       <c r="F252" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G252" t="n">
         <v>0</v>
       </c>
       <c r="H252" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I252" t="n">
         <v>0</v>
@@ -10835,7 +10849,7 @@
     <row r="253">
       <c r="A253" s="1" t="inlineStr">
         <is>
-          <t>衛星定位系統</t>
+          <t>行銷廣告服務</t>
         </is>
       </c>
       <c r="B253" t="inlineStr"/>
@@ -10876,7 +10890,7 @@
     <row r="254">
       <c r="A254" s="1" t="inlineStr">
         <is>
-          <t>裁剪加工</t>
+          <t>衛星定位系統</t>
         </is>
       </c>
       <c r="B254" t="inlineStr"/>
@@ -10902,7 +10916,7 @@
         <v>0</v>
       </c>
       <c r="J254" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K254" t="n">
         <v>0</v>
@@ -10917,7 +10931,7 @@
     <row r="255">
       <c r="A255" s="1" t="inlineStr">
         <is>
-          <t>裝潢業</t>
+          <t>裁剪加工</t>
         </is>
       </c>
       <c r="B255" t="inlineStr"/>
@@ -10928,7 +10942,7 @@
         <v>0</v>
       </c>
       <c r="E255" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F255" t="n">
         <v>0</v>
@@ -10940,7 +10954,7 @@
         <v>0</v>
       </c>
       <c r="I255" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J255" t="n">
         <v>0</v>
@@ -10958,7 +10972,7 @@
     <row r="256">
       <c r="A256" s="1" t="inlineStr">
         <is>
-          <t>裝置/器材零組件</t>
+          <t>裝潢業</t>
         </is>
       </c>
       <c r="B256" t="inlineStr"/>
@@ -10966,7 +10980,7 @@
         <v>0</v>
       </c>
       <c r="D256" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E256" t="n">
         <v>0</v>
@@ -10999,7 +11013,7 @@
     <row r="257">
       <c r="A257" s="1" t="inlineStr">
         <is>
-          <t>裝置/器材顯示器</t>
+          <t>裝置/器材零組件</t>
         </is>
       </c>
       <c r="B257" t="inlineStr"/>
@@ -11040,7 +11054,7 @@
     <row r="258">
       <c r="A258" s="1" t="inlineStr">
         <is>
-          <t>製管</t>
+          <t>裝置/器材顯示器</t>
         </is>
       </c>
       <c r="B258" t="inlineStr"/>
@@ -11057,7 +11071,7 @@
         <v>0</v>
       </c>
       <c r="G258" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H258" t="n">
         <v>0</v>
@@ -11081,12 +11095,12 @@
     <row r="259">
       <c r="A259" s="1" t="inlineStr">
         <is>
-          <t>製造商</t>
+          <t>製管</t>
         </is>
       </c>
       <c r="B259" t="inlineStr"/>
       <c r="C259" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D259" t="n">
         <v>0</v>
@@ -11095,10 +11109,10 @@
         <v>0</v>
       </c>
       <c r="F259" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G259" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H259" t="n">
         <v>0</v>
@@ -11122,7 +11136,7 @@
     <row r="260">
       <c r="A260" s="1" t="inlineStr">
         <is>
-          <t>觸控面板</t>
+          <t>製造商</t>
         </is>
       </c>
       <c r="B260" t="inlineStr"/>
@@ -11136,7 +11150,7 @@
         <v>0</v>
       </c>
       <c r="F260" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G260" t="n">
         <v>0</v>
@@ -11163,33 +11177,33 @@
     <row r="261">
       <c r="A261" s="1" t="inlineStr">
         <is>
-          <t>記憶體</t>
+          <t>觸控面板</t>
         </is>
       </c>
       <c r="B261" t="inlineStr"/>
       <c r="C261" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D261" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E261" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="F261" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G261" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H261" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I261" t="n">
         <v>0</v>
       </c>
       <c r="J261" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K261" t="n">
         <v>0</v>
@@ -11204,31 +11218,31 @@
     <row r="262">
       <c r="A262" s="1" t="inlineStr">
         <is>
-          <t>設備安裝服務</t>
+          <t>記憶體</t>
         </is>
       </c>
       <c r="B262" t="inlineStr"/>
       <c r="C262" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D262" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="E262" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F262" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G262" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H262" t="n">
+        <v>0</v>
+      </c>
+      <c r="I262" t="n">
         <v>2</v>
       </c>
-      <c r="I262" t="n">
-        <v>0</v>
-      </c>
       <c r="J262" t="n">
         <v>0</v>
       </c>
@@ -11236,16 +11250,16 @@
         <v>0</v>
       </c>
       <c r="L262" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M262" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" s="1" t="inlineStr">
         <is>
-          <t>設備管理軟體</t>
+          <t>設備安裝服務</t>
         </is>
       </c>
       <c r="B263" t="inlineStr"/>
@@ -11253,7 +11267,7 @@
         <v>0</v>
       </c>
       <c r="D263" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E263" t="n">
         <v>1</v>
@@ -11265,28 +11279,28 @@
         <v>2</v>
       </c>
       <c r="H263" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I263" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J263" t="n">
         <v>0</v>
       </c>
       <c r="K263" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L263" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M263" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" s="1" t="inlineStr">
         <is>
-          <t>設備維護</t>
+          <t>設備管理軟體</t>
         </is>
       </c>
       <c r="B264" t="inlineStr"/>
@@ -11294,19 +11308,19 @@
         <v>0</v>
       </c>
       <c r="D264" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E264" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F264" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G264" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H264" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I264" t="n">
         <v>0</v>
@@ -11318,7 +11332,7 @@
         <v>0</v>
       </c>
       <c r="L264" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M264" t="n">
         <v>0</v>
@@ -11327,12 +11341,10 @@
     <row r="265">
       <c r="A265" s="1" t="inlineStr">
         <is>
-          <t>證券業</t>
-        </is>
-      </c>
-      <c r="B265" t="n">
-        <v>0</v>
-      </c>
+          <t>設備維護</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr"/>
       <c r="C265" t="n">
         <v>0</v>
       </c>
@@ -11370,10 +11382,12 @@
     <row r="266">
       <c r="A266" s="1" t="inlineStr">
         <is>
-          <t>變壓器</t>
-        </is>
-      </c>
-      <c r="B266" t="inlineStr"/>
+          <t>證券業</t>
+        </is>
+      </c>
+      <c r="B266" t="n">
+        <v>0</v>
+      </c>
       <c r="C266" t="n">
         <v>0</v>
       </c>
@@ -11402,7 +11416,7 @@
         <v>0</v>
       </c>
       <c r="L266" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M266" t="n">
         <v>0</v>
@@ -11411,12 +11425,10 @@
     <row r="267">
       <c r="A267" s="1" t="inlineStr">
         <is>
-          <t>貨櫃航運</t>
-        </is>
-      </c>
-      <c r="B267" t="n">
-        <v>0</v>
-      </c>
+          <t>變壓器</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr"/>
       <c r="C267" t="n">
         <v>0</v>
       </c>
@@ -11442,7 +11454,7 @@
         <v>0</v>
       </c>
       <c r="K267" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L267" t="n">
         <v>0</v>
@@ -11454,12 +11466,10 @@
     <row r="268">
       <c r="A268" s="1" t="inlineStr">
         <is>
-          <t>貨櫃運輸集散及倉儲</t>
-        </is>
-      </c>
-      <c r="B268" t="n">
-        <v>0</v>
-      </c>
+          <t>貨櫃航運</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr"/>
       <c r="C268" t="n">
         <v>0</v>
       </c>
@@ -11497,12 +11507,12 @@
     <row r="269">
       <c r="A269" s="1" t="inlineStr">
         <is>
-          <t>貿易商、代理商、經銷商</t>
+          <t>貨櫃運輸集散及倉儲</t>
         </is>
       </c>
       <c r="B269" t="inlineStr"/>
       <c r="C269" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D269" t="n">
         <v>0</v>
@@ -11520,7 +11530,7 @@
         <v>0</v>
       </c>
       <c r="I269" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J269" t="n">
         <v>0</v>
@@ -11532,13 +11542,13 @@
         <v>0</v>
       </c>
       <c r="M269" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" s="1" t="inlineStr">
         <is>
-          <t>資安審計</t>
+          <t>貿易商、代理商、經銷商</t>
         </is>
       </c>
       <c r="B270" t="inlineStr"/>
@@ -11558,7 +11568,7 @@
         <v>0</v>
       </c>
       <c r="H270" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I270" t="n">
         <v>0</v>
@@ -11570,7 +11580,7 @@
         <v>0</v>
       </c>
       <c r="L270" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M270" t="n">
         <v>0</v>
@@ -11579,7 +11589,7 @@
     <row r="271">
       <c r="A271" s="1" t="inlineStr">
         <is>
-          <t>資安治理</t>
+          <t>資安審計</t>
         </is>
       </c>
       <c r="B271" t="inlineStr"/>
@@ -11596,16 +11606,16 @@
         <v>0</v>
       </c>
       <c r="G271" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H271" t="n">
         <v>0</v>
       </c>
       <c r="I271" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J271" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K271" t="n">
         <v>0</v>
@@ -11620,7 +11630,7 @@
     <row r="272">
       <c r="A272" s="1" t="inlineStr">
         <is>
-          <t>資安營運管理服務</t>
+          <t>資安治理</t>
         </is>
       </c>
       <c r="B272" t="inlineStr"/>
@@ -11634,13 +11644,13 @@
         <v>0</v>
       </c>
       <c r="F272" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G272" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H272" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I272" t="n">
         <v>1</v>
@@ -11661,7 +11671,7 @@
     <row r="273">
       <c r="A273" s="1" t="inlineStr">
         <is>
-          <t>資安防護能力分析與鑑識服務</t>
+          <t>資安營運管理服務</t>
         </is>
       </c>
       <c r="B273" t="inlineStr"/>
@@ -11672,22 +11682,22 @@
         <v>0</v>
       </c>
       <c r="E273" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F273" t="n">
         <v>1</v>
       </c>
       <c r="G273" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H273" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I273" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J273" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K273" t="n">
         <v>0</v>
@@ -11702,7 +11712,7 @@
     <row r="274">
       <c r="A274" s="1" t="inlineStr">
         <is>
-          <t>資安防護軟體</t>
+          <t>資安防護能力分析與鑑識服務</t>
         </is>
       </c>
       <c r="B274" t="inlineStr"/>
@@ -11716,10 +11726,10 @@
         <v>1</v>
       </c>
       <c r="F274" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G274" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H274" t="n">
         <v>1</v>
@@ -11743,7 +11753,7 @@
     <row r="275">
       <c r="A275" s="1" t="inlineStr">
         <is>
-          <t>資安顧問服務</t>
+          <t>資安防護軟體</t>
         </is>
       </c>
       <c r="B275" t="inlineStr"/>
@@ -11751,25 +11761,25 @@
         <v>0</v>
       </c>
       <c r="D275" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E275" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F275" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G275" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H275" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I275" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J275" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K275" t="n">
         <v>0</v>
@@ -11784,7 +11794,7 @@
     <row r="276">
       <c r="A276" s="1" t="inlineStr">
         <is>
-          <t>資料分析處理服務</t>
+          <t>資安顧問服務</t>
         </is>
       </c>
       <c r="B276" t="inlineStr"/>
@@ -11795,19 +11805,19 @@
         <v>0</v>
       </c>
       <c r="E276" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F276" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G276" t="n">
         <v>0</v>
       </c>
       <c r="H276" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I276" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J276" t="n">
         <v>0</v>
@@ -11825,7 +11835,7 @@
     <row r="277">
       <c r="A277" s="1" t="inlineStr">
         <is>
-          <t>資料安全</t>
+          <t>資料分析處理服務</t>
         </is>
       </c>
       <c r="B277" t="inlineStr"/>
@@ -11833,22 +11843,22 @@
         <v>0</v>
       </c>
       <c r="D277" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E277" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F277" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G277" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H277" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I277" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J277" t="n">
         <v>0</v>
@@ -11866,18 +11876,18 @@
     <row r="278">
       <c r="A278" s="1" t="inlineStr">
         <is>
-          <t>資料庫</t>
+          <t>資料安全</t>
         </is>
       </c>
       <c r="B278" t="inlineStr"/>
       <c r="C278" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D278" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E278" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F278" t="n">
         <v>1</v>
@@ -11907,7 +11917,7 @@
     <row r="279">
       <c r="A279" s="1" t="inlineStr">
         <is>
-          <t>資料聚合</t>
+          <t>資料庫</t>
         </is>
       </c>
       <c r="B279" t="inlineStr"/>
@@ -11915,16 +11925,16 @@
         <v>0</v>
       </c>
       <c r="D279" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E279" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F279" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G279" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H279" t="n">
         <v>0</v>
@@ -11948,7 +11958,7 @@
     <row r="280">
       <c r="A280" s="1" t="inlineStr">
         <is>
-          <t>資料處理</t>
+          <t>資料聚合</t>
         </is>
       </c>
       <c r="B280" t="inlineStr"/>
@@ -11962,19 +11972,19 @@
         <v>0</v>
       </c>
       <c r="F280" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G280" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H280" t="n">
         <v>0</v>
       </c>
       <c r="I280" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J280" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K280" t="n">
         <v>0</v>
@@ -11989,12 +11999,10 @@
     <row r="281">
       <c r="A281" s="1" t="inlineStr">
         <is>
-          <t>資料處理服務</t>
-        </is>
-      </c>
-      <c r="B281" t="n">
-        <v>0</v>
-      </c>
+          <t>資料處理</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr"/>
       <c r="C281" t="n">
         <v>0</v>
       </c>
@@ -12002,19 +12010,19 @@
         <v>0</v>
       </c>
       <c r="E281" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F281" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G281" t="n">
         <v>0</v>
       </c>
       <c r="H281" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I281" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J281" t="n">
         <v>0</v>
@@ -12032,7 +12040,7 @@
     <row r="282">
       <c r="A282" s="1" t="inlineStr">
         <is>
-          <t>資服</t>
+          <t>資料處理服務</t>
         </is>
       </c>
       <c r="B282" t="inlineStr"/>
@@ -12073,7 +12081,7 @@
     <row r="283">
       <c r="A283" s="1" t="inlineStr">
         <is>
-          <t>資訊收集設備</t>
+          <t>資服</t>
         </is>
       </c>
       <c r="B283" t="inlineStr"/>
@@ -12114,7 +12122,7 @@
     <row r="284">
       <c r="A284" s="1" t="inlineStr">
         <is>
-          <t>資訊系統建置服務</t>
+          <t>資訊收集設備</t>
         </is>
       </c>
       <c r="B284" t="inlineStr"/>
@@ -12155,7 +12163,7 @@
     <row r="285">
       <c r="A285" s="1" t="inlineStr">
         <is>
-          <t>資訊聚合</t>
+          <t>資訊系統建置服務</t>
         </is>
       </c>
       <c r="B285" t="inlineStr"/>
@@ -12196,7 +12204,7 @@
     <row r="286">
       <c r="A286" s="1" t="inlineStr">
         <is>
-          <t>身分認證與訪問管理</t>
+          <t>資訊聚合</t>
         </is>
       </c>
       <c r="B286" t="inlineStr"/>
@@ -12204,22 +12212,22 @@
         <v>0</v>
       </c>
       <c r="D286" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E286" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F286" t="n">
         <v>0</v>
       </c>
       <c r="G286" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H286" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I286" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J286" t="n">
         <v>0</v>
@@ -12237,7 +12245,7 @@
     <row r="287">
       <c r="A287" s="1" t="inlineStr">
         <is>
-          <t>車燈</t>
+          <t>身分認證與訪問管理</t>
         </is>
       </c>
       <c r="B287" t="inlineStr"/>
@@ -12245,19 +12253,19 @@
         <v>1</v>
       </c>
       <c r="D287" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E287" t="n">
         <v>0</v>
       </c>
       <c r="F287" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G287" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H287" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I287" t="n">
         <v>0</v>
@@ -12278,21 +12286,21 @@
     <row r="288">
       <c r="A288" s="1" t="inlineStr">
         <is>
-          <t>車用機械傳動設備及零配件</t>
+          <t>車燈</t>
         </is>
       </c>
       <c r="B288" t="inlineStr"/>
       <c r="C288" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D288" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E288" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F288" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G288" t="n">
         <v>0</v>
@@ -12313,24 +12321,24 @@
         <v>0</v>
       </c>
       <c r="M288" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" s="1" t="inlineStr">
         <is>
-          <t>軟性電路板</t>
+          <t>車用機械傳動設備及零配件</t>
         </is>
       </c>
       <c r="B289" t="inlineStr"/>
       <c r="C289" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D289" t="n">
         <v>0</v>
       </c>
       <c r="E289" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F289" t="n">
         <v>0</v>
@@ -12351,7 +12359,7 @@
         <v>0</v>
       </c>
       <c r="L289" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M289" t="n">
         <v>0</v>
@@ -12360,7 +12368,7 @@
     <row r="290">
       <c r="A290" s="1" t="inlineStr">
         <is>
-          <t>軟體開發</t>
+          <t>軟性電路板</t>
         </is>
       </c>
       <c r="B290" t="inlineStr"/>
@@ -12401,7 +12409,7 @@
     <row r="291">
       <c r="A291" s="1" t="inlineStr">
         <is>
-          <t>軟體開發工具</t>
+          <t>軟體開發</t>
         </is>
       </c>
       <c r="B291" t="inlineStr"/>
@@ -12418,7 +12426,7 @@
         <v>0</v>
       </c>
       <c r="G291" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H291" t="n">
         <v>0</v>
@@ -12442,7 +12450,7 @@
     <row r="292">
       <c r="A292" s="1" t="inlineStr">
         <is>
-          <t>輪胎</t>
+          <t>軟體開發工具</t>
         </is>
       </c>
       <c r="B292" t="inlineStr"/>
@@ -12456,7 +12464,7 @@
         <v>0</v>
       </c>
       <c r="F292" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G292" t="n">
         <v>0</v>
@@ -12483,7 +12491,7 @@
     <row r="293">
       <c r="A293" s="1" t="inlineStr">
         <is>
-          <t>輸出入模組/介面卡</t>
+          <t>輪胎</t>
         </is>
       </c>
       <c r="B293" t="inlineStr"/>
@@ -12491,16 +12499,16 @@
         <v>0</v>
       </c>
       <c r="D293" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E293" t="n">
         <v>0</v>
       </c>
       <c r="F293" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G293" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H293" t="n">
         <v>0</v>
@@ -12524,21 +12532,21 @@
     <row r="294">
       <c r="A294" s="1" t="inlineStr">
         <is>
-          <t>輸送機械及零配件</t>
+          <t>輸出入模組/介面卡</t>
         </is>
       </c>
       <c r="B294" t="inlineStr"/>
       <c r="C294" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D294" t="n">
         <v>0</v>
       </c>
       <c r="E294" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F294" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G294" t="n">
         <v>0</v>
@@ -12559,13 +12567,13 @@
         <v>0</v>
       </c>
       <c r="M294" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" s="1" t="inlineStr">
         <is>
-          <t>農業科技業</t>
+          <t>輸送機械及零配件</t>
         </is>
       </c>
       <c r="B295" t="inlineStr"/>
@@ -12585,7 +12593,7 @@
         <v>0</v>
       </c>
       <c r="H295" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I295" t="n">
         <v>0</v>
@@ -12597,7 +12605,7 @@
         <v>0</v>
       </c>
       <c r="L295" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M295" t="n">
         <v>0</v>
@@ -12606,7 +12614,7 @@
     <row r="296">
       <c r="A296" s="1" t="inlineStr">
         <is>
-          <t>農藥</t>
+          <t>農業科技業</t>
         </is>
       </c>
       <c r="B296" t="inlineStr"/>
@@ -12623,7 +12631,7 @@
         <v>0</v>
       </c>
       <c r="G296" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H296" t="n">
         <v>0</v>
@@ -12647,7 +12655,7 @@
     <row r="297">
       <c r="A297" s="1" t="inlineStr">
         <is>
-          <t>近眼顯示(Dear-Eye Display)</t>
+          <t>農藥</t>
         </is>
       </c>
       <c r="B297" t="inlineStr"/>
@@ -12688,7 +12696,7 @@
     <row r="298">
       <c r="A298" s="1" t="inlineStr">
         <is>
-          <t>通訊</t>
+          <t>近眼顯示(Dear-Eye Display)</t>
         </is>
       </c>
       <c r="B298" t="inlineStr"/>
@@ -12729,7 +12737,7 @@
     <row r="299">
       <c r="A299" s="1" t="inlineStr">
         <is>
-          <t>通訊服務</t>
+          <t>通訊</t>
         </is>
       </c>
       <c r="B299" t="inlineStr"/>
@@ -12770,12 +12778,10 @@
     <row r="300">
       <c r="A300" s="1" t="inlineStr">
         <is>
-          <t>通路經銷</t>
-        </is>
-      </c>
-      <c r="B300" t="n">
-        <v>0</v>
-      </c>
+          <t>通訊服務</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr"/>
       <c r="C300" t="n">
         <v>0</v>
       </c>
@@ -12786,16 +12792,16 @@
         <v>0</v>
       </c>
       <c r="F300" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G300" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H300" t="n">
         <v>0</v>
       </c>
       <c r="I300" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J300" t="n">
         <v>0</v>
@@ -12813,35 +12819,33 @@
     <row r="301">
       <c r="A301" s="1" t="inlineStr">
         <is>
-          <t>連接器設計、組裝及製造</t>
-        </is>
-      </c>
-      <c r="B301" t="n">
-        <v>0</v>
-      </c>
+          <t>通路經銷</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr"/>
       <c r="C301" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D301" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E301" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F301" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G301" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H301" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I301" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J301" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K301" t="n">
         <v>0</v>
@@ -12850,54 +12854,54 @@
         <v>0</v>
       </c>
       <c r="M301" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" s="1" t="inlineStr">
         <is>
-          <t>連接線</t>
+          <t>連接器設計、組裝及製造</t>
         </is>
       </c>
       <c r="B302" t="inlineStr"/>
       <c r="C302" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D302" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E302" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F302" t="n">
         <v>1</v>
       </c>
       <c r="G302" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H302" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I302" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J302" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K302" t="n">
         <v>0</v>
       </c>
       <c r="L302" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M302" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" s="1" t="inlineStr">
         <is>
-          <t>運動服務/顧問</t>
+          <t>連接線</t>
         </is>
       </c>
       <c r="B303" t="inlineStr"/>
@@ -12905,22 +12909,22 @@
         <v>0</v>
       </c>
       <c r="D303" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E303" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F303" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G303" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H303" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I303" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J303" t="n">
         <v>0</v>
@@ -12929,7 +12933,7 @@
         <v>0</v>
       </c>
       <c r="L303" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M303" t="n">
         <v>0</v>
@@ -12938,7 +12942,7 @@
     <row r="304">
       <c r="A304" s="1" t="inlineStr">
         <is>
-          <t>運動用品</t>
+          <t>運動服務/顧問</t>
         </is>
       </c>
       <c r="B304" t="inlineStr"/>
@@ -12979,7 +12983,7 @@
     <row r="305">
       <c r="A305" s="1" t="inlineStr">
         <is>
-          <t>運動行銷/媒體</t>
+          <t>運動用品</t>
         </is>
       </c>
       <c r="B305" t="inlineStr"/>
@@ -13020,7 +13024,7 @@
     <row r="306">
       <c r="A306" s="1" t="inlineStr">
         <is>
-          <t>運算元件與設備</t>
+          <t>運動行銷/媒體</t>
         </is>
       </c>
       <c r="B306" t="inlineStr"/>
@@ -13031,16 +13035,16 @@
         <v>0</v>
       </c>
       <c r="E306" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F306" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G306" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H306" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I306" t="n">
         <v>0</v>
@@ -13055,13 +13059,13 @@
         <v>0</v>
       </c>
       <c r="M306" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" s="1" t="inlineStr">
         <is>
-          <t>運算設備</t>
+          <t>運算元件與設備</t>
         </is>
       </c>
       <c r="B307" t="inlineStr"/>
@@ -13069,16 +13073,16 @@
         <v>0</v>
       </c>
       <c r="D307" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E307" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F307" t="n">
         <v>1</v>
       </c>
       <c r="G307" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H307" t="n">
         <v>0</v>
@@ -13093,16 +13097,16 @@
         <v>0</v>
       </c>
       <c r="L307" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M307" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" s="1" t="inlineStr">
         <is>
-          <t>運輸工具</t>
+          <t>運算設備</t>
         </is>
       </c>
       <c r="B308" t="inlineStr"/>
@@ -13113,7 +13117,7 @@
         <v>0</v>
       </c>
       <c r="E308" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F308" t="n">
         <v>0</v>
@@ -13134,7 +13138,7 @@
         <v>0</v>
       </c>
       <c r="L308" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M308" t="n">
         <v>0</v>
@@ -13143,7 +13147,7 @@
     <row r="309">
       <c r="A309" s="1" t="inlineStr">
         <is>
-          <t>配電管理設施</t>
+          <t>運輸工具</t>
         </is>
       </c>
       <c r="B309" t="inlineStr"/>
@@ -13163,7 +13167,7 @@
         <v>0</v>
       </c>
       <c r="H309" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I309" t="n">
         <v>0</v>
@@ -13175,16 +13179,16 @@
         <v>0</v>
       </c>
       <c r="L309" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M309" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" s="1" t="inlineStr">
         <is>
-          <t>配電系統</t>
+          <t>配電管理設施</t>
         </is>
       </c>
       <c r="B310" t="inlineStr"/>
@@ -13201,7 +13205,7 @@
         <v>0</v>
       </c>
       <c r="G310" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H310" t="n">
         <v>0</v>
@@ -13213,7 +13217,7 @@
         <v>0</v>
       </c>
       <c r="K310" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L310" t="n">
         <v>1</v>
@@ -13225,7 +13229,7 @@
     <row r="311">
       <c r="A311" s="1" t="inlineStr">
         <is>
-          <t>酚醛樹脂</t>
+          <t>配電系統</t>
         </is>
       </c>
       <c r="B311" t="inlineStr"/>
@@ -13242,10 +13246,10 @@
         <v>0</v>
       </c>
       <c r="G311" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H311" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I311" t="n">
         <v>0</v>
@@ -13254,7 +13258,7 @@
         <v>0</v>
       </c>
       <c r="K311" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L311" t="n">
         <v>0</v>
@@ -13266,20 +13270,18 @@
     <row r="312">
       <c r="A312" s="1" t="inlineStr">
         <is>
-          <t>醫療器材代理銷售及通路</t>
-        </is>
-      </c>
-      <c r="B312" t="n">
-        <v>0</v>
-      </c>
+          <t>酚醛樹脂</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr"/>
       <c r="C312" t="n">
         <v>0</v>
       </c>
       <c r="D312" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E312" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F312" t="n">
         <v>1</v>
@@ -13288,7 +13290,7 @@
         <v>1</v>
       </c>
       <c r="H312" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I312" t="n">
         <v>0</v>
@@ -13303,47 +13305,45 @@
         <v>0</v>
       </c>
       <c r="M312" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" s="1" t="inlineStr">
         <is>
-          <t>醫療器材研發、設計、製造</t>
-        </is>
-      </c>
-      <c r="B313" t="n">
-        <v>0</v>
-      </c>
+          <t>醫療器材代理銷售及通路</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr"/>
       <c r="C313" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D313" t="n">
+        <v>1</v>
+      </c>
+      <c r="E313" t="n">
+        <v>1</v>
+      </c>
+      <c r="F313" t="n">
+        <v>1</v>
+      </c>
+      <c r="G313" t="n">
+        <v>1</v>
+      </c>
+      <c r="H313" t="n">
+        <v>0</v>
+      </c>
+      <c r="I313" t="n">
+        <v>0</v>
+      </c>
+      <c r="J313" t="n">
+        <v>0</v>
+      </c>
+      <c r="K313" t="n">
+        <v>0</v>
+      </c>
+      <c r="L313" t="n">
         <v>2</v>
-      </c>
-      <c r="E313" t="n">
-        <v>2</v>
-      </c>
-      <c r="F313" t="n">
-        <v>0</v>
-      </c>
-      <c r="G313" t="n">
-        <v>1</v>
-      </c>
-      <c r="H313" t="n">
-        <v>0</v>
-      </c>
-      <c r="I313" t="n">
-        <v>0</v>
-      </c>
-      <c r="J313" t="n">
-        <v>1</v>
-      </c>
-      <c r="K313" t="n">
-        <v>0</v>
-      </c>
-      <c r="L313" t="n">
-        <v>0</v>
       </c>
       <c r="M313" t="n">
         <v>1</v>
@@ -13352,21 +13352,23 @@
     <row r="314">
       <c r="A314" s="1" t="inlineStr">
         <is>
-          <t>醫療院所</t>
-        </is>
-      </c>
-      <c r="B314" t="inlineStr"/>
+          <t>醫療器材研發、設計、製造</t>
+        </is>
+      </c>
+      <c r="B314" t="n">
+        <v>0</v>
+      </c>
       <c r="C314" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D314" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E314" t="n">
         <v>0</v>
       </c>
       <c r="F314" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G314" t="n">
         <v>0</v>
@@ -13375,7 +13377,7 @@
         <v>0</v>
       </c>
       <c r="I314" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J314" t="n">
         <v>0</v>
@@ -13384,7 +13386,7 @@
         <v>0</v>
       </c>
       <c r="L314" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M314" t="n">
         <v>0</v>
@@ -13393,7 +13395,7 @@
     <row r="315">
       <c r="A315" s="1" t="inlineStr">
         <is>
-          <t>金屬、塑膠模具</t>
+          <t>醫療院所</t>
         </is>
       </c>
       <c r="B315" t="inlineStr"/>
@@ -13401,22 +13403,22 @@
         <v>0</v>
       </c>
       <c r="D315" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E315" t="n">
         <v>0</v>
       </c>
       <c r="F315" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G315" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H315" t="n">
         <v>0</v>
       </c>
       <c r="I315" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J315" t="n">
         <v>0</v>
@@ -13434,29 +13436,27 @@
     <row r="316">
       <c r="A316" s="1" t="inlineStr">
         <is>
-          <t>金屬加工用機械</t>
-        </is>
-      </c>
-      <c r="B316" t="n">
-        <v>0</v>
-      </c>
+          <t>金屬、塑膠模具</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr"/>
       <c r="C316" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D316" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E316" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F316" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G316" t="n">
         <v>0</v>
       </c>
       <c r="H316" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I316" t="n">
         <v>0</v>
@@ -13477,18 +13477,18 @@
     <row r="317">
       <c r="A317" s="1" t="inlineStr">
         <is>
-          <t>金屬加工處理</t>
+          <t>金屬加工用機械</t>
         </is>
       </c>
       <c r="B317" t="inlineStr"/>
       <c r="C317" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D317" t="n">
         <v>0</v>
       </c>
       <c r="E317" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F317" t="n">
         <v>0</v>
@@ -13503,7 +13503,7 @@
         <v>0</v>
       </c>
       <c r="J317" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K317" t="n">
         <v>0</v>
@@ -13518,7 +13518,7 @@
     <row r="318">
       <c r="A318" s="1" t="inlineStr">
         <is>
-          <t>金屬材料</t>
+          <t>金屬加工處理</t>
         </is>
       </c>
       <c r="B318" t="inlineStr"/>
@@ -13526,7 +13526,7 @@
         <v>0</v>
       </c>
       <c r="D318" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E318" t="n">
         <v>0</v>
@@ -13541,7 +13541,7 @@
         <v>0</v>
       </c>
       <c r="I318" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J318" t="n">
         <v>0</v>
@@ -13559,7 +13559,7 @@
     <row r="319">
       <c r="A319" s="1" t="inlineStr">
         <is>
-          <t>金屬製品</t>
+          <t>金屬材料</t>
         </is>
       </c>
       <c r="B319" t="inlineStr"/>
@@ -13570,7 +13570,7 @@
         <v>0</v>
       </c>
       <c r="E319" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F319" t="n">
         <v>0</v>
@@ -13600,17 +13600,15 @@
     <row r="320">
       <c r="A320" s="1" t="inlineStr">
         <is>
-          <t>金控業/銀行業/保險業</t>
-        </is>
-      </c>
-      <c r="B320" t="n">
-        <v>0</v>
-      </c>
+          <t>金屬製品</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr"/>
       <c r="C320" t="n">
         <v>0</v>
       </c>
       <c r="D320" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E320" t="n">
         <v>0</v>
@@ -13643,10 +13641,12 @@
     <row r="321">
       <c r="A321" s="1" t="inlineStr">
         <is>
-          <t>金流串接處理服務</t>
-        </is>
-      </c>
-      <c r="B321" t="inlineStr"/>
+          <t>金控業/銀行業/保險業</t>
+        </is>
+      </c>
+      <c r="B321" t="n">
+        <v>0</v>
+      </c>
       <c r="C321" t="n">
         <v>0</v>
       </c>
@@ -13684,7 +13684,7 @@
     <row r="322">
       <c r="A322" s="1" t="inlineStr">
         <is>
-          <t>金融提款機(ATM)</t>
+          <t>金流串接處理服務</t>
         </is>
       </c>
       <c r="B322" t="inlineStr"/>
@@ -13725,7 +13725,7 @@
     <row r="323">
       <c r="A323" s="1" t="inlineStr">
         <is>
-          <t>鈑金</t>
+          <t>金融提款機(ATM)</t>
         </is>
       </c>
       <c r="B323" t="inlineStr"/>
@@ -13766,12 +13766,12 @@
     <row r="324">
       <c r="A324" s="1" t="inlineStr">
         <is>
-          <t>銅箔</t>
+          <t>鈑金</t>
         </is>
       </c>
       <c r="B324" t="inlineStr"/>
       <c r="C324" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D324" t="n">
         <v>0</v>
@@ -13780,13 +13780,13 @@
         <v>0</v>
       </c>
       <c r="F324" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G324" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H324" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I324" t="n">
         <v>0</v>
@@ -13801,13 +13801,13 @@
         <v>0</v>
       </c>
       <c r="M324" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" s="1" t="inlineStr">
         <is>
-          <t>銅箔基板</t>
+          <t>銅箔</t>
         </is>
       </c>
       <c r="B325" t="inlineStr"/>
@@ -13818,16 +13818,16 @@
         <v>0</v>
       </c>
       <c r="E325" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F325" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G325" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H325" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I325" t="n">
         <v>0</v>
@@ -13839,21 +13839,21 @@
         <v>0</v>
       </c>
       <c r="L325" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M325" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" s="1" t="inlineStr">
         <is>
-          <t>銷售、進出口業務</t>
+          <t>銅箔基板</t>
         </is>
       </c>
       <c r="B326" t="inlineStr"/>
       <c r="C326" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D326" t="n">
         <v>0</v>
@@ -13862,16 +13862,16 @@
         <v>0</v>
       </c>
       <c r="F326" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G326" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H326" t="n">
         <v>0</v>
       </c>
       <c r="I326" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J326" t="n">
         <v>0</v>
@@ -13880,7 +13880,7 @@
         <v>0</v>
       </c>
       <c r="L326" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M326" t="n">
         <v>0</v>
@@ -13889,7 +13889,7 @@
     <row r="327">
       <c r="A327" s="1" t="inlineStr">
         <is>
-          <t>鋁合金鋼圈</t>
+          <t>銷售、進出口業務</t>
         </is>
       </c>
       <c r="B327" t="inlineStr"/>
@@ -13909,7 +13909,7 @@
         <v>0</v>
       </c>
       <c r="H327" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I327" t="n">
         <v>0</v>
@@ -13930,7 +13930,7 @@
     <row r="328">
       <c r="A328" s="1" t="inlineStr">
         <is>
-          <t>鋰電池材料</t>
+          <t>鋁合金鋼圈</t>
         </is>
       </c>
       <c r="B328" t="inlineStr"/>
@@ -13953,25 +13953,25 @@
         <v>0</v>
       </c>
       <c r="I328" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J328" t="n">
         <v>0</v>
       </c>
       <c r="K328" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L328" t="n">
         <v>0</v>
       </c>
       <c r="M328" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="329">
       <c r="A329" s="1" t="inlineStr">
         <is>
-          <t>鋼材</t>
+          <t>鋰電池材料</t>
         </is>
       </c>
       <c r="B329" t="inlineStr"/>
@@ -13988,22 +13988,22 @@
         <v>0</v>
       </c>
       <c r="G329" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H329" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I329" t="n">
         <v>0</v>
       </c>
       <c r="J329" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K329" t="n">
         <v>0</v>
       </c>
       <c r="L329" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M329" t="n">
         <v>0</v>
@@ -14012,7 +14012,7 @@
     <row r="330">
       <c r="A330" s="1" t="inlineStr">
         <is>
-          <t>鋼筋</t>
+          <t>鋼材</t>
         </is>
       </c>
       <c r="B330" t="inlineStr"/>
@@ -14053,12 +14053,10 @@
     <row r="331">
       <c r="A331" s="1" t="inlineStr">
         <is>
-          <t>鋼線鋼纜</t>
-        </is>
-      </c>
-      <c r="B331" t="n">
-        <v>0</v>
-      </c>
+          <t>鋼筋</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr"/>
       <c r="C331" t="n">
         <v>0</v>
       </c>
@@ -14096,7 +14094,7 @@
     <row r="332">
       <c r="A332" s="1" t="inlineStr">
         <is>
-          <t>鋼胚</t>
+          <t>鋼線鋼纜</t>
         </is>
       </c>
       <c r="B332" t="inlineStr"/>
@@ -14113,7 +14111,7 @@
         <v>0</v>
       </c>
       <c r="G332" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H332" t="n">
         <v>0</v>
@@ -14137,7 +14135,7 @@
     <row r="333">
       <c r="A333" s="1" t="inlineStr">
         <is>
-          <t>鋼鑄鐵元件</t>
+          <t>鋼胚</t>
         </is>
       </c>
       <c r="B333" t="inlineStr"/>
@@ -14163,7 +14161,7 @@
         <v>0</v>
       </c>
       <c r="J333" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K333" t="n">
         <v>0</v>
@@ -14178,7 +14176,7 @@
     <row r="334">
       <c r="A334" s="1" t="inlineStr">
         <is>
-          <t>錢包/資產管理</t>
+          <t>鋼鑄鐵元件</t>
         </is>
       </c>
       <c r="B334" t="inlineStr"/>
@@ -14201,7 +14199,7 @@
         <v>0</v>
       </c>
       <c r="I334" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J334" t="n">
         <v>0</v>
@@ -14219,7 +14217,7 @@
     <row r="335">
       <c r="A335" s="1" t="inlineStr">
         <is>
-          <t>開發工具</t>
+          <t>錢包/資產管理</t>
         </is>
       </c>
       <c r="B335" t="inlineStr"/>
@@ -14236,7 +14234,7 @@
         <v>0</v>
       </c>
       <c r="G335" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H335" t="n">
         <v>0</v>
@@ -14260,27 +14258,27 @@
     <row r="336">
       <c r="A336" s="1" t="inlineStr">
         <is>
-          <t>隨身碟、記憶卡讀卡機</t>
+          <t>開發工具</t>
         </is>
       </c>
       <c r="B336" t="inlineStr"/>
       <c r="C336" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D336" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E336" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F336" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G336" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H336" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I336" t="n">
         <v>0</v>
@@ -14301,27 +14299,27 @@
     <row r="337">
       <c r="A337" s="1" t="inlineStr">
         <is>
-          <t>雲端作業系統</t>
+          <t>隨身碟、記憶卡讀卡機</t>
         </is>
       </c>
       <c r="B337" t="inlineStr"/>
       <c r="C337" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D337" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E337" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F337" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G337" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H337" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I337" t="n">
         <v>0</v>
@@ -14342,7 +14340,7 @@
     <row r="338">
       <c r="A338" s="1" t="inlineStr">
         <is>
-          <t>雲端安全</t>
+          <t>雲端作業系統</t>
         </is>
       </c>
       <c r="B338" t="inlineStr"/>
@@ -14356,19 +14354,19 @@
         <v>1</v>
       </c>
       <c r="F338" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G338" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H338" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I338" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J338" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K338" t="n">
         <v>0</v>
@@ -14383,24 +14381,24 @@
     <row r="339">
       <c r="A339" s="1" t="inlineStr">
         <is>
-          <t>雲端平台</t>
+          <t>雲端安全</t>
         </is>
       </c>
       <c r="B339" t="inlineStr"/>
       <c r="C339" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D339" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E339" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F339" t="n">
         <v>2</v>
       </c>
       <c r="G339" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H339" t="n">
         <v>1</v>
@@ -14424,7 +14422,7 @@
     <row r="340">
       <c r="A340" s="1" t="inlineStr">
         <is>
-          <t>雲端應用服務</t>
+          <t>雲端平台</t>
         </is>
       </c>
       <c r="B340" t="inlineStr"/>
@@ -14432,22 +14430,22 @@
         <v>0</v>
       </c>
       <c r="D340" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E340" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F340" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G340" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H340" t="n">
         <v>1</v>
       </c>
       <c r="I340" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J340" t="n">
         <v>0</v>
@@ -14459,35 +14457,33 @@
         <v>0</v>
       </c>
       <c r="M340" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="341">
       <c r="A341" s="1" t="inlineStr">
         <is>
-          <t>零售通路</t>
-        </is>
-      </c>
-      <c r="B341" t="n">
-        <v>0</v>
-      </c>
+          <t>雲端應用服務</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr"/>
       <c r="C341" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D341" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E341" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F341" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G341" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H341" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I341" t="n">
         <v>0</v>
@@ -14496,19 +14492,19 @@
         <v>0</v>
       </c>
       <c r="K341" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L341" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M341" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="342">
       <c r="A342" s="1" t="inlineStr">
         <is>
-          <t>零組件/材料</t>
+          <t>零售通路</t>
         </is>
       </c>
       <c r="B342" t="inlineStr"/>
@@ -14519,13 +14515,13 @@
         <v>0</v>
       </c>
       <c r="E342" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F342" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G342" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H342" t="n">
         <v>0</v>
@@ -14534,22 +14530,22 @@
         <v>0</v>
       </c>
       <c r="J342" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K342" t="n">
         <v>0</v>
       </c>
       <c r="L342" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M342" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="343">
       <c r="A343" s="1" t="inlineStr">
         <is>
-          <t>電信服務業</t>
+          <t>零組件/材料</t>
         </is>
       </c>
       <c r="B343" t="inlineStr"/>
@@ -14557,19 +14553,19 @@
         <v>0</v>
       </c>
       <c r="D343" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E343" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F343" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G343" t="n">
         <v>0</v>
       </c>
       <c r="H343" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I343" t="n">
         <v>0</v>
@@ -14581,7 +14577,7 @@
         <v>0</v>
       </c>
       <c r="L343" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M343" t="n">
         <v>0</v>
@@ -14590,7 +14586,7 @@
     <row r="344">
       <c r="A344" s="1" t="inlineStr">
         <is>
-          <t>電力系統</t>
+          <t>電信服務業</t>
         </is>
       </c>
       <c r="B344" t="inlineStr"/>
@@ -14607,7 +14603,7 @@
         <v>0</v>
       </c>
       <c r="G344" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H344" t="n">
         <v>0</v>
@@ -14622,16 +14618,16 @@
         <v>0</v>
       </c>
       <c r="L344" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M344" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="345">
       <c r="A345" s="1" t="inlineStr">
         <is>
-          <t>電力設備</t>
+          <t>電力系統</t>
         </is>
       </c>
       <c r="B345" t="inlineStr"/>
@@ -14651,7 +14647,7 @@
         <v>0</v>
       </c>
       <c r="H345" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I345" t="n">
         <v>0</v>
@@ -14660,19 +14656,19 @@
         <v>0</v>
       </c>
       <c r="K345" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L345" t="n">
         <v>1</v>
       </c>
       <c r="M345" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="346">
       <c r="A346" s="1" t="inlineStr">
         <is>
-          <t>電力零售業</t>
+          <t>電力設備</t>
         </is>
       </c>
       <c r="B346" t="inlineStr"/>
@@ -14689,7 +14685,7 @@
         <v>0</v>
       </c>
       <c r="G346" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H346" t="n">
         <v>0</v>
@@ -14701,10 +14697,10 @@
         <v>0</v>
       </c>
       <c r="K346" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L346" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M346" t="n">
         <v>0</v>
@@ -14713,7 +14709,7 @@
     <row r="347">
       <c r="A347" s="1" t="inlineStr">
         <is>
-          <t>電動汽車、電動機車、電動自行車</t>
+          <t>電力零售業</t>
         </is>
       </c>
       <c r="B347" t="inlineStr"/>
@@ -14736,7 +14732,7 @@
         <v>0</v>
       </c>
       <c r="I347" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J347" t="n">
         <v>0</v>
@@ -14748,13 +14744,13 @@
         <v>0</v>
       </c>
       <c r="M347" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="348">
       <c r="A348" s="1" t="inlineStr">
         <is>
-          <t>電子書</t>
+          <t>電動汽車、電動機車、電動自行車</t>
         </is>
       </c>
       <c r="B348" t="inlineStr"/>
@@ -14774,7 +14770,7 @@
         <v>0</v>
       </c>
       <c r="H348" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I348" t="n">
         <v>0</v>
@@ -14786,16 +14782,16 @@
         <v>0</v>
       </c>
       <c r="L348" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M348" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="349">
       <c r="A349" s="1" t="inlineStr">
         <is>
-          <t>電子觸控白板</t>
+          <t>電子書</t>
         </is>
       </c>
       <c r="B349" t="inlineStr"/>
@@ -14827,7 +14823,7 @@
         <v>0</v>
       </c>
       <c r="L349" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M349" t="n">
         <v>0</v>
@@ -14841,16 +14837,16 @@
       </c>
       <c r="B350" t="inlineStr"/>
       <c r="C350" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D350" t="n">
         <v>1</v>
       </c>
       <c r="E350" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F350" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G350" t="n">
         <v>1</v>
@@ -14862,16 +14858,16 @@
         <v>1</v>
       </c>
       <c r="J350" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K350" t="n">
         <v>0</v>
       </c>
       <c r="L350" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M350" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="351">
@@ -14880,39 +14876,41 @@
           <t>電容器</t>
         </is>
       </c>
-      <c r="B351" t="inlineStr"/>
+      <c r="B351" t="n">
+        <v>0</v>
+      </c>
       <c r="C351" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D351" t="n">
         <v>0</v>
       </c>
       <c r="E351" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F351" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G351" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="H351" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="I351" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J351" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K351" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L351" t="n">
         <v>3</v>
       </c>
       <c r="M351" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="352">
@@ -14921,7 +14919,9 @@
           <t>電容器材料(如電蝕／化成鋁箔、介面瓷粉)</t>
         </is>
       </c>
-      <c r="B352" t="inlineStr"/>
+      <c r="B352" t="n">
+        <v>0</v>
+      </c>
       <c r="C352" t="n">
         <v>0</v>
       </c>
@@ -14929,7 +14929,7 @@
         <v>0</v>
       </c>
       <c r="E352" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F352" t="n">
         <v>1</v>
@@ -14938,7 +14938,7 @@
         <v>1</v>
       </c>
       <c r="H352" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I352" t="n">
         <v>0</v>
@@ -14947,10 +14947,10 @@
         <v>0</v>
       </c>
       <c r="K352" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L352" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M352" t="n">
         <v>0</v>
@@ -14962,39 +14962,41 @@
           <t>電感器</t>
         </is>
       </c>
-      <c r="B353" t="inlineStr"/>
+      <c r="B353" t="n">
+        <v>0</v>
+      </c>
       <c r="C353" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D353" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E353" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F353" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G353" t="n">
         <v>2</v>
       </c>
       <c r="H353" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I353" t="n">
+        <v>0</v>
+      </c>
+      <c r="J353" t="n">
+        <v>0</v>
+      </c>
+      <c r="K353" t="n">
         <v>2</v>
       </c>
-      <c r="J353" t="n">
-        <v>0</v>
-      </c>
-      <c r="K353" t="n">
-        <v>0</v>
-      </c>
       <c r="L353" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M353" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="354">
@@ -15011,19 +15013,19 @@
         <v>0</v>
       </c>
       <c r="E354" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F354" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G354" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H354" t="n">
         <v>1</v>
       </c>
       <c r="I354" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J354" t="n">
         <v>0</v>
@@ -15044,41 +15046,39 @@
           <t>電控元件</t>
         </is>
       </c>
-      <c r="B355" t="n">
-        <v>0</v>
-      </c>
+      <c r="B355" t="inlineStr"/>
       <c r="C355" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D355" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E355" t="n">
         <v>0</v>
       </c>
       <c r="F355" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G355" t="n">
+        <v>1</v>
+      </c>
+      <c r="H355" t="n">
+        <v>0</v>
+      </c>
+      <c r="I355" t="n">
+        <v>0</v>
+      </c>
+      <c r="J355" t="n">
+        <v>0</v>
+      </c>
+      <c r="K355" t="n">
+        <v>0</v>
+      </c>
+      <c r="L355" t="n">
         <v>2</v>
       </c>
-      <c r="H355" t="n">
-        <v>1</v>
-      </c>
-      <c r="I355" t="n">
-        <v>0</v>
-      </c>
-      <c r="J355" t="n">
-        <v>0</v>
-      </c>
-      <c r="K355" t="n">
-        <v>0</v>
-      </c>
-      <c r="L355" t="n">
-        <v>0</v>
-      </c>
       <c r="M355" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="356">
@@ -15095,13 +15095,13 @@
         <v>0</v>
       </c>
       <c r="E356" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F356" t="n">
         <v>1</v>
       </c>
       <c r="G356" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H356" t="n">
         <v>0</v>
@@ -15116,10 +15116,10 @@
         <v>0</v>
       </c>
       <c r="L356" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M356" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="357">
@@ -15128,9 +15128,7 @@
           <t>電池模組</t>
         </is>
       </c>
-      <c r="B357" t="n">
-        <v>0</v>
-      </c>
+      <c r="B357" t="inlineStr"/>
       <c r="C357" t="n">
         <v>0</v>
       </c>
@@ -15153,16 +15151,16 @@
         <v>0</v>
       </c>
       <c r="J357" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K357" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L357" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M357" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="358">
@@ -15194,16 +15192,16 @@
         <v>0</v>
       </c>
       <c r="J358" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K358" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L358" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M358" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="359">
@@ -15217,34 +15215,34 @@
         <v>1</v>
       </c>
       <c r="D359" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E359" t="n">
+        <v>1</v>
+      </c>
+      <c r="F359" t="n">
         <v>2</v>
       </c>
-      <c r="F359" t="n">
-        <v>1</v>
-      </c>
       <c r="G359" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H359" t="n">
         <v>1</v>
       </c>
       <c r="I359" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J359" t="n">
         <v>0</v>
       </c>
       <c r="K359" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L359" t="n">
         <v>1</v>
       </c>
       <c r="M359" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="360">
@@ -15279,10 +15277,10 @@
         <v>0</v>
       </c>
       <c r="K360" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L360" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M360" t="n">
         <v>0</v>
@@ -15349,10 +15347,10 @@
         <v>0</v>
       </c>
       <c r="G362" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H362" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I362" t="n">
         <v>0</v>
@@ -15376,39 +15374,41 @@
           <t>電腦視覺</t>
         </is>
       </c>
-      <c r="B363" t="inlineStr"/>
+      <c r="B363" t="n">
+        <v>0</v>
+      </c>
       <c r="C363" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D363" t="n">
         <v>0</v>
       </c>
       <c r="E363" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F363" t="n">
         <v>1</v>
       </c>
       <c r="G363" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H363" t="n">
         <v>0</v>
       </c>
       <c r="I363" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J363" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K363" t="n">
         <v>0</v>
       </c>
       <c r="L363" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M363" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="364">
@@ -15419,37 +15419,37 @@
       </c>
       <c r="B364" t="inlineStr"/>
       <c r="C364" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D364" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E364" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F364" t="n">
+        <v>1</v>
+      </c>
+      <c r="G364" t="n">
         <v>2</v>
       </c>
-      <c r="G364" t="n">
-        <v>1</v>
-      </c>
       <c r="H364" t="n">
+        <v>0</v>
+      </c>
+      <c r="I364" t="n">
+        <v>0</v>
+      </c>
+      <c r="J364" t="n">
+        <v>0</v>
+      </c>
+      <c r="K364" t="n">
+        <v>0</v>
+      </c>
+      <c r="L364" t="n">
         <v>2</v>
       </c>
-      <c r="I364" t="n">
-        <v>0</v>
-      </c>
-      <c r="J364" t="n">
-        <v>0</v>
-      </c>
-      <c r="K364" t="n">
-        <v>0</v>
-      </c>
-      <c r="L364" t="n">
-        <v>0</v>
-      </c>
       <c r="M364" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="365">
@@ -15540,7 +15540,9 @@
           <t>電阻器</t>
         </is>
       </c>
-      <c r="B367" t="inlineStr"/>
+      <c r="B367" t="n">
+        <v>0</v>
+      </c>
       <c r="C367" t="n">
         <v>0</v>
       </c>
@@ -15548,31 +15550,31 @@
         <v>0</v>
       </c>
       <c r="E367" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F367" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G367" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H367" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I367" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J367" t="n">
         <v>0</v>
       </c>
       <c r="K367" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L367" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M367" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="368">
@@ -15589,13 +15591,13 @@
         <v>0</v>
       </c>
       <c r="E368" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F368" t="n">
         <v>1</v>
       </c>
       <c r="G368" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H368" t="n">
         <v>0</v>
@@ -15630,13 +15632,13 @@
         <v>0</v>
       </c>
       <c r="E369" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F369" t="n">
         <v>1</v>
       </c>
       <c r="G369" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H369" t="n">
         <v>0</v>
@@ -15651,10 +15653,10 @@
         <v>0</v>
       </c>
       <c r="L369" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M369" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="370">
@@ -15745,39 +15747,41 @@
           <t>領域解決方案</t>
         </is>
       </c>
-      <c r="B372" t="inlineStr"/>
+      <c r="B372" t="n">
+        <v>0</v>
+      </c>
       <c r="C372" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D372" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E372" t="n">
+        <v>4</v>
+      </c>
+      <c r="F372" t="n">
+        <v>4</v>
+      </c>
+      <c r="G372" t="n">
+        <v>1</v>
+      </c>
+      <c r="H372" t="n">
+        <v>1</v>
+      </c>
+      <c r="I372" t="n">
+        <v>1</v>
+      </c>
+      <c r="J372" t="n">
+        <v>0</v>
+      </c>
+      <c r="K372" t="n">
+        <v>0</v>
+      </c>
+      <c r="L372" t="n">
         <v>2</v>
       </c>
-      <c r="F372" t="n">
-        <v>5</v>
-      </c>
-      <c r="G372" t="n">
-        <v>4</v>
-      </c>
-      <c r="H372" t="n">
-        <v>1</v>
-      </c>
-      <c r="I372" t="n">
-        <v>1</v>
-      </c>
-      <c r="J372" t="n">
-        <v>1</v>
-      </c>
-      <c r="K372" t="n">
-        <v>0</v>
-      </c>
-      <c r="L372" t="n">
-        <v>0</v>
-      </c>
       <c r="M372" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="373">
@@ -15786,21 +15790,23 @@
           <t>頭顯裝置品牌廠</t>
         </is>
       </c>
-      <c r="B373" t="inlineStr"/>
+      <c r="B373" t="n">
+        <v>0</v>
+      </c>
       <c r="C373" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D373" t="n">
         <v>0</v>
       </c>
       <c r="E373" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F373" t="n">
         <v>1</v>
       </c>
       <c r="G373" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H373" t="n">
         <v>0</v>
@@ -15841,10 +15847,10 @@
         <v>0</v>
       </c>
       <c r="G374" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H374" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I374" t="n">
         <v>0</v>
@@ -15873,34 +15879,34 @@
         <v>0</v>
       </c>
       <c r="D375" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E375" t="n">
+        <v>5</v>
+      </c>
+      <c r="F375" t="n">
+        <v>4</v>
+      </c>
+      <c r="G375" t="n">
+        <v>3</v>
+      </c>
+      <c r="H375" t="n">
         <v>2</v>
       </c>
-      <c r="F375" t="n">
-        <v>5</v>
-      </c>
-      <c r="G375" t="n">
-        <v>4</v>
-      </c>
-      <c r="H375" t="n">
+      <c r="I375" t="n">
+        <v>0</v>
+      </c>
+      <c r="J375" t="n">
+        <v>0</v>
+      </c>
+      <c r="K375" t="n">
+        <v>1</v>
+      </c>
+      <c r="L375" t="n">
         <v>3</v>
       </c>
-      <c r="I375" t="n">
-        <v>2</v>
-      </c>
-      <c r="J375" t="n">
-        <v>0</v>
-      </c>
-      <c r="K375" t="n">
-        <v>0</v>
-      </c>
-      <c r="L375" t="n">
-        <v>1</v>
-      </c>
       <c r="M375" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="376">
@@ -15911,19 +15917,19 @@
       </c>
       <c r="B376" t="inlineStr"/>
       <c r="C376" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D376" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E376" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F376" t="n">
         <v>1</v>
       </c>
       <c r="G376" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H376" t="n">
         <v>0</v>
@@ -15950,21 +15956,23 @@
           <t>顯示器模組</t>
         </is>
       </c>
-      <c r="B377" t="inlineStr"/>
+      <c r="B377" t="n">
+        <v>0</v>
+      </c>
       <c r="C377" t="n">
         <v>0</v>
       </c>
       <c r="D377" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E377" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F377" t="n">
         <v>2</v>
       </c>
       <c r="G377" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H377" t="n">
         <v>0</v>
@@ -16157,7 +16165,7 @@
       </c>
       <c r="B382" t="inlineStr"/>
       <c r="C382" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D382" t="n">
         <v>0</v>
@@ -16166,19 +16174,19 @@
         <v>0</v>
       </c>
       <c r="F382" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G382" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H382" t="n">
         <v>0</v>
       </c>
       <c r="I382" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J382" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K382" t="n">
         <v>0</v>
@@ -16187,7 +16195,7 @@
         <v>0</v>
       </c>
       <c r="M382" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="383">
@@ -16248,28 +16256,28 @@
         <v>0</v>
       </c>
       <c r="F384" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G384" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H384" t="n">
+        <v>0</v>
+      </c>
+      <c r="I384" t="n">
+        <v>0</v>
+      </c>
+      <c r="J384" t="n">
+        <v>0</v>
+      </c>
+      <c r="K384" t="n">
+        <v>1</v>
+      </c>
+      <c r="L384" t="n">
         <v>2</v>
       </c>
-      <c r="I384" t="n">
-        <v>0</v>
-      </c>
-      <c r="J384" t="n">
-        <v>0</v>
-      </c>
-      <c r="K384" t="n">
-        <v>0</v>
-      </c>
-      <c r="L384" t="n">
-        <v>1</v>
-      </c>
       <c r="M384" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="385">

--- a/Result/analyze_3.xlsx
+++ b/Result/analyze_3.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M387"/>
+  <dimension ref="A1:M388"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,57 +441,57 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
     </row>
@@ -547,13 +547,13 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E3" t="n">
         <v>1</v>
       </c>
       <c r="F3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -669,25 +669,25 @@
         <v>0</v>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H6" t="n">
         <v>3</v>
       </c>
-      <c r="E6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" t="n">
-        <v>1</v>
-      </c>
       <c r="I6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -696,10 +696,10 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -710,34 +710,34 @@
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D7" t="n">
+        <v>2</v>
+      </c>
+      <c r="E7" t="n">
+        <v>5</v>
+      </c>
+      <c r="F7" t="n">
         <v>3</v>
       </c>
-      <c r="E7" t="n">
+      <c r="G7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
         <v>2</v>
       </c>
-      <c r="F7" t="n">
-        <v>5</v>
-      </c>
-      <c r="G7" t="n">
-        <v>3</v>
-      </c>
-      <c r="H7" t="n">
-        <v>1</v>
-      </c>
-      <c r="I7" t="n">
-        <v>1</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
       <c r="L7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -751,34 +751,34 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D8" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F8" t="n">
         <v>2</v>
       </c>
       <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
         <v>2</v>
       </c>
-      <c r="H8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
       <c r="L8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -794,34 +794,34 @@
         <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D9" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E9" t="n">
         <v>3</v>
       </c>
       <c r="F9" t="n">
+        <v>2</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
         <v>3</v>
       </c>
-      <c r="G9" t="n">
-        <v>2</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" t="n">
-        <v>1</v>
-      </c>
-      <c r="J9" t="n">
-        <v>1</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
       <c r="L9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M9" t="n">
         <v>1</v>
@@ -833,39 +833,41 @@
           <t>IC通路</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
+      <c r="B10" t="n">
+        <v>0</v>
+      </c>
       <c r="C10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E10" t="n">
+        <v>2</v>
+      </c>
+      <c r="F10" t="n">
         <v>3</v>
       </c>
-      <c r="F10" t="n">
-        <v>2</v>
-      </c>
       <c r="G10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
         <v>3</v>
       </c>
-      <c r="H10" t="n">
-        <v>1</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
       <c r="L10" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -876,10 +878,10 @@
       </c>
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -891,22 +893,22 @@
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -920,16 +922,16 @@
         <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -967,10 +969,10 @@
         <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -1122,16 +1124,16 @@
       </c>
       <c r="B17" t="inlineStr"/>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -1152,7 +1154,7 @@
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -1213,16 +1215,16 @@
         <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -1254,10 +1256,10 @@
         <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
@@ -1284,12 +1286,14 @@
           <t>中、西藥製劑</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr"/>
+      <c r="B21" t="n">
+        <v>0</v>
+      </c>
       <c r="C21" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
@@ -1301,22 +1305,22 @@
         <v>1</v>
       </c>
       <c r="H21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
+        <v>1</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
         <v>2</v>
-      </c>
-      <c r="I21" t="n">
-        <v>1</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>1</v>
-      </c>
-      <c r="M21" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -1325,7 +1329,9 @@
           <t>中央處理器</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr"/>
+      <c r="B22" t="n">
+        <v>0</v>
+      </c>
       <c r="C22" t="n">
         <v>0</v>
       </c>
@@ -1336,7 +1342,7 @@
         <v>1</v>
       </c>
       <c r="F22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -1368,7 +1374,7 @@
       </c>
       <c r="B23" t="inlineStr"/>
       <c r="C23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D23" t="n">
         <v>0</v>
@@ -1380,10 +1386,10 @@
         <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I23" t="n">
         <v>0</v>
@@ -1392,13 +1398,13 @@
         <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24">
@@ -1415,13 +1421,13 @@
         <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F24" t="n">
         <v>1</v>
       </c>
       <c r="G24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H24" t="n">
         <v>0</v>
@@ -1433,13 +1439,13 @@
         <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L24" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -1448,9 +1454,7 @@
           <t>主機板</t>
         </is>
       </c>
-      <c r="B25" t="n">
-        <v>0</v>
-      </c>
+      <c r="B25" t="inlineStr"/>
       <c r="C25" t="n">
         <v>1</v>
       </c>
@@ -1461,7 +1465,7 @@
         <v>1</v>
       </c>
       <c r="F25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -1534,10 +1538,10 @@
       </c>
       <c r="B27" t="inlineStr"/>
       <c r="C27" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D27" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E27" t="n">
         <v>0</v>
@@ -1549,10 +1553,10 @@
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -1663,13 +1667,13 @@
         <v>0</v>
       </c>
       <c r="E30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G30" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H30" t="n">
         <v>0</v>
@@ -1698,19 +1702,19 @@
       </c>
       <c r="B31" t="inlineStr"/>
       <c r="C31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G31" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H31" t="n">
         <v>0</v>
@@ -1742,31 +1746,31 @@
         <v>1</v>
       </c>
       <c r="D32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E32" t="n">
         <v>0</v>
       </c>
       <c r="F32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
         <v>0</v>
@@ -1780,16 +1784,16 @@
       </c>
       <c r="B33" t="inlineStr"/>
       <c r="C33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D33" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E33" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -1862,10 +1866,10 @@
       </c>
       <c r="B35" t="inlineStr"/>
       <c r="C35" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D35" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E35" t="n">
         <v>0</v>
@@ -1892,7 +1896,7 @@
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="36">
@@ -1985,16 +1989,16 @@
       </c>
       <c r="B38" t="inlineStr"/>
       <c r="C38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
@@ -2056,7 +2060,7 @@
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="40">
@@ -2111,10 +2115,10 @@
         <v>0</v>
       </c>
       <c r="D41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F41" t="n">
         <v>0</v>
@@ -2132,10 +2136,10 @@
         <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
         <v>0</v>
@@ -2149,10 +2153,10 @@
       </c>
       <c r="B42" t="inlineStr"/>
       <c r="C42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D42" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E42" t="n">
         <v>1</v>
@@ -2161,7 +2165,7 @@
         <v>1</v>
       </c>
       <c r="G42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H42" t="n">
         <v>0</v>
@@ -2173,10 +2177,10 @@
         <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
         <v>0</v>
@@ -2190,10 +2194,10 @@
       </c>
       <c r="B43" t="inlineStr"/>
       <c r="C43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E43" t="n">
         <v>0</v>
@@ -2234,7 +2238,7 @@
         <v>0</v>
       </c>
       <c r="D44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E44" t="n">
         <v>1</v>
@@ -2243,7 +2247,7 @@
         <v>1</v>
       </c>
       <c r="G44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H44" t="n">
         <v>0</v>
@@ -2252,16 +2256,16 @@
         <v>0</v>
       </c>
       <c r="J44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L44" t="n">
         <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="45">
@@ -2275,10 +2279,10 @@
         <v>0</v>
       </c>
       <c r="D45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F45" t="n">
         <v>0</v>
@@ -2316,13 +2320,13 @@
         <v>0</v>
       </c>
       <c r="D46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E46" t="n">
         <v>1</v>
       </c>
       <c r="F46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
@@ -2357,13 +2361,13 @@
         <v>0</v>
       </c>
       <c r="D47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E47" t="n">
         <v>1</v>
       </c>
       <c r="F47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
@@ -2436,37 +2440,37 @@
       </c>
       <c r="B49" t="inlineStr"/>
       <c r="C49" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D49" t="n">
+        <v>1</v>
+      </c>
+      <c r="E49" t="n">
         <v>2</v>
-      </c>
-      <c r="E49" t="n">
-        <v>1</v>
       </c>
       <c r="F49" t="n">
         <v>2</v>
       </c>
       <c r="G49" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I49" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K49" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L49" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="M49" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="50">
@@ -2520,37 +2524,37 @@
         <v>0</v>
       </c>
       <c r="C51" t="n">
+        <v>1</v>
+      </c>
+      <c r="D51" t="n">
+        <v>2</v>
+      </c>
+      <c r="E51" t="n">
+        <v>0</v>
+      </c>
+      <c r="F51" t="n">
+        <v>6</v>
+      </c>
+      <c r="G51" t="n">
+        <v>1</v>
+      </c>
+      <c r="H51" t="n">
+        <v>1</v>
+      </c>
+      <c r="I51" t="n">
+        <v>1</v>
+      </c>
+      <c r="J51" t="n">
+        <v>1</v>
+      </c>
+      <c r="K51" t="n">
         <v>3</v>
       </c>
-      <c r="D51" t="n">
-        <v>1</v>
-      </c>
-      <c r="E51" t="n">
+      <c r="L51" t="n">
+        <v>1</v>
+      </c>
+      <c r="M51" t="n">
         <v>2</v>
-      </c>
-      <c r="F51" t="n">
-        <v>0</v>
-      </c>
-      <c r="G51" t="n">
-        <v>6</v>
-      </c>
-      <c r="H51" t="n">
-        <v>1</v>
-      </c>
-      <c r="I51" t="n">
-        <v>1</v>
-      </c>
-      <c r="J51" t="n">
-        <v>1</v>
-      </c>
-      <c r="K51" t="n">
-        <v>1</v>
-      </c>
-      <c r="L51" t="n">
-        <v>3</v>
-      </c>
-      <c r="M51" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="52">
@@ -2600,38 +2604,36 @@
           <t>其他零組件</t>
         </is>
       </c>
-      <c r="B53" t="n">
-        <v>0</v>
-      </c>
+      <c r="B53" t="inlineStr"/>
       <c r="C53" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D53" t="n">
+        <v>1</v>
+      </c>
+      <c r="E53" t="n">
+        <v>1</v>
+      </c>
+      <c r="F53" t="n">
+        <v>3</v>
+      </c>
+      <c r="G53" t="n">
         <v>2</v>
-      </c>
-      <c r="E53" t="n">
-        <v>1</v>
-      </c>
-      <c r="F53" t="n">
-        <v>1</v>
-      </c>
-      <c r="G53" t="n">
-        <v>3</v>
       </c>
       <c r="H53" t="n">
         <v>2</v>
       </c>
       <c r="I53" t="n">
+        <v>0</v>
+      </c>
+      <c r="J53" t="n">
+        <v>0</v>
+      </c>
+      <c r="K53" t="n">
         <v>2</v>
       </c>
-      <c r="J53" t="n">
-        <v>0</v>
-      </c>
-      <c r="K53" t="n">
-        <v>0</v>
-      </c>
       <c r="L53" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M53" t="n">
         <v>0</v>
@@ -2643,9 +2645,7 @@
           <t>其他電子產品及電子服務產業</t>
         </is>
       </c>
-      <c r="B54" t="n">
-        <v>0</v>
-      </c>
+      <c r="B54" t="inlineStr"/>
       <c r="C54" t="n">
         <v>1</v>
       </c>
@@ -2653,31 +2653,31 @@
         <v>1</v>
       </c>
       <c r="E54" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F54" t="n">
         <v>4</v>
       </c>
       <c r="G54" t="n">
+        <v>0</v>
+      </c>
+      <c r="H54" t="n">
+        <v>0</v>
+      </c>
+      <c r="I54" t="n">
+        <v>1</v>
+      </c>
+      <c r="J54" t="n">
+        <v>1</v>
+      </c>
+      <c r="K54" t="n">
         <v>4</v>
       </c>
-      <c r="H54" t="n">
-        <v>0</v>
-      </c>
-      <c r="I54" t="n">
-        <v>1</v>
-      </c>
-      <c r="J54" t="n">
-        <v>1</v>
-      </c>
-      <c r="K54" t="n">
-        <v>1</v>
-      </c>
       <c r="L54" t="n">
+        <v>0</v>
+      </c>
+      <c r="M54" t="n">
         <v>4</v>
-      </c>
-      <c r="M54" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -2686,39 +2686,41 @@
           <t>其他電腦及週邊設備</t>
         </is>
       </c>
-      <c r="B55" t="inlineStr"/>
+      <c r="B55" t="n">
+        <v>0</v>
+      </c>
       <c r="C55" t="n">
+        <v>1</v>
+      </c>
+      <c r="D55" t="n">
+        <v>2</v>
+      </c>
+      <c r="E55" t="n">
         <v>4</v>
       </c>
-      <c r="D55" t="n">
-        <v>1</v>
-      </c>
-      <c r="E55" t="n">
+      <c r="F55" t="n">
         <v>2</v>
       </c>
-      <c r="F55" t="n">
-        <v>4</v>
-      </c>
       <c r="G55" t="n">
+        <v>1</v>
+      </c>
+      <c r="H55" t="n">
+        <v>0</v>
+      </c>
+      <c r="I55" t="n">
+        <v>0</v>
+      </c>
+      <c r="J55" t="n">
+        <v>1</v>
+      </c>
+      <c r="K55" t="n">
+        <v>1</v>
+      </c>
+      <c r="L55" t="n">
+        <v>1</v>
+      </c>
+      <c r="M55" t="n">
         <v>2</v>
-      </c>
-      <c r="H55" t="n">
-        <v>1</v>
-      </c>
-      <c r="I55" t="n">
-        <v>0</v>
-      </c>
-      <c r="J55" t="n">
-        <v>0</v>
-      </c>
-      <c r="K55" t="n">
-        <v>1</v>
-      </c>
-      <c r="L55" t="n">
-        <v>1</v>
-      </c>
-      <c r="M55" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="56">
@@ -2731,34 +2733,34 @@
         <v>0</v>
       </c>
       <c r="C56" t="n">
+        <v>5</v>
+      </c>
+      <c r="D56" t="n">
         <v>3</v>
       </c>
-      <c r="D56" t="n">
-        <v>5</v>
-      </c>
       <c r="E56" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F56" t="n">
+        <v>4</v>
+      </c>
+      <c r="G56" t="n">
+        <v>1</v>
+      </c>
+      <c r="H56" t="n">
         <v>2</v>
       </c>
-      <c r="G56" t="n">
-        <v>4</v>
-      </c>
-      <c r="H56" t="n">
-        <v>0</v>
-      </c>
       <c r="I56" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
       </c>
       <c r="K56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M56" t="n">
         <v>0</v>
@@ -2813,19 +2815,19 @@
       </c>
       <c r="B58" t="inlineStr"/>
       <c r="C58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E58" t="n">
         <v>0</v>
       </c>
       <c r="F58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H58" t="n">
         <v>0</v>
@@ -2834,10 +2836,10 @@
         <v>0</v>
       </c>
       <c r="J58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L58" t="n">
         <v>0</v>
@@ -2854,7 +2856,7 @@
       </c>
       <c r="B59" t="inlineStr"/>
       <c r="C59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D59" t="n">
         <v>0</v>
@@ -2863,10 +2865,10 @@
         <v>0</v>
       </c>
       <c r="F59" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H59" t="n">
         <v>0</v>
@@ -2875,13 +2877,13 @@
         <v>0</v>
       </c>
       <c r="J59" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K59" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L59" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M59" t="n">
         <v>0</v>
@@ -2893,7 +2895,9 @@
           <t>冷熱軋不鏽鋼板捲</t>
         </is>
       </c>
-      <c r="B60" t="inlineStr"/>
+      <c r="B60" t="n">
+        <v>0</v>
+      </c>
       <c r="C60" t="n">
         <v>0</v>
       </c>
@@ -2904,10 +2908,10 @@
         <v>0</v>
       </c>
       <c r="F60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H60" t="n">
         <v>0</v>
@@ -3018,7 +3022,7 @@
       </c>
       <c r="B63" t="inlineStr"/>
       <c r="C63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D63" t="n">
         <v>1</v>
@@ -3030,7 +3034,7 @@
         <v>1</v>
       </c>
       <c r="G63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H63" t="n">
         <v>0</v>
@@ -3188,10 +3192,10 @@
         <v>0</v>
       </c>
       <c r="E67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
@@ -3229,10 +3233,10 @@
         <v>0</v>
       </c>
       <c r="E68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
@@ -3355,16 +3359,16 @@
         <v>0</v>
       </c>
       <c r="F71" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G71" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H71" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -3376,7 +3380,7 @@
         <v>0</v>
       </c>
       <c r="M71" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="72">
@@ -3396,28 +3400,28 @@
         <v>0</v>
       </c>
       <c r="F72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
       </c>
       <c r="K72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="73">
@@ -3452,10 +3456,10 @@
         <v>0</v>
       </c>
       <c r="K73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L73" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M73" t="n">
         <v>0</v>
@@ -3516,13 +3520,13 @@
         <v>0</v>
       </c>
       <c r="E75" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F75" t="n">
         <v>1</v>
       </c>
       <c r="G75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H75" t="n">
         <v>0</v>
@@ -3549,20 +3553,18 @@
           <t>印表機、傳真機、掃瞄器、多功能事務機、投影機</t>
         </is>
       </c>
-      <c r="B76" t="n">
-        <v>0</v>
-      </c>
+      <c r="B76" t="inlineStr"/>
       <c r="C76" t="n">
         <v>0</v>
       </c>
       <c r="D76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E76" t="n">
         <v>1</v>
       </c>
       <c r="F76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
@@ -3633,41 +3635,39 @@
           <t>原材料</t>
         </is>
       </c>
-      <c r="B78" t="n">
-        <v>0</v>
-      </c>
+      <c r="B78" t="inlineStr"/>
       <c r="C78" t="n">
         <v>1</v>
       </c>
       <c r="D78" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E78" t="n">
         <v>0</v>
       </c>
       <c r="F78" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G78" t="n">
+        <v>1</v>
+      </c>
+      <c r="H78" t="n">
         <v>2</v>
       </c>
-      <c r="H78" t="n">
-        <v>1</v>
-      </c>
       <c r="I78" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J78" t="n">
         <v>1</v>
       </c>
       <c r="K78" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L78" t="n">
         <v>0</v>
       </c>
       <c r="M78" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="79">
@@ -3725,10 +3725,10 @@
         <v>0</v>
       </c>
       <c r="E80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F80" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G80" t="n">
         <v>0</v>
@@ -3810,10 +3810,10 @@
         <v>0</v>
       </c>
       <c r="F82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H82" t="n">
         <v>0</v>
@@ -3842,37 +3842,37 @@
       </c>
       <c r="B83" t="inlineStr"/>
       <c r="C83" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D83" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E83" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F83" t="n">
+        <v>1</v>
+      </c>
+      <c r="G83" t="n">
+        <v>0</v>
+      </c>
+      <c r="H83" t="n">
+        <v>1</v>
+      </c>
+      <c r="I83" t="n">
+        <v>0</v>
+      </c>
+      <c r="J83" t="n">
+        <v>0</v>
+      </c>
+      <c r="K83" t="n">
         <v>2</v>
       </c>
-      <c r="G83" t="n">
-        <v>1</v>
-      </c>
-      <c r="H83" t="n">
-        <v>0</v>
-      </c>
-      <c r="I83" t="n">
-        <v>1</v>
-      </c>
-      <c r="J83" t="n">
-        <v>0</v>
-      </c>
-      <c r="K83" t="n">
-        <v>0</v>
-      </c>
       <c r="L83" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M83" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="84">
@@ -3971,16 +3971,16 @@
         <v>0</v>
       </c>
       <c r="E86" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F86" t="n">
         <v>1</v>
       </c>
       <c r="G86" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H86" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I86" t="n">
         <v>0</v>
@@ -4006,25 +4006,25 @@
       </c>
       <c r="B87" t="inlineStr"/>
       <c r="C87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E87" t="n">
         <v>0</v>
       </c>
       <c r="F87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -4055,10 +4055,10 @@
         <v>0</v>
       </c>
       <c r="E88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G88" t="n">
         <v>0</v>
@@ -4073,10 +4073,10 @@
         <v>0</v>
       </c>
       <c r="K88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M88" t="n">
         <v>0</v>
@@ -4088,38 +4088,36 @@
           <t>塑膠製品</t>
         </is>
       </c>
-      <c r="B89" t="n">
-        <v>0</v>
-      </c>
+      <c r="B89" t="inlineStr"/>
       <c r="C89" t="n">
         <v>1</v>
       </c>
       <c r="D89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E89" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F89" t="n">
         <v>1</v>
       </c>
       <c r="G89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H89" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
       </c>
       <c r="K89" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M89" t="n">
         <v>0</v>
@@ -4177,13 +4175,13 @@
         <v>0</v>
       </c>
       <c r="D91" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E91" t="n">
         <v>1</v>
       </c>
       <c r="F91" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G91" t="n">
         <v>0</v>
@@ -4213,24 +4211,26 @@
           <t>大功率鋰電池芯/模組、電池管理系統、動力馬達等零組件</t>
         </is>
       </c>
-      <c r="B92" t="inlineStr"/>
+      <c r="B92" t="n">
+        <v>0</v>
+      </c>
       <c r="C92" t="n">
         <v>1</v>
       </c>
       <c r="D92" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E92" t="n">
         <v>0</v>
       </c>
       <c r="F92" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G92" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H92" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I92" t="n">
         <v>1</v>
@@ -4239,10 +4239,10 @@
         <v>1</v>
       </c>
       <c r="K92" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L92" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M92" t="n">
         <v>0</v>
@@ -4347,10 +4347,10 @@
         <v>0</v>
       </c>
       <c r="F95" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G95" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H95" t="n">
         <v>0</v>
@@ -4359,13 +4359,13 @@
         <v>0</v>
       </c>
       <c r="J95" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K95" t="n">
         <v>1</v>
       </c>
       <c r="L95" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M95" t="n">
         <v>0</v>
@@ -4388,10 +4388,10 @@
         <v>0</v>
       </c>
       <c r="F96" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G96" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H96" t="n">
         <v>0</v>
@@ -4403,10 +4403,10 @@
         <v>0</v>
       </c>
       <c r="K96" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L96" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M96" t="n">
         <v>0</v>
@@ -4459,9 +4459,7 @@
           <t>太陽能電池模組</t>
         </is>
       </c>
-      <c r="B98" t="n">
-        <v>0</v>
-      </c>
+      <c r="B98" t="inlineStr"/>
       <c r="C98" t="n">
         <v>0</v>
       </c>
@@ -4531,10 +4529,10 @@
         <v>0</v>
       </c>
       <c r="L99" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="100">
@@ -4592,16 +4590,16 @@
         <v>0</v>
       </c>
       <c r="E101" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F101" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G101" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H101" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I101" t="n">
         <v>0</v>
@@ -4616,7 +4614,7 @@
         <v>0</v>
       </c>
       <c r="M101" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="102">
@@ -4630,34 +4628,34 @@
         <v>1</v>
       </c>
       <c r="D102" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E102" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F102" t="n">
+        <v>1</v>
+      </c>
+      <c r="G102" t="n">
+        <v>1</v>
+      </c>
+      <c r="H102" t="n">
+        <v>0</v>
+      </c>
+      <c r="I102" t="n">
+        <v>0</v>
+      </c>
+      <c r="J102" t="n">
+        <v>0</v>
+      </c>
+      <c r="K102" t="n">
         <v>2</v>
       </c>
-      <c r="G102" t="n">
-        <v>1</v>
-      </c>
-      <c r="H102" t="n">
-        <v>1</v>
-      </c>
-      <c r="I102" t="n">
-        <v>0</v>
-      </c>
-      <c r="J102" t="n">
-        <v>0</v>
-      </c>
-      <c r="K102" t="n">
-        <v>0</v>
-      </c>
       <c r="L102" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M102" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="103">
@@ -4715,16 +4713,16 @@
         <v>0</v>
       </c>
       <c r="E104" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F104" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G104" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H104" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I104" t="n">
         <v>0</v>
@@ -4733,10 +4731,10 @@
         <v>0</v>
       </c>
       <c r="K104" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L104" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M104" t="n">
         <v>0</v>
@@ -4750,34 +4748,34 @@
       </c>
       <c r="B105" t="inlineStr"/>
       <c r="C105" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D105" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E105" t="n">
         <v>1</v>
       </c>
       <c r="F105" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G105" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H105" t="n">
         <v>1</v>
       </c>
       <c r="I105" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
       </c>
       <c r="K105" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L105" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M105" t="n">
         <v>0</v>
@@ -4794,31 +4792,31 @@
         <v>0</v>
       </c>
       <c r="D106" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E106" t="n">
+        <v>1</v>
+      </c>
+      <c r="F106" t="n">
         <v>2</v>
       </c>
-      <c r="F106" t="n">
-        <v>1</v>
-      </c>
       <c r="G106" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H106" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I106" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
       </c>
       <c r="K106" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L106" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M106" t="n">
         <v>0</v>
@@ -4958,10 +4956,10 @@
         <v>0</v>
       </c>
       <c r="D110" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E110" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F110" t="n">
         <v>0</v>
@@ -4979,10 +4977,10 @@
         <v>0</v>
       </c>
       <c r="K110" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L110" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M110" t="n">
         <v>0</v>
@@ -4996,22 +4994,22 @@
       </c>
       <c r="B111" t="inlineStr"/>
       <c r="C111" t="n">
+        <v>0</v>
+      </c>
+      <c r="D111" t="n">
         <v>2</v>
       </c>
-      <c r="D111" t="n">
-        <v>0</v>
-      </c>
       <c r="E111" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F111" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G111" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H111" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I111" t="n">
         <v>0</v>
@@ -5026,7 +5024,7 @@
         <v>0</v>
       </c>
       <c r="M111" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="112">
@@ -5046,10 +5044,10 @@
         <v>0</v>
       </c>
       <c r="F112" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G112" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H112" t="n">
         <v>0</v>
@@ -5058,10 +5056,10 @@
         <v>0</v>
       </c>
       <c r="J112" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K112" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L112" t="n">
         <v>0</v>
@@ -5087,10 +5085,10 @@
         <v>0</v>
       </c>
       <c r="F113" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G113" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H113" t="n">
         <v>0</v>
@@ -5099,10 +5097,10 @@
         <v>0</v>
       </c>
       <c r="J113" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K113" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L113" t="n">
         <v>0</v>
@@ -5149,7 +5147,7 @@
         <v>0</v>
       </c>
       <c r="M114" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="115">
@@ -5158,7 +5156,9 @@
           <t>幹細胞收集儲存</t>
         </is>
       </c>
-      <c r="B115" t="inlineStr"/>
+      <c r="B115" t="n">
+        <v>0</v>
+      </c>
       <c r="C115" t="n">
         <v>0</v>
       </c>
@@ -5199,7 +5199,9 @@
           <t>幹細胞開發</t>
         </is>
       </c>
-      <c r="B116" t="inlineStr"/>
+      <c r="B116" t="n">
+        <v>0</v>
+      </c>
       <c r="C116" t="n">
         <v>0</v>
       </c>
@@ -5324,16 +5326,16 @@
       </c>
       <c r="B119" t="inlineStr"/>
       <c r="C119" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D119" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E119" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F119" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G119" t="n">
         <v>0</v>
@@ -5365,34 +5367,34 @@
       </c>
       <c r="B120" t="inlineStr"/>
       <c r="C120" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D120" t="n">
         <v>1</v>
       </c>
       <c r="E120" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F120" t="n">
+        <v>0</v>
+      </c>
+      <c r="G120" t="n">
+        <v>1</v>
+      </c>
+      <c r="H120" t="n">
+        <v>1</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0</v>
+      </c>
+      <c r="K120" t="n">
         <v>2</v>
       </c>
-      <c r="G120" t="n">
-        <v>0</v>
-      </c>
-      <c r="H120" t="n">
-        <v>1</v>
-      </c>
-      <c r="I120" t="n">
-        <v>1</v>
-      </c>
-      <c r="J120" t="n">
-        <v>0</v>
-      </c>
-      <c r="K120" t="n">
-        <v>0</v>
-      </c>
       <c r="L120" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M120" t="n">
         <v>0</v>
@@ -5408,7 +5410,7 @@
         <v>0</v>
       </c>
       <c r="C121" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D121" t="n">
         <v>0</v>
@@ -5417,10 +5419,10 @@
         <v>0</v>
       </c>
       <c r="F121" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G121" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H121" t="n">
         <v>0</v>
@@ -5432,13 +5434,13 @@
         <v>0</v>
       </c>
       <c r="K121" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L121" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M121" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="122">
@@ -5529,21 +5531,23 @@
           <t>微處理器</t>
         </is>
       </c>
-      <c r="B124" t="inlineStr"/>
+      <c r="B124" t="n">
+        <v>0</v>
+      </c>
       <c r="C124" t="n">
         <v>0</v>
       </c>
       <c r="D124" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E124" t="n">
         <v>0</v>
       </c>
       <c r="F124" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G124" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H124" t="n">
         <v>0</v>
@@ -5611,17 +5615,15 @@
           <t>感測器/模組</t>
         </is>
       </c>
-      <c r="B126" t="n">
-        <v>0</v>
-      </c>
+      <c r="B126" t="inlineStr"/>
       <c r="C126" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D126" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E126" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F126" t="n">
         <v>0</v>
@@ -5659,10 +5661,10 @@
         <v>0</v>
       </c>
       <c r="D127" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E127" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F127" t="n">
         <v>0</v>
@@ -5697,7 +5699,7 @@
       </c>
       <c r="B128" t="inlineStr"/>
       <c r="C128" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D128" t="n">
         <v>2</v>
@@ -5706,25 +5708,25 @@
         <v>2</v>
       </c>
       <c r="F128" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G128" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H128" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I128" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J128" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K128" t="n">
         <v>1</v>
       </c>
       <c r="L128" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M128" t="n">
         <v>0</v>
@@ -5738,7 +5740,7 @@
       </c>
       <c r="B129" t="inlineStr"/>
       <c r="C129" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D129" t="n">
         <v>1</v>
@@ -5750,7 +5752,7 @@
         <v>1</v>
       </c>
       <c r="G129" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H129" t="n">
         <v>0</v>
@@ -5785,10 +5787,10 @@
         <v>0</v>
       </c>
       <c r="E130" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F130" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G130" t="n">
         <v>0</v>
@@ -5818,11 +5820,9 @@
           <t>成衣及其它家居紡織類品</t>
         </is>
       </c>
-      <c r="B131" t="n">
-        <v>0</v>
-      </c>
+      <c r="B131" t="inlineStr"/>
       <c r="C131" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D131" t="n">
         <v>0</v>
@@ -5831,7 +5831,7 @@
         <v>0</v>
       </c>
       <c r="F131" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G131" t="n">
         <v>1</v>
@@ -5840,13 +5840,13 @@
         <v>1</v>
       </c>
       <c r="I131" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J131" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K131" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L131" t="n">
         <v>0</v>
@@ -5875,10 +5875,10 @@
         <v>0</v>
       </c>
       <c r="G132" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H132" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I132" t="n">
         <v>0</v>
@@ -5910,10 +5910,10 @@
         <v>0</v>
       </c>
       <c r="E133" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F133" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G133" t="n">
         <v>0</v>
@@ -5943,9 +5943,7 @@
           <t>接著劑(合成樹脂)</t>
         </is>
       </c>
-      <c r="B134" t="n">
-        <v>0</v>
-      </c>
+      <c r="B134" t="inlineStr"/>
       <c r="C134" t="n">
         <v>0</v>
       </c>
@@ -6068,17 +6066,15 @@
           <t>擴散膜、增亮膜、導光板</t>
         </is>
       </c>
-      <c r="B137" t="n">
-        <v>0</v>
-      </c>
+      <c r="B137" t="inlineStr"/>
       <c r="C137" t="n">
         <v>0</v>
       </c>
       <c r="D137" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E137" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F137" t="n">
         <v>0</v>
@@ -6163,7 +6159,7 @@
         <v>1</v>
       </c>
       <c r="F139" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G139" t="n">
         <v>0</v>
@@ -6178,10 +6174,10 @@
         <v>0</v>
       </c>
       <c r="K139" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L139" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M139" t="n">
         <v>0</v>
@@ -6242,7 +6238,7 @@
         <v>0</v>
       </c>
       <c r="E141" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F141" t="n">
         <v>1</v>
@@ -6251,7 +6247,7 @@
         <v>1</v>
       </c>
       <c r="H141" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I141" t="n">
         <v>0</v>
@@ -6324,10 +6320,10 @@
         <v>0</v>
       </c>
       <c r="E143" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F143" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G143" t="n">
         <v>0</v>
@@ -6365,19 +6361,19 @@
         <v>0</v>
       </c>
       <c r="E144" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F144" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G144" t="n">
         <v>0</v>
       </c>
       <c r="H144" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I144" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -6389,7 +6385,7 @@
         <v>0</v>
       </c>
       <c r="M144" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="145">
@@ -6406,16 +6402,16 @@
         <v>0</v>
       </c>
       <c r="E145" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F145" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G145" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H145" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I145" t="n">
         <v>0</v>
@@ -6430,7 +6426,7 @@
         <v>0</v>
       </c>
       <c r="M145" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="146">
@@ -6444,10 +6440,10 @@
         <v>0</v>
       </c>
       <c r="D146" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E146" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F146" t="n">
         <v>0</v>
@@ -6488,16 +6484,16 @@
         <v>0</v>
       </c>
       <c r="E147" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F147" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G147" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H147" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I147" t="n">
         <v>0</v>
@@ -6512,7 +6508,7 @@
         <v>0</v>
       </c>
       <c r="M147" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="148">
@@ -6523,10 +6519,10 @@
       </c>
       <c r="B148" t="inlineStr"/>
       <c r="C148" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D148" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E148" t="n">
         <v>0</v>
@@ -6553,7 +6549,7 @@
         <v>0</v>
       </c>
       <c r="M148" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="149">
@@ -6576,10 +6572,10 @@
         <v>0</v>
       </c>
       <c r="G149" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H149" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I149" t="n">
         <v>0</v>
@@ -6629,10 +6625,10 @@
         <v>0</v>
       </c>
       <c r="K150" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L150" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M150" t="n">
         <v>0</v>
@@ -6644,23 +6640,21 @@
           <t>旅館服務業</t>
         </is>
       </c>
-      <c r="B151" t="n">
-        <v>0</v>
-      </c>
+      <c r="B151" t="inlineStr"/>
       <c r="C151" t="n">
         <v>0</v>
       </c>
       <c r="D151" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E151" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F151" t="n">
         <v>0</v>
       </c>
       <c r="G151" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H151" t="n">
         <v>0</v>
@@ -6669,10 +6663,10 @@
         <v>0</v>
       </c>
       <c r="J151" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K151" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L151" t="n">
         <v>0</v>
@@ -6692,13 +6686,13 @@
         <v>0</v>
       </c>
       <c r="D152" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E152" t="n">
         <v>1</v>
       </c>
       <c r="F152" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G152" t="n">
         <v>0</v>
@@ -6736,31 +6730,31 @@
         <v>0</v>
       </c>
       <c r="E153" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F153" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G153" t="n">
         <v>0</v>
       </c>
       <c r="H153" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I153" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
       </c>
       <c r="K153" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L153" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M153" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="154">
@@ -6780,10 +6774,10 @@
         <v>0</v>
       </c>
       <c r="F154" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G154" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H154" t="n">
         <v>0</v>
@@ -6795,10 +6789,10 @@
         <v>0</v>
       </c>
       <c r="K154" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L154" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M154" t="n">
         <v>0</v>
@@ -6853,25 +6847,25 @@
       </c>
       <c r="B156" t="inlineStr"/>
       <c r="C156" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D156" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E156" t="n">
         <v>0</v>
       </c>
       <c r="F156" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G156" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H156" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I156" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -6900,13 +6894,13 @@
         <v>0</v>
       </c>
       <c r="E157" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F157" t="n">
         <v>2</v>
       </c>
       <c r="G157" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H157" t="n">
         <v>0</v>
@@ -6921,7 +6915,7 @@
         <v>0</v>
       </c>
       <c r="L157" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M157" t="n">
         <v>1</v>
@@ -6935,16 +6929,16 @@
       </c>
       <c r="B158" t="inlineStr"/>
       <c r="C158" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D158" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E158" t="n">
         <v>1</v>
       </c>
       <c r="F158" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G158" t="n">
         <v>0</v>
@@ -6959,10 +6953,10 @@
         <v>0</v>
       </c>
       <c r="K158" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L158" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M158" t="n">
         <v>0</v>
@@ -7023,10 +7017,10 @@
         <v>0</v>
       </c>
       <c r="E160" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F160" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G160" t="n">
         <v>0</v>
@@ -7041,10 +7035,10 @@
         <v>0</v>
       </c>
       <c r="K160" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L160" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M160" t="n">
         <v>0</v>
@@ -7064,10 +7058,10 @@
         <v>0</v>
       </c>
       <c r="E161" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F161" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G161" t="n">
         <v>0</v>
@@ -7105,31 +7099,31 @@
         <v>0</v>
       </c>
       <c r="E162" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F162" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G162" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H162" t="n">
         <v>1</v>
       </c>
       <c r="I162" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
       </c>
       <c r="K162" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L162" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M162" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="163">
@@ -7146,13 +7140,13 @@
         <v>0</v>
       </c>
       <c r="E163" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F163" t="n">
         <v>1</v>
       </c>
       <c r="G163" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H163" t="n">
         <v>0</v>
@@ -7184,13 +7178,13 @@
         <v>0</v>
       </c>
       <c r="D164" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E164" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F164" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G164" t="n">
         <v>0</v>
@@ -7220,26 +7214,24 @@
           <t>機殼</t>
         </is>
       </c>
-      <c r="B165" t="n">
-        <v>0</v>
-      </c>
+      <c r="B165" t="inlineStr"/>
       <c r="C165" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D165" t="n">
         <v>1</v>
       </c>
       <c r="E165" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F165" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G165" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H165" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I165" t="n">
         <v>0</v>
@@ -7254,7 +7246,7 @@
         <v>0</v>
       </c>
       <c r="M165" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="166">
@@ -7274,10 +7266,10 @@
         <v>0</v>
       </c>
       <c r="F166" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G166" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H166" t="n">
         <v>0</v>
@@ -7286,13 +7278,13 @@
         <v>0</v>
       </c>
       <c r="J166" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K166" t="n">
         <v>1</v>
       </c>
       <c r="L166" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M166" t="n">
         <v>0</v>
@@ -7304,21 +7296,23 @@
           <t>機電系統工程</t>
         </is>
       </c>
-      <c r="B167" t="inlineStr"/>
+      <c r="B167" t="n">
+        <v>0</v>
+      </c>
       <c r="C167" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D167" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E167" t="n">
         <v>0</v>
       </c>
       <c r="F167" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G167" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H167" t="n">
         <v>0</v>
@@ -7327,10 +7321,10 @@
         <v>0</v>
       </c>
       <c r="J167" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K167" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L167" t="n">
         <v>0</v>
@@ -7345,9 +7339,7 @@
           <t>橡膠製品</t>
         </is>
       </c>
-      <c r="B168" t="n">
-        <v>0</v>
-      </c>
+      <c r="B168" t="inlineStr"/>
       <c r="C168" t="n">
         <v>0</v>
       </c>
@@ -7522,10 +7514,10 @@
         <v>0</v>
       </c>
       <c r="F172" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G172" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H172" t="n">
         <v>0</v>
@@ -7560,10 +7552,10 @@
         <v>0</v>
       </c>
       <c r="E173" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F173" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G173" t="n">
         <v>0</v>
@@ -7593,7 +7585,9 @@
           <t>海陸空大眾運輸</t>
         </is>
       </c>
-      <c r="B174" t="inlineStr"/>
+      <c r="B174" t="n">
+        <v>0</v>
+      </c>
       <c r="C174" t="n">
         <v>0</v>
       </c>
@@ -7718,26 +7712,24 @@
           <t>濾波器、振盪器</t>
         </is>
       </c>
-      <c r="B177" t="n">
-        <v>0</v>
-      </c>
+      <c r="B177" t="inlineStr"/>
       <c r="C177" t="n">
         <v>0</v>
       </c>
       <c r="D177" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E177" t="n">
         <v>1</v>
       </c>
       <c r="F177" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G177" t="n">
         <v>1</v>
       </c>
       <c r="H177" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I177" t="n">
         <v>0</v>
@@ -7746,10 +7738,10 @@
         <v>0</v>
       </c>
       <c r="K177" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L177" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M177" t="n">
         <v>0</v>
@@ -7802,41 +7794,39 @@
           <t>無線通訊設備(如行動電話、衛星定位系統、衛星通訊設備、微波通訊設備、數位機上盒)</t>
         </is>
       </c>
-      <c r="B179" t="n">
-        <v>0</v>
-      </c>
+      <c r="B179" t="inlineStr"/>
       <c r="C179" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D179" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E179" t="n">
+        <v>5</v>
+      </c>
+      <c r="F179" t="n">
+        <v>1</v>
+      </c>
+      <c r="G179" t="n">
+        <v>0</v>
+      </c>
+      <c r="H179" t="n">
         <v>2</v>
       </c>
-      <c r="F179" t="n">
-        <v>5</v>
-      </c>
-      <c r="G179" t="n">
-        <v>1</v>
-      </c>
-      <c r="H179" t="n">
-        <v>0</v>
-      </c>
       <c r="I179" t="n">
+        <v>0</v>
+      </c>
+      <c r="J179" t="n">
+        <v>0</v>
+      </c>
+      <c r="K179" t="n">
         <v>2</v>
       </c>
-      <c r="J179" t="n">
-        <v>0</v>
-      </c>
-      <c r="K179" t="n">
-        <v>0</v>
-      </c>
       <c r="L179" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M179" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="180">
@@ -7856,10 +7846,10 @@
         <v>0</v>
       </c>
       <c r="F180" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G180" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H180" t="n">
         <v>0</v>
@@ -7886,24 +7876,26 @@
           <t>燈具/應用</t>
         </is>
       </c>
-      <c r="B181" t="inlineStr"/>
+      <c r="B181" t="n">
+        <v>0</v>
+      </c>
       <c r="C181" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D181" t="n">
         <v>0</v>
       </c>
       <c r="E181" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F181" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G181" t="n">
         <v>2</v>
       </c>
       <c r="H181" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I181" t="n">
         <v>0</v>
@@ -7912,10 +7904,10 @@
         <v>0</v>
       </c>
       <c r="K181" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L181" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M181" t="n">
         <v>0</v>
@@ -7927,9 +7919,7 @@
           <t>營造業</t>
         </is>
       </c>
-      <c r="B182" t="n">
-        <v>0</v>
-      </c>
+      <c r="B182" t="inlineStr"/>
       <c r="C182" t="n">
         <v>0</v>
       </c>
@@ -7937,19 +7927,19 @@
         <v>0</v>
       </c>
       <c r="E182" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F182" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G182" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H182" t="n">
         <v>1</v>
       </c>
       <c r="I182" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -8013,22 +8003,22 @@
       </c>
       <c r="B184" t="inlineStr"/>
       <c r="C184" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D184" t="n">
         <v>1</v>
       </c>
       <c r="E184" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F184" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G184" t="n">
         <v>1</v>
       </c>
       <c r="H184" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I184" t="n">
         <v>0</v>
@@ -8043,7 +8033,7 @@
         <v>0</v>
       </c>
       <c r="M184" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="185">
@@ -8183,19 +8173,19 @@
         <v>0</v>
       </c>
       <c r="E188" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F188" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G188" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H188" t="n">
         <v>1</v>
       </c>
       <c r="I188" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -8207,7 +8197,7 @@
         <v>0</v>
       </c>
       <c r="M188" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="189">
@@ -8242,10 +8232,10 @@
         <v>0</v>
       </c>
       <c r="K189" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L189" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M189" t="n">
         <v>0</v>
@@ -8265,10 +8255,10 @@
         <v>0</v>
       </c>
       <c r="E190" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F190" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G190" t="n">
         <v>0</v>
@@ -8298,7 +8288,9 @@
           <t>玻璃基板</t>
         </is>
       </c>
-      <c r="B191" t="inlineStr"/>
+      <c r="B191" t="n">
+        <v>0</v>
+      </c>
       <c r="C191" t="n">
         <v>0</v>
       </c>
@@ -8344,19 +8336,19 @@
         <v>0</v>
       </c>
       <c r="D192" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E192" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F192" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G192" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H192" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I192" t="n">
         <v>0</v>
@@ -8365,10 +8357,10 @@
         <v>0</v>
       </c>
       <c r="K192" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L192" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M192" t="n">
         <v>0</v>
@@ -8423,7 +8415,7 @@
       </c>
       <c r="B194" t="inlineStr"/>
       <c r="C194" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D194" t="n">
         <v>0</v>
@@ -8447,13 +8439,13 @@
         <v>0</v>
       </c>
       <c r="K194" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L194" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M194" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="195">
@@ -8470,13 +8462,13 @@
         <v>0</v>
       </c>
       <c r="E195" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F195" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G195" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H195" t="n">
         <v>0</v>
@@ -8511,28 +8503,28 @@
         <v>1</v>
       </c>
       <c r="E196" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F196" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G196" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H196" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I196" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J196" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K196" t="n">
         <v>1</v>
       </c>
       <c r="L196" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M196" t="n">
         <v>0</v>
@@ -8546,37 +8538,37 @@
       </c>
       <c r="B197" t="inlineStr"/>
       <c r="C197" t="n">
+        <v>3</v>
+      </c>
+      <c r="D197" t="n">
+        <v>5</v>
+      </c>
+      <c r="E197" t="n">
+        <v>1</v>
+      </c>
+      <c r="F197" t="n">
+        <v>6</v>
+      </c>
+      <c r="G197" t="n">
         <v>2</v>
       </c>
-      <c r="D197" t="n">
+      <c r="H197" t="n">
+        <v>1</v>
+      </c>
+      <c r="I197" t="n">
+        <v>1</v>
+      </c>
+      <c r="J197" t="n">
         <v>3</v>
       </c>
-      <c r="E197" t="n">
+      <c r="K197" t="n">
+        <v>8</v>
+      </c>
+      <c r="L197" t="n">
+        <v>0</v>
+      </c>
+      <c r="M197" t="n">
         <v>5</v>
-      </c>
-      <c r="F197" t="n">
-        <v>1</v>
-      </c>
-      <c r="G197" t="n">
-        <v>6</v>
-      </c>
-      <c r="H197" t="n">
-        <v>2</v>
-      </c>
-      <c r="I197" t="n">
-        <v>1</v>
-      </c>
-      <c r="J197" t="n">
-        <v>1</v>
-      </c>
-      <c r="K197" t="n">
-        <v>3</v>
-      </c>
-      <c r="L197" t="n">
-        <v>8</v>
-      </c>
-      <c r="M197" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="198">
@@ -8693,10 +8685,10 @@
         <v>0</v>
       </c>
       <c r="K200" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L200" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M200" t="n">
         <v>0</v>
@@ -8710,10 +8702,10 @@
       </c>
       <c r="B201" t="inlineStr"/>
       <c r="C201" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D201" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E201" t="n">
         <v>0</v>
@@ -8756,10 +8748,10 @@
         <v>0</v>
       </c>
       <c r="D202" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E202" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F202" t="n">
         <v>0</v>
@@ -8800,13 +8792,13 @@
         <v>0</v>
       </c>
       <c r="E203" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F203" t="n">
         <v>1</v>
       </c>
       <c r="G203" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H203" t="n">
         <v>0</v>
@@ -8833,9 +8825,7 @@
           <t>石化中間原料(例如乙烯、丙烯、丁二烯、苯、酚等)</t>
         </is>
       </c>
-      <c r="B204" t="n">
-        <v>0</v>
-      </c>
+      <c r="B204" t="inlineStr"/>
       <c r="C204" t="n">
         <v>0</v>
       </c>
@@ -8846,28 +8836,28 @@
         <v>0</v>
       </c>
       <c r="F204" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G204" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H204" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I204" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J204" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K204" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L204" t="n">
         <v>0</v>
       </c>
       <c r="M204" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="205">
@@ -8884,13 +8874,13 @@
         <v>0</v>
       </c>
       <c r="E205" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F205" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G205" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H205" t="n">
         <v>0</v>
@@ -8972,13 +8962,13 @@
         <v>0</v>
       </c>
       <c r="G207" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H207" t="n">
         <v>1</v>
       </c>
       <c r="I207" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J207" t="n">
         <v>0</v>
@@ -8999,36 +8989,38 @@
           <t>硬板、軟板、IC載板製造</t>
         </is>
       </c>
-      <c r="B208" t="inlineStr"/>
+      <c r="B208" t="n">
+        <v>0</v>
+      </c>
       <c r="C208" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D208" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E208" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F208" t="n">
         <v>5</v>
       </c>
       <c r="G208" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H208" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I208" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J208" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K208" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="L208" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="M208" t="n">
         <v>0</v>
@@ -9040,20 +9032,18 @@
           <t>硬碟機</t>
         </is>
       </c>
-      <c r="B209" t="n">
-        <v>0</v>
-      </c>
+      <c r="B209" t="inlineStr"/>
       <c r="C209" t="n">
         <v>0</v>
       </c>
       <c r="D209" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E209" t="n">
         <v>1</v>
       </c>
       <c r="F209" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G209" t="n">
         <v>0</v>
@@ -9091,10 +9081,10 @@
         <v>0</v>
       </c>
       <c r="E210" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F210" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G210" t="n">
         <v>0</v>
@@ -9126,19 +9116,19 @@
       </c>
       <c r="B211" t="inlineStr"/>
       <c r="C211" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D211" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E211" t="n">
         <v>2</v>
       </c>
       <c r="F211" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G211" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H211" t="n">
         <v>0</v>
@@ -9337,10 +9327,10 @@
         <v>0</v>
       </c>
       <c r="E216" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F216" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G216" t="n">
         <v>0</v>
@@ -9372,25 +9362,25 @@
       </c>
       <c r="B217" t="inlineStr"/>
       <c r="C217" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D217" t="n">
         <v>1</v>
       </c>
       <c r="E217" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F217" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G217" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H217" t="n">
         <v>1</v>
       </c>
       <c r="I217" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J217" t="n">
         <v>0</v>
@@ -9402,7 +9392,7 @@
         <v>0</v>
       </c>
       <c r="M217" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="218">
@@ -9413,22 +9403,22 @@
       </c>
       <c r="B218" t="inlineStr"/>
       <c r="C218" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D218" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E218" t="n">
         <v>1</v>
       </c>
       <c r="F218" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G218" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H218" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I218" t="n">
         <v>0</v>
@@ -9437,10 +9427,10 @@
         <v>0</v>
       </c>
       <c r="K218" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L218" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M218" t="n">
         <v>0</v>
@@ -9457,19 +9447,19 @@
         <v>0</v>
       </c>
       <c r="D219" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E219" t="n">
         <v>1</v>
       </c>
       <c r="F219" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G219" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H219" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I219" t="n">
         <v>0</v>
@@ -9478,10 +9468,10 @@
         <v>0</v>
       </c>
       <c r="K219" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L219" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M219" t="n">
         <v>0</v>
@@ -9493,41 +9483,39 @@
           <t>系統整合</t>
         </is>
       </c>
-      <c r="B220" t="n">
-        <v>0</v>
-      </c>
+      <c r="B220" t="inlineStr"/>
       <c r="C220" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D220" t="n">
+        <v>8</v>
+      </c>
+      <c r="E220" t="n">
         <v>5</v>
       </c>
-      <c r="E220" t="n">
-        <v>7</v>
-      </c>
       <c r="F220" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G220" t="n">
+        <v>2</v>
+      </c>
+      <c r="H220" t="n">
+        <v>1</v>
+      </c>
+      <c r="I220" t="n">
+        <v>0</v>
+      </c>
+      <c r="J220" t="n">
+        <v>1</v>
+      </c>
+      <c r="K220" t="n">
         <v>3</v>
       </c>
-      <c r="H220" t="n">
+      <c r="L220" t="n">
+        <v>0</v>
+      </c>
+      <c r="M220" t="n">
         <v>2</v>
-      </c>
-      <c r="I220" t="n">
-        <v>1</v>
-      </c>
-      <c r="J220" t="n">
-        <v>0</v>
-      </c>
-      <c r="K220" t="n">
-        <v>1</v>
-      </c>
-      <c r="L220" t="n">
-        <v>3</v>
-      </c>
-      <c r="M220" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="221">
@@ -9538,37 +9526,37 @@
       </c>
       <c r="B221" t="inlineStr"/>
       <c r="C221" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D221" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E221" t="n">
         <v>4</v>
       </c>
       <c r="F221" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G221" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H221" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I221" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J221" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K221" t="n">
         <v>1</v>
       </c>
       <c r="L221" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M221" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="222">
@@ -9591,10 +9579,10 @@
         <v>0</v>
       </c>
       <c r="G222" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H222" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I222" t="n">
         <v>0</v>
@@ -9618,21 +9606,23 @@
           <t>紡紗</t>
         </is>
       </c>
-      <c r="B223" t="inlineStr"/>
+      <c r="B223" t="n">
+        <v>0</v>
+      </c>
       <c r="C223" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D223" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E223" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F223" t="n">
         <v>1</v>
       </c>
       <c r="G223" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H223" t="n">
         <v>0</v>
@@ -9741,21 +9731,23 @@
           <t>網路IC</t>
         </is>
       </c>
-      <c r="B226" t="inlineStr"/>
+      <c r="B226" t="n">
+        <v>0</v>
+      </c>
       <c r="C226" t="n">
         <v>0</v>
       </c>
       <c r="D226" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E226" t="n">
         <v>0</v>
       </c>
       <c r="F226" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G226" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H226" t="n">
         <v>0</v>
@@ -9787,13 +9779,13 @@
         <v>0</v>
       </c>
       <c r="D227" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E227" t="n">
         <v>1</v>
       </c>
       <c r="F227" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G227" t="n">
         <v>0</v>
@@ -9828,22 +9820,22 @@
         <v>0</v>
       </c>
       <c r="D228" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E228" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F228" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G228" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H228" t="n">
         <v>1</v>
       </c>
       <c r="I228" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J228" t="n">
         <v>0</v>
@@ -9855,7 +9847,7 @@
         <v>0</v>
       </c>
       <c r="M228" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="229">
@@ -9869,22 +9861,22 @@
         <v>0</v>
       </c>
       <c r="D229" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E229" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F229" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G229" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H229" t="n">
         <v>1</v>
       </c>
       <c r="I229" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J229" t="n">
         <v>0</v>
@@ -9896,7 +9888,7 @@
         <v>0</v>
       </c>
       <c r="M229" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="230">
@@ -9907,37 +9899,37 @@
       </c>
       <c r="B230" t="inlineStr"/>
       <c r="C230" t="n">
+        <v>1</v>
+      </c>
+      <c r="D230" t="n">
         <v>2</v>
       </c>
-      <c r="D230" t="n">
-        <v>1</v>
-      </c>
       <c r="E230" t="n">
+        <v>6</v>
+      </c>
+      <c r="F230" t="n">
+        <v>1</v>
+      </c>
+      <c r="G230" t="n">
+        <v>1</v>
+      </c>
+      <c r="H230" t="n">
         <v>2</v>
       </c>
-      <c r="F230" t="n">
-        <v>6</v>
-      </c>
-      <c r="G230" t="n">
-        <v>1</v>
-      </c>
-      <c r="H230" t="n">
-        <v>1</v>
-      </c>
       <c r="I230" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J230" t="n">
         <v>0</v>
       </c>
       <c r="K230" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L230" t="n">
+        <v>1</v>
+      </c>
+      <c r="M230" t="n">
         <v>3</v>
-      </c>
-      <c r="M230" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="231">
@@ -9951,13 +9943,13 @@
         <v>1</v>
       </c>
       <c r="D231" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E231" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F231" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G231" t="n">
         <v>1</v>
@@ -9966,7 +9958,7 @@
         <v>1</v>
       </c>
       <c r="I231" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J231" t="n">
         <v>0</v>
@@ -9978,7 +9970,7 @@
         <v>0</v>
       </c>
       <c r="M231" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="232">
@@ -10004,22 +9996,22 @@
         <v>0</v>
       </c>
       <c r="H232" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I232" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J232" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K232" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L232" t="n">
         <v>0</v>
       </c>
       <c r="M232" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="233">
@@ -10030,37 +10022,37 @@
       </c>
       <c r="B233" t="inlineStr"/>
       <c r="C233" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D233" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E233" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F233" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G233" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H233" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I233" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J233" t="n">
         <v>0</v>
       </c>
       <c r="K233" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L233" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M233" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="234">
@@ -10112,19 +10104,19 @@
       </c>
       <c r="B235" t="inlineStr"/>
       <c r="C235" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D235" t="n">
         <v>0</v>
       </c>
       <c r="E235" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F235" t="n">
         <v>1</v>
       </c>
       <c r="G235" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H235" t="n">
         <v>0</v>
@@ -10142,7 +10134,7 @@
         <v>0</v>
       </c>
       <c r="M235" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="236">
@@ -10162,10 +10154,10 @@
         <v>0</v>
       </c>
       <c r="F236" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G236" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H236" t="n">
         <v>0</v>
@@ -10235,12 +10227,14 @@
           <t>背光源(發光二極體、冷陰極管)</t>
         </is>
       </c>
-      <c r="B238" t="inlineStr"/>
+      <c r="B238" t="n">
+        <v>0</v>
+      </c>
       <c r="C238" t="n">
         <v>0</v>
       </c>
       <c r="D238" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E238" t="n">
         <v>1</v>
@@ -10249,13 +10243,13 @@
         <v>1</v>
       </c>
       <c r="G238" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H238" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I238" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J238" t="n">
         <v>0</v>
@@ -10284,28 +10278,28 @@
         <v>0</v>
       </c>
       <c r="E239" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F239" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G239" t="n">
         <v>0</v>
       </c>
       <c r="H239" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I239" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J239" t="n">
         <v>0</v>
       </c>
       <c r="K239" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L239" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M239" t="n">
         <v>0</v>
@@ -10328,10 +10322,10 @@
         <v>0</v>
       </c>
       <c r="F240" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G240" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H240" t="n">
         <v>0</v>
@@ -10358,7 +10352,9 @@
           <t>臨床實驗、移植技術、疾病治療</t>
         </is>
       </c>
-      <c r="B241" t="inlineStr"/>
+      <c r="B241" t="n">
+        <v>0</v>
+      </c>
       <c r="C241" t="n">
         <v>0</v>
       </c>
@@ -10425,13 +10421,13 @@
         <v>0</v>
       </c>
       <c r="K242" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L242" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M242" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="243">
@@ -10524,16 +10520,16 @@
       </c>
       <c r="B245" t="inlineStr"/>
       <c r="C245" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D245" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E245" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F245" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G245" t="n">
         <v>0</v>
@@ -10554,7 +10550,7 @@
         <v>0</v>
       </c>
       <c r="M245" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="246">
@@ -10571,16 +10567,16 @@
         <v>0</v>
       </c>
       <c r="E246" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F246" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G246" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H246" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I246" t="n">
         <v>0</v>
@@ -10595,7 +10591,7 @@
         <v>0</v>
       </c>
       <c r="M246" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="247">
@@ -10615,10 +10611,10 @@
         <v>0</v>
       </c>
       <c r="F247" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G247" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H247" t="n">
         <v>0</v>
@@ -10647,10 +10643,10 @@
       </c>
       <c r="B248" t="inlineStr"/>
       <c r="C248" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D248" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E248" t="n">
         <v>0</v>
@@ -10686,14 +10682,12 @@
           <t>處理器/IC</t>
         </is>
       </c>
-      <c r="B249" t="n">
-        <v>0</v>
-      </c>
+      <c r="B249" t="inlineStr"/>
       <c r="C249" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D249" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E249" t="n">
         <v>0</v>
@@ -10731,19 +10725,19 @@
       </c>
       <c r="B250" t="inlineStr"/>
       <c r="C250" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D250" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E250" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F250" t="n">
         <v>1</v>
       </c>
       <c r="G250" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H250" t="n">
         <v>0</v>
@@ -10819,16 +10813,16 @@
         <v>0</v>
       </c>
       <c r="E252" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F252" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G252" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H252" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I252" t="n">
         <v>0</v>
@@ -10843,7 +10837,7 @@
         <v>0</v>
       </c>
       <c r="M252" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="253">
@@ -10951,10 +10945,10 @@
         <v>0</v>
       </c>
       <c r="H255" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I255" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J255" t="n">
         <v>0</v>
@@ -10977,10 +10971,10 @@
       </c>
       <c r="B256" t="inlineStr"/>
       <c r="C256" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D256" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E256" t="n">
         <v>0</v>
@@ -11007,7 +11001,7 @@
         <v>0</v>
       </c>
       <c r="M256" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="257">
@@ -11106,13 +11100,13 @@
         <v>0</v>
       </c>
       <c r="E259" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F259" t="n">
         <v>1</v>
       </c>
       <c r="G259" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H259" t="n">
         <v>0</v>
@@ -11139,7 +11133,9 @@
           <t>製造商</t>
         </is>
       </c>
-      <c r="B260" t="inlineStr"/>
+      <c r="B260" t="n">
+        <v>0</v>
+      </c>
       <c r="C260" t="n">
         <v>0</v>
       </c>
@@ -11180,15 +11176,17 @@
           <t>觸控面板</t>
         </is>
       </c>
-      <c r="B261" t="inlineStr"/>
+      <c r="B261" t="n">
+        <v>0</v>
+      </c>
       <c r="C261" t="n">
         <v>0</v>
       </c>
       <c r="D261" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E261" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F261" t="n">
         <v>0</v>
@@ -11221,27 +11219,29 @@
           <t>記憶體</t>
         </is>
       </c>
-      <c r="B262" t="inlineStr"/>
+      <c r="B262" t="n">
+        <v>0</v>
+      </c>
       <c r="C262" t="n">
+        <v>9</v>
+      </c>
+      <c r="D262" t="n">
+        <v>2</v>
+      </c>
+      <c r="E262" t="n">
+        <v>4</v>
+      </c>
+      <c r="F262" t="n">
         <v>3</v>
       </c>
-      <c r="D262" t="n">
-        <v>10</v>
-      </c>
-      <c r="E262" t="n">
+      <c r="G262" t="n">
+        <v>0</v>
+      </c>
+      <c r="H262" t="n">
         <v>2</v>
       </c>
-      <c r="F262" t="n">
-        <v>4</v>
-      </c>
-      <c r="G262" t="n">
-        <v>3</v>
-      </c>
-      <c r="H262" t="n">
-        <v>0</v>
-      </c>
       <c r="I262" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J262" t="n">
         <v>0</v>
@@ -11264,7 +11264,7 @@
       </c>
       <c r="B263" t="inlineStr"/>
       <c r="C263" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D263" t="n">
         <v>1</v>
@@ -11273,10 +11273,10 @@
         <v>1</v>
       </c>
       <c r="F263" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G263" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H263" t="n">
         <v>0</v>
@@ -11285,13 +11285,13 @@
         <v>0</v>
       </c>
       <c r="J263" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K263" t="n">
         <v>1</v>
       </c>
       <c r="L263" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M263" t="n">
         <v>0</v>
@@ -11305,22 +11305,22 @@
       </c>
       <c r="B264" t="inlineStr"/>
       <c r="C264" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D264" t="n">
         <v>1</v>
       </c>
       <c r="E264" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F264" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G264" t="n">
         <v>1</v>
       </c>
       <c r="H264" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I264" t="n">
         <v>0</v>
@@ -11329,13 +11329,13 @@
         <v>0</v>
       </c>
       <c r="K264" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L264" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M264" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="265">
@@ -11385,9 +11385,7 @@
           <t>證券業</t>
         </is>
       </c>
-      <c r="B266" t="n">
-        <v>0</v>
-      </c>
+      <c r="B266" t="inlineStr"/>
       <c r="C266" t="n">
         <v>0</v>
       </c>
@@ -11451,10 +11449,10 @@
         <v>0</v>
       </c>
       <c r="J267" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K267" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L267" t="n">
         <v>0</v>
@@ -11551,7 +11549,9 @@
           <t>貿易商、代理商、經銷商</t>
         </is>
       </c>
-      <c r="B270" t="inlineStr"/>
+      <c r="B270" t="n">
+        <v>0</v>
+      </c>
       <c r="C270" t="n">
         <v>0</v>
       </c>
@@ -11565,10 +11565,10 @@
         <v>0</v>
       </c>
       <c r="G270" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H270" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I270" t="n">
         <v>0</v>
@@ -11577,13 +11577,13 @@
         <v>0</v>
       </c>
       <c r="K270" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L270" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M270" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="271">
@@ -11641,19 +11641,19 @@
         <v>0</v>
       </c>
       <c r="E272" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F272" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G272" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H272" t="n">
         <v>1</v>
       </c>
       <c r="I272" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J272" t="n">
         <v>0</v>
@@ -11665,7 +11665,7 @@
         <v>0</v>
       </c>
       <c r="M272" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="273">
@@ -11679,19 +11679,19 @@
         <v>0</v>
       </c>
       <c r="D273" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E273" t="n">
         <v>1</v>
       </c>
       <c r="F273" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G273" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H273" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I273" t="n">
         <v>0</v>
@@ -11706,7 +11706,7 @@
         <v>0</v>
       </c>
       <c r="M273" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="274">
@@ -11720,22 +11720,22 @@
         <v>0</v>
       </c>
       <c r="D274" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E274" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F274" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G274" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H274" t="n">
         <v>1</v>
       </c>
       <c r="I274" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J274" t="n">
         <v>0</v>
@@ -11747,7 +11747,7 @@
         <v>0</v>
       </c>
       <c r="M274" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="275">
@@ -11758,22 +11758,22 @@
       </c>
       <c r="B275" t="inlineStr"/>
       <c r="C275" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D275" t="n">
         <v>1</v>
       </c>
       <c r="E275" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F275" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G275" t="n">
         <v>1</v>
       </c>
       <c r="H275" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I275" t="n">
         <v>0</v>
@@ -11788,7 +11788,7 @@
         <v>0</v>
       </c>
       <c r="M275" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="276">
@@ -11802,22 +11802,22 @@
         <v>0</v>
       </c>
       <c r="D276" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E276" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F276" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G276" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H276" t="n">
         <v>1</v>
       </c>
       <c r="I276" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J276" t="n">
         <v>0</v>
@@ -11829,7 +11829,7 @@
         <v>0</v>
       </c>
       <c r="M276" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="277">
@@ -11881,10 +11881,10 @@
       </c>
       <c r="B278" t="inlineStr"/>
       <c r="C278" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D278" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E278" t="n">
         <v>1</v>
@@ -11896,7 +11896,7 @@
         <v>1</v>
       </c>
       <c r="H278" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I278" t="n">
         <v>0</v>
@@ -11911,7 +11911,7 @@
         <v>0</v>
       </c>
       <c r="M278" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="279">
@@ -11922,10 +11922,10 @@
       </c>
       <c r="B279" t="inlineStr"/>
       <c r="C279" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D279" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E279" t="n">
         <v>1</v>
@@ -11934,7 +11934,7 @@
         <v>1</v>
       </c>
       <c r="G279" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H279" t="n">
         <v>0</v>
@@ -12007,22 +12007,22 @@
         <v>0</v>
       </c>
       <c r="D281" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E281" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F281" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G281" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H281" t="n">
         <v>1</v>
       </c>
       <c r="I281" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J281" t="n">
         <v>0</v>
@@ -12034,7 +12034,7 @@
         <v>0</v>
       </c>
       <c r="M281" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="282">
@@ -12253,10 +12253,10 @@
         <v>1</v>
       </c>
       <c r="D287" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E287" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F287" t="n">
         <v>1</v>
@@ -12265,7 +12265,7 @@
         <v>1</v>
       </c>
       <c r="H287" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I287" t="n">
         <v>0</v>
@@ -12280,7 +12280,7 @@
         <v>0</v>
       </c>
       <c r="M287" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="288">
@@ -12294,10 +12294,10 @@
         <v>0</v>
       </c>
       <c r="D288" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E288" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F288" t="n">
         <v>0</v>
@@ -12332,13 +12332,13 @@
       </c>
       <c r="B289" t="inlineStr"/>
       <c r="C289" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D289" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E289" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F289" t="n">
         <v>0</v>
@@ -12356,10 +12356,10 @@
         <v>0</v>
       </c>
       <c r="K289" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L289" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M289" t="n">
         <v>0</v>
@@ -12461,10 +12461,10 @@
         <v>0</v>
       </c>
       <c r="E292" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F292" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G292" t="n">
         <v>0</v>
@@ -12537,16 +12537,16 @@
       </c>
       <c r="B294" t="inlineStr"/>
       <c r="C294" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D294" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E294" t="n">
         <v>1</v>
       </c>
       <c r="F294" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G294" t="n">
         <v>0</v>
@@ -12602,10 +12602,10 @@
         <v>0</v>
       </c>
       <c r="K295" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L295" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M295" t="n">
         <v>0</v>
@@ -12628,10 +12628,10 @@
         <v>0</v>
       </c>
       <c r="F296" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G296" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H296" t="n">
         <v>0</v>
@@ -12827,19 +12827,19 @@
         <v>0</v>
       </c>
       <c r="D301" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E301" t="n">
         <v>1</v>
       </c>
       <c r="F301" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G301" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H301" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I301" t="n">
         <v>0</v>
@@ -12854,7 +12854,7 @@
         <v>0</v>
       </c>
       <c r="M301" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="302">
@@ -12865,37 +12865,37 @@
       </c>
       <c r="B302" t="inlineStr"/>
       <c r="C302" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D302" t="n">
+        <v>0</v>
+      </c>
+      <c r="E302" t="n">
+        <v>1</v>
+      </c>
+      <c r="F302" t="n">
         <v>2</v>
       </c>
-      <c r="E302" t="n">
-        <v>0</v>
-      </c>
-      <c r="F302" t="n">
-        <v>1</v>
-      </c>
       <c r="G302" t="n">
+        <v>1</v>
+      </c>
+      <c r="H302" t="n">
         <v>2</v>
       </c>
-      <c r="H302" t="n">
-        <v>1</v>
-      </c>
       <c r="I302" t="n">
+        <v>0</v>
+      </c>
+      <c r="J302" t="n">
+        <v>0</v>
+      </c>
+      <c r="K302" t="n">
+        <v>1</v>
+      </c>
+      <c r="L302" t="n">
+        <v>0</v>
+      </c>
+      <c r="M302" t="n">
         <v>2</v>
-      </c>
-      <c r="J302" t="n">
-        <v>0</v>
-      </c>
-      <c r="K302" t="n">
-        <v>0</v>
-      </c>
-      <c r="L302" t="n">
-        <v>1</v>
-      </c>
-      <c r="M302" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="303">
@@ -12906,37 +12906,37 @@
       </c>
       <c r="B303" t="inlineStr"/>
       <c r="C303" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D303" t="n">
         <v>1</v>
       </c>
       <c r="E303" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F303" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G303" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H303" t="n">
         <v>1</v>
       </c>
       <c r="I303" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J303" t="n">
         <v>0</v>
       </c>
       <c r="K303" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L303" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M303" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="304">
@@ -13070,7 +13070,7 @@
       </c>
       <c r="B307" t="inlineStr"/>
       <c r="C307" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D307" t="n">
         <v>1</v>
@@ -13082,7 +13082,7 @@
         <v>1</v>
       </c>
       <c r="G307" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H307" t="n">
         <v>0</v>
@@ -13094,10 +13094,10 @@
         <v>0</v>
       </c>
       <c r="K307" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L307" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M307" t="n">
         <v>0</v>
@@ -13114,10 +13114,10 @@
         <v>0</v>
       </c>
       <c r="D308" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E308" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F308" t="n">
         <v>0</v>
@@ -13135,10 +13135,10 @@
         <v>0</v>
       </c>
       <c r="K308" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L308" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M308" t="n">
         <v>0</v>
@@ -13202,10 +13202,10 @@
         <v>0</v>
       </c>
       <c r="F310" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G310" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H310" t="n">
         <v>0</v>
@@ -13214,13 +13214,13 @@
         <v>0</v>
       </c>
       <c r="J310" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K310" t="n">
         <v>1</v>
       </c>
       <c r="L310" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M310" t="n">
         <v>0</v>
@@ -13255,10 +13255,10 @@
         <v>0</v>
       </c>
       <c r="J311" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K311" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L311" t="n">
         <v>0</v>
@@ -13281,13 +13281,13 @@
         <v>0</v>
       </c>
       <c r="E312" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F312" t="n">
         <v>1</v>
       </c>
       <c r="G312" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H312" t="n">
         <v>0</v>
@@ -13328,7 +13328,7 @@
         <v>1</v>
       </c>
       <c r="G313" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H313" t="n">
         <v>0</v>
@@ -13340,13 +13340,13 @@
         <v>0</v>
       </c>
       <c r="K313" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L313" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M313" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="314">
@@ -13362,31 +13362,31 @@
         <v>2</v>
       </c>
       <c r="D314" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E314" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F314" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G314" t="n">
         <v>0</v>
       </c>
       <c r="H314" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I314" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J314" t="n">
         <v>0</v>
       </c>
       <c r="K314" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L314" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M314" t="n">
         <v>0</v>
@@ -13439,24 +13439,26 @@
           <t>金屬、塑膠模具</t>
         </is>
       </c>
-      <c r="B316" t="inlineStr"/>
+      <c r="B316" t="n">
+        <v>0</v>
+      </c>
       <c r="C316" t="n">
+        <v>0</v>
+      </c>
+      <c r="D316" t="n">
+        <v>1</v>
+      </c>
+      <c r="E316" t="n">
         <v>2</v>
       </c>
-      <c r="D316" t="n">
-        <v>0</v>
-      </c>
-      <c r="E316" t="n">
-        <v>1</v>
-      </c>
       <c r="F316" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G316" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H316" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I316" t="n">
         <v>0</v>
@@ -13482,7 +13484,7 @@
       </c>
       <c r="B317" t="inlineStr"/>
       <c r="C317" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D317" t="n">
         <v>0</v>
@@ -13523,10 +13525,10 @@
       </c>
       <c r="B318" t="inlineStr"/>
       <c r="C318" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D318" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E318" t="n">
         <v>0</v>
@@ -13538,10 +13540,10 @@
         <v>0</v>
       </c>
       <c r="H318" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I318" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J318" t="n">
         <v>0</v>
@@ -13605,10 +13607,10 @@
       </c>
       <c r="B320" t="inlineStr"/>
       <c r="C320" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D320" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E320" t="n">
         <v>0</v>
@@ -13824,7 +13826,7 @@
         <v>1</v>
       </c>
       <c r="G325" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H325" t="n">
         <v>0</v>
@@ -13836,10 +13838,10 @@
         <v>0</v>
       </c>
       <c r="K325" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L325" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M325" t="n">
         <v>0</v>
@@ -13859,13 +13861,13 @@
         <v>0</v>
       </c>
       <c r="E326" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F326" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G326" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H326" t="n">
         <v>0</v>
@@ -13877,13 +13879,13 @@
         <v>0</v>
       </c>
       <c r="K326" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L326" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M326" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="327">
@@ -13906,10 +13908,10 @@
         <v>0</v>
       </c>
       <c r="G327" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H327" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I327" t="n">
         <v>0</v>
@@ -13985,25 +13987,25 @@
         <v>0</v>
       </c>
       <c r="F329" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G329" t="n">
         <v>1</v>
       </c>
       <c r="H329" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I329" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J329" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K329" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L329" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M329" t="n">
         <v>0</v>
@@ -14108,10 +14110,10 @@
         <v>0</v>
       </c>
       <c r="F332" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G332" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H332" t="n">
         <v>0</v>
@@ -14196,10 +14198,10 @@
         <v>0</v>
       </c>
       <c r="H334" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I334" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J334" t="n">
         <v>0</v>
@@ -14269,10 +14271,10 @@
         <v>0</v>
       </c>
       <c r="E336" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F336" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G336" t="n">
         <v>0</v>
@@ -14304,19 +14306,19 @@
       </c>
       <c r="B337" t="inlineStr"/>
       <c r="C337" t="n">
+        <v>4</v>
+      </c>
+      <c r="D337" t="n">
         <v>2</v>
       </c>
-      <c r="D337" t="n">
-        <v>4</v>
-      </c>
       <c r="E337" t="n">
+        <v>3</v>
+      </c>
+      <c r="F337" t="n">
         <v>2</v>
       </c>
-      <c r="F337" t="n">
-        <v>3</v>
-      </c>
       <c r="G337" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H337" t="n">
         <v>0</v>
@@ -14345,7 +14347,7 @@
       </c>
       <c r="B338" t="inlineStr"/>
       <c r="C338" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D338" t="n">
         <v>1</v>
@@ -14357,7 +14359,7 @@
         <v>1</v>
       </c>
       <c r="G338" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H338" t="n">
         <v>0</v>
@@ -14389,13 +14391,13 @@
         <v>1</v>
       </c>
       <c r="D339" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E339" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F339" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G339" t="n">
         <v>1</v>
@@ -14404,7 +14406,7 @@
         <v>1</v>
       </c>
       <c r="I339" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J339" t="n">
         <v>0</v>
@@ -14416,7 +14418,7 @@
         <v>0</v>
       </c>
       <c r="M339" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="340">
@@ -14427,22 +14429,22 @@
       </c>
       <c r="B340" t="inlineStr"/>
       <c r="C340" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D340" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E340" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F340" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G340" t="n">
         <v>1</v>
       </c>
       <c r="H340" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I340" t="n">
         <v>0</v>
@@ -14457,7 +14459,7 @@
         <v>0</v>
       </c>
       <c r="M340" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="341">
@@ -14468,22 +14470,22 @@
       </c>
       <c r="B341" t="inlineStr"/>
       <c r="C341" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D341" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E341" t="n">
         <v>2</v>
       </c>
       <c r="F341" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G341" t="n">
         <v>1</v>
       </c>
       <c r="H341" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I341" t="n">
         <v>0</v>
@@ -14492,13 +14494,13 @@
         <v>0</v>
       </c>
       <c r="K341" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L341" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M341" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="342">
@@ -14527,19 +14529,19 @@
         <v>0</v>
       </c>
       <c r="I342" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J342" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K342" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L342" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M342" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="343">
@@ -14550,16 +14552,16 @@
       </c>
       <c r="B343" t="inlineStr"/>
       <c r="C343" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D343" t="n">
         <v>1</v>
       </c>
       <c r="E343" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F343" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G343" t="n">
         <v>0</v>
@@ -14574,13 +14576,13 @@
         <v>0</v>
       </c>
       <c r="K343" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L343" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M343" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="344">
@@ -14600,10 +14602,10 @@
         <v>0</v>
       </c>
       <c r="F344" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G344" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H344" t="n">
         <v>0</v>
@@ -14653,13 +14655,13 @@
         <v>0</v>
       </c>
       <c r="J345" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K345" t="n">
         <v>1</v>
       </c>
       <c r="L345" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M345" t="n">
         <v>0</v>
@@ -14682,10 +14684,10 @@
         <v>0</v>
       </c>
       <c r="F346" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G346" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H346" t="n">
         <v>0</v>
@@ -14694,13 +14696,13 @@
         <v>0</v>
       </c>
       <c r="J346" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K346" t="n">
         <v>1</v>
       </c>
       <c r="L346" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M346" t="n">
         <v>0</v>
@@ -14767,10 +14769,10 @@
         <v>0</v>
       </c>
       <c r="G348" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H348" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I348" t="n">
         <v>0</v>
@@ -14779,10 +14781,10 @@
         <v>0</v>
       </c>
       <c r="K348" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L348" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M348" t="n">
         <v>0</v>
@@ -14820,10 +14822,10 @@
         <v>0</v>
       </c>
       <c r="K349" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L349" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M349" t="n">
         <v>0</v>
@@ -14832,30 +14834,30 @@
     <row r="350">
       <c r="A350" s="1" t="inlineStr">
         <is>
-          <t>電子零組件、塑膠零件、五金零件</t>
+          <t>電子觸控白板</t>
         </is>
       </c>
       <c r="B350" t="inlineStr"/>
       <c r="C350" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D350" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E350" t="n">
         <v>0</v>
       </c>
       <c r="F350" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G350" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H350" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I350" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J350" t="n">
         <v>0</v>
@@ -14864,7 +14866,7 @@
         <v>0</v>
       </c>
       <c r="L350" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M350" t="n">
         <v>0</v>
@@ -14873,26 +14875,24 @@
     <row r="351">
       <c r="A351" s="1" t="inlineStr">
         <is>
-          <t>電容器</t>
-        </is>
-      </c>
-      <c r="B351" t="n">
-        <v>0</v>
-      </c>
+          <t>電子零組件、塑膠零件、五金零件</t>
+        </is>
+      </c>
+      <c r="B351" t="inlineStr"/>
       <c r="C351" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D351" t="n">
         <v>0</v>
       </c>
       <c r="E351" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F351" t="n">
         <v>1</v>
       </c>
       <c r="G351" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="H351" t="n">
         <v>1</v>
@@ -14901,22 +14901,22 @@
         <v>0</v>
       </c>
       <c r="J351" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K351" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L351" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M351" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="352">
       <c r="A352" s="1" t="inlineStr">
         <is>
-          <t>電容器材料(如電蝕／化成鋁箔、介面瓷粉)</t>
+          <t>電容器</t>
         </is>
       </c>
       <c r="B352" t="n">
@@ -14926,13 +14926,13 @@
         <v>0</v>
       </c>
       <c r="D352" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E352" t="n">
         <v>1</v>
       </c>
       <c r="F352" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="G352" t="n">
         <v>1</v>
@@ -14941,30 +14941,28 @@
         <v>0</v>
       </c>
       <c r="I352" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J352" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K352" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L352" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M352" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="353">
       <c r="A353" s="1" t="inlineStr">
         <is>
-          <t>電感器</t>
-        </is>
-      </c>
-      <c r="B353" t="n">
-        <v>0</v>
-      </c>
+          <t>電容器材料(如電蝕／化成鋁箔、介面瓷粉)</t>
+        </is>
+      </c>
+      <c r="B353" t="inlineStr"/>
       <c r="C353" t="n">
         <v>0</v>
       </c>
@@ -14972,28 +14970,28 @@
         <v>1</v>
       </c>
       <c r="E353" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F353" t="n">
         <v>2</v>
       </c>
       <c r="G353" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H353" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I353" t="n">
         <v>0</v>
       </c>
       <c r="J353" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K353" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L353" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M353" t="n">
         <v>0</v>
@@ -15002,36 +15000,38 @@
     <row r="354">
       <c r="A354" s="1" t="inlineStr">
         <is>
-          <t>電感器材料(如鐵氧體、導電漿墨)</t>
-        </is>
-      </c>
-      <c r="B354" t="inlineStr"/>
+          <t>電感器</t>
+        </is>
+      </c>
+      <c r="B354" t="n">
+        <v>0</v>
+      </c>
       <c r="C354" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D354" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E354" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F354" t="n">
+        <v>3</v>
+      </c>
+      <c r="G354" t="n">
         <v>2</v>
       </c>
-      <c r="G354" t="n">
-        <v>1</v>
-      </c>
       <c r="H354" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I354" t="n">
         <v>0</v>
       </c>
       <c r="J354" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K354" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L354" t="n">
         <v>0</v>
@@ -15043,7 +15043,7 @@
     <row r="355">
       <c r="A355" s="1" t="inlineStr">
         <is>
-          <t>電控元件</t>
+          <t>電感器材料(如鐵氧體、導電漿墨)</t>
         </is>
       </c>
       <c r="B355" t="inlineStr"/>
@@ -15054,10 +15054,10 @@
         <v>1</v>
       </c>
       <c r="E355" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F355" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G355" t="n">
         <v>1</v>
@@ -15075,7 +15075,7 @@
         <v>0</v>
       </c>
       <c r="L355" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M355" t="n">
         <v>0</v>
@@ -15084,18 +15084,20 @@
     <row r="356">
       <c r="A356" s="1" t="inlineStr">
         <is>
-          <t>電池</t>
-        </is>
-      </c>
-      <c r="B356" t="inlineStr"/>
+          <t>電控元件</t>
+        </is>
+      </c>
+      <c r="B356" t="n">
+        <v>0</v>
+      </c>
       <c r="C356" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D356" t="n">
         <v>0</v>
       </c>
       <c r="E356" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F356" t="n">
         <v>1</v>
@@ -15113,10 +15115,10 @@
         <v>0</v>
       </c>
       <c r="K356" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L356" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M356" t="n">
         <v>0</v>
@@ -15125,7 +15127,7 @@
     <row r="357">
       <c r="A357" s="1" t="inlineStr">
         <is>
-          <t>電池模組</t>
+          <t>電池</t>
         </is>
       </c>
       <c r="B357" t="inlineStr"/>
@@ -15133,10 +15135,10 @@
         <v>0</v>
       </c>
       <c r="D357" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E357" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F357" t="n">
         <v>0</v>
@@ -15151,13 +15153,13 @@
         <v>0</v>
       </c>
       <c r="J357" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K357" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L357" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M357" t="n">
         <v>0</v>
@@ -15166,10 +15168,12 @@
     <row r="358">
       <c r="A358" s="1" t="inlineStr">
         <is>
-          <t>電池芯</t>
-        </is>
-      </c>
-      <c r="B358" t="inlineStr"/>
+          <t>電池模組</t>
+        </is>
+      </c>
+      <c r="B358" t="n">
+        <v>0</v>
+      </c>
       <c r="C358" t="n">
         <v>0</v>
       </c>
@@ -15189,16 +15193,16 @@
         <v>0</v>
       </c>
       <c r="I358" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J358" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K358" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L358" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M358" t="n">
         <v>0</v>
@@ -15207,30 +15211,30 @@
     <row r="359">
       <c r="A359" s="1" t="inlineStr">
         <is>
-          <t>電源供應器</t>
+          <t>電池芯</t>
         </is>
       </c>
       <c r="B359" t="inlineStr"/>
       <c r="C359" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D359" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E359" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F359" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G359" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H359" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I359" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J359" t="n">
         <v>0</v>
@@ -15239,7 +15243,7 @@
         <v>1</v>
       </c>
       <c r="L359" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M359" t="n">
         <v>0</v>
@@ -15248,24 +15252,24 @@
     <row r="360">
       <c r="A360" s="1" t="inlineStr">
         <is>
-          <t>電網營造</t>
+          <t>電源供應器</t>
         </is>
       </c>
       <c r="B360" t="inlineStr"/>
       <c r="C360" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D360" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E360" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F360" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G360" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H360" t="n">
         <v>0</v>
@@ -15274,7 +15278,7 @@
         <v>0</v>
       </c>
       <c r="J360" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K360" t="n">
         <v>1</v>
@@ -15283,13 +15287,13 @@
         <v>0</v>
       </c>
       <c r="M360" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="361">
       <c r="A361" s="1" t="inlineStr">
         <is>
-          <t>電網維運</t>
+          <t>電網營造</t>
         </is>
       </c>
       <c r="B361" t="inlineStr"/>
@@ -15315,7 +15319,7 @@
         <v>0</v>
       </c>
       <c r="J361" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K361" t="n">
         <v>0</v>
@@ -15330,7 +15334,7 @@
     <row r="362">
       <c r="A362" s="1" t="inlineStr">
         <is>
-          <t>電纜</t>
+          <t>電網維運</t>
         </is>
       </c>
       <c r="B362" t="inlineStr"/>
@@ -15347,7 +15351,7 @@
         <v>0</v>
       </c>
       <c r="G362" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H362" t="n">
         <v>0</v>
@@ -15371,12 +15375,10 @@
     <row r="363">
       <c r="A363" s="1" t="inlineStr">
         <is>
-          <t>電腦視覺</t>
-        </is>
-      </c>
-      <c r="B363" t="n">
-        <v>0</v>
-      </c>
+          <t>電纜</t>
+        </is>
+      </c>
+      <c r="B363" t="inlineStr"/>
       <c r="C363" t="n">
         <v>0</v>
       </c>
@@ -15387,7 +15389,7 @@
         <v>0</v>
       </c>
       <c r="F363" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G363" t="n">
         <v>0</v>
@@ -15396,7 +15398,7 @@
         <v>0</v>
       </c>
       <c r="I363" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J363" t="n">
         <v>0</v>
@@ -15405,7 +15407,7 @@
         <v>0</v>
       </c>
       <c r="L363" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M363" t="n">
         <v>0</v>
@@ -15414,7 +15416,7 @@
     <row r="364">
       <c r="A364" s="1" t="inlineStr">
         <is>
-          <t>電腦設備</t>
+          <t>電腦視覺</t>
         </is>
       </c>
       <c r="B364" t="inlineStr"/>
@@ -15422,19 +15424,19 @@
         <v>1</v>
       </c>
       <c r="D364" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E364" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F364" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G364" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H364" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I364" t="n">
         <v>0</v>
@@ -15443,10 +15445,10 @@
         <v>0</v>
       </c>
       <c r="K364" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L364" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M364" t="n">
         <v>0</v>
@@ -15455,21 +15457,21 @@
     <row r="365">
       <c r="A365" s="1" t="inlineStr">
         <is>
-          <t>電視</t>
+          <t>電腦設備</t>
         </is>
       </c>
       <c r="B365" t="inlineStr"/>
       <c r="C365" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D365" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E365" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F365" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G365" t="n">
         <v>0</v>
@@ -15484,7 +15486,7 @@
         <v>0</v>
       </c>
       <c r="K365" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L365" t="n">
         <v>0</v>
@@ -15496,10 +15498,12 @@
     <row r="366">
       <c r="A366" s="1" t="inlineStr">
         <is>
-          <t>電鍍材料</t>
-        </is>
-      </c>
-      <c r="B366" t="inlineStr"/>
+          <t>電視</t>
+        </is>
+      </c>
+      <c r="B366" t="n">
+        <v>0</v>
+      </c>
       <c r="C366" t="n">
         <v>0</v>
       </c>
@@ -15537,12 +15541,10 @@
     <row r="367">
       <c r="A367" s="1" t="inlineStr">
         <is>
-          <t>電阻器</t>
-        </is>
-      </c>
-      <c r="B367" t="n">
-        <v>0</v>
-      </c>
+          <t>電鍍材料</t>
+        </is>
+      </c>
+      <c r="B367" t="inlineStr"/>
       <c r="C367" t="n">
         <v>0</v>
       </c>
@@ -15550,16 +15552,16 @@
         <v>0</v>
       </c>
       <c r="E367" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F367" t="n">
         <v>0</v>
       </c>
       <c r="G367" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H367" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I367" t="n">
         <v>0</v>
@@ -15568,10 +15570,10 @@
         <v>0</v>
       </c>
       <c r="K367" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L367" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M367" t="n">
         <v>0</v>
@@ -15580,7 +15582,7 @@
     <row r="368">
       <c r="A368" s="1" t="inlineStr">
         <is>
-          <t>電阻器材料(氧化鋁陶瓷基板、導電漿墨)</t>
+          <t>電阻器</t>
         </is>
       </c>
       <c r="B368" t="inlineStr"/>
@@ -15588,16 +15590,16 @@
         <v>0</v>
       </c>
       <c r="D368" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E368" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F368" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G368" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H368" t="n">
         <v>0</v>
@@ -15606,10 +15608,10 @@
         <v>0</v>
       </c>
       <c r="J368" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K368" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L368" t="n">
         <v>0</v>
@@ -15621,7 +15623,7 @@
     <row r="369">
       <c r="A369" s="1" t="inlineStr">
         <is>
-          <t>面板</t>
+          <t>電阻器材料(氧化鋁陶瓷基板、導電漿墨)</t>
         </is>
       </c>
       <c r="B369" t="inlineStr"/>
@@ -15629,13 +15631,13 @@
         <v>0</v>
       </c>
       <c r="D369" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E369" t="n">
         <v>1</v>
       </c>
       <c r="F369" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G369" t="n">
         <v>0</v>
@@ -15653,7 +15655,7 @@
         <v>0</v>
       </c>
       <c r="L369" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M369" t="n">
         <v>0</v>
@@ -15662,7 +15664,7 @@
     <row r="370">
       <c r="A370" s="1" t="inlineStr">
         <is>
-          <t>預拌混凝土</t>
+          <t>面板</t>
         </is>
       </c>
       <c r="B370" t="inlineStr"/>
@@ -15670,10 +15672,10 @@
         <v>0</v>
       </c>
       <c r="D370" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E370" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F370" t="n">
         <v>0</v>
@@ -15691,7 +15693,7 @@
         <v>0</v>
       </c>
       <c r="K370" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L370" t="n">
         <v>0</v>
@@ -15703,7 +15705,7 @@
     <row r="371">
       <c r="A371" s="1" t="inlineStr">
         <is>
-          <t>領域方案</t>
+          <t>預拌混凝土</t>
         </is>
       </c>
       <c r="B371" t="inlineStr"/>
@@ -15744,32 +15746,30 @@
     <row r="372">
       <c r="A372" s="1" t="inlineStr">
         <is>
-          <t>領域解決方案</t>
-        </is>
-      </c>
-      <c r="B372" t="n">
-        <v>0</v>
-      </c>
+          <t>領域方案</t>
+        </is>
+      </c>
+      <c r="B372" t="inlineStr"/>
       <c r="C372" t="n">
         <v>0</v>
       </c>
       <c r="D372" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E372" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F372" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G372" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H372" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I372" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J372" t="n">
         <v>0</v>
@@ -15778,38 +15778,36 @@
         <v>0</v>
       </c>
       <c r="L372" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M372" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="373">
       <c r="A373" s="1" t="inlineStr">
         <is>
-          <t>頭顯裝置品牌廠</t>
-        </is>
-      </c>
-      <c r="B373" t="n">
-        <v>0</v>
-      </c>
+          <t>領域解決方案</t>
+        </is>
+      </c>
+      <c r="B373" t="inlineStr"/>
       <c r="C373" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D373" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E373" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F373" t="n">
         <v>1</v>
       </c>
       <c r="G373" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H373" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I373" t="n">
         <v>0</v>
@@ -15818,36 +15816,36 @@
         <v>0</v>
       </c>
       <c r="K373" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L373" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M373" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="374">
       <c r="A374" s="1" t="inlineStr">
         <is>
-          <t>顏染料</t>
+          <t>頭顯裝置品牌廠</t>
         </is>
       </c>
       <c r="B374" t="inlineStr"/>
       <c r="C374" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D374" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E374" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F374" t="n">
         <v>0</v>
       </c>
       <c r="G374" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H374" t="n">
         <v>0</v>
@@ -15871,7 +15869,7 @@
     <row r="375">
       <c r="A375" s="1" t="inlineStr">
         <is>
-          <t>顧問諮詢</t>
+          <t>顏染料</t>
         </is>
       </c>
       <c r="B375" t="inlineStr"/>
@@ -15879,19 +15877,19 @@
         <v>0</v>
       </c>
       <c r="D375" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E375" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F375" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G375" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H375" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I375" t="n">
         <v>0</v>
@@ -15900,10 +15898,10 @@
         <v>0</v>
       </c>
       <c r="K375" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L375" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M375" t="n">
         <v>0</v>
@@ -15912,24 +15910,24 @@
     <row r="376">
       <c r="A376" s="1" t="inlineStr">
         <is>
-          <t>顯示卡</t>
+          <t>顧問諮詢</t>
         </is>
       </c>
       <c r="B376" t="inlineStr"/>
       <c r="C376" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D376" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E376" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F376" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G376" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H376" t="n">
         <v>0</v>
@@ -15938,27 +15936,25 @@
         <v>0</v>
       </c>
       <c r="J376" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K376" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L376" t="n">
         <v>0</v>
       </c>
       <c r="M376" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="377">
       <c r="A377" s="1" t="inlineStr">
         <is>
-          <t>顯示器模組</t>
-        </is>
-      </c>
-      <c r="B377" t="n">
-        <v>0</v>
-      </c>
+          <t>顯示卡</t>
+        </is>
+      </c>
+      <c r="B377" t="inlineStr"/>
       <c r="C377" t="n">
         <v>0</v>
       </c>
@@ -15966,10 +15962,10 @@
         <v>1</v>
       </c>
       <c r="E377" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F377" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G377" t="n">
         <v>0</v>
@@ -15996,18 +15992,18 @@
     <row r="378">
       <c r="A378" s="1" t="inlineStr">
         <is>
-          <t>風場營造</t>
+          <t>顯示器模組</t>
         </is>
       </c>
       <c r="B378" t="inlineStr"/>
       <c r="C378" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D378" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E378" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F378" t="n">
         <v>0</v>
@@ -16031,13 +16027,13 @@
         <v>0</v>
       </c>
       <c r="M378" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="379">
       <c r="A379" s="1" t="inlineStr">
         <is>
-          <t>風場規劃</t>
+          <t>風場營造</t>
         </is>
       </c>
       <c r="B379" t="inlineStr"/>
@@ -16078,7 +16074,7 @@
     <row r="380">
       <c r="A380" s="1" t="inlineStr">
         <is>
-          <t>風場開發</t>
+          <t>風場規劃</t>
         </is>
       </c>
       <c r="B380" t="inlineStr"/>
@@ -16119,7 +16115,7 @@
     <row r="381">
       <c r="A381" s="1" t="inlineStr">
         <is>
-          <t>風機維護</t>
+          <t>風場開發</t>
         </is>
       </c>
       <c r="B381" t="inlineStr"/>
@@ -16160,7 +16156,7 @@
     <row r="382">
       <c r="A382" s="1" t="inlineStr">
         <is>
-          <t>餐飲連鎖</t>
+          <t>風機維護</t>
         </is>
       </c>
       <c r="B382" t="inlineStr"/>
@@ -16174,7 +16170,7 @@
         <v>0</v>
       </c>
       <c r="F382" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G382" t="n">
         <v>0</v>
@@ -16183,7 +16179,7 @@
         <v>0</v>
       </c>
       <c r="I382" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J382" t="n">
         <v>0</v>
@@ -16195,13 +16191,13 @@
         <v>0</v>
       </c>
       <c r="M382" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="383">
       <c r="A383" s="1" t="inlineStr">
         <is>
-          <t>驅動IC</t>
+          <t>餐飲連鎖</t>
         </is>
       </c>
       <c r="B383" t="inlineStr"/>
@@ -16212,7 +16208,7 @@
         <v>0</v>
       </c>
       <c r="E383" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F383" t="n">
         <v>0</v>
@@ -16221,7 +16217,7 @@
         <v>0</v>
       </c>
       <c r="H383" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I383" t="n">
         <v>0</v>
@@ -16233,7 +16229,7 @@
         <v>0</v>
       </c>
       <c r="L383" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M383" t="n">
         <v>0</v>
@@ -16242,7 +16238,7 @@
     <row r="384">
       <c r="A384" s="1" t="inlineStr">
         <is>
-          <t>高/低壓輸電設施</t>
+          <t>驅動IC</t>
         </is>
       </c>
       <c r="B384" t="inlineStr"/>
@@ -16256,10 +16252,10 @@
         <v>0</v>
       </c>
       <c r="F384" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G384" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H384" t="n">
         <v>0</v>
@@ -16271,10 +16267,10 @@
         <v>0</v>
       </c>
       <c r="K384" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L384" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M384" t="n">
         <v>0</v>
@@ -16283,7 +16279,7 @@
     <row r="385">
       <c r="A385" s="1" t="inlineStr">
         <is>
-          <t>高壓AMI</t>
+          <t>高/低壓輸電設施</t>
         </is>
       </c>
       <c r="B385" t="inlineStr"/>
@@ -16294,10 +16290,10 @@
         <v>0</v>
       </c>
       <c r="E385" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F385" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G385" t="n">
         <v>0</v>
@@ -16309,10 +16305,10 @@
         <v>0</v>
       </c>
       <c r="J385" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K385" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L385" t="n">
         <v>0</v>
@@ -16324,7 +16320,7 @@
     <row r="386">
       <c r="A386" s="1" t="inlineStr">
         <is>
-          <t>高爾夫球具業</t>
+          <t>高壓AMI</t>
         </is>
       </c>
       <c r="B386" t="inlineStr"/>
@@ -16365,7 +16361,7 @@
     <row r="387">
       <c r="A387" s="1" t="inlineStr">
         <is>
-          <t>齒輪箱</t>
+          <t>高爾夫球具業</t>
         </is>
       </c>
       <c r="B387" t="inlineStr"/>
@@ -16400,6 +16396,47 @@
         <v>0</v>
       </c>
       <c r="M387" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" s="1" t="inlineStr">
+        <is>
+          <t>齒輪箱</t>
+        </is>
+      </c>
+      <c r="B388" t="inlineStr"/>
+      <c r="C388" t="n">
+        <v>0</v>
+      </c>
+      <c r="D388" t="n">
+        <v>0</v>
+      </c>
+      <c r="E388" t="n">
+        <v>0</v>
+      </c>
+      <c r="F388" t="n">
+        <v>0</v>
+      </c>
+      <c r="G388" t="n">
+        <v>0</v>
+      </c>
+      <c r="H388" t="n">
+        <v>0</v>
+      </c>
+      <c r="I388" t="n">
+        <v>0</v>
+      </c>
+      <c r="J388" t="n">
+        <v>0</v>
+      </c>
+      <c r="K388" t="n">
+        <v>0</v>
+      </c>
+      <c r="L388" t="n">
+        <v>0</v>
+      </c>
+      <c r="M388" t="n">
         <v>0</v>
       </c>
     </row>

--- a/Result/analyze_3.xlsx
+++ b/Result/analyze_3.xlsx
@@ -441,57 +441,57 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
     </row>
@@ -544,13 +544,13 @@
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D3" t="n">
         <v>1</v>
       </c>
       <c r="E3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -665,38 +665,36 @@
           <t>IC/晶圓製造</t>
         </is>
       </c>
-      <c r="B6" t="n">
-        <v>0</v>
-      </c>
+      <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" t="n">
         <v>3</v>
       </c>
-      <c r="D6" t="n">
-        <v>1</v>
-      </c>
-      <c r="E6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" t="n">
-        <v>1</v>
-      </c>
       <c r="H6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M6" t="n">
         <v>2</v>
@@ -708,39 +706,41 @@
           <t>IC封裝測試</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr"/>
+      <c r="B7" t="n">
+        <v>0</v>
+      </c>
       <c r="C7" t="n">
+        <v>2</v>
+      </c>
+      <c r="D7" t="n">
+        <v>5</v>
+      </c>
+      <c r="E7" t="n">
         <v>3</v>
       </c>
-      <c r="D7" t="n">
+      <c r="F7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
         <v>2</v>
       </c>
-      <c r="E7" t="n">
-        <v>5</v>
-      </c>
-      <c r="F7" t="n">
-        <v>3</v>
-      </c>
-      <c r="G7" t="n">
-        <v>1</v>
-      </c>
-      <c r="H7" t="n">
-        <v>1</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
       <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
         <v>2</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -751,37 +751,37 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E8" t="n">
         <v>2</v>
       </c>
       <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
         <v>2</v>
       </c>
-      <c r="G8" t="n">
-        <v>0</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
       <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
         <v>2</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -790,41 +790,39 @@
           <t>IC設計</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>0</v>
-      </c>
+      <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D9" t="n">
+        <v>3</v>
+      </c>
+      <c r="E9" t="n">
+        <v>2</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="n">
+        <v>3</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1</v>
+      </c>
+      <c r="M9" t="n">
         <v>4</v>
-      </c>
-      <c r="E9" t="n">
-        <v>3</v>
-      </c>
-      <c r="F9" t="n">
-        <v>2</v>
-      </c>
-      <c r="G9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H9" t="n">
-        <v>1</v>
-      </c>
-      <c r="I9" t="n">
-        <v>1</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" t="n">
-        <v>3</v>
-      </c>
-      <c r="L9" t="n">
-        <v>1</v>
-      </c>
-      <c r="M9" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -833,41 +831,39 @@
           <t>IC通路</t>
         </is>
       </c>
-      <c r="B10" t="n">
-        <v>0</v>
-      </c>
+      <c r="B10" t="inlineStr"/>
       <c r="C10" t="n">
         <v>3</v>
       </c>
       <c r="D10" t="n">
+        <v>2</v>
+      </c>
+      <c r="E10" t="n">
         <v>3</v>
       </c>
-      <c r="E10" t="n">
-        <v>2</v>
-      </c>
       <c r="F10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
         <v>3</v>
       </c>
-      <c r="G10" t="n">
-        <v>1</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
       <c r="K10" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -878,7 +874,7 @@
       </c>
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
@@ -890,25 +886,25 @@
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="n">
+        <v>1</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1</v>
+      </c>
+      <c r="M11" t="n">
         <v>2</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>1</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -919,16 +915,16 @@
       </c>
       <c r="B12" t="inlineStr"/>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -966,10 +962,10 @@
         <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -1040,40 +1036,20 @@
           <t>ITO靶材</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr"/>
-      <c r="C15" t="n">
-        <v>0</v>
-      </c>
-      <c r="D15" t="n">
-        <v>0</v>
-      </c>
-      <c r="E15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
+      <c r="B15" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
@@ -1124,13 +1100,13 @@
       </c>
       <c r="B17" t="inlineStr"/>
       <c r="C17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F17" t="n">
         <v>0</v>
@@ -1151,10 +1127,10 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -1212,16 +1188,16 @@
         <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
@@ -1253,10 +1229,10 @@
         <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -1286,41 +1262,39 @@
           <t>中、西藥製劑</t>
         </is>
       </c>
-      <c r="B21" t="n">
-        <v>0</v>
-      </c>
+      <c r="B21" t="inlineStr"/>
       <c r="C21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G21" t="n">
         <v>1</v>
       </c>
       <c r="H21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -1329,17 +1303,15 @@
           <t>中央處理器</t>
         </is>
       </c>
-      <c r="B22" t="n">
-        <v>0</v>
-      </c>
+      <c r="B22" t="inlineStr"/>
       <c r="C22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D22" t="n">
         <v>1</v>
       </c>
       <c r="E22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F22" t="n">
         <v>0</v>
@@ -1383,10 +1355,10 @@
         <v>0</v>
       </c>
       <c r="F23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H23" t="n">
         <v>0</v>
@@ -1395,16 +1367,16 @@
         <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -1418,13 +1390,13 @@
         <v>0</v>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E24" t="n">
         <v>1</v>
       </c>
       <c r="F24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -1436,16 +1408,16 @@
         <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K24" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M24" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="25">
@@ -1462,7 +1434,7 @@
         <v>1</v>
       </c>
       <c r="E25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
@@ -1486,7 +1458,7 @@
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -1538,7 +1510,7 @@
       </c>
       <c r="B27" t="inlineStr"/>
       <c r="C27" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D27" t="n">
         <v>0</v>
@@ -1550,10 +1522,10 @@
         <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I27" t="n">
         <v>0</v>
@@ -1664,13 +1636,13 @@
         <v>0</v>
       </c>
       <c r="D30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F30" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -1702,16 +1674,16 @@
       </c>
       <c r="B31" t="inlineStr"/>
       <c r="C31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F31" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
@@ -1743,31 +1715,31 @@
       </c>
       <c r="B32" t="inlineStr"/>
       <c r="C32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D32" t="n">
         <v>0</v>
       </c>
       <c r="E32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I32" t="n">
         <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
@@ -1784,13 +1756,13 @@
       </c>
       <c r="B33" t="inlineStr"/>
       <c r="C33" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D33" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F33" t="n">
         <v>0</v>
@@ -1864,9 +1836,11 @@
           <t>保健食品代理銷售及通路</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr"/>
+      <c r="B35" t="n">
+        <v>0</v>
+      </c>
       <c r="C35" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D35" t="n">
         <v>0</v>
@@ -1893,7 +1867,7 @@
         <v>0</v>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M35" t="n">
         <v>1</v>
@@ -1989,13 +1963,13 @@
       </c>
       <c r="B38" t="inlineStr"/>
       <c r="C38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F38" t="n">
         <v>0</v>
@@ -2057,10 +2031,10 @@
         <v>0</v>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -2112,10 +2086,10 @@
       </c>
       <c r="B41" t="inlineStr"/>
       <c r="C41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E41" t="n">
         <v>0</v>
@@ -2133,10 +2107,10 @@
         <v>0</v>
       </c>
       <c r="J41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L41" t="n">
         <v>0</v>
@@ -2153,7 +2127,7 @@
       </c>
       <c r="B42" t="inlineStr"/>
       <c r="C42" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D42" t="n">
         <v>1</v>
@@ -2162,7 +2136,7 @@
         <v>1</v>
       </c>
       <c r="F42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
@@ -2174,16 +2148,16 @@
         <v>0</v>
       </c>
       <c r="J42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L42" t="n">
         <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="43">
@@ -2194,7 +2168,7 @@
       </c>
       <c r="B43" t="inlineStr"/>
       <c r="C43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D43" t="n">
         <v>0</v>
@@ -2224,7 +2198,7 @@
         <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="44">
@@ -2235,7 +2209,7 @@
       </c>
       <c r="B44" t="inlineStr"/>
       <c r="C44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D44" t="n">
         <v>1</v>
@@ -2244,7 +2218,7 @@
         <v>1</v>
       </c>
       <c r="F44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
@@ -2253,19 +2227,19 @@
         <v>0</v>
       </c>
       <c r="I44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K44" t="n">
         <v>0</v>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M44" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -2276,10 +2250,10 @@
       </c>
       <c r="B45" t="inlineStr"/>
       <c r="C45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E45" t="n">
         <v>0</v>
@@ -2306,7 +2280,7 @@
         <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="46">
@@ -2317,13 +2291,13 @@
       </c>
       <c r="B46" t="inlineStr"/>
       <c r="C46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D46" t="n">
         <v>1</v>
       </c>
       <c r="E46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F46" t="n">
         <v>0</v>
@@ -2358,13 +2332,13 @@
       </c>
       <c r="B47" t="inlineStr"/>
       <c r="C47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D47" t="n">
         <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F47" t="n">
         <v>0</v>
@@ -2388,7 +2362,7 @@
         <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="48">
@@ -2440,37 +2414,37 @@
       </c>
       <c r="B49" t="inlineStr"/>
       <c r="C49" t="n">
+        <v>1</v>
+      </c>
+      <c r="D49" t="n">
         <v>2</v>
-      </c>
-      <c r="D49" t="n">
-        <v>1</v>
       </c>
       <c r="E49" t="n">
         <v>2</v>
       </c>
       <c r="F49" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G49" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H49" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J49" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K49" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L49" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="M49" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="50">
@@ -2524,16 +2498,16 @@
         <v>0</v>
       </c>
       <c r="C51" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D51" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E51" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F51" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G51" t="n">
         <v>1</v>
@@ -2545,16 +2519,16 @@
         <v>1</v>
       </c>
       <c r="J51" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K51" t="n">
+        <v>1</v>
+      </c>
+      <c r="L51" t="n">
         <v>3</v>
       </c>
-      <c r="L51" t="n">
-        <v>1</v>
-      </c>
       <c r="M51" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="52">
@@ -2606,31 +2580,31 @@
       </c>
       <c r="B53" t="inlineStr"/>
       <c r="C53" t="n">
+        <v>1</v>
+      </c>
+      <c r="D53" t="n">
+        <v>1</v>
+      </c>
+      <c r="E53" t="n">
+        <v>3</v>
+      </c>
+      <c r="F53" t="n">
         <v>2</v>
-      </c>
-      <c r="D53" t="n">
-        <v>1</v>
-      </c>
-      <c r="E53" t="n">
-        <v>1</v>
-      </c>
-      <c r="F53" t="n">
-        <v>3</v>
       </c>
       <c r="G53" t="n">
         <v>2</v>
       </c>
       <c r="H53" t="n">
+        <v>0</v>
+      </c>
+      <c r="I53" t="n">
+        <v>0</v>
+      </c>
+      <c r="J53" t="n">
         <v>2</v>
       </c>
-      <c r="I53" t="n">
-        <v>0</v>
-      </c>
-      <c r="J53" t="n">
-        <v>0</v>
-      </c>
       <c r="K53" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L53" t="n">
         <v>0</v>
@@ -2650,34 +2624,34 @@
         <v>1</v>
       </c>
       <c r="D54" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E54" t="n">
         <v>4</v>
       </c>
       <c r="F54" t="n">
+        <v>0</v>
+      </c>
+      <c r="G54" t="n">
+        <v>1</v>
+      </c>
+      <c r="H54" t="n">
+        <v>1</v>
+      </c>
+      <c r="I54" t="n">
+        <v>1</v>
+      </c>
+      <c r="J54" t="n">
         <v>4</v>
       </c>
-      <c r="G54" t="n">
-        <v>0</v>
-      </c>
-      <c r="H54" t="n">
-        <v>0</v>
-      </c>
-      <c r="I54" t="n">
-        <v>1</v>
-      </c>
-      <c r="J54" t="n">
-        <v>1</v>
-      </c>
       <c r="K54" t="n">
+        <v>0</v>
+      </c>
+      <c r="L54" t="n">
         <v>4</v>
       </c>
-      <c r="L54" t="n">
-        <v>0</v>
-      </c>
       <c r="M54" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="55">
@@ -2686,29 +2660,27 @@
           <t>其他電腦及週邊設備</t>
         </is>
       </c>
-      <c r="B55" t="n">
-        <v>0</v>
-      </c>
+      <c r="B55" t="inlineStr"/>
       <c r="C55" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D55" t="n">
+        <v>4</v>
+      </c>
+      <c r="E55" t="n">
         <v>2</v>
       </c>
-      <c r="E55" t="n">
-        <v>4</v>
-      </c>
       <c r="F55" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H55" t="n">
         <v>0</v>
       </c>
       <c r="I55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J55" t="n">
         <v>1</v>
@@ -2717,10 +2689,10 @@
         <v>1</v>
       </c>
       <c r="L55" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M55" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="56">
@@ -2729,41 +2701,39 @@
           <t>其他電腦及週邊設備之零組件</t>
         </is>
       </c>
-      <c r="B56" t="n">
-        <v>0</v>
-      </c>
+      <c r="B56" t="inlineStr"/>
       <c r="C56" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D56" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E56" t="n">
+        <v>4</v>
+      </c>
+      <c r="F56" t="n">
+        <v>1</v>
+      </c>
+      <c r="G56" t="n">
         <v>2</v>
       </c>
-      <c r="F56" t="n">
-        <v>4</v>
-      </c>
-      <c r="G56" t="n">
-        <v>1</v>
-      </c>
       <c r="H56" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I56" t="n">
         <v>0</v>
       </c>
       <c r="J56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="57">
@@ -2815,16 +2785,16 @@
       </c>
       <c r="B58" t="inlineStr"/>
       <c r="C58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D58" t="n">
         <v>0</v>
       </c>
       <c r="E58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
@@ -2833,10 +2803,10 @@
         <v>0</v>
       </c>
       <c r="I58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K58" t="n">
         <v>0</v>
@@ -2862,10 +2832,10 @@
         <v>0</v>
       </c>
       <c r="E59" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
@@ -2874,13 +2844,13 @@
         <v>0</v>
       </c>
       <c r="I59" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J59" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K59" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L59" t="n">
         <v>0</v>
@@ -2895,9 +2865,7 @@
           <t>冷熱軋不鏽鋼板捲</t>
         </is>
       </c>
-      <c r="B60" t="n">
-        <v>0</v>
-      </c>
+      <c r="B60" t="inlineStr"/>
       <c r="C60" t="n">
         <v>0</v>
       </c>
@@ -2905,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="E60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
@@ -3031,7 +2999,7 @@
         <v>1</v>
       </c>
       <c r="F63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
@@ -3189,10 +3157,10 @@
         <v>0</v>
       </c>
       <c r="D67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F67" t="n">
         <v>0</v>
@@ -3216,7 +3184,7 @@
         <v>0</v>
       </c>
       <c r="M67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="68">
@@ -3230,10 +3198,10 @@
         <v>0</v>
       </c>
       <c r="D68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F68" t="n">
         <v>0</v>
@@ -3356,31 +3324,31 @@
         <v>0</v>
       </c>
       <c r="E71" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F71" t="n">
+        <v>0</v>
+      </c>
+      <c r="G71" t="n">
+        <v>1</v>
+      </c>
+      <c r="H71" t="n">
+        <v>0</v>
+      </c>
+      <c r="I71" t="n">
+        <v>0</v>
+      </c>
+      <c r="J71" t="n">
+        <v>0</v>
+      </c>
+      <c r="K71" t="n">
+        <v>0</v>
+      </c>
+      <c r="L71" t="n">
+        <v>1</v>
+      </c>
+      <c r="M71" t="n">
         <v>2</v>
-      </c>
-      <c r="G71" t="n">
-        <v>0</v>
-      </c>
-      <c r="H71" t="n">
-        <v>1</v>
-      </c>
-      <c r="I71" t="n">
-        <v>0</v>
-      </c>
-      <c r="J71" t="n">
-        <v>0</v>
-      </c>
-      <c r="K71" t="n">
-        <v>0</v>
-      </c>
-      <c r="L71" t="n">
-        <v>0</v>
-      </c>
-      <c r="M71" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="72">
@@ -3389,7 +3357,9 @@
           <t>化學品</t>
         </is>
       </c>
-      <c r="B72" t="inlineStr"/>
+      <c r="B72" t="n">
+        <v>0</v>
+      </c>
       <c r="C72" t="n">
         <v>0</v>
       </c>
@@ -3397,31 +3367,31 @@
         <v>0</v>
       </c>
       <c r="E72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I72" t="n">
         <v>0</v>
       </c>
       <c r="J72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M72" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="73">
@@ -3430,7 +3400,9 @@
           <t>化學品(如光阻劑、靶材等)</t>
         </is>
       </c>
-      <c r="B73" t="inlineStr"/>
+      <c r="B73" t="n">
+        <v>0</v>
+      </c>
       <c r="C73" t="n">
         <v>0</v>
       </c>
@@ -3453,10 +3425,10 @@
         <v>0</v>
       </c>
       <c r="J73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K73" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L73" t="n">
         <v>0</v>
@@ -3517,13 +3489,13 @@
         <v>0</v>
       </c>
       <c r="D75" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E75" t="n">
         <v>1</v>
       </c>
       <c r="F75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G75" t="n">
         <v>0</v>
@@ -3555,13 +3527,13 @@
       </c>
       <c r="B76" t="inlineStr"/>
       <c r="C76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D76" t="n">
         <v>1</v>
       </c>
       <c r="E76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F76" t="n">
         <v>0</v>
@@ -3585,7 +3557,7 @@
         <v>0</v>
       </c>
       <c r="M76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="77">
@@ -3626,7 +3598,7 @@
         <v>0</v>
       </c>
       <c r="M77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="78">
@@ -3635,39 +3607,41 @@
           <t>原材料</t>
         </is>
       </c>
-      <c r="B78" t="inlineStr"/>
+      <c r="B78" t="n">
+        <v>0</v>
+      </c>
       <c r="C78" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D78" t="n">
         <v>0</v>
       </c>
       <c r="E78" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F78" t="n">
+        <v>1</v>
+      </c>
+      <c r="G78" t="n">
         <v>2</v>
-      </c>
-      <c r="G78" t="n">
-        <v>1</v>
       </c>
       <c r="H78" t="n">
         <v>2</v>
       </c>
       <c r="I78" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J78" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K78" t="n">
         <v>0</v>
       </c>
       <c r="L78" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M78" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="79">
@@ -3722,10 +3696,10 @@
         <v>0</v>
       </c>
       <c r="D80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E80" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F80" t="n">
         <v>0</v>
@@ -3790,7 +3764,7 @@
         <v>0</v>
       </c>
       <c r="M81" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="82">
@@ -3807,10 +3781,10 @@
         <v>0</v>
       </c>
       <c r="E82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
@@ -3842,37 +3816,37 @@
       </c>
       <c r="B83" t="inlineStr"/>
       <c r="C83" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D83" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E83" t="n">
+        <v>1</v>
+      </c>
+      <c r="F83" t="n">
+        <v>0</v>
+      </c>
+      <c r="G83" t="n">
+        <v>1</v>
+      </c>
+      <c r="H83" t="n">
+        <v>0</v>
+      </c>
+      <c r="I83" t="n">
+        <v>0</v>
+      </c>
+      <c r="J83" t="n">
         <v>2</v>
       </c>
-      <c r="F83" t="n">
-        <v>1</v>
-      </c>
-      <c r="G83" t="n">
-        <v>0</v>
-      </c>
-      <c r="H83" t="n">
-        <v>1</v>
-      </c>
-      <c r="I83" t="n">
-        <v>0</v>
-      </c>
-      <c r="J83" t="n">
-        <v>0</v>
-      </c>
       <c r="K83" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L83" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M83" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="84">
@@ -3968,16 +3942,16 @@
         <v>0</v>
       </c>
       <c r="D86" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E86" t="n">
         <v>1</v>
       </c>
       <c r="F86" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G86" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H86" t="n">
         <v>0</v>
@@ -4006,22 +3980,22 @@
       </c>
       <c r="B87" t="inlineStr"/>
       <c r="C87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D87" t="n">
         <v>0</v>
       </c>
       <c r="E87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I87" t="n">
         <v>0</v>
@@ -4045,17 +4019,15 @@
           <t>塑膠框</t>
         </is>
       </c>
-      <c r="B88" t="n">
-        <v>0</v>
-      </c>
+      <c r="B88" t="inlineStr"/>
       <c r="C88" t="n">
         <v>0</v>
       </c>
       <c r="D88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F88" t="n">
         <v>0</v>
@@ -4070,10 +4042,10 @@
         <v>0</v>
       </c>
       <c r="J88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L88" t="n">
         <v>0</v>
@@ -4090,31 +4062,31 @@
       </c>
       <c r="B89" t="inlineStr"/>
       <c r="C89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D89" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E89" t="n">
         <v>1</v>
       </c>
       <c r="F89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G89" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I89" t="n">
         <v>0</v>
       </c>
       <c r="J89" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L89" t="n">
         <v>0</v>
@@ -4172,13 +4144,13 @@
       </c>
       <c r="B91" t="inlineStr"/>
       <c r="C91" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D91" t="n">
         <v>1</v>
       </c>
       <c r="E91" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F91" t="n">
         <v>0</v>
@@ -4211,23 +4183,21 @@
           <t>大功率鋰電池芯/模組、電池管理系統、動力馬達等零組件</t>
         </is>
       </c>
-      <c r="B92" t="n">
-        <v>0</v>
-      </c>
+      <c r="B92" t="inlineStr"/>
       <c r="C92" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D92" t="n">
         <v>0</v>
       </c>
       <c r="E92" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F92" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G92" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H92" t="n">
         <v>1</v>
@@ -4236,10 +4206,10 @@
         <v>1</v>
       </c>
       <c r="J92" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K92" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L92" t="n">
         <v>0</v>
@@ -4344,31 +4314,31 @@
         <v>0</v>
       </c>
       <c r="E95" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F95" t="n">
+        <v>0</v>
+      </c>
+      <c r="G95" t="n">
+        <v>0</v>
+      </c>
+      <c r="H95" t="n">
+        <v>0</v>
+      </c>
+      <c r="I95" t="n">
+        <v>1</v>
+      </c>
+      <c r="J95" t="n">
+        <v>1</v>
+      </c>
+      <c r="K95" t="n">
+        <v>0</v>
+      </c>
+      <c r="L95" t="n">
+        <v>0</v>
+      </c>
+      <c r="M95" t="n">
         <v>2</v>
-      </c>
-      <c r="G95" t="n">
-        <v>0</v>
-      </c>
-      <c r="H95" t="n">
-        <v>0</v>
-      </c>
-      <c r="I95" t="n">
-        <v>0</v>
-      </c>
-      <c r="J95" t="n">
-        <v>1</v>
-      </c>
-      <c r="K95" t="n">
-        <v>1</v>
-      </c>
-      <c r="L95" t="n">
-        <v>0</v>
-      </c>
-      <c r="M95" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="96">
@@ -4385,10 +4355,10 @@
         <v>0</v>
       </c>
       <c r="E96" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F96" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G96" t="n">
         <v>0</v>
@@ -4400,16 +4370,16 @@
         <v>0</v>
       </c>
       <c r="J96" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K96" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L96" t="n">
         <v>0</v>
       </c>
       <c r="M96" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="97">
@@ -4526,10 +4496,10 @@
         <v>0</v>
       </c>
       <c r="K99" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M99" t="n">
         <v>0</v>
@@ -4587,16 +4557,16 @@
         <v>0</v>
       </c>
       <c r="D101" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E101" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F101" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G101" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H101" t="n">
         <v>0</v>
@@ -4611,10 +4581,10 @@
         <v>0</v>
       </c>
       <c r="L101" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M101" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="102">
@@ -4625,34 +4595,34 @@
       </c>
       <c r="B102" t="inlineStr"/>
       <c r="C102" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D102" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E102" t="n">
+        <v>1</v>
+      </c>
+      <c r="F102" t="n">
+        <v>1</v>
+      </c>
+      <c r="G102" t="n">
+        <v>0</v>
+      </c>
+      <c r="H102" t="n">
+        <v>0</v>
+      </c>
+      <c r="I102" t="n">
+        <v>0</v>
+      </c>
+      <c r="J102" t="n">
         <v>2</v>
       </c>
-      <c r="F102" t="n">
-        <v>1</v>
-      </c>
-      <c r="G102" t="n">
-        <v>1</v>
-      </c>
-      <c r="H102" t="n">
-        <v>0</v>
-      </c>
-      <c r="I102" t="n">
-        <v>0</v>
-      </c>
-      <c r="J102" t="n">
-        <v>0</v>
-      </c>
       <c r="K102" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L102" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M102" t="n">
         <v>0</v>
@@ -4710,16 +4680,16 @@
         <v>0</v>
       </c>
       <c r="D104" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E104" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F104" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G104" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H104" t="n">
         <v>0</v>
@@ -4728,16 +4698,16 @@
         <v>0</v>
       </c>
       <c r="J104" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K104" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L104" t="n">
         <v>0</v>
       </c>
       <c r="M104" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="105">
@@ -4748,37 +4718,37 @@
       </c>
       <c r="B105" t="inlineStr"/>
       <c r="C105" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D105" t="n">
         <v>1</v>
       </c>
       <c r="E105" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F105" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G105" t="n">
         <v>1</v>
       </c>
       <c r="H105" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I105" t="n">
         <v>0</v>
       </c>
       <c r="J105" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K105" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L105" t="n">
         <v>0</v>
       </c>
       <c r="M105" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="106">
@@ -4789,31 +4759,31 @@
       </c>
       <c r="B106" t="inlineStr"/>
       <c r="C106" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D106" t="n">
+        <v>1</v>
+      </c>
+      <c r="E106" t="n">
         <v>2</v>
       </c>
-      <c r="E106" t="n">
-        <v>1</v>
-      </c>
       <c r="F106" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G106" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H106" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I106" t="n">
         <v>0</v>
       </c>
       <c r="J106" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K106" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L106" t="n">
         <v>0</v>
@@ -4953,10 +4923,10 @@
       </c>
       <c r="B110" t="inlineStr"/>
       <c r="C110" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D110" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E110" t="n">
         <v>0</v>
@@ -4974,10 +4944,10 @@
         <v>0</v>
       </c>
       <c r="J110" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K110" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L110" t="n">
         <v>0</v>
@@ -4994,19 +4964,19 @@
       </c>
       <c r="B111" t="inlineStr"/>
       <c r="C111" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D111" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E111" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F111" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G111" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H111" t="n">
         <v>0</v>
@@ -5021,7 +4991,7 @@
         <v>0</v>
       </c>
       <c r="L111" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M111" t="n">
         <v>1</v>
@@ -5041,10 +5011,10 @@
         <v>0</v>
       </c>
       <c r="E112" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F112" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G112" t="n">
         <v>0</v>
@@ -5053,10 +5023,10 @@
         <v>0</v>
       </c>
       <c r="I112" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J112" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K112" t="n">
         <v>0</v>
@@ -5065,7 +5035,7 @@
         <v>0</v>
       </c>
       <c r="M112" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="113">
@@ -5082,10 +5052,10 @@
         <v>0</v>
       </c>
       <c r="E113" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F113" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G113" t="n">
         <v>0</v>
@@ -5094,10 +5064,10 @@
         <v>0</v>
       </c>
       <c r="I113" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J113" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K113" t="n">
         <v>0</v>
@@ -5144,10 +5114,10 @@
         <v>0</v>
       </c>
       <c r="L114" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M114" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="115">
@@ -5156,9 +5126,7 @@
           <t>幹細胞收集儲存</t>
         </is>
       </c>
-      <c r="B115" t="n">
-        <v>0</v>
-      </c>
+      <c r="B115" t="inlineStr"/>
       <c r="C115" t="n">
         <v>0</v>
       </c>
@@ -5190,7 +5158,7 @@
         <v>0</v>
       </c>
       <c r="M115" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="116">
@@ -5199,9 +5167,7 @@
           <t>幹細胞開發</t>
         </is>
       </c>
-      <c r="B116" t="n">
-        <v>0</v>
-      </c>
+      <c r="B116" t="inlineStr"/>
       <c r="C116" t="n">
         <v>0</v>
       </c>
@@ -5233,7 +5199,7 @@
         <v>0</v>
       </c>
       <c r="M116" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="117">
@@ -5326,13 +5292,13 @@
       </c>
       <c r="B119" t="inlineStr"/>
       <c r="C119" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D119" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E119" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F119" t="n">
         <v>0</v>
@@ -5370,28 +5336,28 @@
         <v>1</v>
       </c>
       <c r="D120" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E120" t="n">
+        <v>0</v>
+      </c>
+      <c r="F120" t="n">
+        <v>1</v>
+      </c>
+      <c r="G120" t="n">
+        <v>1</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0</v>
+      </c>
+      <c r="J120" t="n">
         <v>2</v>
       </c>
-      <c r="F120" t="n">
-        <v>0</v>
-      </c>
-      <c r="G120" t="n">
-        <v>1</v>
-      </c>
-      <c r="H120" t="n">
-        <v>1</v>
-      </c>
-      <c r="I120" t="n">
-        <v>0</v>
-      </c>
-      <c r="J120" t="n">
-        <v>0</v>
-      </c>
       <c r="K120" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L120" t="n">
         <v>0</v>
@@ -5406,9 +5372,7 @@
           <t>建設業</t>
         </is>
       </c>
-      <c r="B121" t="n">
-        <v>0</v>
-      </c>
+      <c r="B121" t="inlineStr"/>
       <c r="C121" t="n">
         <v>0</v>
       </c>
@@ -5416,10 +5380,10 @@
         <v>0</v>
       </c>
       <c r="E121" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F121" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G121" t="n">
         <v>0</v>
@@ -5431,16 +5395,16 @@
         <v>0</v>
       </c>
       <c r="J121" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K121" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L121" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M121" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="122">
@@ -5531,9 +5495,7 @@
           <t>微處理器</t>
         </is>
       </c>
-      <c r="B124" t="n">
-        <v>0</v>
-      </c>
+      <c r="B124" t="inlineStr"/>
       <c r="C124" t="n">
         <v>0</v>
       </c>
@@ -5541,10 +5503,10 @@
         <v>0</v>
       </c>
       <c r="E124" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F124" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G124" t="n">
         <v>0</v>
@@ -5617,10 +5579,10 @@
       </c>
       <c r="B126" t="inlineStr"/>
       <c r="C126" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D126" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E126" t="n">
         <v>0</v>
@@ -5658,10 +5620,10 @@
       </c>
       <c r="B127" t="inlineStr"/>
       <c r="C127" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D127" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E127" t="n">
         <v>0</v>
@@ -5705,25 +5667,25 @@
         <v>2</v>
       </c>
       <c r="E128" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F128" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G128" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H128" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I128" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J128" t="n">
         <v>1</v>
       </c>
       <c r="K128" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L128" t="n">
         <v>0</v>
@@ -5749,7 +5711,7 @@
         <v>1</v>
       </c>
       <c r="F129" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G129" t="n">
         <v>0</v>
@@ -5784,10 +5746,10 @@
         <v>0</v>
       </c>
       <c r="D130" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E130" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F130" t="n">
         <v>0</v>
@@ -5828,7 +5790,7 @@
         <v>0</v>
       </c>
       <c r="E131" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F131" t="n">
         <v>1</v>
@@ -5837,13 +5799,13 @@
         <v>1</v>
       </c>
       <c r="H131" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I131" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J131" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K131" t="n">
         <v>0</v>
@@ -5872,10 +5834,10 @@
         <v>0</v>
       </c>
       <c r="F132" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G132" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H132" t="n">
         <v>0</v>
@@ -5907,10 +5869,10 @@
         <v>0</v>
       </c>
       <c r="D133" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E133" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F133" t="n">
         <v>0</v>
@@ -6068,10 +6030,10 @@
       </c>
       <c r="B137" t="inlineStr"/>
       <c r="C137" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D137" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E137" t="n">
         <v>0</v>
@@ -6156,7 +6118,7 @@
         <v>1</v>
       </c>
       <c r="E139" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F139" t="n">
         <v>0</v>
@@ -6171,10 +6133,10 @@
         <v>0</v>
       </c>
       <c r="J139" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K139" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L139" t="n">
         <v>0</v>
@@ -6221,7 +6183,7 @@
         <v>0</v>
       </c>
       <c r="M140" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="141">
@@ -6235,7 +6197,7 @@
         <v>0</v>
       </c>
       <c r="D141" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E141" t="n">
         <v>1</v>
@@ -6244,7 +6206,7 @@
         <v>1</v>
       </c>
       <c r="G141" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H141" t="n">
         <v>0</v>
@@ -6262,7 +6224,7 @@
         <v>0</v>
       </c>
       <c r="M141" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="142">
@@ -6303,7 +6265,7 @@
         <v>0</v>
       </c>
       <c r="M142" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="143">
@@ -6317,10 +6279,10 @@
         <v>0</v>
       </c>
       <c r="D143" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E143" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F143" t="n">
         <v>0</v>
@@ -6358,19 +6320,19 @@
         <v>0</v>
       </c>
       <c r="D144" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E144" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F144" t="n">
         <v>0</v>
       </c>
       <c r="G144" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H144" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I144" t="n">
         <v>0</v>
@@ -6382,10 +6344,10 @@
         <v>0</v>
       </c>
       <c r="L144" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M144" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="145">
@@ -6399,16 +6361,16 @@
         <v>0</v>
       </c>
       <c r="D145" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E145" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F145" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G145" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H145" t="n">
         <v>0</v>
@@ -6423,10 +6385,10 @@
         <v>0</v>
       </c>
       <c r="L145" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M145" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="146">
@@ -6437,10 +6399,10 @@
       </c>
       <c r="B146" t="inlineStr"/>
       <c r="C146" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D146" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E146" t="n">
         <v>0</v>
@@ -6481,16 +6443,16 @@
         <v>0</v>
       </c>
       <c r="D147" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E147" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F147" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G147" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H147" t="n">
         <v>0</v>
@@ -6505,10 +6467,10 @@
         <v>0</v>
       </c>
       <c r="L147" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M147" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="148">
@@ -6519,7 +6481,7 @@
       </c>
       <c r="B148" t="inlineStr"/>
       <c r="C148" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D148" t="n">
         <v>0</v>
@@ -6546,10 +6508,10 @@
         <v>0</v>
       </c>
       <c r="L148" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M148" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="149">
@@ -6569,10 +6531,10 @@
         <v>0</v>
       </c>
       <c r="F149" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G149" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H149" t="n">
         <v>0</v>
@@ -6622,10 +6584,10 @@
         <v>0</v>
       </c>
       <c r="J150" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K150" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L150" t="n">
         <v>0</v>
@@ -6642,28 +6604,28 @@
       </c>
       <c r="B151" t="inlineStr"/>
       <c r="C151" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D151" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E151" t="n">
         <v>0</v>
       </c>
       <c r="F151" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G151" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H151" t="n">
         <v>0</v>
       </c>
       <c r="I151" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J151" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K151" t="n">
         <v>0</v>
@@ -6683,13 +6645,13 @@
       </c>
       <c r="B152" t="inlineStr"/>
       <c r="C152" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D152" t="n">
         <v>1</v>
       </c>
       <c r="E152" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F152" t="n">
         <v>0</v>
@@ -6727,31 +6689,31 @@
         <v>0</v>
       </c>
       <c r="D153" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E153" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F153" t="n">
         <v>0</v>
       </c>
       <c r="G153" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H153" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I153" t="n">
         <v>0</v>
       </c>
       <c r="J153" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K153" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L153" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M153" t="n">
         <v>0</v>
@@ -6771,10 +6733,10 @@
         <v>0</v>
       </c>
       <c r="E154" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F154" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G154" t="n">
         <v>0</v>
@@ -6786,10 +6748,10 @@
         <v>0</v>
       </c>
       <c r="J154" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K154" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L154" t="n">
         <v>0</v>
@@ -6845,24 +6807,26 @@
           <t>材料</t>
         </is>
       </c>
-      <c r="B156" t="inlineStr"/>
+      <c r="B156" t="n">
+        <v>0</v>
+      </c>
       <c r="C156" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D156" t="n">
         <v>0</v>
       </c>
       <c r="E156" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F156" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G156" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H156" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I156" t="n">
         <v>0</v>
@@ -6891,13 +6855,13 @@
         <v>0</v>
       </c>
       <c r="D157" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E157" t="n">
         <v>2</v>
       </c>
       <c r="F157" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G157" t="n">
         <v>0</v>
@@ -6912,13 +6876,13 @@
         <v>0</v>
       </c>
       <c r="K157" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L157" t="n">
         <v>1</v>
       </c>
       <c r="M157" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="158">
@@ -6929,13 +6893,13 @@
       </c>
       <c r="B158" t="inlineStr"/>
       <c r="C158" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D158" t="n">
         <v>1</v>
       </c>
       <c r="E158" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F158" t="n">
         <v>0</v>
@@ -6950,10 +6914,10 @@
         <v>0</v>
       </c>
       <c r="J158" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K158" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L158" t="n">
         <v>0</v>
@@ -7014,10 +6978,10 @@
         <v>0</v>
       </c>
       <c r="D160" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E160" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F160" t="n">
         <v>0</v>
@@ -7032,10 +6996,10 @@
         <v>0</v>
       </c>
       <c r="J160" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K160" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L160" t="n">
         <v>0</v>
@@ -7055,10 +7019,10 @@
         <v>0</v>
       </c>
       <c r="D161" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E161" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F161" t="n">
         <v>0</v>
@@ -7096,34 +7060,34 @@
         <v>0</v>
       </c>
       <c r="D162" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E162" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F162" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G162" t="n">
         <v>1</v>
       </c>
       <c r="H162" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I162" t="n">
         <v>0</v>
       </c>
       <c r="J162" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K162" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L162" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M162" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="163">
@@ -7137,13 +7101,13 @@
         <v>0</v>
       </c>
       <c r="D163" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E163" t="n">
         <v>1</v>
       </c>
       <c r="F163" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G163" t="n">
         <v>0</v>
@@ -7175,13 +7139,13 @@
       </c>
       <c r="B164" t="inlineStr"/>
       <c r="C164" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D164" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E164" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F164" t="n">
         <v>0</v>
@@ -7219,16 +7183,16 @@
         <v>1</v>
       </c>
       <c r="D165" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E165" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F165" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G165" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H165" t="n">
         <v>0</v>
@@ -7243,7 +7207,7 @@
         <v>0</v>
       </c>
       <c r="L165" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M165" t="n">
         <v>1</v>
@@ -7263,10 +7227,10 @@
         <v>0</v>
       </c>
       <c r="E166" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F166" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G166" t="n">
         <v>0</v>
@@ -7275,13 +7239,13 @@
         <v>0</v>
       </c>
       <c r="I166" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J166" t="n">
         <v>1</v>
       </c>
       <c r="K166" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L166" t="n">
         <v>0</v>
@@ -7296,20 +7260,18 @@
           <t>機電系統工程</t>
         </is>
       </c>
-      <c r="B167" t="n">
-        <v>0</v>
-      </c>
+      <c r="B167" t="inlineStr"/>
       <c r="C167" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D167" t="n">
         <v>0</v>
       </c>
       <c r="E167" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F167" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G167" t="n">
         <v>0</v>
@@ -7318,10 +7280,10 @@
         <v>0</v>
       </c>
       <c r="I167" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J167" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K167" t="n">
         <v>0</v>
@@ -7371,7 +7333,7 @@
         <v>0</v>
       </c>
       <c r="M168" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="169">
@@ -7511,10 +7473,10 @@
         <v>0</v>
       </c>
       <c r="E172" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F172" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G172" t="n">
         <v>0</v>
@@ -7535,7 +7497,7 @@
         <v>0</v>
       </c>
       <c r="M172" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="173">
@@ -7549,10 +7511,10 @@
         <v>0</v>
       </c>
       <c r="D173" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E173" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F173" t="n">
         <v>0</v>
@@ -7585,9 +7547,7 @@
           <t>海陸空大眾運輸</t>
         </is>
       </c>
-      <c r="B174" t="n">
-        <v>0</v>
-      </c>
+      <c r="B174" t="inlineStr"/>
       <c r="C174" t="n">
         <v>0</v>
       </c>
@@ -7619,7 +7579,7 @@
         <v>0</v>
       </c>
       <c r="M174" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="175">
@@ -7628,9 +7588,7 @@
           <t>海陸空貨運承攬</t>
         </is>
       </c>
-      <c r="B175" t="n">
-        <v>0</v>
-      </c>
+      <c r="B175" t="inlineStr"/>
       <c r="C175" t="n">
         <v>0</v>
       </c>
@@ -7662,7 +7620,7 @@
         <v>0</v>
       </c>
       <c r="M175" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="176">
@@ -7714,19 +7672,19 @@
       </c>
       <c r="B177" t="inlineStr"/>
       <c r="C177" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D177" t="n">
         <v>1</v>
       </c>
       <c r="E177" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F177" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G177" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H177" t="n">
         <v>0</v>
@@ -7735,10 +7693,10 @@
         <v>0</v>
       </c>
       <c r="J177" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K177" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L177" t="n">
         <v>0</v>
@@ -7753,7 +7711,9 @@
           <t>濾波器、振盪器材料(鉭酸鋰／鈮酸鋰晶圓／片、石英基板、金屬及陶瓷封裝材料)</t>
         </is>
       </c>
-      <c r="B178" t="inlineStr"/>
+      <c r="B178" t="n">
+        <v>0</v>
+      </c>
       <c r="C178" t="n">
         <v>0</v>
       </c>
@@ -7796,37 +7756,37 @@
       </c>
       <c r="B179" t="inlineStr"/>
       <c r="C179" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D179" t="n">
+        <v>5</v>
+      </c>
+      <c r="E179" t="n">
+        <v>1</v>
+      </c>
+      <c r="F179" t="n">
+        <v>0</v>
+      </c>
+      <c r="G179" t="n">
         <v>2</v>
       </c>
-      <c r="E179" t="n">
-        <v>5</v>
-      </c>
-      <c r="F179" t="n">
-        <v>1</v>
-      </c>
-      <c r="G179" t="n">
-        <v>0</v>
-      </c>
       <c r="H179" t="n">
+        <v>0</v>
+      </c>
+      <c r="I179" t="n">
+        <v>0</v>
+      </c>
+      <c r="J179" t="n">
         <v>2</v>
       </c>
-      <c r="I179" t="n">
-        <v>0</v>
-      </c>
-      <c r="J179" t="n">
-        <v>0</v>
-      </c>
       <c r="K179" t="n">
+        <v>1</v>
+      </c>
+      <c r="L179" t="n">
+        <v>4</v>
+      </c>
+      <c r="M179" t="n">
         <v>2</v>
-      </c>
-      <c r="L179" t="n">
-        <v>1</v>
-      </c>
-      <c r="M179" t="n">
-        <v>4</v>
       </c>
     </row>
     <row r="180">
@@ -7843,10 +7803,10 @@
         <v>0</v>
       </c>
       <c r="E180" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F180" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G180" t="n">
         <v>0</v>
@@ -7876,23 +7836,21 @@
           <t>燈具/應用</t>
         </is>
       </c>
-      <c r="B181" t="n">
-        <v>0</v>
-      </c>
+      <c r="B181" t="inlineStr"/>
       <c r="C181" t="n">
         <v>0</v>
       </c>
       <c r="D181" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E181" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F181" t="n">
         <v>2</v>
       </c>
       <c r="G181" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H181" t="n">
         <v>0</v>
@@ -7901,16 +7859,16 @@
         <v>0</v>
       </c>
       <c r="J181" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K181" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L181" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M181" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="182">
@@ -7924,19 +7882,19 @@
         <v>0</v>
       </c>
       <c r="D182" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E182" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F182" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G182" t="n">
         <v>1</v>
       </c>
       <c r="H182" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I182" t="n">
         <v>0</v>
@@ -8006,16 +7964,16 @@
         <v>1</v>
       </c>
       <c r="D184" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E184" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F184" t="n">
         <v>1</v>
       </c>
       <c r="G184" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H184" t="n">
         <v>0</v>
@@ -8030,10 +7988,10 @@
         <v>0</v>
       </c>
       <c r="L184" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M184" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="185">
@@ -8170,19 +8128,19 @@
         <v>0</v>
       </c>
       <c r="D188" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E188" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F188" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G188" t="n">
         <v>1</v>
       </c>
       <c r="H188" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I188" t="n">
         <v>0</v>
@@ -8194,10 +8152,10 @@
         <v>0</v>
       </c>
       <c r="L188" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M188" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="189">
@@ -8229,10 +8187,10 @@
         <v>0</v>
       </c>
       <c r="J189" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K189" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L189" t="n">
         <v>0</v>
@@ -8252,10 +8210,10 @@
         <v>0</v>
       </c>
       <c r="D190" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E190" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F190" t="n">
         <v>0</v>
@@ -8288,9 +8246,7 @@
           <t>玻璃基板</t>
         </is>
       </c>
-      <c r="B191" t="n">
-        <v>0</v>
-      </c>
+      <c r="B191" t="inlineStr"/>
       <c r="C191" t="n">
         <v>0</v>
       </c>
@@ -8333,19 +8289,19 @@
       </c>
       <c r="B192" t="inlineStr"/>
       <c r="C192" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D192" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E192" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F192" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G192" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H192" t="n">
         <v>0</v>
@@ -8354,10 +8310,10 @@
         <v>0</v>
       </c>
       <c r="J192" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K192" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L192" t="n">
         <v>0</v>
@@ -8413,7 +8369,9 @@
           <t>環保潔能服務產業</t>
         </is>
       </c>
-      <c r="B194" t="inlineStr"/>
+      <c r="B194" t="n">
+        <v>0</v>
+      </c>
       <c r="C194" t="n">
         <v>0</v>
       </c>
@@ -8436,13 +8394,13 @@
         <v>0</v>
       </c>
       <c r="J194" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K194" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L194" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M194" t="n">
         <v>1</v>
@@ -8459,13 +8417,13 @@
         <v>0</v>
       </c>
       <c r="D195" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E195" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F195" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G195" t="n">
         <v>0</v>
@@ -8486,7 +8444,7 @@
         <v>0</v>
       </c>
       <c r="M195" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="196">
@@ -8500,34 +8458,34 @@
         <v>1</v>
       </c>
       <c r="D196" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E196" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F196" t="n">
+        <v>0</v>
+      </c>
+      <c r="G196" t="n">
+        <v>1</v>
+      </c>
+      <c r="H196" t="n">
+        <v>0</v>
+      </c>
+      <c r="I196" t="n">
+        <v>1</v>
+      </c>
+      <c r="J196" t="n">
+        <v>1</v>
+      </c>
+      <c r="K196" t="n">
+        <v>0</v>
+      </c>
+      <c r="L196" t="n">
+        <v>0</v>
+      </c>
+      <c r="M196" t="n">
         <v>3</v>
-      </c>
-      <c r="G196" t="n">
-        <v>0</v>
-      </c>
-      <c r="H196" t="n">
-        <v>1</v>
-      </c>
-      <c r="I196" t="n">
-        <v>0</v>
-      </c>
-      <c r="J196" t="n">
-        <v>1</v>
-      </c>
-      <c r="K196" t="n">
-        <v>1</v>
-      </c>
-      <c r="L196" t="n">
-        <v>0</v>
-      </c>
-      <c r="M196" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="197">
@@ -8536,39 +8494,41 @@
           <t>生產製程及檢測設備</t>
         </is>
       </c>
-      <c r="B197" t="inlineStr"/>
+      <c r="B197" t="n">
+        <v>0</v>
+      </c>
       <c r="C197" t="n">
+        <v>5</v>
+      </c>
+      <c r="D197" t="n">
+        <v>1</v>
+      </c>
+      <c r="E197" t="n">
+        <v>6</v>
+      </c>
+      <c r="F197" t="n">
+        <v>2</v>
+      </c>
+      <c r="G197" t="n">
+        <v>1</v>
+      </c>
+      <c r="H197" t="n">
+        <v>1</v>
+      </c>
+      <c r="I197" t="n">
         <v>3</v>
       </c>
-      <c r="D197" t="n">
+      <c r="J197" t="n">
+        <v>8</v>
+      </c>
+      <c r="K197" t="n">
+        <v>0</v>
+      </c>
+      <c r="L197" t="n">
         <v>5</v>
       </c>
-      <c r="E197" t="n">
-        <v>1</v>
-      </c>
-      <c r="F197" t="n">
-        <v>6</v>
-      </c>
-      <c r="G197" t="n">
-        <v>2</v>
-      </c>
-      <c r="H197" t="n">
-        <v>1</v>
-      </c>
-      <c r="I197" t="n">
-        <v>1</v>
-      </c>
-      <c r="J197" t="n">
-        <v>3</v>
-      </c>
-      <c r="K197" t="n">
-        <v>8</v>
-      </c>
-      <c r="L197" t="n">
-        <v>0</v>
-      </c>
       <c r="M197" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="198">
@@ -8682,10 +8642,10 @@
         <v>0</v>
       </c>
       <c r="J200" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K200" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L200" t="n">
         <v>0</v>
@@ -8702,7 +8662,7 @@
       </c>
       <c r="B201" t="inlineStr"/>
       <c r="C201" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D201" t="n">
         <v>0</v>
@@ -8741,14 +8701,12 @@
           <t>監視器/顯示器</t>
         </is>
       </c>
-      <c r="B202" t="n">
-        <v>0</v>
-      </c>
+      <c r="B202" t="inlineStr"/>
       <c r="C202" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D202" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E202" t="n">
         <v>0</v>
@@ -8789,13 +8747,13 @@
         <v>0</v>
       </c>
       <c r="D203" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E203" t="n">
         <v>1</v>
       </c>
       <c r="F203" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G203" t="n">
         <v>0</v>
@@ -8833,31 +8791,31 @@
         <v>0</v>
       </c>
       <c r="E204" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F204" t="n">
+        <v>0</v>
+      </c>
+      <c r="G204" t="n">
+        <v>1</v>
+      </c>
+      <c r="H204" t="n">
+        <v>0</v>
+      </c>
+      <c r="I204" t="n">
+        <v>1</v>
+      </c>
+      <c r="J204" t="n">
+        <v>0</v>
+      </c>
+      <c r="K204" t="n">
+        <v>0</v>
+      </c>
+      <c r="L204" t="n">
+        <v>1</v>
+      </c>
+      <c r="M204" t="n">
         <v>2</v>
-      </c>
-      <c r="G204" t="n">
-        <v>0</v>
-      </c>
-      <c r="H204" t="n">
-        <v>1</v>
-      </c>
-      <c r="I204" t="n">
-        <v>0</v>
-      </c>
-      <c r="J204" t="n">
-        <v>1</v>
-      </c>
-      <c r="K204" t="n">
-        <v>0</v>
-      </c>
-      <c r="L204" t="n">
-        <v>0</v>
-      </c>
-      <c r="M204" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="205">
@@ -8871,13 +8829,13 @@
         <v>0</v>
       </c>
       <c r="D205" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E205" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F205" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G205" t="n">
         <v>0</v>
@@ -8959,13 +8917,13 @@
         <v>0</v>
       </c>
       <c r="F207" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G207" t="n">
         <v>1</v>
       </c>
       <c r="H207" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I207" t="n">
         <v>0</v>
@@ -8993,37 +8951,37 @@
         <v>0</v>
       </c>
       <c r="C208" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D208" t="n">
+        <v>4</v>
+      </c>
+      <c r="E208" t="n">
+        <v>4</v>
+      </c>
+      <c r="F208" t="n">
+        <v>0</v>
+      </c>
+      <c r="G208" t="n">
         <v>2</v>
       </c>
-      <c r="E208" t="n">
-        <v>5</v>
-      </c>
-      <c r="F208" t="n">
-        <v>5</v>
-      </c>
-      <c r="G208" t="n">
-        <v>0</v>
-      </c>
       <c r="H208" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I208" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J208" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="K208" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="L208" t="n">
         <v>0</v>
       </c>
       <c r="M208" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="209">
@@ -9032,15 +8990,17 @@
           <t>硬碟機</t>
         </is>
       </c>
-      <c r="B209" t="inlineStr"/>
+      <c r="B209" t="n">
+        <v>0</v>
+      </c>
       <c r="C209" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D209" t="n">
         <v>1</v>
       </c>
       <c r="E209" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F209" t="n">
         <v>0</v>
@@ -9078,10 +9038,10 @@
         <v>0</v>
       </c>
       <c r="D210" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E210" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F210" t="n">
         <v>0</v>
@@ -9116,16 +9076,16 @@
       </c>
       <c r="B211" t="inlineStr"/>
       <c r="C211" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D211" t="n">
         <v>2</v>
       </c>
       <c r="E211" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F211" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G211" t="n">
         <v>0</v>
@@ -9324,10 +9284,10 @@
         <v>0</v>
       </c>
       <c r="D216" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E216" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F216" t="n">
         <v>0</v>
@@ -9360,24 +9320,26 @@
           <t>端點安全防護</t>
         </is>
       </c>
-      <c r="B217" t="inlineStr"/>
+      <c r="B217" t="n">
+        <v>0</v>
+      </c>
       <c r="C217" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D217" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E217" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F217" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G217" t="n">
         <v>1</v>
       </c>
       <c r="H217" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I217" t="n">
         <v>0</v>
@@ -9389,10 +9351,10 @@
         <v>0</v>
       </c>
       <c r="L217" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M217" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="218">
@@ -9403,19 +9365,19 @@
       </c>
       <c r="B218" t="inlineStr"/>
       <c r="C218" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D218" t="n">
         <v>1</v>
       </c>
       <c r="E218" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F218" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G218" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H218" t="n">
         <v>0</v>
@@ -9424,10 +9386,10 @@
         <v>0</v>
       </c>
       <c r="J218" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K218" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L218" t="n">
         <v>0</v>
@@ -9444,19 +9406,19 @@
       </c>
       <c r="B219" t="inlineStr"/>
       <c r="C219" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D219" t="n">
         <v>1</v>
       </c>
       <c r="E219" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F219" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G219" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H219" t="n">
         <v>0</v>
@@ -9465,10 +9427,10 @@
         <v>0</v>
       </c>
       <c r="J219" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K219" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L219" t="n">
         <v>0</v>
@@ -9483,39 +9445,41 @@
           <t>系統整合</t>
         </is>
       </c>
-      <c r="B220" t="inlineStr"/>
+      <c r="B220" t="n">
+        <v>0</v>
+      </c>
       <c r="C220" t="n">
         <v>6</v>
       </c>
       <c r="D220" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E220" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F220" t="n">
+        <v>2</v>
+      </c>
+      <c r="G220" t="n">
+        <v>1</v>
+      </c>
+      <c r="H220" t="n">
+        <v>0</v>
+      </c>
+      <c r="I220" t="n">
+        <v>1</v>
+      </c>
+      <c r="J220" t="n">
         <v>3</v>
       </c>
-      <c r="G220" t="n">
+      <c r="K220" t="n">
+        <v>0</v>
+      </c>
+      <c r="L220" t="n">
         <v>2</v>
       </c>
-      <c r="H220" t="n">
-        <v>1</v>
-      </c>
-      <c r="I220" t="n">
-        <v>0</v>
-      </c>
-      <c r="J220" t="n">
-        <v>1</v>
-      </c>
-      <c r="K220" t="n">
-        <v>3</v>
-      </c>
-      <c r="L220" t="n">
-        <v>0</v>
-      </c>
       <c r="M220" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="221">
@@ -9524,39 +9488,41 @@
           <t>系統整合服務</t>
         </is>
       </c>
-      <c r="B221" t="inlineStr"/>
+      <c r="B221" t="n">
+        <v>0</v>
+      </c>
       <c r="C221" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D221" t="n">
         <v>4</v>
       </c>
       <c r="E221" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F221" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G221" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H221" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I221" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J221" t="n">
         <v>1</v>
       </c>
       <c r="K221" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L221" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M221" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="222">
@@ -9576,10 +9542,10 @@
         <v>0</v>
       </c>
       <c r="F222" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G222" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H222" t="n">
         <v>0</v>
@@ -9606,20 +9572,18 @@
           <t>紡紗</t>
         </is>
       </c>
-      <c r="B223" t="n">
-        <v>0</v>
-      </c>
+      <c r="B223" t="inlineStr"/>
       <c r="C223" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D223" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E223" t="n">
         <v>1</v>
       </c>
       <c r="F223" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G223" t="n">
         <v>0</v>
@@ -9681,7 +9645,7 @@
         <v>0</v>
       </c>
       <c r="M224" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="225">
@@ -9731,9 +9695,7 @@
           <t>網路IC</t>
         </is>
       </c>
-      <c r="B226" t="n">
-        <v>0</v>
-      </c>
+      <c r="B226" t="inlineStr"/>
       <c r="C226" t="n">
         <v>0</v>
       </c>
@@ -9741,10 +9703,10 @@
         <v>0</v>
       </c>
       <c r="E226" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F226" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G226" t="n">
         <v>0</v>
@@ -9776,13 +9738,13 @@
       </c>
       <c r="B227" t="inlineStr"/>
       <c r="C227" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D227" t="n">
         <v>1</v>
       </c>
       <c r="E227" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F227" t="n">
         <v>0</v>
@@ -9815,24 +9777,26 @@
           <t>網路基礎設施</t>
         </is>
       </c>
-      <c r="B228" t="inlineStr"/>
+      <c r="B228" t="n">
+        <v>0</v>
+      </c>
       <c r="C228" t="n">
         <v>0</v>
       </c>
       <c r="D228" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E228" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F228" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G228" t="n">
         <v>1</v>
       </c>
       <c r="H228" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I228" t="n">
         <v>0</v>
@@ -9844,7 +9808,7 @@
         <v>0</v>
       </c>
       <c r="L228" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M228" t="n">
         <v>1</v>
@@ -9856,24 +9820,26 @@
           <t>網路安全防護</t>
         </is>
       </c>
-      <c r="B229" t="inlineStr"/>
+      <c r="B229" t="n">
+        <v>0</v>
+      </c>
       <c r="C229" t="n">
         <v>0</v>
       </c>
       <c r="D229" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E229" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F229" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G229" t="n">
         <v>1</v>
       </c>
       <c r="H229" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I229" t="n">
         <v>0</v>
@@ -9885,10 +9851,10 @@
         <v>0</v>
       </c>
       <c r="L229" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M229" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="230">
@@ -9899,37 +9865,37 @@
       </c>
       <c r="B230" t="inlineStr"/>
       <c r="C230" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D230" t="n">
+        <v>6</v>
+      </c>
+      <c r="E230" t="n">
+        <v>1</v>
+      </c>
+      <c r="F230" t="n">
+        <v>1</v>
+      </c>
+      <c r="G230" t="n">
         <v>2</v>
       </c>
-      <c r="E230" t="n">
-        <v>6</v>
-      </c>
-      <c r="F230" t="n">
-        <v>1</v>
-      </c>
-      <c r="G230" t="n">
-        <v>1</v>
-      </c>
       <c r="H230" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I230" t="n">
         <v>0</v>
       </c>
       <c r="J230" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K230" t="n">
+        <v>1</v>
+      </c>
+      <c r="L230" t="n">
         <v>3</v>
       </c>
-      <c r="L230" t="n">
-        <v>1</v>
-      </c>
       <c r="M230" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="231">
@@ -9940,13 +9906,13 @@
       </c>
       <c r="B231" t="inlineStr"/>
       <c r="C231" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D231" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E231" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F231" t="n">
         <v>1</v>
@@ -9955,7 +9921,7 @@
         <v>1</v>
       </c>
       <c r="H231" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I231" t="n">
         <v>0</v>
@@ -9967,10 +9933,10 @@
         <v>0</v>
       </c>
       <c r="L231" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M231" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="232">
@@ -9993,25 +9959,25 @@
         <v>0</v>
       </c>
       <c r="G232" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H232" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I232" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J232" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K232" t="n">
         <v>0</v>
       </c>
       <c r="L232" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M232" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="233">
@@ -10022,37 +9988,37 @@
       </c>
       <c r="B233" t="inlineStr"/>
       <c r="C233" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D233" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E233" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F233" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G233" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H233" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I233" t="n">
         <v>0</v>
       </c>
       <c r="J233" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K233" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L233" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M233" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="234">
@@ -10107,13 +10073,13 @@
         <v>0</v>
       </c>
       <c r="D235" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E235" t="n">
         <v>1</v>
       </c>
       <c r="F235" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G235" t="n">
         <v>0</v>
@@ -10131,10 +10097,10 @@
         <v>0</v>
       </c>
       <c r="L235" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M235" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="236">
@@ -10151,10 +10117,10 @@
         <v>0</v>
       </c>
       <c r="E236" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F236" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G236" t="n">
         <v>0</v>
@@ -10175,7 +10141,7 @@
         <v>0</v>
       </c>
       <c r="M236" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="237">
@@ -10184,9 +10150,7 @@
           <t>背光模組</t>
         </is>
       </c>
-      <c r="B237" t="n">
-        <v>0</v>
-      </c>
+      <c r="B237" t="inlineStr"/>
       <c r="C237" t="n">
         <v>0</v>
       </c>
@@ -10218,7 +10182,7 @@
         <v>0</v>
       </c>
       <c r="M237" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="238">
@@ -10227,26 +10191,24 @@
           <t>背光源(發光二極體、冷陰極管)</t>
         </is>
       </c>
-      <c r="B238" t="n">
-        <v>0</v>
-      </c>
+      <c r="B238" t="inlineStr"/>
       <c r="C238" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D238" t="n">
         <v>1</v>
       </c>
       <c r="E238" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F238" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G238" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H238" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I238" t="n">
         <v>0</v>
@@ -10275,28 +10237,28 @@
         <v>0</v>
       </c>
       <c r="D239" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E239" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F239" t="n">
         <v>0</v>
       </c>
       <c r="G239" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H239" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I239" t="n">
         <v>0</v>
       </c>
       <c r="J239" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K239" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L239" t="n">
         <v>0</v>
@@ -10319,10 +10281,10 @@
         <v>0</v>
       </c>
       <c r="E240" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F240" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G240" t="n">
         <v>0</v>
@@ -10343,7 +10305,7 @@
         <v>0</v>
       </c>
       <c r="M240" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="241">
@@ -10352,9 +10314,7 @@
           <t>臨床實驗、移植技術、疾病治療</t>
         </is>
       </c>
-      <c r="B241" t="n">
-        <v>0</v>
-      </c>
+      <c r="B241" t="inlineStr"/>
       <c r="C241" t="n">
         <v>0</v>
       </c>
@@ -10386,7 +10346,7 @@
         <v>0</v>
       </c>
       <c r="M241" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="242">
@@ -10418,16 +10378,16 @@
         <v>0</v>
       </c>
       <c r="J242" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K242" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L242" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M242" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="243">
@@ -10520,13 +10480,13 @@
       </c>
       <c r="B245" t="inlineStr"/>
       <c r="C245" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D245" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E245" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F245" t="n">
         <v>0</v>
@@ -10547,10 +10507,10 @@
         <v>0</v>
       </c>
       <c r="L245" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M245" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="246">
@@ -10564,16 +10524,16 @@
         <v>0</v>
       </c>
       <c r="D246" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E246" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F246" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G246" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H246" t="n">
         <v>0</v>
@@ -10588,10 +10548,10 @@
         <v>0</v>
       </c>
       <c r="L246" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M246" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="247">
@@ -10608,10 +10568,10 @@
         <v>0</v>
       </c>
       <c r="E247" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F247" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G247" t="n">
         <v>0</v>
@@ -10632,7 +10592,7 @@
         <v>0</v>
       </c>
       <c r="M247" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="248">
@@ -10641,9 +10601,11 @@
           <t>藥品代理銷售及通路</t>
         </is>
       </c>
-      <c r="B248" t="inlineStr"/>
+      <c r="B248" t="n">
+        <v>0</v>
+      </c>
       <c r="C248" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D248" t="n">
         <v>0</v>
@@ -10673,7 +10635,7 @@
         <v>0</v>
       </c>
       <c r="M248" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="249">
@@ -10687,7 +10649,7 @@
         <v>1</v>
       </c>
       <c r="D249" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E249" t="n">
         <v>0</v>
@@ -10723,18 +10685,20 @@
           <t>虛擬化軟體</t>
         </is>
       </c>
-      <c r="B250" t="inlineStr"/>
+      <c r="B250" t="n">
+        <v>0</v>
+      </c>
       <c r="C250" t="n">
         <v>1</v>
       </c>
       <c r="D250" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E250" t="n">
         <v>1</v>
       </c>
       <c r="F250" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G250" t="n">
         <v>0</v>
@@ -10810,16 +10774,16 @@
         <v>0</v>
       </c>
       <c r="D252" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E252" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F252" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G252" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H252" t="n">
         <v>0</v>
@@ -10834,10 +10798,10 @@
         <v>0</v>
       </c>
       <c r="L252" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M252" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="253">
@@ -10942,10 +10906,10 @@
         <v>0</v>
       </c>
       <c r="G255" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H255" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I255" t="n">
         <v>0</v>
@@ -10971,7 +10935,7 @@
       </c>
       <c r="B256" t="inlineStr"/>
       <c r="C256" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D256" t="n">
         <v>0</v>
@@ -10998,10 +10962,10 @@
         <v>0</v>
       </c>
       <c r="L256" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M256" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="257">
@@ -11097,13 +11061,13 @@
         <v>0</v>
       </c>
       <c r="D259" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E259" t="n">
         <v>1</v>
       </c>
       <c r="F259" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G259" t="n">
         <v>0</v>
@@ -11133,9 +11097,7 @@
           <t>製造商</t>
         </is>
       </c>
-      <c r="B260" t="n">
-        <v>0</v>
-      </c>
+      <c r="B260" t="inlineStr"/>
       <c r="C260" t="n">
         <v>0</v>
       </c>
@@ -11176,14 +11138,12 @@
           <t>觸控面板</t>
         </is>
       </c>
-      <c r="B261" t="n">
-        <v>0</v>
-      </c>
+      <c r="B261" t="inlineStr"/>
       <c r="C261" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D261" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E261" t="n">
         <v>0</v>
@@ -11219,26 +11179,24 @@
           <t>記憶體</t>
         </is>
       </c>
-      <c r="B262" t="n">
-        <v>0</v>
-      </c>
+      <c r="B262" t="inlineStr"/>
       <c r="C262" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D262" t="n">
+        <v>4</v>
+      </c>
+      <c r="E262" t="n">
+        <v>3</v>
+      </c>
+      <c r="F262" t="n">
+        <v>0</v>
+      </c>
+      <c r="G262" t="n">
         <v>2</v>
       </c>
-      <c r="E262" t="n">
-        <v>4</v>
-      </c>
-      <c r="F262" t="n">
-        <v>3</v>
-      </c>
-      <c r="G262" t="n">
-        <v>0</v>
-      </c>
       <c r="H262" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I262" t="n">
         <v>0</v>
@@ -11253,7 +11211,7 @@
         <v>0</v>
       </c>
       <c r="M262" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="263">
@@ -11270,10 +11228,10 @@
         <v>1</v>
       </c>
       <c r="E263" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F263" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G263" t="n">
         <v>0</v>
@@ -11282,13 +11240,13 @@
         <v>0</v>
       </c>
       <c r="I263" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J263" t="n">
         <v>1</v>
       </c>
       <c r="K263" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L263" t="n">
         <v>0</v>
@@ -11308,16 +11266,16 @@
         <v>1</v>
       </c>
       <c r="D264" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E264" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F264" t="n">
         <v>1</v>
       </c>
       <c r="G264" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H264" t="n">
         <v>0</v>
@@ -11326,16 +11284,16 @@
         <v>0</v>
       </c>
       <c r="J264" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K264" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L264" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M264" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="265">
@@ -11446,10 +11404,10 @@
         <v>0</v>
       </c>
       <c r="I267" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J267" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K267" t="n">
         <v>0</v>
@@ -11540,7 +11498,7 @@
         <v>0</v>
       </c>
       <c r="M269" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="270">
@@ -11549,9 +11507,7 @@
           <t>貿易商、代理商、經銷商</t>
         </is>
       </c>
-      <c r="B270" t="n">
-        <v>0</v>
-      </c>
+      <c r="B270" t="inlineStr"/>
       <c r="C270" t="n">
         <v>0</v>
       </c>
@@ -11562,10 +11518,10 @@
         <v>0</v>
       </c>
       <c r="F270" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G270" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H270" t="n">
         <v>0</v>
@@ -11574,13 +11530,13 @@
         <v>0</v>
       </c>
       <c r="J270" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K270" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L270" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M270" t="n">
         <v>1</v>
@@ -11638,19 +11594,19 @@
         <v>0</v>
       </c>
       <c r="D272" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E272" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F272" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G272" t="n">
         <v>1</v>
       </c>
       <c r="H272" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I272" t="n">
         <v>0</v>
@@ -11662,10 +11618,10 @@
         <v>0</v>
       </c>
       <c r="L272" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M272" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="273">
@@ -11674,7 +11630,9 @@
           <t>資安營運管理服務</t>
         </is>
       </c>
-      <c r="B273" t="inlineStr"/>
+      <c r="B273" t="n">
+        <v>0</v>
+      </c>
       <c r="C273" t="n">
         <v>0</v>
       </c>
@@ -11682,13 +11640,13 @@
         <v>1</v>
       </c>
       <c r="E273" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F273" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G273" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H273" t="n">
         <v>0</v>
@@ -11703,10 +11661,10 @@
         <v>0</v>
       </c>
       <c r="L273" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M273" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="274">
@@ -11715,24 +11673,26 @@
           <t>資安防護能力分析與鑑識服務</t>
         </is>
       </c>
-      <c r="B274" t="inlineStr"/>
+      <c r="B274" t="n">
+        <v>0</v>
+      </c>
       <c r="C274" t="n">
         <v>0</v>
       </c>
       <c r="D274" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E274" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F274" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G274" t="n">
         <v>1</v>
       </c>
       <c r="H274" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I274" t="n">
         <v>0</v>
@@ -11744,10 +11704,10 @@
         <v>0</v>
       </c>
       <c r="L274" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M274" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="275">
@@ -11761,16 +11721,16 @@
         <v>1</v>
       </c>
       <c r="D275" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E275" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F275" t="n">
         <v>1</v>
       </c>
       <c r="G275" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H275" t="n">
         <v>0</v>
@@ -11785,10 +11745,10 @@
         <v>0</v>
       </c>
       <c r="L275" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M275" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="276">
@@ -11797,24 +11757,26 @@
           <t>資安顧問服務</t>
         </is>
       </c>
-      <c r="B276" t="inlineStr"/>
+      <c r="B276" t="n">
+        <v>0</v>
+      </c>
       <c r="C276" t="n">
         <v>0</v>
       </c>
       <c r="D276" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E276" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F276" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G276" t="n">
         <v>1</v>
       </c>
       <c r="H276" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I276" t="n">
         <v>0</v>
@@ -11826,10 +11788,10 @@
         <v>0</v>
       </c>
       <c r="L276" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M276" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="277">
@@ -11879,9 +11841,11 @@
           <t>資料安全</t>
         </is>
       </c>
-      <c r="B278" t="inlineStr"/>
+      <c r="B278" t="n">
+        <v>0</v>
+      </c>
       <c r="C278" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D278" t="n">
         <v>1</v>
@@ -11893,7 +11857,7 @@
         <v>1</v>
       </c>
       <c r="G278" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H278" t="n">
         <v>0</v>
@@ -11908,10 +11872,10 @@
         <v>0</v>
       </c>
       <c r="L278" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M278" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="279">
@@ -11922,7 +11886,7 @@
       </c>
       <c r="B279" t="inlineStr"/>
       <c r="C279" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D279" t="n">
         <v>1</v>
@@ -11931,7 +11895,7 @@
         <v>1</v>
       </c>
       <c r="F279" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G279" t="n">
         <v>0</v>
@@ -12002,24 +11966,26 @@
           <t>資料處理</t>
         </is>
       </c>
-      <c r="B281" t="inlineStr"/>
+      <c r="B281" t="n">
+        <v>0</v>
+      </c>
       <c r="C281" t="n">
         <v>0</v>
       </c>
       <c r="D281" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E281" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F281" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G281" t="n">
         <v>1</v>
       </c>
       <c r="H281" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I281" t="n">
         <v>0</v>
@@ -12031,10 +11997,10 @@
         <v>0</v>
       </c>
       <c r="L281" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M281" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="282">
@@ -12250,10 +12216,10 @@
       </c>
       <c r="B287" t="inlineStr"/>
       <c r="C287" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D287" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E287" t="n">
         <v>1</v>
@@ -12262,7 +12228,7 @@
         <v>1</v>
       </c>
       <c r="G287" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H287" t="n">
         <v>0</v>
@@ -12277,10 +12243,10 @@
         <v>0</v>
       </c>
       <c r="L287" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M287" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="288">
@@ -12289,12 +12255,14 @@
           <t>車燈</t>
         </is>
       </c>
-      <c r="B288" t="inlineStr"/>
+      <c r="B288" t="n">
+        <v>0</v>
+      </c>
       <c r="C288" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D288" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E288" t="n">
         <v>0</v>
@@ -12330,12 +12298,14 @@
           <t>車用機械傳動設備及零配件</t>
         </is>
       </c>
-      <c r="B289" t="inlineStr"/>
+      <c r="B289" t="n">
+        <v>0</v>
+      </c>
       <c r="C289" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D289" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E289" t="n">
         <v>0</v>
@@ -12353,10 +12323,10 @@
         <v>0</v>
       </c>
       <c r="J289" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K289" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L289" t="n">
         <v>0</v>
@@ -12458,10 +12428,10 @@
         <v>0</v>
       </c>
       <c r="D292" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E292" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F292" t="n">
         <v>0</v>
@@ -12537,13 +12507,13 @@
       </c>
       <c r="B294" t="inlineStr"/>
       <c r="C294" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D294" t="n">
         <v>1</v>
       </c>
       <c r="E294" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F294" t="n">
         <v>0</v>
@@ -12599,10 +12569,10 @@
         <v>0</v>
       </c>
       <c r="J295" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K295" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L295" t="n">
         <v>0</v>
@@ -12625,10 +12595,10 @@
         <v>0</v>
       </c>
       <c r="E296" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F296" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G296" t="n">
         <v>0</v>
@@ -12649,7 +12619,7 @@
         <v>0</v>
       </c>
       <c r="M296" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="297">
@@ -12731,7 +12701,7 @@
         <v>0</v>
       </c>
       <c r="M298" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="299">
@@ -12824,19 +12794,19 @@
       </c>
       <c r="B301" t="inlineStr"/>
       <c r="C301" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D301" t="n">
         <v>1</v>
       </c>
       <c r="E301" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F301" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G301" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H301" t="n">
         <v>0</v>
@@ -12851,10 +12821,10 @@
         <v>0</v>
       </c>
       <c r="L301" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M301" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="302">
@@ -12863,36 +12833,38 @@
           <t>連接器設計、組裝及製造</t>
         </is>
       </c>
-      <c r="B302" t="inlineStr"/>
+      <c r="B302" t="n">
+        <v>0</v>
+      </c>
       <c r="C302" t="n">
+        <v>0</v>
+      </c>
+      <c r="D302" t="n">
+        <v>1</v>
+      </c>
+      <c r="E302" t="n">
         <v>2</v>
       </c>
-      <c r="D302" t="n">
-        <v>0</v>
-      </c>
-      <c r="E302" t="n">
-        <v>1</v>
-      </c>
       <c r="F302" t="n">
+        <v>1</v>
+      </c>
+      <c r="G302" t="n">
         <v>2</v>
       </c>
-      <c r="G302" t="n">
-        <v>1</v>
-      </c>
       <c r="H302" t="n">
+        <v>0</v>
+      </c>
+      <c r="I302" t="n">
+        <v>0</v>
+      </c>
+      <c r="J302" t="n">
+        <v>1</v>
+      </c>
+      <c r="K302" t="n">
+        <v>0</v>
+      </c>
+      <c r="L302" t="n">
         <v>2</v>
-      </c>
-      <c r="I302" t="n">
-        <v>0</v>
-      </c>
-      <c r="J302" t="n">
-        <v>0</v>
-      </c>
-      <c r="K302" t="n">
-        <v>1</v>
-      </c>
-      <c r="L302" t="n">
-        <v>0</v>
       </c>
       <c r="M302" t="n">
         <v>2</v>
@@ -12909,31 +12881,31 @@
         <v>1</v>
       </c>
       <c r="D303" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E303" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F303" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G303" t="n">
         <v>1</v>
       </c>
       <c r="H303" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I303" t="n">
         <v>0</v>
       </c>
       <c r="J303" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K303" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L303" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M303" t="n">
         <v>1</v>
@@ -13079,7 +13051,7 @@
         <v>1</v>
       </c>
       <c r="F307" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G307" t="n">
         <v>0</v>
@@ -13091,10 +13063,10 @@
         <v>0</v>
       </c>
       <c r="J307" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K307" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L307" t="n">
         <v>0</v>
@@ -13111,10 +13083,10 @@
       </c>
       <c r="B308" t="inlineStr"/>
       <c r="C308" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D308" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E308" t="n">
         <v>0</v>
@@ -13132,10 +13104,10 @@
         <v>0</v>
       </c>
       <c r="J308" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K308" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L308" t="n">
         <v>0</v>
@@ -13199,10 +13171,10 @@
         <v>0</v>
       </c>
       <c r="E310" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F310" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G310" t="n">
         <v>0</v>
@@ -13211,13 +13183,13 @@
         <v>0</v>
       </c>
       <c r="I310" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J310" t="n">
         <v>1</v>
       </c>
       <c r="K310" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L310" t="n">
         <v>0</v>
@@ -13252,10 +13224,10 @@
         <v>0</v>
       </c>
       <c r="I311" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J311" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K311" t="n">
         <v>0</v>
@@ -13278,13 +13250,13 @@
         <v>0</v>
       </c>
       <c r="D312" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E312" t="n">
         <v>1</v>
       </c>
       <c r="F312" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G312" t="n">
         <v>0</v>
@@ -13314,7 +13286,9 @@
           <t>醫療器材代理銷售及通路</t>
         </is>
       </c>
-      <c r="B313" t="inlineStr"/>
+      <c r="B313" t="n">
+        <v>0</v>
+      </c>
       <c r="C313" t="n">
         <v>1</v>
       </c>
@@ -13325,7 +13299,7 @@
         <v>1</v>
       </c>
       <c r="F313" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G313" t="n">
         <v>0</v>
@@ -13337,16 +13311,16 @@
         <v>0</v>
       </c>
       <c r="J313" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K313" t="n">
+        <v>1</v>
+      </c>
+      <c r="L313" t="n">
+        <v>0</v>
+      </c>
+      <c r="M313" t="n">
         <v>2</v>
-      </c>
-      <c r="L313" t="n">
-        <v>1</v>
-      </c>
-      <c r="M313" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="314">
@@ -13359,37 +13333,37 @@
         <v>0</v>
       </c>
       <c r="C314" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D314" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E314" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F314" t="n">
         <v>0</v>
       </c>
       <c r="G314" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H314" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I314" t="n">
         <v>0</v>
       </c>
       <c r="J314" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K314" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L314" t="n">
         <v>0</v>
       </c>
       <c r="M314" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="315">
@@ -13430,7 +13404,7 @@
         <v>0</v>
       </c>
       <c r="M315" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="316">
@@ -13439,23 +13413,21 @@
           <t>金屬、塑膠模具</t>
         </is>
       </c>
-      <c r="B316" t="n">
-        <v>0</v>
-      </c>
+      <c r="B316" t="inlineStr"/>
       <c r="C316" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D316" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E316" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F316" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G316" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H316" t="n">
         <v>0</v>
@@ -13470,7 +13442,7 @@
         <v>0</v>
       </c>
       <c r="L316" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M316" t="n">
         <v>0</v>
@@ -13525,7 +13497,7 @@
       </c>
       <c r="B318" t="inlineStr"/>
       <c r="C318" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D318" t="n">
         <v>0</v>
@@ -13537,10 +13509,10 @@
         <v>0</v>
       </c>
       <c r="G318" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H318" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I318" t="n">
         <v>0</v>
@@ -13607,7 +13579,7 @@
       </c>
       <c r="B320" t="inlineStr"/>
       <c r="C320" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D320" t="n">
         <v>0</v>
@@ -13646,9 +13618,7 @@
           <t>金控業/銀行業/保險業</t>
         </is>
       </c>
-      <c r="B321" t="n">
-        <v>0</v>
-      </c>
+      <c r="B321" t="inlineStr"/>
       <c r="C321" t="n">
         <v>0</v>
       </c>
@@ -13814,16 +13784,16 @@
       </c>
       <c r="B325" t="inlineStr"/>
       <c r="C325" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D325" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E325" t="n">
         <v>1</v>
       </c>
       <c r="F325" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G325" t="n">
         <v>0</v>
@@ -13835,10 +13805,10 @@
         <v>0</v>
       </c>
       <c r="J325" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K325" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L325" t="n">
         <v>0</v>
@@ -13858,34 +13828,34 @@
         <v>0</v>
       </c>
       <c r="D326" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E326" t="n">
+        <v>1</v>
+      </c>
+      <c r="F326" t="n">
+        <v>0</v>
+      </c>
+      <c r="G326" t="n">
+        <v>0</v>
+      </c>
+      <c r="H326" t="n">
+        <v>0</v>
+      </c>
+      <c r="I326" t="n">
+        <v>0</v>
+      </c>
+      <c r="J326" t="n">
+        <v>5</v>
+      </c>
+      <c r="K326" t="n">
+        <v>0</v>
+      </c>
+      <c r="L326" t="n">
+        <v>2</v>
+      </c>
+      <c r="M326" t="n">
         <v>4</v>
-      </c>
-      <c r="F326" t="n">
-        <v>1</v>
-      </c>
-      <c r="G326" t="n">
-        <v>0</v>
-      </c>
-      <c r="H326" t="n">
-        <v>0</v>
-      </c>
-      <c r="I326" t="n">
-        <v>0</v>
-      </c>
-      <c r="J326" t="n">
-        <v>0</v>
-      </c>
-      <c r="K326" t="n">
-        <v>5</v>
-      </c>
-      <c r="L326" t="n">
-        <v>0</v>
-      </c>
-      <c r="M326" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="327">
@@ -13905,10 +13875,10 @@
         <v>0</v>
       </c>
       <c r="F327" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G327" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H327" t="n">
         <v>0</v>
@@ -13984,25 +13954,25 @@
         <v>0</v>
       </c>
       <c r="E329" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F329" t="n">
         <v>1</v>
       </c>
       <c r="G329" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H329" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I329" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J329" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K329" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L329" t="n">
         <v>0</v>
@@ -14107,10 +14077,10 @@
         <v>0</v>
       </c>
       <c r="E332" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F332" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G332" t="n">
         <v>0</v>
@@ -14195,10 +14165,10 @@
         <v>0</v>
       </c>
       <c r="G334" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H334" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I334" t="n">
         <v>0</v>
@@ -14268,10 +14238,10 @@
         <v>0</v>
       </c>
       <c r="D336" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E336" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F336" t="n">
         <v>0</v>
@@ -14306,16 +14276,16 @@
       </c>
       <c r="B337" t="inlineStr"/>
       <c r="C337" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D337" t="n">
+        <v>3</v>
+      </c>
+      <c r="E337" t="n">
         <v>2</v>
       </c>
-      <c r="E337" t="n">
-        <v>3</v>
-      </c>
       <c r="F337" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G337" t="n">
         <v>0</v>
@@ -14336,7 +14306,7 @@
         <v>0</v>
       </c>
       <c r="M337" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="338">
@@ -14356,7 +14326,7 @@
         <v>1</v>
       </c>
       <c r="F338" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G338" t="n">
         <v>0</v>
@@ -14388,13 +14358,13 @@
       </c>
       <c r="B339" t="inlineStr"/>
       <c r="C339" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D339" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E339" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F339" t="n">
         <v>1</v>
@@ -14403,7 +14373,7 @@
         <v>1</v>
       </c>
       <c r="H339" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I339" t="n">
         <v>0</v>
@@ -14415,10 +14385,10 @@
         <v>0</v>
       </c>
       <c r="L339" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M339" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="340">
@@ -14427,21 +14397,23 @@
           <t>雲端平台</t>
         </is>
       </c>
-      <c r="B340" t="inlineStr"/>
+      <c r="B340" t="n">
+        <v>0</v>
+      </c>
       <c r="C340" t="n">
         <v>1</v>
       </c>
       <c r="D340" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E340" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F340" t="n">
         <v>1</v>
       </c>
       <c r="G340" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H340" t="n">
         <v>0</v>
@@ -14456,10 +14428,10 @@
         <v>0</v>
       </c>
       <c r="L340" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M340" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="341">
@@ -14468,7 +14440,9 @@
           <t>雲端應用服務</t>
         </is>
       </c>
-      <c r="B341" t="inlineStr"/>
+      <c r="B341" t="n">
+        <v>0</v>
+      </c>
       <c r="C341" t="n">
         <v>1</v>
       </c>
@@ -14476,13 +14450,13 @@
         <v>2</v>
       </c>
       <c r="E341" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F341" t="n">
         <v>1</v>
       </c>
       <c r="G341" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H341" t="n">
         <v>0</v>
@@ -14491,16 +14465,16 @@
         <v>0</v>
       </c>
       <c r="J341" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K341" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L341" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M341" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="342">
@@ -14526,22 +14500,22 @@
         <v>0</v>
       </c>
       <c r="H342" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I342" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J342" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K342" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L342" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M342" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="343">
@@ -14555,34 +14529,34 @@
         <v>1</v>
       </c>
       <c r="D343" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E343" t="n">
+        <v>0</v>
+      </c>
+      <c r="F343" t="n">
+        <v>0</v>
+      </c>
+      <c r="G343" t="n">
+        <v>0</v>
+      </c>
+      <c r="H343" t="n">
+        <v>0</v>
+      </c>
+      <c r="I343" t="n">
+        <v>0</v>
+      </c>
+      <c r="J343" t="n">
+        <v>1</v>
+      </c>
+      <c r="K343" t="n">
+        <v>0</v>
+      </c>
+      <c r="L343" t="n">
+        <v>1</v>
+      </c>
+      <c r="M343" t="n">
         <v>2</v>
-      </c>
-      <c r="F343" t="n">
-        <v>0</v>
-      </c>
-      <c r="G343" t="n">
-        <v>0</v>
-      </c>
-      <c r="H343" t="n">
-        <v>0</v>
-      </c>
-      <c r="I343" t="n">
-        <v>0</v>
-      </c>
-      <c r="J343" t="n">
-        <v>0</v>
-      </c>
-      <c r="K343" t="n">
-        <v>1</v>
-      </c>
-      <c r="L343" t="n">
-        <v>0</v>
-      </c>
-      <c r="M343" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="344">
@@ -14599,10 +14573,10 @@
         <v>0</v>
       </c>
       <c r="E344" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F344" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G344" t="n">
         <v>0</v>
@@ -14652,13 +14626,13 @@
         <v>0</v>
       </c>
       <c r="I345" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J345" t="n">
         <v>1</v>
       </c>
       <c r="K345" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L345" t="n">
         <v>0</v>
@@ -14681,10 +14655,10 @@
         <v>0</v>
       </c>
       <c r="E346" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F346" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G346" t="n">
         <v>0</v>
@@ -14693,13 +14667,13 @@
         <v>0</v>
       </c>
       <c r="I346" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J346" t="n">
         <v>1</v>
       </c>
       <c r="K346" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L346" t="n">
         <v>0</v>
@@ -14766,10 +14740,10 @@
         <v>0</v>
       </c>
       <c r="F348" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G348" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H348" t="n">
         <v>0</v>
@@ -14778,10 +14752,10 @@
         <v>0</v>
       </c>
       <c r="J348" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K348" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L348" t="n">
         <v>0</v>
@@ -14819,10 +14793,10 @@
         <v>0</v>
       </c>
       <c r="J349" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K349" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L349" t="n">
         <v>0</v>
@@ -14880,10 +14854,10 @@
       </c>
       <c r="B351" t="inlineStr"/>
       <c r="C351" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D351" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E351" t="n">
         <v>1</v>
@@ -14895,22 +14869,22 @@
         <v>1</v>
       </c>
       <c r="H351" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I351" t="n">
         <v>0</v>
       </c>
       <c r="J351" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K351" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L351" t="n">
         <v>0</v>
       </c>
       <c r="M351" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="352">
@@ -14919,41 +14893,39 @@
           <t>電容器</t>
         </is>
       </c>
-      <c r="B352" t="n">
-        <v>0</v>
-      </c>
+      <c r="B352" t="inlineStr"/>
       <c r="C352" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D352" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E352" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="F352" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="G352" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H352" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I352" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J352" t="n">
         <v>3</v>
       </c>
       <c r="K352" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L352" t="n">
         <v>2</v>
       </c>
       <c r="M352" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="353">
@@ -14964,16 +14936,16 @@
       </c>
       <c r="B353" t="inlineStr"/>
       <c r="C353" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D353" t="n">
         <v>1</v>
       </c>
       <c r="E353" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F353" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G353" t="n">
         <v>0</v>
@@ -14982,10 +14954,10 @@
         <v>0</v>
       </c>
       <c r="I353" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J353" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K353" t="n">
         <v>0</v>
@@ -15003,35 +14975,33 @@
           <t>電感器</t>
         </is>
       </c>
-      <c r="B354" t="n">
-        <v>0</v>
-      </c>
+      <c r="B354" t="inlineStr"/>
       <c r="C354" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D354" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E354" t="n">
+        <v>3</v>
+      </c>
+      <c r="F354" t="n">
         <v>2</v>
       </c>
-      <c r="F354" t="n">
-        <v>3</v>
-      </c>
       <c r="G354" t="n">
+        <v>0</v>
+      </c>
+      <c r="H354" t="n">
+        <v>0</v>
+      </c>
+      <c r="I354" t="n">
         <v>2</v>
       </c>
-      <c r="H354" t="n">
-        <v>0</v>
-      </c>
-      <c r="I354" t="n">
-        <v>0</v>
-      </c>
       <c r="J354" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K354" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L354" t="n">
         <v>0</v>
@@ -15048,19 +15018,19 @@
       </c>
       <c r="B355" t="inlineStr"/>
       <c r="C355" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D355" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E355" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F355" t="n">
         <v>1</v>
       </c>
       <c r="G355" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H355" t="n">
         <v>0</v>
@@ -15087,35 +15057,33 @@
           <t>電控元件</t>
         </is>
       </c>
-      <c r="B356" t="n">
-        <v>0</v>
-      </c>
+      <c r="B356" t="inlineStr"/>
       <c r="C356" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D356" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E356" t="n">
+        <v>1</v>
+      </c>
+      <c r="F356" t="n">
+        <v>0</v>
+      </c>
+      <c r="G356" t="n">
+        <v>0</v>
+      </c>
+      <c r="H356" t="n">
+        <v>0</v>
+      </c>
+      <c r="I356" t="n">
+        <v>0</v>
+      </c>
+      <c r="J356" t="n">
         <v>2</v>
       </c>
-      <c r="F356" t="n">
-        <v>1</v>
-      </c>
-      <c r="G356" t="n">
-        <v>0</v>
-      </c>
-      <c r="H356" t="n">
-        <v>0</v>
-      </c>
-      <c r="I356" t="n">
-        <v>0</v>
-      </c>
-      <c r="J356" t="n">
-        <v>0</v>
-      </c>
       <c r="K356" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L356" t="n">
         <v>0</v>
@@ -15132,13 +15100,13 @@
       </c>
       <c r="B357" t="inlineStr"/>
       <c r="C357" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D357" t="n">
         <v>1</v>
       </c>
       <c r="E357" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F357" t="n">
         <v>0</v>
@@ -15153,10 +15121,10 @@
         <v>0</v>
       </c>
       <c r="J357" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K357" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L357" t="n">
         <v>0</v>
@@ -15171,9 +15139,7 @@
           <t>電池模組</t>
         </is>
       </c>
-      <c r="B358" t="n">
-        <v>0</v>
-      </c>
+      <c r="B358" t="inlineStr"/>
       <c r="C358" t="n">
         <v>0</v>
       </c>
@@ -15190,16 +15156,16 @@
         <v>0</v>
       </c>
       <c r="H358" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I358" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J358" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K358" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L358" t="n">
         <v>0</v>
@@ -15231,16 +15197,16 @@
         <v>0</v>
       </c>
       <c r="H359" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I359" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J359" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K359" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L359" t="n">
         <v>0</v>
@@ -15257,34 +15223,34 @@
       </c>
       <c r="B360" t="inlineStr"/>
       <c r="C360" t="n">
+        <v>1</v>
+      </c>
+      <c r="D360" t="n">
         <v>2</v>
       </c>
-      <c r="D360" t="n">
-        <v>1</v>
-      </c>
       <c r="E360" t="n">
+        <v>1</v>
+      </c>
+      <c r="F360" t="n">
+        <v>1</v>
+      </c>
+      <c r="G360" t="n">
+        <v>0</v>
+      </c>
+      <c r="H360" t="n">
+        <v>0</v>
+      </c>
+      <c r="I360" t="n">
+        <v>1</v>
+      </c>
+      <c r="J360" t="n">
+        <v>1</v>
+      </c>
+      <c r="K360" t="n">
+        <v>0</v>
+      </c>
+      <c r="L360" t="n">
         <v>2</v>
-      </c>
-      <c r="F360" t="n">
-        <v>1</v>
-      </c>
-      <c r="G360" t="n">
-        <v>1</v>
-      </c>
-      <c r="H360" t="n">
-        <v>0</v>
-      </c>
-      <c r="I360" t="n">
-        <v>0</v>
-      </c>
-      <c r="J360" t="n">
-        <v>1</v>
-      </c>
-      <c r="K360" t="n">
-        <v>1</v>
-      </c>
-      <c r="L360" t="n">
-        <v>0</v>
       </c>
       <c r="M360" t="n">
         <v>2</v>
@@ -15316,10 +15282,10 @@
         <v>0</v>
       </c>
       <c r="I361" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J361" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K361" t="n">
         <v>0</v>
@@ -15386,10 +15352,10 @@
         <v>0</v>
       </c>
       <c r="E363" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F363" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G363" t="n">
         <v>0</v>
@@ -15427,25 +15393,25 @@
         <v>1</v>
       </c>
       <c r="E364" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F364" t="n">
         <v>0</v>
       </c>
       <c r="G364" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H364" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I364" t="n">
         <v>0</v>
       </c>
       <c r="J364" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K364" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L364" t="n">
         <v>0</v>
@@ -15462,37 +15428,37 @@
       </c>
       <c r="B365" t="inlineStr"/>
       <c r="C365" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D365" t="n">
+        <v>1</v>
+      </c>
+      <c r="E365" t="n">
         <v>2</v>
       </c>
-      <c r="E365" t="n">
-        <v>1</v>
-      </c>
       <c r="F365" t="n">
+        <v>0</v>
+      </c>
+      <c r="G365" t="n">
+        <v>0</v>
+      </c>
+      <c r="H365" t="n">
+        <v>0</v>
+      </c>
+      <c r="I365" t="n">
+        <v>0</v>
+      </c>
+      <c r="J365" t="n">
         <v>2</v>
       </c>
-      <c r="G365" t="n">
-        <v>0</v>
-      </c>
-      <c r="H365" t="n">
-        <v>0</v>
-      </c>
-      <c r="I365" t="n">
-        <v>0</v>
-      </c>
-      <c r="J365" t="n">
-        <v>0</v>
-      </c>
       <c r="K365" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L365" t="n">
         <v>0</v>
       </c>
       <c r="M365" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="366">
@@ -15501,9 +15467,7 @@
           <t>電視</t>
         </is>
       </c>
-      <c r="B366" t="n">
-        <v>0</v>
-      </c>
+      <c r="B366" t="inlineStr"/>
       <c r="C366" t="n">
         <v>0</v>
       </c>
@@ -15587,31 +15551,31 @@
       </c>
       <c r="B368" t="inlineStr"/>
       <c r="C368" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D368" t="n">
+        <v>0</v>
+      </c>
+      <c r="E368" t="n">
         <v>2</v>
       </c>
-      <c r="E368" t="n">
-        <v>0</v>
-      </c>
       <c r="F368" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G368" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H368" t="n">
         <v>0</v>
       </c>
       <c r="I368" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J368" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K368" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L368" t="n">
         <v>0</v>
@@ -15628,13 +15592,13 @@
       </c>
       <c r="B369" t="inlineStr"/>
       <c r="C369" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D369" t="n">
         <v>1</v>
       </c>
       <c r="E369" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F369" t="n">
         <v>0</v>
@@ -15669,13 +15633,13 @@
       </c>
       <c r="B370" t="inlineStr"/>
       <c r="C370" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D370" t="n">
         <v>1</v>
       </c>
       <c r="E370" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F370" t="n">
         <v>0</v>
@@ -15690,10 +15654,10 @@
         <v>0</v>
       </c>
       <c r="J370" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K370" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L370" t="n">
         <v>0</v>
@@ -15790,33 +15754,35 @@
           <t>領域解決方案</t>
         </is>
       </c>
-      <c r="B373" t="inlineStr"/>
+      <c r="B373" t="n">
+        <v>0</v>
+      </c>
       <c r="C373" t="n">
+        <v>4</v>
+      </c>
+      <c r="D373" t="n">
+        <v>4</v>
+      </c>
+      <c r="E373" t="n">
+        <v>1</v>
+      </c>
+      <c r="F373" t="n">
+        <v>1</v>
+      </c>
+      <c r="G373" t="n">
+        <v>1</v>
+      </c>
+      <c r="H373" t="n">
+        <v>0</v>
+      </c>
+      <c r="I373" t="n">
+        <v>0</v>
+      </c>
+      <c r="J373" t="n">
         <v>2</v>
       </c>
-      <c r="D373" t="n">
-        <v>5</v>
-      </c>
-      <c r="E373" t="n">
-        <v>4</v>
-      </c>
-      <c r="F373" t="n">
-        <v>1</v>
-      </c>
-      <c r="G373" t="n">
-        <v>1</v>
-      </c>
-      <c r="H373" t="n">
-        <v>1</v>
-      </c>
-      <c r="I373" t="n">
-        <v>0</v>
-      </c>
-      <c r="J373" t="n">
-        <v>0</v>
-      </c>
       <c r="K373" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L373" t="n">
         <v>1</v>
@@ -15839,7 +15805,7 @@
         <v>1</v>
       </c>
       <c r="E374" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F374" t="n">
         <v>0</v>
@@ -15880,10 +15846,10 @@
         <v>0</v>
       </c>
       <c r="E375" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F375" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G375" t="n">
         <v>0</v>
@@ -15913,39 +15879,41 @@
           <t>顧問諮詢</t>
         </is>
       </c>
-      <c r="B376" t="inlineStr"/>
+      <c r="B376" t="n">
+        <v>0</v>
+      </c>
       <c r="C376" t="n">
         <v>2</v>
       </c>
       <c r="D376" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E376" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F376" t="n">
+        <v>2</v>
+      </c>
+      <c r="G376" t="n">
+        <v>0</v>
+      </c>
+      <c r="H376" t="n">
+        <v>0</v>
+      </c>
+      <c r="I376" t="n">
+        <v>1</v>
+      </c>
+      <c r="J376" t="n">
         <v>3</v>
       </c>
-      <c r="G376" t="n">
+      <c r="K376" t="n">
+        <v>0</v>
+      </c>
+      <c r="L376" t="n">
         <v>2</v>
       </c>
-      <c r="H376" t="n">
-        <v>0</v>
-      </c>
-      <c r="I376" t="n">
-        <v>0</v>
-      </c>
-      <c r="J376" t="n">
-        <v>1</v>
-      </c>
-      <c r="K376" t="n">
-        <v>3</v>
-      </c>
-      <c r="L376" t="n">
-        <v>0</v>
-      </c>
       <c r="M376" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="377">
@@ -15956,13 +15924,13 @@
       </c>
       <c r="B377" t="inlineStr"/>
       <c r="C377" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D377" t="n">
         <v>1</v>
       </c>
       <c r="E377" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F377" t="n">
         <v>0</v>
@@ -15997,13 +15965,13 @@
       </c>
       <c r="B378" t="inlineStr"/>
       <c r="C378" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D378" t="n">
         <v>2</v>
       </c>
       <c r="E378" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F378" t="n">
         <v>0</v>
@@ -16024,10 +15992,10 @@
         <v>0</v>
       </c>
       <c r="L378" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M378" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="379">
@@ -16068,7 +16036,7 @@
         <v>0</v>
       </c>
       <c r="M379" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="380">
@@ -16205,34 +16173,34 @@
         <v>0</v>
       </c>
       <c r="D383" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E383" t="n">
+        <v>0</v>
+      </c>
+      <c r="F383" t="n">
+        <v>0</v>
+      </c>
+      <c r="G383" t="n">
+        <v>1</v>
+      </c>
+      <c r="H383" t="n">
+        <v>0</v>
+      </c>
+      <c r="I383" t="n">
+        <v>0</v>
+      </c>
+      <c r="J383" t="n">
+        <v>0</v>
+      </c>
+      <c r="K383" t="n">
+        <v>1</v>
+      </c>
+      <c r="L383" t="n">
+        <v>0</v>
+      </c>
+      <c r="M383" t="n">
         <v>2</v>
-      </c>
-      <c r="F383" t="n">
-        <v>0</v>
-      </c>
-      <c r="G383" t="n">
-        <v>0</v>
-      </c>
-      <c r="H383" t="n">
-        <v>1</v>
-      </c>
-      <c r="I383" t="n">
-        <v>0</v>
-      </c>
-      <c r="J383" t="n">
-        <v>0</v>
-      </c>
-      <c r="K383" t="n">
-        <v>0</v>
-      </c>
-      <c r="L383" t="n">
-        <v>1</v>
-      </c>
-      <c r="M383" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="384">
@@ -16287,13 +16255,13 @@
         <v>0</v>
       </c>
       <c r="D385" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E385" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F385" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G385" t="n">
         <v>0</v>
@@ -16302,13 +16270,13 @@
         <v>0</v>
       </c>
       <c r="I385" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J385" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K385" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L385" t="n">
         <v>0</v>

--- a/Result/analyze_3.xlsx
+++ b/Result/analyze_3.xlsx
@@ -441,57 +441,57 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
     </row>
@@ -547,7 +547,7 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -670,28 +670,28 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L6" t="n">
         <v>2</v>
@@ -706,41 +706,39 @@
           <t>IC封裝測試</t>
         </is>
       </c>
-      <c r="B7" t="n">
-        <v>0</v>
-      </c>
+      <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
+        <v>5</v>
+      </c>
+      <c r="D7" t="n">
+        <v>3</v>
+      </c>
+      <c r="E7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
         <v>2</v>
       </c>
-      <c r="D7" t="n">
-        <v>5</v>
-      </c>
-      <c r="E7" t="n">
-        <v>3</v>
-      </c>
-      <c r="F7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G7" t="n">
-        <v>1</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0</v>
-      </c>
       <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
         <v>2</v>
       </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
       <c r="M7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -751,37 +749,37 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D8" t="n">
         <v>2</v>
       </c>
       <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="n">
         <v>2</v>
       </c>
-      <c r="F8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" t="n">
-        <v>0</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0</v>
-      </c>
       <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
         <v>2</v>
       </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
       <c r="M8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -790,36 +788,38 @@
           <t>IC設計</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr"/>
+      <c r="B9" t="n">
+        <v>0</v>
+      </c>
       <c r="C9" t="n">
+        <v>3</v>
+      </c>
+      <c r="D9" t="n">
+        <v>2</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="n">
+        <v>3</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1</v>
+      </c>
+      <c r="L9" t="n">
         <v>4</v>
-      </c>
-      <c r="D9" t="n">
-        <v>3</v>
-      </c>
-      <c r="E9" t="n">
-        <v>2</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" t="n">
-        <v>1</v>
-      </c>
-      <c r="H9" t="n">
-        <v>1</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" t="n">
-        <v>3</v>
-      </c>
-      <c r="K9" t="n">
-        <v>1</v>
-      </c>
-      <c r="L9" t="n">
-        <v>1</v>
       </c>
       <c r="M9" t="n">
         <v>4</v>
@@ -831,39 +831,41 @@
           <t>IC通路</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
+      <c r="B10" t="n">
+        <v>0</v>
+      </c>
       <c r="C10" t="n">
+        <v>2</v>
+      </c>
+      <c r="D10" t="n">
         <v>3</v>
       </c>
-      <c r="D10" t="n">
-        <v>2</v>
-      </c>
       <c r="E10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="n">
         <v>3</v>
       </c>
-      <c r="F10" t="n">
-        <v>1</v>
-      </c>
-      <c r="G10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0</v>
-      </c>
       <c r="J10" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -883,28 +885,28 @@
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>1</v>
+      </c>
+      <c r="L11" t="n">
         <v>2</v>
       </c>
-      <c r="H11" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" t="n">
-        <v>1</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>1</v>
-      </c>
       <c r="M11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -915,13 +917,13 @@
       </c>
       <c r="B12" t="inlineStr"/>
       <c r="C12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
@@ -959,10 +961,10 @@
         <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
@@ -1036,20 +1038,40 @@
           <t>ITO靶材</t>
         </is>
       </c>
-      <c r="B15" t="n">
-        <v>0</v>
-      </c>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
@@ -1100,10 +1122,10 @@
       </c>
       <c r="B17" t="inlineStr"/>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -1124,10 +1146,10 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
         <v>0</v>
@@ -1185,16 +1207,16 @@
         <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -1226,10 +1248,10 @@
         <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
@@ -1262,39 +1284,41 @@
           <t>中、西藥製劑</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr"/>
+      <c r="B21" t="n">
+        <v>0</v>
+      </c>
       <c r="C21" t="n">
         <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F21" t="n">
+        <v>1</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
         <v>2</v>
       </c>
-      <c r="G21" t="n">
-        <v>1</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" t="n">
-        <v>1</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
       <c r="L21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -1308,7 +1332,7 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -1352,10 +1376,10 @@
         <v>0</v>
       </c>
       <c r="E23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -1364,19 +1388,19 @@
         <v>0</v>
       </c>
       <c r="I23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -1385,15 +1409,17 @@
           <t>主/被動元件</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr"/>
+      <c r="B24" t="n">
+        <v>0</v>
+      </c>
       <c r="C24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D24" t="n">
         <v>1</v>
       </c>
       <c r="E24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
@@ -1405,19 +1431,19 @@
         <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="n">
+        <v>1</v>
+      </c>
+      <c r="L24" t="n">
+        <v>3</v>
+      </c>
+      <c r="M24" t="n">
         <v>2</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="n">
-        <v>1</v>
-      </c>
-      <c r="M24" t="n">
-        <v>3</v>
       </c>
     </row>
     <row r="25">
@@ -1431,7 +1457,7 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>
@@ -1455,7 +1481,7 @@
         <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M25" t="n">
         <v>1</v>
@@ -1519,10 +1545,10 @@
         <v>0</v>
       </c>
       <c r="F27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H27" t="n">
         <v>0</v>
@@ -1540,7 +1566,7 @@
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -1633,13 +1659,13 @@
       </c>
       <c r="B30" t="inlineStr"/>
       <c r="C30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E30" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F30" t="n">
         <v>0</v>
@@ -1674,13 +1700,13 @@
       </c>
       <c r="B31" t="inlineStr"/>
       <c r="C31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E31" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F31" t="n">
         <v>0</v>
@@ -1704,7 +1730,7 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -1718,25 +1744,25 @@
         <v>0</v>
       </c>
       <c r="D32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H32" t="n">
         <v>0</v>
       </c>
       <c r="I32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K32" t="n">
         <v>0</v>
@@ -1745,7 +1771,7 @@
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="33">
@@ -1756,10 +1782,10 @@
       </c>
       <c r="B33" t="inlineStr"/>
       <c r="C33" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E33" t="n">
         <v>0</v>
@@ -1786,7 +1812,7 @@
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="34">
@@ -1836,9 +1862,7 @@
           <t>保健食品代理銷售及通路</t>
         </is>
       </c>
-      <c r="B35" t="n">
-        <v>0</v>
-      </c>
+      <c r="B35" t="inlineStr"/>
       <c r="C35" t="n">
         <v>0</v>
       </c>
@@ -1864,7 +1888,7 @@
         <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L35" t="n">
         <v>1</v>
@@ -1963,10 +1987,10 @@
       </c>
       <c r="B38" t="inlineStr"/>
       <c r="C38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E38" t="n">
         <v>0</v>
@@ -2028,10 +2052,10 @@
         <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
         <v>0</v>
@@ -2086,7 +2110,7 @@
       </c>
       <c r="B41" t="inlineStr"/>
       <c r="C41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D41" t="n">
         <v>0</v>
@@ -2104,10 +2128,10 @@
         <v>0</v>
       </c>
       <c r="I41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K41" t="n">
         <v>0</v>
@@ -2125,7 +2149,9 @@
           <t>儲存處理</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr"/>
+      <c r="B42" t="n">
+        <v>0</v>
+      </c>
       <c r="C42" t="n">
         <v>1</v>
       </c>
@@ -2133,7 +2159,7 @@
         <v>1</v>
       </c>
       <c r="E42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F42" t="n">
         <v>0</v>
@@ -2145,19 +2171,19 @@
         <v>0</v>
       </c>
       <c r="I42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K42" t="n">
         <v>0</v>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -2195,10 +2221,10 @@
         <v>0</v>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -2207,7 +2233,9 @@
           <t>光學鏡片、鏡頭</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr"/>
+      <c r="B44" t="n">
+        <v>0</v>
+      </c>
       <c r="C44" t="n">
         <v>1</v>
       </c>
@@ -2215,7 +2243,7 @@
         <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F44" t="n">
         <v>0</v>
@@ -2224,19 +2252,19 @@
         <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
       </c>
       <c r="K44" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L44" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
         <v>0</v>
@@ -2250,7 +2278,7 @@
       </c>
       <c r="B45" t="inlineStr"/>
       <c r="C45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D45" t="n">
         <v>0</v>
@@ -2277,7 +2305,7 @@
         <v>0</v>
       </c>
       <c r="L45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M45" t="n">
         <v>1</v>
@@ -2294,7 +2322,7 @@
         <v>1</v>
       </c>
       <c r="D46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E46" t="n">
         <v>0</v>
@@ -2335,7 +2363,7 @@
         <v>1</v>
       </c>
       <c r="D47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E47" t="n">
         <v>0</v>
@@ -2359,10 +2387,10 @@
         <v>0</v>
       </c>
       <c r="L47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -2412,36 +2440,38 @@
           <t>光通訊設備(如光纖電纜、光傳輸設備)</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr"/>
+      <c r="B49" t="n">
+        <v>0</v>
+      </c>
       <c r="C49" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D49" t="n">
         <v>2</v>
       </c>
       <c r="E49" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F49" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G49" t="n">
+        <v>0</v>
+      </c>
+      <c r="H49" t="n">
+        <v>1</v>
+      </c>
+      <c r="I49" t="n">
         <v>4</v>
       </c>
-      <c r="H49" t="n">
-        <v>0</v>
-      </c>
-      <c r="I49" t="n">
-        <v>1</v>
-      </c>
       <c r="J49" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K49" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="L49" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="M49" t="n">
         <v>3</v>
@@ -2498,37 +2528,37 @@
         <v>0</v>
       </c>
       <c r="C51" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D51" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E51" t="n">
+        <v>1</v>
+      </c>
+      <c r="F51" t="n">
+        <v>1</v>
+      </c>
+      <c r="G51" t="n">
+        <v>1</v>
+      </c>
+      <c r="H51" t="n">
+        <v>1</v>
+      </c>
+      <c r="I51" t="n">
+        <v>3</v>
+      </c>
+      <c r="J51" t="n">
+        <v>1</v>
+      </c>
+      <c r="K51" t="n">
+        <v>3</v>
+      </c>
+      <c r="L51" t="n">
+        <v>4</v>
+      </c>
+      <c r="M51" t="n">
         <v>6</v>
-      </c>
-      <c r="F51" t="n">
-        <v>1</v>
-      </c>
-      <c r="G51" t="n">
-        <v>1</v>
-      </c>
-      <c r="H51" t="n">
-        <v>1</v>
-      </c>
-      <c r="I51" t="n">
-        <v>1</v>
-      </c>
-      <c r="J51" t="n">
-        <v>3</v>
-      </c>
-      <c r="K51" t="n">
-        <v>1</v>
-      </c>
-      <c r="L51" t="n">
-        <v>3</v>
-      </c>
-      <c r="M51" t="n">
-        <v>4</v>
       </c>
     </row>
     <row r="52">
@@ -2578,30 +2608,32 @@
           <t>其他零組件</t>
         </is>
       </c>
-      <c r="B53" t="inlineStr"/>
+      <c r="B53" t="n">
+        <v>0</v>
+      </c>
       <c r="C53" t="n">
         <v>1</v>
       </c>
       <c r="D53" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E53" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F53" t="n">
         <v>2</v>
       </c>
       <c r="G53" t="n">
+        <v>0</v>
+      </c>
+      <c r="H53" t="n">
+        <v>0</v>
+      </c>
+      <c r="I53" t="n">
         <v>2</v>
       </c>
-      <c r="H53" t="n">
-        <v>0</v>
-      </c>
-      <c r="I53" t="n">
-        <v>0</v>
-      </c>
       <c r="J53" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K53" t="n">
         <v>0</v>
@@ -2610,7 +2642,7 @@
         <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="54">
@@ -2619,39 +2651,41 @@
           <t>其他電子產品及電子服務產業</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr"/>
+      <c r="B54" t="n">
+        <v>0</v>
+      </c>
       <c r="C54" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D54" t="n">
         <v>4</v>
       </c>
       <c r="E54" t="n">
+        <v>0</v>
+      </c>
+      <c r="F54" t="n">
+        <v>1</v>
+      </c>
+      <c r="G54" t="n">
+        <v>1</v>
+      </c>
+      <c r="H54" t="n">
+        <v>1</v>
+      </c>
+      <c r="I54" t="n">
+        <v>3</v>
+      </c>
+      <c r="J54" t="n">
+        <v>0</v>
+      </c>
+      <c r="K54" t="n">
         <v>4</v>
       </c>
-      <c r="F54" t="n">
-        <v>0</v>
-      </c>
-      <c r="G54" t="n">
-        <v>1</v>
-      </c>
-      <c r="H54" t="n">
-        <v>1</v>
-      </c>
-      <c r="I54" t="n">
-        <v>1</v>
-      </c>
-      <c r="J54" t="n">
+      <c r="L54" t="n">
+        <v>5</v>
+      </c>
+      <c r="M54" t="n">
         <v>4</v>
-      </c>
-      <c r="K54" t="n">
-        <v>0</v>
-      </c>
-      <c r="L54" t="n">
-        <v>4</v>
-      </c>
-      <c r="M54" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="55">
@@ -2662,22 +2696,22 @@
       </c>
       <c r="B55" t="inlineStr"/>
       <c r="C55" t="n">
+        <v>4</v>
+      </c>
+      <c r="D55" t="n">
         <v>2</v>
       </c>
-      <c r="D55" t="n">
-        <v>4</v>
-      </c>
       <c r="E55" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
       </c>
       <c r="H55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I55" t="n">
         <v>1</v>
@@ -2686,13 +2720,13 @@
         <v>1</v>
       </c>
       <c r="K55" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L55" t="n">
+        <v>1</v>
+      </c>
+      <c r="M55" t="n">
         <v>3</v>
-      </c>
-      <c r="M55" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="56">
@@ -2701,33 +2735,35 @@
           <t>其他電腦及週邊設備之零組件</t>
         </is>
       </c>
-      <c r="B56" t="inlineStr"/>
+      <c r="B56" t="n">
+        <v>0</v>
+      </c>
       <c r="C56" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D56" t="n">
+        <v>4</v>
+      </c>
+      <c r="E56" t="n">
+        <v>1</v>
+      </c>
+      <c r="F56" t="n">
         <v>2</v>
       </c>
-      <c r="E56" t="n">
-        <v>4</v>
-      </c>
-      <c r="F56" t="n">
-        <v>1</v>
-      </c>
       <c r="G56" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H56" t="n">
         <v>0</v>
       </c>
       <c r="I56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L56" t="n">
         <v>1</v>
@@ -2783,15 +2819,17 @@
           <t>冷凍空調設備及零件</t>
         </is>
       </c>
-      <c r="B58" t="inlineStr"/>
+      <c r="B58" t="n">
+        <v>0</v>
+      </c>
       <c r="C58" t="n">
         <v>0</v>
       </c>
       <c r="D58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F58" t="n">
         <v>0</v>
@@ -2800,10 +2838,10 @@
         <v>0</v>
       </c>
       <c r="H58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -2815,7 +2853,7 @@
         <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="59">
@@ -2829,10 +2867,10 @@
         <v>0</v>
       </c>
       <c r="D59" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F59" t="n">
         <v>0</v>
@@ -2841,13 +2879,13 @@
         <v>0</v>
       </c>
       <c r="H59" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I59" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J59" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K59" t="n">
         <v>0</v>
@@ -2870,10 +2908,10 @@
         <v>0</v>
       </c>
       <c r="D60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F60" t="n">
         <v>0</v>
@@ -2988,7 +3026,9 @@
           <t>分析工具</t>
         </is>
       </c>
-      <c r="B63" t="inlineStr"/>
+      <c r="B63" t="n">
+        <v>0</v>
+      </c>
       <c r="C63" t="n">
         <v>1</v>
       </c>
@@ -2996,7 +3036,7 @@
         <v>1</v>
       </c>
       <c r="E63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F63" t="n">
         <v>0</v>
@@ -3154,10 +3194,10 @@
       </c>
       <c r="B67" t="inlineStr"/>
       <c r="C67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E67" t="n">
         <v>0</v>
@@ -3181,10 +3221,10 @@
         <v>0</v>
       </c>
       <c r="L67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="68">
@@ -3195,10 +3235,10 @@
       </c>
       <c r="B68" t="inlineStr"/>
       <c r="C68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E68" t="n">
         <v>0</v>
@@ -3321,34 +3361,34 @@
         <v>0</v>
       </c>
       <c r="D71" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E71" t="n">
+        <v>0</v>
+      </c>
+      <c r="F71" t="n">
+        <v>1</v>
+      </c>
+      <c r="G71" t="n">
+        <v>0</v>
+      </c>
+      <c r="H71" t="n">
+        <v>0</v>
+      </c>
+      <c r="I71" t="n">
+        <v>0</v>
+      </c>
+      <c r="J71" t="n">
+        <v>0</v>
+      </c>
+      <c r="K71" t="n">
+        <v>1</v>
+      </c>
+      <c r="L71" t="n">
         <v>2</v>
       </c>
-      <c r="F71" t="n">
-        <v>0</v>
-      </c>
-      <c r="G71" t="n">
-        <v>1</v>
-      </c>
-      <c r="H71" t="n">
-        <v>0</v>
-      </c>
-      <c r="I71" t="n">
-        <v>0</v>
-      </c>
-      <c r="J71" t="n">
-        <v>0</v>
-      </c>
-      <c r="K71" t="n">
-        <v>0</v>
-      </c>
-      <c r="L71" t="n">
-        <v>1</v>
-      </c>
       <c r="M71" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="72">
@@ -3357,41 +3397,39 @@
           <t>化學品</t>
         </is>
       </c>
-      <c r="B72" t="n">
-        <v>0</v>
-      </c>
+      <c r="B72" t="inlineStr"/>
       <c r="C72" t="n">
         <v>0</v>
       </c>
       <c r="D72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H72" t="n">
         <v>0</v>
       </c>
       <c r="I72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L72" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M72" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="73">
@@ -3400,9 +3438,7 @@
           <t>化學品(如光阻劑、靶材等)</t>
         </is>
       </c>
-      <c r="B73" t="n">
-        <v>0</v>
-      </c>
+      <c r="B73" t="inlineStr"/>
       <c r="C73" t="n">
         <v>0</v>
       </c>
@@ -3422,10 +3458,10 @@
         <v>0</v>
       </c>
       <c r="I73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J73" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K73" t="n">
         <v>0</v>
@@ -3486,13 +3522,13 @@
       </c>
       <c r="B75" t="inlineStr"/>
       <c r="C75" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D75" t="n">
         <v>1</v>
       </c>
       <c r="E75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F75" t="n">
         <v>0</v>
@@ -3530,7 +3566,7 @@
         <v>1</v>
       </c>
       <c r="D76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E76" t="n">
         <v>0</v>
@@ -3554,10 +3590,10 @@
         <v>0</v>
       </c>
       <c r="L76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M76" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="77">
@@ -3595,10 +3631,10 @@
         <v>0</v>
       </c>
       <c r="L77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M77" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="78">
@@ -3607,41 +3643,39 @@
           <t>原材料</t>
         </is>
       </c>
-      <c r="B78" t="n">
-        <v>0</v>
-      </c>
+      <c r="B78" t="inlineStr"/>
       <c r="C78" t="n">
         <v>0</v>
       </c>
       <c r="D78" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E78" t="n">
+        <v>1</v>
+      </c>
+      <c r="F78" t="n">
         <v>2</v>
-      </c>
-      <c r="F78" t="n">
-        <v>1</v>
       </c>
       <c r="G78" t="n">
         <v>2</v>
       </c>
       <c r="H78" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I78" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
       </c>
       <c r="K78" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L78" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M78" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="79">
@@ -3693,10 +3727,10 @@
       </c>
       <c r="B80" t="inlineStr"/>
       <c r="C80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D80" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E80" t="n">
         <v>0</v>
@@ -3761,7 +3795,7 @@
         <v>0</v>
       </c>
       <c r="L81" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M81" t="n">
         <v>1</v>
@@ -3773,15 +3807,17 @@
           <t>基板</t>
         </is>
       </c>
-      <c r="B82" t="inlineStr"/>
+      <c r="B82" t="n">
+        <v>0</v>
+      </c>
       <c r="C82" t="n">
         <v>0</v>
       </c>
       <c r="D82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F82" t="n">
         <v>0</v>
@@ -3814,39 +3850,41 @@
           <t>基板組裝加工及相關製造</t>
         </is>
       </c>
-      <c r="B83" t="inlineStr"/>
+      <c r="B83" t="n">
+        <v>0</v>
+      </c>
       <c r="C83" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D83" t="n">
+        <v>1</v>
+      </c>
+      <c r="E83" t="n">
+        <v>0</v>
+      </c>
+      <c r="F83" t="n">
+        <v>1</v>
+      </c>
+      <c r="G83" t="n">
+        <v>0</v>
+      </c>
+      <c r="H83" t="n">
+        <v>0</v>
+      </c>
+      <c r="I83" t="n">
         <v>2</v>
       </c>
-      <c r="E83" t="n">
-        <v>1</v>
-      </c>
-      <c r="F83" t="n">
-        <v>0</v>
-      </c>
-      <c r="G83" t="n">
-        <v>1</v>
-      </c>
-      <c r="H83" t="n">
-        <v>0</v>
-      </c>
-      <c r="I83" t="n">
-        <v>0</v>
-      </c>
       <c r="J83" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K83" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L83" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M83" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="84">
@@ -3937,18 +3975,20 @@
           <t>塑膠/金屬機殼</t>
         </is>
       </c>
-      <c r="B86" t="inlineStr"/>
+      <c r="B86" t="n">
+        <v>0</v>
+      </c>
       <c r="C86" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D86" t="n">
         <v>1</v>
       </c>
       <c r="E86" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F86" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G86" t="n">
         <v>0</v>
@@ -3978,21 +4018,23 @@
           <t>塑膠材料</t>
         </is>
       </c>
-      <c r="B87" t="inlineStr"/>
+      <c r="B87" t="n">
+        <v>0</v>
+      </c>
       <c r="C87" t="n">
         <v>0</v>
       </c>
       <c r="D87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H87" t="n">
         <v>0</v>
@@ -4021,10 +4063,10 @@
       </c>
       <c r="B88" t="inlineStr"/>
       <c r="C88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E88" t="n">
         <v>0</v>
@@ -4039,10 +4081,10 @@
         <v>0</v>
       </c>
       <c r="I88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K88" t="n">
         <v>0</v>
@@ -4062,28 +4104,28 @@
       </c>
       <c r="B89" t="inlineStr"/>
       <c r="C89" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D89" t="n">
         <v>1</v>
       </c>
       <c r="E89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F89" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H89" t="n">
         <v>0</v>
       </c>
       <c r="I89" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K89" t="n">
         <v>0</v>
@@ -4092,7 +4134,7 @@
         <v>0</v>
       </c>
       <c r="M89" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="90">
@@ -4147,7 +4189,7 @@
         <v>1</v>
       </c>
       <c r="D91" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E91" t="n">
         <v>0</v>
@@ -4183,18 +4225,20 @@
           <t>大功率鋰電池芯/模組、電池管理系統、動力馬達等零組件</t>
         </is>
       </c>
-      <c r="B92" t="inlineStr"/>
+      <c r="B92" t="n">
+        <v>0</v>
+      </c>
       <c r="C92" t="n">
         <v>0</v>
       </c>
       <c r="D92" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E92" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F92" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G92" t="n">
         <v>1</v>
@@ -4203,10 +4247,10 @@
         <v>1</v>
       </c>
       <c r="I92" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J92" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K92" t="n">
         <v>0</v>
@@ -4215,7 +4259,7 @@
         <v>0</v>
       </c>
       <c r="M92" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="93">
@@ -4297,7 +4341,7 @@
         <v>0</v>
       </c>
       <c r="M94" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="95">
@@ -4311,31 +4355,31 @@
         <v>0</v>
       </c>
       <c r="D95" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E95" t="n">
+        <v>0</v>
+      </c>
+      <c r="F95" t="n">
+        <v>0</v>
+      </c>
+      <c r="G95" t="n">
+        <v>0</v>
+      </c>
+      <c r="H95" t="n">
+        <v>1</v>
+      </c>
+      <c r="I95" t="n">
+        <v>1</v>
+      </c>
+      <c r="J95" t="n">
+        <v>0</v>
+      </c>
+      <c r="K95" t="n">
+        <v>0</v>
+      </c>
+      <c r="L95" t="n">
         <v>2</v>
-      </c>
-      <c r="F95" t="n">
-        <v>0</v>
-      </c>
-      <c r="G95" t="n">
-        <v>0</v>
-      </c>
-      <c r="H95" t="n">
-        <v>0</v>
-      </c>
-      <c r="I95" t="n">
-        <v>1</v>
-      </c>
-      <c r="J95" t="n">
-        <v>1</v>
-      </c>
-      <c r="K95" t="n">
-        <v>0</v>
-      </c>
-      <c r="L95" t="n">
-        <v>0</v>
       </c>
       <c r="M95" t="n">
         <v>2</v>
@@ -4352,10 +4396,10 @@
         <v>0</v>
       </c>
       <c r="D96" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E96" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F96" t="n">
         <v>0</v>
@@ -4367,19 +4411,19 @@
         <v>0</v>
       </c>
       <c r="I96" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J96" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K96" t="n">
         <v>0</v>
       </c>
       <c r="L96" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M96" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="97">
@@ -4461,7 +4505,7 @@
         <v>0</v>
       </c>
       <c r="M98" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="99">
@@ -4493,16 +4537,16 @@
         <v>0</v>
       </c>
       <c r="J99" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L99" t="n">
         <v>0</v>
       </c>
       <c r="M99" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="100">
@@ -4554,16 +4598,16 @@
       </c>
       <c r="B101" t="inlineStr"/>
       <c r="C101" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D101" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E101" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F101" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G101" t="n">
         <v>0</v>
@@ -4578,13 +4622,13 @@
         <v>0</v>
       </c>
       <c r="K101" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L101" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M101" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="102">
@@ -4595,37 +4639,37 @@
       </c>
       <c r="B102" t="inlineStr"/>
       <c r="C102" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D102" t="n">
+        <v>1</v>
+      </c>
+      <c r="E102" t="n">
+        <v>1</v>
+      </c>
+      <c r="F102" t="n">
+        <v>0</v>
+      </c>
+      <c r="G102" t="n">
+        <v>0</v>
+      </c>
+      <c r="H102" t="n">
+        <v>0</v>
+      </c>
+      <c r="I102" t="n">
         <v>2</v>
       </c>
-      <c r="E102" t="n">
-        <v>1</v>
-      </c>
-      <c r="F102" t="n">
-        <v>1</v>
-      </c>
-      <c r="G102" t="n">
-        <v>0</v>
-      </c>
-      <c r="H102" t="n">
-        <v>0</v>
-      </c>
-      <c r="I102" t="n">
-        <v>0</v>
-      </c>
       <c r="J102" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K102" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L102" t="n">
         <v>0</v>
       </c>
       <c r="M102" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="103">
@@ -4677,16 +4721,16 @@
       </c>
       <c r="B104" t="inlineStr"/>
       <c r="C104" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D104" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E104" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F104" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G104" t="n">
         <v>0</v>
@@ -4695,16 +4739,16 @@
         <v>0</v>
       </c>
       <c r="I104" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J104" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K104" t="n">
         <v>0</v>
       </c>
       <c r="L104" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M104" t="n">
         <v>1</v>
@@ -4721,34 +4765,34 @@
         <v>1</v>
       </c>
       <c r="D105" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E105" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F105" t="n">
         <v>1</v>
       </c>
       <c r="G105" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H105" t="n">
         <v>0</v>
       </c>
       <c r="I105" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J105" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K105" t="n">
         <v>0</v>
       </c>
       <c r="L105" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M105" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="106">
@@ -4759,28 +4803,28 @@
       </c>
       <c r="B106" t="inlineStr"/>
       <c r="C106" t="n">
+        <v>1</v>
+      </c>
+      <c r="D106" t="n">
         <v>2</v>
       </c>
-      <c r="D106" t="n">
-        <v>1</v>
-      </c>
       <c r="E106" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F106" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G106" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H106" t="n">
         <v>0</v>
       </c>
       <c r="I106" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J106" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K106" t="n">
         <v>0</v>
@@ -4923,7 +4967,7 @@
       </c>
       <c r="B110" t="inlineStr"/>
       <c r="C110" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D110" t="n">
         <v>0</v>
@@ -4941,10 +4985,10 @@
         <v>0</v>
       </c>
       <c r="I110" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J110" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K110" t="n">
         <v>0</v>
@@ -4964,16 +5008,16 @@
       </c>
       <c r="B111" t="inlineStr"/>
       <c r="C111" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D111" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E111" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F111" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G111" t="n">
         <v>0</v>
@@ -4988,13 +5032,13 @@
         <v>0</v>
       </c>
       <c r="K111" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L111" t="n">
         <v>1</v>
       </c>
       <c r="M111" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="112">
@@ -5008,10 +5052,10 @@
         <v>0</v>
       </c>
       <c r="D112" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E112" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F112" t="n">
         <v>0</v>
@@ -5020,10 +5064,10 @@
         <v>0</v>
       </c>
       <c r="H112" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I112" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -5032,10 +5076,10 @@
         <v>0</v>
       </c>
       <c r="L112" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M112" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="113">
@@ -5049,10 +5093,10 @@
         <v>0</v>
       </c>
       <c r="D113" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E113" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F113" t="n">
         <v>0</v>
@@ -5061,10 +5105,10 @@
         <v>0</v>
       </c>
       <c r="H113" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I113" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -5111,10 +5155,10 @@
         <v>0</v>
       </c>
       <c r="K114" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L114" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M114" t="n">
         <v>0</v>
@@ -5155,10 +5199,10 @@
         <v>0</v>
       </c>
       <c r="L115" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M115" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="116">
@@ -5196,10 +5240,10 @@
         <v>0</v>
       </c>
       <c r="L116" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M116" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="117">
@@ -5292,10 +5336,10 @@
       </c>
       <c r="B119" t="inlineStr"/>
       <c r="C119" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D119" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E119" t="n">
         <v>0</v>
@@ -5333,28 +5377,28 @@
       </c>
       <c r="B120" t="inlineStr"/>
       <c r="C120" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D120" t="n">
+        <v>0</v>
+      </c>
+      <c r="E120" t="n">
+        <v>1</v>
+      </c>
+      <c r="F120" t="n">
+        <v>1</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0</v>
+      </c>
+      <c r="I120" t="n">
         <v>2</v>
       </c>
-      <c r="E120" t="n">
-        <v>0</v>
-      </c>
-      <c r="F120" t="n">
-        <v>1</v>
-      </c>
-      <c r="G120" t="n">
-        <v>1</v>
-      </c>
-      <c r="H120" t="n">
-        <v>0</v>
-      </c>
-      <c r="I120" t="n">
-        <v>0</v>
-      </c>
       <c r="J120" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K120" t="n">
         <v>0</v>
@@ -5363,7 +5407,7 @@
         <v>0</v>
       </c>
       <c r="M120" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="121">
@@ -5372,15 +5416,17 @@
           <t>建設業</t>
         </is>
       </c>
-      <c r="B121" t="inlineStr"/>
+      <c r="B121" t="n">
+        <v>0</v>
+      </c>
       <c r="C121" t="n">
         <v>0</v>
       </c>
       <c r="D121" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E121" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F121" t="n">
         <v>0</v>
@@ -5392,19 +5438,19 @@
         <v>0</v>
       </c>
       <c r="I121" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J121" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K121" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L121" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M121" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="122">
@@ -5500,10 +5546,10 @@
         <v>0</v>
       </c>
       <c r="D124" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E124" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F124" t="n">
         <v>0</v>
@@ -5579,7 +5625,7 @@
       </c>
       <c r="B126" t="inlineStr"/>
       <c r="C126" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D126" t="n">
         <v>0</v>
@@ -5618,9 +5664,11 @@
           <t>感測裝置</t>
         </is>
       </c>
-      <c r="B127" t="inlineStr"/>
+      <c r="B127" t="n">
+        <v>0</v>
+      </c>
       <c r="C127" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D127" t="n">
         <v>0</v>
@@ -5664,34 +5712,34 @@
         <v>2</v>
       </c>
       <c r="D128" t="n">
+        <v>1</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0</v>
+      </c>
+      <c r="F128" t="n">
+        <v>1</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0</v>
+      </c>
+      <c r="H128" t="n">
+        <v>1</v>
+      </c>
+      <c r="I128" t="n">
+        <v>1</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0</v>
+      </c>
+      <c r="M128" t="n">
         <v>2</v>
-      </c>
-      <c r="E128" t="n">
-        <v>1</v>
-      </c>
-      <c r="F128" t="n">
-        <v>0</v>
-      </c>
-      <c r="G128" t="n">
-        <v>1</v>
-      </c>
-      <c r="H128" t="n">
-        <v>0</v>
-      </c>
-      <c r="I128" t="n">
-        <v>1</v>
-      </c>
-      <c r="J128" t="n">
-        <v>1</v>
-      </c>
-      <c r="K128" t="n">
-        <v>0</v>
-      </c>
-      <c r="L128" t="n">
-        <v>0</v>
-      </c>
-      <c r="M128" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="129">
@@ -5700,7 +5748,9 @@
           <t>應用軟體</t>
         </is>
       </c>
-      <c r="B129" t="inlineStr"/>
+      <c r="B129" t="n">
+        <v>0</v>
+      </c>
       <c r="C129" t="n">
         <v>1</v>
       </c>
@@ -5708,7 +5758,7 @@
         <v>1</v>
       </c>
       <c r="E129" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F129" t="n">
         <v>0</v>
@@ -5743,10 +5793,10 @@
       </c>
       <c r="B130" t="inlineStr"/>
       <c r="C130" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D130" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E130" t="n">
         <v>0</v>
@@ -5787,7 +5837,7 @@
         <v>0</v>
       </c>
       <c r="D131" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E131" t="n">
         <v>1</v>
@@ -5796,13 +5846,13 @@
         <v>1</v>
       </c>
       <c r="G131" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H131" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I131" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -5831,10 +5881,10 @@
         <v>0</v>
       </c>
       <c r="E132" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F132" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G132" t="n">
         <v>0</v>
@@ -5866,10 +5916,10 @@
       </c>
       <c r="B133" t="inlineStr"/>
       <c r="C133" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D133" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E133" t="n">
         <v>0</v>
@@ -5946,7 +5996,9 @@
           <t>控制IC</t>
         </is>
       </c>
-      <c r="B135" t="inlineStr"/>
+      <c r="B135" t="n">
+        <v>0</v>
+      </c>
       <c r="C135" t="n">
         <v>0</v>
       </c>
@@ -6030,7 +6082,7 @@
       </c>
       <c r="B137" t="inlineStr"/>
       <c r="C137" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D137" t="n">
         <v>0</v>
@@ -6110,12 +6162,14 @@
           <t>散熱片、風扇馬達、散熱模組</t>
         </is>
       </c>
-      <c r="B139" t="inlineStr"/>
+      <c r="B139" t="n">
+        <v>0</v>
+      </c>
       <c r="C139" t="n">
         <v>1</v>
       </c>
       <c r="D139" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E139" t="n">
         <v>0</v>
@@ -6130,10 +6184,10 @@
         <v>0</v>
       </c>
       <c r="I139" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J139" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K139" t="n">
         <v>0</v>
@@ -6142,7 +6196,7 @@
         <v>0</v>
       </c>
       <c r="M139" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="140">
@@ -6180,7 +6234,7 @@
         <v>0</v>
       </c>
       <c r="L140" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M140" t="n">
         <v>1</v>
@@ -6194,7 +6248,7 @@
       </c>
       <c r="B141" t="inlineStr"/>
       <c r="C141" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D141" t="n">
         <v>1</v>
@@ -6203,7 +6257,7 @@
         <v>1</v>
       </c>
       <c r="F141" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G141" t="n">
         <v>0</v>
@@ -6221,7 +6275,7 @@
         <v>0</v>
       </c>
       <c r="L141" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M141" t="n">
         <v>1</v>
@@ -6262,7 +6316,7 @@
         <v>0</v>
       </c>
       <c r="L142" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M142" t="n">
         <v>1</v>
@@ -6276,10 +6330,10 @@
       </c>
       <c r="B143" t="inlineStr"/>
       <c r="C143" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D143" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E143" t="n">
         <v>0</v>
@@ -6317,19 +6371,19 @@
       </c>
       <c r="B144" t="inlineStr"/>
       <c r="C144" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D144" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E144" t="n">
         <v>0</v>
       </c>
       <c r="F144" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G144" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H144" t="n">
         <v>0</v>
@@ -6341,10 +6395,10 @@
         <v>0</v>
       </c>
       <c r="K144" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L144" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M144" t="n">
         <v>0</v>
@@ -6358,16 +6412,16 @@
       </c>
       <c r="B145" t="inlineStr"/>
       <c r="C145" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D145" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E145" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F145" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G145" t="n">
         <v>0</v>
@@ -6382,13 +6436,13 @@
         <v>0</v>
       </c>
       <c r="K145" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L145" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M145" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="146">
@@ -6399,7 +6453,7 @@
       </c>
       <c r="B146" t="inlineStr"/>
       <c r="C146" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D146" t="n">
         <v>0</v>
@@ -6440,16 +6494,16 @@
       </c>
       <c r="B147" t="inlineStr"/>
       <c r="C147" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D147" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E147" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F147" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G147" t="n">
         <v>0</v>
@@ -6464,13 +6518,13 @@
         <v>0</v>
       </c>
       <c r="K147" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L147" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M147" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="148">
@@ -6479,7 +6533,9 @@
           <t>文化印刷業</t>
         </is>
       </c>
-      <c r="B148" t="inlineStr"/>
+      <c r="B148" t="n">
+        <v>0</v>
+      </c>
       <c r="C148" t="n">
         <v>0</v>
       </c>
@@ -6505,10 +6561,10 @@
         <v>0</v>
       </c>
       <c r="K148" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L148" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M148" t="n">
         <v>0</v>
@@ -6528,10 +6584,10 @@
         <v>0</v>
       </c>
       <c r="E149" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F149" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G149" t="n">
         <v>0</v>
@@ -6581,10 +6637,10 @@
         <v>0</v>
       </c>
       <c r="I150" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J150" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K150" t="n">
         <v>0</v>
@@ -6602,27 +6658,29 @@
           <t>旅館服務業</t>
         </is>
       </c>
-      <c r="B151" t="inlineStr"/>
+      <c r="B151" t="n">
+        <v>0</v>
+      </c>
       <c r="C151" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D151" t="n">
         <v>0</v>
       </c>
       <c r="E151" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F151" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G151" t="n">
         <v>0</v>
       </c>
       <c r="H151" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I151" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -6634,7 +6692,7 @@
         <v>0</v>
       </c>
       <c r="M151" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="152">
@@ -6648,7 +6706,7 @@
         <v>1</v>
       </c>
       <c r="D152" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E152" t="n">
         <v>0</v>
@@ -6684,33 +6742,35 @@
           <t>智慧設備</t>
         </is>
       </c>
-      <c r="B153" t="inlineStr"/>
+      <c r="B153" t="n">
+        <v>0</v>
+      </c>
       <c r="C153" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D153" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E153" t="n">
         <v>0</v>
       </c>
       <c r="F153" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G153" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H153" t="n">
         <v>0</v>
       </c>
       <c r="I153" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J153" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K153" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L153" t="n">
         <v>0</v>
@@ -6725,15 +6785,17 @@
           <t>有線通訊設備(如電話機、傳真機)</t>
         </is>
       </c>
-      <c r="B154" t="inlineStr"/>
+      <c r="B154" t="n">
+        <v>0</v>
+      </c>
       <c r="C154" t="n">
         <v>0</v>
       </c>
       <c r="D154" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E154" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F154" t="n">
         <v>0</v>
@@ -6748,7 +6810,7 @@
         <v>0</v>
       </c>
       <c r="J154" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K154" t="n">
         <v>0</v>
@@ -6807,23 +6869,21 @@
           <t>材料</t>
         </is>
       </c>
-      <c r="B156" t="n">
-        <v>0</v>
-      </c>
+      <c r="B156" t="inlineStr"/>
       <c r="C156" t="n">
         <v>0</v>
       </c>
       <c r="D156" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E156" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F156" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G156" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H156" t="n">
         <v>0</v>
@@ -6852,13 +6912,13 @@
       </c>
       <c r="B157" t="inlineStr"/>
       <c r="C157" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D157" t="n">
         <v>2</v>
       </c>
       <c r="E157" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F157" t="n">
         <v>0</v>
@@ -6873,13 +6933,13 @@
         <v>0</v>
       </c>
       <c r="J157" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K157" t="n">
         <v>1</v>
       </c>
       <c r="L157" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M157" t="n">
         <v>0</v>
@@ -6896,7 +6956,7 @@
         <v>1</v>
       </c>
       <c r="D158" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E158" t="n">
         <v>0</v>
@@ -6911,10 +6971,10 @@
         <v>0</v>
       </c>
       <c r="I158" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J158" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K158" t="n">
         <v>0</v>
@@ -6975,10 +7035,10 @@
       </c>
       <c r="B160" t="inlineStr"/>
       <c r="C160" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D160" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E160" t="n">
         <v>0</v>
@@ -6993,10 +7053,10 @@
         <v>0</v>
       </c>
       <c r="I160" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J160" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K160" t="n">
         <v>0</v>
@@ -7016,10 +7076,10 @@
       </c>
       <c r="B161" t="inlineStr"/>
       <c r="C161" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D161" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E161" t="n">
         <v>0</v>
@@ -7055,39 +7115,41 @@
           <t>機器學習</t>
         </is>
       </c>
-      <c r="B162" t="inlineStr"/>
+      <c r="B162" t="n">
+        <v>0</v>
+      </c>
       <c r="C162" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D162" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E162" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F162" t="n">
         <v>1</v>
       </c>
       <c r="G162" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H162" t="n">
         <v>0</v>
       </c>
       <c r="I162" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J162" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K162" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L162" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M162" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="163">
@@ -7096,15 +7158,17 @@
           <t>機械設備之沖壓零組件</t>
         </is>
       </c>
-      <c r="B163" t="inlineStr"/>
+      <c r="B163" t="n">
+        <v>0</v>
+      </c>
       <c r="C163" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D163" t="n">
         <v>1</v>
       </c>
       <c r="E163" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F163" t="n">
         <v>0</v>
@@ -7139,10 +7203,10 @@
       </c>
       <c r="B164" t="inlineStr"/>
       <c r="C164" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D164" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E164" t="n">
         <v>0</v>
@@ -7169,7 +7233,7 @@
         <v>0</v>
       </c>
       <c r="M164" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="165">
@@ -7178,18 +7242,20 @@
           <t>機殼</t>
         </is>
       </c>
-      <c r="B165" t="inlineStr"/>
+      <c r="B165" t="n">
+        <v>0</v>
+      </c>
       <c r="C165" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D165" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E165" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F165" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G165" t="n">
         <v>0</v>
@@ -7204,13 +7270,13 @@
         <v>0</v>
       </c>
       <c r="K165" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L165" t="n">
         <v>1</v>
       </c>
       <c r="M165" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="166">
@@ -7224,10 +7290,10 @@
         <v>0</v>
       </c>
       <c r="D166" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E166" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F166" t="n">
         <v>0</v>
@@ -7236,13 +7302,13 @@
         <v>0</v>
       </c>
       <c r="H166" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I166" t="n">
         <v>1</v>
       </c>
       <c r="J166" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K166" t="n">
         <v>0</v>
@@ -7265,10 +7331,10 @@
         <v>0</v>
       </c>
       <c r="D167" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E167" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F167" t="n">
         <v>0</v>
@@ -7277,10 +7343,10 @@
         <v>0</v>
       </c>
       <c r="H167" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I167" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -7330,10 +7396,10 @@
         <v>0</v>
       </c>
       <c r="L168" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M168" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="169">
@@ -7470,10 +7536,10 @@
         <v>0</v>
       </c>
       <c r="D172" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E172" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F172" t="n">
         <v>0</v>
@@ -7494,10 +7560,10 @@
         <v>0</v>
       </c>
       <c r="L172" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M172" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="173">
@@ -7508,10 +7574,10 @@
       </c>
       <c r="B173" t="inlineStr"/>
       <c r="C173" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D173" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E173" t="n">
         <v>0</v>
@@ -7576,10 +7642,10 @@
         <v>0</v>
       </c>
       <c r="L174" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M174" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="175">
@@ -7617,10 +7683,10 @@
         <v>0</v>
       </c>
       <c r="L175" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M175" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="176">
@@ -7670,18 +7736,20 @@
           <t>濾波器、振盪器</t>
         </is>
       </c>
-      <c r="B177" t="inlineStr"/>
+      <c r="B177" t="n">
+        <v>0</v>
+      </c>
       <c r="C177" t="n">
         <v>1</v>
       </c>
       <c r="D177" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E177" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F177" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G177" t="n">
         <v>0</v>
@@ -7690,10 +7758,10 @@
         <v>0</v>
       </c>
       <c r="I177" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J177" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K177" t="n">
         <v>0</v>
@@ -7711,9 +7779,7 @@
           <t>濾波器、振盪器材料(鉭酸鋰／鈮酸鋰晶圓／片、石英基板、金屬及陶瓷封裝材料)</t>
         </is>
       </c>
-      <c r="B178" t="n">
-        <v>0</v>
-      </c>
+      <c r="B178" t="inlineStr"/>
       <c r="C178" t="n">
         <v>0</v>
       </c>
@@ -7756,34 +7822,34 @@
       </c>
       <c r="B179" t="inlineStr"/>
       <c r="C179" t="n">
+        <v>5</v>
+      </c>
+      <c r="D179" t="n">
+        <v>1</v>
+      </c>
+      <c r="E179" t="n">
+        <v>0</v>
+      </c>
+      <c r="F179" t="n">
         <v>2</v>
       </c>
-      <c r="D179" t="n">
-        <v>5</v>
-      </c>
-      <c r="E179" t="n">
-        <v>1</v>
-      </c>
-      <c r="F179" t="n">
-        <v>0</v>
-      </c>
       <c r="G179" t="n">
+        <v>0</v>
+      </c>
+      <c r="H179" t="n">
+        <v>0</v>
+      </c>
+      <c r="I179" t="n">
         <v>2</v>
       </c>
-      <c r="H179" t="n">
-        <v>0</v>
-      </c>
-      <c r="I179" t="n">
-        <v>0</v>
-      </c>
       <c r="J179" t="n">
+        <v>1</v>
+      </c>
+      <c r="K179" t="n">
+        <v>4</v>
+      </c>
+      <c r="L179" t="n">
         <v>2</v>
-      </c>
-      <c r="K179" t="n">
-        <v>1</v>
-      </c>
-      <c r="L179" t="n">
-        <v>4</v>
       </c>
       <c r="M179" t="n">
         <v>2</v>
@@ -7800,10 +7866,10 @@
         <v>0</v>
       </c>
       <c r="D180" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E180" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F180" t="n">
         <v>0</v>
@@ -7836,18 +7902,20 @@
           <t>燈具/應用</t>
         </is>
       </c>
-      <c r="B181" t="inlineStr"/>
+      <c r="B181" t="n">
+        <v>0</v>
+      </c>
       <c r="C181" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D181" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E181" t="n">
         <v>2</v>
       </c>
       <c r="F181" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G181" t="n">
         <v>0</v>
@@ -7856,13 +7924,13 @@
         <v>0</v>
       </c>
       <c r="I181" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J181" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K181" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L181" t="n">
         <v>1</v>
@@ -7877,21 +7945,23 @@
           <t>營造業</t>
         </is>
       </c>
-      <c r="B182" t="inlineStr"/>
+      <c r="B182" t="n">
+        <v>0</v>
+      </c>
       <c r="C182" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D182" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E182" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F182" t="n">
         <v>1</v>
       </c>
       <c r="G182" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H182" t="n">
         <v>0</v>
@@ -7961,16 +8031,16 @@
       </c>
       <c r="B184" t="inlineStr"/>
       <c r="C184" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D184" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E184" t="n">
         <v>1</v>
       </c>
       <c r="F184" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G184" t="n">
         <v>0</v>
@@ -7985,13 +8055,13 @@
         <v>0</v>
       </c>
       <c r="K184" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L184" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M184" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="185">
@@ -8125,19 +8195,19 @@
       </c>
       <c r="B188" t="inlineStr"/>
       <c r="C188" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D188" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E188" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F188" t="n">
         <v>1</v>
       </c>
       <c r="G188" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H188" t="n">
         <v>0</v>
@@ -8149,13 +8219,13 @@
         <v>0</v>
       </c>
       <c r="K188" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L188" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M188" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="189">
@@ -8164,7 +8234,9 @@
           <t>特殊照明業</t>
         </is>
       </c>
-      <c r="B189" t="inlineStr"/>
+      <c r="B189" t="n">
+        <v>0</v>
+      </c>
       <c r="C189" t="n">
         <v>0</v>
       </c>
@@ -8184,10 +8256,10 @@
         <v>0</v>
       </c>
       <c r="I189" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J189" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K189" t="n">
         <v>0</v>
@@ -8207,10 +8279,10 @@
       </c>
       <c r="B190" t="inlineStr"/>
       <c r="C190" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D190" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E190" t="n">
         <v>0</v>
@@ -8289,16 +8361,16 @@
       </c>
       <c r="B192" t="inlineStr"/>
       <c r="C192" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D192" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E192" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F192" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G192" t="n">
         <v>0</v>
@@ -8307,10 +8379,10 @@
         <v>0</v>
       </c>
       <c r="I192" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J192" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K192" t="n">
         <v>0</v>
@@ -8369,9 +8441,7 @@
           <t>環保潔能服務產業</t>
         </is>
       </c>
-      <c r="B194" t="n">
-        <v>0</v>
-      </c>
+      <c r="B194" t="inlineStr"/>
       <c r="C194" t="n">
         <v>0</v>
       </c>
@@ -8391,13 +8461,13 @@
         <v>0</v>
       </c>
       <c r="I194" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J194" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K194" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L194" t="n">
         <v>1</v>
@@ -8414,13 +8484,13 @@
       </c>
       <c r="B195" t="inlineStr"/>
       <c r="C195" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D195" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E195" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F195" t="n">
         <v>0</v>
@@ -8441,7 +8511,7 @@
         <v>0</v>
       </c>
       <c r="L195" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M195" t="n">
         <v>1</v>
@@ -8453,39 +8523,41 @@
           <t>生產製程、檢測設備及原物料</t>
         </is>
       </c>
-      <c r="B196" t="inlineStr"/>
+      <c r="B196" t="n">
+        <v>0</v>
+      </c>
       <c r="C196" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D196" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E196" t="n">
+        <v>0</v>
+      </c>
+      <c r="F196" t="n">
+        <v>1</v>
+      </c>
+      <c r="G196" t="n">
+        <v>0</v>
+      </c>
+      <c r="H196" t="n">
+        <v>1</v>
+      </c>
+      <c r="I196" t="n">
+        <v>1</v>
+      </c>
+      <c r="J196" t="n">
+        <v>0</v>
+      </c>
+      <c r="K196" t="n">
+        <v>0</v>
+      </c>
+      <c r="L196" t="n">
         <v>3</v>
       </c>
-      <c r="F196" t="n">
-        <v>0</v>
-      </c>
-      <c r="G196" t="n">
-        <v>1</v>
-      </c>
-      <c r="H196" t="n">
-        <v>0</v>
-      </c>
-      <c r="I196" t="n">
-        <v>1</v>
-      </c>
-      <c r="J196" t="n">
-        <v>1</v>
-      </c>
-      <c r="K196" t="n">
-        <v>0</v>
-      </c>
-      <c r="L196" t="n">
-        <v>0</v>
-      </c>
       <c r="M196" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="197">
@@ -8494,41 +8566,39 @@
           <t>生產製程及檢測設備</t>
         </is>
       </c>
-      <c r="B197" t="n">
-        <v>0</v>
-      </c>
+      <c r="B197" t="inlineStr"/>
       <c r="C197" t="n">
+        <v>1</v>
+      </c>
+      <c r="D197" t="n">
+        <v>6</v>
+      </c>
+      <c r="E197" t="n">
+        <v>2</v>
+      </c>
+      <c r="F197" t="n">
+        <v>1</v>
+      </c>
+      <c r="G197" t="n">
+        <v>1</v>
+      </c>
+      <c r="H197" t="n">
+        <v>3</v>
+      </c>
+      <c r="I197" t="n">
+        <v>8</v>
+      </c>
+      <c r="J197" t="n">
+        <v>0</v>
+      </c>
+      <c r="K197" t="n">
         <v>5</v>
       </c>
-      <c r="D197" t="n">
-        <v>1</v>
-      </c>
-      <c r="E197" t="n">
-        <v>6</v>
-      </c>
-      <c r="F197" t="n">
-        <v>2</v>
-      </c>
-      <c r="G197" t="n">
-        <v>1</v>
-      </c>
-      <c r="H197" t="n">
-        <v>1</v>
-      </c>
-      <c r="I197" t="n">
-        <v>3</v>
-      </c>
-      <c r="J197" t="n">
-        <v>8</v>
-      </c>
-      <c r="K197" t="n">
-        <v>0</v>
-      </c>
       <c r="L197" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="M197" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
     </row>
     <row r="198">
@@ -8569,7 +8639,7 @@
         <v>0</v>
       </c>
       <c r="M198" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="199">
@@ -8639,10 +8709,10 @@
         <v>0</v>
       </c>
       <c r="I200" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J200" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K200" t="n">
         <v>0</v>
@@ -8703,7 +8773,7 @@
       </c>
       <c r="B202" t="inlineStr"/>
       <c r="C202" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D202" t="n">
         <v>0</v>
@@ -8744,13 +8814,13 @@
       </c>
       <c r="B203" t="inlineStr"/>
       <c r="C203" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D203" t="n">
         <v>1</v>
       </c>
       <c r="E203" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F203" t="n">
         <v>0</v>
@@ -8788,34 +8858,34 @@
         <v>0</v>
       </c>
       <c r="D204" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E204" t="n">
+        <v>0</v>
+      </c>
+      <c r="F204" t="n">
+        <v>1</v>
+      </c>
+      <c r="G204" t="n">
+        <v>0</v>
+      </c>
+      <c r="H204" t="n">
+        <v>1</v>
+      </c>
+      <c r="I204" t="n">
+        <v>0</v>
+      </c>
+      <c r="J204" t="n">
+        <v>0</v>
+      </c>
+      <c r="K204" t="n">
+        <v>1</v>
+      </c>
+      <c r="L204" t="n">
         <v>2</v>
       </c>
-      <c r="F204" t="n">
-        <v>0</v>
-      </c>
-      <c r="G204" t="n">
-        <v>1</v>
-      </c>
-      <c r="H204" t="n">
-        <v>0</v>
-      </c>
-      <c r="I204" t="n">
-        <v>1</v>
-      </c>
-      <c r="J204" t="n">
-        <v>0</v>
-      </c>
-      <c r="K204" t="n">
-        <v>0</v>
-      </c>
-      <c r="L204" t="n">
-        <v>1</v>
-      </c>
       <c r="M204" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="205">
@@ -8826,13 +8896,13 @@
       </c>
       <c r="B205" t="inlineStr"/>
       <c r="C205" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D205" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E205" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F205" t="n">
         <v>0</v>
@@ -8914,13 +8984,13 @@
         <v>0</v>
       </c>
       <c r="E207" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F207" t="n">
         <v>1</v>
       </c>
       <c r="G207" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H207" t="n">
         <v>0</v>
@@ -8947,41 +9017,39 @@
           <t>硬板、軟板、IC載板製造</t>
         </is>
       </c>
-      <c r="B208" t="n">
-        <v>0</v>
-      </c>
+      <c r="B208" t="inlineStr"/>
       <c r="C208" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D208" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E208" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F208" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G208" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H208" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I208" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J208" t="n">
+        <v>0</v>
+      </c>
+      <c r="K208" t="n">
+        <v>0</v>
+      </c>
+      <c r="L208" t="n">
         <v>8</v>
       </c>
-      <c r="K208" t="n">
-        <v>0</v>
-      </c>
-      <c r="L208" t="n">
-        <v>0</v>
-      </c>
       <c r="M208" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="209">
@@ -8990,14 +9058,12 @@
           <t>硬碟機</t>
         </is>
       </c>
-      <c r="B209" t="n">
-        <v>0</v>
-      </c>
+      <c r="B209" t="inlineStr"/>
       <c r="C209" t="n">
         <v>1</v>
       </c>
       <c r="D209" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E209" t="n">
         <v>0</v>
@@ -9035,10 +9101,10 @@
       </c>
       <c r="B210" t="inlineStr"/>
       <c r="C210" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D210" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E210" t="n">
         <v>0</v>
@@ -9079,10 +9145,10 @@
         <v>2</v>
       </c>
       <c r="D211" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E211" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F211" t="n">
         <v>0</v>
@@ -9156,7 +9222,9 @@
           <t>租賃業</t>
         </is>
       </c>
-      <c r="B213" t="inlineStr"/>
+      <c r="B213" t="n">
+        <v>0</v>
+      </c>
       <c r="C213" t="n">
         <v>0</v>
       </c>
@@ -9197,7 +9265,9 @@
           <t>移動控制</t>
         </is>
       </c>
-      <c r="B214" t="inlineStr"/>
+      <c r="B214" t="n">
+        <v>0</v>
+      </c>
       <c r="C214" t="n">
         <v>0</v>
       </c>
@@ -9238,7 +9308,9 @@
           <t>稜鏡片</t>
         </is>
       </c>
-      <c r="B215" t="inlineStr"/>
+      <c r="B215" t="n">
+        <v>0</v>
+      </c>
       <c r="C215" t="n">
         <v>0</v>
       </c>
@@ -9281,10 +9353,10 @@
       </c>
       <c r="B216" t="inlineStr"/>
       <c r="C216" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D216" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E216" t="n">
         <v>0</v>
@@ -9320,23 +9392,21 @@
           <t>端點安全防護</t>
         </is>
       </c>
-      <c r="B217" t="n">
-        <v>0</v>
-      </c>
+      <c r="B217" t="inlineStr"/>
       <c r="C217" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D217" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E217" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F217" t="n">
         <v>1</v>
       </c>
       <c r="G217" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H217" t="n">
         <v>0</v>
@@ -9348,13 +9418,13 @@
         <v>0</v>
       </c>
       <c r="K217" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L217" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M217" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="218">
@@ -9368,13 +9438,13 @@
         <v>1</v>
       </c>
       <c r="D218" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E218" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F218" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G218" t="n">
         <v>0</v>
@@ -9383,10 +9453,10 @@
         <v>0</v>
       </c>
       <c r="I218" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J218" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K218" t="n">
         <v>0</v>
@@ -9409,13 +9479,13 @@
         <v>1</v>
       </c>
       <c r="D219" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E219" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F219" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G219" t="n">
         <v>0</v>
@@ -9424,10 +9494,10 @@
         <v>0</v>
       </c>
       <c r="I219" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J219" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K219" t="n">
         <v>0</v>
@@ -9449,37 +9519,37 @@
         <v>0</v>
       </c>
       <c r="C220" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D220" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E220" t="n">
+        <v>2</v>
+      </c>
+      <c r="F220" t="n">
+        <v>1</v>
+      </c>
+      <c r="G220" t="n">
+        <v>0</v>
+      </c>
+      <c r="H220" t="n">
+        <v>1</v>
+      </c>
+      <c r="I220" t="n">
         <v>3</v>
       </c>
-      <c r="F220" t="n">
+      <c r="J220" t="n">
+        <v>0</v>
+      </c>
+      <c r="K220" t="n">
         <v>2</v>
       </c>
-      <c r="G220" t="n">
-        <v>1</v>
-      </c>
-      <c r="H220" t="n">
-        <v>0</v>
-      </c>
-      <c r="I220" t="n">
-        <v>1</v>
-      </c>
-      <c r="J220" t="n">
+      <c r="L220" t="n">
+        <v>1</v>
+      </c>
+      <c r="M220" t="n">
         <v>3</v>
-      </c>
-      <c r="K220" t="n">
-        <v>0</v>
-      </c>
-      <c r="L220" t="n">
-        <v>2</v>
-      </c>
-      <c r="M220" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="221">
@@ -9492,37 +9562,37 @@
         <v>0</v>
       </c>
       <c r="C221" t="n">
+        <v>4</v>
+      </c>
+      <c r="D221" t="n">
+        <v>1</v>
+      </c>
+      <c r="E221" t="n">
+        <v>2</v>
+      </c>
+      <c r="F221" t="n">
         <v>3</v>
       </c>
-      <c r="D221" t="n">
-        <v>4</v>
-      </c>
-      <c r="E221" t="n">
-        <v>1</v>
-      </c>
-      <c r="F221" t="n">
-        <v>2</v>
-      </c>
       <c r="G221" t="n">
+        <v>0</v>
+      </c>
+      <c r="H221" t="n">
+        <v>1</v>
+      </c>
+      <c r="I221" t="n">
+        <v>1</v>
+      </c>
+      <c r="J221" t="n">
+        <v>0</v>
+      </c>
+      <c r="K221" t="n">
+        <v>1</v>
+      </c>
+      <c r="L221" t="n">
+        <v>0</v>
+      </c>
+      <c r="M221" t="n">
         <v>3</v>
-      </c>
-      <c r="H221" t="n">
-        <v>0</v>
-      </c>
-      <c r="I221" t="n">
-        <v>1</v>
-      </c>
-      <c r="J221" t="n">
-        <v>1</v>
-      </c>
-      <c r="K221" t="n">
-        <v>0</v>
-      </c>
-      <c r="L221" t="n">
-        <v>1</v>
-      </c>
-      <c r="M221" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="222">
@@ -9539,10 +9609,10 @@
         <v>0</v>
       </c>
       <c r="E222" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F222" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G222" t="n">
         <v>0</v>
@@ -9574,13 +9644,13 @@
       </c>
       <c r="B223" t="inlineStr"/>
       <c r="C223" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D223" t="n">
         <v>1</v>
       </c>
       <c r="E223" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F223" t="n">
         <v>0</v>
@@ -9604,7 +9674,7 @@
         <v>0</v>
       </c>
       <c r="M223" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="224">
@@ -9642,7 +9712,7 @@
         <v>0</v>
       </c>
       <c r="L224" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M224" t="n">
         <v>1</v>
@@ -9695,15 +9765,17 @@
           <t>網路IC</t>
         </is>
       </c>
-      <c r="B226" t="inlineStr"/>
+      <c r="B226" t="n">
+        <v>0</v>
+      </c>
       <c r="C226" t="n">
         <v>0</v>
       </c>
       <c r="D226" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E226" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F226" t="n">
         <v>0</v>
@@ -9741,7 +9813,7 @@
         <v>1</v>
       </c>
       <c r="D227" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E227" t="n">
         <v>0</v>
@@ -9777,23 +9849,21 @@
           <t>網路基礎設施</t>
         </is>
       </c>
-      <c r="B228" t="n">
-        <v>0</v>
-      </c>
+      <c r="B228" t="inlineStr"/>
       <c r="C228" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D228" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E228" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F228" t="n">
         <v>1</v>
       </c>
       <c r="G228" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H228" t="n">
         <v>0</v>
@@ -9805,7 +9875,7 @@
         <v>0</v>
       </c>
       <c r="K228" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L228" t="n">
         <v>1</v>
@@ -9820,23 +9890,21 @@
           <t>網路安全防護</t>
         </is>
       </c>
-      <c r="B229" t="n">
-        <v>0</v>
-      </c>
+      <c r="B229" t="inlineStr"/>
       <c r="C229" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D229" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E229" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F229" t="n">
         <v>1</v>
       </c>
       <c r="G229" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H229" t="n">
         <v>0</v>
@@ -9848,13 +9916,13 @@
         <v>0</v>
       </c>
       <c r="K229" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L229" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M229" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="230">
@@ -9863,39 +9931,41 @@
           <t>網路設備(如數據機、網路卡、閘道器、路由器、網路電話)</t>
         </is>
       </c>
-      <c r="B230" t="inlineStr"/>
+      <c r="B230" t="n">
+        <v>0</v>
+      </c>
       <c r="C230" t="n">
+        <v>6</v>
+      </c>
+      <c r="D230" t="n">
+        <v>1</v>
+      </c>
+      <c r="E230" t="n">
+        <v>1</v>
+      </c>
+      <c r="F230" t="n">
         <v>2</v>
       </c>
-      <c r="D230" t="n">
-        <v>6</v>
-      </c>
-      <c r="E230" t="n">
-        <v>1</v>
-      </c>
-      <c r="F230" t="n">
-        <v>1</v>
-      </c>
       <c r="G230" t="n">
+        <v>0</v>
+      </c>
+      <c r="H230" t="n">
+        <v>0</v>
+      </c>
+      <c r="I230" t="n">
         <v>2</v>
       </c>
-      <c r="H230" t="n">
-        <v>0</v>
-      </c>
-      <c r="I230" t="n">
-        <v>0</v>
-      </c>
       <c r="J230" t="n">
+        <v>1</v>
+      </c>
+      <c r="K230" t="n">
         <v>3</v>
       </c>
-      <c r="K230" t="n">
-        <v>1</v>
-      </c>
       <c r="L230" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M230" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="231">
@@ -9906,10 +9976,10 @@
       </c>
       <c r="B231" t="inlineStr"/>
       <c r="C231" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D231" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E231" t="n">
         <v>1</v>
@@ -9918,7 +9988,7 @@
         <v>1</v>
       </c>
       <c r="G231" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H231" t="n">
         <v>0</v>
@@ -9930,13 +10000,13 @@
         <v>0</v>
       </c>
       <c r="K231" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L231" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M231" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="232">
@@ -9956,25 +10026,25 @@
         <v>0</v>
       </c>
       <c r="F232" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G232" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H232" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I232" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J232" t="n">
         <v>0</v>
       </c>
       <c r="K232" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L232" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M232" t="n">
         <v>0</v>
@@ -9986,36 +10056,38 @@
           <t>線材</t>
         </is>
       </c>
-      <c r="B233" t="inlineStr"/>
+      <c r="B233" t="n">
+        <v>0</v>
+      </c>
       <c r="C233" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D233" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E233" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F233" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G233" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H233" t="n">
         <v>0</v>
       </c>
       <c r="I233" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J233" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K233" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L233" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M233" t="n">
         <v>0</v>
@@ -10070,13 +10142,13 @@
       </c>
       <c r="B235" t="inlineStr"/>
       <c r="C235" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D235" t="n">
         <v>1</v>
       </c>
       <c r="E235" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F235" t="n">
         <v>0</v>
@@ -10094,13 +10166,13 @@
         <v>0</v>
       </c>
       <c r="K235" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L235" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M235" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="236">
@@ -10114,10 +10186,10 @@
         <v>0</v>
       </c>
       <c r="D236" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E236" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F236" t="n">
         <v>0</v>
@@ -10138,7 +10210,7 @@
         <v>0</v>
       </c>
       <c r="L236" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M236" t="n">
         <v>1</v>
@@ -10179,7 +10251,7 @@
         <v>0</v>
       </c>
       <c r="L237" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M237" t="n">
         <v>1</v>
@@ -10196,16 +10268,16 @@
         <v>1</v>
       </c>
       <c r="D238" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E238" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F238" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G238" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H238" t="n">
         <v>0</v>
@@ -10223,7 +10295,7 @@
         <v>0</v>
       </c>
       <c r="M238" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="239">
@@ -10234,28 +10306,28 @@
       </c>
       <c r="B239" t="inlineStr"/>
       <c r="C239" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D239" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E239" t="n">
         <v>0</v>
       </c>
       <c r="F239" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G239" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H239" t="n">
         <v>0</v>
       </c>
       <c r="I239" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J239" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K239" t="n">
         <v>0</v>
@@ -10264,7 +10336,7 @@
         <v>0</v>
       </c>
       <c r="M239" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="240">
@@ -10278,10 +10350,10 @@
         <v>0</v>
       </c>
       <c r="D240" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E240" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F240" t="n">
         <v>0</v>
@@ -10302,7 +10374,7 @@
         <v>0</v>
       </c>
       <c r="L240" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M240" t="n">
         <v>1</v>
@@ -10343,10 +10415,10 @@
         <v>0</v>
       </c>
       <c r="L241" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M241" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="242">
@@ -10375,19 +10447,19 @@
         <v>0</v>
       </c>
       <c r="I242" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J242" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K242" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L242" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M242" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="243">
@@ -10428,7 +10500,7 @@
         <v>0</v>
       </c>
       <c r="M243" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="244">
@@ -10480,10 +10552,10 @@
       </c>
       <c r="B245" t="inlineStr"/>
       <c r="C245" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D245" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E245" t="n">
         <v>0</v>
@@ -10504,10 +10576,10 @@
         <v>0</v>
       </c>
       <c r="K245" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L245" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M245" t="n">
         <v>0</v>
@@ -10519,18 +10591,20 @@
           <t>自然語言處理</t>
         </is>
       </c>
-      <c r="B246" t="inlineStr"/>
+      <c r="B246" t="n">
+        <v>0</v>
+      </c>
       <c r="C246" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D246" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E246" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F246" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G246" t="n">
         <v>0</v>
@@ -10545,13 +10619,13 @@
         <v>0</v>
       </c>
       <c r="K246" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L246" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M246" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="247">
@@ -10565,10 +10639,10 @@
         <v>0</v>
       </c>
       <c r="D247" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E247" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F247" t="n">
         <v>0</v>
@@ -10589,10 +10663,10 @@
         <v>0</v>
       </c>
       <c r="L247" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M247" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="248">
@@ -10601,9 +10675,7 @@
           <t>藥品代理銷售及通路</t>
         </is>
       </c>
-      <c r="B248" t="n">
-        <v>0</v>
-      </c>
+      <c r="B248" t="inlineStr"/>
       <c r="C248" t="n">
         <v>0</v>
       </c>
@@ -10632,10 +10704,10 @@
         <v>0</v>
       </c>
       <c r="L248" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M248" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="249">
@@ -10646,7 +10718,7 @@
       </c>
       <c r="B249" t="inlineStr"/>
       <c r="C249" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D249" t="n">
         <v>0</v>
@@ -10685,9 +10757,7 @@
           <t>虛擬化軟體</t>
         </is>
       </c>
-      <c r="B250" t="n">
-        <v>0</v>
-      </c>
+      <c r="B250" t="inlineStr"/>
       <c r="C250" t="n">
         <v>1</v>
       </c>
@@ -10695,7 +10765,7 @@
         <v>1</v>
       </c>
       <c r="E250" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F250" t="n">
         <v>0</v>
@@ -10771,16 +10841,16 @@
       </c>
       <c r="B252" t="inlineStr"/>
       <c r="C252" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D252" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E252" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F252" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G252" t="n">
         <v>0</v>
@@ -10795,13 +10865,13 @@
         <v>0</v>
       </c>
       <c r="K252" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L252" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M252" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="253">
@@ -10903,10 +10973,10 @@
         <v>0</v>
       </c>
       <c r="F255" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G255" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H255" t="n">
         <v>0</v>
@@ -10959,13 +11029,13 @@
         <v>0</v>
       </c>
       <c r="K256" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L256" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M256" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="257">
@@ -10974,7 +11044,9 @@
           <t>裝置/器材零組件</t>
         </is>
       </c>
-      <c r="B257" t="inlineStr"/>
+      <c r="B257" t="n">
+        <v>0</v>
+      </c>
       <c r="C257" t="n">
         <v>0</v>
       </c>
@@ -11015,40 +11087,20 @@
           <t>裝置/器材顯示器</t>
         </is>
       </c>
-      <c r="B258" t="inlineStr"/>
-      <c r="C258" t="n">
-        <v>0</v>
-      </c>
-      <c r="D258" t="n">
-        <v>0</v>
-      </c>
-      <c r="E258" t="n">
-        <v>0</v>
-      </c>
-      <c r="F258" t="n">
-        <v>0</v>
-      </c>
-      <c r="G258" t="n">
-        <v>0</v>
-      </c>
-      <c r="H258" t="n">
-        <v>0</v>
-      </c>
-      <c r="I258" t="n">
-        <v>0</v>
-      </c>
-      <c r="J258" t="n">
-        <v>0</v>
-      </c>
-      <c r="K258" t="n">
-        <v>0</v>
-      </c>
-      <c r="L258" t="n">
-        <v>0</v>
-      </c>
-      <c r="M258" t="n">
-        <v>0</v>
-      </c>
+      <c r="B258" t="n">
+        <v>0</v>
+      </c>
+      <c r="C258" t="inlineStr"/>
+      <c r="D258" t="inlineStr"/>
+      <c r="E258" t="inlineStr"/>
+      <c r="F258" t="inlineStr"/>
+      <c r="G258" t="inlineStr"/>
+      <c r="H258" t="inlineStr"/>
+      <c r="I258" t="inlineStr"/>
+      <c r="J258" t="inlineStr"/>
+      <c r="K258" t="inlineStr"/>
+      <c r="L258" t="inlineStr"/>
+      <c r="M258" t="inlineStr"/>
     </row>
     <row r="259">
       <c r="A259" s="1" t="inlineStr">
@@ -11058,13 +11110,13 @@
       </c>
       <c r="B259" t="inlineStr"/>
       <c r="C259" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D259" t="n">
         <v>1</v>
       </c>
       <c r="E259" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F259" t="n">
         <v>0</v>
@@ -11138,9 +11190,11 @@
           <t>觸控面板</t>
         </is>
       </c>
-      <c r="B261" t="inlineStr"/>
+      <c r="B261" t="n">
+        <v>0</v>
+      </c>
       <c r="C261" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D261" t="n">
         <v>0</v>
@@ -11170,7 +11224,7 @@
         <v>0</v>
       </c>
       <c r="M261" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="262">
@@ -11181,19 +11235,19 @@
       </c>
       <c r="B262" t="inlineStr"/>
       <c r="C262" t="n">
+        <v>4</v>
+      </c>
+      <c r="D262" t="n">
+        <v>3</v>
+      </c>
+      <c r="E262" t="n">
+        <v>0</v>
+      </c>
+      <c r="F262" t="n">
         <v>2</v>
       </c>
-      <c r="D262" t="n">
-        <v>4</v>
-      </c>
-      <c r="E262" t="n">
-        <v>3</v>
-      </c>
-      <c r="F262" t="n">
-        <v>0</v>
-      </c>
       <c r="G262" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H262" t="n">
         <v>0</v>
@@ -11208,7 +11262,7 @@
         <v>0</v>
       </c>
       <c r="L262" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M262" t="n">
         <v>1</v>
@@ -11225,10 +11279,10 @@
         <v>1</v>
       </c>
       <c r="D263" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E263" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F263" t="n">
         <v>0</v>
@@ -11237,13 +11291,13 @@
         <v>0</v>
       </c>
       <c r="H263" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I263" t="n">
         <v>1</v>
       </c>
       <c r="J263" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K263" t="n">
         <v>0</v>
@@ -11263,16 +11317,16 @@
       </c>
       <c r="B264" t="inlineStr"/>
       <c r="C264" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D264" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E264" t="n">
         <v>1</v>
       </c>
       <c r="F264" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G264" t="n">
         <v>0</v>
@@ -11281,19 +11335,19 @@
         <v>0</v>
       </c>
       <c r="I264" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J264" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K264" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L264" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M264" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="265">
@@ -11343,7 +11397,9 @@
           <t>證券業</t>
         </is>
       </c>
-      <c r="B266" t="inlineStr"/>
+      <c r="B266" t="n">
+        <v>0</v>
+      </c>
       <c r="C266" t="n">
         <v>0</v>
       </c>
@@ -11401,10 +11457,10 @@
         <v>0</v>
       </c>
       <c r="H267" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I267" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J267" t="n">
         <v>0</v>
@@ -11466,7 +11522,9 @@
           <t>貨櫃運輸集散及倉儲</t>
         </is>
       </c>
-      <c r="B269" t="inlineStr"/>
+      <c r="B269" t="n">
+        <v>0</v>
+      </c>
       <c r="C269" t="n">
         <v>0</v>
       </c>
@@ -11495,7 +11553,7 @@
         <v>0</v>
       </c>
       <c r="L269" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M269" t="n">
         <v>1</v>
@@ -11515,10 +11573,10 @@
         <v>0</v>
       </c>
       <c r="E270" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F270" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G270" t="n">
         <v>0</v>
@@ -11527,19 +11585,19 @@
         <v>0</v>
       </c>
       <c r="I270" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J270" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K270" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L270" t="n">
         <v>1</v>
       </c>
       <c r="M270" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="271">
@@ -11591,19 +11649,19 @@
       </c>
       <c r="B272" t="inlineStr"/>
       <c r="C272" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D272" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E272" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F272" t="n">
         <v>1</v>
       </c>
       <c r="G272" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H272" t="n">
         <v>0</v>
@@ -11615,13 +11673,13 @@
         <v>0</v>
       </c>
       <c r="K272" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L272" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M272" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="273">
@@ -11630,20 +11688,18 @@
           <t>資安營運管理服務</t>
         </is>
       </c>
-      <c r="B273" t="n">
-        <v>0</v>
-      </c>
+      <c r="B273" t="inlineStr"/>
       <c r="C273" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D273" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E273" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F273" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G273" t="n">
         <v>0</v>
@@ -11658,13 +11714,13 @@
         <v>0</v>
       </c>
       <c r="K273" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L273" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M273" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="274">
@@ -11673,23 +11729,21 @@
           <t>資安防護能力分析與鑑識服務</t>
         </is>
       </c>
-      <c r="B274" t="n">
-        <v>0</v>
-      </c>
+      <c r="B274" t="inlineStr"/>
       <c r="C274" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D274" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E274" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F274" t="n">
         <v>1</v>
       </c>
       <c r="G274" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H274" t="n">
         <v>0</v>
@@ -11701,13 +11755,13 @@
         <v>0</v>
       </c>
       <c r="K274" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L274" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M274" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="275">
@@ -11718,16 +11772,16 @@
       </c>
       <c r="B275" t="inlineStr"/>
       <c r="C275" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D275" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E275" t="n">
         <v>1</v>
       </c>
       <c r="F275" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G275" t="n">
         <v>0</v>
@@ -11742,13 +11796,13 @@
         <v>0</v>
       </c>
       <c r="K275" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L275" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M275" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="276">
@@ -11757,23 +11811,21 @@
           <t>資安顧問服務</t>
         </is>
       </c>
-      <c r="B276" t="n">
-        <v>0</v>
-      </c>
+      <c r="B276" t="inlineStr"/>
       <c r="C276" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D276" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E276" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F276" t="n">
         <v>1</v>
       </c>
       <c r="G276" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H276" t="n">
         <v>0</v>
@@ -11785,13 +11837,13 @@
         <v>0</v>
       </c>
       <c r="K276" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L276" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M276" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="277">
@@ -11841,11 +11893,9 @@
           <t>資料安全</t>
         </is>
       </c>
-      <c r="B278" t="n">
-        <v>0</v>
-      </c>
+      <c r="B278" t="inlineStr"/>
       <c r="C278" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D278" t="n">
         <v>1</v>
@@ -11854,7 +11904,7 @@
         <v>1</v>
       </c>
       <c r="F278" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G278" t="n">
         <v>0</v>
@@ -11869,13 +11919,13 @@
         <v>0</v>
       </c>
       <c r="K278" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L278" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M278" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="279">
@@ -11884,7 +11934,9 @@
           <t>資料庫</t>
         </is>
       </c>
-      <c r="B279" t="inlineStr"/>
+      <c r="B279" t="n">
+        <v>0</v>
+      </c>
       <c r="C279" t="n">
         <v>1</v>
       </c>
@@ -11892,7 +11944,7 @@
         <v>1</v>
       </c>
       <c r="E279" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F279" t="n">
         <v>0</v>
@@ -11970,19 +12022,19 @@
         <v>0</v>
       </c>
       <c r="C281" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D281" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E281" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F281" t="n">
         <v>1</v>
       </c>
       <c r="G281" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H281" t="n">
         <v>0</v>
@@ -11994,13 +12046,13 @@
         <v>0</v>
       </c>
       <c r="K281" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L281" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M281" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="282">
@@ -12041,7 +12093,7 @@
         <v>0</v>
       </c>
       <c r="M282" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="283">
@@ -12216,7 +12268,7 @@
       </c>
       <c r="B287" t="inlineStr"/>
       <c r="C287" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D287" t="n">
         <v>1</v>
@@ -12225,7 +12277,7 @@
         <v>1</v>
       </c>
       <c r="F287" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G287" t="n">
         <v>0</v>
@@ -12240,13 +12292,13 @@
         <v>0</v>
       </c>
       <c r="K287" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L287" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M287" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="288">
@@ -12259,7 +12311,7 @@
         <v>0</v>
       </c>
       <c r="C288" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D288" t="n">
         <v>0</v>
@@ -12298,11 +12350,9 @@
           <t>車用機械傳動設備及零配件</t>
         </is>
       </c>
-      <c r="B289" t="n">
-        <v>0</v>
-      </c>
+      <c r="B289" t="inlineStr"/>
       <c r="C289" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D289" t="n">
         <v>0</v>
@@ -12320,10 +12370,10 @@
         <v>0</v>
       </c>
       <c r="I289" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J289" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K289" t="n">
         <v>0</v>
@@ -12425,10 +12475,10 @@
       </c>
       <c r="B292" t="inlineStr"/>
       <c r="C292" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D292" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E292" t="n">
         <v>0</v>
@@ -12510,7 +12560,7 @@
         <v>1</v>
       </c>
       <c r="D294" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E294" t="n">
         <v>0</v>
@@ -12546,7 +12596,9 @@
           <t>輸送機械及零配件</t>
         </is>
       </c>
-      <c r="B295" t="inlineStr"/>
+      <c r="B295" t="n">
+        <v>0</v>
+      </c>
       <c r="C295" t="n">
         <v>0</v>
       </c>
@@ -12566,10 +12618,10 @@
         <v>0</v>
       </c>
       <c r="I295" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J295" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K295" t="n">
         <v>0</v>
@@ -12587,15 +12639,17 @@
           <t>農業科技業</t>
         </is>
       </c>
-      <c r="B296" t="inlineStr"/>
+      <c r="B296" t="n">
+        <v>0</v>
+      </c>
       <c r="C296" t="n">
         <v>0</v>
       </c>
       <c r="D296" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E296" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F296" t="n">
         <v>0</v>
@@ -12616,7 +12670,7 @@
         <v>0</v>
       </c>
       <c r="L296" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M296" t="n">
         <v>1</v>
@@ -12669,7 +12723,9 @@
           <t>近眼顯示(Dear-Eye Display)</t>
         </is>
       </c>
-      <c r="B298" t="inlineStr"/>
+      <c r="B298" t="n">
+        <v>0</v>
+      </c>
       <c r="C298" t="n">
         <v>0</v>
       </c>
@@ -12698,7 +12754,7 @@
         <v>0</v>
       </c>
       <c r="L298" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M298" t="n">
         <v>1</v>
@@ -12797,13 +12853,13 @@
         <v>1</v>
       </c>
       <c r="D301" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E301" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F301" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G301" t="n">
         <v>0</v>
@@ -12818,13 +12874,13 @@
         <v>0</v>
       </c>
       <c r="K301" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L301" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M301" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="302">
@@ -12837,37 +12893,37 @@
         <v>0</v>
       </c>
       <c r="C302" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D302" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E302" t="n">
+        <v>1</v>
+      </c>
+      <c r="F302" t="n">
         <v>2</v>
       </c>
-      <c r="F302" t="n">
-        <v>1</v>
-      </c>
       <c r="G302" t="n">
+        <v>0</v>
+      </c>
+      <c r="H302" t="n">
+        <v>0</v>
+      </c>
+      <c r="I302" t="n">
+        <v>1</v>
+      </c>
+      <c r="J302" t="n">
+        <v>0</v>
+      </c>
+      <c r="K302" t="n">
         <v>2</v>
-      </c>
-      <c r="H302" t="n">
-        <v>0</v>
-      </c>
-      <c r="I302" t="n">
-        <v>0</v>
-      </c>
-      <c r="J302" t="n">
-        <v>1</v>
-      </c>
-      <c r="K302" t="n">
-        <v>0</v>
       </c>
       <c r="L302" t="n">
         <v>2</v>
       </c>
       <c r="M302" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="303">
@@ -12876,39 +12932,41 @@
           <t>連接線</t>
         </is>
       </c>
-      <c r="B303" t="inlineStr"/>
+      <c r="B303" t="n">
+        <v>0</v>
+      </c>
       <c r="C303" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D303" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E303" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F303" t="n">
         <v>1</v>
       </c>
       <c r="G303" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H303" t="n">
         <v>0</v>
       </c>
       <c r="I303" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J303" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K303" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L303" t="n">
         <v>1</v>
       </c>
       <c r="M303" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="304">
@@ -13040,7 +13098,9 @@
           <t>運算元件與設備</t>
         </is>
       </c>
-      <c r="B307" t="inlineStr"/>
+      <c r="B307" t="n">
+        <v>0</v>
+      </c>
       <c r="C307" t="n">
         <v>1</v>
       </c>
@@ -13048,7 +13108,7 @@
         <v>1</v>
       </c>
       <c r="E307" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F307" t="n">
         <v>0</v>
@@ -13060,10 +13120,10 @@
         <v>0</v>
       </c>
       <c r="I307" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J307" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K307" t="n">
         <v>0</v>
@@ -13081,9 +13141,11 @@
           <t>運算設備</t>
         </is>
       </c>
-      <c r="B308" t="inlineStr"/>
+      <c r="B308" t="n">
+        <v>0</v>
+      </c>
       <c r="C308" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D308" t="n">
         <v>0</v>
@@ -13101,10 +13163,10 @@
         <v>0</v>
       </c>
       <c r="I308" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J308" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K308" t="n">
         <v>0</v>
@@ -13113,7 +13175,7 @@
         <v>0</v>
       </c>
       <c r="M308" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="309">
@@ -13163,15 +13225,17 @@
           <t>配電管理設施</t>
         </is>
       </c>
-      <c r="B310" t="inlineStr"/>
+      <c r="B310" t="n">
+        <v>0</v>
+      </c>
       <c r="C310" t="n">
         <v>0</v>
       </c>
       <c r="D310" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E310" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F310" t="n">
         <v>0</v>
@@ -13180,13 +13244,13 @@
         <v>0</v>
       </c>
       <c r="H310" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I310" t="n">
         <v>1</v>
       </c>
       <c r="J310" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K310" t="n">
         <v>0</v>
@@ -13221,10 +13285,10 @@
         <v>0</v>
       </c>
       <c r="H311" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I311" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J311" t="n">
         <v>0</v>
@@ -13247,13 +13311,13 @@
       </c>
       <c r="B312" t="inlineStr"/>
       <c r="C312" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D312" t="n">
         <v>1</v>
       </c>
       <c r="E312" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F312" t="n">
         <v>0</v>
@@ -13286,9 +13350,7 @@
           <t>醫療器材代理銷售及通路</t>
         </is>
       </c>
-      <c r="B313" t="n">
-        <v>0</v>
-      </c>
+      <c r="B313" t="inlineStr"/>
       <c r="C313" t="n">
         <v>1</v>
       </c>
@@ -13296,7 +13358,7 @@
         <v>1</v>
       </c>
       <c r="E313" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F313" t="n">
         <v>0</v>
@@ -13308,19 +13370,19 @@
         <v>0</v>
       </c>
       <c r="I313" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J313" t="n">
+        <v>1</v>
+      </c>
+      <c r="K313" t="n">
+        <v>0</v>
+      </c>
+      <c r="L313" t="n">
         <v>2</v>
       </c>
-      <c r="K313" t="n">
-        <v>1</v>
-      </c>
-      <c r="L313" t="n">
-        <v>0</v>
-      </c>
       <c r="M313" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="314">
@@ -13329,41 +13391,39 @@
           <t>醫療器材研發、設計、製造</t>
         </is>
       </c>
-      <c r="B314" t="n">
-        <v>0</v>
-      </c>
+      <c r="B314" t="inlineStr"/>
       <c r="C314" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D314" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E314" t="n">
         <v>0</v>
       </c>
       <c r="F314" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G314" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H314" t="n">
         <v>0</v>
       </c>
       <c r="I314" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J314" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K314" t="n">
         <v>0</v>
       </c>
       <c r="L314" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M314" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="315">
@@ -13401,10 +13461,10 @@
         <v>0</v>
       </c>
       <c r="L315" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M315" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="316">
@@ -13413,18 +13473,20 @@
           <t>金屬、塑膠模具</t>
         </is>
       </c>
-      <c r="B316" t="inlineStr"/>
+      <c r="B316" t="n">
+        <v>0</v>
+      </c>
       <c r="C316" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D316" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E316" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F316" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G316" t="n">
         <v>0</v>
@@ -13439,10 +13501,10 @@
         <v>0</v>
       </c>
       <c r="K316" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L316" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M316" t="n">
         <v>0</v>
@@ -13486,7 +13548,7 @@
         <v>0</v>
       </c>
       <c r="M317" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="318">
@@ -13506,10 +13568,10 @@
         <v>0</v>
       </c>
       <c r="F318" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G318" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H318" t="n">
         <v>0</v>
@@ -13527,7 +13589,7 @@
         <v>0</v>
       </c>
       <c r="M318" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="319">
@@ -13536,7 +13598,9 @@
           <t>金屬材料</t>
         </is>
       </c>
-      <c r="B319" t="inlineStr"/>
+      <c r="B319" t="n">
+        <v>0</v>
+      </c>
       <c r="C319" t="n">
         <v>0</v>
       </c>
@@ -13618,7 +13682,9 @@
           <t>金控業/銀行業/保險業</t>
         </is>
       </c>
-      <c r="B321" t="inlineStr"/>
+      <c r="B321" t="n">
+        <v>0</v>
+      </c>
       <c r="C321" t="n">
         <v>0</v>
       </c>
@@ -13732,7 +13798,7 @@
         <v>0</v>
       </c>
       <c r="M323" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="324">
@@ -13790,7 +13856,7 @@
         <v>1</v>
       </c>
       <c r="E325" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F325" t="n">
         <v>0</v>
@@ -13802,10 +13868,10 @@
         <v>0</v>
       </c>
       <c r="I325" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J325" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K325" t="n">
         <v>0</v>
@@ -13823,39 +13889,41 @@
           <t>銅箔基板</t>
         </is>
       </c>
-      <c r="B326" t="inlineStr"/>
+      <c r="B326" t="n">
+        <v>0</v>
+      </c>
       <c r="C326" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D326" t="n">
+        <v>1</v>
+      </c>
+      <c r="E326" t="n">
+        <v>0</v>
+      </c>
+      <c r="F326" t="n">
+        <v>0</v>
+      </c>
+      <c r="G326" t="n">
+        <v>0</v>
+      </c>
+      <c r="H326" t="n">
+        <v>0</v>
+      </c>
+      <c r="I326" t="n">
+        <v>5</v>
+      </c>
+      <c r="J326" t="n">
+        <v>0</v>
+      </c>
+      <c r="K326" t="n">
+        <v>2</v>
+      </c>
+      <c r="L326" t="n">
         <v>4</v>
       </c>
-      <c r="E326" t="n">
-        <v>1</v>
-      </c>
-      <c r="F326" t="n">
-        <v>0</v>
-      </c>
-      <c r="G326" t="n">
-        <v>0</v>
-      </c>
-      <c r="H326" t="n">
-        <v>0</v>
-      </c>
-      <c r="I326" t="n">
-        <v>0</v>
-      </c>
-      <c r="J326" t="n">
-        <v>5</v>
-      </c>
-      <c r="K326" t="n">
-        <v>0</v>
-      </c>
-      <c r="L326" t="n">
-        <v>2</v>
-      </c>
       <c r="M326" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="327">
@@ -13872,10 +13940,10 @@
         <v>0</v>
       </c>
       <c r="E327" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F327" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G327" t="n">
         <v>0</v>
@@ -13951,25 +14019,25 @@
         <v>0</v>
       </c>
       <c r="D329" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E329" t="n">
         <v>1</v>
       </c>
       <c r="F329" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G329" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H329" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I329" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J329" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K329" t="n">
         <v>0</v>
@@ -14074,10 +14142,10 @@
         <v>0</v>
       </c>
       <c r="D332" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E332" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F332" t="n">
         <v>0</v>
@@ -14162,10 +14230,10 @@
         <v>0</v>
       </c>
       <c r="F334" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G334" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H334" t="n">
         <v>0</v>
@@ -14235,10 +14303,10 @@
       </c>
       <c r="B336" t="inlineStr"/>
       <c r="C336" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D336" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E336" t="n">
         <v>0</v>
@@ -14276,13 +14344,13 @@
       </c>
       <c r="B337" t="inlineStr"/>
       <c r="C337" t="n">
+        <v>3</v>
+      </c>
+      <c r="D337" t="n">
         <v>2</v>
       </c>
-      <c r="D337" t="n">
-        <v>3</v>
-      </c>
       <c r="E337" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F337" t="n">
         <v>0</v>
@@ -14303,10 +14371,10 @@
         <v>0</v>
       </c>
       <c r="L337" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M337" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="338">
@@ -14323,7 +14391,7 @@
         <v>1</v>
       </c>
       <c r="E338" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F338" t="n">
         <v>0</v>
@@ -14358,10 +14426,10 @@
       </c>
       <c r="B339" t="inlineStr"/>
       <c r="C339" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D339" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E339" t="n">
         <v>1</v>
@@ -14370,7 +14438,7 @@
         <v>1</v>
       </c>
       <c r="G339" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H339" t="n">
         <v>0</v>
@@ -14382,13 +14450,13 @@
         <v>0</v>
       </c>
       <c r="K339" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L339" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M339" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="340">
@@ -14401,16 +14469,16 @@
         <v>0</v>
       </c>
       <c r="C340" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D340" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E340" t="n">
         <v>1</v>
       </c>
       <c r="F340" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G340" t="n">
         <v>0</v>
@@ -14425,13 +14493,13 @@
         <v>0</v>
       </c>
       <c r="K340" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L340" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M340" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="341">
@@ -14440,20 +14508,18 @@
           <t>雲端應用服務</t>
         </is>
       </c>
-      <c r="B341" t="n">
-        <v>0</v>
-      </c>
+      <c r="B341" t="inlineStr"/>
       <c r="C341" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D341" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E341" t="n">
         <v>1</v>
       </c>
       <c r="F341" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G341" t="n">
         <v>0</v>
@@ -14462,19 +14528,19 @@
         <v>0</v>
       </c>
       <c r="I341" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J341" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K341" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L341" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M341" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="342">
@@ -14497,22 +14563,22 @@
         <v>0</v>
       </c>
       <c r="G342" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H342" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I342" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J342" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K342" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L342" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M342" t="n">
         <v>0</v>
@@ -14526,37 +14592,37 @@
       </c>
       <c r="B343" t="inlineStr"/>
       <c r="C343" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D343" t="n">
+        <v>0</v>
+      </c>
+      <c r="E343" t="n">
+        <v>0</v>
+      </c>
+      <c r="F343" t="n">
+        <v>0</v>
+      </c>
+      <c r="G343" t="n">
+        <v>0</v>
+      </c>
+      <c r="H343" t="n">
+        <v>0</v>
+      </c>
+      <c r="I343" t="n">
+        <v>1</v>
+      </c>
+      <c r="J343" t="n">
+        <v>0</v>
+      </c>
+      <c r="K343" t="n">
+        <v>1</v>
+      </c>
+      <c r="L343" t="n">
         <v>2</v>
       </c>
-      <c r="E343" t="n">
-        <v>0</v>
-      </c>
-      <c r="F343" t="n">
-        <v>0</v>
-      </c>
-      <c r="G343" t="n">
-        <v>0</v>
-      </c>
-      <c r="H343" t="n">
-        <v>0</v>
-      </c>
-      <c r="I343" t="n">
-        <v>0</v>
-      </c>
-      <c r="J343" t="n">
-        <v>1</v>
-      </c>
-      <c r="K343" t="n">
-        <v>0</v>
-      </c>
-      <c r="L343" t="n">
-        <v>1</v>
-      </c>
       <c r="M343" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="344">
@@ -14570,10 +14636,10 @@
         <v>0</v>
       </c>
       <c r="D344" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E344" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F344" t="n">
         <v>0</v>
@@ -14623,13 +14689,13 @@
         <v>0</v>
       </c>
       <c r="H345" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I345" t="n">
         <v>1</v>
       </c>
       <c r="J345" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K345" t="n">
         <v>0</v>
@@ -14647,15 +14713,17 @@
           <t>電力設備</t>
         </is>
       </c>
-      <c r="B346" t="inlineStr"/>
+      <c r="B346" t="n">
+        <v>0</v>
+      </c>
       <c r="C346" t="n">
         <v>0</v>
       </c>
       <c r="D346" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E346" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F346" t="n">
         <v>0</v>
@@ -14664,13 +14732,13 @@
         <v>0</v>
       </c>
       <c r="H346" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I346" t="n">
         <v>1</v>
       </c>
       <c r="J346" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K346" t="n">
         <v>0</v>
@@ -14679,7 +14747,7 @@
         <v>0</v>
       </c>
       <c r="M346" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="347">
@@ -14720,7 +14788,7 @@
         <v>0</v>
       </c>
       <c r="M347" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="348">
@@ -14737,10 +14805,10 @@
         <v>0</v>
       </c>
       <c r="E348" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F348" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G348" t="n">
         <v>0</v>
@@ -14749,10 +14817,10 @@
         <v>0</v>
       </c>
       <c r="I348" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J348" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K348" t="n">
         <v>0</v>
@@ -14761,7 +14829,7 @@
         <v>0</v>
       </c>
       <c r="M348" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="349">
@@ -14790,10 +14858,10 @@
         <v>0</v>
       </c>
       <c r="I349" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J349" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K349" t="n">
         <v>0</v>
@@ -14852,9 +14920,11 @@
           <t>電子零組件、塑膠零件、五金零件</t>
         </is>
       </c>
-      <c r="B351" t="inlineStr"/>
+      <c r="B351" t="n">
+        <v>0</v>
+      </c>
       <c r="C351" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D351" t="n">
         <v>1</v>
@@ -14866,25 +14936,25 @@
         <v>1</v>
       </c>
       <c r="G351" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H351" t="n">
         <v>0</v>
       </c>
       <c r="I351" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J351" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K351" t="n">
         <v>0</v>
       </c>
       <c r="L351" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M351" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="352">
@@ -14895,37 +14965,37 @@
       </c>
       <c r="B352" t="inlineStr"/>
       <c r="C352" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D352" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E352" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="F352" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G352" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H352" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I352" t="n">
         <v>3</v>
       </c>
       <c r="J352" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K352" t="n">
         <v>2</v>
       </c>
       <c r="L352" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M352" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="353">
@@ -14939,10 +15009,10 @@
         <v>1</v>
       </c>
       <c r="D353" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E353" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F353" t="n">
         <v>0</v>
@@ -14951,10 +15021,10 @@
         <v>0</v>
       </c>
       <c r="H353" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I353" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J353" t="n">
         <v>0</v>
@@ -14977,28 +15047,28 @@
       </c>
       <c r="B354" t="inlineStr"/>
       <c r="C354" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D354" t="n">
+        <v>3</v>
+      </c>
+      <c r="E354" t="n">
         <v>2</v>
       </c>
-      <c r="E354" t="n">
-        <v>3</v>
-      </c>
       <c r="F354" t="n">
+        <v>0</v>
+      </c>
+      <c r="G354" t="n">
+        <v>0</v>
+      </c>
+      <c r="H354" t="n">
         <v>2</v>
       </c>
-      <c r="G354" t="n">
-        <v>0</v>
-      </c>
-      <c r="H354" t="n">
-        <v>0</v>
-      </c>
       <c r="I354" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J354" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K354" t="n">
         <v>0</v>
@@ -15016,18 +15086,20 @@
           <t>電感器材料(如鐵氧體、導電漿墨)</t>
         </is>
       </c>
-      <c r="B355" t="inlineStr"/>
+      <c r="B355" t="n">
+        <v>0</v>
+      </c>
       <c r="C355" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D355" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E355" t="n">
         <v>1</v>
       </c>
       <c r="F355" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G355" t="n">
         <v>0</v>
@@ -15057,30 +15129,32 @@
           <t>電控元件</t>
         </is>
       </c>
-      <c r="B356" t="inlineStr"/>
+      <c r="B356" t="n">
+        <v>0</v>
+      </c>
       <c r="C356" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D356" t="n">
+        <v>1</v>
+      </c>
+      <c r="E356" t="n">
+        <v>0</v>
+      </c>
+      <c r="F356" t="n">
+        <v>0</v>
+      </c>
+      <c r="G356" t="n">
+        <v>0</v>
+      </c>
+      <c r="H356" t="n">
+        <v>0</v>
+      </c>
+      <c r="I356" t="n">
         <v>2</v>
       </c>
-      <c r="E356" t="n">
-        <v>1</v>
-      </c>
-      <c r="F356" t="n">
-        <v>0</v>
-      </c>
-      <c r="G356" t="n">
-        <v>0</v>
-      </c>
-      <c r="H356" t="n">
-        <v>0</v>
-      </c>
-      <c r="I356" t="n">
-        <v>0</v>
-      </c>
       <c r="J356" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K356" t="n">
         <v>0</v>
@@ -15103,7 +15177,7 @@
         <v>1</v>
       </c>
       <c r="D357" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E357" t="n">
         <v>0</v>
@@ -15118,10 +15192,10 @@
         <v>0</v>
       </c>
       <c r="I357" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J357" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K357" t="n">
         <v>0</v>
@@ -15130,7 +15204,7 @@
         <v>0</v>
       </c>
       <c r="M357" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="358">
@@ -15139,7 +15213,9 @@
           <t>電池模組</t>
         </is>
       </c>
-      <c r="B358" t="inlineStr"/>
+      <c r="B358" t="n">
+        <v>0</v>
+      </c>
       <c r="C358" t="n">
         <v>0</v>
       </c>
@@ -15153,16 +15229,16 @@
         <v>0</v>
       </c>
       <c r="G358" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H358" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I358" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J358" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K358" t="n">
         <v>0</v>
@@ -15171,7 +15247,7 @@
         <v>0</v>
       </c>
       <c r="M358" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="359">
@@ -15194,16 +15270,16 @@
         <v>0</v>
       </c>
       <c r="G359" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H359" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I359" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J359" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K359" t="n">
         <v>0</v>
@@ -15223,37 +15299,37 @@
       </c>
       <c r="B360" t="inlineStr"/>
       <c r="C360" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D360" t="n">
+        <v>1</v>
+      </c>
+      <c r="E360" t="n">
+        <v>1</v>
+      </c>
+      <c r="F360" t="n">
+        <v>0</v>
+      </c>
+      <c r="G360" t="n">
+        <v>0</v>
+      </c>
+      <c r="H360" t="n">
+        <v>1</v>
+      </c>
+      <c r="I360" t="n">
+        <v>1</v>
+      </c>
+      <c r="J360" t="n">
+        <v>0</v>
+      </c>
+      <c r="K360" t="n">
         <v>2</v>
-      </c>
-      <c r="E360" t="n">
-        <v>1</v>
-      </c>
-      <c r="F360" t="n">
-        <v>1</v>
-      </c>
-      <c r="G360" t="n">
-        <v>0</v>
-      </c>
-      <c r="H360" t="n">
-        <v>0</v>
-      </c>
-      <c r="I360" t="n">
-        <v>1</v>
-      </c>
-      <c r="J360" t="n">
-        <v>1</v>
-      </c>
-      <c r="K360" t="n">
-        <v>0</v>
       </c>
       <c r="L360" t="n">
         <v>2</v>
       </c>
       <c r="M360" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="361">
@@ -15279,10 +15355,10 @@
         <v>0</v>
       </c>
       <c r="H361" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I361" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J361" t="n">
         <v>0</v>
@@ -15349,10 +15425,10 @@
         <v>0</v>
       </c>
       <c r="D363" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E363" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F363" t="n">
         <v>0</v>
@@ -15385,30 +15461,32 @@
           <t>電腦視覺</t>
         </is>
       </c>
-      <c r="B364" t="inlineStr"/>
+      <c r="B364" t="n">
+        <v>0</v>
+      </c>
       <c r="C364" t="n">
         <v>1</v>
       </c>
       <c r="D364" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E364" t="n">
         <v>0</v>
       </c>
       <c r="F364" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G364" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H364" t="n">
         <v>0</v>
       </c>
       <c r="I364" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J364" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K364" t="n">
         <v>0</v>
@@ -15428,34 +15506,34 @@
       </c>
       <c r="B365" t="inlineStr"/>
       <c r="C365" t="n">
+        <v>1</v>
+      </c>
+      <c r="D365" t="n">
         <v>2</v>
       </c>
-      <c r="D365" t="n">
-        <v>1</v>
-      </c>
       <c r="E365" t="n">
+        <v>0</v>
+      </c>
+      <c r="F365" t="n">
+        <v>0</v>
+      </c>
+      <c r="G365" t="n">
+        <v>0</v>
+      </c>
+      <c r="H365" t="n">
+        <v>0</v>
+      </c>
+      <c r="I365" t="n">
         <v>2</v>
       </c>
-      <c r="F365" t="n">
-        <v>0</v>
-      </c>
-      <c r="G365" t="n">
-        <v>0</v>
-      </c>
-      <c r="H365" t="n">
-        <v>0</v>
-      </c>
-      <c r="I365" t="n">
-        <v>0</v>
-      </c>
       <c r="J365" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K365" t="n">
         <v>0</v>
       </c>
       <c r="L365" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M365" t="n">
         <v>1</v>
@@ -15508,7 +15586,9 @@
           <t>電鍍材料</t>
         </is>
       </c>
-      <c r="B367" t="inlineStr"/>
+      <c r="B367" t="n">
+        <v>0</v>
+      </c>
       <c r="C367" t="n">
         <v>0</v>
       </c>
@@ -15549,30 +15629,32 @@
           <t>電阻器</t>
         </is>
       </c>
-      <c r="B368" t="inlineStr"/>
+      <c r="B368" t="n">
+        <v>0</v>
+      </c>
       <c r="C368" t="n">
+        <v>0</v>
+      </c>
+      <c r="D368" t="n">
         <v>2</v>
       </c>
-      <c r="D368" t="n">
-        <v>0</v>
-      </c>
       <c r="E368" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F368" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G368" t="n">
         <v>0</v>
       </c>
       <c r="H368" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I368" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J368" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K368" t="n">
         <v>0</v>
@@ -15595,7 +15677,7 @@
         <v>1</v>
       </c>
       <c r="D369" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E369" t="n">
         <v>0</v>
@@ -15631,12 +15713,14 @@
           <t>面板</t>
         </is>
       </c>
-      <c r="B370" t="inlineStr"/>
+      <c r="B370" t="n">
+        <v>0</v>
+      </c>
       <c r="C370" t="n">
         <v>1</v>
       </c>
       <c r="D370" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E370" t="n">
         <v>0</v>
@@ -15651,10 +15735,10 @@
         <v>0</v>
       </c>
       <c r="I370" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J370" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K370" t="n">
         <v>0</v>
@@ -15761,7 +15845,7 @@
         <v>4</v>
       </c>
       <c r="D373" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E373" t="n">
         <v>1</v>
@@ -15770,25 +15854,25 @@
         <v>1</v>
       </c>
       <c r="G373" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H373" t="n">
         <v>0</v>
       </c>
       <c r="I373" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J373" t="n">
+        <v>1</v>
+      </c>
+      <c r="K373" t="n">
+        <v>1</v>
+      </c>
+      <c r="L373" t="n">
+        <v>1</v>
+      </c>
+      <c r="M373" t="n">
         <v>2</v>
-      </c>
-      <c r="K373" t="n">
-        <v>1</v>
-      </c>
-      <c r="L373" t="n">
-        <v>1</v>
-      </c>
-      <c r="M373" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="374">
@@ -15802,7 +15886,7 @@
         <v>1</v>
       </c>
       <c r="D374" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E374" t="n">
         <v>0</v>
@@ -15843,10 +15927,10 @@
         <v>0</v>
       </c>
       <c r="D375" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E375" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F375" t="n">
         <v>0</v>
@@ -15883,37 +15967,37 @@
         <v>0</v>
       </c>
       <c r="C376" t="n">
+        <v>4</v>
+      </c>
+      <c r="D376" t="n">
+        <v>3</v>
+      </c>
+      <c r="E376" t="n">
         <v>2</v>
       </c>
-      <c r="D376" t="n">
-        <v>4</v>
-      </c>
-      <c r="E376" t="n">
+      <c r="F376" t="n">
+        <v>0</v>
+      </c>
+      <c r="G376" t="n">
+        <v>0</v>
+      </c>
+      <c r="H376" t="n">
+        <v>1</v>
+      </c>
+      <c r="I376" t="n">
         <v>3</v>
       </c>
-      <c r="F376" t="n">
+      <c r="J376" t="n">
+        <v>0</v>
+      </c>
+      <c r="K376" t="n">
         <v>2</v>
       </c>
-      <c r="G376" t="n">
-        <v>0</v>
-      </c>
-      <c r="H376" t="n">
-        <v>0</v>
-      </c>
-      <c r="I376" t="n">
-        <v>1</v>
-      </c>
-      <c r="J376" t="n">
-        <v>3</v>
-      </c>
-      <c r="K376" t="n">
-        <v>0</v>
-      </c>
       <c r="L376" t="n">
+        <v>0</v>
+      </c>
+      <c r="M376" t="n">
         <v>2</v>
-      </c>
-      <c r="M376" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="377">
@@ -15927,7 +16011,7 @@
         <v>1</v>
       </c>
       <c r="D377" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E377" t="n">
         <v>0</v>
@@ -15968,7 +16052,7 @@
         <v>2</v>
       </c>
       <c r="D378" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E378" t="n">
         <v>0</v>
@@ -15989,10 +16073,10 @@
         <v>0</v>
       </c>
       <c r="K378" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L378" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M378" t="n">
         <v>0</v>
@@ -16033,7 +16117,7 @@
         <v>0</v>
       </c>
       <c r="L379" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M379" t="n">
         <v>1</v>
@@ -16118,7 +16202,7 @@
         <v>0</v>
       </c>
       <c r="M381" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="382">
@@ -16170,37 +16254,37 @@
       </c>
       <c r="B383" t="inlineStr"/>
       <c r="C383" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D383" t="n">
+        <v>0</v>
+      </c>
+      <c r="E383" t="n">
+        <v>0</v>
+      </c>
+      <c r="F383" t="n">
+        <v>1</v>
+      </c>
+      <c r="G383" t="n">
+        <v>0</v>
+      </c>
+      <c r="H383" t="n">
+        <v>0</v>
+      </c>
+      <c r="I383" t="n">
+        <v>0</v>
+      </c>
+      <c r="J383" t="n">
+        <v>1</v>
+      </c>
+      <c r="K383" t="n">
+        <v>0</v>
+      </c>
+      <c r="L383" t="n">
         <v>2</v>
       </c>
-      <c r="E383" t="n">
-        <v>0</v>
-      </c>
-      <c r="F383" t="n">
-        <v>0</v>
-      </c>
-      <c r="G383" t="n">
-        <v>1</v>
-      </c>
-      <c r="H383" t="n">
-        <v>0</v>
-      </c>
-      <c r="I383" t="n">
-        <v>0</v>
-      </c>
-      <c r="J383" t="n">
-        <v>0</v>
-      </c>
-      <c r="K383" t="n">
-        <v>1</v>
-      </c>
-      <c r="L383" t="n">
-        <v>0</v>
-      </c>
       <c r="M383" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="384">
@@ -16209,7 +16293,9 @@
           <t>驅動IC</t>
         </is>
       </c>
-      <c r="B384" t="inlineStr"/>
+      <c r="B384" t="n">
+        <v>0</v>
+      </c>
       <c r="C384" t="n">
         <v>0</v>
       </c>
@@ -16250,15 +16336,17 @@
           <t>高/低壓輸電設施</t>
         </is>
       </c>
-      <c r="B385" t="inlineStr"/>
+      <c r="B385" t="n">
+        <v>0</v>
+      </c>
       <c r="C385" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D385" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E385" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F385" t="n">
         <v>0</v>
@@ -16267,13 +16355,13 @@
         <v>0</v>
       </c>
       <c r="H385" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I385" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J385" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K385" t="n">
         <v>0</v>

--- a/Result/analyze_3.xlsx
+++ b/Result/analyze_3.xlsx
@@ -441,57 +441,57 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
     </row>
@@ -544,7 +544,7 @@
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -667,28 +667,28 @@
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K6" t="n">
         <v>2</v>
@@ -697,7 +697,7 @@
         <v>2</v>
       </c>
       <c r="M6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
@@ -708,37 +708,37 @@
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E7" t="n">
         <v>1</v>
       </c>
       <c r="F7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
         <v>2</v>
       </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
       <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
         <v>2</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -752,31 +752,31 @@
         <v>2</v>
       </c>
       <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="n">
         <v>2</v>
       </c>
-      <c r="E8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" t="n">
-        <v>0</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0</v>
-      </c>
       <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
         <v>2</v>
       </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
       <c r="L8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M8" t="n">
         <v>1</v>
@@ -788,41 +788,39 @@
           <t>IC設計</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>0</v>
-      </c>
+      <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
+        <v>2</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
         <v>3</v>
       </c>
-      <c r="D9" t="n">
-        <v>2</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" t="n">
-        <v>1</v>
-      </c>
-      <c r="G9" t="n">
-        <v>1</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0</v>
-      </c>
       <c r="I9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J9" t="n">
         <v>1</v>
       </c>
       <c r="K9" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L9" t="n">
         <v>4</v>
       </c>
       <c r="M9" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -831,41 +829,39 @@
           <t>IC通路</t>
         </is>
       </c>
-      <c r="B10" t="n">
-        <v>0</v>
-      </c>
+      <c r="B10" t="inlineStr"/>
       <c r="C10" t="n">
+        <v>3</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="n">
+        <v>3</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1</v>
+      </c>
+      <c r="M10" t="n">
         <v>2</v>
-      </c>
-      <c r="D10" t="n">
-        <v>3</v>
-      </c>
-      <c r="E10" t="n">
-        <v>1</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" t="n">
-        <v>3</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
-        <v>1</v>
-      </c>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -882,31 +878,31 @@
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="n">
+        <v>1</v>
+      </c>
+      <c r="K11" t="n">
         <v>2</v>
       </c>
-      <c r="G11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" t="n">
-        <v>1</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>1</v>
-      </c>
       <c r="L11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -917,10 +913,10 @@
       </c>
       <c r="B12" t="inlineStr"/>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -958,10 +954,10 @@
       </c>
       <c r="B13" t="inlineStr"/>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -1122,7 +1118,7 @@
       </c>
       <c r="B17" t="inlineStr"/>
       <c r="C17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
         <v>0</v>
@@ -1143,10 +1139,10 @@
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
@@ -1202,18 +1198,20 @@
           <t>不鏽鋼棒線</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr"/>
+      <c r="B19" t="n">
+        <v>0</v>
+      </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -1245,10 +1243,10 @@
       </c>
       <c r="B20" t="inlineStr"/>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -1284,41 +1282,39 @@
           <t>中、西藥製劑</t>
         </is>
       </c>
-      <c r="B21" t="n">
-        <v>0</v>
-      </c>
+      <c r="B21" t="inlineStr"/>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E21" t="n">
+        <v>1</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" t="n">
         <v>2</v>
       </c>
-      <c r="F21" t="n">
-        <v>1</v>
-      </c>
-      <c r="G21" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" t="n">
-        <v>1</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0</v>
-      </c>
       <c r="K21" t="n">
+        <v>1</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
         <v>2</v>
-      </c>
-      <c r="L21" t="n">
-        <v>1</v>
-      </c>
-      <c r="M21" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -1329,7 +1325,7 @@
       </c>
       <c r="B22" t="inlineStr"/>
       <c r="C22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D22" t="n">
         <v>0</v>
@@ -1373,10 +1369,10 @@
         <v>0</v>
       </c>
       <c r="D23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F23" t="n">
         <v>0</v>
@@ -1385,19 +1381,19 @@
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
         <v>0</v>
@@ -1409,14 +1405,12 @@
           <t>主/被動元件</t>
         </is>
       </c>
-      <c r="B24" t="n">
-        <v>0</v>
-      </c>
+      <c r="B24" t="inlineStr"/>
       <c r="C24" t="n">
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
@@ -1428,19 +1422,19 @@
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" t="n">
+        <v>1</v>
+      </c>
+      <c r="K24" t="n">
+        <v>3</v>
+      </c>
+      <c r="L24" t="n">
         <v>2</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" t="n">
-        <v>1</v>
-      </c>
-      <c r="L24" t="n">
-        <v>3</v>
       </c>
       <c r="M24" t="n">
         <v>2</v>
@@ -1454,7 +1448,7 @@
       </c>
       <c r="B25" t="inlineStr"/>
       <c r="C25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D25" t="n">
         <v>0</v>
@@ -1478,13 +1472,13 @@
         <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L25" t="n">
         <v>1</v>
       </c>
       <c r="M25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -1542,10 +1536,10 @@
         <v>0</v>
       </c>
       <c r="E27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
@@ -1563,10 +1557,10 @@
         <v>0</v>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -1659,10 +1653,10 @@
       </c>
       <c r="B30" t="inlineStr"/>
       <c r="C30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D30" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E30" t="n">
         <v>0</v>
@@ -1689,7 +1683,7 @@
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -1700,10 +1694,10 @@
       </c>
       <c r="B31" t="inlineStr"/>
       <c r="C31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D31" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E31" t="n">
         <v>0</v>
@@ -1727,7 +1721,7 @@
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M31" t="n">
         <v>1</v>
@@ -1741,25 +1735,25 @@
       </c>
       <c r="B32" t="inlineStr"/>
       <c r="C32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -1768,10 +1762,10 @@
         <v>0</v>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M32" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33">
@@ -1782,7 +1776,7 @@
       </c>
       <c r="B33" t="inlineStr"/>
       <c r="C33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D33" t="n">
         <v>0</v>
@@ -1809,10 +1803,10 @@
         <v>0</v>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -1885,7 +1879,7 @@
         <v>0</v>
       </c>
       <c r="J35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K35" t="n">
         <v>1</v>
@@ -1987,7 +1981,7 @@
       </c>
       <c r="B38" t="inlineStr"/>
       <c r="C38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D38" t="n">
         <v>0</v>
@@ -2049,10 +2043,10 @@
         <v>0</v>
       </c>
       <c r="J39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L39" t="n">
         <v>0</v>
@@ -2125,10 +2119,10 @@
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -2149,14 +2143,12 @@
           <t>儲存處理</t>
         </is>
       </c>
-      <c r="B42" t="n">
-        <v>0</v>
-      </c>
+      <c r="B42" t="inlineStr"/>
       <c r="C42" t="n">
         <v>1</v>
       </c>
       <c r="D42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E42" t="n">
         <v>0</v>
@@ -2168,22 +2160,22 @@
         <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="43">
@@ -2218,10 +2210,10 @@
         <v>0</v>
       </c>
       <c r="K43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M43" t="n">
         <v>0</v>
@@ -2233,14 +2225,12 @@
           <t>光學鏡片、鏡頭</t>
         </is>
       </c>
-      <c r="B44" t="n">
-        <v>0</v>
-      </c>
+      <c r="B44" t="inlineStr"/>
       <c r="C44" t="n">
         <v>1</v>
       </c>
       <c r="D44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E44" t="n">
         <v>0</v>
@@ -2249,19 +2239,19 @@
         <v>0</v>
       </c>
       <c r="G44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I44" t="n">
         <v>0</v>
       </c>
       <c r="J44" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K44" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L44" t="n">
         <v>0</v>
@@ -2302,13 +2292,13 @@
         <v>0</v>
       </c>
       <c r="K45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L45" t="n">
         <v>1</v>
       </c>
       <c r="M45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -2319,7 +2309,7 @@
       </c>
       <c r="B46" t="inlineStr"/>
       <c r="C46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D46" t="n">
         <v>0</v>
@@ -2360,7 +2350,7 @@
       </c>
       <c r="B47" t="inlineStr"/>
       <c r="C47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D47" t="n">
         <v>0</v>
@@ -2384,10 +2374,10 @@
         <v>0</v>
       </c>
       <c r="K47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M47" t="n">
         <v>0</v>
@@ -2440,35 +2430,33 @@
           <t>光通訊設備(如光纖電纜、光傳輸設備)</t>
         </is>
       </c>
-      <c r="B49" t="n">
-        <v>0</v>
-      </c>
+      <c r="B49" t="inlineStr"/>
       <c r="C49" t="n">
         <v>2</v>
       </c>
       <c r="D49" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F49" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H49" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I49" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J49" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="K49" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="L49" t="n">
         <v>3</v>
@@ -2524,14 +2512,12 @@
           <t>其他</t>
         </is>
       </c>
-      <c r="B51" t="n">
-        <v>0</v>
-      </c>
+      <c r="B51" t="inlineStr"/>
       <c r="C51" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D51" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E51" t="n">
         <v>1</v>
@@ -2543,22 +2529,22 @@
         <v>1</v>
       </c>
       <c r="H51" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I51" t="n">
+        <v>1</v>
+      </c>
+      <c r="J51" t="n">
         <v>3</v>
-      </c>
-      <c r="J51" t="n">
-        <v>1</v>
       </c>
       <c r="K51" t="n">
         <v>3</v>
       </c>
       <c r="L51" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M51" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="52">
@@ -2608,29 +2594,27 @@
           <t>其他零組件</t>
         </is>
       </c>
-      <c r="B53" t="n">
-        <v>0</v>
-      </c>
+      <c r="B53" t="inlineStr"/>
       <c r="C53" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D53" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E53" t="n">
         <v>2</v>
       </c>
       <c r="F53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G53" t="n">
+        <v>0</v>
+      </c>
+      <c r="H53" t="n">
         <v>2</v>
       </c>
-      <c r="G53" t="n">
-        <v>0</v>
-      </c>
-      <c r="H53" t="n">
-        <v>0</v>
-      </c>
       <c r="I53" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -2639,10 +2623,10 @@
         <v>0</v>
       </c>
       <c r="L53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -2651,41 +2635,39 @@
           <t>其他電子產品及電子服務產業</t>
         </is>
       </c>
-      <c r="B54" t="n">
-        <v>0</v>
-      </c>
+      <c r="B54" t="inlineStr"/>
       <c r="C54" t="n">
+        <v>3</v>
+      </c>
+      <c r="D54" t="n">
+        <v>0</v>
+      </c>
+      <c r="E54" t="n">
+        <v>1</v>
+      </c>
+      <c r="F54" t="n">
+        <v>1</v>
+      </c>
+      <c r="G54" t="n">
+        <v>1</v>
+      </c>
+      <c r="H54" t="n">
         <v>4</v>
       </c>
-      <c r="D54" t="n">
+      <c r="I54" t="n">
+        <v>0</v>
+      </c>
+      <c r="J54" t="n">
         <v>4</v>
       </c>
-      <c r="E54" t="n">
-        <v>0</v>
-      </c>
-      <c r="F54" t="n">
-        <v>1</v>
-      </c>
-      <c r="G54" t="n">
-        <v>1</v>
-      </c>
-      <c r="H54" t="n">
-        <v>1</v>
-      </c>
-      <c r="I54" t="n">
-        <v>3</v>
-      </c>
-      <c r="J54" t="n">
-        <v>0</v>
-      </c>
       <c r="K54" t="n">
+        <v>5</v>
+      </c>
+      <c r="L54" t="n">
         <v>4</v>
       </c>
-      <c r="L54" t="n">
-        <v>5</v>
-      </c>
       <c r="M54" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="55">
@@ -2696,37 +2678,37 @@
       </c>
       <c r="B55" t="inlineStr"/>
       <c r="C55" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D55" t="n">
+        <v>1</v>
+      </c>
+      <c r="E55" t="n">
+        <v>0</v>
+      </c>
+      <c r="F55" t="n">
+        <v>0</v>
+      </c>
+      <c r="G55" t="n">
+        <v>1</v>
+      </c>
+      <c r="H55" t="n">
+        <v>1</v>
+      </c>
+      <c r="I55" t="n">
+        <v>1</v>
+      </c>
+      <c r="J55" t="n">
+        <v>3</v>
+      </c>
+      <c r="K55" t="n">
+        <v>1</v>
+      </c>
+      <c r="L55" t="n">
+        <v>3</v>
+      </c>
+      <c r="M55" t="n">
         <v>2</v>
-      </c>
-      <c r="E55" t="n">
-        <v>1</v>
-      </c>
-      <c r="F55" t="n">
-        <v>0</v>
-      </c>
-      <c r="G55" t="n">
-        <v>0</v>
-      </c>
-      <c r="H55" t="n">
-        <v>1</v>
-      </c>
-      <c r="I55" t="n">
-        <v>1</v>
-      </c>
-      <c r="J55" t="n">
-        <v>1</v>
-      </c>
-      <c r="K55" t="n">
-        <v>3</v>
-      </c>
-      <c r="L55" t="n">
-        <v>1</v>
-      </c>
-      <c r="M55" t="n">
-        <v>3</v>
       </c>
     </row>
     <row r="56">
@@ -2735,32 +2717,30 @@
           <t>其他電腦及週邊設備之零組件</t>
         </is>
       </c>
-      <c r="B56" t="n">
-        <v>0</v>
-      </c>
+      <c r="B56" t="inlineStr"/>
       <c r="C56" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D56" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F56" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
       </c>
       <c r="H56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K56" t="n">
         <v>1</v>
@@ -2819,14 +2799,12 @@
           <t>冷凍空調設備及零件</t>
         </is>
       </c>
-      <c r="B58" t="n">
-        <v>0</v>
-      </c>
+      <c r="B58" t="inlineStr"/>
       <c r="C58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E58" t="n">
         <v>0</v>
@@ -2835,10 +2813,10 @@
         <v>0</v>
       </c>
       <c r="G58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I58" t="n">
         <v>0</v>
@@ -2850,10 +2828,10 @@
         <v>0</v>
       </c>
       <c r="L58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59">
@@ -2864,10 +2842,10 @@
       </c>
       <c r="B59" t="inlineStr"/>
       <c r="C59" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E59" t="n">
         <v>0</v>
@@ -2876,13 +2854,13 @@
         <v>0</v>
       </c>
       <c r="G59" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H59" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I59" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -2905,10 +2883,10 @@
       </c>
       <c r="B60" t="inlineStr"/>
       <c r="C60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E60" t="n">
         <v>0</v>
@@ -3026,14 +3004,12 @@
           <t>分析工具</t>
         </is>
       </c>
-      <c r="B63" t="n">
-        <v>0</v>
-      </c>
+      <c r="B63" t="inlineStr"/>
       <c r="C63" t="n">
         <v>1</v>
       </c>
       <c r="D63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E63" t="n">
         <v>0</v>
@@ -3060,7 +3036,7 @@
         <v>0</v>
       </c>
       <c r="M63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="64">
@@ -3194,7 +3170,7 @@
       </c>
       <c r="B67" t="inlineStr"/>
       <c r="C67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D67" t="n">
         <v>0</v>
@@ -3218,10 +3194,10 @@
         <v>0</v>
       </c>
       <c r="K67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M67" t="n">
         <v>0</v>
@@ -3235,7 +3211,7 @@
       </c>
       <c r="B68" t="inlineStr"/>
       <c r="C68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D68" t="n">
         <v>0</v>
@@ -3358,37 +3334,37 @@
       </c>
       <c r="B71" t="inlineStr"/>
       <c r="C71" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D71" t="n">
+        <v>0</v>
+      </c>
+      <c r="E71" t="n">
+        <v>1</v>
+      </c>
+      <c r="F71" t="n">
+        <v>0</v>
+      </c>
+      <c r="G71" t="n">
+        <v>0</v>
+      </c>
+      <c r="H71" t="n">
+        <v>0</v>
+      </c>
+      <c r="I71" t="n">
+        <v>0</v>
+      </c>
+      <c r="J71" t="n">
+        <v>1</v>
+      </c>
+      <c r="K71" t="n">
         <v>2</v>
       </c>
-      <c r="E71" t="n">
-        <v>0</v>
-      </c>
-      <c r="F71" t="n">
-        <v>1</v>
-      </c>
-      <c r="G71" t="n">
-        <v>0</v>
-      </c>
-      <c r="H71" t="n">
-        <v>0</v>
-      </c>
-      <c r="I71" t="n">
-        <v>0</v>
-      </c>
-      <c r="J71" t="n">
-        <v>0</v>
-      </c>
-      <c r="K71" t="n">
-        <v>1</v>
-      </c>
       <c r="L71" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="72">
@@ -3399,34 +3375,34 @@
       </c>
       <c r="B72" t="inlineStr"/>
       <c r="C72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
       </c>
       <c r="H72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K72" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L72" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M72" t="n">
         <v>1</v>
@@ -3455,10 +3431,10 @@
         <v>0</v>
       </c>
       <c r="H73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I73" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -3470,7 +3446,7 @@
         <v>0</v>
       </c>
       <c r="M73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="74">
@@ -3525,7 +3501,7 @@
         <v>1</v>
       </c>
       <c r="D75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E75" t="n">
         <v>0</v>
@@ -3563,7 +3539,7 @@
       </c>
       <c r="B76" t="inlineStr"/>
       <c r="C76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D76" t="n">
         <v>0</v>
@@ -3587,13 +3563,13 @@
         <v>0</v>
       </c>
       <c r="K76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L76" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M76" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="77">
@@ -3628,10 +3604,10 @@
         <v>0</v>
       </c>
       <c r="K77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L77" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M77" t="n">
         <v>0</v>
@@ -3645,37 +3621,37 @@
       </c>
       <c r="B78" t="inlineStr"/>
       <c r="C78" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D78" t="n">
+        <v>1</v>
+      </c>
+      <c r="E78" t="n">
         <v>2</v>
-      </c>
-      <c r="E78" t="n">
-        <v>1</v>
       </c>
       <c r="F78" t="n">
         <v>2</v>
       </c>
       <c r="G78" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H78" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I78" t="n">
         <v>0</v>
       </c>
       <c r="J78" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K78" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L78" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M78" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="79">
@@ -3727,7 +3703,7 @@
       </c>
       <c r="B80" t="inlineStr"/>
       <c r="C80" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D80" t="n">
         <v>0</v>
@@ -3792,13 +3768,13 @@
         <v>0</v>
       </c>
       <c r="K81" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L81" t="n">
         <v>1</v>
       </c>
       <c r="M81" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="82">
@@ -3807,14 +3783,12 @@
           <t>基板</t>
         </is>
       </c>
-      <c r="B82" t="n">
-        <v>0</v>
-      </c>
+      <c r="B82" t="inlineStr"/>
       <c r="C82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E82" t="n">
         <v>0</v>
@@ -3850,38 +3824,36 @@
           <t>基板組裝加工及相關製造</t>
         </is>
       </c>
-      <c r="B83" t="n">
-        <v>0</v>
-      </c>
+      <c r="B83" t="inlineStr"/>
       <c r="C83" t="n">
+        <v>1</v>
+      </c>
+      <c r="D83" t="n">
+        <v>0</v>
+      </c>
+      <c r="E83" t="n">
+        <v>1</v>
+      </c>
+      <c r="F83" t="n">
+        <v>0</v>
+      </c>
+      <c r="G83" t="n">
+        <v>0</v>
+      </c>
+      <c r="H83" t="n">
         <v>2</v>
       </c>
-      <c r="D83" t="n">
-        <v>1</v>
-      </c>
-      <c r="E83" t="n">
-        <v>0</v>
-      </c>
-      <c r="F83" t="n">
-        <v>1</v>
-      </c>
-      <c r="G83" t="n">
-        <v>0</v>
-      </c>
-      <c r="H83" t="n">
-        <v>0</v>
-      </c>
       <c r="I83" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J83" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K83" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L83" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M83" t="n">
         <v>1</v>
@@ -3975,17 +3947,15 @@
           <t>塑膠/金屬機殼</t>
         </is>
       </c>
-      <c r="B86" t="n">
-        <v>0</v>
-      </c>
+      <c r="B86" t="inlineStr"/>
       <c r="C86" t="n">
         <v>1</v>
       </c>
       <c r="D86" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E86" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F86" t="n">
         <v>0</v>
@@ -4018,20 +3988,18 @@
           <t>塑膠材料</t>
         </is>
       </c>
-      <c r="B87" t="n">
-        <v>0</v>
-      </c>
+      <c r="B87" t="inlineStr"/>
       <c r="C87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G87" t="n">
         <v>0</v>
@@ -4063,7 +4031,7 @@
       </c>
       <c r="B88" t="inlineStr"/>
       <c r="C88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D88" t="n">
         <v>0</v>
@@ -4078,10 +4046,10 @@
         <v>0</v>
       </c>
       <c r="H88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -4107,22 +4075,22 @@
         <v>1</v>
       </c>
       <c r="D89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E89" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G89" t="n">
         <v>0</v>
       </c>
       <c r="H89" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -4131,10 +4099,10 @@
         <v>0</v>
       </c>
       <c r="L89" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="90">
@@ -4186,7 +4154,7 @@
       </c>
       <c r="B91" t="inlineStr"/>
       <c r="C91" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D91" t="n">
         <v>0</v>
@@ -4225,17 +4193,15 @@
           <t>大功率鋰電池芯/模組、電池管理系統、動力馬達等零組件</t>
         </is>
       </c>
-      <c r="B92" t="n">
-        <v>0</v>
-      </c>
+      <c r="B92" t="inlineStr"/>
       <c r="C92" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D92" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E92" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F92" t="n">
         <v>1</v>
@@ -4244,10 +4210,10 @@
         <v>1</v>
       </c>
       <c r="H92" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I92" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -4256,7 +4222,7 @@
         <v>0</v>
       </c>
       <c r="L92" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M92" t="n">
         <v>1</v>
@@ -4338,10 +4304,10 @@
         <v>0</v>
       </c>
       <c r="L94" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M94" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="95">
@@ -4352,37 +4318,37 @@
       </c>
       <c r="B95" t="inlineStr"/>
       <c r="C95" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D95" t="n">
+        <v>0</v>
+      </c>
+      <c r="E95" t="n">
+        <v>0</v>
+      </c>
+      <c r="F95" t="n">
+        <v>0</v>
+      </c>
+      <c r="G95" t="n">
+        <v>1</v>
+      </c>
+      <c r="H95" t="n">
+        <v>1</v>
+      </c>
+      <c r="I95" t="n">
+        <v>0</v>
+      </c>
+      <c r="J95" t="n">
+        <v>0</v>
+      </c>
+      <c r="K95" t="n">
         <v>2</v>
-      </c>
-      <c r="E95" t="n">
-        <v>0</v>
-      </c>
-      <c r="F95" t="n">
-        <v>0</v>
-      </c>
-      <c r="G95" t="n">
-        <v>0</v>
-      </c>
-      <c r="H95" t="n">
-        <v>1</v>
-      </c>
-      <c r="I95" t="n">
-        <v>1</v>
-      </c>
-      <c r="J95" t="n">
-        <v>0</v>
-      </c>
-      <c r="K95" t="n">
-        <v>0</v>
       </c>
       <c r="L95" t="n">
         <v>2</v>
       </c>
       <c r="M95" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="96">
@@ -4393,10 +4359,10 @@
       </c>
       <c r="B96" t="inlineStr"/>
       <c r="C96" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D96" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E96" t="n">
         <v>0</v>
@@ -4408,22 +4374,22 @@
         <v>0</v>
       </c>
       <c r="H96" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I96" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
       </c>
       <c r="K96" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L96" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M96" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="97">
@@ -4502,10 +4468,10 @@
         <v>0</v>
       </c>
       <c r="L98" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M98" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="99">
@@ -4534,19 +4500,19 @@
         <v>0</v>
       </c>
       <c r="I99" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K99" t="n">
         <v>0</v>
       </c>
       <c r="L99" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="100">
@@ -4598,13 +4564,13 @@
       </c>
       <c r="B101" t="inlineStr"/>
       <c r="C101" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D101" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E101" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F101" t="n">
         <v>0</v>
@@ -4619,16 +4585,16 @@
         <v>0</v>
       </c>
       <c r="J101" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K101" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L101" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M101" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="102">
@@ -4639,37 +4605,37 @@
       </c>
       <c r="B102" t="inlineStr"/>
       <c r="C102" t="n">
+        <v>1</v>
+      </c>
+      <c r="D102" t="n">
+        <v>1</v>
+      </c>
+      <c r="E102" t="n">
+        <v>0</v>
+      </c>
+      <c r="F102" t="n">
+        <v>0</v>
+      </c>
+      <c r="G102" t="n">
+        <v>0</v>
+      </c>
+      <c r="H102" t="n">
         <v>2</v>
       </c>
-      <c r="D102" t="n">
-        <v>1</v>
-      </c>
-      <c r="E102" t="n">
-        <v>1</v>
-      </c>
-      <c r="F102" t="n">
-        <v>0</v>
-      </c>
-      <c r="G102" t="n">
-        <v>0</v>
-      </c>
-      <c r="H102" t="n">
-        <v>0</v>
-      </c>
       <c r="I102" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J102" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K102" t="n">
         <v>0</v>
       </c>
       <c r="L102" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M102" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="103">
@@ -4721,13 +4687,13 @@
       </c>
       <c r="B104" t="inlineStr"/>
       <c r="C104" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D104" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E104" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F104" t="n">
         <v>0</v>
@@ -4736,22 +4702,22 @@
         <v>0</v>
       </c>
       <c r="H104" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I104" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
       </c>
       <c r="K104" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L104" t="n">
         <v>1</v>
       </c>
       <c r="M104" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="105">
@@ -4762,34 +4728,34 @@
       </c>
       <c r="B105" t="inlineStr"/>
       <c r="C105" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D105" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E105" t="n">
         <v>1</v>
       </c>
       <c r="F105" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G105" t="n">
         <v>0</v>
       </c>
       <c r="H105" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I105" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
       </c>
       <c r="K105" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L105" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M105" t="n">
         <v>0</v>
@@ -4803,25 +4769,25 @@
       </c>
       <c r="B106" t="inlineStr"/>
       <c r="C106" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D106" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E106" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F106" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G106" t="n">
         <v>0</v>
       </c>
       <c r="H106" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I106" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -4982,10 +4948,10 @@
         <v>0</v>
       </c>
       <c r="H110" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I110" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -5008,13 +4974,13 @@
       </c>
       <c r="B111" t="inlineStr"/>
       <c r="C111" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D111" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E111" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F111" t="n">
         <v>0</v>
@@ -5029,16 +4995,16 @@
         <v>0</v>
       </c>
       <c r="J111" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K111" t="n">
         <v>1</v>
       </c>
       <c r="L111" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M111" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="112">
@@ -5049,10 +5015,10 @@
       </c>
       <c r="B112" t="inlineStr"/>
       <c r="C112" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D112" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E112" t="n">
         <v>0</v>
@@ -5061,10 +5027,10 @@
         <v>0</v>
       </c>
       <c r="G112" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H112" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I112" t="n">
         <v>0</v>
@@ -5073,13 +5039,13 @@
         <v>0</v>
       </c>
       <c r="K112" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L112" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M112" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="113">
@@ -5090,10 +5056,10 @@
       </c>
       <c r="B113" t="inlineStr"/>
       <c r="C113" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D113" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E113" t="n">
         <v>0</v>
@@ -5102,10 +5068,10 @@
         <v>0</v>
       </c>
       <c r="G113" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H113" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I113" t="n">
         <v>0</v>
@@ -5152,10 +5118,10 @@
         <v>0</v>
       </c>
       <c r="J114" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K114" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L114" t="n">
         <v>0</v>
@@ -5196,10 +5162,10 @@
         <v>0</v>
       </c>
       <c r="K115" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L115" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M115" t="n">
         <v>0</v>
@@ -5237,10 +5203,10 @@
         <v>0</v>
       </c>
       <c r="K116" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L116" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M116" t="n">
         <v>0</v>
@@ -5336,7 +5302,7 @@
       </c>
       <c r="B119" t="inlineStr"/>
       <c r="C119" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D119" t="n">
         <v>0</v>
@@ -5377,25 +5343,25 @@
       </c>
       <c r="B120" t="inlineStr"/>
       <c r="C120" t="n">
+        <v>0</v>
+      </c>
+      <c r="D120" t="n">
+        <v>1</v>
+      </c>
+      <c r="E120" t="n">
+        <v>1</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0</v>
+      </c>
+      <c r="H120" t="n">
         <v>2</v>
       </c>
-      <c r="D120" t="n">
-        <v>0</v>
-      </c>
-      <c r="E120" t="n">
-        <v>1</v>
-      </c>
-      <c r="F120" t="n">
-        <v>1</v>
-      </c>
-      <c r="G120" t="n">
-        <v>0</v>
-      </c>
-      <c r="H120" t="n">
-        <v>0</v>
-      </c>
       <c r="I120" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -5404,10 +5370,10 @@
         <v>0</v>
       </c>
       <c r="L120" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M120" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="121">
@@ -5416,14 +5382,12 @@
           <t>建設業</t>
         </is>
       </c>
-      <c r="B121" t="n">
-        <v>0</v>
-      </c>
+      <c r="B121" t="inlineStr"/>
       <c r="C121" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D121" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E121" t="n">
         <v>0</v>
@@ -5435,19 +5399,19 @@
         <v>0</v>
       </c>
       <c r="H121" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I121" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J121" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K121" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L121" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M121" t="n">
         <v>1</v>
@@ -5543,10 +5507,10 @@
       </c>
       <c r="B124" t="inlineStr"/>
       <c r="C124" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D124" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E124" t="n">
         <v>0</v>
@@ -5664,9 +5628,7 @@
           <t>感測裝置</t>
         </is>
       </c>
-      <c r="B127" t="n">
-        <v>0</v>
-      </c>
+      <c r="B127" t="inlineStr"/>
       <c r="C127" t="n">
         <v>0</v>
       </c>
@@ -5709,37 +5671,37 @@
       </c>
       <c r="B128" t="inlineStr"/>
       <c r="C128" t="n">
+        <v>1</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0</v>
+      </c>
+      <c r="E128" t="n">
+        <v>1</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0</v>
+      </c>
+      <c r="G128" t="n">
+        <v>1</v>
+      </c>
+      <c r="H128" t="n">
+        <v>1</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0</v>
+      </c>
+      <c r="L128" t="n">
         <v>2</v>
       </c>
-      <c r="D128" t="n">
-        <v>1</v>
-      </c>
-      <c r="E128" t="n">
-        <v>0</v>
-      </c>
-      <c r="F128" t="n">
-        <v>1</v>
-      </c>
-      <c r="G128" t="n">
-        <v>0</v>
-      </c>
-      <c r="H128" t="n">
-        <v>1</v>
-      </c>
-      <c r="I128" t="n">
-        <v>1</v>
-      </c>
-      <c r="J128" t="n">
-        <v>0</v>
-      </c>
-      <c r="K128" t="n">
-        <v>0</v>
-      </c>
-      <c r="L128" t="n">
-        <v>0</v>
-      </c>
       <c r="M128" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="129">
@@ -5748,14 +5710,12 @@
           <t>應用軟體</t>
         </is>
       </c>
-      <c r="B129" t="n">
-        <v>0</v>
-      </c>
+      <c r="B129" t="inlineStr"/>
       <c r="C129" t="n">
         <v>1</v>
       </c>
       <c r="D129" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E129" t="n">
         <v>0</v>
@@ -5782,7 +5742,7 @@
         <v>0</v>
       </c>
       <c r="M129" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="130">
@@ -5793,7 +5753,7 @@
       </c>
       <c r="B130" t="inlineStr"/>
       <c r="C130" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D130" t="n">
         <v>0</v>
@@ -5834,7 +5794,7 @@
       </c>
       <c r="B131" t="inlineStr"/>
       <c r="C131" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D131" t="n">
         <v>1</v>
@@ -5843,13 +5803,13 @@
         <v>1</v>
       </c>
       <c r="F131" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G131" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H131" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I131" t="n">
         <v>0</v>
@@ -5878,10 +5838,10 @@
         <v>0</v>
       </c>
       <c r="D132" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E132" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F132" t="n">
         <v>0</v>
@@ -5916,7 +5876,7 @@
       </c>
       <c r="B133" t="inlineStr"/>
       <c r="C133" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D133" t="n">
         <v>0</v>
@@ -5996,9 +5956,7 @@
           <t>控制IC</t>
         </is>
       </c>
-      <c r="B135" t="n">
-        <v>0</v>
-      </c>
+      <c r="B135" t="inlineStr"/>
       <c r="C135" t="n">
         <v>0</v>
       </c>
@@ -6162,11 +6120,9 @@
           <t>散熱片、風扇馬達、散熱模組</t>
         </is>
       </c>
-      <c r="B139" t="n">
-        <v>0</v>
-      </c>
+      <c r="B139" t="inlineStr"/>
       <c r="C139" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D139" t="n">
         <v>0</v>
@@ -6181,10 +6137,10 @@
         <v>0</v>
       </c>
       <c r="H139" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I139" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -6193,10 +6149,10 @@
         <v>0</v>
       </c>
       <c r="L139" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M139" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="140">
@@ -6231,13 +6187,13 @@
         <v>0</v>
       </c>
       <c r="K140" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L140" t="n">
         <v>1</v>
       </c>
       <c r="M140" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="141">
@@ -6254,7 +6210,7 @@
         <v>1</v>
       </c>
       <c r="E141" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F141" t="n">
         <v>0</v>
@@ -6272,13 +6228,13 @@
         <v>0</v>
       </c>
       <c r="K141" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L141" t="n">
         <v>1</v>
       </c>
       <c r="M141" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="142">
@@ -6313,13 +6269,13 @@
         <v>0</v>
       </c>
       <c r="K142" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L142" t="n">
         <v>1</v>
       </c>
       <c r="M142" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="143">
@@ -6330,7 +6286,7 @@
       </c>
       <c r="B143" t="inlineStr"/>
       <c r="C143" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D143" t="n">
         <v>0</v>
@@ -6371,16 +6327,16 @@
       </c>
       <c r="B144" t="inlineStr"/>
       <c r="C144" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D144" t="n">
         <v>0</v>
       </c>
       <c r="E144" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F144" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G144" t="n">
         <v>0</v>
@@ -6392,10 +6348,10 @@
         <v>0</v>
       </c>
       <c r="J144" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K144" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L144" t="n">
         <v>0</v>
@@ -6412,13 +6368,13 @@
       </c>
       <c r="B145" t="inlineStr"/>
       <c r="C145" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D145" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E145" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F145" t="n">
         <v>0</v>
@@ -6433,16 +6389,16 @@
         <v>0</v>
       </c>
       <c r="J145" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K145" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L145" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M145" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="146">
@@ -6494,13 +6450,13 @@
       </c>
       <c r="B147" t="inlineStr"/>
       <c r="C147" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D147" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E147" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F147" t="n">
         <v>0</v>
@@ -6515,16 +6471,16 @@
         <v>0</v>
       </c>
       <c r="J147" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K147" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L147" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M147" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="148">
@@ -6533,9 +6489,7 @@
           <t>文化印刷業</t>
         </is>
       </c>
-      <c r="B148" t="n">
-        <v>0</v>
-      </c>
+      <c r="B148" t="inlineStr"/>
       <c r="C148" t="n">
         <v>0</v>
       </c>
@@ -6558,16 +6512,16 @@
         <v>0</v>
       </c>
       <c r="J148" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K148" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L148" t="n">
         <v>0</v>
       </c>
       <c r="M148" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="149">
@@ -6581,10 +6535,10 @@
         <v>0</v>
       </c>
       <c r="D149" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E149" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F149" t="n">
         <v>0</v>
@@ -6634,10 +6588,10 @@
         <v>0</v>
       </c>
       <c r="H150" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I150" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -6665,10 +6619,10 @@
         <v>0</v>
       </c>
       <c r="D151" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E151" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F151" t="n">
         <v>0</v>
@@ -6677,7 +6631,7 @@
         <v>0</v>
       </c>
       <c r="H151" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I151" t="n">
         <v>0</v>
@@ -6689,10 +6643,10 @@
         <v>0</v>
       </c>
       <c r="L151" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M151" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="152">
@@ -6703,7 +6657,7 @@
       </c>
       <c r="B152" t="inlineStr"/>
       <c r="C152" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D152" t="n">
         <v>0</v>
@@ -6742,32 +6696,30 @@
           <t>智慧設備</t>
         </is>
       </c>
-      <c r="B153" t="n">
-        <v>0</v>
-      </c>
+      <c r="B153" t="inlineStr"/>
       <c r="C153" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D153" t="n">
         <v>0</v>
       </c>
       <c r="E153" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F153" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G153" t="n">
         <v>0</v>
       </c>
       <c r="H153" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I153" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J153" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K153" t="n">
         <v>0</v>
@@ -6785,14 +6737,12 @@
           <t>有線通訊設備(如電話機、傳真機)</t>
         </is>
       </c>
-      <c r="B154" t="n">
-        <v>0</v>
-      </c>
+      <c r="B154" t="inlineStr"/>
       <c r="C154" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D154" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E154" t="n">
         <v>0</v>
@@ -6804,7 +6754,7 @@
         <v>0</v>
       </c>
       <c r="H154" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I154" t="n">
         <v>0</v>
@@ -6871,16 +6821,16 @@
       </c>
       <c r="B156" t="inlineStr"/>
       <c r="C156" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D156" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E156" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F156" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G156" t="n">
         <v>0</v>
@@ -6915,7 +6865,7 @@
         <v>2</v>
       </c>
       <c r="D157" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E157" t="n">
         <v>0</v>
@@ -6930,19 +6880,19 @@
         <v>0</v>
       </c>
       <c r="I157" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J157" t="n">
         <v>1</v>
       </c>
       <c r="K157" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L157" t="n">
         <v>0</v>
       </c>
       <c r="M157" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="158">
@@ -6953,7 +6903,7 @@
       </c>
       <c r="B158" t="inlineStr"/>
       <c r="C158" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D158" t="n">
         <v>0</v>
@@ -6968,10 +6918,10 @@
         <v>0</v>
       </c>
       <c r="H158" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I158" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -6992,7 +6942,9 @@
           <t>棒鋼盤元(捲狀條鋼)</t>
         </is>
       </c>
-      <c r="B159" t="inlineStr"/>
+      <c r="B159" t="n">
+        <v>0</v>
+      </c>
       <c r="C159" t="n">
         <v>0</v>
       </c>
@@ -7035,7 +6987,7 @@
       </c>
       <c r="B160" t="inlineStr"/>
       <c r="C160" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D160" t="n">
         <v>0</v>
@@ -7050,10 +7002,10 @@
         <v>0</v>
       </c>
       <c r="H160" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I160" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -7076,7 +7028,7 @@
       </c>
       <c r="B161" t="inlineStr"/>
       <c r="C161" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D161" t="n">
         <v>0</v>
@@ -7115,41 +7067,39 @@
           <t>機器學習</t>
         </is>
       </c>
-      <c r="B162" t="n">
-        <v>0</v>
-      </c>
+      <c r="B162" t="inlineStr"/>
       <c r="C162" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D162" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E162" t="n">
         <v>1</v>
       </c>
       <c r="F162" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G162" t="n">
         <v>0</v>
       </c>
       <c r="H162" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I162" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J162" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K162" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L162" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M162" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="163">
@@ -7158,14 +7108,12 @@
           <t>機械設備之沖壓零組件</t>
         </is>
       </c>
-      <c r="B163" t="n">
-        <v>0</v>
-      </c>
+      <c r="B163" t="inlineStr"/>
       <c r="C163" t="n">
         <v>1</v>
       </c>
       <c r="D163" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E163" t="n">
         <v>0</v>
@@ -7192,7 +7140,7 @@
         <v>0</v>
       </c>
       <c r="M163" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="164">
@@ -7203,7 +7151,7 @@
       </c>
       <c r="B164" t="inlineStr"/>
       <c r="C164" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D164" t="n">
         <v>0</v>
@@ -7230,7 +7178,7 @@
         <v>0</v>
       </c>
       <c r="L164" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M164" t="n">
         <v>1</v>
@@ -7242,41 +7190,39 @@
           <t>機殼</t>
         </is>
       </c>
-      <c r="B165" t="n">
-        <v>0</v>
-      </c>
+      <c r="B165" t="inlineStr"/>
       <c r="C165" t="n">
+        <v>0</v>
+      </c>
+      <c r="D165" t="n">
+        <v>1</v>
+      </c>
+      <c r="E165" t="n">
+        <v>0</v>
+      </c>
+      <c r="F165" t="n">
+        <v>0</v>
+      </c>
+      <c r="G165" t="n">
+        <v>0</v>
+      </c>
+      <c r="H165" t="n">
+        <v>0</v>
+      </c>
+      <c r="I165" t="n">
+        <v>0</v>
+      </c>
+      <c r="J165" t="n">
+        <v>1</v>
+      </c>
+      <c r="K165" t="n">
+        <v>1</v>
+      </c>
+      <c r="L165" t="n">
         <v>2</v>
       </c>
-      <c r="D165" t="n">
-        <v>0</v>
-      </c>
-      <c r="E165" t="n">
-        <v>1</v>
-      </c>
-      <c r="F165" t="n">
-        <v>0</v>
-      </c>
-      <c r="G165" t="n">
-        <v>0</v>
-      </c>
-      <c r="H165" t="n">
-        <v>0</v>
-      </c>
-      <c r="I165" t="n">
-        <v>0</v>
-      </c>
-      <c r="J165" t="n">
-        <v>0</v>
-      </c>
-      <c r="K165" t="n">
-        <v>1</v>
-      </c>
-      <c r="L165" t="n">
-        <v>1</v>
-      </c>
       <c r="M165" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="166">
@@ -7287,10 +7233,10 @@
       </c>
       <c r="B166" t="inlineStr"/>
       <c r="C166" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D166" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E166" t="n">
         <v>0</v>
@@ -7299,13 +7245,13 @@
         <v>0</v>
       </c>
       <c r="G166" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H166" t="n">
         <v>1</v>
       </c>
       <c r="I166" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -7328,10 +7274,10 @@
       </c>
       <c r="B167" t="inlineStr"/>
       <c r="C167" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D167" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E167" t="n">
         <v>0</v>
@@ -7340,10 +7286,10 @@
         <v>0</v>
       </c>
       <c r="G167" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H167" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I167" t="n">
         <v>0</v>
@@ -7393,10 +7339,10 @@
         <v>0</v>
       </c>
       <c r="K168" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L168" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M168" t="n">
         <v>0</v>
@@ -7533,10 +7479,10 @@
       </c>
       <c r="B172" t="inlineStr"/>
       <c r="C172" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D172" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E172" t="n">
         <v>0</v>
@@ -7557,10 +7503,10 @@
         <v>0</v>
       </c>
       <c r="K172" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L172" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M172" t="n">
         <v>0</v>
@@ -7574,7 +7520,7 @@
       </c>
       <c r="B173" t="inlineStr"/>
       <c r="C173" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D173" t="n">
         <v>0</v>
@@ -7639,10 +7585,10 @@
         <v>0</v>
       </c>
       <c r="K174" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L174" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M174" t="n">
         <v>0</v>
@@ -7680,10 +7626,10 @@
         <v>0</v>
       </c>
       <c r="K175" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L175" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M175" t="n">
         <v>0</v>
@@ -7743,10 +7689,10 @@
         <v>1</v>
       </c>
       <c r="D177" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E177" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F177" t="n">
         <v>0</v>
@@ -7755,10 +7701,10 @@
         <v>0</v>
       </c>
       <c r="H177" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I177" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -7822,31 +7768,31 @@
       </c>
       <c r="B179" t="inlineStr"/>
       <c r="C179" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D179" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E179" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F179" t="n">
+        <v>0</v>
+      </c>
+      <c r="G179" t="n">
+        <v>0</v>
+      </c>
+      <c r="H179" t="n">
         <v>2</v>
       </c>
-      <c r="G179" t="n">
-        <v>0</v>
-      </c>
-      <c r="H179" t="n">
-        <v>0</v>
-      </c>
       <c r="I179" t="n">
+        <v>1</v>
+      </c>
+      <c r="J179" t="n">
+        <v>4</v>
+      </c>
+      <c r="K179" t="n">
         <v>2</v>
-      </c>
-      <c r="J179" t="n">
-        <v>1</v>
-      </c>
-      <c r="K179" t="n">
-        <v>4</v>
       </c>
       <c r="L179" t="n">
         <v>2</v>
@@ -7863,10 +7809,10 @@
       </c>
       <c r="B180" t="inlineStr"/>
       <c r="C180" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D180" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E180" t="n">
         <v>0</v>
@@ -7902,17 +7848,15 @@
           <t>燈具/應用</t>
         </is>
       </c>
-      <c r="B181" t="n">
-        <v>0</v>
-      </c>
+      <c r="B181" t="inlineStr"/>
       <c r="C181" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D181" t="n">
         <v>2</v>
       </c>
       <c r="E181" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F181" t="n">
         <v>0</v>
@@ -7921,13 +7865,13 @@
         <v>0</v>
       </c>
       <c r="H181" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I181" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J181" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K181" t="n">
         <v>1</v>
@@ -7936,7 +7880,7 @@
         <v>1</v>
       </c>
       <c r="M181" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="182">
@@ -7945,20 +7889,18 @@
           <t>營造業</t>
         </is>
       </c>
-      <c r="B182" t="n">
-        <v>0</v>
-      </c>
+      <c r="B182" t="inlineStr"/>
       <c r="C182" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D182" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E182" t="n">
         <v>1</v>
       </c>
       <c r="F182" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G182" t="n">
         <v>0</v>
@@ -8031,13 +7973,13 @@
       </c>
       <c r="B184" t="inlineStr"/>
       <c r="C184" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D184" t="n">
         <v>1</v>
       </c>
       <c r="E184" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F184" t="n">
         <v>0</v>
@@ -8052,13 +7994,13 @@
         <v>0</v>
       </c>
       <c r="J184" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K184" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L184" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M184" t="n">
         <v>1</v>
@@ -8195,16 +8137,16 @@
       </c>
       <c r="B188" t="inlineStr"/>
       <c r="C188" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D188" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E188" t="n">
         <v>1</v>
       </c>
       <c r="F188" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G188" t="n">
         <v>0</v>
@@ -8216,16 +8158,16 @@
         <v>0</v>
       </c>
       <c r="J188" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K188" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L188" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M188" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="189">
@@ -8234,9 +8176,7 @@
           <t>特殊照明業</t>
         </is>
       </c>
-      <c r="B189" t="n">
-        <v>0</v>
-      </c>
+      <c r="B189" t="inlineStr"/>
       <c r="C189" t="n">
         <v>0</v>
       </c>
@@ -8253,10 +8193,10 @@
         <v>0</v>
       </c>
       <c r="H189" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I189" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -8279,7 +8219,7 @@
       </c>
       <c r="B190" t="inlineStr"/>
       <c r="C190" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D190" t="n">
         <v>0</v>
@@ -8361,37 +8301,37 @@
       </c>
       <c r="B192" t="inlineStr"/>
       <c r="C192" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D192" t="n">
+        <v>1</v>
+      </c>
+      <c r="E192" t="n">
+        <v>0</v>
+      </c>
+      <c r="F192" t="n">
+        <v>0</v>
+      </c>
+      <c r="G192" t="n">
+        <v>0</v>
+      </c>
+      <c r="H192" t="n">
+        <v>4</v>
+      </c>
+      <c r="I192" t="n">
+        <v>0</v>
+      </c>
+      <c r="J192" t="n">
+        <v>0</v>
+      </c>
+      <c r="K192" t="n">
+        <v>0</v>
+      </c>
+      <c r="L192" t="n">
+        <v>0</v>
+      </c>
+      <c r="M192" t="n">
         <v>2</v>
-      </c>
-      <c r="E192" t="n">
-        <v>1</v>
-      </c>
-      <c r="F192" t="n">
-        <v>0</v>
-      </c>
-      <c r="G192" t="n">
-        <v>0</v>
-      </c>
-      <c r="H192" t="n">
-        <v>0</v>
-      </c>
-      <c r="I192" t="n">
-        <v>4</v>
-      </c>
-      <c r="J192" t="n">
-        <v>0</v>
-      </c>
-      <c r="K192" t="n">
-        <v>0</v>
-      </c>
-      <c r="L192" t="n">
-        <v>0</v>
-      </c>
-      <c r="M192" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="193">
@@ -8458,13 +8398,13 @@
         <v>0</v>
       </c>
       <c r="H194" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I194" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J194" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K194" t="n">
         <v>1</v>
@@ -8484,10 +8424,10 @@
       </c>
       <c r="B195" t="inlineStr"/>
       <c r="C195" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D195" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E195" t="n">
         <v>0</v>
@@ -8508,7 +8448,7 @@
         <v>0</v>
       </c>
       <c r="K195" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L195" t="n">
         <v>1</v>
@@ -8523,38 +8463,36 @@
           <t>生產製程、檢測設備及原物料</t>
         </is>
       </c>
-      <c r="B196" t="n">
-        <v>0</v>
-      </c>
+      <c r="B196" t="inlineStr"/>
       <c r="C196" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D196" t="n">
+        <v>0</v>
+      </c>
+      <c r="E196" t="n">
+        <v>1</v>
+      </c>
+      <c r="F196" t="n">
+        <v>0</v>
+      </c>
+      <c r="G196" t="n">
+        <v>1</v>
+      </c>
+      <c r="H196" t="n">
+        <v>1</v>
+      </c>
+      <c r="I196" t="n">
+        <v>0</v>
+      </c>
+      <c r="J196" t="n">
+        <v>0</v>
+      </c>
+      <c r="K196" t="n">
         <v>3</v>
       </c>
-      <c r="E196" t="n">
-        <v>0</v>
-      </c>
-      <c r="F196" t="n">
-        <v>1</v>
-      </c>
-      <c r="G196" t="n">
-        <v>0</v>
-      </c>
-      <c r="H196" t="n">
-        <v>1</v>
-      </c>
-      <c r="I196" t="n">
-        <v>1</v>
-      </c>
-      <c r="J196" t="n">
-        <v>0</v>
-      </c>
-      <c r="K196" t="n">
-        <v>0</v>
-      </c>
       <c r="L196" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M196" t="n">
         <v>0</v>
@@ -8568,37 +8506,37 @@
       </c>
       <c r="B197" t="inlineStr"/>
       <c r="C197" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D197" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E197" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F197" t="n">
         <v>1</v>
       </c>
       <c r="G197" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H197" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="I197" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J197" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K197" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="L197" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="M197" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="198">
@@ -8636,10 +8574,10 @@
         <v>0</v>
       </c>
       <c r="L198" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M198" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="199">
@@ -8706,10 +8644,10 @@
         <v>0</v>
       </c>
       <c r="H200" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I200" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J200" t="n">
         <v>0</v>
@@ -8817,7 +8755,7 @@
         <v>1</v>
       </c>
       <c r="D203" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E203" t="n">
         <v>0</v>
@@ -8844,7 +8782,7 @@
         <v>0</v>
       </c>
       <c r="M203" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="204">
@@ -8855,37 +8793,37 @@
       </c>
       <c r="B204" t="inlineStr"/>
       <c r="C204" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D204" t="n">
+        <v>0</v>
+      </c>
+      <c r="E204" t="n">
+        <v>1</v>
+      </c>
+      <c r="F204" t="n">
+        <v>0</v>
+      </c>
+      <c r="G204" t="n">
+        <v>1</v>
+      </c>
+      <c r="H204" t="n">
+        <v>0</v>
+      </c>
+      <c r="I204" t="n">
+        <v>0</v>
+      </c>
+      <c r="J204" t="n">
+        <v>1</v>
+      </c>
+      <c r="K204" t="n">
         <v>2</v>
       </c>
-      <c r="E204" t="n">
-        <v>0</v>
-      </c>
-      <c r="F204" t="n">
-        <v>1</v>
-      </c>
-      <c r="G204" t="n">
-        <v>0</v>
-      </c>
-      <c r="H204" t="n">
-        <v>1</v>
-      </c>
-      <c r="I204" t="n">
-        <v>0</v>
-      </c>
-      <c r="J204" t="n">
-        <v>0</v>
-      </c>
-      <c r="K204" t="n">
-        <v>1</v>
-      </c>
       <c r="L204" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M204" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="205">
@@ -8896,10 +8834,10 @@
       </c>
       <c r="B205" t="inlineStr"/>
       <c r="C205" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D205" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E205" t="n">
         <v>0</v>
@@ -8926,7 +8864,7 @@
         <v>0</v>
       </c>
       <c r="M205" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="206">
@@ -8976,18 +8914,20 @@
           <t>矽晶圓/矽晶片</t>
         </is>
       </c>
-      <c r="B207" t="inlineStr"/>
+      <c r="B207" t="n">
+        <v>0</v>
+      </c>
       <c r="C207" t="n">
         <v>0</v>
       </c>
       <c r="D207" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E207" t="n">
         <v>1</v>
       </c>
       <c r="F207" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G207" t="n">
         <v>0</v>
@@ -9017,39 +8957,41 @@
           <t>硬板、軟板、IC載板製造</t>
         </is>
       </c>
-      <c r="B208" t="inlineStr"/>
+      <c r="B208" t="n">
+        <v>0</v>
+      </c>
       <c r="C208" t="n">
         <v>5</v>
       </c>
       <c r="D208" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E208" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F208" t="n">
+        <v>0</v>
+      </c>
+      <c r="G208" t="n">
+        <v>0</v>
+      </c>
+      <c r="H208" t="n">
+        <v>9</v>
+      </c>
+      <c r="I208" t="n">
+        <v>0</v>
+      </c>
+      <c r="J208" t="n">
+        <v>0</v>
+      </c>
+      <c r="K208" t="n">
+        <v>8</v>
+      </c>
+      <c r="L208" t="n">
+        <v>1</v>
+      </c>
+      <c r="M208" t="n">
         <v>2</v>
-      </c>
-      <c r="G208" t="n">
-        <v>1</v>
-      </c>
-      <c r="H208" t="n">
-        <v>0</v>
-      </c>
-      <c r="I208" t="n">
-        <v>9</v>
-      </c>
-      <c r="J208" t="n">
-        <v>0</v>
-      </c>
-      <c r="K208" t="n">
-        <v>0</v>
-      </c>
-      <c r="L208" t="n">
-        <v>8</v>
-      </c>
-      <c r="M208" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="209">
@@ -9060,7 +9002,7 @@
       </c>
       <c r="B209" t="inlineStr"/>
       <c r="C209" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D209" t="n">
         <v>0</v>
@@ -9101,7 +9043,7 @@
       </c>
       <c r="B210" t="inlineStr"/>
       <c r="C210" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D210" t="n">
         <v>0</v>
@@ -9142,37 +9084,37 @@
       </c>
       <c r="B211" t="inlineStr"/>
       <c r="C211" t="n">
+        <v>1</v>
+      </c>
+      <c r="D211" t="n">
+        <v>0</v>
+      </c>
+      <c r="E211" t="n">
+        <v>0</v>
+      </c>
+      <c r="F211" t="n">
+        <v>0</v>
+      </c>
+      <c r="G211" t="n">
+        <v>0</v>
+      </c>
+      <c r="H211" t="n">
+        <v>0</v>
+      </c>
+      <c r="I211" t="n">
+        <v>0</v>
+      </c>
+      <c r="J211" t="n">
+        <v>0</v>
+      </c>
+      <c r="K211" t="n">
+        <v>0</v>
+      </c>
+      <c r="L211" t="n">
+        <v>0</v>
+      </c>
+      <c r="M211" t="n">
         <v>2</v>
-      </c>
-      <c r="D211" t="n">
-        <v>1</v>
-      </c>
-      <c r="E211" t="n">
-        <v>0</v>
-      </c>
-      <c r="F211" t="n">
-        <v>0</v>
-      </c>
-      <c r="G211" t="n">
-        <v>0</v>
-      </c>
-      <c r="H211" t="n">
-        <v>0</v>
-      </c>
-      <c r="I211" t="n">
-        <v>0</v>
-      </c>
-      <c r="J211" t="n">
-        <v>0</v>
-      </c>
-      <c r="K211" t="n">
-        <v>0</v>
-      </c>
-      <c r="L211" t="n">
-        <v>0</v>
-      </c>
-      <c r="M211" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="212">
@@ -9222,9 +9164,7 @@
           <t>租賃業</t>
         </is>
       </c>
-      <c r="B213" t="n">
-        <v>0</v>
-      </c>
+      <c r="B213" t="inlineStr"/>
       <c r="C213" t="n">
         <v>0</v>
       </c>
@@ -9265,9 +9205,7 @@
           <t>移動控制</t>
         </is>
       </c>
-      <c r="B214" t="n">
-        <v>0</v>
-      </c>
+      <c r="B214" t="inlineStr"/>
       <c r="C214" t="n">
         <v>0</v>
       </c>
@@ -9308,9 +9246,7 @@
           <t>稜鏡片</t>
         </is>
       </c>
-      <c r="B215" t="n">
-        <v>0</v>
-      </c>
+      <c r="B215" t="inlineStr"/>
       <c r="C215" t="n">
         <v>0</v>
       </c>
@@ -9353,7 +9289,7 @@
       </c>
       <c r="B216" t="inlineStr"/>
       <c r="C216" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D216" t="n">
         <v>0</v>
@@ -9394,16 +9330,16 @@
       </c>
       <c r="B217" t="inlineStr"/>
       <c r="C217" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D217" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E217" t="n">
         <v>1</v>
       </c>
       <c r="F217" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G217" t="n">
         <v>0</v>
@@ -9415,16 +9351,16 @@
         <v>0</v>
       </c>
       <c r="J217" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K217" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L217" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M217" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="218">
@@ -9435,13 +9371,13 @@
       </c>
       <c r="B218" t="inlineStr"/>
       <c r="C218" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D218" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E218" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F218" t="n">
         <v>0</v>
@@ -9450,10 +9386,10 @@
         <v>0</v>
       </c>
       <c r="H218" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I218" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J218" t="n">
         <v>0</v>
@@ -9476,13 +9412,13 @@
       </c>
       <c r="B219" t="inlineStr"/>
       <c r="C219" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D219" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E219" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F219" t="n">
         <v>0</v>
@@ -9491,10 +9427,10 @@
         <v>0</v>
       </c>
       <c r="H219" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I219" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J219" t="n">
         <v>0</v>
@@ -9515,41 +9451,39 @@
           <t>系統整合</t>
         </is>
       </c>
-      <c r="B220" t="n">
-        <v>0</v>
-      </c>
+      <c r="B220" t="inlineStr"/>
       <c r="C220" t="n">
+        <v>3</v>
+      </c>
+      <c r="D220" t="n">
+        <v>2</v>
+      </c>
+      <c r="E220" t="n">
+        <v>1</v>
+      </c>
+      <c r="F220" t="n">
+        <v>0</v>
+      </c>
+      <c r="G220" t="n">
+        <v>1</v>
+      </c>
+      <c r="H220" t="n">
+        <v>3</v>
+      </c>
+      <c r="I220" t="n">
+        <v>0</v>
+      </c>
+      <c r="J220" t="n">
+        <v>2</v>
+      </c>
+      <c r="K220" t="n">
+        <v>1</v>
+      </c>
+      <c r="L220" t="n">
+        <v>3</v>
+      </c>
+      <c r="M220" t="n">
         <v>5</v>
-      </c>
-      <c r="D220" t="n">
-        <v>3</v>
-      </c>
-      <c r="E220" t="n">
-        <v>2</v>
-      </c>
-      <c r="F220" t="n">
-        <v>1</v>
-      </c>
-      <c r="G220" t="n">
-        <v>0</v>
-      </c>
-      <c r="H220" t="n">
-        <v>1</v>
-      </c>
-      <c r="I220" t="n">
-        <v>3</v>
-      </c>
-      <c r="J220" t="n">
-        <v>0</v>
-      </c>
-      <c r="K220" t="n">
-        <v>2</v>
-      </c>
-      <c r="L220" t="n">
-        <v>1</v>
-      </c>
-      <c r="M220" t="n">
-        <v>3</v>
       </c>
     </row>
     <row r="221">
@@ -9558,41 +9492,39 @@
           <t>系統整合服務</t>
         </is>
       </c>
-      <c r="B221" t="n">
-        <v>0</v>
-      </c>
+      <c r="B221" t="inlineStr"/>
       <c r="C221" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D221" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E221" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F221" t="n">
+        <v>0</v>
+      </c>
+      <c r="G221" t="n">
+        <v>1</v>
+      </c>
+      <c r="H221" t="n">
+        <v>1</v>
+      </c>
+      <c r="I221" t="n">
+        <v>0</v>
+      </c>
+      <c r="J221" t="n">
+        <v>1</v>
+      </c>
+      <c r="K221" t="n">
+        <v>0</v>
+      </c>
+      <c r="L221" t="n">
         <v>3</v>
       </c>
-      <c r="G221" t="n">
-        <v>0</v>
-      </c>
-      <c r="H221" t="n">
-        <v>1</v>
-      </c>
-      <c r="I221" t="n">
-        <v>1</v>
-      </c>
-      <c r="J221" t="n">
-        <v>0</v>
-      </c>
-      <c r="K221" t="n">
-        <v>1</v>
-      </c>
-      <c r="L221" t="n">
-        <v>0</v>
-      </c>
       <c r="M221" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="222">
@@ -9606,10 +9538,10 @@
         <v>0</v>
       </c>
       <c r="D222" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E222" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F222" t="n">
         <v>0</v>
@@ -9647,7 +9579,7 @@
         <v>1</v>
       </c>
       <c r="D223" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E223" t="n">
         <v>0</v>
@@ -9671,10 +9603,10 @@
         <v>0</v>
       </c>
       <c r="L223" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M223" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="224">
@@ -9709,13 +9641,13 @@
         <v>0</v>
       </c>
       <c r="K224" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L224" t="n">
         <v>1</v>
       </c>
       <c r="M224" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="225">
@@ -9765,14 +9697,12 @@
           <t>網路IC</t>
         </is>
       </c>
-      <c r="B226" t="n">
-        <v>0</v>
-      </c>
+      <c r="B226" t="inlineStr"/>
       <c r="C226" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D226" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E226" t="n">
         <v>0</v>
@@ -9810,7 +9740,7 @@
       </c>
       <c r="B227" t="inlineStr"/>
       <c r="C227" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D227" t="n">
         <v>0</v>
@@ -9851,16 +9781,16 @@
       </c>
       <c r="B228" t="inlineStr"/>
       <c r="C228" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D228" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E228" t="n">
         <v>1</v>
       </c>
       <c r="F228" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G228" t="n">
         <v>0</v>
@@ -9872,7 +9802,7 @@
         <v>0</v>
       </c>
       <c r="J228" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K228" t="n">
         <v>1</v>
@@ -9892,16 +9822,16 @@
       </c>
       <c r="B229" t="inlineStr"/>
       <c r="C229" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D229" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E229" t="n">
         <v>1</v>
       </c>
       <c r="F229" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G229" t="n">
         <v>0</v>
@@ -9913,16 +9843,16 @@
         <v>0</v>
       </c>
       <c r="J229" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K229" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L229" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M229" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="230">
@@ -9931,38 +9861,36 @@
           <t>網路設備(如數據機、網路卡、閘道器、路由器、網路電話)</t>
         </is>
       </c>
-      <c r="B230" t="n">
-        <v>0</v>
-      </c>
+      <c r="B230" t="inlineStr"/>
       <c r="C230" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D230" t="n">
         <v>1</v>
       </c>
       <c r="E230" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F230" t="n">
+        <v>0</v>
+      </c>
+      <c r="G230" t="n">
+        <v>0</v>
+      </c>
+      <c r="H230" t="n">
+        <v>3</v>
+      </c>
+      <c r="I230" t="n">
+        <v>1</v>
+      </c>
+      <c r="J230" t="n">
+        <v>3</v>
+      </c>
+      <c r="K230" t="n">
+        <v>0</v>
+      </c>
+      <c r="L230" t="n">
         <v>2</v>
-      </c>
-      <c r="G230" t="n">
-        <v>0</v>
-      </c>
-      <c r="H230" t="n">
-        <v>0</v>
-      </c>
-      <c r="I230" t="n">
-        <v>2</v>
-      </c>
-      <c r="J230" t="n">
-        <v>1</v>
-      </c>
-      <c r="K230" t="n">
-        <v>3</v>
-      </c>
-      <c r="L230" t="n">
-        <v>0</v>
       </c>
       <c r="M230" t="n">
         <v>2</v>
@@ -9976,7 +9904,7 @@
       </c>
       <c r="B231" t="inlineStr"/>
       <c r="C231" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D231" t="n">
         <v>1</v>
@@ -9985,7 +9913,7 @@
         <v>1</v>
       </c>
       <c r="F231" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G231" t="n">
         <v>0</v>
@@ -9997,16 +9925,16 @@
         <v>0</v>
       </c>
       <c r="J231" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K231" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L231" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M231" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="232">
@@ -10023,25 +9951,25 @@
         <v>0</v>
       </c>
       <c r="E232" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F232" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G232" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H232" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I232" t="n">
         <v>0</v>
       </c>
       <c r="J232" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K232" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L232" t="n">
         <v>0</v>
@@ -10056,35 +9984,33 @@
           <t>線材</t>
         </is>
       </c>
-      <c r="B233" t="n">
-        <v>0</v>
-      </c>
+      <c r="B233" t="inlineStr"/>
       <c r="C233" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D233" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E233" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F233" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G233" t="n">
         <v>0</v>
       </c>
       <c r="H233" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I233" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J233" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K233" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L233" t="n">
         <v>0</v>
@@ -10099,7 +10025,9 @@
           <t>線材盤元</t>
         </is>
       </c>
-      <c r="B234" t="inlineStr"/>
+      <c r="B234" t="n">
+        <v>0</v>
+      </c>
       <c r="C234" t="n">
         <v>0</v>
       </c>
@@ -10145,7 +10073,7 @@
         <v>1</v>
       </c>
       <c r="D235" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E235" t="n">
         <v>0</v>
@@ -10163,16 +10091,16 @@
         <v>0</v>
       </c>
       <c r="J235" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K235" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L235" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M235" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="236">
@@ -10183,10 +10111,10 @@
       </c>
       <c r="B236" t="inlineStr"/>
       <c r="C236" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D236" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E236" t="n">
         <v>0</v>
@@ -10207,13 +10135,13 @@
         <v>0</v>
       </c>
       <c r="K236" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L236" t="n">
         <v>1</v>
       </c>
       <c r="M236" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="237">
@@ -10248,13 +10176,13 @@
         <v>0</v>
       </c>
       <c r="K237" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L237" t="n">
         <v>1</v>
       </c>
       <c r="M237" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="238">
@@ -10265,16 +10193,16 @@
       </c>
       <c r="B238" t="inlineStr"/>
       <c r="C238" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D238" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E238" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F238" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G238" t="n">
         <v>0</v>
@@ -10292,10 +10220,10 @@
         <v>0</v>
       </c>
       <c r="L238" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M238" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="239">
@@ -10306,25 +10234,25 @@
       </c>
       <c r="B239" t="inlineStr"/>
       <c r="C239" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D239" t="n">
         <v>0</v>
       </c>
       <c r="E239" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F239" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G239" t="n">
         <v>0</v>
       </c>
       <c r="H239" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I239" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J239" t="n">
         <v>0</v>
@@ -10333,10 +10261,10 @@
         <v>0</v>
       </c>
       <c r="L239" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M239" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="240">
@@ -10347,10 +10275,10 @@
       </c>
       <c r="B240" t="inlineStr"/>
       <c r="C240" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D240" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E240" t="n">
         <v>0</v>
@@ -10371,13 +10299,13 @@
         <v>0</v>
       </c>
       <c r="K240" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L240" t="n">
         <v>1</v>
       </c>
       <c r="M240" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="241">
@@ -10412,10 +10340,10 @@
         <v>0</v>
       </c>
       <c r="K241" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L241" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M241" t="n">
         <v>0</v>
@@ -10444,22 +10372,22 @@
         <v>0</v>
       </c>
       <c r="H242" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I242" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J242" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K242" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L242" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M242" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="243">
@@ -10497,10 +10425,10 @@
         <v>0</v>
       </c>
       <c r="L243" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M243" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="244">
@@ -10552,7 +10480,7 @@
       </c>
       <c r="B245" t="inlineStr"/>
       <c r="C245" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D245" t="n">
         <v>0</v>
@@ -10573,10 +10501,10 @@
         <v>0</v>
       </c>
       <c r="J245" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K245" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L245" t="n">
         <v>0</v>
@@ -10591,17 +10519,15 @@
           <t>自然語言處理</t>
         </is>
       </c>
-      <c r="B246" t="n">
-        <v>0</v>
-      </c>
+      <c r="B246" t="inlineStr"/>
       <c r="C246" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D246" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E246" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F246" t="n">
         <v>0</v>
@@ -10616,16 +10542,16 @@
         <v>0</v>
       </c>
       <c r="J246" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K246" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L246" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M246" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="247">
@@ -10636,10 +10562,10 @@
       </c>
       <c r="B247" t="inlineStr"/>
       <c r="C247" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D247" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E247" t="n">
         <v>0</v>
@@ -10660,10 +10586,10 @@
         <v>0</v>
       </c>
       <c r="K247" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L247" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M247" t="n">
         <v>0</v>
@@ -10701,13 +10627,13 @@
         <v>0</v>
       </c>
       <c r="K248" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L248" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M248" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="249">
@@ -10762,7 +10688,7 @@
         <v>1</v>
       </c>
       <c r="D250" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E250" t="n">
         <v>0</v>
@@ -10789,7 +10715,7 @@
         <v>0</v>
       </c>
       <c r="M250" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="251">
@@ -10841,13 +10767,13 @@
       </c>
       <c r="B252" t="inlineStr"/>
       <c r="C252" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D252" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E252" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F252" t="n">
         <v>0</v>
@@ -10862,16 +10788,16 @@
         <v>0</v>
       </c>
       <c r="J252" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K252" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L252" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M252" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="253">
@@ -10970,10 +10896,10 @@
         <v>0</v>
       </c>
       <c r="E255" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F255" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G255" t="n">
         <v>0</v>
@@ -11026,16 +10952,16 @@
         <v>0</v>
       </c>
       <c r="J256" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K256" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L256" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M256" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="257">
@@ -11044,9 +10970,7 @@
           <t>裝置/器材零組件</t>
         </is>
       </c>
-      <c r="B257" t="n">
-        <v>0</v>
-      </c>
+      <c r="B257" t="inlineStr"/>
       <c r="C257" t="n">
         <v>0</v>
       </c>
@@ -11087,20 +11011,40 @@
           <t>裝置/器材顯示器</t>
         </is>
       </c>
-      <c r="B258" t="n">
-        <v>0</v>
-      </c>
-      <c r="C258" t="inlineStr"/>
-      <c r="D258" t="inlineStr"/>
-      <c r="E258" t="inlineStr"/>
-      <c r="F258" t="inlineStr"/>
-      <c r="G258" t="inlineStr"/>
-      <c r="H258" t="inlineStr"/>
-      <c r="I258" t="inlineStr"/>
-      <c r="J258" t="inlineStr"/>
-      <c r="K258" t="inlineStr"/>
-      <c r="L258" t="inlineStr"/>
-      <c r="M258" t="inlineStr"/>
+      <c r="B258" t="inlineStr"/>
+      <c r="C258" t="n">
+        <v>0</v>
+      </c>
+      <c r="D258" t="n">
+        <v>0</v>
+      </c>
+      <c r="E258" t="n">
+        <v>0</v>
+      </c>
+      <c r="F258" t="n">
+        <v>0</v>
+      </c>
+      <c r="G258" t="n">
+        <v>0</v>
+      </c>
+      <c r="H258" t="n">
+        <v>0</v>
+      </c>
+      <c r="I258" t="n">
+        <v>0</v>
+      </c>
+      <c r="J258" t="n">
+        <v>0</v>
+      </c>
+      <c r="K258" t="n">
+        <v>0</v>
+      </c>
+      <c r="L258" t="n">
+        <v>0</v>
+      </c>
+      <c r="M258" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="259">
       <c r="A259" s="1" t="inlineStr">
@@ -11113,7 +11057,7 @@
         <v>1</v>
       </c>
       <c r="D259" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E259" t="n">
         <v>0</v>
@@ -11190,9 +11134,7 @@
           <t>觸控面板</t>
         </is>
       </c>
-      <c r="B261" t="n">
-        <v>0</v>
-      </c>
+      <c r="B261" t="inlineStr"/>
       <c r="C261" t="n">
         <v>0</v>
       </c>
@@ -11221,10 +11163,10 @@
         <v>0</v>
       </c>
       <c r="L261" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M261" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="262">
@@ -11235,37 +11177,37 @@
       </c>
       <c r="B262" t="inlineStr"/>
       <c r="C262" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D262" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E262" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F262" t="n">
+        <v>0</v>
+      </c>
+      <c r="G262" t="n">
+        <v>0</v>
+      </c>
+      <c r="H262" t="n">
+        <v>0</v>
+      </c>
+      <c r="I262" t="n">
+        <v>0</v>
+      </c>
+      <c r="J262" t="n">
+        <v>0</v>
+      </c>
+      <c r="K262" t="n">
+        <v>1</v>
+      </c>
+      <c r="L262" t="n">
+        <v>1</v>
+      </c>
+      <c r="M262" t="n">
         <v>2</v>
-      </c>
-      <c r="G262" t="n">
-        <v>0</v>
-      </c>
-      <c r="H262" t="n">
-        <v>0</v>
-      </c>
-      <c r="I262" t="n">
-        <v>0</v>
-      </c>
-      <c r="J262" t="n">
-        <v>0</v>
-      </c>
-      <c r="K262" t="n">
-        <v>0</v>
-      </c>
-      <c r="L262" t="n">
-        <v>1</v>
-      </c>
-      <c r="M262" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="263">
@@ -11276,10 +11218,10 @@
       </c>
       <c r="B263" t="inlineStr"/>
       <c r="C263" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D263" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E263" t="n">
         <v>0</v>
@@ -11288,13 +11230,13 @@
         <v>0</v>
       </c>
       <c r="G263" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H263" t="n">
         <v>1</v>
       </c>
       <c r="I263" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J263" t="n">
         <v>0</v>
@@ -11306,7 +11248,7 @@
         <v>0</v>
       </c>
       <c r="M263" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="264">
@@ -11317,13 +11259,13 @@
       </c>
       <c r="B264" t="inlineStr"/>
       <c r="C264" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D264" t="n">
         <v>1</v>
       </c>
       <c r="E264" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F264" t="n">
         <v>0</v>
@@ -11332,19 +11274,19 @@
         <v>0</v>
       </c>
       <c r="H264" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I264" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J264" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K264" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L264" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M264" t="n">
         <v>1</v>
@@ -11397,9 +11339,7 @@
           <t>證券業</t>
         </is>
       </c>
-      <c r="B266" t="n">
-        <v>0</v>
-      </c>
+      <c r="B266" t="inlineStr"/>
       <c r="C266" t="n">
         <v>0</v>
       </c>
@@ -11454,10 +11394,10 @@
         <v>0</v>
       </c>
       <c r="G267" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H267" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I267" t="n">
         <v>0</v>
@@ -11522,9 +11462,7 @@
           <t>貨櫃運輸集散及倉儲</t>
         </is>
       </c>
-      <c r="B269" t="n">
-        <v>0</v>
-      </c>
+      <c r="B269" t="inlineStr"/>
       <c r="C269" t="n">
         <v>0</v>
       </c>
@@ -11550,13 +11488,13 @@
         <v>0</v>
       </c>
       <c r="K269" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L269" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M269" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="270">
@@ -11570,10 +11508,10 @@
         <v>0</v>
       </c>
       <c r="D270" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E270" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F270" t="n">
         <v>0</v>
@@ -11582,19 +11520,19 @@
         <v>0</v>
       </c>
       <c r="H270" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I270" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J270" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K270" t="n">
         <v>1</v>
       </c>
       <c r="L270" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M270" t="n">
         <v>0</v>
@@ -11649,16 +11587,16 @@
       </c>
       <c r="B272" t="inlineStr"/>
       <c r="C272" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D272" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E272" t="n">
         <v>1</v>
       </c>
       <c r="F272" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G272" t="n">
         <v>0</v>
@@ -11670,16 +11608,16 @@
         <v>0</v>
       </c>
       <c r="J272" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K272" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L272" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M272" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="273">
@@ -11690,13 +11628,13 @@
       </c>
       <c r="B273" t="inlineStr"/>
       <c r="C273" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D273" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E273" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F273" t="n">
         <v>0</v>
@@ -11711,16 +11649,16 @@
         <v>0</v>
       </c>
       <c r="J273" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K273" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L273" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M273" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="274">
@@ -11731,16 +11669,16 @@
       </c>
       <c r="B274" t="inlineStr"/>
       <c r="C274" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D274" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E274" t="n">
         <v>1</v>
       </c>
       <c r="F274" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G274" t="n">
         <v>0</v>
@@ -11752,16 +11690,16 @@
         <v>0</v>
       </c>
       <c r="J274" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K274" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L274" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M274" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="275">
@@ -11772,13 +11710,13 @@
       </c>
       <c r="B275" t="inlineStr"/>
       <c r="C275" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D275" t="n">
         <v>1</v>
       </c>
       <c r="E275" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F275" t="n">
         <v>0</v>
@@ -11793,13 +11731,13 @@
         <v>0</v>
       </c>
       <c r="J275" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K275" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L275" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M275" t="n">
         <v>1</v>
@@ -11813,16 +11751,16 @@
       </c>
       <c r="B276" t="inlineStr"/>
       <c r="C276" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D276" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E276" t="n">
         <v>1</v>
       </c>
       <c r="F276" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G276" t="n">
         <v>0</v>
@@ -11834,16 +11772,16 @@
         <v>0</v>
       </c>
       <c r="J276" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K276" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L276" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M276" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="277">
@@ -11901,7 +11839,7 @@
         <v>1</v>
       </c>
       <c r="E278" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F278" t="n">
         <v>0</v>
@@ -11916,16 +11854,16 @@
         <v>0</v>
       </c>
       <c r="J278" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K278" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L278" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M278" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="279">
@@ -11934,14 +11872,12 @@
           <t>資料庫</t>
         </is>
       </c>
-      <c r="B279" t="n">
-        <v>0</v>
-      </c>
+      <c r="B279" t="inlineStr"/>
       <c r="C279" t="n">
         <v>1</v>
       </c>
       <c r="D279" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E279" t="n">
         <v>0</v>
@@ -11968,7 +11904,7 @@
         <v>0</v>
       </c>
       <c r="M279" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="280">
@@ -12018,20 +11954,18 @@
           <t>資料處理</t>
         </is>
       </c>
-      <c r="B281" t="n">
-        <v>0</v>
-      </c>
+      <c r="B281" t="inlineStr"/>
       <c r="C281" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D281" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E281" t="n">
         <v>1</v>
       </c>
       <c r="F281" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G281" t="n">
         <v>0</v>
@@ -12043,16 +11977,16 @@
         <v>0</v>
       </c>
       <c r="J281" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K281" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L281" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M281" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="282">
@@ -12090,10 +12024,10 @@
         <v>0</v>
       </c>
       <c r="L282" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M282" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="283">
@@ -12274,7 +12208,7 @@
         <v>1</v>
       </c>
       <c r="E287" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F287" t="n">
         <v>0</v>
@@ -12289,16 +12223,16 @@
         <v>0</v>
       </c>
       <c r="J287" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K287" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L287" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M287" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="288">
@@ -12307,9 +12241,7 @@
           <t>車燈</t>
         </is>
       </c>
-      <c r="B288" t="n">
-        <v>0</v>
-      </c>
+      <c r="B288" t="inlineStr"/>
       <c r="C288" t="n">
         <v>0</v>
       </c>
@@ -12367,10 +12299,10 @@
         <v>0</v>
       </c>
       <c r="H289" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I289" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J289" t="n">
         <v>0</v>
@@ -12475,7 +12407,7 @@
       </c>
       <c r="B292" t="inlineStr"/>
       <c r="C292" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D292" t="n">
         <v>0</v>
@@ -12557,7 +12489,7 @@
       </c>
       <c r="B294" t="inlineStr"/>
       <c r="C294" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D294" t="n">
         <v>0</v>
@@ -12587,7 +12519,7 @@
         <v>0</v>
       </c>
       <c r="M294" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="295">
@@ -12596,9 +12528,7 @@
           <t>輸送機械及零配件</t>
         </is>
       </c>
-      <c r="B295" t="n">
-        <v>0</v>
-      </c>
+      <c r="B295" t="inlineStr"/>
       <c r="C295" t="n">
         <v>0</v>
       </c>
@@ -12615,10 +12545,10 @@
         <v>0</v>
       </c>
       <c r="H295" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I295" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J295" t="n">
         <v>0</v>
@@ -12639,14 +12569,12 @@
           <t>農業科技業</t>
         </is>
       </c>
-      <c r="B296" t="n">
-        <v>0</v>
-      </c>
+      <c r="B296" t="inlineStr"/>
       <c r="C296" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D296" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E296" t="n">
         <v>0</v>
@@ -12667,13 +12595,13 @@
         <v>0</v>
       </c>
       <c r="K296" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L296" t="n">
         <v>1</v>
       </c>
       <c r="M296" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="297">
@@ -12723,9 +12651,7 @@
           <t>近眼顯示(Dear-Eye Display)</t>
         </is>
       </c>
-      <c r="B298" t="n">
-        <v>0</v>
-      </c>
+      <c r="B298" t="inlineStr"/>
       <c r="C298" t="n">
         <v>0</v>
       </c>
@@ -12751,13 +12677,13 @@
         <v>0</v>
       </c>
       <c r="K298" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L298" t="n">
         <v>1</v>
       </c>
       <c r="M298" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="299">
@@ -12850,13 +12776,13 @@
       </c>
       <c r="B301" t="inlineStr"/>
       <c r="C301" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D301" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E301" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F301" t="n">
         <v>0</v>
@@ -12871,16 +12797,16 @@
         <v>0</v>
       </c>
       <c r="J301" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K301" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L301" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M301" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="302">
@@ -12889,41 +12815,39 @@
           <t>連接器設計、組裝及製造</t>
         </is>
       </c>
-      <c r="B302" t="n">
-        <v>0</v>
-      </c>
+      <c r="B302" t="inlineStr"/>
       <c r="C302" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D302" t="n">
+        <v>1</v>
+      </c>
+      <c r="E302" t="n">
         <v>2</v>
       </c>
-      <c r="E302" t="n">
-        <v>1</v>
-      </c>
       <c r="F302" t="n">
+        <v>0</v>
+      </c>
+      <c r="G302" t="n">
+        <v>0</v>
+      </c>
+      <c r="H302" t="n">
+        <v>1</v>
+      </c>
+      <c r="I302" t="n">
+        <v>0</v>
+      </c>
+      <c r="J302" t="n">
         <v>2</v>
-      </c>
-      <c r="G302" t="n">
-        <v>0</v>
-      </c>
-      <c r="H302" t="n">
-        <v>0</v>
-      </c>
-      <c r="I302" t="n">
-        <v>1</v>
-      </c>
-      <c r="J302" t="n">
-        <v>0</v>
       </c>
       <c r="K302" t="n">
         <v>2</v>
       </c>
       <c r="L302" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M302" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="303">
@@ -12932,38 +12856,36 @@
           <t>連接線</t>
         </is>
       </c>
-      <c r="B303" t="n">
-        <v>0</v>
-      </c>
+      <c r="B303" t="inlineStr"/>
       <c r="C303" t="n">
         <v>3</v>
       </c>
       <c r="D303" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E303" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F303" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G303" t="n">
         <v>0</v>
       </c>
       <c r="H303" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I303" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J303" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K303" t="n">
         <v>1</v>
       </c>
       <c r="L303" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M303" t="n">
         <v>0</v>
@@ -13098,14 +13020,12 @@
           <t>運算元件與設備</t>
         </is>
       </c>
-      <c r="B307" t="n">
-        <v>0</v>
-      </c>
+      <c r="B307" t="inlineStr"/>
       <c r="C307" t="n">
         <v>1</v>
       </c>
       <c r="D307" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E307" t="n">
         <v>0</v>
@@ -13117,10 +13037,10 @@
         <v>0</v>
       </c>
       <c r="H307" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I307" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J307" t="n">
         <v>0</v>
@@ -13132,7 +13052,7 @@
         <v>0</v>
       </c>
       <c r="M307" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="308">
@@ -13141,9 +13061,7 @@
           <t>運算設備</t>
         </is>
       </c>
-      <c r="B308" t="n">
-        <v>0</v>
-      </c>
+      <c r="B308" t="inlineStr"/>
       <c r="C308" t="n">
         <v>0</v>
       </c>
@@ -13160,10 +13078,10 @@
         <v>0</v>
       </c>
       <c r="H308" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I308" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J308" t="n">
         <v>0</v>
@@ -13172,7 +13090,7 @@
         <v>0</v>
       </c>
       <c r="L308" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M308" t="n">
         <v>1</v>
@@ -13225,14 +13143,12 @@
           <t>配電管理設施</t>
         </is>
       </c>
-      <c r="B310" t="n">
-        <v>0</v>
-      </c>
+      <c r="B310" t="inlineStr"/>
       <c r="C310" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D310" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E310" t="n">
         <v>0</v>
@@ -13241,13 +13157,13 @@
         <v>0</v>
       </c>
       <c r="G310" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H310" t="n">
         <v>1</v>
       </c>
       <c r="I310" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J310" t="n">
         <v>0</v>
@@ -13282,10 +13198,10 @@
         <v>0</v>
       </c>
       <c r="G311" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H311" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I311" t="n">
         <v>0</v>
@@ -13314,7 +13230,7 @@
         <v>1</v>
       </c>
       <c r="D312" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E312" t="n">
         <v>0</v>
@@ -13341,7 +13257,7 @@
         <v>0</v>
       </c>
       <c r="M312" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="313">
@@ -13355,7 +13271,7 @@
         <v>1</v>
       </c>
       <c r="D313" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E313" t="n">
         <v>0</v>
@@ -13367,22 +13283,22 @@
         <v>0</v>
       </c>
       <c r="H313" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I313" t="n">
+        <v>1</v>
+      </c>
+      <c r="J313" t="n">
+        <v>0</v>
+      </c>
+      <c r="K313" t="n">
         <v>2</v>
       </c>
-      <c r="J313" t="n">
-        <v>1</v>
-      </c>
-      <c r="K313" t="n">
-        <v>0</v>
-      </c>
       <c r="L313" t="n">
+        <v>0</v>
+      </c>
+      <c r="M313" t="n">
         <v>2</v>
-      </c>
-      <c r="M313" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="314">
@@ -13393,37 +13309,37 @@
       </c>
       <c r="B314" t="inlineStr"/>
       <c r="C314" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D314" t="n">
         <v>0</v>
       </c>
       <c r="E314" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F314" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G314" t="n">
         <v>0</v>
       </c>
       <c r="H314" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I314" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J314" t="n">
         <v>0</v>
       </c>
       <c r="K314" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L314" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M314" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="315">
@@ -13458,10 +13374,10 @@
         <v>0</v>
       </c>
       <c r="K315" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L315" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M315" t="n">
         <v>0</v>
@@ -13473,17 +13389,15 @@
           <t>金屬、塑膠模具</t>
         </is>
       </c>
-      <c r="B316" t="n">
-        <v>0</v>
-      </c>
+      <c r="B316" t="inlineStr"/>
       <c r="C316" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D316" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E316" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F316" t="n">
         <v>0</v>
@@ -13498,10 +13412,10 @@
         <v>0</v>
       </c>
       <c r="J316" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K316" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L316" t="n">
         <v>0</v>
@@ -13545,10 +13459,10 @@
         <v>0</v>
       </c>
       <c r="L317" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M317" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="318">
@@ -13557,7 +13471,9 @@
           <t>金屬加工處理</t>
         </is>
       </c>
-      <c r="B318" t="inlineStr"/>
+      <c r="B318" t="n">
+        <v>0</v>
+      </c>
       <c r="C318" t="n">
         <v>0</v>
       </c>
@@ -13568,7 +13484,7 @@
         <v>0</v>
       </c>
       <c r="F318" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G318" t="n">
         <v>0</v>
@@ -13586,10 +13502,10 @@
         <v>0</v>
       </c>
       <c r="L318" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M318" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="319">
@@ -13598,9 +13514,7 @@
           <t>金屬材料</t>
         </is>
       </c>
-      <c r="B319" t="n">
-        <v>0</v>
-      </c>
+      <c r="B319" t="inlineStr"/>
       <c r="C319" t="n">
         <v>0</v>
       </c>
@@ -13682,9 +13596,7 @@
           <t>金控業/銀行業/保險業</t>
         </is>
       </c>
-      <c r="B321" t="n">
-        <v>0</v>
-      </c>
+      <c r="B321" t="inlineStr"/>
       <c r="C321" t="n">
         <v>0</v>
       </c>
@@ -13795,10 +13707,10 @@
         <v>0</v>
       </c>
       <c r="L323" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M323" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="324">
@@ -13853,7 +13765,7 @@
         <v>1</v>
       </c>
       <c r="D325" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E325" t="n">
         <v>0</v>
@@ -13865,10 +13777,10 @@
         <v>0</v>
       </c>
       <c r="H325" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I325" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J325" t="n">
         <v>0</v>
@@ -13880,7 +13792,7 @@
         <v>0</v>
       </c>
       <c r="M325" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="326">
@@ -13889,41 +13801,39 @@
           <t>銅箔基板</t>
         </is>
       </c>
-      <c r="B326" t="n">
-        <v>0</v>
-      </c>
+      <c r="B326" t="inlineStr"/>
       <c r="C326" t="n">
+        <v>1</v>
+      </c>
+      <c r="D326" t="n">
+        <v>0</v>
+      </c>
+      <c r="E326" t="n">
+        <v>0</v>
+      </c>
+      <c r="F326" t="n">
+        <v>0</v>
+      </c>
+      <c r="G326" t="n">
+        <v>0</v>
+      </c>
+      <c r="H326" t="n">
+        <v>5</v>
+      </c>
+      <c r="I326" t="n">
+        <v>0</v>
+      </c>
+      <c r="J326" t="n">
+        <v>2</v>
+      </c>
+      <c r="K326" t="n">
         <v>4</v>
       </c>
-      <c r="D326" t="n">
-        <v>1</v>
-      </c>
-      <c r="E326" t="n">
-        <v>0</v>
-      </c>
-      <c r="F326" t="n">
-        <v>0</v>
-      </c>
-      <c r="G326" t="n">
-        <v>0</v>
-      </c>
-      <c r="H326" t="n">
-        <v>0</v>
-      </c>
-      <c r="I326" t="n">
-        <v>5</v>
-      </c>
-      <c r="J326" t="n">
-        <v>0</v>
-      </c>
-      <c r="K326" t="n">
-        <v>2</v>
-      </c>
       <c r="L326" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M326" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="327">
@@ -13937,10 +13847,10 @@
         <v>0</v>
       </c>
       <c r="D327" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E327" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F327" t="n">
         <v>0</v>
@@ -14016,25 +13926,25 @@
       </c>
       <c r="B329" t="inlineStr"/>
       <c r="C329" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D329" t="n">
         <v>1</v>
       </c>
       <c r="E329" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F329" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G329" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H329" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I329" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J329" t="n">
         <v>0</v>
@@ -14139,10 +14049,10 @@
       </c>
       <c r="B332" t="inlineStr"/>
       <c r="C332" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D332" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E332" t="n">
         <v>0</v>
@@ -14219,7 +14129,9 @@
           <t>鋼鑄鐵元件</t>
         </is>
       </c>
-      <c r="B334" t="inlineStr"/>
+      <c r="B334" t="n">
+        <v>0</v>
+      </c>
       <c r="C334" t="n">
         <v>0</v>
       </c>
@@ -14230,7 +14142,7 @@
         <v>0</v>
       </c>
       <c r="F334" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G334" t="n">
         <v>0</v>
@@ -14303,7 +14215,7 @@
       </c>
       <c r="B336" t="inlineStr"/>
       <c r="C336" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D336" t="n">
         <v>0</v>
@@ -14344,10 +14256,10 @@
       </c>
       <c r="B337" t="inlineStr"/>
       <c r="C337" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D337" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E337" t="n">
         <v>0</v>
@@ -14368,10 +14280,10 @@
         <v>0</v>
       </c>
       <c r="K337" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L337" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M337" t="n">
         <v>0</v>
@@ -14388,7 +14300,7 @@
         <v>1</v>
       </c>
       <c r="D338" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E338" t="n">
         <v>0</v>
@@ -14415,7 +14327,7 @@
         <v>0</v>
       </c>
       <c r="M338" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="339">
@@ -14426,7 +14338,7 @@
       </c>
       <c r="B339" t="inlineStr"/>
       <c r="C339" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D339" t="n">
         <v>1</v>
@@ -14435,7 +14347,7 @@
         <v>1</v>
       </c>
       <c r="F339" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G339" t="n">
         <v>0</v>
@@ -14447,16 +14359,16 @@
         <v>0</v>
       </c>
       <c r="J339" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K339" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L339" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M339" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="340">
@@ -14465,41 +14377,39 @@
           <t>雲端平台</t>
         </is>
       </c>
-      <c r="B340" t="n">
-        <v>0</v>
-      </c>
+      <c r="B340" t="inlineStr"/>
       <c r="C340" t="n">
+        <v>1</v>
+      </c>
+      <c r="D340" t="n">
+        <v>1</v>
+      </c>
+      <c r="E340" t="n">
+        <v>0</v>
+      </c>
+      <c r="F340" t="n">
+        <v>0</v>
+      </c>
+      <c r="G340" t="n">
+        <v>0</v>
+      </c>
+      <c r="H340" t="n">
+        <v>0</v>
+      </c>
+      <c r="I340" t="n">
+        <v>0</v>
+      </c>
+      <c r="J340" t="n">
+        <v>1</v>
+      </c>
+      <c r="K340" t="n">
+        <v>0</v>
+      </c>
+      <c r="L340" t="n">
+        <v>1</v>
+      </c>
+      <c r="M340" t="n">
         <v>3</v>
-      </c>
-      <c r="D340" t="n">
-        <v>1</v>
-      </c>
-      <c r="E340" t="n">
-        <v>1</v>
-      </c>
-      <c r="F340" t="n">
-        <v>0</v>
-      </c>
-      <c r="G340" t="n">
-        <v>0</v>
-      </c>
-      <c r="H340" t="n">
-        <v>0</v>
-      </c>
-      <c r="I340" t="n">
-        <v>0</v>
-      </c>
-      <c r="J340" t="n">
-        <v>0</v>
-      </c>
-      <c r="K340" t="n">
-        <v>1</v>
-      </c>
-      <c r="L340" t="n">
-        <v>0</v>
-      </c>
-      <c r="M340" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="341">
@@ -14510,37 +14420,37 @@
       </c>
       <c r="B341" t="inlineStr"/>
       <c r="C341" t="n">
+        <v>1</v>
+      </c>
+      <c r="D341" t="n">
+        <v>1</v>
+      </c>
+      <c r="E341" t="n">
+        <v>0</v>
+      </c>
+      <c r="F341" t="n">
+        <v>0</v>
+      </c>
+      <c r="G341" t="n">
+        <v>0</v>
+      </c>
+      <c r="H341" t="n">
+        <v>1</v>
+      </c>
+      <c r="I341" t="n">
+        <v>0</v>
+      </c>
+      <c r="J341" t="n">
+        <v>1</v>
+      </c>
+      <c r="K341" t="n">
+        <v>0</v>
+      </c>
+      <c r="L341" t="n">
+        <v>1</v>
+      </c>
+      <c r="M341" t="n">
         <v>2</v>
-      </c>
-      <c r="D341" t="n">
-        <v>1</v>
-      </c>
-      <c r="E341" t="n">
-        <v>1</v>
-      </c>
-      <c r="F341" t="n">
-        <v>0</v>
-      </c>
-      <c r="G341" t="n">
-        <v>0</v>
-      </c>
-      <c r="H341" t="n">
-        <v>0</v>
-      </c>
-      <c r="I341" t="n">
-        <v>1</v>
-      </c>
-      <c r="J341" t="n">
-        <v>0</v>
-      </c>
-      <c r="K341" t="n">
-        <v>1</v>
-      </c>
-      <c r="L341" t="n">
-        <v>0</v>
-      </c>
-      <c r="M341" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="342">
@@ -14560,22 +14470,22 @@
         <v>0</v>
       </c>
       <c r="F342" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G342" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H342" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I342" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J342" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K342" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L342" t="n">
         <v>0</v>
@@ -14592,34 +14502,34 @@
       </c>
       <c r="B343" t="inlineStr"/>
       <c r="C343" t="n">
+        <v>0</v>
+      </c>
+      <c r="D343" t="n">
+        <v>0</v>
+      </c>
+      <c r="E343" t="n">
+        <v>0</v>
+      </c>
+      <c r="F343" t="n">
+        <v>0</v>
+      </c>
+      <c r="G343" t="n">
+        <v>0</v>
+      </c>
+      <c r="H343" t="n">
+        <v>1</v>
+      </c>
+      <c r="I343" t="n">
+        <v>0</v>
+      </c>
+      <c r="J343" t="n">
+        <v>1</v>
+      </c>
+      <c r="K343" t="n">
         <v>2</v>
       </c>
-      <c r="D343" t="n">
-        <v>0</v>
-      </c>
-      <c r="E343" t="n">
-        <v>0</v>
-      </c>
-      <c r="F343" t="n">
-        <v>0</v>
-      </c>
-      <c r="G343" t="n">
-        <v>0</v>
-      </c>
-      <c r="H343" t="n">
-        <v>0</v>
-      </c>
-      <c r="I343" t="n">
-        <v>1</v>
-      </c>
-      <c r="J343" t="n">
-        <v>0</v>
-      </c>
-      <c r="K343" t="n">
-        <v>1</v>
-      </c>
       <c r="L343" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M343" t="n">
         <v>0</v>
@@ -14633,10 +14543,10 @@
       </c>
       <c r="B344" t="inlineStr"/>
       <c r="C344" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D344" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E344" t="n">
         <v>0</v>
@@ -14686,13 +14596,13 @@
         <v>0</v>
       </c>
       <c r="G345" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H345" t="n">
         <v>1</v>
       </c>
       <c r="I345" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J345" t="n">
         <v>0</v>
@@ -14713,14 +14623,12 @@
           <t>電力設備</t>
         </is>
       </c>
-      <c r="B346" t="n">
-        <v>0</v>
-      </c>
+      <c r="B346" t="inlineStr"/>
       <c r="C346" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D346" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E346" t="n">
         <v>0</v>
@@ -14729,13 +14637,13 @@
         <v>0</v>
       </c>
       <c r="G346" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H346" t="n">
         <v>1</v>
       </c>
       <c r="I346" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J346" t="n">
         <v>0</v>
@@ -14744,7 +14652,7 @@
         <v>0</v>
       </c>
       <c r="L346" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M346" t="n">
         <v>1</v>
@@ -14785,10 +14693,10 @@
         <v>0</v>
       </c>
       <c r="L347" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M347" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="348">
@@ -14802,10 +14710,10 @@
         <v>0</v>
       </c>
       <c r="D348" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E348" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F348" t="n">
         <v>0</v>
@@ -14814,10 +14722,10 @@
         <v>0</v>
       </c>
       <c r="H348" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I348" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J348" t="n">
         <v>0</v>
@@ -14826,10 +14734,10 @@
         <v>0</v>
       </c>
       <c r="L348" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M348" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="349">
@@ -14855,10 +14763,10 @@
         <v>0</v>
       </c>
       <c r="H349" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I349" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J349" t="n">
         <v>0</v>
@@ -14920,9 +14828,7 @@
           <t>電子零組件、塑膠零件、五金零件</t>
         </is>
       </c>
-      <c r="B351" t="n">
-        <v>0</v>
-      </c>
+      <c r="B351" t="inlineStr"/>
       <c r="C351" t="n">
         <v>1</v>
       </c>
@@ -14933,25 +14839,25 @@
         <v>1</v>
       </c>
       <c r="F351" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G351" t="n">
         <v>0</v>
       </c>
       <c r="H351" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I351" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J351" t="n">
         <v>0</v>
       </c>
       <c r="K351" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L351" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M351" t="n">
         <v>0</v>
@@ -14963,39 +14869,41 @@
           <t>電容器</t>
         </is>
       </c>
-      <c r="B352" t="inlineStr"/>
+      <c r="B352" t="n">
+        <v>0</v>
+      </c>
       <c r="C352" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D352" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E352" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F352" t="n">
         <v>0</v>
       </c>
       <c r="G352" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H352" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I352" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J352" t="n">
         <v>2</v>
       </c>
       <c r="K352" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L352" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M352" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="353">
@@ -15006,10 +14914,10 @@
       </c>
       <c r="B353" t="inlineStr"/>
       <c r="C353" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D353" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E353" t="n">
         <v>0</v>
@@ -15018,10 +14926,10 @@
         <v>0</v>
       </c>
       <c r="G353" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H353" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I353" t="n">
         <v>0</v>
@@ -15045,27 +14953,29 @@
           <t>電感器</t>
         </is>
       </c>
-      <c r="B354" t="inlineStr"/>
+      <c r="B354" t="n">
+        <v>0</v>
+      </c>
       <c r="C354" t="n">
         <v>2</v>
       </c>
       <c r="D354" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E354" t="n">
+        <v>0</v>
+      </c>
+      <c r="F354" t="n">
+        <v>0</v>
+      </c>
+      <c r="G354" t="n">
         <v>2</v>
       </c>
-      <c r="F354" t="n">
-        <v>0</v>
-      </c>
-      <c r="G354" t="n">
-        <v>0</v>
-      </c>
       <c r="H354" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I354" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J354" t="n">
         <v>0</v>
@@ -15077,7 +14987,7 @@
         <v>0</v>
       </c>
       <c r="M354" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="355">
@@ -15090,13 +15000,13 @@
         <v>0</v>
       </c>
       <c r="C355" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D355" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E355" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F355" t="n">
         <v>0</v>
@@ -15129,29 +15039,27 @@
           <t>電控元件</t>
         </is>
       </c>
-      <c r="B356" t="n">
-        <v>0</v>
-      </c>
+      <c r="B356" t="inlineStr"/>
       <c r="C356" t="n">
+        <v>1</v>
+      </c>
+      <c r="D356" t="n">
+        <v>0</v>
+      </c>
+      <c r="E356" t="n">
+        <v>0</v>
+      </c>
+      <c r="F356" t="n">
+        <v>0</v>
+      </c>
+      <c r="G356" t="n">
+        <v>0</v>
+      </c>
+      <c r="H356" t="n">
         <v>2</v>
       </c>
-      <c r="D356" t="n">
-        <v>1</v>
-      </c>
-      <c r="E356" t="n">
-        <v>0</v>
-      </c>
-      <c r="F356" t="n">
-        <v>0</v>
-      </c>
-      <c r="G356" t="n">
-        <v>0</v>
-      </c>
-      <c r="H356" t="n">
-        <v>0</v>
-      </c>
       <c r="I356" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J356" t="n">
         <v>0</v>
@@ -15163,7 +15071,7 @@
         <v>0</v>
       </c>
       <c r="M356" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="357">
@@ -15174,7 +15082,7 @@
       </c>
       <c r="B357" t="inlineStr"/>
       <c r="C357" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D357" t="n">
         <v>0</v>
@@ -15189,10 +15097,10 @@
         <v>0</v>
       </c>
       <c r="H357" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I357" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J357" t="n">
         <v>0</v>
@@ -15201,7 +15109,7 @@
         <v>0</v>
       </c>
       <c r="L357" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M357" t="n">
         <v>1</v>
@@ -15213,9 +15121,7 @@
           <t>電池模組</t>
         </is>
       </c>
-      <c r="B358" t="n">
-        <v>0</v>
-      </c>
+      <c r="B358" t="inlineStr"/>
       <c r="C358" t="n">
         <v>0</v>
       </c>
@@ -15226,16 +15132,16 @@
         <v>0</v>
       </c>
       <c r="F358" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G358" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H358" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I358" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J358" t="n">
         <v>0</v>
@@ -15244,7 +15150,7 @@
         <v>0</v>
       </c>
       <c r="L358" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M358" t="n">
         <v>1</v>
@@ -15267,16 +15173,16 @@
         <v>0</v>
       </c>
       <c r="F359" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G359" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H359" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I359" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J359" t="n">
         <v>0</v>
@@ -15299,34 +15205,34 @@
       </c>
       <c r="B360" t="inlineStr"/>
       <c r="C360" t="n">
+        <v>1</v>
+      </c>
+      <c r="D360" t="n">
+        <v>1</v>
+      </c>
+      <c r="E360" t="n">
+        <v>0</v>
+      </c>
+      <c r="F360" t="n">
+        <v>0</v>
+      </c>
+      <c r="G360" t="n">
+        <v>1</v>
+      </c>
+      <c r="H360" t="n">
+        <v>1</v>
+      </c>
+      <c r="I360" t="n">
+        <v>0</v>
+      </c>
+      <c r="J360" t="n">
         <v>2</v>
-      </c>
-      <c r="D360" t="n">
-        <v>1</v>
-      </c>
-      <c r="E360" t="n">
-        <v>1</v>
-      </c>
-      <c r="F360" t="n">
-        <v>0</v>
-      </c>
-      <c r="G360" t="n">
-        <v>0</v>
-      </c>
-      <c r="H360" t="n">
-        <v>1</v>
-      </c>
-      <c r="I360" t="n">
-        <v>1</v>
-      </c>
-      <c r="J360" t="n">
-        <v>0</v>
       </c>
       <c r="K360" t="n">
         <v>2</v>
       </c>
       <c r="L360" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M360" t="n">
         <v>1</v>
@@ -15352,10 +15258,10 @@
         <v>0</v>
       </c>
       <c r="G361" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H361" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I361" t="n">
         <v>0</v>
@@ -15422,10 +15328,10 @@
       </c>
       <c r="B363" t="inlineStr"/>
       <c r="C363" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D363" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E363" t="n">
         <v>0</v>
@@ -15461,29 +15367,27 @@
           <t>電腦視覺</t>
         </is>
       </c>
-      <c r="B364" t="n">
-        <v>0</v>
-      </c>
+      <c r="B364" t="inlineStr"/>
       <c r="C364" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D364" t="n">
         <v>0</v>
       </c>
       <c r="E364" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F364" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G364" t="n">
         <v>0</v>
       </c>
       <c r="H364" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I364" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J364" t="n">
         <v>0</v>
@@ -15506,37 +15410,37 @@
       </c>
       <c r="B365" t="inlineStr"/>
       <c r="C365" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D365" t="n">
+        <v>0</v>
+      </c>
+      <c r="E365" t="n">
+        <v>0</v>
+      </c>
+      <c r="F365" t="n">
+        <v>0</v>
+      </c>
+      <c r="G365" t="n">
+        <v>0</v>
+      </c>
+      <c r="H365" t="n">
         <v>2</v>
       </c>
-      <c r="E365" t="n">
-        <v>0</v>
-      </c>
-      <c r="F365" t="n">
-        <v>0</v>
-      </c>
-      <c r="G365" t="n">
-        <v>0</v>
-      </c>
-      <c r="H365" t="n">
-        <v>0</v>
-      </c>
       <c r="I365" t="n">
+        <v>0</v>
+      </c>
+      <c r="J365" t="n">
+        <v>0</v>
+      </c>
+      <c r="K365" t="n">
+        <v>1</v>
+      </c>
+      <c r="L365" t="n">
+        <v>1</v>
+      </c>
+      <c r="M365" t="n">
         <v>2</v>
-      </c>
-      <c r="J365" t="n">
-        <v>0</v>
-      </c>
-      <c r="K365" t="n">
-        <v>0</v>
-      </c>
-      <c r="L365" t="n">
-        <v>1</v>
-      </c>
-      <c r="M365" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="366">
@@ -15586,9 +15490,7 @@
           <t>電鍍材料</t>
         </is>
       </c>
-      <c r="B367" t="n">
-        <v>0</v>
-      </c>
+      <c r="B367" t="inlineStr"/>
       <c r="C367" t="n">
         <v>0</v>
       </c>
@@ -15629,29 +15531,27 @@
           <t>電阻器</t>
         </is>
       </c>
-      <c r="B368" t="n">
-        <v>0</v>
-      </c>
+      <c r="B368" t="inlineStr"/>
       <c r="C368" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D368" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E368" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F368" t="n">
         <v>0</v>
       </c>
       <c r="G368" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H368" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I368" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J368" t="n">
         <v>0</v>
@@ -15674,7 +15574,7 @@
       </c>
       <c r="B369" t="inlineStr"/>
       <c r="C369" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D369" t="n">
         <v>0</v>
@@ -15717,7 +15617,7 @@
         <v>0</v>
       </c>
       <c r="C370" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D370" t="n">
         <v>0</v>
@@ -15732,10 +15632,10 @@
         <v>0</v>
       </c>
       <c r="H370" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I370" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J370" t="n">
         <v>0</v>
@@ -15838,11 +15738,9 @@
           <t>領域解決方案</t>
         </is>
       </c>
-      <c r="B373" t="n">
-        <v>0</v>
-      </c>
+      <c r="B373" t="inlineStr"/>
       <c r="C373" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D373" t="n">
         <v>1</v>
@@ -15851,28 +15749,28 @@
         <v>1</v>
       </c>
       <c r="F373" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G373" t="n">
         <v>0</v>
       </c>
       <c r="H373" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I373" t="n">
+        <v>1</v>
+      </c>
+      <c r="J373" t="n">
+        <v>1</v>
+      </c>
+      <c r="K373" t="n">
+        <v>1</v>
+      </c>
+      <c r="L373" t="n">
         <v>2</v>
       </c>
-      <c r="J373" t="n">
-        <v>1</v>
-      </c>
-      <c r="K373" t="n">
-        <v>1</v>
-      </c>
-      <c r="L373" t="n">
-        <v>1</v>
-      </c>
       <c r="M373" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="374">
@@ -15883,7 +15781,7 @@
       </c>
       <c r="B374" t="inlineStr"/>
       <c r="C374" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D374" t="n">
         <v>0</v>
@@ -15924,10 +15822,10 @@
       </c>
       <c r="B375" t="inlineStr"/>
       <c r="C375" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D375" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E375" t="n">
         <v>0</v>
@@ -15963,38 +15861,36 @@
           <t>顧問諮詢</t>
         </is>
       </c>
-      <c r="B376" t="n">
-        <v>0</v>
-      </c>
+      <c r="B376" t="inlineStr"/>
       <c r="C376" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D376" t="n">
+        <v>2</v>
+      </c>
+      <c r="E376" t="n">
+        <v>0</v>
+      </c>
+      <c r="F376" t="n">
+        <v>0</v>
+      </c>
+      <c r="G376" t="n">
+        <v>1</v>
+      </c>
+      <c r="H376" t="n">
         <v>3</v>
       </c>
-      <c r="E376" t="n">
+      <c r="I376" t="n">
+        <v>0</v>
+      </c>
+      <c r="J376" t="n">
         <v>2</v>
       </c>
-      <c r="F376" t="n">
-        <v>0</v>
-      </c>
-      <c r="G376" t="n">
-        <v>0</v>
-      </c>
-      <c r="H376" t="n">
-        <v>1</v>
-      </c>
-      <c r="I376" t="n">
-        <v>3</v>
-      </c>
-      <c r="J376" t="n">
-        <v>0</v>
-      </c>
       <c r="K376" t="n">
+        <v>0</v>
+      </c>
+      <c r="L376" t="n">
         <v>2</v>
-      </c>
-      <c r="L376" t="n">
-        <v>0</v>
       </c>
       <c r="M376" t="n">
         <v>2</v>
@@ -16008,7 +15904,7 @@
       </c>
       <c r="B377" t="inlineStr"/>
       <c r="C377" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D377" t="n">
         <v>0</v>
@@ -16049,7 +15945,7 @@
       </c>
       <c r="B378" t="inlineStr"/>
       <c r="C378" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D378" t="n">
         <v>0</v>
@@ -16070,16 +15966,16 @@
         <v>0</v>
       </c>
       <c r="J378" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K378" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L378" t="n">
         <v>0</v>
       </c>
       <c r="M378" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="379">
@@ -16117,10 +16013,10 @@
         <v>0</v>
       </c>
       <c r="L379" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M379" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="380">
@@ -16199,10 +16095,10 @@
         <v>0</v>
       </c>
       <c r="L381" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M381" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="382">
@@ -16254,37 +16150,37 @@
       </c>
       <c r="B383" t="inlineStr"/>
       <c r="C383" t="n">
+        <v>0</v>
+      </c>
+      <c r="D383" t="n">
+        <v>0</v>
+      </c>
+      <c r="E383" t="n">
+        <v>1</v>
+      </c>
+      <c r="F383" t="n">
+        <v>0</v>
+      </c>
+      <c r="G383" t="n">
+        <v>0</v>
+      </c>
+      <c r="H383" t="n">
+        <v>0</v>
+      </c>
+      <c r="I383" t="n">
+        <v>1</v>
+      </c>
+      <c r="J383" t="n">
+        <v>0</v>
+      </c>
+      <c r="K383" t="n">
         <v>2</v>
       </c>
-      <c r="D383" t="n">
-        <v>0</v>
-      </c>
-      <c r="E383" t="n">
-        <v>0</v>
-      </c>
-      <c r="F383" t="n">
-        <v>1</v>
-      </c>
-      <c r="G383" t="n">
-        <v>0</v>
-      </c>
-      <c r="H383" t="n">
-        <v>0</v>
-      </c>
-      <c r="I383" t="n">
-        <v>0</v>
-      </c>
-      <c r="J383" t="n">
-        <v>1</v>
-      </c>
-      <c r="K383" t="n">
-        <v>0</v>
-      </c>
       <c r="L383" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M383" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="384">
@@ -16293,9 +16189,7 @@
           <t>驅動IC</t>
         </is>
       </c>
-      <c r="B384" t="n">
-        <v>0</v>
-      </c>
+      <c r="B384" t="inlineStr"/>
       <c r="C384" t="n">
         <v>0</v>
       </c>
@@ -16336,14 +16230,12 @@
           <t>高/低壓輸電設施</t>
         </is>
       </c>
-      <c r="B385" t="n">
-        <v>0</v>
-      </c>
+      <c r="B385" t="inlineStr"/>
       <c r="C385" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D385" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E385" t="n">
         <v>0</v>
@@ -16352,13 +16244,13 @@
         <v>0</v>
       </c>
       <c r="G385" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H385" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I385" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J385" t="n">
         <v>0</v>

--- a/Result/analyze_3.xlsx
+++ b/Result/analyze_3.xlsx
@@ -441,57 +441,57 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
     </row>
@@ -667,25 +667,25 @@
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J6" t="n">
         <v>2</v>
@@ -694,10 +694,10 @@
         <v>2</v>
       </c>
       <c r="L6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -706,39 +706,41 @@
           <t>IC封裝測試</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr"/>
+      <c r="B7" t="n">
+        <v>0</v>
+      </c>
       <c r="C7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D7" t="n">
         <v>1</v>
       </c>
       <c r="E7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
         <v>2</v>
       </c>
-      <c r="I7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
       <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
         <v>2</v>
       </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
       <c r="M7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -749,37 +751,37 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="n">
         <v>2</v>
       </c>
-      <c r="D8" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" t="n">
-        <v>0</v>
-      </c>
       <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
         <v>2</v>
       </c>
-      <c r="I8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
       <c r="K8" t="n">
+        <v>1</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1</v>
+      </c>
+      <c r="M8" t="n">
         <v>2</v>
-      </c>
-      <c r="L8" t="n">
-        <v>1</v>
-      </c>
-      <c r="M8" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -790,37 +792,37 @@
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E9" t="n">
         <v>1</v>
       </c>
       <c r="F9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I9" t="n">
         <v>1</v>
       </c>
       <c r="J9" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K9" t="n">
         <v>4</v>
       </c>
       <c r="L9" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10">
@@ -829,36 +831,38 @@
           <t>IC通路</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
+      <c r="B10" t="n">
+        <v>0</v>
+      </c>
       <c r="C10" t="n">
+        <v>1</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="n">
         <v>3</v>
       </c>
-      <c r="D10" t="n">
-        <v>1</v>
-      </c>
-      <c r="E10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" t="n">
-        <v>0</v>
-      </c>
       <c r="H10" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M10" t="n">
         <v>2</v>
@@ -875,34 +879,34 @@
         <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1</v>
+      </c>
+      <c r="J11" t="n">
         <v>2</v>
       </c>
-      <c r="F11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" t="n">
-        <v>1</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" t="n">
-        <v>1</v>
-      </c>
       <c r="K11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -913,7 +917,7 @@
       </c>
       <c r="B12" t="inlineStr"/>
       <c r="C12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
@@ -954,7 +958,7 @@
       </c>
       <c r="B13" t="inlineStr"/>
       <c r="C13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D13" t="n">
         <v>0</v>
@@ -1136,10 +1140,10 @@
         <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
@@ -1198,17 +1202,15 @@
           <t>不鏽鋼棒線</t>
         </is>
       </c>
-      <c r="B19" t="n">
-        <v>0</v>
-      </c>
+      <c r="B19" t="inlineStr"/>
       <c r="C19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F19" t="n">
         <v>0</v>
@@ -1243,7 +1245,7 @@
       </c>
       <c r="B20" t="inlineStr"/>
       <c r="C20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
         <v>0</v>
@@ -1282,39 +1284,41 @@
           <t>中、西藥製劑</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr"/>
+      <c r="B21" t="n">
+        <v>0</v>
+      </c>
       <c r="C21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D21" t="n">
+        <v>1</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" t="n">
+        <v>1</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" t="n">
         <v>2</v>
       </c>
-      <c r="E21" t="n">
-        <v>1</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0</v>
-      </c>
-      <c r="G21" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" t="n">
-        <v>1</v>
-      </c>
-      <c r="I21" t="n">
-        <v>0</v>
-      </c>
       <c r="J21" t="n">
+        <v>1</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
         <v>2</v>
       </c>
-      <c r="K21" t="n">
-        <v>1</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
       <c r="M21" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -1366,10 +1370,10 @@
       </c>
       <c r="B23" t="inlineStr"/>
       <c r="C23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -1378,19 +1382,19 @@
         <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
@@ -1405,9 +1409,11 @@
           <t>主/被動元件</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr"/>
+      <c r="B24" t="n">
+        <v>0</v>
+      </c>
       <c r="C24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D24" t="n">
         <v>0</v>
@@ -1419,25 +1425,25 @@
         <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" t="n">
+        <v>1</v>
+      </c>
+      <c r="J24" t="n">
+        <v>3</v>
+      </c>
+      <c r="K24" t="n">
         <v>2</v>
-      </c>
-      <c r="I24" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" t="n">
-        <v>1</v>
-      </c>
-      <c r="K24" t="n">
-        <v>3</v>
       </c>
       <c r="L24" t="n">
         <v>2</v>
       </c>
       <c r="M24" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -1469,13 +1475,13 @@
         <v>0</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K25" t="n">
         <v>1</v>
       </c>
       <c r="L25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
         <v>0</v>
@@ -1533,10 +1539,10 @@
         <v>0</v>
       </c>
       <c r="D27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F27" t="n">
         <v>0</v>
@@ -1554,10 +1560,10 @@
         <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
         <v>0</v>
@@ -1653,7 +1659,7 @@
       </c>
       <c r="B30" t="inlineStr"/>
       <c r="C30" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D30" t="n">
         <v>0</v>
@@ -1680,10 +1686,10 @@
         <v>0</v>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -1694,7 +1700,7 @@
       </c>
       <c r="B31" t="inlineStr"/>
       <c r="C31" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D31" t="n">
         <v>0</v>
@@ -1718,13 +1724,13 @@
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L31" t="n">
         <v>1</v>
       </c>
       <c r="M31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -1735,22 +1741,22 @@
       </c>
       <c r="B32" t="inlineStr"/>
       <c r="C32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F32" t="n">
         <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I32" t="n">
         <v>0</v>
@@ -1759,10 +1765,10 @@
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L32" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
         <v>0</v>
@@ -1800,10 +1806,10 @@
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
         <v>0</v>
@@ -1856,7 +1862,9 @@
           <t>保健食品代理銷售及通路</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr"/>
+      <c r="B35" t="n">
+        <v>0</v>
+      </c>
       <c r="C35" t="n">
         <v>0</v>
       </c>
@@ -1876,7 +1884,7 @@
         <v>0</v>
       </c>
       <c r="I35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J35" t="n">
         <v>1</v>
@@ -1888,7 +1896,7 @@
         <v>1</v>
       </c>
       <c r="M35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -2040,10 +2048,10 @@
         <v>0</v>
       </c>
       <c r="I39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K39" t="n">
         <v>0</v>
@@ -2116,10 +2124,10 @@
         <v>0</v>
       </c>
       <c r="G41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I41" t="n">
         <v>0</v>
@@ -2145,7 +2153,7 @@
       </c>
       <c r="B42" t="inlineStr"/>
       <c r="C42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D42" t="n">
         <v>0</v>
@@ -2157,25 +2165,25 @@
         <v>0</v>
       </c>
       <c r="G42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I42" t="n">
         <v>0</v>
       </c>
       <c r="J42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M42" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -2207,10 +2215,10 @@
         <v>0</v>
       </c>
       <c r="J43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L43" t="n">
         <v>0</v>
@@ -2227,7 +2235,7 @@
       </c>
       <c r="B44" t="inlineStr"/>
       <c r="C44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D44" t="n">
         <v>0</v>
@@ -2236,19 +2244,19 @@
         <v>0</v>
       </c>
       <c r="F44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H44" t="n">
         <v>0</v>
       </c>
       <c r="I44" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J44" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K44" t="n">
         <v>0</v>
@@ -2289,13 +2297,13 @@
         <v>0</v>
       </c>
       <c r="J45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K45" t="n">
         <v>1</v>
       </c>
       <c r="L45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M45" t="n">
         <v>0</v>
@@ -2371,10 +2379,10 @@
         <v>0</v>
       </c>
       <c r="J47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L47" t="n">
         <v>0</v>
@@ -2432,28 +2440,28 @@
       </c>
       <c r="B49" t="inlineStr"/>
       <c r="C49" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D49" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E49" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G49" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H49" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I49" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J49" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="K49" t="n">
         <v>3</v>
@@ -2512,39 +2520,41 @@
           <t>其他</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr"/>
+      <c r="B51" t="n">
+        <v>0</v>
+      </c>
       <c r="C51" t="n">
+        <v>1</v>
+      </c>
+      <c r="D51" t="n">
+        <v>1</v>
+      </c>
+      <c r="E51" t="n">
+        <v>1</v>
+      </c>
+      <c r="F51" t="n">
+        <v>1</v>
+      </c>
+      <c r="G51" t="n">
+        <v>3</v>
+      </c>
+      <c r="H51" t="n">
+        <v>1</v>
+      </c>
+      <c r="I51" t="n">
+        <v>3</v>
+      </c>
+      <c r="J51" t="n">
+        <v>4</v>
+      </c>
+      <c r="K51" t="n">
         <v>6</v>
       </c>
-      <c r="D51" t="n">
-        <v>1</v>
-      </c>
-      <c r="E51" t="n">
-        <v>1</v>
-      </c>
-      <c r="F51" t="n">
-        <v>1</v>
-      </c>
-      <c r="G51" t="n">
-        <v>1</v>
-      </c>
-      <c r="H51" t="n">
-        <v>3</v>
-      </c>
-      <c r="I51" t="n">
-        <v>1</v>
-      </c>
-      <c r="J51" t="n">
-        <v>3</v>
-      </c>
-      <c r="K51" t="n">
-        <v>3</v>
-      </c>
       <c r="L51" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="M51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -2596,37 +2606,37 @@
       </c>
       <c r="B53" t="inlineStr"/>
       <c r="C53" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D53" t="n">
         <v>2</v>
       </c>
       <c r="E53" t="n">
+        <v>0</v>
+      </c>
+      <c r="F53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G53" t="n">
         <v>2</v>
       </c>
-      <c r="F53" t="n">
-        <v>0</v>
-      </c>
-      <c r="G53" t="n">
-        <v>0</v>
-      </c>
       <c r="H53" t="n">
+        <v>0</v>
+      </c>
+      <c r="I53" t="n">
+        <v>0</v>
+      </c>
+      <c r="J53" t="n">
+        <v>0</v>
+      </c>
+      <c r="K53" t="n">
+        <v>1</v>
+      </c>
+      <c r="L53" t="n">
+        <v>0</v>
+      </c>
+      <c r="M53" t="n">
         <v>2</v>
-      </c>
-      <c r="I53" t="n">
-        <v>0</v>
-      </c>
-      <c r="J53" t="n">
-        <v>0</v>
-      </c>
-      <c r="K53" t="n">
-        <v>0</v>
-      </c>
-      <c r="L53" t="n">
-        <v>1</v>
-      </c>
-      <c r="M53" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -2637,10 +2647,10 @@
       </c>
       <c r="B54" t="inlineStr"/>
       <c r="C54" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E54" t="n">
         <v>1</v>
@@ -2649,25 +2659,25 @@
         <v>1</v>
       </c>
       <c r="G54" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H54" t="n">
+        <v>0</v>
+      </c>
+      <c r="I54" t="n">
         <v>4</v>
       </c>
-      <c r="I54" t="n">
-        <v>0</v>
-      </c>
       <c r="J54" t="n">
+        <v>5</v>
+      </c>
+      <c r="K54" t="n">
         <v>4</v>
       </c>
-      <c r="K54" t="n">
-        <v>5</v>
-      </c>
       <c r="L54" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M54" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="55">
@@ -2678,37 +2688,37 @@
       </c>
       <c r="B55" t="inlineStr"/>
       <c r="C55" t="n">
+        <v>1</v>
+      </c>
+      <c r="D55" t="n">
+        <v>0</v>
+      </c>
+      <c r="E55" t="n">
+        <v>0</v>
+      </c>
+      <c r="F55" t="n">
+        <v>1</v>
+      </c>
+      <c r="G55" t="n">
+        <v>1</v>
+      </c>
+      <c r="H55" t="n">
+        <v>1</v>
+      </c>
+      <c r="I55" t="n">
+        <v>3</v>
+      </c>
+      <c r="J55" t="n">
+        <v>1</v>
+      </c>
+      <c r="K55" t="n">
+        <v>3</v>
+      </c>
+      <c r="L55" t="n">
         <v>2</v>
       </c>
-      <c r="D55" t="n">
-        <v>1</v>
-      </c>
-      <c r="E55" t="n">
-        <v>0</v>
-      </c>
-      <c r="F55" t="n">
-        <v>0</v>
-      </c>
-      <c r="G55" t="n">
-        <v>1</v>
-      </c>
-      <c r="H55" t="n">
-        <v>1</v>
-      </c>
-      <c r="I55" t="n">
-        <v>1</v>
-      </c>
-      <c r="J55" t="n">
+      <c r="M55" t="n">
         <v>3</v>
-      </c>
-      <c r="K55" t="n">
-        <v>1</v>
-      </c>
-      <c r="L55" t="n">
-        <v>3</v>
-      </c>
-      <c r="M55" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="56">
@@ -2719,25 +2729,25 @@
       </c>
       <c r="B56" t="inlineStr"/>
       <c r="C56" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D56" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E56" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F56" t="n">
         <v>0</v>
       </c>
       <c r="G56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J56" t="n">
         <v>1</v>
@@ -2801,7 +2811,7 @@
       </c>
       <c r="B58" t="inlineStr"/>
       <c r="C58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D58" t="n">
         <v>0</v>
@@ -2810,10 +2820,10 @@
         <v>0</v>
       </c>
       <c r="F58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H58" t="n">
         <v>0</v>
@@ -2825,10 +2835,10 @@
         <v>0</v>
       </c>
       <c r="K58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M58" t="n">
         <v>0</v>
@@ -2842,7 +2852,7 @@
       </c>
       <c r="B59" t="inlineStr"/>
       <c r="C59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D59" t="n">
         <v>0</v>
@@ -2851,13 +2861,13 @@
         <v>0</v>
       </c>
       <c r="F59" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G59" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H59" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I59" t="n">
         <v>0</v>
@@ -2883,7 +2893,7 @@
       </c>
       <c r="B60" t="inlineStr"/>
       <c r="C60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D60" t="n">
         <v>0</v>
@@ -3006,7 +3016,7 @@
       </c>
       <c r="B63" t="inlineStr"/>
       <c r="C63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D63" t="n">
         <v>0</v>
@@ -3033,10 +3043,10 @@
         <v>0</v>
       </c>
       <c r="L63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="64">
@@ -3168,7 +3178,9 @@
           <t>加工製成品</t>
         </is>
       </c>
-      <c r="B67" t="inlineStr"/>
+      <c r="B67" t="n">
+        <v>0</v>
+      </c>
       <c r="C67" t="n">
         <v>0</v>
       </c>
@@ -3191,10 +3203,10 @@
         <v>0</v>
       </c>
       <c r="J67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L67" t="n">
         <v>0</v>
@@ -3282,7 +3294,7 @@
         <v>0</v>
       </c>
       <c r="M69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="70">
@@ -3334,34 +3346,34 @@
       </c>
       <c r="B71" t="inlineStr"/>
       <c r="C71" t="n">
+        <v>0</v>
+      </c>
+      <c r="D71" t="n">
+        <v>1</v>
+      </c>
+      <c r="E71" t="n">
+        <v>0</v>
+      </c>
+      <c r="F71" t="n">
+        <v>0</v>
+      </c>
+      <c r="G71" t="n">
+        <v>0</v>
+      </c>
+      <c r="H71" t="n">
+        <v>0</v>
+      </c>
+      <c r="I71" t="n">
+        <v>1</v>
+      </c>
+      <c r="J71" t="n">
         <v>2</v>
       </c>
-      <c r="D71" t="n">
-        <v>0</v>
-      </c>
-      <c r="E71" t="n">
-        <v>1</v>
-      </c>
-      <c r="F71" t="n">
-        <v>0</v>
-      </c>
-      <c r="G71" t="n">
-        <v>0</v>
-      </c>
-      <c r="H71" t="n">
-        <v>0</v>
-      </c>
-      <c r="I71" t="n">
-        <v>0</v>
-      </c>
-      <c r="J71" t="n">
-        <v>1</v>
-      </c>
       <c r="K71" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M71" t="n">
         <v>0</v>
@@ -3375,31 +3387,31 @@
       </c>
       <c r="B72" t="inlineStr"/>
       <c r="C72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F72" t="n">
         <v>0</v>
       </c>
       <c r="G72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J72" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K72" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L72" t="n">
         <v>1</v>
@@ -3428,10 +3440,10 @@
         <v>0</v>
       </c>
       <c r="G73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H73" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I73" t="n">
         <v>0</v>
@@ -3443,7 +3455,7 @@
         <v>0</v>
       </c>
       <c r="L73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M73" t="n">
         <v>1</v>
@@ -3498,7 +3510,7 @@
       </c>
       <c r="B75" t="inlineStr"/>
       <c r="C75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D75" t="n">
         <v>0</v>
@@ -3560,13 +3572,13 @@
         <v>0</v>
       </c>
       <c r="J76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K76" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L76" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M76" t="n">
         <v>0</v>
@@ -3601,10 +3613,10 @@
         <v>0</v>
       </c>
       <c r="J77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K77" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L77" t="n">
         <v>0</v>
@@ -3619,39 +3631,41 @@
           <t>原材料</t>
         </is>
       </c>
-      <c r="B78" t="inlineStr"/>
+      <c r="B78" t="n">
+        <v>0</v>
+      </c>
       <c r="C78" t="n">
+        <v>1</v>
+      </c>
+      <c r="D78" t="n">
         <v>2</v>
-      </c>
-      <c r="D78" t="n">
-        <v>1</v>
       </c>
       <c r="E78" t="n">
         <v>2</v>
       </c>
       <c r="F78" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G78" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H78" t="n">
         <v>0</v>
       </c>
       <c r="I78" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J78" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K78" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L78" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M78" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="79">
@@ -3765,13 +3779,13 @@
         <v>0</v>
       </c>
       <c r="J81" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K81" t="n">
         <v>1</v>
       </c>
       <c r="L81" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M81" t="n">
         <v>0</v>
@@ -3785,7 +3799,7 @@
       </c>
       <c r="B82" t="inlineStr"/>
       <c r="C82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D82" t="n">
         <v>0</v>
@@ -3826,37 +3840,37 @@
       </c>
       <c r="B83" t="inlineStr"/>
       <c r="C83" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D83" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E83" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F83" t="n">
         <v>0</v>
       </c>
       <c r="G83" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H83" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I83" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J83" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K83" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L83" t="n">
         <v>1</v>
       </c>
       <c r="M83" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="84">
@@ -3949,10 +3963,10 @@
       </c>
       <c r="B86" t="inlineStr"/>
       <c r="C86" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D86" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E86" t="n">
         <v>0</v>
@@ -3990,13 +4004,13 @@
       </c>
       <c r="B87" t="inlineStr"/>
       <c r="C87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F87" t="n">
         <v>0</v>
@@ -4043,10 +4057,10 @@
         <v>0</v>
       </c>
       <c r="G88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I88" t="n">
         <v>0</v>
@@ -4072,22 +4086,22 @@
       </c>
       <c r="B89" t="inlineStr"/>
       <c r="C89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D89" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F89" t="n">
         <v>0</v>
       </c>
       <c r="G89" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I89" t="n">
         <v>0</v>
@@ -4096,10 +4110,10 @@
         <v>0</v>
       </c>
       <c r="K89" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M89" t="n">
         <v>0</v>
@@ -4195,10 +4209,10 @@
       </c>
       <c r="B92" t="inlineStr"/>
       <c r="C92" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D92" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E92" t="n">
         <v>1</v>
@@ -4207,25 +4221,25 @@
         <v>1</v>
       </c>
       <c r="G92" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H92" t="n">
+        <v>0</v>
+      </c>
+      <c r="I92" t="n">
+        <v>0</v>
+      </c>
+      <c r="J92" t="n">
+        <v>0</v>
+      </c>
+      <c r="K92" t="n">
+        <v>1</v>
+      </c>
+      <c r="L92" t="n">
+        <v>1</v>
+      </c>
+      <c r="M92" t="n">
         <v>2</v>
-      </c>
-      <c r="I92" t="n">
-        <v>0</v>
-      </c>
-      <c r="J92" t="n">
-        <v>0</v>
-      </c>
-      <c r="K92" t="n">
-        <v>0</v>
-      </c>
-      <c r="L92" t="n">
-        <v>1</v>
-      </c>
-      <c r="M92" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="93">
@@ -4301,10 +4315,10 @@
         <v>0</v>
       </c>
       <c r="K94" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L94" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M94" t="n">
         <v>0</v>
@@ -4318,37 +4332,37 @@
       </c>
       <c r="B95" t="inlineStr"/>
       <c r="C95" t="n">
+        <v>0</v>
+      </c>
+      <c r="D95" t="n">
+        <v>0</v>
+      </c>
+      <c r="E95" t="n">
+        <v>0</v>
+      </c>
+      <c r="F95" t="n">
+        <v>1</v>
+      </c>
+      <c r="G95" t="n">
+        <v>1</v>
+      </c>
+      <c r="H95" t="n">
+        <v>0</v>
+      </c>
+      <c r="I95" t="n">
+        <v>0</v>
+      </c>
+      <c r="J95" t="n">
         <v>2</v>
-      </c>
-      <c r="D95" t="n">
-        <v>0</v>
-      </c>
-      <c r="E95" t="n">
-        <v>0</v>
-      </c>
-      <c r="F95" t="n">
-        <v>0</v>
-      </c>
-      <c r="G95" t="n">
-        <v>1</v>
-      </c>
-      <c r="H95" t="n">
-        <v>1</v>
-      </c>
-      <c r="I95" t="n">
-        <v>0</v>
-      </c>
-      <c r="J95" t="n">
-        <v>0</v>
       </c>
       <c r="K95" t="n">
         <v>2</v>
       </c>
       <c r="L95" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M95" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="96">
@@ -4359,7 +4373,7 @@
       </c>
       <c r="B96" t="inlineStr"/>
       <c r="C96" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D96" t="n">
         <v>0</v>
@@ -4371,22 +4385,22 @@
         <v>0</v>
       </c>
       <c r="G96" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H96" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I96" t="n">
         <v>0</v>
       </c>
       <c r="J96" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K96" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L96" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M96" t="n">
         <v>0</v>
@@ -4465,10 +4479,10 @@
         <v>0</v>
       </c>
       <c r="K98" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L98" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M98" t="n">
         <v>0</v>
@@ -4497,19 +4511,19 @@
         <v>0</v>
       </c>
       <c r="H99" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
       </c>
       <c r="K99" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M99" t="n">
         <v>0</v>
@@ -4564,10 +4578,10 @@
       </c>
       <c r="B101" t="inlineStr"/>
       <c r="C101" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D101" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E101" t="n">
         <v>0</v>
@@ -4582,16 +4596,16 @@
         <v>0</v>
       </c>
       <c r="I101" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J101" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K101" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L101" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M101" t="n">
         <v>0</v>
@@ -4608,7 +4622,7 @@
         <v>1</v>
       </c>
       <c r="D102" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E102" t="n">
         <v>0</v>
@@ -4617,25 +4631,25 @@
         <v>0</v>
       </c>
       <c r="G102" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H102" t="n">
+        <v>1</v>
+      </c>
+      <c r="I102" t="n">
+        <v>0</v>
+      </c>
+      <c r="J102" t="n">
+        <v>0</v>
+      </c>
+      <c r="K102" t="n">
+        <v>1</v>
+      </c>
+      <c r="L102" t="n">
+        <v>3</v>
+      </c>
+      <c r="M102" t="n">
         <v>2</v>
-      </c>
-      <c r="I102" t="n">
-        <v>1</v>
-      </c>
-      <c r="J102" t="n">
-        <v>0</v>
-      </c>
-      <c r="K102" t="n">
-        <v>0</v>
-      </c>
-      <c r="L102" t="n">
-        <v>1</v>
-      </c>
-      <c r="M102" t="n">
-        <v>3</v>
       </c>
     </row>
     <row r="103">
@@ -4685,12 +4699,14 @@
           <t>封裝/模組</t>
         </is>
       </c>
-      <c r="B104" t="inlineStr"/>
+      <c r="B104" t="n">
+        <v>0</v>
+      </c>
       <c r="C104" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D104" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E104" t="n">
         <v>0</v>
@@ -4699,25 +4715,25 @@
         <v>0</v>
       </c>
       <c r="G104" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H104" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I104" t="n">
         <v>0</v>
       </c>
       <c r="J104" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K104" t="n">
         <v>1</v>
       </c>
       <c r="L104" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M104" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="105">
@@ -4726,33 +4742,35 @@
           <t>專用機械(如紡織成衣生產用機械、食品飲料生產用機械、農林用機械等)</t>
         </is>
       </c>
-      <c r="B105" t="inlineStr"/>
+      <c r="B105" t="n">
+        <v>0</v>
+      </c>
       <c r="C105" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D105" t="n">
         <v>1</v>
       </c>
       <c r="E105" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F105" t="n">
         <v>0</v>
       </c>
       <c r="G105" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H105" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I105" t="n">
         <v>0</v>
       </c>
       <c r="J105" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K105" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L105" t="n">
         <v>0</v>
@@ -4769,22 +4787,22 @@
       </c>
       <c r="B106" t="inlineStr"/>
       <c r="C106" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D106" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E106" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F106" t="n">
         <v>0</v>
       </c>
       <c r="G106" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H106" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I106" t="n">
         <v>0</v>
@@ -4799,7 +4817,7 @@
         <v>0</v>
       </c>
       <c r="M106" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="107">
@@ -4945,10 +4963,10 @@
         <v>0</v>
       </c>
       <c r="G110" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H110" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I110" t="n">
         <v>0</v>
@@ -4972,12 +4990,14 @@
           <t>工業電腦</t>
         </is>
       </c>
-      <c r="B111" t="inlineStr"/>
+      <c r="B111" t="n">
+        <v>0</v>
+      </c>
       <c r="C111" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D111" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E111" t="n">
         <v>0</v>
@@ -4992,19 +5012,19 @@
         <v>0</v>
       </c>
       <c r="I111" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J111" t="n">
         <v>1</v>
       </c>
       <c r="K111" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L111" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M111" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="112">
@@ -5015,7 +5035,7 @@
       </c>
       <c r="B112" t="inlineStr"/>
       <c r="C112" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D112" t="n">
         <v>0</v>
@@ -5024,10 +5044,10 @@
         <v>0</v>
       </c>
       <c r="F112" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G112" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H112" t="n">
         <v>0</v>
@@ -5036,13 +5056,13 @@
         <v>0</v>
       </c>
       <c r="J112" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K112" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L112" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M112" t="n">
         <v>1</v>
@@ -5056,7 +5076,7 @@
       </c>
       <c r="B113" t="inlineStr"/>
       <c r="C113" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D113" t="n">
         <v>0</v>
@@ -5065,10 +5085,10 @@
         <v>0</v>
       </c>
       <c r="F113" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G113" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H113" t="n">
         <v>0</v>
@@ -5115,10 +5135,10 @@
         <v>0</v>
       </c>
       <c r="I114" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J114" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K114" t="n">
         <v>0</v>
@@ -5159,10 +5179,10 @@
         <v>0</v>
       </c>
       <c r="J115" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K115" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L115" t="n">
         <v>0</v>
@@ -5200,10 +5220,10 @@
         <v>0</v>
       </c>
       <c r="J116" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K116" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L116" t="n">
         <v>0</v>
@@ -5343,22 +5363,22 @@
       </c>
       <c r="B120" t="inlineStr"/>
       <c r="C120" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D120" t="n">
         <v>1</v>
       </c>
       <c r="E120" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F120" t="n">
         <v>0</v>
       </c>
       <c r="G120" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H120" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I120" t="n">
         <v>0</v>
@@ -5367,13 +5387,13 @@
         <v>0</v>
       </c>
       <c r="K120" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L120" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M120" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="121">
@@ -5384,7 +5404,7 @@
       </c>
       <c r="B121" t="inlineStr"/>
       <c r="C121" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D121" t="n">
         <v>0</v>
@@ -5396,25 +5416,25 @@
         <v>0</v>
       </c>
       <c r="G121" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H121" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I121" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J121" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K121" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L121" t="n">
         <v>1</v>
       </c>
       <c r="M121" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="122">
@@ -5507,7 +5527,7 @@
       </c>
       <c r="B124" t="inlineStr"/>
       <c r="C124" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D124" t="n">
         <v>0</v>
@@ -5671,22 +5691,22 @@
       </c>
       <c r="B128" t="inlineStr"/>
       <c r="C128" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D128" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E128" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F128" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G128" t="n">
         <v>1</v>
       </c>
       <c r="H128" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I128" t="n">
         <v>0</v>
@@ -5695,10 +5715,10 @@
         <v>0</v>
       </c>
       <c r="K128" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L128" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M128" t="n">
         <v>1</v>
@@ -5712,7 +5732,7 @@
       </c>
       <c r="B129" t="inlineStr"/>
       <c r="C129" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D129" t="n">
         <v>0</v>
@@ -5739,10 +5759,10 @@
         <v>0</v>
       </c>
       <c r="L129" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M129" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="130">
@@ -5800,13 +5820,13 @@
         <v>1</v>
       </c>
       <c r="E131" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F131" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G131" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H131" t="n">
         <v>0</v>
@@ -5835,10 +5855,10 @@
       </c>
       <c r="B132" t="inlineStr"/>
       <c r="C132" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D132" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E132" t="n">
         <v>0</v>
@@ -6070,7 +6090,7 @@
         <v>0</v>
       </c>
       <c r="M137" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="138">
@@ -6134,25 +6154,25 @@
         <v>0</v>
       </c>
       <c r="G139" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H139" t="n">
+        <v>0</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0</v>
+      </c>
+      <c r="K139" t="n">
+        <v>1</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0</v>
+      </c>
+      <c r="M139" t="n">
         <v>2</v>
-      </c>
-      <c r="I139" t="n">
-        <v>0</v>
-      </c>
-      <c r="J139" t="n">
-        <v>0</v>
-      </c>
-      <c r="K139" t="n">
-        <v>0</v>
-      </c>
-      <c r="L139" t="n">
-        <v>1</v>
-      </c>
-      <c r="M139" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="140">
@@ -6184,13 +6204,13 @@
         <v>0</v>
       </c>
       <c r="J140" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K140" t="n">
         <v>1</v>
       </c>
       <c r="L140" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M140" t="n">
         <v>0</v>
@@ -6207,7 +6227,7 @@
         <v>1</v>
       </c>
       <c r="D141" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E141" t="n">
         <v>0</v>
@@ -6225,13 +6245,13 @@
         <v>0</v>
       </c>
       <c r="J141" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K141" t="n">
         <v>1</v>
       </c>
       <c r="L141" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M141" t="n">
         <v>0</v>
@@ -6266,13 +6286,13 @@
         <v>0</v>
       </c>
       <c r="J142" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K142" t="n">
         <v>1</v>
       </c>
       <c r="L142" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M142" t="n">
         <v>0</v>
@@ -6330,10 +6350,10 @@
         <v>0</v>
       </c>
       <c r="D144" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E144" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F144" t="n">
         <v>0</v>
@@ -6345,10 +6365,10 @@
         <v>0</v>
       </c>
       <c r="I144" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J144" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K144" t="n">
         <v>0</v>
@@ -6368,10 +6388,10 @@
       </c>
       <c r="B145" t="inlineStr"/>
       <c r="C145" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D145" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E145" t="n">
         <v>0</v>
@@ -6386,16 +6406,16 @@
         <v>0</v>
       </c>
       <c r="I145" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J145" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K145" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L145" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M145" t="n">
         <v>0</v>
@@ -6450,10 +6470,10 @@
       </c>
       <c r="B147" t="inlineStr"/>
       <c r="C147" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D147" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E147" t="n">
         <v>0</v>
@@ -6468,16 +6488,16 @@
         <v>0</v>
       </c>
       <c r="I147" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J147" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K147" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L147" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M147" t="n">
         <v>0</v>
@@ -6489,7 +6509,9 @@
           <t>文化印刷業</t>
         </is>
       </c>
-      <c r="B148" t="inlineStr"/>
+      <c r="B148" t="n">
+        <v>0</v>
+      </c>
       <c r="C148" t="n">
         <v>0</v>
       </c>
@@ -6509,10 +6531,10 @@
         <v>0</v>
       </c>
       <c r="I148" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J148" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K148" t="n">
         <v>0</v>
@@ -6521,7 +6543,7 @@
         <v>0</v>
       </c>
       <c r="M148" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="149">
@@ -6532,10 +6554,10 @@
       </c>
       <c r="B149" t="inlineStr"/>
       <c r="C149" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D149" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E149" t="n">
         <v>0</v>
@@ -6585,10 +6607,10 @@
         <v>0</v>
       </c>
       <c r="G150" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H150" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I150" t="n">
         <v>0</v>
@@ -6612,20 +6634,18 @@
           <t>旅館服務業</t>
         </is>
       </c>
-      <c r="B151" t="n">
-        <v>0</v>
-      </c>
+      <c r="B151" t="inlineStr"/>
       <c r="C151" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D151" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E151" t="n">
         <v>0</v>
       </c>
       <c r="F151" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G151" t="n">
         <v>0</v>
@@ -6640,10 +6660,10 @@
         <v>0</v>
       </c>
       <c r="K151" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L151" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M151" t="n">
         <v>0</v>
@@ -6701,34 +6721,34 @@
         <v>0</v>
       </c>
       <c r="D153" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E153" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F153" t="n">
         <v>0</v>
       </c>
       <c r="G153" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H153" t="n">
+        <v>1</v>
+      </c>
+      <c r="I153" t="n">
+        <v>0</v>
+      </c>
+      <c r="J153" t="n">
+        <v>0</v>
+      </c>
+      <c r="K153" t="n">
+        <v>0</v>
+      </c>
+      <c r="L153" t="n">
+        <v>0</v>
+      </c>
+      <c r="M153" t="n">
         <v>2</v>
-      </c>
-      <c r="I153" t="n">
-        <v>1</v>
-      </c>
-      <c r="J153" t="n">
-        <v>0</v>
-      </c>
-      <c r="K153" t="n">
-        <v>0</v>
-      </c>
-      <c r="L153" t="n">
-        <v>0</v>
-      </c>
-      <c r="M153" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="154">
@@ -6739,7 +6759,7 @@
       </c>
       <c r="B154" t="inlineStr"/>
       <c r="C154" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D154" t="n">
         <v>0</v>
@@ -6751,10 +6771,10 @@
         <v>0</v>
       </c>
       <c r="G154" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H154" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I154" t="n">
         <v>0</v>
@@ -6819,15 +6839,17 @@
           <t>材料</t>
         </is>
       </c>
-      <c r="B156" t="inlineStr"/>
+      <c r="B156" t="n">
+        <v>0</v>
+      </c>
       <c r="C156" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D156" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E156" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F156" t="n">
         <v>0</v>
@@ -6862,7 +6884,7 @@
       </c>
       <c r="B157" t="inlineStr"/>
       <c r="C157" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D157" t="n">
         <v>0</v>
@@ -6877,22 +6899,22 @@
         <v>0</v>
       </c>
       <c r="H157" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I157" t="n">
         <v>1</v>
       </c>
       <c r="J157" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K157" t="n">
         <v>0</v>
       </c>
       <c r="L157" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M157" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="158">
@@ -6901,7 +6923,9 @@
           <t>桌上型電腦</t>
         </is>
       </c>
-      <c r="B158" t="inlineStr"/>
+      <c r="B158" t="n">
+        <v>0</v>
+      </c>
       <c r="C158" t="n">
         <v>0</v>
       </c>
@@ -6915,10 +6939,10 @@
         <v>0</v>
       </c>
       <c r="G158" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H158" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I158" t="n">
         <v>0</v>
@@ -6942,9 +6966,7 @@
           <t>棒鋼盤元(捲狀條鋼)</t>
         </is>
       </c>
-      <c r="B159" t="n">
-        <v>0</v>
-      </c>
+      <c r="B159" t="inlineStr"/>
       <c r="C159" t="n">
         <v>0</v>
       </c>
@@ -6999,10 +7021,10 @@
         <v>0</v>
       </c>
       <c r="G160" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H160" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I160" t="n">
         <v>0</v>
@@ -7069,37 +7091,37 @@
       </c>
       <c r="B162" t="inlineStr"/>
       <c r="C162" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D162" t="n">
         <v>1</v>
       </c>
       <c r="E162" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F162" t="n">
         <v>0</v>
       </c>
       <c r="G162" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H162" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I162" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J162" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K162" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L162" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M162" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="163">
@@ -7110,7 +7132,7 @@
       </c>
       <c r="B163" t="inlineStr"/>
       <c r="C163" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D163" t="n">
         <v>0</v>
@@ -7137,10 +7159,10 @@
         <v>0</v>
       </c>
       <c r="L163" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M163" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="164">
@@ -7175,13 +7197,13 @@
         <v>0</v>
       </c>
       <c r="K164" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L164" t="n">
         <v>1</v>
       </c>
       <c r="M164" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="165">
@@ -7192,10 +7214,10 @@
       </c>
       <c r="B165" t="inlineStr"/>
       <c r="C165" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D165" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E165" t="n">
         <v>0</v>
@@ -7210,19 +7232,19 @@
         <v>0</v>
       </c>
       <c r="I165" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J165" t="n">
         <v>1</v>
       </c>
       <c r="K165" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L165" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M165" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="166">
@@ -7233,7 +7255,7 @@
       </c>
       <c r="B166" t="inlineStr"/>
       <c r="C166" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D166" t="n">
         <v>0</v>
@@ -7242,13 +7264,13 @@
         <v>0</v>
       </c>
       <c r="F166" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G166" t="n">
         <v>1</v>
       </c>
       <c r="H166" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I166" t="n">
         <v>0</v>
@@ -7274,7 +7296,7 @@
       </c>
       <c r="B167" t="inlineStr"/>
       <c r="C167" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D167" t="n">
         <v>0</v>
@@ -7283,10 +7305,10 @@
         <v>0</v>
       </c>
       <c r="F167" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G167" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H167" t="n">
         <v>0</v>
@@ -7336,10 +7358,10 @@
         <v>0</v>
       </c>
       <c r="J168" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K168" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L168" t="n">
         <v>0</v>
@@ -7479,7 +7501,7 @@
       </c>
       <c r="B172" t="inlineStr"/>
       <c r="C172" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D172" t="n">
         <v>0</v>
@@ -7500,10 +7522,10 @@
         <v>0</v>
       </c>
       <c r="J172" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K172" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L172" t="n">
         <v>0</v>
@@ -7582,10 +7604,10 @@
         <v>0</v>
       </c>
       <c r="J174" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K174" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L174" t="n">
         <v>0</v>
@@ -7623,10 +7645,10 @@
         <v>0</v>
       </c>
       <c r="J175" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K175" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L175" t="n">
         <v>0</v>
@@ -7682,9 +7704,7 @@
           <t>濾波器、振盪器</t>
         </is>
       </c>
-      <c r="B177" t="n">
-        <v>0</v>
-      </c>
+      <c r="B177" t="inlineStr"/>
       <c r="C177" t="n">
         <v>1</v>
       </c>
@@ -7698,10 +7718,10 @@
         <v>0</v>
       </c>
       <c r="G177" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H177" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I177" t="n">
         <v>0</v>
@@ -7713,7 +7733,7 @@
         <v>0</v>
       </c>
       <c r="L177" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M177" t="n">
         <v>0</v>
@@ -7768,28 +7788,28 @@
       </c>
       <c r="B179" t="inlineStr"/>
       <c r="C179" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D179" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E179" t="n">
+        <v>0</v>
+      </c>
+      <c r="F179" t="n">
+        <v>0</v>
+      </c>
+      <c r="G179" t="n">
         <v>2</v>
       </c>
-      <c r="F179" t="n">
-        <v>0</v>
-      </c>
-      <c r="G179" t="n">
-        <v>0</v>
-      </c>
       <c r="H179" t="n">
+        <v>1</v>
+      </c>
+      <c r="I179" t="n">
+        <v>4</v>
+      </c>
+      <c r="J179" t="n">
         <v>2</v>
-      </c>
-      <c r="I179" t="n">
-        <v>1</v>
-      </c>
-      <c r="J179" t="n">
-        <v>4</v>
       </c>
       <c r="K179" t="n">
         <v>2</v>
@@ -7798,7 +7818,7 @@
         <v>2</v>
       </c>
       <c r="M179" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="180">
@@ -7809,7 +7829,7 @@
       </c>
       <c r="B180" t="inlineStr"/>
       <c r="C180" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D180" t="n">
         <v>0</v>
@@ -7853,34 +7873,34 @@
         <v>2</v>
       </c>
       <c r="D181" t="n">
+        <v>0</v>
+      </c>
+      <c r="E181" t="n">
+        <v>0</v>
+      </c>
+      <c r="F181" t="n">
+        <v>0</v>
+      </c>
+      <c r="G181" t="n">
+        <v>3</v>
+      </c>
+      <c r="H181" t="n">
+        <v>0</v>
+      </c>
+      <c r="I181" t="n">
+        <v>1</v>
+      </c>
+      <c r="J181" t="n">
+        <v>1</v>
+      </c>
+      <c r="K181" t="n">
+        <v>1</v>
+      </c>
+      <c r="L181" t="n">
+        <v>0</v>
+      </c>
+      <c r="M181" t="n">
         <v>2</v>
-      </c>
-      <c r="E181" t="n">
-        <v>0</v>
-      </c>
-      <c r="F181" t="n">
-        <v>0</v>
-      </c>
-      <c r="G181" t="n">
-        <v>0</v>
-      </c>
-      <c r="H181" t="n">
-        <v>3</v>
-      </c>
-      <c r="I181" t="n">
-        <v>0</v>
-      </c>
-      <c r="J181" t="n">
-        <v>1</v>
-      </c>
-      <c r="K181" t="n">
-        <v>1</v>
-      </c>
-      <c r="L181" t="n">
-        <v>1</v>
-      </c>
-      <c r="M181" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="182">
@@ -7891,13 +7911,13 @@
       </c>
       <c r="B182" t="inlineStr"/>
       <c r="C182" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D182" t="n">
         <v>1</v>
       </c>
       <c r="E182" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F182" t="n">
         <v>0</v>
@@ -7976,7 +7996,7 @@
         <v>1</v>
       </c>
       <c r="D184" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E184" t="n">
         <v>0</v>
@@ -7991,19 +8011,19 @@
         <v>0</v>
       </c>
       <c r="I184" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J184" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K184" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L184" t="n">
         <v>1</v>
       </c>
       <c r="M184" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="185">
@@ -8137,13 +8157,13 @@
       </c>
       <c r="B188" t="inlineStr"/>
       <c r="C188" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D188" t="n">
         <v>1</v>
       </c>
       <c r="E188" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F188" t="n">
         <v>0</v>
@@ -8155,19 +8175,19 @@
         <v>0</v>
       </c>
       <c r="I188" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J188" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K188" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L188" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M188" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="189">
@@ -8190,10 +8210,10 @@
         <v>0</v>
       </c>
       <c r="G189" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H189" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I189" t="n">
         <v>0</v>
@@ -8301,37 +8321,37 @@
       </c>
       <c r="B192" t="inlineStr"/>
       <c r="C192" t="n">
+        <v>1</v>
+      </c>
+      <c r="D192" t="n">
+        <v>0</v>
+      </c>
+      <c r="E192" t="n">
+        <v>0</v>
+      </c>
+      <c r="F192" t="n">
+        <v>0</v>
+      </c>
+      <c r="G192" t="n">
+        <v>4</v>
+      </c>
+      <c r="H192" t="n">
+        <v>0</v>
+      </c>
+      <c r="I192" t="n">
+        <v>0</v>
+      </c>
+      <c r="J192" t="n">
+        <v>0</v>
+      </c>
+      <c r="K192" t="n">
+        <v>0</v>
+      </c>
+      <c r="L192" t="n">
         <v>2</v>
       </c>
-      <c r="D192" t="n">
-        <v>1</v>
-      </c>
-      <c r="E192" t="n">
-        <v>0</v>
-      </c>
-      <c r="F192" t="n">
-        <v>0</v>
-      </c>
-      <c r="G192" t="n">
-        <v>0</v>
-      </c>
-      <c r="H192" t="n">
-        <v>4</v>
-      </c>
-      <c r="I192" t="n">
-        <v>0</v>
-      </c>
-      <c r="J192" t="n">
-        <v>0</v>
-      </c>
-      <c r="K192" t="n">
-        <v>0</v>
-      </c>
-      <c r="L192" t="n">
-        <v>0</v>
-      </c>
       <c r="M192" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="193">
@@ -8381,7 +8401,9 @@
           <t>環保潔能服務產業</t>
         </is>
       </c>
-      <c r="B194" t="inlineStr"/>
+      <c r="B194" t="n">
+        <v>0</v>
+      </c>
       <c r="C194" t="n">
         <v>0</v>
       </c>
@@ -8395,13 +8417,13 @@
         <v>0</v>
       </c>
       <c r="G194" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H194" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I194" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J194" t="n">
         <v>1</v>
@@ -8424,7 +8446,7 @@
       </c>
       <c r="B195" t="inlineStr"/>
       <c r="C195" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D195" t="n">
         <v>0</v>
@@ -8445,7 +8467,7 @@
         <v>0</v>
       </c>
       <c r="J195" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K195" t="n">
         <v>1</v>
@@ -8454,7 +8476,7 @@
         <v>1</v>
       </c>
       <c r="M195" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="196">
@@ -8465,37 +8487,37 @@
       </c>
       <c r="B196" t="inlineStr"/>
       <c r="C196" t="n">
+        <v>0</v>
+      </c>
+      <c r="D196" t="n">
+        <v>1</v>
+      </c>
+      <c r="E196" t="n">
+        <v>0</v>
+      </c>
+      <c r="F196" t="n">
+        <v>1</v>
+      </c>
+      <c r="G196" t="n">
+        <v>1</v>
+      </c>
+      <c r="H196" t="n">
+        <v>0</v>
+      </c>
+      <c r="I196" t="n">
+        <v>0</v>
+      </c>
+      <c r="J196" t="n">
         <v>3</v>
       </c>
-      <c r="D196" t="n">
-        <v>0</v>
-      </c>
-      <c r="E196" t="n">
-        <v>1</v>
-      </c>
-      <c r="F196" t="n">
-        <v>0</v>
-      </c>
-      <c r="G196" t="n">
-        <v>1</v>
-      </c>
-      <c r="H196" t="n">
-        <v>1</v>
-      </c>
-      <c r="I196" t="n">
-        <v>0</v>
-      </c>
-      <c r="J196" t="n">
-        <v>0</v>
-      </c>
       <c r="K196" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L196" t="n">
         <v>0</v>
       </c>
       <c r="M196" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="197">
@@ -8506,37 +8528,37 @@
       </c>
       <c r="B197" t="inlineStr"/>
       <c r="C197" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D197" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E197" t="n">
         <v>1</v>
       </c>
       <c r="F197" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G197" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="H197" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="I197" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J197" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="K197" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="L197" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M197" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
     </row>
     <row r="198">
@@ -8571,10 +8593,10 @@
         <v>0</v>
       </c>
       <c r="K198" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L198" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M198" t="n">
         <v>0</v>
@@ -8641,10 +8663,10 @@
         <v>0</v>
       </c>
       <c r="G200" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H200" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I200" t="n">
         <v>0</v>
@@ -8752,7 +8774,7 @@
       </c>
       <c r="B203" t="inlineStr"/>
       <c r="C203" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D203" t="n">
         <v>0</v>
@@ -8779,10 +8801,10 @@
         <v>0</v>
       </c>
       <c r="L203" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M203" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="204">
@@ -8793,34 +8815,34 @@
       </c>
       <c r="B204" t="inlineStr"/>
       <c r="C204" t="n">
+        <v>0</v>
+      </c>
+      <c r="D204" t="n">
+        <v>1</v>
+      </c>
+      <c r="E204" t="n">
+        <v>0</v>
+      </c>
+      <c r="F204" t="n">
+        <v>1</v>
+      </c>
+      <c r="G204" t="n">
+        <v>0</v>
+      </c>
+      <c r="H204" t="n">
+        <v>0</v>
+      </c>
+      <c r="I204" t="n">
+        <v>1</v>
+      </c>
+      <c r="J204" t="n">
         <v>2</v>
       </c>
-      <c r="D204" t="n">
-        <v>0</v>
-      </c>
-      <c r="E204" t="n">
-        <v>1</v>
-      </c>
-      <c r="F204" t="n">
-        <v>0</v>
-      </c>
-      <c r="G204" t="n">
-        <v>1</v>
-      </c>
-      <c r="H204" t="n">
-        <v>0</v>
-      </c>
-      <c r="I204" t="n">
-        <v>0</v>
-      </c>
-      <c r="J204" t="n">
-        <v>1</v>
-      </c>
       <c r="K204" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L204" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M204" t="n">
         <v>0</v>
@@ -8834,7 +8856,7 @@
       </c>
       <c r="B205" t="inlineStr"/>
       <c r="C205" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D205" t="n">
         <v>0</v>
@@ -8861,10 +8883,10 @@
         <v>0</v>
       </c>
       <c r="L205" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M205" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="206">
@@ -8914,17 +8936,15 @@
           <t>矽晶圓/矽晶片</t>
         </is>
       </c>
-      <c r="B207" t="n">
-        <v>0</v>
-      </c>
+      <c r="B207" t="inlineStr"/>
       <c r="C207" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D207" t="n">
         <v>1</v>
       </c>
       <c r="E207" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F207" t="n">
         <v>0</v>
@@ -8961,10 +8981,10 @@
         <v>0</v>
       </c>
       <c r="C208" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D208" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E208" t="n">
         <v>1</v>
@@ -8973,25 +8993,25 @@
         <v>0</v>
       </c>
       <c r="G208" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="H208" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="I208" t="n">
         <v>0</v>
       </c>
       <c r="J208" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="K208" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="L208" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M208" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="209">
@@ -9084,7 +9104,7 @@
       </c>
       <c r="B211" t="inlineStr"/>
       <c r="C211" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D211" t="n">
         <v>0</v>
@@ -9111,10 +9131,10 @@
         <v>0</v>
       </c>
       <c r="L211" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M211" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="212">
@@ -9330,13 +9350,13 @@
       </c>
       <c r="B217" t="inlineStr"/>
       <c r="C217" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D217" t="n">
         <v>1</v>
       </c>
       <c r="E217" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F217" t="n">
         <v>0</v>
@@ -9348,19 +9368,19 @@
         <v>0</v>
       </c>
       <c r="I217" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J217" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K217" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L217" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M217" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="218">
@@ -9369,12 +9389,14 @@
           <t>筆記型電腦</t>
         </is>
       </c>
-      <c r="B218" t="inlineStr"/>
+      <c r="B218" t="n">
+        <v>0</v>
+      </c>
       <c r="C218" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D218" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E218" t="n">
         <v>0</v>
@@ -9383,10 +9405,10 @@
         <v>0</v>
       </c>
       <c r="G218" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H218" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I218" t="n">
         <v>0</v>
@@ -9410,12 +9432,14 @@
           <t>精簡型電腦</t>
         </is>
       </c>
-      <c r="B219" t="inlineStr"/>
+      <c r="B219" t="n">
+        <v>0</v>
+      </c>
       <c r="C219" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D219" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E219" t="n">
         <v>0</v>
@@ -9424,10 +9448,10 @@
         <v>0</v>
       </c>
       <c r="G219" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H219" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I219" t="n">
         <v>0</v>
@@ -9453,37 +9477,37 @@
       </c>
       <c r="B220" t="inlineStr"/>
       <c r="C220" t="n">
+        <v>2</v>
+      </c>
+      <c r="D220" t="n">
+        <v>1</v>
+      </c>
+      <c r="E220" t="n">
+        <v>0</v>
+      </c>
+      <c r="F220" t="n">
+        <v>1</v>
+      </c>
+      <c r="G220" t="n">
         <v>3</v>
       </c>
-      <c r="D220" t="n">
+      <c r="H220" t="n">
+        <v>0</v>
+      </c>
+      <c r="I220" t="n">
         <v>2</v>
       </c>
-      <c r="E220" t="n">
-        <v>1</v>
-      </c>
-      <c r="F220" t="n">
-        <v>0</v>
-      </c>
-      <c r="G220" t="n">
-        <v>1</v>
-      </c>
-      <c r="H220" t="n">
+      <c r="J220" t="n">
+        <v>1</v>
+      </c>
+      <c r="K220" t="n">
         <v>3</v>
       </c>
-      <c r="I220" t="n">
-        <v>0</v>
-      </c>
-      <c r="J220" t="n">
-        <v>2</v>
-      </c>
-      <c r="K220" t="n">
-        <v>1</v>
-      </c>
       <c r="L220" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M220" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="221">
@@ -9494,37 +9518,37 @@
       </c>
       <c r="B221" t="inlineStr"/>
       <c r="C221" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D221" t="n">
+        <v>3</v>
+      </c>
+      <c r="E221" t="n">
+        <v>0</v>
+      </c>
+      <c r="F221" t="n">
+        <v>1</v>
+      </c>
+      <c r="G221" t="n">
+        <v>1</v>
+      </c>
+      <c r="H221" t="n">
+        <v>0</v>
+      </c>
+      <c r="I221" t="n">
+        <v>1</v>
+      </c>
+      <c r="J221" t="n">
+        <v>0</v>
+      </c>
+      <c r="K221" t="n">
+        <v>3</v>
+      </c>
+      <c r="L221" t="n">
+        <v>1</v>
+      </c>
+      <c r="M221" t="n">
         <v>2</v>
-      </c>
-      <c r="E221" t="n">
-        <v>3</v>
-      </c>
-      <c r="F221" t="n">
-        <v>0</v>
-      </c>
-      <c r="G221" t="n">
-        <v>1</v>
-      </c>
-      <c r="H221" t="n">
-        <v>1</v>
-      </c>
-      <c r="I221" t="n">
-        <v>0</v>
-      </c>
-      <c r="J221" t="n">
-        <v>1</v>
-      </c>
-      <c r="K221" t="n">
-        <v>0</v>
-      </c>
-      <c r="L221" t="n">
-        <v>3</v>
-      </c>
-      <c r="M221" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="222">
@@ -9535,10 +9559,10 @@
       </c>
       <c r="B222" t="inlineStr"/>
       <c r="C222" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D222" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E222" t="n">
         <v>0</v>
@@ -9565,7 +9589,7 @@
         <v>0</v>
       </c>
       <c r="M222" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="223">
@@ -9576,7 +9600,7 @@
       </c>
       <c r="B223" t="inlineStr"/>
       <c r="C223" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D223" t="n">
         <v>0</v>
@@ -9600,10 +9624,10 @@
         <v>0</v>
       </c>
       <c r="K223" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L223" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M223" t="n">
         <v>0</v>
@@ -9638,13 +9662,13 @@
         <v>0</v>
       </c>
       <c r="J224" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K224" t="n">
         <v>1</v>
       </c>
       <c r="L224" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M224" t="n">
         <v>0</v>
@@ -9699,7 +9723,7 @@
       </c>
       <c r="B226" t="inlineStr"/>
       <c r="C226" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D226" t="n">
         <v>0</v>
@@ -9781,13 +9805,13 @@
       </c>
       <c r="B228" t="inlineStr"/>
       <c r="C228" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D228" t="n">
         <v>1</v>
       </c>
       <c r="E228" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F228" t="n">
         <v>0</v>
@@ -9799,7 +9823,7 @@
         <v>0</v>
       </c>
       <c r="I228" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J228" t="n">
         <v>1</v>
@@ -9822,13 +9846,13 @@
       </c>
       <c r="B229" t="inlineStr"/>
       <c r="C229" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D229" t="n">
         <v>1</v>
       </c>
       <c r="E229" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F229" t="n">
         <v>0</v>
@@ -9840,19 +9864,19 @@
         <v>0</v>
       </c>
       <c r="I229" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J229" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K229" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L229" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M229" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="230">
@@ -9866,34 +9890,34 @@
         <v>1</v>
       </c>
       <c r="D230" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E230" t="n">
+        <v>0</v>
+      </c>
+      <c r="F230" t="n">
+        <v>0</v>
+      </c>
+      <c r="G230" t="n">
+        <v>3</v>
+      </c>
+      <c r="H230" t="n">
+        <v>1</v>
+      </c>
+      <c r="I230" t="n">
+        <v>3</v>
+      </c>
+      <c r="J230" t="n">
+        <v>0</v>
+      </c>
+      <c r="K230" t="n">
         <v>2</v>
-      </c>
-      <c r="F230" t="n">
-        <v>0</v>
-      </c>
-      <c r="G230" t="n">
-        <v>0</v>
-      </c>
-      <c r="H230" t="n">
-        <v>3</v>
-      </c>
-      <c r="I230" t="n">
-        <v>1</v>
-      </c>
-      <c r="J230" t="n">
-        <v>3</v>
-      </c>
-      <c r="K230" t="n">
-        <v>0</v>
       </c>
       <c r="L230" t="n">
         <v>2</v>
       </c>
       <c r="M230" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="231">
@@ -9910,7 +9934,7 @@
         <v>1</v>
       </c>
       <c r="E231" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F231" t="n">
         <v>0</v>
@@ -9922,19 +9946,19 @@
         <v>0</v>
       </c>
       <c r="I231" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J231" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K231" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L231" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M231" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="232">
@@ -9943,30 +9967,32 @@
           <t>線上遊戲業</t>
         </is>
       </c>
-      <c r="B232" t="inlineStr"/>
+      <c r="B232" t="n">
+        <v>0</v>
+      </c>
       <c r="C232" t="n">
         <v>0</v>
       </c>
       <c r="D232" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E232" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F232" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G232" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H232" t="n">
         <v>0</v>
       </c>
       <c r="I232" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J232" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K232" t="n">
         <v>0</v>
@@ -9986,28 +10012,28 @@
       </c>
       <c r="B233" t="inlineStr"/>
       <c r="C233" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D233" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E233" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F233" t="n">
         <v>0</v>
       </c>
       <c r="G233" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H233" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I233" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J233" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K233" t="n">
         <v>0</v>
@@ -10025,9 +10051,7 @@
           <t>線材盤元</t>
         </is>
       </c>
-      <c r="B234" t="n">
-        <v>0</v>
-      </c>
+      <c r="B234" t="inlineStr"/>
       <c r="C234" t="n">
         <v>0</v>
       </c>
@@ -10070,7 +10094,7 @@
       </c>
       <c r="B235" t="inlineStr"/>
       <c r="C235" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D235" t="n">
         <v>0</v>
@@ -10088,16 +10112,16 @@
         <v>0</v>
       </c>
       <c r="I235" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J235" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K235" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L235" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M235" t="n">
         <v>0</v>
@@ -10111,7 +10135,7 @@
       </c>
       <c r="B236" t="inlineStr"/>
       <c r="C236" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D236" t="n">
         <v>0</v>
@@ -10132,13 +10156,13 @@
         <v>0</v>
       </c>
       <c r="J236" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K236" t="n">
         <v>1</v>
       </c>
       <c r="L236" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M236" t="n">
         <v>0</v>
@@ -10173,13 +10197,13 @@
         <v>0</v>
       </c>
       <c r="J237" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K237" t="n">
         <v>1</v>
       </c>
       <c r="L237" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M237" t="n">
         <v>0</v>
@@ -10193,13 +10217,13 @@
       </c>
       <c r="B238" t="inlineStr"/>
       <c r="C238" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D238" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E238" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F238" t="n">
         <v>0</v>
@@ -10217,10 +10241,10 @@
         <v>0</v>
       </c>
       <c r="K238" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L238" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M238" t="n">
         <v>0</v>
@@ -10237,19 +10261,19 @@
         <v>0</v>
       </c>
       <c r="D239" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E239" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F239" t="n">
         <v>0</v>
       </c>
       <c r="G239" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H239" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I239" t="n">
         <v>0</v>
@@ -10258,13 +10282,13 @@
         <v>0</v>
       </c>
       <c r="K239" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L239" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M239" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="240">
@@ -10275,7 +10299,7 @@
       </c>
       <c r="B240" t="inlineStr"/>
       <c r="C240" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D240" t="n">
         <v>0</v>
@@ -10296,13 +10320,13 @@
         <v>0</v>
       </c>
       <c r="J240" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K240" t="n">
         <v>1</v>
       </c>
       <c r="L240" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M240" t="n">
         <v>0</v>
@@ -10337,10 +10361,10 @@
         <v>0</v>
       </c>
       <c r="J241" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K241" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L241" t="n">
         <v>0</v>
@@ -10369,22 +10393,22 @@
         <v>0</v>
       </c>
       <c r="G242" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H242" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I242" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J242" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K242" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L242" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M242" t="n">
         <v>0</v>
@@ -10422,10 +10446,10 @@
         <v>0</v>
       </c>
       <c r="K243" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L243" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M243" t="n">
         <v>0</v>
@@ -10498,10 +10522,10 @@
         <v>0</v>
       </c>
       <c r="I245" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J245" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K245" t="n">
         <v>0</v>
@@ -10521,10 +10545,10 @@
       </c>
       <c r="B246" t="inlineStr"/>
       <c r="C246" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D246" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E246" t="n">
         <v>0</v>
@@ -10539,16 +10563,16 @@
         <v>0</v>
       </c>
       <c r="I246" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J246" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K246" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L246" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M246" t="n">
         <v>0</v>
@@ -10562,7 +10586,7 @@
       </c>
       <c r="B247" t="inlineStr"/>
       <c r="C247" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D247" t="n">
         <v>0</v>
@@ -10583,10 +10607,10 @@
         <v>0</v>
       </c>
       <c r="J247" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K247" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L247" t="n">
         <v>0</v>
@@ -10601,7 +10625,9 @@
           <t>藥品代理銷售及通路</t>
         </is>
       </c>
-      <c r="B248" t="inlineStr"/>
+      <c r="B248" t="n">
+        <v>0</v>
+      </c>
       <c r="C248" t="n">
         <v>0</v>
       </c>
@@ -10624,16 +10650,16 @@
         <v>0</v>
       </c>
       <c r="J248" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K248" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L248" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M248" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="249">
@@ -10685,7 +10711,7 @@
       </c>
       <c r="B250" t="inlineStr"/>
       <c r="C250" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D250" t="n">
         <v>0</v>
@@ -10712,10 +10738,10 @@
         <v>0</v>
       </c>
       <c r="L250" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M250" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="251">
@@ -10767,10 +10793,10 @@
       </c>
       <c r="B252" t="inlineStr"/>
       <c r="C252" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D252" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E252" t="n">
         <v>0</v>
@@ -10785,16 +10811,16 @@
         <v>0</v>
       </c>
       <c r="I252" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J252" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K252" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L252" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M252" t="n">
         <v>0</v>
@@ -10893,10 +10919,10 @@
         <v>0</v>
       </c>
       <c r="D255" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E255" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F255" t="n">
         <v>0</v>
@@ -10949,16 +10975,16 @@
         <v>0</v>
       </c>
       <c r="I256" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J256" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K256" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L256" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M256" t="n">
         <v>0</v>
@@ -11054,7 +11080,7 @@
       </c>
       <c r="B259" t="inlineStr"/>
       <c r="C259" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D259" t="n">
         <v>0</v>
@@ -11160,10 +11186,10 @@
         <v>0</v>
       </c>
       <c r="K261" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L261" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M261" t="n">
         <v>0</v>
@@ -11177,37 +11203,37 @@
       </c>
       <c r="B262" t="inlineStr"/>
       <c r="C262" t="n">
+        <v>0</v>
+      </c>
+      <c r="D262" t="n">
+        <v>2</v>
+      </c>
+      <c r="E262" t="n">
+        <v>0</v>
+      </c>
+      <c r="F262" t="n">
+        <v>0</v>
+      </c>
+      <c r="G262" t="n">
+        <v>0</v>
+      </c>
+      <c r="H262" t="n">
+        <v>0</v>
+      </c>
+      <c r="I262" t="n">
+        <v>0</v>
+      </c>
+      <c r="J262" t="n">
+        <v>1</v>
+      </c>
+      <c r="K262" t="n">
+        <v>1</v>
+      </c>
+      <c r="L262" t="n">
+        <v>2</v>
+      </c>
+      <c r="M262" t="n">
         <v>3</v>
-      </c>
-      <c r="D262" t="n">
-        <v>0</v>
-      </c>
-      <c r="E262" t="n">
-        <v>2</v>
-      </c>
-      <c r="F262" t="n">
-        <v>0</v>
-      </c>
-      <c r="G262" t="n">
-        <v>0</v>
-      </c>
-      <c r="H262" t="n">
-        <v>0</v>
-      </c>
-      <c r="I262" t="n">
-        <v>0</v>
-      </c>
-      <c r="J262" t="n">
-        <v>0</v>
-      </c>
-      <c r="K262" t="n">
-        <v>1</v>
-      </c>
-      <c r="L262" t="n">
-        <v>1</v>
-      </c>
-      <c r="M262" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="263">
@@ -11218,7 +11244,7 @@
       </c>
       <c r="B263" t="inlineStr"/>
       <c r="C263" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D263" t="n">
         <v>0</v>
@@ -11227,13 +11253,13 @@
         <v>0</v>
       </c>
       <c r="F263" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G263" t="n">
         <v>1</v>
       </c>
       <c r="H263" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I263" t="n">
         <v>0</v>
@@ -11245,10 +11271,10 @@
         <v>0</v>
       </c>
       <c r="L263" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M263" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="264">
@@ -11262,7 +11288,7 @@
         <v>1</v>
       </c>
       <c r="D264" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E264" t="n">
         <v>0</v>
@@ -11271,25 +11297,25 @@
         <v>0</v>
       </c>
       <c r="G264" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H264" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I264" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J264" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K264" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L264" t="n">
         <v>1</v>
       </c>
       <c r="M264" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="265">
@@ -11391,10 +11417,10 @@
         <v>0</v>
       </c>
       <c r="F267" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G267" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H267" t="n">
         <v>0</v>
@@ -11485,7 +11511,7 @@
         <v>0</v>
       </c>
       <c r="J269" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K269" t="n">
         <v>1</v>
@@ -11505,10 +11531,10 @@
       </c>
       <c r="B270" t="inlineStr"/>
       <c r="C270" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D270" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E270" t="n">
         <v>0</v>
@@ -11517,19 +11543,19 @@
         <v>0</v>
       </c>
       <c r="G270" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H270" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I270" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J270" t="n">
         <v>1</v>
       </c>
       <c r="K270" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L270" t="n">
         <v>0</v>
@@ -11587,13 +11613,13 @@
       </c>
       <c r="B272" t="inlineStr"/>
       <c r="C272" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D272" t="n">
         <v>1</v>
       </c>
       <c r="E272" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F272" t="n">
         <v>0</v>
@@ -11605,19 +11631,19 @@
         <v>0</v>
       </c>
       <c r="I272" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J272" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K272" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L272" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M272" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="273">
@@ -11628,10 +11654,10 @@
       </c>
       <c r="B273" t="inlineStr"/>
       <c r="C273" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D273" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E273" t="n">
         <v>0</v>
@@ -11646,16 +11672,16 @@
         <v>0</v>
       </c>
       <c r="I273" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J273" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K273" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L273" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M273" t="n">
         <v>0</v>
@@ -11669,13 +11695,13 @@
       </c>
       <c r="B274" t="inlineStr"/>
       <c r="C274" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D274" t="n">
         <v>1</v>
       </c>
       <c r="E274" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F274" t="n">
         <v>0</v>
@@ -11687,19 +11713,19 @@
         <v>0</v>
       </c>
       <c r="I274" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J274" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K274" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L274" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M274" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="275">
@@ -11713,7 +11739,7 @@
         <v>1</v>
       </c>
       <c r="D275" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E275" t="n">
         <v>0</v>
@@ -11728,19 +11754,19 @@
         <v>0</v>
       </c>
       <c r="I275" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J275" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K275" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L275" t="n">
         <v>1</v>
       </c>
       <c r="M275" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="276">
@@ -11751,13 +11777,13 @@
       </c>
       <c r="B276" t="inlineStr"/>
       <c r="C276" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D276" t="n">
         <v>1</v>
       </c>
       <c r="E276" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F276" t="n">
         <v>0</v>
@@ -11769,19 +11795,19 @@
         <v>0</v>
       </c>
       <c r="I276" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J276" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K276" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L276" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M276" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="277">
@@ -11836,7 +11862,7 @@
         <v>1</v>
       </c>
       <c r="D278" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E278" t="n">
         <v>0</v>
@@ -11851,19 +11877,19 @@
         <v>0</v>
       </c>
       <c r="I278" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J278" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K278" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L278" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M278" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="279">
@@ -11874,7 +11900,7 @@
       </c>
       <c r="B279" t="inlineStr"/>
       <c r="C279" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D279" t="n">
         <v>0</v>
@@ -11901,10 +11927,10 @@
         <v>0</v>
       </c>
       <c r="L279" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M279" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="280">
@@ -11956,13 +11982,13 @@
       </c>
       <c r="B281" t="inlineStr"/>
       <c r="C281" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D281" t="n">
         <v>1</v>
       </c>
       <c r="E281" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F281" t="n">
         <v>0</v>
@@ -11974,19 +12000,19 @@
         <v>0</v>
       </c>
       <c r="I281" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J281" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K281" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L281" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M281" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="282">
@@ -12021,10 +12047,10 @@
         <v>0</v>
       </c>
       <c r="K282" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L282" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M282" t="n">
         <v>0</v>
@@ -12205,7 +12231,7 @@
         <v>1</v>
       </c>
       <c r="D287" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E287" t="n">
         <v>0</v>
@@ -12220,19 +12246,19 @@
         <v>0</v>
       </c>
       <c r="I287" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J287" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K287" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L287" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M287" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="288">
@@ -12273,7 +12299,7 @@
         <v>0</v>
       </c>
       <c r="M288" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="289">
@@ -12296,10 +12322,10 @@
         <v>0</v>
       </c>
       <c r="G289" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H289" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I289" t="n">
         <v>0</v>
@@ -12323,40 +12349,20 @@
           <t>軟性電路板</t>
         </is>
       </c>
-      <c r="B290" t="inlineStr"/>
-      <c r="C290" t="n">
-        <v>0</v>
-      </c>
-      <c r="D290" t="n">
-        <v>0</v>
-      </c>
-      <c r="E290" t="n">
-        <v>0</v>
-      </c>
-      <c r="F290" t="n">
-        <v>0</v>
-      </c>
-      <c r="G290" t="n">
-        <v>0</v>
-      </c>
-      <c r="H290" t="n">
-        <v>0</v>
-      </c>
-      <c r="I290" t="n">
-        <v>0</v>
-      </c>
-      <c r="J290" t="n">
-        <v>0</v>
-      </c>
-      <c r="K290" t="n">
-        <v>0</v>
-      </c>
-      <c r="L290" t="n">
-        <v>0</v>
-      </c>
-      <c r="M290" t="n">
-        <v>0</v>
-      </c>
+      <c r="B290" t="n">
+        <v>0</v>
+      </c>
+      <c r="C290" t="inlineStr"/>
+      <c r="D290" t="inlineStr"/>
+      <c r="E290" t="inlineStr"/>
+      <c r="F290" t="inlineStr"/>
+      <c r="G290" t="inlineStr"/>
+      <c r="H290" t="inlineStr"/>
+      <c r="I290" t="inlineStr"/>
+      <c r="J290" t="inlineStr"/>
+      <c r="K290" t="inlineStr"/>
+      <c r="L290" t="inlineStr"/>
+      <c r="M290" t="inlineStr"/>
     </row>
     <row r="291">
       <c r="A291" s="1" t="inlineStr">
@@ -12516,10 +12522,10 @@
         <v>0</v>
       </c>
       <c r="L294" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M294" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="295">
@@ -12542,10 +12548,10 @@
         <v>0</v>
       </c>
       <c r="G295" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H295" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I295" t="n">
         <v>0</v>
@@ -12571,7 +12577,7 @@
       </c>
       <c r="B296" t="inlineStr"/>
       <c r="C296" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D296" t="n">
         <v>0</v>
@@ -12592,13 +12598,13 @@
         <v>0</v>
       </c>
       <c r="J296" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K296" t="n">
         <v>1</v>
       </c>
       <c r="L296" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M296" t="n">
         <v>0</v>
@@ -12674,13 +12680,13 @@
         <v>0</v>
       </c>
       <c r="J298" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K298" t="n">
         <v>1</v>
       </c>
       <c r="L298" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M298" t="n">
         <v>0</v>
@@ -12776,10 +12782,10 @@
       </c>
       <c r="B301" t="inlineStr"/>
       <c r="C301" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D301" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E301" t="n">
         <v>0</v>
@@ -12794,16 +12800,16 @@
         <v>0</v>
       </c>
       <c r="I301" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J301" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K301" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L301" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M301" t="n">
         <v>0</v>
@@ -12815,39 +12821,41 @@
           <t>連接器設計、組裝及製造</t>
         </is>
       </c>
-      <c r="B302" t="inlineStr"/>
+      <c r="B302" t="n">
+        <v>0</v>
+      </c>
       <c r="C302" t="n">
+        <v>1</v>
+      </c>
+      <c r="D302" t="n">
         <v>2</v>
       </c>
-      <c r="D302" t="n">
-        <v>1</v>
-      </c>
       <c r="E302" t="n">
+        <v>0</v>
+      </c>
+      <c r="F302" t="n">
+        <v>0</v>
+      </c>
+      <c r="G302" t="n">
+        <v>1</v>
+      </c>
+      <c r="H302" t="n">
+        <v>0</v>
+      </c>
+      <c r="I302" t="n">
         <v>2</v>
-      </c>
-      <c r="F302" t="n">
-        <v>0</v>
-      </c>
-      <c r="G302" t="n">
-        <v>0</v>
-      </c>
-      <c r="H302" t="n">
-        <v>1</v>
-      </c>
-      <c r="I302" t="n">
-        <v>0</v>
       </c>
       <c r="J302" t="n">
         <v>2</v>
       </c>
       <c r="K302" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L302" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M302" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="303">
@@ -12858,31 +12866,31 @@
       </c>
       <c r="B303" t="inlineStr"/>
       <c r="C303" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D303" t="n">
         <v>1</v>
       </c>
       <c r="E303" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F303" t="n">
         <v>0</v>
       </c>
       <c r="G303" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H303" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I303" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J303" t="n">
         <v>1</v>
       </c>
       <c r="K303" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L303" t="n">
         <v>0</v>
@@ -13022,7 +13030,7 @@
       </c>
       <c r="B307" t="inlineStr"/>
       <c r="C307" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D307" t="n">
         <v>0</v>
@@ -13034,10 +13042,10 @@
         <v>0</v>
       </c>
       <c r="G307" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H307" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I307" t="n">
         <v>0</v>
@@ -13049,10 +13057,10 @@
         <v>0</v>
       </c>
       <c r="L307" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M307" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="308">
@@ -13075,10 +13083,10 @@
         <v>0</v>
       </c>
       <c r="G308" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H308" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I308" t="n">
         <v>0</v>
@@ -13087,13 +13095,13 @@
         <v>0</v>
       </c>
       <c r="K308" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L308" t="n">
         <v>1</v>
       </c>
       <c r="M308" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="309">
@@ -13145,7 +13153,7 @@
       </c>
       <c r="B310" t="inlineStr"/>
       <c r="C310" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D310" t="n">
         <v>0</v>
@@ -13154,13 +13162,13 @@
         <v>0</v>
       </c>
       <c r="F310" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G310" t="n">
         <v>1</v>
       </c>
       <c r="H310" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I310" t="n">
         <v>0</v>
@@ -13195,10 +13203,10 @@
         <v>0</v>
       </c>
       <c r="F311" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G311" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H311" t="n">
         <v>0</v>
@@ -13227,7 +13235,7 @@
       </c>
       <c r="B312" t="inlineStr"/>
       <c r="C312" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D312" t="n">
         <v>0</v>
@@ -13254,10 +13262,10 @@
         <v>0</v>
       </c>
       <c r="L312" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M312" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="313">
@@ -13268,7 +13276,7 @@
       </c>
       <c r="B313" t="inlineStr"/>
       <c r="C313" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D313" t="n">
         <v>0</v>
@@ -13280,25 +13288,25 @@
         <v>0</v>
       </c>
       <c r="G313" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H313" t="n">
+        <v>1</v>
+      </c>
+      <c r="I313" t="n">
+        <v>0</v>
+      </c>
+      <c r="J313" t="n">
         <v>2</v>
       </c>
-      <c r="I313" t="n">
-        <v>1</v>
-      </c>
-      <c r="J313" t="n">
-        <v>0</v>
-      </c>
       <c r="K313" t="n">
+        <v>0</v>
+      </c>
+      <c r="L313" t="n">
         <v>2</v>
       </c>
-      <c r="L313" t="n">
-        <v>0</v>
-      </c>
       <c r="M313" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="314">
@@ -13307,39 +13315,41 @@
           <t>醫療器材研發、設計、製造</t>
         </is>
       </c>
-      <c r="B314" t="inlineStr"/>
+      <c r="B314" t="n">
+        <v>0</v>
+      </c>
       <c r="C314" t="n">
         <v>0</v>
       </c>
       <c r="D314" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E314" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F314" t="n">
         <v>0</v>
       </c>
       <c r="G314" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H314" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I314" t="n">
         <v>0</v>
       </c>
       <c r="J314" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K314" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L314" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M314" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="315">
@@ -13371,10 +13381,10 @@
         <v>0</v>
       </c>
       <c r="J315" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K315" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L315" t="n">
         <v>0</v>
@@ -13391,10 +13401,10 @@
       </c>
       <c r="B316" t="inlineStr"/>
       <c r="C316" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D316" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E316" t="n">
         <v>0</v>
@@ -13409,10 +13419,10 @@
         <v>0</v>
       </c>
       <c r="I316" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J316" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K316" t="n">
         <v>0</v>
@@ -13456,10 +13466,10 @@
         <v>0</v>
       </c>
       <c r="K317" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L317" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M317" t="n">
         <v>0</v>
@@ -13471,14 +13481,12 @@
           <t>金屬加工處理</t>
         </is>
       </c>
-      <c r="B318" t="n">
-        <v>0</v>
-      </c>
+      <c r="B318" t="inlineStr"/>
       <c r="C318" t="n">
         <v>0</v>
       </c>
       <c r="D318" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E318" t="n">
         <v>0</v>
@@ -13499,10 +13507,10 @@
         <v>0</v>
       </c>
       <c r="K318" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L318" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M318" t="n">
         <v>0</v>
@@ -13704,10 +13712,10 @@
         <v>0</v>
       </c>
       <c r="K323" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L323" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M323" t="n">
         <v>0</v>
@@ -13751,7 +13759,7 @@
         <v>0</v>
       </c>
       <c r="M324" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="325">
@@ -13762,7 +13770,7 @@
       </c>
       <c r="B325" t="inlineStr"/>
       <c r="C325" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D325" t="n">
         <v>0</v>
@@ -13774,10 +13782,10 @@
         <v>0</v>
       </c>
       <c r="G325" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H325" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I325" t="n">
         <v>0</v>
@@ -13789,10 +13797,10 @@
         <v>0</v>
       </c>
       <c r="L325" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M325" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="326">
@@ -13803,7 +13811,7 @@
       </c>
       <c r="B326" t="inlineStr"/>
       <c r="C326" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D326" t="n">
         <v>0</v>
@@ -13815,25 +13823,25 @@
         <v>0</v>
       </c>
       <c r="G326" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H326" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I326" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J326" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K326" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L326" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M326" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="327">
@@ -13844,10 +13852,10 @@
       </c>
       <c r="B327" t="inlineStr"/>
       <c r="C327" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D327" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E327" t="n">
         <v>0</v>
@@ -13929,19 +13937,19 @@
         <v>1</v>
       </c>
       <c r="D329" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E329" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F329" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G329" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H329" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I329" t="n">
         <v>0</v>
@@ -14049,7 +14057,7 @@
       </c>
       <c r="B332" t="inlineStr"/>
       <c r="C332" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D332" t="n">
         <v>0</v>
@@ -14129,14 +14137,12 @@
           <t>鋼鑄鐵元件</t>
         </is>
       </c>
-      <c r="B334" t="n">
-        <v>0</v>
-      </c>
+      <c r="B334" t="inlineStr"/>
       <c r="C334" t="n">
         <v>0</v>
       </c>
       <c r="D334" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E334" t="n">
         <v>0</v>
@@ -14256,7 +14262,7 @@
       </c>
       <c r="B337" t="inlineStr"/>
       <c r="C337" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D337" t="n">
         <v>0</v>
@@ -14277,16 +14283,16 @@
         <v>0</v>
       </c>
       <c r="J337" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K337" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L337" t="n">
         <v>0</v>
       </c>
       <c r="M337" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="338">
@@ -14297,7 +14303,7 @@
       </c>
       <c r="B338" t="inlineStr"/>
       <c r="C338" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D338" t="n">
         <v>0</v>
@@ -14324,10 +14330,10 @@
         <v>0</v>
       </c>
       <c r="L338" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M338" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="339">
@@ -14344,7 +14350,7 @@
         <v>1</v>
       </c>
       <c r="E339" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F339" t="n">
         <v>0</v>
@@ -14356,19 +14362,19 @@
         <v>0</v>
       </c>
       <c r="I339" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J339" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K339" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L339" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M339" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="340">
@@ -14382,7 +14388,7 @@
         <v>1</v>
       </c>
       <c r="D340" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E340" t="n">
         <v>0</v>
@@ -14397,19 +14403,19 @@
         <v>0</v>
       </c>
       <c r="I340" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J340" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K340" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L340" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M340" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="341">
@@ -14423,7 +14429,7 @@
         <v>1</v>
       </c>
       <c r="D341" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E341" t="n">
         <v>0</v>
@@ -14432,25 +14438,25 @@
         <v>0</v>
       </c>
       <c r="G341" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H341" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I341" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J341" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K341" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L341" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M341" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="342">
@@ -14467,22 +14473,22 @@
         <v>0</v>
       </c>
       <c r="E342" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F342" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G342" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H342" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I342" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J342" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K342" t="n">
         <v>0</v>
@@ -14514,19 +14520,19 @@
         <v>0</v>
       </c>
       <c r="G343" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H343" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I343" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J343" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K343" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L343" t="n">
         <v>0</v>
@@ -14543,7 +14549,7 @@
       </c>
       <c r="B344" t="inlineStr"/>
       <c r="C344" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D344" t="n">
         <v>0</v>
@@ -14593,13 +14599,13 @@
         <v>0</v>
       </c>
       <c r="F345" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G345" t="n">
         <v>1</v>
       </c>
       <c r="H345" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I345" t="n">
         <v>0</v>
@@ -14625,7 +14631,7 @@
       </c>
       <c r="B346" t="inlineStr"/>
       <c r="C346" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D346" t="n">
         <v>0</v>
@@ -14634,13 +14640,13 @@
         <v>0</v>
       </c>
       <c r="F346" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G346" t="n">
         <v>1</v>
       </c>
       <c r="H346" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I346" t="n">
         <v>0</v>
@@ -14649,7 +14655,7 @@
         <v>0</v>
       </c>
       <c r="K346" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L346" t="n">
         <v>1</v>
@@ -14690,10 +14696,10 @@
         <v>0</v>
       </c>
       <c r="K347" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L347" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M347" t="n">
         <v>0</v>
@@ -14707,10 +14713,10 @@
       </c>
       <c r="B348" t="inlineStr"/>
       <c r="C348" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D348" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E348" t="n">
         <v>0</v>
@@ -14719,10 +14725,10 @@
         <v>0</v>
       </c>
       <c r="G348" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H348" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I348" t="n">
         <v>0</v>
@@ -14731,10 +14737,10 @@
         <v>0</v>
       </c>
       <c r="K348" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L348" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M348" t="n">
         <v>0</v>
@@ -14760,10 +14766,10 @@
         <v>0</v>
       </c>
       <c r="G349" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H349" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I349" t="n">
         <v>0</v>
@@ -14836,25 +14842,25 @@
         <v>1</v>
       </c>
       <c r="E351" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F351" t="n">
         <v>0</v>
       </c>
       <c r="G351" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H351" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I351" t="n">
         <v>0</v>
       </c>
       <c r="J351" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K351" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L351" t="n">
         <v>0</v>
@@ -14869,20 +14875,18 @@
           <t>電容器</t>
         </is>
       </c>
-      <c r="B352" t="n">
-        <v>0</v>
-      </c>
+      <c r="B352" t="inlineStr"/>
       <c r="C352" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D352" t="n">
         <v>0</v>
       </c>
       <c r="E352" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F352" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G352" t="n">
         <v>3</v>
@@ -14891,19 +14895,19 @@
         <v>2</v>
       </c>
       <c r="I352" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J352" t="n">
+        <v>1</v>
+      </c>
+      <c r="K352" t="n">
+        <v>0</v>
+      </c>
+      <c r="L352" t="n">
+        <v>3</v>
+      </c>
+      <c r="M352" t="n">
         <v>2</v>
-      </c>
-      <c r="K352" t="n">
-        <v>1</v>
-      </c>
-      <c r="L352" t="n">
-        <v>0</v>
-      </c>
-      <c r="M352" t="n">
-        <v>3</v>
       </c>
     </row>
     <row r="353">
@@ -14912,9 +14916,11 @@
           <t>電容器材料(如電蝕／化成鋁箔、介面瓷粉)</t>
         </is>
       </c>
-      <c r="B353" t="inlineStr"/>
+      <c r="B353" t="n">
+        <v>0</v>
+      </c>
       <c r="C353" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D353" t="n">
         <v>0</v>
@@ -14923,10 +14929,10 @@
         <v>0</v>
       </c>
       <c r="F353" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G353" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H353" t="n">
         <v>0</v>
@@ -14944,7 +14950,7 @@
         <v>0</v>
       </c>
       <c r="M353" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="354">
@@ -14953,41 +14959,39 @@
           <t>電感器</t>
         </is>
       </c>
-      <c r="B354" t="n">
-        <v>0</v>
-      </c>
+      <c r="B354" t="inlineStr"/>
       <c r="C354" t="n">
         <v>2</v>
       </c>
       <c r="D354" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E354" t="n">
         <v>0</v>
       </c>
       <c r="F354" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G354" t="n">
+        <v>1</v>
+      </c>
+      <c r="H354" t="n">
+        <v>0</v>
+      </c>
+      <c r="I354" t="n">
+        <v>0</v>
+      </c>
+      <c r="J354" t="n">
+        <v>0</v>
+      </c>
+      <c r="K354" t="n">
+        <v>0</v>
+      </c>
+      <c r="L354" t="n">
         <v>2</v>
       </c>
-      <c r="H354" t="n">
-        <v>1</v>
-      </c>
-      <c r="I354" t="n">
-        <v>0</v>
-      </c>
-      <c r="J354" t="n">
-        <v>0</v>
-      </c>
-      <c r="K354" t="n">
-        <v>0</v>
-      </c>
-      <c r="L354" t="n">
-        <v>0</v>
-      </c>
       <c r="M354" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="355">
@@ -15000,7 +15004,7 @@
         <v>0</v>
       </c>
       <c r="C355" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D355" t="n">
         <v>0</v>
@@ -15027,7 +15031,7 @@
         <v>0</v>
       </c>
       <c r="L355" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M355" t="n">
         <v>0</v>
@@ -15041,7 +15045,7 @@
       </c>
       <c r="B356" t="inlineStr"/>
       <c r="C356" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D356" t="n">
         <v>0</v>
@@ -15053,10 +15057,10 @@
         <v>0</v>
       </c>
       <c r="G356" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H356" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I356" t="n">
         <v>0</v>
@@ -15068,10 +15072,10 @@
         <v>0</v>
       </c>
       <c r="L356" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M356" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="357">
@@ -15094,10 +15098,10 @@
         <v>0</v>
       </c>
       <c r="G357" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H357" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I357" t="n">
         <v>0</v>
@@ -15106,13 +15110,13 @@
         <v>0</v>
       </c>
       <c r="K357" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L357" t="n">
         <v>1</v>
       </c>
       <c r="M357" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="358">
@@ -15129,16 +15133,16 @@
         <v>0</v>
       </c>
       <c r="E358" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F358" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G358" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H358" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I358" t="n">
         <v>0</v>
@@ -15147,13 +15151,13 @@
         <v>0</v>
       </c>
       <c r="K358" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L358" t="n">
         <v>1</v>
       </c>
       <c r="M358" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="359">
@@ -15170,16 +15174,16 @@
         <v>0</v>
       </c>
       <c r="E359" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F359" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G359" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H359" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I359" t="n">
         <v>0</v>
@@ -15208,28 +15212,28 @@
         <v>1</v>
       </c>
       <c r="D360" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E360" t="n">
         <v>0</v>
       </c>
       <c r="F360" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G360" t="n">
         <v>1</v>
       </c>
       <c r="H360" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I360" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J360" t="n">
         <v>2</v>
       </c>
       <c r="K360" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L360" t="n">
         <v>1</v>
@@ -15255,10 +15259,10 @@
         <v>0</v>
       </c>
       <c r="F361" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G361" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H361" t="n">
         <v>0</v>
@@ -15328,7 +15332,7 @@
       </c>
       <c r="B363" t="inlineStr"/>
       <c r="C363" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D363" t="n">
         <v>0</v>
@@ -15372,19 +15376,19 @@
         <v>0</v>
       </c>
       <c r="D364" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E364" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F364" t="n">
         <v>0</v>
       </c>
       <c r="G364" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H364" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I364" t="n">
         <v>0</v>
@@ -15399,7 +15403,7 @@
         <v>0</v>
       </c>
       <c r="M364" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="365">
@@ -15410,37 +15414,37 @@
       </c>
       <c r="B365" t="inlineStr"/>
       <c r="C365" t="n">
+        <v>0</v>
+      </c>
+      <c r="D365" t="n">
+        <v>0</v>
+      </c>
+      <c r="E365" t="n">
+        <v>0</v>
+      </c>
+      <c r="F365" t="n">
+        <v>0</v>
+      </c>
+      <c r="G365" t="n">
         <v>2</v>
       </c>
-      <c r="D365" t="n">
-        <v>0</v>
-      </c>
-      <c r="E365" t="n">
-        <v>0</v>
-      </c>
-      <c r="F365" t="n">
-        <v>0</v>
-      </c>
-      <c r="G365" t="n">
-        <v>0</v>
-      </c>
       <c r="H365" t="n">
+        <v>0</v>
+      </c>
+      <c r="I365" t="n">
+        <v>0</v>
+      </c>
+      <c r="J365" t="n">
+        <v>1</v>
+      </c>
+      <c r="K365" t="n">
+        <v>1</v>
+      </c>
+      <c r="L365" t="n">
         <v>2</v>
       </c>
-      <c r="I365" t="n">
-        <v>0</v>
-      </c>
-      <c r="J365" t="n">
-        <v>0</v>
-      </c>
-      <c r="K365" t="n">
-        <v>1</v>
-      </c>
-      <c r="L365" t="n">
-        <v>1</v>
-      </c>
       <c r="M365" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="366">
@@ -15533,22 +15537,22 @@
       </c>
       <c r="B368" t="inlineStr"/>
       <c r="C368" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D368" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E368" t="n">
         <v>0</v>
       </c>
       <c r="F368" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G368" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H368" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I368" t="n">
         <v>0</v>
@@ -15572,7 +15576,9 @@
           <t>電阻器材料(氧化鋁陶瓷基板、導電漿墨)</t>
         </is>
       </c>
-      <c r="B369" t="inlineStr"/>
+      <c r="B369" t="n">
+        <v>0</v>
+      </c>
       <c r="C369" t="n">
         <v>0</v>
       </c>
@@ -15613,9 +15619,7 @@
           <t>面板</t>
         </is>
       </c>
-      <c r="B370" t="n">
-        <v>0</v>
-      </c>
+      <c r="B370" t="inlineStr"/>
       <c r="C370" t="n">
         <v>0</v>
       </c>
@@ -15629,10 +15633,10 @@
         <v>0</v>
       </c>
       <c r="G370" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H370" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I370" t="n">
         <v>0</v>
@@ -15746,28 +15750,28 @@
         <v>1</v>
       </c>
       <c r="E373" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F373" t="n">
         <v>0</v>
       </c>
       <c r="G373" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H373" t="n">
+        <v>1</v>
+      </c>
+      <c r="I373" t="n">
+        <v>1</v>
+      </c>
+      <c r="J373" t="n">
+        <v>1</v>
+      </c>
+      <c r="K373" t="n">
         <v>2</v>
       </c>
-      <c r="I373" t="n">
-        <v>1</v>
-      </c>
-      <c r="J373" t="n">
-        <v>1</v>
-      </c>
-      <c r="K373" t="n">
-        <v>1</v>
-      </c>
       <c r="L373" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M373" t="n">
         <v>1</v>
@@ -15822,7 +15826,7 @@
       </c>
       <c r="B375" t="inlineStr"/>
       <c r="C375" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D375" t="n">
         <v>0</v>
@@ -15863,37 +15867,37 @@
       </c>
       <c r="B376" t="inlineStr"/>
       <c r="C376" t="n">
+        <v>2</v>
+      </c>
+      <c r="D376" t="n">
+        <v>0</v>
+      </c>
+      <c r="E376" t="n">
+        <v>0</v>
+      </c>
+      <c r="F376" t="n">
+        <v>1</v>
+      </c>
+      <c r="G376" t="n">
         <v>3</v>
       </c>
-      <c r="D376" t="n">
+      <c r="H376" t="n">
+        <v>0</v>
+      </c>
+      <c r="I376" t="n">
         <v>2</v>
       </c>
-      <c r="E376" t="n">
-        <v>0</v>
-      </c>
-      <c r="F376" t="n">
-        <v>0</v>
-      </c>
-      <c r="G376" t="n">
-        <v>1</v>
-      </c>
-      <c r="H376" t="n">
-        <v>3</v>
-      </c>
-      <c r="I376" t="n">
-        <v>0</v>
-      </c>
       <c r="J376" t="n">
+        <v>0</v>
+      </c>
+      <c r="K376" t="n">
         <v>2</v>
-      </c>
-      <c r="K376" t="n">
-        <v>0</v>
       </c>
       <c r="L376" t="n">
         <v>2</v>
       </c>
       <c r="M376" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="377">
@@ -15902,7 +15906,9 @@
           <t>顯示卡</t>
         </is>
       </c>
-      <c r="B377" t="inlineStr"/>
+      <c r="B377" t="n">
+        <v>0</v>
+      </c>
       <c r="C377" t="n">
         <v>0</v>
       </c>
@@ -15963,16 +15969,16 @@
         <v>0</v>
       </c>
       <c r="I378" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J378" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K378" t="n">
         <v>0</v>
       </c>
       <c r="L378" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M378" t="n">
         <v>1</v>
@@ -16007,10 +16013,10 @@
         <v>0</v>
       </c>
       <c r="J379" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K379" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L379" t="n">
         <v>0</v>
@@ -16092,10 +16098,10 @@
         <v>0</v>
       </c>
       <c r="K381" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L381" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M381" t="n">
         <v>0</v>
@@ -16153,10 +16159,10 @@
         <v>0</v>
       </c>
       <c r="D383" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E383" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F383" t="n">
         <v>0</v>
@@ -16165,19 +16171,19 @@
         <v>0</v>
       </c>
       <c r="H383" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I383" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J383" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K383" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L383" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M383" t="n">
         <v>0</v>
@@ -16232,7 +16238,7 @@
       </c>
       <c r="B385" t="inlineStr"/>
       <c r="C385" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D385" t="n">
         <v>0</v>
@@ -16241,13 +16247,13 @@
         <v>0</v>
       </c>
       <c r="F385" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G385" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H385" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I385" t="n">
         <v>0</v>
@@ -16312,7 +16318,9 @@
           <t>高爾夫球具業</t>
         </is>
       </c>
-      <c r="B387" t="inlineStr"/>
+      <c r="B387" t="n">
+        <v>0</v>
+      </c>
       <c r="C387" t="n">
         <v>0</v>
       </c>

--- a/Result/analyze_3.xlsx
+++ b/Result/analyze_3.xlsx
@@ -441,57 +441,57 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
     </row>
@@ -665,24 +665,26 @@
           <t>IC/晶圓製造</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr"/>
+      <c r="B6" t="n">
+        <v>0</v>
+      </c>
       <c r="C6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I6" t="n">
         <v>2</v>
@@ -691,13 +693,13 @@
         <v>2</v>
       </c>
       <c r="K6" t="n">
+        <v>3</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1</v>
+      </c>
+      <c r="M6" t="n">
         <v>2</v>
-      </c>
-      <c r="L6" t="n">
-        <v>3</v>
-      </c>
-      <c r="M6" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -706,38 +708,36 @@
           <t>IC封裝測試</t>
         </is>
       </c>
-      <c r="B7" t="n">
-        <v>0</v>
-      </c>
+      <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
         <v>2</v>
       </c>
-      <c r="H7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0</v>
-      </c>
       <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
         <v>2</v>
       </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
       <c r="L7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M7" t="n">
         <v>1</v>
@@ -760,28 +760,28 @@
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="n">
         <v>2</v>
       </c>
-      <c r="H8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0</v>
-      </c>
       <c r="J8" t="n">
+        <v>1</v>
+      </c>
+      <c r="K8" t="n">
+        <v>1</v>
+      </c>
+      <c r="L8" t="n">
         <v>2</v>
       </c>
-      <c r="K8" t="n">
-        <v>1</v>
-      </c>
-      <c r="L8" t="n">
-        <v>1</v>
-      </c>
       <c r="M8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -792,37 +792,37 @@
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D9" t="n">
         <v>1</v>
       </c>
       <c r="E9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H9" t="n">
         <v>1</v>
       </c>
       <c r="I9" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J9" t="n">
         <v>4</v>
       </c>
       <c r="K9" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -831,11 +831,9 @@
           <t>IC通路</t>
         </is>
       </c>
-      <c r="B10" t="n">
-        <v>0</v>
-      </c>
+      <c r="B10" t="inlineStr"/>
       <c r="C10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
@@ -844,28 +842,28 @@
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G10" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L10" t="n">
         <v>2</v>
       </c>
       <c r="M10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -876,37 +874,37 @@
       </c>
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1</v>
+      </c>
+      <c r="I11" t="n">
         <v>2</v>
       </c>
-      <c r="E11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" t="n">
-        <v>1</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" t="n">
-        <v>1</v>
-      </c>
       <c r="J11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1137,10 +1135,10 @@
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1204,10 +1202,10 @@
       </c>
       <c r="B19" t="inlineStr"/>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -1284,38 +1282,36 @@
           <t>中、西藥製劑</t>
         </is>
       </c>
-      <c r="B21" t="n">
-        <v>0</v>
-      </c>
+      <c r="B21" t="inlineStr"/>
       <c r="C21" t="n">
+        <v>1</v>
+      </c>
+      <c r="D21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" t="n">
+        <v>1</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" t="n">
         <v>2</v>
       </c>
-      <c r="D21" t="n">
-        <v>1</v>
-      </c>
-      <c r="E21" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0</v>
-      </c>
-      <c r="G21" t="n">
-        <v>1</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0</v>
-      </c>
       <c r="I21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
         <v>2</v>
       </c>
-      <c r="J21" t="n">
-        <v>1</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
       <c r="L21" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
         <v>0</v>
@@ -1370,7 +1366,7 @@
       </c>
       <c r="B23" t="inlineStr"/>
       <c r="C23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D23" t="n">
         <v>0</v>
@@ -1379,19 +1375,19 @@
         <v>0</v>
       </c>
       <c r="F23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
@@ -1409,9 +1405,7 @@
           <t>主/被動元件</t>
         </is>
       </c>
-      <c r="B24" t="n">
-        <v>0</v>
-      </c>
+      <c r="B24" t="inlineStr"/>
       <c r="C24" t="n">
         <v>0</v>
       </c>
@@ -1422,28 +1416,28 @@
         <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" t="n">
+        <v>1</v>
+      </c>
+      <c r="I24" t="n">
+        <v>3</v>
+      </c>
+      <c r="J24" t="n">
         <v>2</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" t="n">
-        <v>1</v>
-      </c>
-      <c r="J24" t="n">
-        <v>3</v>
       </c>
       <c r="K24" t="n">
         <v>2</v>
       </c>
       <c r="L24" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -1472,13 +1466,13 @@
         <v>0</v>
       </c>
       <c r="I25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J25" t="n">
         <v>1</v>
       </c>
       <c r="K25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
@@ -1536,10 +1530,10 @@
       </c>
       <c r="B27" t="inlineStr"/>
       <c r="C27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E27" t="n">
         <v>0</v>
@@ -1557,16 +1551,16 @@
         <v>0</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -1683,10 +1677,10 @@
         <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
         <v>0</v>
@@ -1721,13 +1715,13 @@
         <v>0</v>
       </c>
       <c r="J31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K31" t="n">
         <v>1</v>
       </c>
       <c r="L31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
         <v>0</v>
@@ -1741,19 +1735,19 @@
       </c>
       <c r="B32" t="inlineStr"/>
       <c r="C32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E32" t="n">
         <v>0</v>
       </c>
       <c r="F32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H32" t="n">
         <v>0</v>
@@ -1762,10 +1756,10 @@
         <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K32" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
@@ -1803,10 +1797,10 @@
         <v>0</v>
       </c>
       <c r="J33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L33" t="n">
         <v>0</v>
@@ -1862,9 +1856,7 @@
           <t>保健食品代理銷售及通路</t>
         </is>
       </c>
-      <c r="B35" t="n">
-        <v>0</v>
-      </c>
+      <c r="B35" t="inlineStr"/>
       <c r="C35" t="n">
         <v>0</v>
       </c>
@@ -1881,7 +1873,7 @@
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I35" t="n">
         <v>1</v>
@@ -1893,7 +1885,7 @@
         <v>1</v>
       </c>
       <c r="L35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
         <v>0</v>
@@ -2045,10 +2037,10 @@
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -2110,7 +2102,9 @@
           <t>傳動元件</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr"/>
+      <c r="B41" t="n">
+        <v>0</v>
+      </c>
       <c r="C41" t="n">
         <v>0</v>
       </c>
@@ -2121,10 +2115,10 @@
         <v>0</v>
       </c>
       <c r="F41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H41" t="n">
         <v>0</v>
@@ -2162,25 +2156,25 @@
         <v>0</v>
       </c>
       <c r="F42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H42" t="n">
         <v>0</v>
       </c>
       <c r="I42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L42" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
         <v>0</v>
@@ -2212,10 +2206,10 @@
         <v>0</v>
       </c>
       <c r="I43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K43" t="n">
         <v>0</v>
@@ -2241,19 +2235,19 @@
         <v>0</v>
       </c>
       <c r="E44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I44" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -2265,7 +2259,7 @@
         <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="45">
@@ -2294,19 +2288,19 @@
         <v>0</v>
       </c>
       <c r="I45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J45" t="n">
         <v>1</v>
       </c>
       <c r="K45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L45" t="n">
         <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="46">
@@ -2376,10 +2370,10 @@
         <v>0</v>
       </c>
       <c r="I47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K47" t="n">
         <v>0</v>
@@ -2388,7 +2382,7 @@
         <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="48">
@@ -2440,25 +2434,25 @@
       </c>
       <c r="B49" t="inlineStr"/>
       <c r="C49" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D49" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F49" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G49" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H49" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I49" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J49" t="n">
         <v>3</v>
@@ -2470,7 +2464,7 @@
         <v>3</v>
       </c>
       <c r="M49" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="50">
@@ -2533,25 +2527,25 @@
         <v>1</v>
       </c>
       <c r="F51" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G51" t="n">
+        <v>1</v>
+      </c>
+      <c r="H51" t="n">
         <v>3</v>
       </c>
-      <c r="H51" t="n">
-        <v>1</v>
-      </c>
       <c r="I51" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J51" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K51" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="L51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M51" t="n">
         <v>0</v>
@@ -2609,34 +2603,34 @@
         <v>2</v>
       </c>
       <c r="D53" t="n">
+        <v>0</v>
+      </c>
+      <c r="E53" t="n">
+        <v>0</v>
+      </c>
+      <c r="F53" t="n">
         <v>2</v>
       </c>
-      <c r="E53" t="n">
-        <v>0</v>
-      </c>
-      <c r="F53" t="n">
-        <v>0</v>
-      </c>
       <c r="G53" t="n">
+        <v>0</v>
+      </c>
+      <c r="H53" t="n">
+        <v>0</v>
+      </c>
+      <c r="I53" t="n">
+        <v>0</v>
+      </c>
+      <c r="J53" t="n">
+        <v>1</v>
+      </c>
+      <c r="K53" t="n">
+        <v>0</v>
+      </c>
+      <c r="L53" t="n">
         <v>2</v>
       </c>
-      <c r="H53" t="n">
-        <v>0</v>
-      </c>
-      <c r="I53" t="n">
-        <v>0</v>
-      </c>
-      <c r="J53" t="n">
-        <v>0</v>
-      </c>
-      <c r="K53" t="n">
-        <v>1</v>
-      </c>
-      <c r="L53" t="n">
-        <v>0</v>
-      </c>
       <c r="M53" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="54">
@@ -2647,7 +2641,7 @@
       </c>
       <c r="B54" t="inlineStr"/>
       <c r="C54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D54" t="n">
         <v>1</v>
@@ -2656,28 +2650,28 @@
         <v>1</v>
       </c>
       <c r="F54" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G54" t="n">
+        <v>0</v>
+      </c>
+      <c r="H54" t="n">
         <v>4</v>
       </c>
-      <c r="H54" t="n">
-        <v>0</v>
-      </c>
       <c r="I54" t="n">
+        <v>5</v>
+      </c>
+      <c r="J54" t="n">
         <v>4</v>
       </c>
-      <c r="J54" t="n">
-        <v>5</v>
-      </c>
       <c r="K54" t="n">
+        <v>1</v>
+      </c>
+      <c r="L54" t="n">
+        <v>7</v>
+      </c>
+      <c r="M54" t="n">
         <v>4</v>
-      </c>
-      <c r="L54" t="n">
-        <v>1</v>
-      </c>
-      <c r="M54" t="n">
-        <v>7</v>
       </c>
     </row>
     <row r="55">
@@ -2688,13 +2682,13 @@
       </c>
       <c r="B55" t="inlineStr"/>
       <c r="C55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D55" t="n">
         <v>0</v>
       </c>
       <c r="E55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F55" t="n">
         <v>1</v>
@@ -2703,22 +2697,22 @@
         <v>1</v>
       </c>
       <c r="H55" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I55" t="n">
+        <v>1</v>
+      </c>
+      <c r="J55" t="n">
         <v>3</v>
       </c>
-      <c r="J55" t="n">
-        <v>1</v>
-      </c>
       <c r="K55" t="n">
+        <v>2</v>
+      </c>
+      <c r="L55" t="n">
         <v>3</v>
       </c>
-      <c r="L55" t="n">
+      <c r="M55" t="n">
         <v>2</v>
-      </c>
-      <c r="M55" t="n">
-        <v>3</v>
       </c>
     </row>
     <row r="56">
@@ -2729,22 +2723,22 @@
       </c>
       <c r="B56" t="inlineStr"/>
       <c r="C56" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D56" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E56" t="n">
         <v>0</v>
       </c>
       <c r="F56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I56" t="n">
         <v>1</v>
@@ -2759,7 +2753,7 @@
         <v>1</v>
       </c>
       <c r="M56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -2809,7 +2803,9 @@
           <t>冷凍空調設備及零件</t>
         </is>
       </c>
-      <c r="B58" t="inlineStr"/>
+      <c r="B58" t="n">
+        <v>0</v>
+      </c>
       <c r="C58" t="n">
         <v>0</v>
       </c>
@@ -2817,10 +2813,10 @@
         <v>0</v>
       </c>
       <c r="E58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
@@ -2832,16 +2828,16 @@
         <v>0</v>
       </c>
       <c r="J58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L58" t="n">
         <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="59">
@@ -2858,13 +2854,13 @@
         <v>0</v>
       </c>
       <c r="E59" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F59" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G59" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H59" t="n">
         <v>0</v>
@@ -2923,7 +2919,7 @@
         <v>0</v>
       </c>
       <c r="M60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="61">
@@ -2932,7 +2928,9 @@
           <t>冷熱軋鋼板捲</t>
         </is>
       </c>
-      <c r="B61" t="inlineStr"/>
+      <c r="B61" t="n">
+        <v>0</v>
+      </c>
       <c r="C61" t="n">
         <v>0</v>
       </c>
@@ -2964,7 +2962,7 @@
         <v>0</v>
       </c>
       <c r="M61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="62">
@@ -3040,10 +3038,10 @@
         <v>0</v>
       </c>
       <c r="K63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M63" t="n">
         <v>0</v>
@@ -3055,7 +3053,9 @@
           <t>創意生活產業</t>
         </is>
       </c>
-      <c r="B64" t="inlineStr"/>
+      <c r="B64" t="n">
+        <v>0</v>
+      </c>
       <c r="C64" t="n">
         <v>0</v>
       </c>
@@ -3178,9 +3178,7 @@
           <t>加工製成品</t>
         </is>
       </c>
-      <c r="B67" t="n">
-        <v>0</v>
-      </c>
+      <c r="B67" t="inlineStr"/>
       <c r="C67" t="n">
         <v>0</v>
       </c>
@@ -3200,10 +3198,10 @@
         <v>0</v>
       </c>
       <c r="I67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K67" t="n">
         <v>0</v>
@@ -3291,10 +3289,10 @@
         <v>0</v>
       </c>
       <c r="L69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="70">
@@ -3346,10 +3344,10 @@
       </c>
       <c r="B71" t="inlineStr"/>
       <c r="C71" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E71" t="n">
         <v>0</v>
@@ -3361,22 +3359,22 @@
         <v>0</v>
       </c>
       <c r="H71" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I71" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J71" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L71" t="n">
         <v>0</v>
       </c>
       <c r="M71" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="72">
@@ -3387,28 +3385,28 @@
       </c>
       <c r="B72" t="inlineStr"/>
       <c r="C72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E72" t="n">
         <v>0</v>
       </c>
       <c r="F72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I72" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J72" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K72" t="n">
         <v>1</v>
@@ -3437,10 +3435,10 @@
         <v>0</v>
       </c>
       <c r="F73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G73" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H73" t="n">
         <v>0</v>
@@ -3452,13 +3450,13 @@
         <v>0</v>
       </c>
       <c r="K73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L73" t="n">
         <v>1</v>
       </c>
       <c r="M73" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74">
@@ -3569,13 +3567,13 @@
         <v>0</v>
       </c>
       <c r="I76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J76" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K76" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L76" t="n">
         <v>0</v>
@@ -3610,10 +3608,10 @@
         <v>0</v>
       </c>
       <c r="I77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J77" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K77" t="n">
         <v>0</v>
@@ -3631,38 +3629,36 @@
           <t>原材料</t>
         </is>
       </c>
-      <c r="B78" t="n">
-        <v>0</v>
-      </c>
+      <c r="B78" t="inlineStr"/>
       <c r="C78" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D78" t="n">
         <v>2</v>
       </c>
       <c r="E78" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F78" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G78" t="n">
         <v>0</v>
       </c>
       <c r="H78" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I78" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J78" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K78" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L78" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M78" t="n">
         <v>1</v>
@@ -3776,13 +3772,13 @@
         <v>0</v>
       </c>
       <c r="I81" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J81" t="n">
         <v>1</v>
       </c>
       <c r="K81" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L81" t="n">
         <v>0</v>
@@ -3840,34 +3836,34 @@
       </c>
       <c r="B83" t="inlineStr"/>
       <c r="C83" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D83" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E83" t="n">
         <v>0</v>
       </c>
       <c r="F83" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G83" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H83" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I83" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J83" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K83" t="n">
         <v>1</v>
       </c>
       <c r="L83" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M83" t="n">
         <v>0</v>
@@ -3963,7 +3959,7 @@
       </c>
       <c r="B86" t="inlineStr"/>
       <c r="C86" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D86" t="n">
         <v>0</v>
@@ -4004,10 +4000,10 @@
       </c>
       <c r="B87" t="inlineStr"/>
       <c r="C87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E87" t="n">
         <v>0</v>
@@ -4054,10 +4050,10 @@
         <v>0</v>
       </c>
       <c r="F88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H88" t="n">
         <v>0</v>
@@ -4086,19 +4082,19 @@
       </c>
       <c r="B89" t="inlineStr"/>
       <c r="C89" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E89" t="n">
         <v>0</v>
       </c>
       <c r="F89" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H89" t="n">
         <v>0</v>
@@ -4107,10 +4103,10 @@
         <v>0</v>
       </c>
       <c r="J89" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L89" t="n">
         <v>0</v>
@@ -4207,9 +4203,11 @@
           <t>大功率鋰電池芯/模組、電池管理系統、動力馬達等零組件</t>
         </is>
       </c>
-      <c r="B92" t="inlineStr"/>
+      <c r="B92" t="n">
+        <v>0</v>
+      </c>
       <c r="C92" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D92" t="n">
         <v>1</v>
@@ -4218,28 +4216,28 @@
         <v>1</v>
       </c>
       <c r="F92" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G92" t="n">
+        <v>0</v>
+      </c>
+      <c r="H92" t="n">
+        <v>0</v>
+      </c>
+      <c r="I92" t="n">
+        <v>0</v>
+      </c>
+      <c r="J92" t="n">
+        <v>1</v>
+      </c>
+      <c r="K92" t="n">
+        <v>1</v>
+      </c>
+      <c r="L92" t="n">
         <v>2</v>
       </c>
-      <c r="H92" t="n">
-        <v>0</v>
-      </c>
-      <c r="I92" t="n">
-        <v>0</v>
-      </c>
-      <c r="J92" t="n">
-        <v>0</v>
-      </c>
-      <c r="K92" t="n">
-        <v>1</v>
-      </c>
-      <c r="L92" t="n">
-        <v>1</v>
-      </c>
       <c r="M92" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="93">
@@ -4312,10 +4310,10 @@
         <v>0</v>
       </c>
       <c r="J94" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K94" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L94" t="n">
         <v>0</v>
@@ -4338,31 +4336,31 @@
         <v>0</v>
       </c>
       <c r="E95" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F95" t="n">
         <v>1</v>
       </c>
       <c r="G95" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H95" t="n">
         <v>0</v>
       </c>
       <c r="I95" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J95" t="n">
         <v>2</v>
       </c>
       <c r="K95" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L95" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M95" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="96">
@@ -4382,22 +4380,22 @@
         <v>0</v>
       </c>
       <c r="F96" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G96" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H96" t="n">
         <v>0</v>
       </c>
       <c r="I96" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J96" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K96" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L96" t="n">
         <v>0</v>
@@ -4476,16 +4474,16 @@
         <v>0</v>
       </c>
       <c r="J98" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K98" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L98" t="n">
         <v>0</v>
       </c>
       <c r="M98" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="99">
@@ -4494,7 +4492,9 @@
           <t>娛樂服務業</t>
         </is>
       </c>
-      <c r="B99" t="inlineStr"/>
+      <c r="B99" t="n">
+        <v>0</v>
+      </c>
       <c r="C99" t="n">
         <v>0</v>
       </c>
@@ -4511,16 +4511,16 @@
         <v>0</v>
       </c>
       <c r="H99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I99" t="n">
         <v>0</v>
       </c>
       <c r="J99" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L99" t="n">
         <v>0</v>
@@ -4578,7 +4578,7 @@
       </c>
       <c r="B101" t="inlineStr"/>
       <c r="C101" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D101" t="n">
         <v>0</v>
@@ -4593,16 +4593,16 @@
         <v>0</v>
       </c>
       <c r="H101" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I101" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J101" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K101" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L101" t="n">
         <v>0</v>
@@ -4619,7 +4619,7 @@
       </c>
       <c r="B102" t="inlineStr"/>
       <c r="C102" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D102" t="n">
         <v>0</v>
@@ -4628,28 +4628,28 @@
         <v>0</v>
       </c>
       <c r="F102" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G102" t="n">
+        <v>1</v>
+      </c>
+      <c r="H102" t="n">
+        <v>0</v>
+      </c>
+      <c r="I102" t="n">
+        <v>0</v>
+      </c>
+      <c r="J102" t="n">
+        <v>1</v>
+      </c>
+      <c r="K102" t="n">
+        <v>3</v>
+      </c>
+      <c r="L102" t="n">
         <v>2</v>
       </c>
-      <c r="H102" t="n">
-        <v>1</v>
-      </c>
-      <c r="I102" t="n">
-        <v>0</v>
-      </c>
-      <c r="J102" t="n">
-        <v>0</v>
-      </c>
-      <c r="K102" t="n">
-        <v>1</v>
-      </c>
-      <c r="L102" t="n">
-        <v>3</v>
-      </c>
       <c r="M102" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="103">
@@ -4699,11 +4699,9 @@
           <t>封裝/模組</t>
         </is>
       </c>
-      <c r="B104" t="n">
-        <v>0</v>
-      </c>
+      <c r="B104" t="inlineStr"/>
       <c r="C104" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D104" t="n">
         <v>0</v>
@@ -4712,28 +4710,28 @@
         <v>0</v>
       </c>
       <c r="F104" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G104" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H104" t="n">
         <v>0</v>
       </c>
       <c r="I104" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J104" t="n">
         <v>1</v>
       </c>
       <c r="K104" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L104" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M104" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="105">
@@ -4742,32 +4740,30 @@
           <t>專用機械(如紡織成衣生產用機械、食品飲料生產用機械、農林用機械等)</t>
         </is>
       </c>
-      <c r="B105" t="n">
-        <v>0</v>
-      </c>
+      <c r="B105" t="inlineStr"/>
       <c r="C105" t="n">
         <v>1</v>
       </c>
       <c r="D105" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E105" t="n">
         <v>0</v>
       </c>
       <c r="F105" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G105" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H105" t="n">
         <v>0</v>
       </c>
       <c r="I105" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J105" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K105" t="n">
         <v>0</v>
@@ -4776,7 +4772,7 @@
         <v>0</v>
       </c>
       <c r="M105" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="106">
@@ -4787,19 +4783,19 @@
       </c>
       <c r="B106" t="inlineStr"/>
       <c r="C106" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D106" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E106" t="n">
         <v>0</v>
       </c>
       <c r="F106" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G106" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H106" t="n">
         <v>0</v>
@@ -4814,10 +4810,10 @@
         <v>0</v>
       </c>
       <c r="L106" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M106" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="107">
@@ -4960,10 +4956,10 @@
         <v>0</v>
       </c>
       <c r="F110" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G110" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H110" t="n">
         <v>0</v>
@@ -4990,11 +4986,9 @@
           <t>工業電腦</t>
         </is>
       </c>
-      <c r="B111" t="n">
-        <v>0</v>
-      </c>
+      <c r="B111" t="inlineStr"/>
       <c r="C111" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D111" t="n">
         <v>0</v>
@@ -5009,19 +5003,19 @@
         <v>0</v>
       </c>
       <c r="H111" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I111" t="n">
         <v>1</v>
       </c>
       <c r="J111" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K111" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L111" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M111" t="n">
         <v>1</v>
@@ -5041,10 +5035,10 @@
         <v>0</v>
       </c>
       <c r="E112" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F112" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G112" t="n">
         <v>0</v>
@@ -5053,19 +5047,19 @@
         <v>0</v>
       </c>
       <c r="I112" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J112" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K112" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L112" t="n">
         <v>1</v>
       </c>
       <c r="M112" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="113">
@@ -5082,10 +5076,10 @@
         <v>0</v>
       </c>
       <c r="E113" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F113" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G113" t="n">
         <v>0</v>
@@ -5132,10 +5126,10 @@
         <v>0</v>
       </c>
       <c r="H114" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I114" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -5176,10 +5170,10 @@
         <v>0</v>
       </c>
       <c r="I115" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J115" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K115" t="n">
         <v>0</v>
@@ -5217,10 +5211,10 @@
         <v>0</v>
       </c>
       <c r="I116" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J116" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K116" t="n">
         <v>0</v>
@@ -5366,16 +5360,16 @@
         <v>1</v>
       </c>
       <c r="D120" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E120" t="n">
         <v>0</v>
       </c>
       <c r="F120" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G120" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H120" t="n">
         <v>0</v>
@@ -5384,16 +5378,16 @@
         <v>0</v>
       </c>
       <c r="J120" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K120" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L120" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M120" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="121">
@@ -5413,25 +5407,25 @@
         <v>0</v>
       </c>
       <c r="F121" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G121" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H121" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I121" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J121" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K121" t="n">
         <v>1</v>
       </c>
       <c r="L121" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M121" t="n">
         <v>0</v>
@@ -5691,19 +5685,19 @@
       </c>
       <c r="B128" t="inlineStr"/>
       <c r="C128" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D128" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E128" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F128" t="n">
         <v>1</v>
       </c>
       <c r="G128" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H128" t="n">
         <v>0</v>
@@ -5712,10 +5706,10 @@
         <v>0</v>
       </c>
       <c r="J128" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K128" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L128" t="n">
         <v>1</v>
@@ -5756,10 +5750,10 @@
         <v>0</v>
       </c>
       <c r="K129" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L129" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M129" t="n">
         <v>0</v>
@@ -5817,13 +5811,13 @@
         <v>1</v>
       </c>
       <c r="D131" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E131" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F131" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G131" t="n">
         <v>0</v>
@@ -5855,7 +5849,7 @@
       </c>
       <c r="B132" t="inlineStr"/>
       <c r="C132" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D132" t="n">
         <v>0</v>
@@ -6087,10 +6081,10 @@
         <v>0</v>
       </c>
       <c r="L137" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M137" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="138">
@@ -6151,28 +6145,28 @@
         <v>0</v>
       </c>
       <c r="F139" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G139" t="n">
+        <v>0</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0</v>
+      </c>
+      <c r="J139" t="n">
+        <v>1</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0</v>
+      </c>
+      <c r="L139" t="n">
         <v>2</v>
       </c>
-      <c r="H139" t="n">
-        <v>0</v>
-      </c>
-      <c r="I139" t="n">
-        <v>0</v>
-      </c>
-      <c r="J139" t="n">
-        <v>0</v>
-      </c>
-      <c r="K139" t="n">
-        <v>1</v>
-      </c>
-      <c r="L139" t="n">
-        <v>0</v>
-      </c>
       <c r="M139" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="140">
@@ -6201,13 +6195,13 @@
         <v>0</v>
       </c>
       <c r="I140" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J140" t="n">
         <v>1</v>
       </c>
       <c r="K140" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L140" t="n">
         <v>0</v>
@@ -6224,7 +6218,7 @@
       </c>
       <c r="B141" t="inlineStr"/>
       <c r="C141" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D141" t="n">
         <v>0</v>
@@ -6242,13 +6236,13 @@
         <v>0</v>
       </c>
       <c r="I141" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J141" t="n">
         <v>1</v>
       </c>
       <c r="K141" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L141" t="n">
         <v>0</v>
@@ -6283,13 +6277,13 @@
         <v>0</v>
       </c>
       <c r="I142" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J142" t="n">
         <v>1</v>
       </c>
       <c r="K142" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L142" t="n">
         <v>0</v>
@@ -6345,12 +6339,14 @@
           <t>數位內容產業</t>
         </is>
       </c>
-      <c r="B144" t="inlineStr"/>
+      <c r="B144" t="n">
+        <v>0</v>
+      </c>
       <c r="C144" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D144" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E144" t="n">
         <v>0</v>
@@ -6362,10 +6358,10 @@
         <v>0</v>
       </c>
       <c r="H144" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I144" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -6388,7 +6384,7 @@
       </c>
       <c r="B145" t="inlineStr"/>
       <c r="C145" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D145" t="n">
         <v>0</v>
@@ -6403,16 +6399,16 @@
         <v>0</v>
       </c>
       <c r="H145" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I145" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J145" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K145" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L145" t="n">
         <v>0</v>
@@ -6470,7 +6466,7 @@
       </c>
       <c r="B147" t="inlineStr"/>
       <c r="C147" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D147" t="n">
         <v>0</v>
@@ -6485,16 +6481,16 @@
         <v>0</v>
       </c>
       <c r="H147" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I147" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J147" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K147" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L147" t="n">
         <v>0</v>
@@ -6509,9 +6505,7 @@
           <t>文化印刷業</t>
         </is>
       </c>
-      <c r="B148" t="n">
-        <v>0</v>
-      </c>
+      <c r="B148" t="inlineStr"/>
       <c r="C148" t="n">
         <v>0</v>
       </c>
@@ -6528,16 +6522,16 @@
         <v>0</v>
       </c>
       <c r="H148" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I148" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
       </c>
       <c r="K148" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L148" t="n">
         <v>0</v>
@@ -6554,7 +6548,7 @@
       </c>
       <c r="B149" t="inlineStr"/>
       <c r="C149" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D149" t="n">
         <v>0</v>
@@ -6604,10 +6598,10 @@
         <v>0</v>
       </c>
       <c r="F150" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G150" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H150" t="n">
         <v>0</v>
@@ -6636,16 +6630,16 @@
       </c>
       <c r="B151" t="inlineStr"/>
       <c r="C151" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D151" t="n">
         <v>0</v>
       </c>
       <c r="E151" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F151" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G151" t="n">
         <v>0</v>
@@ -6657,10 +6651,10 @@
         <v>0</v>
       </c>
       <c r="J151" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K151" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L151" t="n">
         <v>0</v>
@@ -6718,37 +6712,37 @@
       </c>
       <c r="B153" t="inlineStr"/>
       <c r="C153" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D153" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E153" t="n">
         <v>0</v>
       </c>
       <c r="F153" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G153" t="n">
+        <v>1</v>
+      </c>
+      <c r="H153" t="n">
+        <v>0</v>
+      </c>
+      <c r="I153" t="n">
+        <v>0</v>
+      </c>
+      <c r="J153" t="n">
+        <v>0</v>
+      </c>
+      <c r="K153" t="n">
+        <v>0</v>
+      </c>
+      <c r="L153" t="n">
         <v>2</v>
       </c>
-      <c r="H153" t="n">
-        <v>1</v>
-      </c>
-      <c r="I153" t="n">
-        <v>0</v>
-      </c>
-      <c r="J153" t="n">
-        <v>0</v>
-      </c>
-      <c r="K153" t="n">
-        <v>0</v>
-      </c>
-      <c r="L153" t="n">
-        <v>0</v>
-      </c>
       <c r="M153" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="154">
@@ -6768,10 +6762,10 @@
         <v>0</v>
       </c>
       <c r="F154" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G154" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H154" t="n">
         <v>0</v>
@@ -6839,14 +6833,12 @@
           <t>材料</t>
         </is>
       </c>
-      <c r="B156" t="n">
-        <v>0</v>
-      </c>
+      <c r="B156" t="inlineStr"/>
       <c r="C156" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D156" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E156" t="n">
         <v>0</v>
@@ -6882,7 +6874,9 @@
           <t>染整</t>
         </is>
       </c>
-      <c r="B157" t="inlineStr"/>
+      <c r="B157" t="n">
+        <v>0</v>
+      </c>
       <c r="C157" t="n">
         <v>0</v>
       </c>
@@ -6902,16 +6896,16 @@
         <v>1</v>
       </c>
       <c r="I157" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
       </c>
       <c r="K157" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L157" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M157" t="n">
         <v>0</v>
@@ -6923,9 +6917,7 @@
           <t>桌上型電腦</t>
         </is>
       </c>
-      <c r="B158" t="n">
-        <v>0</v>
-      </c>
+      <c r="B158" t="inlineStr"/>
       <c r="C158" t="n">
         <v>0</v>
       </c>
@@ -6936,10 +6928,10 @@
         <v>0</v>
       </c>
       <c r="F158" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G158" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H158" t="n">
         <v>0</v>
@@ -7018,10 +7010,10 @@
         <v>0</v>
       </c>
       <c r="F160" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G160" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H160" t="n">
         <v>0</v>
@@ -7094,31 +7086,31 @@
         <v>1</v>
       </c>
       <c r="D162" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E162" t="n">
         <v>0</v>
       </c>
       <c r="F162" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G162" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H162" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I162" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J162" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K162" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L162" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M162" t="n">
         <v>1</v>
@@ -7156,10 +7148,10 @@
         <v>0</v>
       </c>
       <c r="K163" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L163" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M163" t="n">
         <v>0</v>
@@ -7194,13 +7186,13 @@
         <v>0</v>
       </c>
       <c r="J164" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K164" t="n">
         <v>1</v>
       </c>
       <c r="L164" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M164" t="n">
         <v>0</v>
@@ -7214,7 +7206,7 @@
       </c>
       <c r="B165" t="inlineStr"/>
       <c r="C165" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D165" t="n">
         <v>0</v>
@@ -7229,22 +7221,22 @@
         <v>0</v>
       </c>
       <c r="H165" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I165" t="n">
         <v>1</v>
       </c>
       <c r="J165" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K165" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L165" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M165" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="166">
@@ -7253,7 +7245,9 @@
           <t>機電工程</t>
         </is>
       </c>
-      <c r="B166" t="inlineStr"/>
+      <c r="B166" t="n">
+        <v>0</v>
+      </c>
       <c r="C166" t="n">
         <v>0</v>
       </c>
@@ -7261,13 +7255,13 @@
         <v>0</v>
       </c>
       <c r="E166" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F166" t="n">
         <v>1</v>
       </c>
       <c r="G166" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H166" t="n">
         <v>0</v>
@@ -7294,7 +7288,9 @@
           <t>機電系統工程</t>
         </is>
       </c>
-      <c r="B167" t="inlineStr"/>
+      <c r="B167" t="n">
+        <v>0</v>
+      </c>
       <c r="C167" t="n">
         <v>0</v>
       </c>
@@ -7302,10 +7298,10 @@
         <v>0</v>
       </c>
       <c r="E167" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F167" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G167" t="n">
         <v>0</v>
@@ -7355,10 +7351,10 @@
         <v>0</v>
       </c>
       <c r="I168" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J168" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K168" t="n">
         <v>0</v>
@@ -7519,10 +7515,10 @@
         <v>0</v>
       </c>
       <c r="I172" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J172" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K172" t="n">
         <v>0</v>
@@ -7601,10 +7597,10 @@
         <v>0</v>
       </c>
       <c r="I174" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J174" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K174" t="n">
         <v>0</v>
@@ -7642,10 +7638,10 @@
         <v>0</v>
       </c>
       <c r="I175" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J175" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K175" t="n">
         <v>0</v>
@@ -7706,7 +7702,7 @@
       </c>
       <c r="B177" t="inlineStr"/>
       <c r="C177" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D177" t="n">
         <v>0</v>
@@ -7715,10 +7711,10 @@
         <v>0</v>
       </c>
       <c r="F177" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G177" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H177" t="n">
         <v>0</v>
@@ -7730,10 +7726,10 @@
         <v>0</v>
       </c>
       <c r="K177" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L177" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M177" t="n">
         <v>0</v>
@@ -7788,25 +7784,25 @@
       </c>
       <c r="B179" t="inlineStr"/>
       <c r="C179" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D179" t="n">
+        <v>0</v>
+      </c>
+      <c r="E179" t="n">
+        <v>0</v>
+      </c>
+      <c r="F179" t="n">
         <v>2</v>
       </c>
-      <c r="E179" t="n">
-        <v>0</v>
-      </c>
-      <c r="F179" t="n">
-        <v>0</v>
-      </c>
       <c r="G179" t="n">
+        <v>1</v>
+      </c>
+      <c r="H179" t="n">
+        <v>4</v>
+      </c>
+      <c r="I179" t="n">
         <v>2</v>
-      </c>
-      <c r="H179" t="n">
-        <v>1</v>
-      </c>
-      <c r="I179" t="n">
-        <v>4</v>
       </c>
       <c r="J179" t="n">
         <v>2</v>
@@ -7815,10 +7811,10 @@
         <v>2</v>
       </c>
       <c r="L179" t="n">
+        <v>3</v>
+      </c>
+      <c r="M179" t="n">
         <v>2</v>
-      </c>
-      <c r="M179" t="n">
-        <v>3</v>
       </c>
     </row>
     <row r="180">
@@ -7870,34 +7866,34 @@
       </c>
       <c r="B181" t="inlineStr"/>
       <c r="C181" t="n">
+        <v>0</v>
+      </c>
+      <c r="D181" t="n">
+        <v>0</v>
+      </c>
+      <c r="E181" t="n">
+        <v>0</v>
+      </c>
+      <c r="F181" t="n">
+        <v>3</v>
+      </c>
+      <c r="G181" t="n">
+        <v>0</v>
+      </c>
+      <c r="H181" t="n">
+        <v>1</v>
+      </c>
+      <c r="I181" t="n">
+        <v>1</v>
+      </c>
+      <c r="J181" t="n">
+        <v>1</v>
+      </c>
+      <c r="K181" t="n">
+        <v>0</v>
+      </c>
+      <c r="L181" t="n">
         <v>2</v>
-      </c>
-      <c r="D181" t="n">
-        <v>0</v>
-      </c>
-      <c r="E181" t="n">
-        <v>0</v>
-      </c>
-      <c r="F181" t="n">
-        <v>0</v>
-      </c>
-      <c r="G181" t="n">
-        <v>3</v>
-      </c>
-      <c r="H181" t="n">
-        <v>0</v>
-      </c>
-      <c r="I181" t="n">
-        <v>1</v>
-      </c>
-      <c r="J181" t="n">
-        <v>1</v>
-      </c>
-      <c r="K181" t="n">
-        <v>1</v>
-      </c>
-      <c r="L181" t="n">
-        <v>0</v>
       </c>
       <c r="M181" t="n">
         <v>2</v>
@@ -7914,7 +7910,7 @@
         <v>1</v>
       </c>
       <c r="D182" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E182" t="n">
         <v>0</v>
@@ -7941,7 +7937,7 @@
         <v>0</v>
       </c>
       <c r="M182" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="183">
@@ -7993,7 +7989,7 @@
       </c>
       <c r="B184" t="inlineStr"/>
       <c r="C184" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D184" t="n">
         <v>0</v>
@@ -8008,19 +8004,19 @@
         <v>0</v>
       </c>
       <c r="H184" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I184" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J184" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K184" t="n">
         <v>1</v>
       </c>
       <c r="L184" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M184" t="n">
         <v>0</v>
@@ -8160,7 +8156,7 @@
         <v>1</v>
       </c>
       <c r="D188" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E188" t="n">
         <v>0</v>
@@ -8172,19 +8168,19 @@
         <v>0</v>
       </c>
       <c r="H188" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I188" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J188" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K188" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L188" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M188" t="n">
         <v>1</v>
@@ -8207,10 +8203,10 @@
         <v>0</v>
       </c>
       <c r="F189" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G189" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H189" t="n">
         <v>0</v>
@@ -8321,7 +8317,7 @@
       </c>
       <c r="B192" t="inlineStr"/>
       <c r="C192" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D192" t="n">
         <v>0</v>
@@ -8330,10 +8326,10 @@
         <v>0</v>
       </c>
       <c r="F192" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G192" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H192" t="n">
         <v>0</v>
@@ -8345,13 +8341,13 @@
         <v>0</v>
       </c>
       <c r="K192" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L192" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M192" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="193">
@@ -8401,9 +8397,7 @@
           <t>環保潔能服務產業</t>
         </is>
       </c>
-      <c r="B194" t="n">
-        <v>0</v>
-      </c>
+      <c r="B194" t="inlineStr"/>
       <c r="C194" t="n">
         <v>0</v>
       </c>
@@ -8414,13 +8408,13 @@
         <v>0</v>
       </c>
       <c r="F194" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G194" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H194" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I194" t="n">
         <v>1</v>
@@ -8464,7 +8458,7 @@
         <v>0</v>
       </c>
       <c r="I195" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J195" t="n">
         <v>1</v>
@@ -8473,10 +8467,10 @@
         <v>1</v>
       </c>
       <c r="L195" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M195" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="196">
@@ -8487,34 +8481,34 @@
       </c>
       <c r="B196" t="inlineStr"/>
       <c r="C196" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D196" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E196" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F196" t="n">
         <v>1</v>
       </c>
       <c r="G196" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H196" t="n">
         <v>0</v>
       </c>
       <c r="I196" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J196" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K196" t="n">
         <v>0</v>
       </c>
       <c r="L196" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M196" t="n">
         <v>1</v>
@@ -8528,37 +8522,37 @@
       </c>
       <c r="B197" t="inlineStr"/>
       <c r="C197" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D197" t="n">
         <v>1</v>
       </c>
       <c r="E197" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F197" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="G197" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="H197" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I197" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J197" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="K197" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L197" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="M197" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
     </row>
     <row r="198">
@@ -8590,10 +8584,10 @@
         <v>0</v>
       </c>
       <c r="J198" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K198" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L198" t="n">
         <v>0</v>
@@ -8649,7 +8643,9 @@
           <t>監控系統</t>
         </is>
       </c>
-      <c r="B200" t="inlineStr"/>
+      <c r="B200" t="n">
+        <v>0</v>
+      </c>
       <c r="C200" t="n">
         <v>0</v>
       </c>
@@ -8660,10 +8656,10 @@
         <v>0</v>
       </c>
       <c r="F200" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G200" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H200" t="n">
         <v>0</v>
@@ -8798,10 +8794,10 @@
         <v>0</v>
       </c>
       <c r="K203" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L203" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M203" t="n">
         <v>0</v>
@@ -8813,39 +8809,41 @@
           <t>石化中間原料(例如乙烯、丙烯、丁二烯、苯、酚等)</t>
         </is>
       </c>
-      <c r="B204" t="inlineStr"/>
+      <c r="B204" t="n">
+        <v>0</v>
+      </c>
       <c r="C204" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D204" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E204" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F204" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G204" t="n">
         <v>0</v>
       </c>
       <c r="H204" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I204" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J204" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K204" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L204" t="n">
         <v>0</v>
       </c>
       <c r="M204" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="205">
@@ -8880,10 +8878,10 @@
         <v>0</v>
       </c>
       <c r="K205" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L205" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M205" t="n">
         <v>0</v>
@@ -8941,7 +8939,7 @@
         <v>1</v>
       </c>
       <c r="D207" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E207" t="n">
         <v>0</v>
@@ -8977,41 +8975,39 @@
           <t>硬板、軟板、IC載板製造</t>
         </is>
       </c>
-      <c r="B208" t="n">
-        <v>0</v>
-      </c>
+      <c r="B208" t="inlineStr"/>
       <c r="C208" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D208" t="n">
+        <v>1</v>
+      </c>
+      <c r="E208" t="n">
+        <v>0</v>
+      </c>
+      <c r="F208" t="n">
+        <v>9</v>
+      </c>
+      <c r="G208" t="n">
+        <v>0</v>
+      </c>
+      <c r="H208" t="n">
+        <v>0</v>
+      </c>
+      <c r="I208" t="n">
+        <v>8</v>
+      </c>
+      <c r="J208" t="n">
+        <v>1</v>
+      </c>
+      <c r="K208" t="n">
         <v>2</v>
       </c>
-      <c r="E208" t="n">
-        <v>1</v>
-      </c>
-      <c r="F208" t="n">
-        <v>0</v>
-      </c>
-      <c r="G208" t="n">
-        <v>9</v>
-      </c>
-      <c r="H208" t="n">
-        <v>0</v>
-      </c>
-      <c r="I208" t="n">
-        <v>0</v>
-      </c>
-      <c r="J208" t="n">
-        <v>8</v>
-      </c>
-      <c r="K208" t="n">
-        <v>1</v>
-      </c>
       <c r="L208" t="n">
+        <v>1</v>
+      </c>
+      <c r="M208" t="n">
         <v>2</v>
-      </c>
-      <c r="M208" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="209">
@@ -9128,10 +9124,10 @@
         <v>0</v>
       </c>
       <c r="K211" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L211" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M211" t="n">
         <v>0</v>
@@ -9225,7 +9221,9 @@
           <t>移動控制</t>
         </is>
       </c>
-      <c r="B214" t="inlineStr"/>
+      <c r="B214" t="n">
+        <v>0</v>
+      </c>
       <c r="C214" t="n">
         <v>0</v>
       </c>
@@ -9353,7 +9351,7 @@
         <v>1</v>
       </c>
       <c r="D217" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E217" t="n">
         <v>0</v>
@@ -9365,19 +9363,19 @@
         <v>0</v>
       </c>
       <c r="H217" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I217" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J217" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K217" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L217" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M217" t="n">
         <v>1</v>
@@ -9389,11 +9387,9 @@
           <t>筆記型電腦</t>
         </is>
       </c>
-      <c r="B218" t="n">
-        <v>0</v>
-      </c>
+      <c r="B218" t="inlineStr"/>
       <c r="C218" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D218" t="n">
         <v>0</v>
@@ -9402,10 +9398,10 @@
         <v>0</v>
       </c>
       <c r="F218" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G218" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H218" t="n">
         <v>0</v>
@@ -9432,11 +9428,9 @@
           <t>精簡型電腦</t>
         </is>
       </c>
-      <c r="B219" t="n">
-        <v>0</v>
-      </c>
+      <c r="B219" t="inlineStr"/>
       <c r="C219" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D219" t="n">
         <v>0</v>
@@ -9445,10 +9439,10 @@
         <v>0</v>
       </c>
       <c r="F219" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G219" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H219" t="n">
         <v>0</v>
@@ -9477,34 +9471,34 @@
       </c>
       <c r="B220" t="inlineStr"/>
       <c r="C220" t="n">
+        <v>1</v>
+      </c>
+      <c r="D220" t="n">
+        <v>0</v>
+      </c>
+      <c r="E220" t="n">
+        <v>1</v>
+      </c>
+      <c r="F220" t="n">
+        <v>3</v>
+      </c>
+      <c r="G220" t="n">
+        <v>0</v>
+      </c>
+      <c r="H220" t="n">
         <v>2</v>
       </c>
-      <c r="D220" t="n">
-        <v>1</v>
-      </c>
-      <c r="E220" t="n">
-        <v>0</v>
-      </c>
-      <c r="F220" t="n">
-        <v>1</v>
-      </c>
-      <c r="G220" t="n">
+      <c r="I220" t="n">
+        <v>1</v>
+      </c>
+      <c r="J220" t="n">
         <v>3</v>
       </c>
-      <c r="H220" t="n">
-        <v>0</v>
-      </c>
-      <c r="I220" t="n">
-        <v>2</v>
-      </c>
-      <c r="J220" t="n">
-        <v>1</v>
-      </c>
       <c r="K220" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L220" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="M220" t="n">
         <v>1</v>
@@ -9518,34 +9512,34 @@
       </c>
       <c r="B221" t="inlineStr"/>
       <c r="C221" t="n">
+        <v>3</v>
+      </c>
+      <c r="D221" t="n">
+        <v>0</v>
+      </c>
+      <c r="E221" t="n">
+        <v>1</v>
+      </c>
+      <c r="F221" t="n">
+        <v>1</v>
+      </c>
+      <c r="G221" t="n">
+        <v>0</v>
+      </c>
+      <c r="H221" t="n">
+        <v>1</v>
+      </c>
+      <c r="I221" t="n">
+        <v>0</v>
+      </c>
+      <c r="J221" t="n">
+        <v>3</v>
+      </c>
+      <c r="K221" t="n">
+        <v>1</v>
+      </c>
+      <c r="L221" t="n">
         <v>2</v>
-      </c>
-      <c r="D221" t="n">
-        <v>3</v>
-      </c>
-      <c r="E221" t="n">
-        <v>0</v>
-      </c>
-      <c r="F221" t="n">
-        <v>1</v>
-      </c>
-      <c r="G221" t="n">
-        <v>1</v>
-      </c>
-      <c r="H221" t="n">
-        <v>0</v>
-      </c>
-      <c r="I221" t="n">
-        <v>1</v>
-      </c>
-      <c r="J221" t="n">
-        <v>0</v>
-      </c>
-      <c r="K221" t="n">
-        <v>3</v>
-      </c>
-      <c r="L221" t="n">
-        <v>1</v>
       </c>
       <c r="M221" t="n">
         <v>2</v>
@@ -9559,7 +9553,7 @@
       </c>
       <c r="B222" t="inlineStr"/>
       <c r="C222" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D222" t="n">
         <v>0</v>
@@ -9586,10 +9580,10 @@
         <v>0</v>
       </c>
       <c r="L222" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M222" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="223">
@@ -9621,10 +9615,10 @@
         <v>0</v>
       </c>
       <c r="J223" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K223" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L223" t="n">
         <v>0</v>
@@ -9659,13 +9653,13 @@
         <v>0</v>
       </c>
       <c r="I224" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J224" t="n">
         <v>1</v>
       </c>
       <c r="K224" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L224" t="n">
         <v>0</v>
@@ -9808,7 +9802,7 @@
         <v>1</v>
       </c>
       <c r="D228" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E228" t="n">
         <v>0</v>
@@ -9820,7 +9814,7 @@
         <v>0</v>
       </c>
       <c r="H228" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I228" t="n">
         <v>1</v>
@@ -9849,7 +9843,7 @@
         <v>1</v>
       </c>
       <c r="D229" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E229" t="n">
         <v>0</v>
@@ -9861,19 +9855,19 @@
         <v>0</v>
       </c>
       <c r="H229" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I229" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J229" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K229" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L229" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M229" t="n">
         <v>1</v>
@@ -9887,37 +9881,37 @@
       </c>
       <c r="B230" t="inlineStr"/>
       <c r="C230" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D230" t="n">
+        <v>0</v>
+      </c>
+      <c r="E230" t="n">
+        <v>0</v>
+      </c>
+      <c r="F230" t="n">
+        <v>3</v>
+      </c>
+      <c r="G230" t="n">
+        <v>1</v>
+      </c>
+      <c r="H230" t="n">
+        <v>3</v>
+      </c>
+      <c r="I230" t="n">
+        <v>0</v>
+      </c>
+      <c r="J230" t="n">
         <v>2</v>
-      </c>
-      <c r="E230" t="n">
-        <v>0</v>
-      </c>
-      <c r="F230" t="n">
-        <v>0</v>
-      </c>
-      <c r="G230" t="n">
-        <v>3</v>
-      </c>
-      <c r="H230" t="n">
-        <v>1</v>
-      </c>
-      <c r="I230" t="n">
-        <v>3</v>
-      </c>
-      <c r="J230" t="n">
-        <v>0</v>
       </c>
       <c r="K230" t="n">
         <v>2</v>
       </c>
       <c r="L230" t="n">
+        <v>4</v>
+      </c>
+      <c r="M230" t="n">
         <v>2</v>
-      </c>
-      <c r="M230" t="n">
-        <v>4</v>
       </c>
     </row>
     <row r="231">
@@ -9931,7 +9925,7 @@
         <v>1</v>
       </c>
       <c r="D231" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E231" t="n">
         <v>0</v>
@@ -9943,22 +9937,22 @@
         <v>0</v>
       </c>
       <c r="H231" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I231" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J231" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K231" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L231" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M231" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="232">
@@ -9967,29 +9961,27 @@
           <t>線上遊戲業</t>
         </is>
       </c>
-      <c r="B232" t="n">
-        <v>0</v>
-      </c>
+      <c r="B232" t="inlineStr"/>
       <c r="C232" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D232" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E232" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F232" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G232" t="n">
         <v>0</v>
       </c>
       <c r="H232" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I232" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J232" t="n">
         <v>0</v>
@@ -10012,25 +10004,25 @@
       </c>
       <c r="B233" t="inlineStr"/>
       <c r="C233" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D233" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E233" t="n">
         <v>0</v>
       </c>
       <c r="F233" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G233" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H233" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I233" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J233" t="n">
         <v>0</v>
@@ -10092,7 +10084,9 @@
           <t>織布</t>
         </is>
       </c>
-      <c r="B235" t="inlineStr"/>
+      <c r="B235" t="n">
+        <v>0</v>
+      </c>
       <c r="C235" t="n">
         <v>0</v>
       </c>
@@ -10109,16 +10103,16 @@
         <v>0</v>
       </c>
       <c r="H235" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I235" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J235" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K235" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L235" t="n">
         <v>0</v>
@@ -10153,19 +10147,19 @@
         <v>0</v>
       </c>
       <c r="I236" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J236" t="n">
         <v>1</v>
       </c>
       <c r="K236" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L236" t="n">
         <v>0</v>
       </c>
       <c r="M236" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="237">
@@ -10194,13 +10188,13 @@
         <v>0</v>
       </c>
       <c r="I237" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J237" t="n">
         <v>1</v>
       </c>
       <c r="K237" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L237" t="n">
         <v>0</v>
@@ -10217,10 +10211,10 @@
       </c>
       <c r="B238" t="inlineStr"/>
       <c r="C238" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D238" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E238" t="n">
         <v>0</v>
@@ -10238,10 +10232,10 @@
         <v>0</v>
       </c>
       <c r="J238" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K238" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L238" t="n">
         <v>0</v>
@@ -10258,19 +10252,19 @@
       </c>
       <c r="B239" t="inlineStr"/>
       <c r="C239" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D239" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E239" t="n">
         <v>0</v>
       </c>
       <c r="F239" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G239" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H239" t="n">
         <v>0</v>
@@ -10279,13 +10273,13 @@
         <v>0</v>
       </c>
       <c r="J239" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K239" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L239" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M239" t="n">
         <v>1</v>
@@ -10317,19 +10311,19 @@
         <v>0</v>
       </c>
       <c r="I240" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J240" t="n">
         <v>1</v>
       </c>
       <c r="K240" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L240" t="n">
         <v>0</v>
       </c>
       <c r="M240" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="241">
@@ -10358,10 +10352,10 @@
         <v>0</v>
       </c>
       <c r="I241" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J241" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K241" t="n">
         <v>0</v>
@@ -10390,28 +10384,28 @@
         <v>0</v>
       </c>
       <c r="F242" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G242" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H242" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I242" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J242" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K242" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L242" t="n">
         <v>0</v>
       </c>
       <c r="M242" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="243">
@@ -10443,10 +10437,10 @@
         <v>0</v>
       </c>
       <c r="J243" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K243" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L243" t="n">
         <v>0</v>
@@ -10519,10 +10513,10 @@
         <v>0</v>
       </c>
       <c r="H245" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I245" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J245" t="n">
         <v>0</v>
@@ -10545,7 +10539,7 @@
       </c>
       <c r="B246" t="inlineStr"/>
       <c r="C246" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D246" t="n">
         <v>0</v>
@@ -10560,16 +10554,16 @@
         <v>0</v>
       </c>
       <c r="H246" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I246" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J246" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K246" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L246" t="n">
         <v>0</v>
@@ -10604,10 +10598,10 @@
         <v>0</v>
       </c>
       <c r="I247" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J247" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K247" t="n">
         <v>0</v>
@@ -10616,7 +10610,7 @@
         <v>0</v>
       </c>
       <c r="M247" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="248">
@@ -10647,16 +10641,16 @@
         <v>0</v>
       </c>
       <c r="I248" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J248" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K248" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L248" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M248" t="n">
         <v>0</v>
@@ -10735,10 +10729,10 @@
         <v>0</v>
       </c>
       <c r="K250" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L250" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M250" t="n">
         <v>0</v>
@@ -10793,7 +10787,7 @@
       </c>
       <c r="B252" t="inlineStr"/>
       <c r="C252" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D252" t="n">
         <v>0</v>
@@ -10808,16 +10802,16 @@
         <v>0</v>
       </c>
       <c r="H252" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I252" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J252" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K252" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L252" t="n">
         <v>0</v>
@@ -10916,10 +10910,10 @@
       </c>
       <c r="B255" t="inlineStr"/>
       <c r="C255" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D255" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E255" t="n">
         <v>0</v>
@@ -10972,16 +10966,16 @@
         <v>0</v>
       </c>
       <c r="H256" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I256" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J256" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K256" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L256" t="n">
         <v>0</v>
@@ -11183,10 +11177,10 @@
         <v>0</v>
       </c>
       <c r="J261" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K261" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L261" t="n">
         <v>0</v>
@@ -11203,37 +11197,37 @@
       </c>
       <c r="B262" t="inlineStr"/>
       <c r="C262" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D262" t="n">
+        <v>0</v>
+      </c>
+      <c r="E262" t="n">
+        <v>0</v>
+      </c>
+      <c r="F262" t="n">
+        <v>0</v>
+      </c>
+      <c r="G262" t="n">
+        <v>0</v>
+      </c>
+      <c r="H262" t="n">
+        <v>0</v>
+      </c>
+      <c r="I262" t="n">
+        <v>1</v>
+      </c>
+      <c r="J262" t="n">
+        <v>1</v>
+      </c>
+      <c r="K262" t="n">
         <v>2</v>
       </c>
-      <c r="E262" t="n">
-        <v>0</v>
-      </c>
-      <c r="F262" t="n">
-        <v>0</v>
-      </c>
-      <c r="G262" t="n">
-        <v>0</v>
-      </c>
-      <c r="H262" t="n">
-        <v>0</v>
-      </c>
-      <c r="I262" t="n">
-        <v>0</v>
-      </c>
-      <c r="J262" t="n">
-        <v>1</v>
-      </c>
-      <c r="K262" t="n">
-        <v>1</v>
-      </c>
       <c r="L262" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M262" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="263">
@@ -11250,13 +11244,13 @@
         <v>0</v>
       </c>
       <c r="E263" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F263" t="n">
         <v>1</v>
       </c>
       <c r="G263" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H263" t="n">
         <v>0</v>
@@ -11268,10 +11262,10 @@
         <v>0</v>
       </c>
       <c r="K263" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L263" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M263" t="n">
         <v>0</v>
@@ -11285,7 +11279,7 @@
       </c>
       <c r="B264" t="inlineStr"/>
       <c r="C264" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D264" t="n">
         <v>0</v>
@@ -11294,25 +11288,25 @@
         <v>0</v>
       </c>
       <c r="F264" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G264" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H264" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I264" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J264" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K264" t="n">
         <v>1</v>
       </c>
       <c r="L264" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M264" t="n">
         <v>0</v>
@@ -11414,10 +11408,10 @@
         <v>0</v>
       </c>
       <c r="E267" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F267" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G267" t="n">
         <v>0</v>
@@ -11508,13 +11502,13 @@
         <v>0</v>
       </c>
       <c r="I269" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J269" t="n">
         <v>1</v>
       </c>
       <c r="K269" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L269" t="n">
         <v>0</v>
@@ -11531,7 +11525,7 @@
       </c>
       <c r="B270" t="inlineStr"/>
       <c r="C270" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D270" t="n">
         <v>0</v>
@@ -11540,19 +11534,19 @@
         <v>0</v>
       </c>
       <c r="F270" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G270" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H270" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I270" t="n">
         <v>1</v>
       </c>
       <c r="J270" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K270" t="n">
         <v>0</v>
@@ -11616,7 +11610,7 @@
         <v>1</v>
       </c>
       <c r="D272" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E272" t="n">
         <v>0</v>
@@ -11628,19 +11622,19 @@
         <v>0</v>
       </c>
       <c r="H272" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I272" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J272" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K272" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L272" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M272" t="n">
         <v>1</v>
@@ -11654,7 +11648,7 @@
       </c>
       <c r="B273" t="inlineStr"/>
       <c r="C273" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D273" t="n">
         <v>0</v>
@@ -11669,16 +11663,16 @@
         <v>0</v>
       </c>
       <c r="H273" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I273" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J273" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K273" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L273" t="n">
         <v>0</v>
@@ -11698,7 +11692,7 @@
         <v>1</v>
       </c>
       <c r="D274" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E274" t="n">
         <v>0</v>
@@ -11710,19 +11704,19 @@
         <v>0</v>
       </c>
       <c r="H274" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I274" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J274" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K274" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L274" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M274" t="n">
         <v>1</v>
@@ -11736,7 +11730,7 @@
       </c>
       <c r="B275" t="inlineStr"/>
       <c r="C275" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D275" t="n">
         <v>0</v>
@@ -11751,19 +11745,19 @@
         <v>0</v>
       </c>
       <c r="H275" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I275" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J275" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K275" t="n">
         <v>1</v>
       </c>
       <c r="L275" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M275" t="n">
         <v>0</v>
@@ -11780,7 +11774,7 @@
         <v>1</v>
       </c>
       <c r="D276" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E276" t="n">
         <v>0</v>
@@ -11792,19 +11786,19 @@
         <v>0</v>
       </c>
       <c r="H276" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I276" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J276" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K276" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L276" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M276" t="n">
         <v>1</v>
@@ -11859,7 +11853,7 @@
       </c>
       <c r="B278" t="inlineStr"/>
       <c r="C278" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D278" t="n">
         <v>0</v>
@@ -11874,22 +11868,22 @@
         <v>0</v>
       </c>
       <c r="H278" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I278" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J278" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K278" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L278" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M278" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="279">
@@ -11924,10 +11918,10 @@
         <v>0</v>
       </c>
       <c r="K279" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L279" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M279" t="n">
         <v>0</v>
@@ -11985,7 +11979,7 @@
         <v>1</v>
       </c>
       <c r="D281" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E281" t="n">
         <v>0</v>
@@ -11997,19 +11991,19 @@
         <v>0</v>
       </c>
       <c r="H281" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I281" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J281" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K281" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L281" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M281" t="n">
         <v>1</v>
@@ -12044,10 +12038,10 @@
         <v>0</v>
       </c>
       <c r="J282" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K282" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L282" t="n">
         <v>0</v>
@@ -12228,7 +12222,7 @@
       </c>
       <c r="B287" t="inlineStr"/>
       <c r="C287" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D287" t="n">
         <v>0</v>
@@ -12243,22 +12237,22 @@
         <v>0</v>
       </c>
       <c r="H287" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I287" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J287" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K287" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L287" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M287" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="288">
@@ -12296,10 +12290,10 @@
         <v>0</v>
       </c>
       <c r="L288" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M288" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="289">
@@ -12319,10 +12313,10 @@
         <v>0</v>
       </c>
       <c r="F289" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G289" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H289" t="n">
         <v>0</v>
@@ -12349,20 +12343,40 @@
           <t>軟性電路板</t>
         </is>
       </c>
-      <c r="B290" t="n">
-        <v>0</v>
-      </c>
-      <c r="C290" t="inlineStr"/>
-      <c r="D290" t="inlineStr"/>
-      <c r="E290" t="inlineStr"/>
-      <c r="F290" t="inlineStr"/>
-      <c r="G290" t="inlineStr"/>
-      <c r="H290" t="inlineStr"/>
-      <c r="I290" t="inlineStr"/>
-      <c r="J290" t="inlineStr"/>
-      <c r="K290" t="inlineStr"/>
-      <c r="L290" t="inlineStr"/>
-      <c r="M290" t="inlineStr"/>
+      <c r="B290" t="inlineStr"/>
+      <c r="C290" t="n">
+        <v>0</v>
+      </c>
+      <c r="D290" t="n">
+        <v>0</v>
+      </c>
+      <c r="E290" t="n">
+        <v>0</v>
+      </c>
+      <c r="F290" t="n">
+        <v>0</v>
+      </c>
+      <c r="G290" t="n">
+        <v>0</v>
+      </c>
+      <c r="H290" t="n">
+        <v>0</v>
+      </c>
+      <c r="I290" t="n">
+        <v>0</v>
+      </c>
+      <c r="J290" t="n">
+        <v>0</v>
+      </c>
+      <c r="K290" t="n">
+        <v>0</v>
+      </c>
+      <c r="L290" t="n">
+        <v>0</v>
+      </c>
+      <c r="M290" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="291">
       <c r="A291" s="1" t="inlineStr">
@@ -12519,10 +12533,10 @@
         <v>0</v>
       </c>
       <c r="K294" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L294" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M294" t="n">
         <v>0</v>
@@ -12545,10 +12559,10 @@
         <v>0</v>
       </c>
       <c r="F295" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G295" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H295" t="n">
         <v>0</v>
@@ -12595,19 +12609,19 @@
         <v>0</v>
       </c>
       <c r="I296" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J296" t="n">
         <v>1</v>
       </c>
       <c r="K296" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L296" t="n">
         <v>0</v>
       </c>
       <c r="M296" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="297">
@@ -12648,7 +12662,7 @@
         <v>0</v>
       </c>
       <c r="M297" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="298">
@@ -12677,13 +12691,13 @@
         <v>0</v>
       </c>
       <c r="I298" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J298" t="n">
         <v>1</v>
       </c>
       <c r="K298" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L298" t="n">
         <v>0</v>
@@ -12782,7 +12796,7 @@
       </c>
       <c r="B301" t="inlineStr"/>
       <c r="C301" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D301" t="n">
         <v>0</v>
@@ -12797,16 +12811,16 @@
         <v>0</v>
       </c>
       <c r="H301" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I301" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J301" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K301" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L301" t="n">
         <v>0</v>
@@ -12821,38 +12835,36 @@
           <t>連接器設計、組裝及製造</t>
         </is>
       </c>
-      <c r="B302" t="n">
-        <v>0</v>
-      </c>
+      <c r="B302" t="inlineStr"/>
       <c r="C302" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D302" t="n">
+        <v>0</v>
+      </c>
+      <c r="E302" t="n">
+        <v>0</v>
+      </c>
+      <c r="F302" t="n">
+        <v>1</v>
+      </c>
+      <c r="G302" t="n">
+        <v>0</v>
+      </c>
+      <c r="H302" t="n">
         <v>2</v>
-      </c>
-      <c r="E302" t="n">
-        <v>0</v>
-      </c>
-      <c r="F302" t="n">
-        <v>0</v>
-      </c>
-      <c r="G302" t="n">
-        <v>1</v>
-      </c>
-      <c r="H302" t="n">
-        <v>0</v>
       </c>
       <c r="I302" t="n">
         <v>2</v>
       </c>
       <c r="J302" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K302" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L302" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M302" t="n">
         <v>1</v>
@@ -12869,25 +12881,25 @@
         <v>1</v>
       </c>
       <c r="D303" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E303" t="n">
         <v>0</v>
       </c>
       <c r="F303" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G303" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H303" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I303" t="n">
         <v>1</v>
       </c>
       <c r="J303" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K303" t="n">
         <v>0</v>
@@ -13039,10 +13051,10 @@
         <v>0</v>
       </c>
       <c r="F307" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G307" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H307" t="n">
         <v>0</v>
@@ -13054,10 +13066,10 @@
         <v>0</v>
       </c>
       <c r="K307" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L307" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M307" t="n">
         <v>0</v>
@@ -13080,10 +13092,10 @@
         <v>0</v>
       </c>
       <c r="F308" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G308" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H308" t="n">
         <v>0</v>
@@ -13092,13 +13104,13 @@
         <v>0</v>
       </c>
       <c r="J308" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K308" t="n">
         <v>1</v>
       </c>
       <c r="L308" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M308" t="n">
         <v>0</v>
@@ -13159,13 +13171,13 @@
         <v>0</v>
       </c>
       <c r="E310" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F310" t="n">
         <v>1</v>
       </c>
       <c r="G310" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H310" t="n">
         <v>0</v>
@@ -13200,10 +13212,10 @@
         <v>0</v>
       </c>
       <c r="E311" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F311" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G311" t="n">
         <v>0</v>
@@ -13259,10 +13271,10 @@
         <v>0</v>
       </c>
       <c r="K312" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L312" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M312" t="n">
         <v>0</v>
@@ -13285,25 +13297,25 @@
         <v>0</v>
       </c>
       <c r="F313" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G313" t="n">
+        <v>1</v>
+      </c>
+      <c r="H313" t="n">
+        <v>0</v>
+      </c>
+      <c r="I313" t="n">
         <v>2</v>
       </c>
-      <c r="H313" t="n">
-        <v>1</v>
-      </c>
-      <c r="I313" t="n">
-        <v>0</v>
-      </c>
       <c r="J313" t="n">
+        <v>0</v>
+      </c>
+      <c r="K313" t="n">
         <v>2</v>
       </c>
-      <c r="K313" t="n">
-        <v>0</v>
-      </c>
       <c r="L313" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M313" t="n">
         <v>0</v>
@@ -13315,38 +13327,36 @@
           <t>醫療器材研發、設計、製造</t>
         </is>
       </c>
-      <c r="B314" t="n">
-        <v>0</v>
-      </c>
+      <c r="B314" t="inlineStr"/>
       <c r="C314" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D314" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E314" t="n">
         <v>0</v>
       </c>
       <c r="F314" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G314" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H314" t="n">
         <v>0</v>
       </c>
       <c r="I314" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J314" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K314" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L314" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M314" t="n">
         <v>0</v>
@@ -13378,10 +13388,10 @@
         <v>0</v>
       </c>
       <c r="I315" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J315" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K315" t="n">
         <v>0</v>
@@ -13401,7 +13411,7 @@
       </c>
       <c r="B316" t="inlineStr"/>
       <c r="C316" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D316" t="n">
         <v>0</v>
@@ -13416,10 +13426,10 @@
         <v>0</v>
       </c>
       <c r="H316" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I316" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J316" t="n">
         <v>0</v>
@@ -13463,10 +13473,10 @@
         <v>0</v>
       </c>
       <c r="J317" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K317" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L317" t="n">
         <v>0</v>
@@ -13483,10 +13493,10 @@
       </c>
       <c r="B318" t="inlineStr"/>
       <c r="C318" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D318" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E318" t="n">
         <v>0</v>
@@ -13504,16 +13514,16 @@
         <v>0</v>
       </c>
       <c r="J318" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K318" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L318" t="n">
         <v>0</v>
       </c>
       <c r="M318" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="319">
@@ -13709,10 +13719,10 @@
         <v>0</v>
       </c>
       <c r="J323" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K323" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L323" t="n">
         <v>0</v>
@@ -13756,10 +13766,10 @@
         <v>0</v>
       </c>
       <c r="L324" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M324" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="325">
@@ -13779,10 +13789,10 @@
         <v>0</v>
       </c>
       <c r="F325" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G325" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H325" t="n">
         <v>0</v>
@@ -13794,10 +13804,10 @@
         <v>0</v>
       </c>
       <c r="K325" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L325" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M325" t="n">
         <v>0</v>
@@ -13820,28 +13830,28 @@
         <v>0</v>
       </c>
       <c r="F326" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G326" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H326" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I326" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J326" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K326" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L326" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M326" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="327">
@@ -13852,7 +13862,7 @@
       </c>
       <c r="B327" t="inlineStr"/>
       <c r="C327" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D327" t="n">
         <v>0</v>
@@ -13934,19 +13944,19 @@
       </c>
       <c r="B329" t="inlineStr"/>
       <c r="C329" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D329" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E329" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F329" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G329" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H329" t="n">
         <v>0</v>
@@ -14139,10 +14149,10 @@
       </c>
       <c r="B334" t="inlineStr"/>
       <c r="C334" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D334" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E334" t="n">
         <v>0</v>
@@ -14280,19 +14290,19 @@
         <v>0</v>
       </c>
       <c r="I337" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J337" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K337" t="n">
         <v>0</v>
       </c>
       <c r="L337" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M337" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="338">
@@ -14327,10 +14337,10 @@
         <v>0</v>
       </c>
       <c r="K338" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L338" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M338" t="n">
         <v>0</v>
@@ -14347,7 +14357,7 @@
         <v>1</v>
       </c>
       <c r="D339" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E339" t="n">
         <v>0</v>
@@ -14359,22 +14369,22 @@
         <v>0</v>
       </c>
       <c r="H339" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I339" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J339" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K339" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L339" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M339" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="340">
@@ -14385,7 +14395,7 @@
       </c>
       <c r="B340" t="inlineStr"/>
       <c r="C340" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D340" t="n">
         <v>0</v>
@@ -14400,19 +14410,19 @@
         <v>0</v>
       </c>
       <c r="H340" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I340" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J340" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K340" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L340" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M340" t="n">
         <v>0</v>
@@ -14426,7 +14436,7 @@
       </c>
       <c r="B341" t="inlineStr"/>
       <c r="C341" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D341" t="n">
         <v>0</v>
@@ -14435,25 +14445,25 @@
         <v>0</v>
       </c>
       <c r="F341" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G341" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H341" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I341" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J341" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K341" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L341" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M341" t="n">
         <v>0</v>
@@ -14470,22 +14480,22 @@
         <v>0</v>
       </c>
       <c r="D342" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E342" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F342" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G342" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H342" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I342" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J342" t="n">
         <v>0</v>
@@ -14497,7 +14507,7 @@
         <v>0</v>
       </c>
       <c r="M342" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="343">
@@ -14517,19 +14527,19 @@
         <v>0</v>
       </c>
       <c r="F343" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G343" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H343" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I343" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J343" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K343" t="n">
         <v>0</v>
@@ -14588,7 +14598,9 @@
           <t>電力系統</t>
         </is>
       </c>
-      <c r="B345" t="inlineStr"/>
+      <c r="B345" t="n">
+        <v>0</v>
+      </c>
       <c r="C345" t="n">
         <v>0</v>
       </c>
@@ -14596,13 +14608,13 @@
         <v>0</v>
       </c>
       <c r="E345" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F345" t="n">
         <v>1</v>
       </c>
       <c r="G345" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H345" t="n">
         <v>0</v>
@@ -14637,13 +14649,13 @@
         <v>0</v>
       </c>
       <c r="E346" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F346" t="n">
         <v>1</v>
       </c>
       <c r="G346" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H346" t="n">
         <v>0</v>
@@ -14652,7 +14664,7 @@
         <v>0</v>
       </c>
       <c r="J346" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K346" t="n">
         <v>1</v>
@@ -14661,7 +14673,7 @@
         <v>1</v>
       </c>
       <c r="M346" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="347">
@@ -14693,10 +14705,10 @@
         <v>0</v>
       </c>
       <c r="J347" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K347" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L347" t="n">
         <v>0</v>
@@ -14713,7 +14725,7 @@
       </c>
       <c r="B348" t="inlineStr"/>
       <c r="C348" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D348" t="n">
         <v>0</v>
@@ -14722,10 +14734,10 @@
         <v>0</v>
       </c>
       <c r="F348" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G348" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H348" t="n">
         <v>0</v>
@@ -14734,10 +14746,10 @@
         <v>0</v>
       </c>
       <c r="J348" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K348" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L348" t="n">
         <v>0</v>
@@ -14763,10 +14775,10 @@
         <v>0</v>
       </c>
       <c r="F349" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G349" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H349" t="n">
         <v>0</v>
@@ -14839,25 +14851,25 @@
         <v>1</v>
       </c>
       <c r="D351" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E351" t="n">
         <v>0</v>
       </c>
       <c r="F351" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G351" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H351" t="n">
         <v>0</v>
       </c>
       <c r="I351" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J351" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K351" t="n">
         <v>0</v>
@@ -14877,37 +14889,37 @@
       </c>
       <c r="B352" t="inlineStr"/>
       <c r="C352" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D352" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E352" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F352" t="n">
         <v>3</v>
       </c>
       <c r="G352" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H352" t="n">
         <v>2</v>
       </c>
       <c r="I352" t="n">
+        <v>1</v>
+      </c>
+      <c r="J352" t="n">
+        <v>0</v>
+      </c>
+      <c r="K352" t="n">
+        <v>3</v>
+      </c>
+      <c r="L352" t="n">
         <v>2</v>
       </c>
-      <c r="J352" t="n">
-        <v>1</v>
-      </c>
-      <c r="K352" t="n">
-        <v>0</v>
-      </c>
-      <c r="L352" t="n">
-        <v>3</v>
-      </c>
       <c r="M352" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="353">
@@ -14916,9 +14928,7 @@
           <t>電容器材料(如電蝕／化成鋁箔、介面瓷粉)</t>
         </is>
       </c>
-      <c r="B353" t="n">
-        <v>0</v>
-      </c>
+      <c r="B353" t="inlineStr"/>
       <c r="C353" t="n">
         <v>0</v>
       </c>
@@ -14926,10 +14936,10 @@
         <v>0</v>
       </c>
       <c r="E353" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F353" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G353" t="n">
         <v>0</v>
@@ -14947,10 +14957,10 @@
         <v>0</v>
       </c>
       <c r="L353" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M353" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="354">
@@ -14961,34 +14971,34 @@
       </c>
       <c r="B354" t="inlineStr"/>
       <c r="C354" t="n">
+        <v>0</v>
+      </c>
+      <c r="D354" t="n">
+        <v>0</v>
+      </c>
+      <c r="E354" t="n">
         <v>2</v>
       </c>
-      <c r="D354" t="n">
-        <v>0</v>
-      </c>
-      <c r="E354" t="n">
-        <v>0</v>
-      </c>
       <c r="F354" t="n">
+        <v>1</v>
+      </c>
+      <c r="G354" t="n">
+        <v>0</v>
+      </c>
+      <c r="H354" t="n">
+        <v>0</v>
+      </c>
+      <c r="I354" t="n">
+        <v>0</v>
+      </c>
+      <c r="J354" t="n">
+        <v>0</v>
+      </c>
+      <c r="K354" t="n">
         <v>2</v>
       </c>
-      <c r="G354" t="n">
-        <v>1</v>
-      </c>
-      <c r="H354" t="n">
-        <v>0</v>
-      </c>
-      <c r="I354" t="n">
-        <v>0</v>
-      </c>
-      <c r="J354" t="n">
-        <v>0</v>
-      </c>
-      <c r="K354" t="n">
-        <v>0</v>
-      </c>
       <c r="L354" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M354" t="n">
         <v>0</v>
@@ -15000,11 +15010,9 @@
           <t>電感器材料(如鐵氧體、導電漿墨)</t>
         </is>
       </c>
-      <c r="B355" t="n">
-        <v>0</v>
-      </c>
+      <c r="B355" t="inlineStr"/>
       <c r="C355" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D355" t="n">
         <v>0</v>
@@ -15028,10 +15036,10 @@
         <v>0</v>
       </c>
       <c r="K355" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L355" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M355" t="n">
         <v>0</v>
@@ -15043,7 +15051,9 @@
           <t>電控元件</t>
         </is>
       </c>
-      <c r="B356" t="inlineStr"/>
+      <c r="B356" t="n">
+        <v>0</v>
+      </c>
       <c r="C356" t="n">
         <v>0</v>
       </c>
@@ -15054,10 +15064,10 @@
         <v>0</v>
       </c>
       <c r="F356" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G356" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H356" t="n">
         <v>0</v>
@@ -15069,10 +15079,10 @@
         <v>0</v>
       </c>
       <c r="K356" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L356" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M356" t="n">
         <v>0</v>
@@ -15095,10 +15105,10 @@
         <v>0</v>
       </c>
       <c r="F357" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G357" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H357" t="n">
         <v>0</v>
@@ -15107,16 +15117,16 @@
         <v>0</v>
       </c>
       <c r="J357" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K357" t="n">
         <v>1</v>
       </c>
       <c r="L357" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M357" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="358">
@@ -15130,16 +15140,16 @@
         <v>0</v>
       </c>
       <c r="D358" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E358" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F358" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G358" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H358" t="n">
         <v>0</v>
@@ -15148,16 +15158,16 @@
         <v>0</v>
       </c>
       <c r="J358" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K358" t="n">
         <v>1</v>
       </c>
       <c r="L358" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M358" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="359">
@@ -15171,16 +15181,16 @@
         <v>0</v>
       </c>
       <c r="D359" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E359" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F359" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G359" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H359" t="n">
         <v>0</v>
@@ -15209,28 +15219,28 @@
       </c>
       <c r="B360" t="inlineStr"/>
       <c r="C360" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D360" t="n">
         <v>0</v>
       </c>
       <c r="E360" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F360" t="n">
         <v>1</v>
       </c>
       <c r="G360" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H360" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I360" t="n">
         <v>2</v>
       </c>
       <c r="J360" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K360" t="n">
         <v>1</v>
@@ -15239,7 +15249,7 @@
         <v>1</v>
       </c>
       <c r="M360" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="361">
@@ -15256,10 +15266,10 @@
         <v>0</v>
       </c>
       <c r="E361" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F361" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G361" t="n">
         <v>0</v>
@@ -15373,19 +15383,19 @@
       </c>
       <c r="B364" t="inlineStr"/>
       <c r="C364" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D364" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E364" t="n">
         <v>0</v>
       </c>
       <c r="F364" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G364" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H364" t="n">
         <v>0</v>
@@ -15400,7 +15410,7 @@
         <v>0</v>
       </c>
       <c r="L364" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M364" t="n">
         <v>1</v>
@@ -15423,28 +15433,28 @@
         <v>0</v>
       </c>
       <c r="F365" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G365" t="n">
+        <v>0</v>
+      </c>
+      <c r="H365" t="n">
+        <v>0</v>
+      </c>
+      <c r="I365" t="n">
+        <v>1</v>
+      </c>
+      <c r="J365" t="n">
+        <v>1</v>
+      </c>
+      <c r="K365" t="n">
         <v>2</v>
       </c>
-      <c r="H365" t="n">
-        <v>0</v>
-      </c>
-      <c r="I365" t="n">
-        <v>0</v>
-      </c>
-      <c r="J365" t="n">
-        <v>1</v>
-      </c>
-      <c r="K365" t="n">
-        <v>1</v>
-      </c>
       <c r="L365" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M365" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="366">
@@ -15537,19 +15547,19 @@
       </c>
       <c r="B368" t="inlineStr"/>
       <c r="C368" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D368" t="n">
         <v>0</v>
       </c>
       <c r="E368" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F368" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G368" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H368" t="n">
         <v>0</v>
@@ -15576,9 +15586,7 @@
           <t>電阻器材料(氧化鋁陶瓷基板、導電漿墨)</t>
         </is>
       </c>
-      <c r="B369" t="n">
-        <v>0</v>
-      </c>
+      <c r="B369" t="inlineStr"/>
       <c r="C369" t="n">
         <v>0</v>
       </c>
@@ -15630,10 +15638,10 @@
         <v>0</v>
       </c>
       <c r="F370" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G370" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H370" t="n">
         <v>0</v>
@@ -15747,28 +15755,28 @@
         <v>1</v>
       </c>
       <c r="D373" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E373" t="n">
         <v>0</v>
       </c>
       <c r="F373" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G373" t="n">
+        <v>1</v>
+      </c>
+      <c r="H373" t="n">
+        <v>1</v>
+      </c>
+      <c r="I373" t="n">
+        <v>1</v>
+      </c>
+      <c r="J373" t="n">
         <v>2</v>
       </c>
-      <c r="H373" t="n">
-        <v>1</v>
-      </c>
-      <c r="I373" t="n">
-        <v>1</v>
-      </c>
-      <c r="J373" t="n">
-        <v>1</v>
-      </c>
       <c r="K373" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L373" t="n">
         <v>1</v>
@@ -15867,34 +15875,34 @@
       </c>
       <c r="B376" t="inlineStr"/>
       <c r="C376" t="n">
+        <v>0</v>
+      </c>
+      <c r="D376" t="n">
+        <v>0</v>
+      </c>
+      <c r="E376" t="n">
+        <v>1</v>
+      </c>
+      <c r="F376" t="n">
+        <v>3</v>
+      </c>
+      <c r="G376" t="n">
+        <v>0</v>
+      </c>
+      <c r="H376" t="n">
         <v>2</v>
       </c>
-      <c r="D376" t="n">
-        <v>0</v>
-      </c>
-      <c r="E376" t="n">
-        <v>0</v>
-      </c>
-      <c r="F376" t="n">
-        <v>1</v>
-      </c>
-      <c r="G376" t="n">
-        <v>3</v>
-      </c>
-      <c r="H376" t="n">
-        <v>0</v>
-      </c>
       <c r="I376" t="n">
+        <v>0</v>
+      </c>
+      <c r="J376" t="n">
         <v>2</v>
-      </c>
-      <c r="J376" t="n">
-        <v>0</v>
       </c>
       <c r="K376" t="n">
         <v>2</v>
       </c>
       <c r="L376" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M376" t="n">
         <v>0</v>
@@ -15906,9 +15914,7 @@
           <t>顯示卡</t>
         </is>
       </c>
-      <c r="B377" t="n">
-        <v>0</v>
-      </c>
+      <c r="B377" t="inlineStr"/>
       <c r="C377" t="n">
         <v>0</v>
       </c>
@@ -15966,22 +15972,22 @@
         <v>0</v>
       </c>
       <c r="H378" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I378" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J378" t="n">
         <v>0</v>
       </c>
       <c r="K378" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L378" t="n">
         <v>1</v>
       </c>
       <c r="M378" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="379">
@@ -16010,13 +16016,13 @@
         <v>0</v>
       </c>
       <c r="I379" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J379" t="n">
         <v>1</v>
       </c>
       <c r="K379" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L379" t="n">
         <v>0</v>
@@ -16095,10 +16101,10 @@
         <v>0</v>
       </c>
       <c r="J381" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K381" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L381" t="n">
         <v>0</v>
@@ -16156,10 +16162,10 @@
       </c>
       <c r="B383" t="inlineStr"/>
       <c r="C383" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D383" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E383" t="n">
         <v>0</v>
@@ -16168,19 +16174,19 @@
         <v>0</v>
       </c>
       <c r="G383" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H383" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I383" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J383" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K383" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L383" t="n">
         <v>0</v>
@@ -16244,13 +16250,13 @@
         <v>0</v>
       </c>
       <c r="E385" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F385" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G385" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H385" t="n">
         <v>0</v>
@@ -16318,9 +16324,7 @@
           <t>高爾夫球具業</t>
         </is>
       </c>
-      <c r="B387" t="n">
-        <v>0</v>
-      </c>
+      <c r="B387" t="inlineStr"/>
       <c r="C387" t="n">
         <v>0</v>
       </c>

--- a/Result/analyze_3.xlsx
+++ b/Result/analyze_3.xlsx
@@ -441,57 +441,57 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
     </row>
@@ -665,23 +665,21 @@
           <t>IC/晶圓製造</t>
         </is>
       </c>
-      <c r="B6" t="n">
-        <v>0</v>
-      </c>
+      <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H6" t="n">
         <v>2</v>
@@ -690,16 +688,16 @@
         <v>2</v>
       </c>
       <c r="J6" t="n">
+        <v>3</v>
+      </c>
+      <c r="K6" t="n">
+        <v>1</v>
+      </c>
+      <c r="L6" t="n">
         <v>2</v>
       </c>
-      <c r="K6" t="n">
-        <v>3</v>
-      </c>
-      <c r="L6" t="n">
-        <v>1</v>
-      </c>
       <c r="M6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -710,37 +708,37 @@
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="n">
         <v>2</v>
       </c>
-      <c r="G7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0</v>
-      </c>
       <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
         <v>2</v>
       </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
       <c r="K7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L7" t="n">
         <v>1</v>
       </c>
       <c r="M7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -757,28 +755,28 @@
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="n">
         <v>2</v>
       </c>
-      <c r="G8" t="n">
-        <v>0</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0</v>
-      </c>
       <c r="I8" t="n">
+        <v>1</v>
+      </c>
+      <c r="J8" t="n">
+        <v>1</v>
+      </c>
+      <c r="K8" t="n">
         <v>2</v>
       </c>
-      <c r="J8" t="n">
-        <v>1</v>
-      </c>
-      <c r="K8" t="n">
-        <v>1</v>
-      </c>
       <c r="L8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -790,36 +788,38 @@
           <t>IC設計</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr"/>
+      <c r="B9" t="n">
+        <v>0</v>
+      </c>
       <c r="C9" t="n">
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G9" t="n">
         <v>1</v>
       </c>
       <c r="H9" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I9" t="n">
         <v>4</v>
       </c>
       <c r="J9" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M9" t="n">
         <v>2</v>
@@ -839,31 +839,31 @@
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F10" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K10" t="n">
         <v>2</v>
       </c>
       <c r="L10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -874,34 +874,34 @@
       </c>
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1</v>
+      </c>
+      <c r="H11" t="n">
         <v>2</v>
       </c>
-      <c r="D11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" t="n">
-        <v>1</v>
-      </c>
-      <c r="G11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" t="n">
-        <v>1</v>
-      </c>
       <c r="I11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
@@ -1132,10 +1132,10 @@
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
@@ -1202,7 +1202,7 @@
       </c>
       <c r="B19" t="inlineStr"/>
       <c r="C19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
         <v>0</v>
@@ -1284,37 +1284,37 @@
       </c>
       <c r="B21" t="inlineStr"/>
       <c r="C21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" t="n">
         <v>2</v>
       </c>
-      <c r="I21" t="n">
-        <v>1</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0</v>
-      </c>
       <c r="K21" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -1372,19 +1372,19 @@
         <v>0</v>
       </c>
       <c r="E23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -1396,7 +1396,7 @@
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -1413,31 +1413,31 @@
         <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F24" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" t="n">
+        <v>1</v>
+      </c>
+      <c r="H24" t="n">
+        <v>3</v>
+      </c>
+      <c r="I24" t="n">
         <v>2</v>
-      </c>
-      <c r="G24" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" t="n">
-        <v>1</v>
-      </c>
-      <c r="I24" t="n">
-        <v>3</v>
       </c>
       <c r="J24" t="n">
         <v>2</v>
       </c>
       <c r="K24" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -1463,13 +1463,13 @@
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I25" t="n">
         <v>1</v>
       </c>
       <c r="J25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K25" t="n">
         <v>0</v>
@@ -1530,7 +1530,7 @@
       </c>
       <c r="B27" t="inlineStr"/>
       <c r="C27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D27" t="n">
         <v>0</v>
@@ -1548,19 +1548,19 @@
         <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K27" t="n">
         <v>0</v>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -1674,10 +1674,10 @@
         <v>0</v>
       </c>
       <c r="J30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L30" t="n">
         <v>0</v>
@@ -1712,13 +1712,13 @@
         <v>0</v>
       </c>
       <c r="I31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J31" t="n">
         <v>1</v>
       </c>
       <c r="K31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
@@ -1735,16 +1735,16 @@
       </c>
       <c r="B32" t="inlineStr"/>
       <c r="C32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D32" t="n">
         <v>0</v>
       </c>
       <c r="E32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
@@ -1753,10 +1753,10 @@
         <v>0</v>
       </c>
       <c r="I32" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J32" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K32" t="n">
         <v>0</v>
@@ -1794,10 +1794,10 @@
         <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K33" t="n">
         <v>0</v>
@@ -1870,7 +1870,7 @@
         <v>0</v>
       </c>
       <c r="G35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H35" t="n">
         <v>1</v>
@@ -1882,7 +1882,7 @@
         <v>1</v>
       </c>
       <c r="K35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L35" t="n">
         <v>0</v>
@@ -2034,10 +2034,10 @@
         <v>0</v>
       </c>
       <c r="G39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I39" t="n">
         <v>0</v>
@@ -2102,9 +2102,7 @@
           <t>傳動元件</t>
         </is>
       </c>
-      <c r="B41" t="n">
-        <v>0</v>
-      </c>
+      <c r="B41" t="inlineStr"/>
       <c r="C41" t="n">
         <v>0</v>
       </c>
@@ -2112,10 +2110,10 @@
         <v>0</v>
       </c>
       <c r="E41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
@@ -2153,25 +2151,25 @@
         <v>0</v>
       </c>
       <c r="E42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K42" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L42" t="n">
         <v>0</v>
@@ -2203,10 +2201,10 @@
         <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -2232,19 +2230,19 @@
         <v>0</v>
       </c>
       <c r="D44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F44" t="n">
         <v>0</v>
       </c>
       <c r="G44" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H44" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I44" t="n">
         <v>0</v>
@@ -2256,10 +2254,10 @@
         <v>0</v>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -2285,22 +2283,22 @@
         <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I45" t="n">
         <v>1</v>
       </c>
       <c r="J45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K45" t="n">
         <v>0</v>
       </c>
       <c r="L45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M45" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="46">
@@ -2367,10 +2365,10 @@
         <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -2379,7 +2377,7 @@
         <v>0</v>
       </c>
       <c r="L47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M47" t="n">
         <v>1</v>
@@ -2434,22 +2432,22 @@
       </c>
       <c r="B49" t="inlineStr"/>
       <c r="C49" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E49" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F49" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G49" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H49" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I49" t="n">
         <v>3</v>
@@ -2461,10 +2459,10 @@
         <v>3</v>
       </c>
       <c r="L49" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M49" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="50">
@@ -2524,31 +2522,31 @@
         <v>1</v>
       </c>
       <c r="E51" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F51" t="n">
+        <v>1</v>
+      </c>
+      <c r="G51" t="n">
         <v>3</v>
       </c>
-      <c r="G51" t="n">
-        <v>1</v>
-      </c>
       <c r="H51" t="n">
+        <v>4</v>
+      </c>
+      <c r="I51" t="n">
+        <v>6</v>
+      </c>
+      <c r="J51" t="n">
+        <v>1</v>
+      </c>
+      <c r="K51" t="n">
+        <v>0</v>
+      </c>
+      <c r="L51" t="n">
+        <v>0</v>
+      </c>
+      <c r="M51" t="n">
         <v>3</v>
-      </c>
-      <c r="I51" t="n">
-        <v>4</v>
-      </c>
-      <c r="J51" t="n">
-        <v>6</v>
-      </c>
-      <c r="K51" t="n">
-        <v>1</v>
-      </c>
-      <c r="L51" t="n">
-        <v>0</v>
-      </c>
-      <c r="M51" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -2600,34 +2598,34 @@
       </c>
       <c r="B53" t="inlineStr"/>
       <c r="C53" t="n">
+        <v>0</v>
+      </c>
+      <c r="D53" t="n">
+        <v>0</v>
+      </c>
+      <c r="E53" t="n">
         <v>2</v>
       </c>
-      <c r="D53" t="n">
-        <v>0</v>
-      </c>
-      <c r="E53" t="n">
-        <v>0</v>
-      </c>
       <c r="F53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G53" t="n">
+        <v>0</v>
+      </c>
+      <c r="H53" t="n">
+        <v>0</v>
+      </c>
+      <c r="I53" t="n">
+        <v>1</v>
+      </c>
+      <c r="J53" t="n">
+        <v>0</v>
+      </c>
+      <c r="K53" t="n">
         <v>2</v>
       </c>
-      <c r="G53" t="n">
-        <v>0</v>
-      </c>
-      <c r="H53" t="n">
-        <v>0</v>
-      </c>
-      <c r="I53" t="n">
-        <v>0</v>
-      </c>
-      <c r="J53" t="n">
-        <v>1</v>
-      </c>
-      <c r="K53" t="n">
-        <v>0</v>
-      </c>
       <c r="L53" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M53" t="n">
         <v>1</v>
@@ -2647,28 +2645,28 @@
         <v>1</v>
       </c>
       <c r="E54" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F54" t="n">
+        <v>0</v>
+      </c>
+      <c r="G54" t="n">
         <v>4</v>
       </c>
-      <c r="G54" t="n">
-        <v>0</v>
-      </c>
       <c r="H54" t="n">
+        <v>5</v>
+      </c>
+      <c r="I54" t="n">
         <v>4</v>
       </c>
-      <c r="I54" t="n">
-        <v>5</v>
-      </c>
       <c r="J54" t="n">
+        <v>1</v>
+      </c>
+      <c r="K54" t="n">
+        <v>7</v>
+      </c>
+      <c r="L54" t="n">
         <v>4</v>
-      </c>
-      <c r="K54" t="n">
-        <v>1</v>
-      </c>
-      <c r="L54" t="n">
-        <v>7</v>
       </c>
       <c r="M54" t="n">
         <v>4</v>
@@ -2685,7 +2683,7 @@
         <v>0</v>
       </c>
       <c r="D55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E55" t="n">
         <v>1</v>
@@ -2694,25 +2692,25 @@
         <v>1</v>
       </c>
       <c r="G55" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H55" t="n">
+        <v>1</v>
+      </c>
+      <c r="I55" t="n">
         <v>3</v>
       </c>
-      <c r="I55" t="n">
-        <v>1</v>
-      </c>
       <c r="J55" t="n">
+        <v>2</v>
+      </c>
+      <c r="K55" t="n">
         <v>3</v>
       </c>
-      <c r="K55" t="n">
+      <c r="L55" t="n">
         <v>2</v>
       </c>
-      <c r="L55" t="n">
-        <v>3</v>
-      </c>
       <c r="M55" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="56">
@@ -2723,19 +2721,19 @@
       </c>
       <c r="B56" t="inlineStr"/>
       <c r="C56" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D56" t="n">
         <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H56" t="n">
         <v>1</v>
@@ -2750,7 +2748,7 @@
         <v>1</v>
       </c>
       <c r="L56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M56" t="n">
         <v>0</v>
@@ -2803,17 +2801,15 @@
           <t>冷凍空調設備及零件</t>
         </is>
       </c>
-      <c r="B58" t="n">
-        <v>0</v>
-      </c>
+      <c r="B58" t="inlineStr"/>
       <c r="C58" t="n">
         <v>0</v>
       </c>
       <c r="D58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F58" t="n">
         <v>0</v>
@@ -2825,19 +2821,19 @@
         <v>0</v>
       </c>
       <c r="I58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K58" t="n">
         <v>0</v>
       </c>
       <c r="L58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59">
@@ -2851,13 +2847,13 @@
         <v>0</v>
       </c>
       <c r="D59" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F59" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
@@ -2916,10 +2912,10 @@
         <v>0</v>
       </c>
       <c r="L60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61">
@@ -2928,9 +2924,7 @@
           <t>冷熱軋鋼板捲</t>
         </is>
       </c>
-      <c r="B61" t="n">
-        <v>0</v>
-      </c>
+      <c r="B61" t="inlineStr"/>
       <c r="C61" t="n">
         <v>0</v>
       </c>
@@ -2959,10 +2953,10 @@
         <v>0</v>
       </c>
       <c r="L61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62">
@@ -3035,10 +3029,10 @@
         <v>0</v>
       </c>
       <c r="J63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L63" t="n">
         <v>0</v>
@@ -3053,9 +3047,7 @@
           <t>創意生活產業</t>
         </is>
       </c>
-      <c r="B64" t="n">
-        <v>0</v>
-      </c>
+      <c r="B64" t="inlineStr"/>
       <c r="C64" t="n">
         <v>0</v>
       </c>
@@ -3195,10 +3187,10 @@
         <v>0</v>
       </c>
       <c r="H67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -3219,7 +3211,9 @@
           <t>加工食品</t>
         </is>
       </c>
-      <c r="B68" t="inlineStr"/>
+      <c r="B68" t="n">
+        <v>0</v>
+      </c>
       <c r="C68" t="n">
         <v>0</v>
       </c>
@@ -3286,13 +3280,13 @@
         <v>0</v>
       </c>
       <c r="K69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="70">
@@ -3344,7 +3338,7 @@
       </c>
       <c r="B71" t="inlineStr"/>
       <c r="C71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D71" t="n">
         <v>0</v>
@@ -3356,22 +3350,22 @@
         <v>0</v>
       </c>
       <c r="G71" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H71" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I71" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K71" t="n">
         <v>0</v>
       </c>
       <c r="L71" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M71" t="n">
         <v>1</v>
@@ -3385,37 +3379,37 @@
       </c>
       <c r="B72" t="inlineStr"/>
       <c r="C72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D72" t="n">
         <v>0</v>
       </c>
       <c r="E72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H72" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I72" t="n">
+        <v>1</v>
+      </c>
+      <c r="J72" t="n">
+        <v>1</v>
+      </c>
+      <c r="K72" t="n">
+        <v>1</v>
+      </c>
+      <c r="L72" t="n">
+        <v>1</v>
+      </c>
+      <c r="M72" t="n">
         <v>2</v>
-      </c>
-      <c r="J72" t="n">
-        <v>1</v>
-      </c>
-      <c r="K72" t="n">
-        <v>1</v>
-      </c>
-      <c r="L72" t="n">
-        <v>1</v>
-      </c>
-      <c r="M72" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="73">
@@ -3432,10 +3426,10 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F73" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
@@ -3447,16 +3441,16 @@
         <v>0</v>
       </c>
       <c r="J73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K73" t="n">
         <v>1</v>
       </c>
       <c r="L73" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="74">
@@ -3564,13 +3558,13 @@
         <v>0</v>
       </c>
       <c r="H76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I76" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J76" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K76" t="n">
         <v>0</v>
@@ -3605,10 +3599,10 @@
         <v>0</v>
       </c>
       <c r="H77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I77" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -3634,28 +3628,28 @@
         <v>2</v>
       </c>
       <c r="D78" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E78" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F78" t="n">
         <v>0</v>
       </c>
       <c r="G78" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H78" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I78" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J78" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K78" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L78" t="n">
         <v>1</v>
@@ -3670,7 +3664,9 @@
           <t>原物料</t>
         </is>
       </c>
-      <c r="B79" t="inlineStr"/>
+      <c r="B79" t="n">
+        <v>0</v>
+      </c>
       <c r="C79" t="n">
         <v>0</v>
       </c>
@@ -3769,13 +3765,13 @@
         <v>0</v>
       </c>
       <c r="H81" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I81" t="n">
         <v>1</v>
       </c>
       <c r="J81" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K81" t="n">
         <v>0</v>
@@ -3836,31 +3832,31 @@
       </c>
       <c r="B83" t="inlineStr"/>
       <c r="C83" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D83" t="n">
         <v>0</v>
       </c>
       <c r="E83" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F83" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G83" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H83" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I83" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J83" t="n">
         <v>1</v>
       </c>
       <c r="K83" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L83" t="n">
         <v>0</v>
@@ -4000,7 +3996,7 @@
       </c>
       <c r="B87" t="inlineStr"/>
       <c r="C87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D87" t="n">
         <v>0</v>
@@ -4047,10 +4043,10 @@
         <v>0</v>
       </c>
       <c r="E88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G88" t="n">
         <v>0</v>
@@ -4082,16 +4078,16 @@
       </c>
       <c r="B89" t="inlineStr"/>
       <c r="C89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D89" t="n">
         <v>0</v>
       </c>
       <c r="E89" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G89" t="n">
         <v>0</v>
@@ -4100,10 +4096,10 @@
         <v>0</v>
       </c>
       <c r="I89" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K89" t="n">
         <v>0</v>
@@ -4112,7 +4108,7 @@
         <v>0</v>
       </c>
       <c r="M89" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="90">
@@ -4194,7 +4190,7 @@
         <v>0</v>
       </c>
       <c r="M91" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="92">
@@ -4203,9 +4199,7 @@
           <t>大功率鋰電池芯/模組、電池管理系統、動力馬達等零組件</t>
         </is>
       </c>
-      <c r="B92" t="n">
-        <v>0</v>
-      </c>
+      <c r="B92" t="inlineStr"/>
       <c r="C92" t="n">
         <v>1</v>
       </c>
@@ -4213,28 +4207,28 @@
         <v>1</v>
       </c>
       <c r="E92" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F92" t="n">
+        <v>0</v>
+      </c>
+      <c r="G92" t="n">
+        <v>0</v>
+      </c>
+      <c r="H92" t="n">
+        <v>0</v>
+      </c>
+      <c r="I92" t="n">
+        <v>1</v>
+      </c>
+      <c r="J92" t="n">
+        <v>1</v>
+      </c>
+      <c r="K92" t="n">
         <v>2</v>
       </c>
-      <c r="G92" t="n">
-        <v>0</v>
-      </c>
-      <c r="H92" t="n">
-        <v>0</v>
-      </c>
-      <c r="I92" t="n">
-        <v>0</v>
-      </c>
-      <c r="J92" t="n">
-        <v>1</v>
-      </c>
-      <c r="K92" t="n">
-        <v>1</v>
-      </c>
       <c r="L92" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M92" t="n">
         <v>0</v>
@@ -4307,10 +4301,10 @@
         <v>0</v>
       </c>
       <c r="I94" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J94" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K94" t="n">
         <v>0</v>
@@ -4328,36 +4322,38 @@
           <t>太陽能發電設備/系統及系統工程</t>
         </is>
       </c>
-      <c r="B95" t="inlineStr"/>
+      <c r="B95" t="n">
+        <v>0</v>
+      </c>
       <c r="C95" t="n">
         <v>0</v>
       </c>
       <c r="D95" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E95" t="n">
         <v>1</v>
       </c>
       <c r="F95" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G95" t="n">
         <v>0</v>
       </c>
       <c r="H95" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I95" t="n">
         <v>2</v>
       </c>
       <c r="J95" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K95" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L95" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M95" t="n">
         <v>0</v>
@@ -4377,22 +4373,22 @@
         <v>0</v>
       </c>
       <c r="E96" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F96" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G96" t="n">
         <v>0</v>
       </c>
       <c r="H96" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I96" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J96" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K96" t="n">
         <v>0</v>
@@ -4442,7 +4438,7 @@
         <v>0</v>
       </c>
       <c r="M97" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="98">
@@ -4471,19 +4467,19 @@
         <v>0</v>
       </c>
       <c r="I98" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J98" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K98" t="n">
         <v>0</v>
       </c>
       <c r="L98" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M98" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="99">
@@ -4492,9 +4488,7 @@
           <t>娛樂服務業</t>
         </is>
       </c>
-      <c r="B99" t="n">
-        <v>0</v>
-      </c>
+      <c r="B99" t="inlineStr"/>
       <c r="C99" t="n">
         <v>0</v>
       </c>
@@ -4505,7 +4499,7 @@
         <v>0</v>
       </c>
       <c r="F99" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G99" t="n">
         <v>0</v>
@@ -4514,10 +4508,10 @@
         <v>0</v>
       </c>
       <c r="I99" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K99" t="n">
         <v>0</v>
@@ -4590,16 +4584,16 @@
         <v>0</v>
       </c>
       <c r="G101" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H101" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I101" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J101" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K101" t="n">
         <v>0</v>
@@ -4625,28 +4619,28 @@
         <v>0</v>
       </c>
       <c r="E102" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F102" t="n">
+        <v>1</v>
+      </c>
+      <c r="G102" t="n">
+        <v>0</v>
+      </c>
+      <c r="H102" t="n">
+        <v>0</v>
+      </c>
+      <c r="I102" t="n">
+        <v>1</v>
+      </c>
+      <c r="J102" t="n">
+        <v>3</v>
+      </c>
+      <c r="K102" t="n">
         <v>2</v>
       </c>
-      <c r="G102" t="n">
-        <v>1</v>
-      </c>
-      <c r="H102" t="n">
-        <v>0</v>
-      </c>
-      <c r="I102" t="n">
-        <v>0</v>
-      </c>
-      <c r="J102" t="n">
-        <v>1</v>
-      </c>
-      <c r="K102" t="n">
-        <v>3</v>
-      </c>
       <c r="L102" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M102" t="n">
         <v>1</v>
@@ -4707,31 +4701,31 @@
         <v>0</v>
       </c>
       <c r="E104" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F104" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G104" t="n">
         <v>0</v>
       </c>
       <c r="H104" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I104" t="n">
         <v>1</v>
       </c>
       <c r="J104" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K104" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L104" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M104" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="105">
@@ -4742,25 +4736,25 @@
       </c>
       <c r="B105" t="inlineStr"/>
       <c r="C105" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D105" t="n">
         <v>0</v>
       </c>
       <c r="E105" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F105" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G105" t="n">
         <v>0</v>
       </c>
       <c r="H105" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I105" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -4769,7 +4763,7 @@
         <v>0</v>
       </c>
       <c r="L105" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M105" t="n">
         <v>1</v>
@@ -4783,16 +4777,16 @@
       </c>
       <c r="B106" t="inlineStr"/>
       <c r="C106" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D106" t="n">
         <v>0</v>
       </c>
       <c r="E106" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F106" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G106" t="n">
         <v>0</v>
@@ -4807,10 +4801,10 @@
         <v>0</v>
       </c>
       <c r="K106" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L106" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M106" t="n">
         <v>0</v>
@@ -4953,10 +4947,10 @@
         <v>0</v>
       </c>
       <c r="E110" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F110" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G110" t="n">
         <v>0</v>
@@ -4986,7 +4980,9 @@
           <t>工業電腦</t>
         </is>
       </c>
-      <c r="B111" t="inlineStr"/>
+      <c r="B111" t="n">
+        <v>0</v>
+      </c>
       <c r="C111" t="n">
         <v>0</v>
       </c>
@@ -5000,25 +4996,25 @@
         <v>0</v>
       </c>
       <c r="G111" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H111" t="n">
         <v>1</v>
       </c>
       <c r="I111" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J111" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K111" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L111" t="n">
         <v>1</v>
       </c>
       <c r="M111" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="112">
@@ -5032,10 +5028,10 @@
         <v>0</v>
       </c>
       <c r="D112" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E112" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F112" t="n">
         <v>0</v>
@@ -5044,19 +5040,19 @@
         <v>0</v>
       </c>
       <c r="H112" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I112" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J112" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K112" t="n">
         <v>1</v>
       </c>
       <c r="L112" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M112" t="n">
         <v>0</v>
@@ -5073,10 +5069,10 @@
         <v>0</v>
       </c>
       <c r="D113" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E113" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F113" t="n">
         <v>0</v>
@@ -5123,10 +5119,10 @@
         <v>0</v>
       </c>
       <c r="G114" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H114" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I114" t="n">
         <v>0</v>
@@ -5167,10 +5163,10 @@
         <v>0</v>
       </c>
       <c r="H115" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I115" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -5208,10 +5204,10 @@
         <v>0</v>
       </c>
       <c r="H116" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I116" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -5357,16 +5353,16 @@
       </c>
       <c r="B120" t="inlineStr"/>
       <c r="C120" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D120" t="n">
         <v>0</v>
       </c>
       <c r="E120" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F120" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G120" t="n">
         <v>0</v>
@@ -5375,16 +5371,16 @@
         <v>0</v>
       </c>
       <c r="I120" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J120" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K120" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L120" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M120" t="n">
         <v>0</v>
@@ -5404,25 +5400,25 @@
         <v>0</v>
       </c>
       <c r="E121" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F121" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G121" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H121" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I121" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J121" t="n">
         <v>1</v>
       </c>
       <c r="K121" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L121" t="n">
         <v>0</v>
@@ -5685,16 +5681,16 @@
       </c>
       <c r="B128" t="inlineStr"/>
       <c r="C128" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D128" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E128" t="n">
         <v>1</v>
       </c>
       <c r="F128" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G128" t="n">
         <v>0</v>
@@ -5703,10 +5699,10 @@
         <v>0</v>
       </c>
       <c r="I128" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J128" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K128" t="n">
         <v>1</v>
@@ -5747,10 +5743,10 @@
         <v>0</v>
       </c>
       <c r="J129" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K129" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L129" t="n">
         <v>0</v>
@@ -5808,13 +5804,13 @@
       </c>
       <c r="B131" t="inlineStr"/>
       <c r="C131" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D131" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E131" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F131" t="n">
         <v>0</v>
@@ -5879,7 +5875,7 @@
         <v>0</v>
       </c>
       <c r="M132" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="133">
@@ -6078,10 +6074,10 @@
         <v>0</v>
       </c>
       <c r="K137" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L137" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M137" t="n">
         <v>0</v>
@@ -6142,28 +6138,28 @@
         <v>0</v>
       </c>
       <c r="E139" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F139" t="n">
+        <v>0</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0</v>
+      </c>
+      <c r="I139" t="n">
+        <v>1</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0</v>
+      </c>
+      <c r="K139" t="n">
         <v>2</v>
       </c>
-      <c r="G139" t="n">
-        <v>0</v>
-      </c>
-      <c r="H139" t="n">
-        <v>0</v>
-      </c>
-      <c r="I139" t="n">
-        <v>0</v>
-      </c>
-      <c r="J139" t="n">
-        <v>1</v>
-      </c>
-      <c r="K139" t="n">
-        <v>0</v>
-      </c>
       <c r="L139" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M139" t="n">
         <v>0</v>
@@ -6192,13 +6188,13 @@
         <v>0</v>
       </c>
       <c r="H140" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I140" t="n">
         <v>1</v>
       </c>
       <c r="J140" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K140" t="n">
         <v>0</v>
@@ -6207,7 +6203,7 @@
         <v>0</v>
       </c>
       <c r="M140" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="141">
@@ -6233,13 +6229,13 @@
         <v>0</v>
       </c>
       <c r="H141" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I141" t="n">
         <v>1</v>
       </c>
       <c r="J141" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K141" t="n">
         <v>0</v>
@@ -6274,13 +6270,13 @@
         <v>0</v>
       </c>
       <c r="H142" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I142" t="n">
         <v>1</v>
       </c>
       <c r="J142" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K142" t="n">
         <v>0</v>
@@ -6339,11 +6335,9 @@
           <t>數位內容產業</t>
         </is>
       </c>
-      <c r="B144" t="n">
-        <v>0</v>
-      </c>
+      <c r="B144" t="inlineStr"/>
       <c r="C144" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D144" t="n">
         <v>0</v>
@@ -6355,10 +6349,10 @@
         <v>0</v>
       </c>
       <c r="G144" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H144" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I144" t="n">
         <v>0</v>
@@ -6396,16 +6390,16 @@
         <v>0</v>
       </c>
       <c r="G145" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H145" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I145" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J145" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K145" t="n">
         <v>0</v>
@@ -6478,16 +6472,16 @@
         <v>0</v>
       </c>
       <c r="G147" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H147" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I147" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J147" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K147" t="n">
         <v>0</v>
@@ -6519,19 +6513,19 @@
         <v>0</v>
       </c>
       <c r="G148" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H148" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I148" t="n">
         <v>0</v>
       </c>
       <c r="J148" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K148" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L148" t="n">
         <v>0</v>
@@ -6595,10 +6589,10 @@
         <v>0</v>
       </c>
       <c r="E150" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F150" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G150" t="n">
         <v>0</v>
@@ -6633,10 +6627,10 @@
         <v>0</v>
       </c>
       <c r="D151" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E151" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F151" t="n">
         <v>0</v>
@@ -6648,10 +6642,10 @@
         <v>0</v>
       </c>
       <c r="I151" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J151" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K151" t="n">
         <v>0</v>
@@ -6712,34 +6706,34 @@
       </c>
       <c r="B153" t="inlineStr"/>
       <c r="C153" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D153" t="n">
         <v>0</v>
       </c>
       <c r="E153" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F153" t="n">
+        <v>1</v>
+      </c>
+      <c r="G153" t="n">
+        <v>0</v>
+      </c>
+      <c r="H153" t="n">
+        <v>0</v>
+      </c>
+      <c r="I153" t="n">
+        <v>0</v>
+      </c>
+      <c r="J153" t="n">
+        <v>0</v>
+      </c>
+      <c r="K153" t="n">
         <v>2</v>
       </c>
-      <c r="G153" t="n">
-        <v>1</v>
-      </c>
-      <c r="H153" t="n">
-        <v>0</v>
-      </c>
-      <c r="I153" t="n">
-        <v>0</v>
-      </c>
-      <c r="J153" t="n">
-        <v>0</v>
-      </c>
-      <c r="K153" t="n">
-        <v>0</v>
-      </c>
       <c r="L153" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M153" t="n">
         <v>1</v>
@@ -6759,10 +6753,10 @@
         <v>0</v>
       </c>
       <c r="E154" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F154" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G154" t="n">
         <v>0</v>
@@ -6835,7 +6829,7 @@
       </c>
       <c r="B156" t="inlineStr"/>
       <c r="C156" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D156" t="n">
         <v>0</v>
@@ -6874,9 +6868,7 @@
           <t>染整</t>
         </is>
       </c>
-      <c r="B157" t="n">
-        <v>0</v>
-      </c>
+      <c r="B157" t="inlineStr"/>
       <c r="C157" t="n">
         <v>0</v>
       </c>
@@ -6887,22 +6879,22 @@
         <v>0</v>
       </c>
       <c r="F157" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G157" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H157" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I157" t="n">
         <v>0</v>
       </c>
       <c r="J157" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K157" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L157" t="n">
         <v>0</v>
@@ -6925,10 +6917,10 @@
         <v>0</v>
       </c>
       <c r="E158" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F158" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G158" t="n">
         <v>0</v>
@@ -7007,10 +6999,10 @@
         <v>0</v>
       </c>
       <c r="E160" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F160" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G160" t="n">
         <v>0</v>
@@ -7083,31 +7075,31 @@
       </c>
       <c r="B162" t="inlineStr"/>
       <c r="C162" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D162" t="n">
         <v>0</v>
       </c>
       <c r="E162" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F162" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G162" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H162" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I162" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J162" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K162" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L162" t="n">
         <v>1</v>
@@ -7145,10 +7137,10 @@
         <v>0</v>
       </c>
       <c r="J163" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K163" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L163" t="n">
         <v>0</v>
@@ -7183,13 +7175,13 @@
         <v>0</v>
       </c>
       <c r="I164" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J164" t="n">
         <v>1</v>
       </c>
       <c r="K164" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L164" t="n">
         <v>0</v>
@@ -7218,22 +7210,22 @@
         <v>0</v>
       </c>
       <c r="G165" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H165" t="n">
         <v>1</v>
       </c>
       <c r="I165" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J165" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K165" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L165" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M165" t="n">
         <v>0</v>
@@ -7245,20 +7237,18 @@
           <t>機電工程</t>
         </is>
       </c>
-      <c r="B166" t="n">
-        <v>0</v>
-      </c>
+      <c r="B166" t="inlineStr"/>
       <c r="C166" t="n">
         <v>0</v>
       </c>
       <c r="D166" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E166" t="n">
         <v>1</v>
       </c>
       <c r="F166" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G166" t="n">
         <v>0</v>
@@ -7288,17 +7278,15 @@
           <t>機電系統工程</t>
         </is>
       </c>
-      <c r="B167" t="n">
-        <v>0</v>
-      </c>
+      <c r="B167" t="inlineStr"/>
       <c r="C167" t="n">
         <v>0</v>
       </c>
       <c r="D167" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E167" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F167" t="n">
         <v>0</v>
@@ -7331,7 +7319,9 @@
           <t>橡膠製品</t>
         </is>
       </c>
-      <c r="B168" t="inlineStr"/>
+      <c r="B168" t="n">
+        <v>0</v>
+      </c>
       <c r="C168" t="n">
         <v>0</v>
       </c>
@@ -7348,10 +7338,10 @@
         <v>0</v>
       </c>
       <c r="H168" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I168" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -7512,10 +7502,10 @@
         <v>0</v>
       </c>
       <c r="H172" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I172" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -7594,10 +7584,10 @@
         <v>0</v>
       </c>
       <c r="H174" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I174" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -7609,7 +7599,7 @@
         <v>0</v>
       </c>
       <c r="M174" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="175">
@@ -7635,10 +7625,10 @@
         <v>0</v>
       </c>
       <c r="H175" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I175" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -7650,7 +7640,7 @@
         <v>0</v>
       </c>
       <c r="M175" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="176">
@@ -7708,10 +7698,10 @@
         <v>0</v>
       </c>
       <c r="E177" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F177" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G177" t="n">
         <v>0</v>
@@ -7723,10 +7713,10 @@
         <v>0</v>
       </c>
       <c r="J177" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K177" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L177" t="n">
         <v>0</v>
@@ -7784,22 +7774,22 @@
       </c>
       <c r="B179" t="inlineStr"/>
       <c r="C179" t="n">
+        <v>0</v>
+      </c>
+      <c r="D179" t="n">
+        <v>0</v>
+      </c>
+      <c r="E179" t="n">
         <v>2</v>
       </c>
-      <c r="D179" t="n">
-        <v>0</v>
-      </c>
-      <c r="E179" t="n">
-        <v>0</v>
-      </c>
       <c r="F179" t="n">
+        <v>1</v>
+      </c>
+      <c r="G179" t="n">
+        <v>4</v>
+      </c>
+      <c r="H179" t="n">
         <v>2</v>
-      </c>
-      <c r="G179" t="n">
-        <v>1</v>
-      </c>
-      <c r="H179" t="n">
-        <v>4</v>
       </c>
       <c r="I179" t="n">
         <v>2</v>
@@ -7808,10 +7798,10 @@
         <v>2</v>
       </c>
       <c r="K179" t="n">
+        <v>3</v>
+      </c>
+      <c r="L179" t="n">
         <v>2</v>
-      </c>
-      <c r="L179" t="n">
-        <v>3</v>
       </c>
       <c r="M179" t="n">
         <v>2</v>
@@ -7864,7 +7854,9 @@
           <t>燈具/應用</t>
         </is>
       </c>
-      <c r="B181" t="inlineStr"/>
+      <c r="B181" t="n">
+        <v>0</v>
+      </c>
       <c r="C181" t="n">
         <v>0</v>
       </c>
@@ -7872,13 +7864,13 @@
         <v>0</v>
       </c>
       <c r="E181" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F181" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G181" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H181" t="n">
         <v>1</v>
@@ -7887,16 +7879,16 @@
         <v>1</v>
       </c>
       <c r="J181" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K181" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L181" t="n">
         <v>2</v>
       </c>
       <c r="M181" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="182">
@@ -7907,7 +7899,7 @@
       </c>
       <c r="B182" t="inlineStr"/>
       <c r="C182" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D182" t="n">
         <v>0</v>
@@ -7934,10 +7926,10 @@
         <v>0</v>
       </c>
       <c r="L182" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M182" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="183">
@@ -8001,19 +7993,19 @@
         <v>0</v>
       </c>
       <c r="G184" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H184" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I184" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J184" t="n">
         <v>1</v>
       </c>
       <c r="K184" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L184" t="n">
         <v>0</v>
@@ -8153,7 +8145,7 @@
       </c>
       <c r="B188" t="inlineStr"/>
       <c r="C188" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D188" t="n">
         <v>0</v>
@@ -8165,19 +8157,19 @@
         <v>0</v>
       </c>
       <c r="G188" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H188" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I188" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J188" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K188" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L188" t="n">
         <v>1</v>
@@ -8192,7 +8184,9 @@
           <t>特殊照明業</t>
         </is>
       </c>
-      <c r="B189" t="inlineStr"/>
+      <c r="B189" t="n">
+        <v>0</v>
+      </c>
       <c r="C189" t="n">
         <v>0</v>
       </c>
@@ -8200,10 +8194,10 @@
         <v>0</v>
       </c>
       <c r="E189" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F189" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G189" t="n">
         <v>0</v>
@@ -8323,10 +8317,10 @@
         <v>0</v>
       </c>
       <c r="E192" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F192" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G192" t="n">
         <v>0</v>
@@ -8338,16 +8332,16 @@
         <v>0</v>
       </c>
       <c r="J192" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K192" t="n">
+        <v>1</v>
+      </c>
+      <c r="L192" t="n">
+        <v>0</v>
+      </c>
+      <c r="M192" t="n">
         <v>2</v>
-      </c>
-      <c r="L192" t="n">
-        <v>1</v>
-      </c>
-      <c r="M192" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="193">
@@ -8405,31 +8399,31 @@
         <v>0</v>
       </c>
       <c r="E194" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F194" t="n">
+        <v>0</v>
+      </c>
+      <c r="G194" t="n">
+        <v>1</v>
+      </c>
+      <c r="H194" t="n">
+        <v>1</v>
+      </c>
+      <c r="I194" t="n">
+        <v>1</v>
+      </c>
+      <c r="J194" t="n">
+        <v>1</v>
+      </c>
+      <c r="K194" t="n">
+        <v>1</v>
+      </c>
+      <c r="L194" t="n">
+        <v>1</v>
+      </c>
+      <c r="M194" t="n">
         <v>2</v>
-      </c>
-      <c r="G194" t="n">
-        <v>0</v>
-      </c>
-      <c r="H194" t="n">
-        <v>1</v>
-      </c>
-      <c r="I194" t="n">
-        <v>1</v>
-      </c>
-      <c r="J194" t="n">
-        <v>1</v>
-      </c>
-      <c r="K194" t="n">
-        <v>1</v>
-      </c>
-      <c r="L194" t="n">
-        <v>1</v>
-      </c>
-      <c r="M194" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="195">
@@ -8455,7 +8449,7 @@
         <v>0</v>
       </c>
       <c r="H195" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I195" t="n">
         <v>1</v>
@@ -8464,10 +8458,10 @@
         <v>1</v>
       </c>
       <c r="K195" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L195" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M195" t="n">
         <v>1</v>
@@ -8481,31 +8475,31 @@
       </c>
       <c r="B196" t="inlineStr"/>
       <c r="C196" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D196" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E196" t="n">
         <v>1</v>
       </c>
       <c r="F196" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G196" t="n">
         <v>0</v>
       </c>
       <c r="H196" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I196" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J196" t="n">
         <v>0</v>
       </c>
       <c r="K196" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L196" t="n">
         <v>1</v>
@@ -8525,34 +8519,34 @@
         <v>1</v>
       </c>
       <c r="D197" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E197" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="F197" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="G197" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H197" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="I197" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="J197" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K197" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="L197" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="M197" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="198">
@@ -8581,10 +8575,10 @@
         <v>0</v>
       </c>
       <c r="I198" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J198" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K198" t="n">
         <v>0</v>
@@ -8643,9 +8637,7 @@
           <t>監控系統</t>
         </is>
       </c>
-      <c r="B200" t="n">
-        <v>0</v>
-      </c>
+      <c r="B200" t="inlineStr"/>
       <c r="C200" t="n">
         <v>0</v>
       </c>
@@ -8653,10 +8645,10 @@
         <v>0</v>
       </c>
       <c r="E200" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F200" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G200" t="n">
         <v>0</v>
@@ -8791,10 +8783,10 @@
         <v>0</v>
       </c>
       <c r="J203" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K203" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L203" t="n">
         <v>0</v>
@@ -8809,41 +8801,39 @@
           <t>石化中間原料(例如乙烯、丙烯、丁二烯、苯、酚等)</t>
         </is>
       </c>
-      <c r="B204" t="n">
-        <v>0</v>
-      </c>
+      <c r="B204" t="inlineStr"/>
       <c r="C204" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D204" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E204" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F204" t="n">
         <v>0</v>
       </c>
       <c r="G204" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H204" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I204" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J204" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K204" t="n">
         <v>0</v>
       </c>
       <c r="L204" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M204" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="205">
@@ -8875,10 +8865,10 @@
         <v>0</v>
       </c>
       <c r="J205" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K205" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L205" t="n">
         <v>0</v>
@@ -8936,7 +8926,7 @@
       </c>
       <c r="B207" t="inlineStr"/>
       <c r="C207" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D207" t="n">
         <v>0</v>
@@ -8977,37 +8967,37 @@
       </c>
       <c r="B208" t="inlineStr"/>
       <c r="C208" t="n">
+        <v>1</v>
+      </c>
+      <c r="D208" t="n">
+        <v>0</v>
+      </c>
+      <c r="E208" t="n">
+        <v>9</v>
+      </c>
+      <c r="F208" t="n">
+        <v>0</v>
+      </c>
+      <c r="G208" t="n">
+        <v>0</v>
+      </c>
+      <c r="H208" t="n">
+        <v>8</v>
+      </c>
+      <c r="I208" t="n">
+        <v>1</v>
+      </c>
+      <c r="J208" t="n">
         <v>2</v>
       </c>
-      <c r="D208" t="n">
-        <v>1</v>
-      </c>
-      <c r="E208" t="n">
-        <v>0</v>
-      </c>
-      <c r="F208" t="n">
-        <v>9</v>
-      </c>
-      <c r="G208" t="n">
-        <v>0</v>
-      </c>
-      <c r="H208" t="n">
-        <v>0</v>
-      </c>
-      <c r="I208" t="n">
-        <v>8</v>
-      </c>
-      <c r="J208" t="n">
-        <v>1</v>
-      </c>
       <c r="K208" t="n">
+        <v>1</v>
+      </c>
+      <c r="L208" t="n">
         <v>2</v>
       </c>
-      <c r="L208" t="n">
-        <v>1</v>
-      </c>
       <c r="M208" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="209">
@@ -9121,10 +9111,10 @@
         <v>0</v>
       </c>
       <c r="J211" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K211" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L211" t="n">
         <v>0</v>
@@ -9221,9 +9211,7 @@
           <t>移動控制</t>
         </is>
       </c>
-      <c r="B214" t="n">
-        <v>0</v>
-      </c>
+      <c r="B214" t="inlineStr"/>
       <c r="C214" t="n">
         <v>0</v>
       </c>
@@ -9348,7 +9336,7 @@
       </c>
       <c r="B217" t="inlineStr"/>
       <c r="C217" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D217" t="n">
         <v>0</v>
@@ -9360,19 +9348,19 @@
         <v>0</v>
       </c>
       <c r="G217" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H217" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I217" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J217" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K217" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L217" t="n">
         <v>1</v>
@@ -9395,10 +9383,10 @@
         <v>0</v>
       </c>
       <c r="E218" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F218" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G218" t="n">
         <v>0</v>
@@ -9436,10 +9424,10 @@
         <v>0</v>
       </c>
       <c r="E219" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F219" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G219" t="n">
         <v>0</v>
@@ -9471,31 +9459,31 @@
       </c>
       <c r="B220" t="inlineStr"/>
       <c r="C220" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D220" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E220" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F220" t="n">
+        <v>0</v>
+      </c>
+      <c r="G220" t="n">
+        <v>2</v>
+      </c>
+      <c r="H220" t="n">
+        <v>1</v>
+      </c>
+      <c r="I220" t="n">
         <v>3</v>
       </c>
-      <c r="G220" t="n">
-        <v>0</v>
-      </c>
-      <c r="H220" t="n">
-        <v>2</v>
-      </c>
-      <c r="I220" t="n">
-        <v>1</v>
-      </c>
       <c r="J220" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K220" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L220" t="n">
         <v>1</v>
@@ -9510,33 +9498,35 @@
           <t>系統整合服務</t>
         </is>
       </c>
-      <c r="B221" t="inlineStr"/>
+      <c r="B221" t="n">
+        <v>0</v>
+      </c>
       <c r="C221" t="n">
+        <v>0</v>
+      </c>
+      <c r="D221" t="n">
+        <v>0</v>
+      </c>
+      <c r="E221" t="n">
+        <v>1</v>
+      </c>
+      <c r="F221" t="n">
+        <v>0</v>
+      </c>
+      <c r="G221" t="n">
+        <v>1</v>
+      </c>
+      <c r="H221" t="n">
+        <v>0</v>
+      </c>
+      <c r="I221" t="n">
         <v>3</v>
       </c>
-      <c r="D221" t="n">
-        <v>0</v>
-      </c>
-      <c r="E221" t="n">
-        <v>1</v>
-      </c>
-      <c r="F221" t="n">
-        <v>1</v>
-      </c>
-      <c r="G221" t="n">
-        <v>0</v>
-      </c>
-      <c r="H221" t="n">
-        <v>1</v>
-      </c>
-      <c r="I221" t="n">
-        <v>0</v>
-      </c>
       <c r="J221" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K221" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L221" t="n">
         <v>2</v>
@@ -9577,10 +9567,10 @@
         <v>0</v>
       </c>
       <c r="K222" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L222" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M222" t="n">
         <v>0</v>
@@ -9612,10 +9602,10 @@
         <v>0</v>
       </c>
       <c r="I223" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J223" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K223" t="n">
         <v>0</v>
@@ -9650,13 +9640,13 @@
         <v>0</v>
       </c>
       <c r="H224" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I224" t="n">
         <v>1</v>
       </c>
       <c r="J224" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K224" t="n">
         <v>0</v>
@@ -9799,7 +9789,7 @@
       </c>
       <c r="B228" t="inlineStr"/>
       <c r="C228" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D228" t="n">
         <v>0</v>
@@ -9811,7 +9801,7 @@
         <v>0</v>
       </c>
       <c r="G228" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H228" t="n">
         <v>1</v>
@@ -9840,7 +9830,7 @@
       </c>
       <c r="B229" t="inlineStr"/>
       <c r="C229" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D229" t="n">
         <v>0</v>
@@ -9852,19 +9842,19 @@
         <v>0</v>
       </c>
       <c r="G229" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H229" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I229" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J229" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K229" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L229" t="n">
         <v>1</v>
@@ -9879,39 +9869,41 @@
           <t>網路設備(如數據機、網路卡、閘道器、路由器、網路電話)</t>
         </is>
       </c>
-      <c r="B230" t="inlineStr"/>
+      <c r="B230" t="n">
+        <v>0</v>
+      </c>
       <c r="C230" t="n">
+        <v>0</v>
+      </c>
+      <c r="D230" t="n">
+        <v>0</v>
+      </c>
+      <c r="E230" t="n">
+        <v>3</v>
+      </c>
+      <c r="F230" t="n">
+        <v>1</v>
+      </c>
+      <c r="G230" t="n">
+        <v>3</v>
+      </c>
+      <c r="H230" t="n">
+        <v>0</v>
+      </c>
+      <c r="I230" t="n">
         <v>2</v>
-      </c>
-      <c r="D230" t="n">
-        <v>0</v>
-      </c>
-      <c r="E230" t="n">
-        <v>0</v>
-      </c>
-      <c r="F230" t="n">
-        <v>3</v>
-      </c>
-      <c r="G230" t="n">
-        <v>1</v>
-      </c>
-      <c r="H230" t="n">
-        <v>3</v>
-      </c>
-      <c r="I230" t="n">
-        <v>0</v>
       </c>
       <c r="J230" t="n">
         <v>2</v>
       </c>
       <c r="K230" t="n">
+        <v>4</v>
+      </c>
+      <c r="L230" t="n">
         <v>2</v>
       </c>
-      <c r="L230" t="n">
-        <v>4</v>
-      </c>
       <c r="M230" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="231">
@@ -9922,7 +9914,7 @@
       </c>
       <c r="B231" t="inlineStr"/>
       <c r="C231" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D231" t="n">
         <v>0</v>
@@ -9934,22 +9926,22 @@
         <v>0</v>
       </c>
       <c r="G231" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H231" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I231" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J231" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K231" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L231" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M231" t="n">
         <v>1</v>
@@ -9961,24 +9953,26 @@
           <t>線上遊戲業</t>
         </is>
       </c>
-      <c r="B232" t="inlineStr"/>
+      <c r="B232" t="n">
+        <v>0</v>
+      </c>
       <c r="C232" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D232" t="n">
         <v>0</v>
       </c>
       <c r="E232" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F232" t="n">
         <v>0</v>
       </c>
       <c r="G232" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H232" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I232" t="n">
         <v>0</v>
@@ -10004,22 +9998,22 @@
       </c>
       <c r="B233" t="inlineStr"/>
       <c r="C233" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D233" t="n">
         <v>0</v>
       </c>
       <c r="E233" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F233" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G233" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H233" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I233" t="n">
         <v>0</v>
@@ -10084,9 +10078,7 @@
           <t>織布</t>
         </is>
       </c>
-      <c r="B235" t="n">
-        <v>0</v>
-      </c>
+      <c r="B235" t="inlineStr"/>
       <c r="C235" t="n">
         <v>0</v>
       </c>
@@ -10100,16 +10092,16 @@
         <v>0</v>
       </c>
       <c r="G235" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H235" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I235" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J235" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K235" t="n">
         <v>0</v>
@@ -10144,19 +10136,19 @@
         <v>0</v>
       </c>
       <c r="H236" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I236" t="n">
         <v>1</v>
       </c>
       <c r="J236" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K236" t="n">
         <v>0</v>
       </c>
       <c r="L236" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M236" t="n">
         <v>1</v>
@@ -10185,13 +10177,13 @@
         <v>0</v>
       </c>
       <c r="H237" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I237" t="n">
         <v>1</v>
       </c>
       <c r="J237" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K237" t="n">
         <v>0</v>
@@ -10211,7 +10203,7 @@
       </c>
       <c r="B238" t="inlineStr"/>
       <c r="C238" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D238" t="n">
         <v>0</v>
@@ -10229,10 +10221,10 @@
         <v>0</v>
       </c>
       <c r="I238" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J238" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K238" t="n">
         <v>0</v>
@@ -10252,16 +10244,16 @@
       </c>
       <c r="B239" t="inlineStr"/>
       <c r="C239" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D239" t="n">
         <v>0</v>
       </c>
       <c r="E239" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F239" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G239" t="n">
         <v>0</v>
@@ -10270,13 +10262,13 @@
         <v>0</v>
       </c>
       <c r="I239" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J239" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K239" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L239" t="n">
         <v>1</v>
@@ -10308,19 +10300,19 @@
         <v>0</v>
       </c>
       <c r="H240" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I240" t="n">
         <v>1</v>
       </c>
       <c r="J240" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K240" t="n">
         <v>0</v>
       </c>
       <c r="L240" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M240" t="n">
         <v>1</v>
@@ -10349,10 +10341,10 @@
         <v>0</v>
       </c>
       <c r="H241" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I241" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J241" t="n">
         <v>0</v>
@@ -10381,31 +10373,31 @@
         <v>0</v>
       </c>
       <c r="E242" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F242" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G242" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H242" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I242" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J242" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K242" t="n">
         <v>0</v>
       </c>
       <c r="L242" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M242" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="243">
@@ -10434,10 +10426,10 @@
         <v>0</v>
       </c>
       <c r="I243" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J243" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K243" t="n">
         <v>0</v>
@@ -10510,10 +10502,10 @@
         <v>0</v>
       </c>
       <c r="G245" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H245" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I245" t="n">
         <v>0</v>
@@ -10551,16 +10543,16 @@
         <v>0</v>
       </c>
       <c r="G246" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H246" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I246" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J246" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K246" t="n">
         <v>0</v>
@@ -10595,10 +10587,10 @@
         <v>0</v>
       </c>
       <c r="H247" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I247" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J247" t="n">
         <v>0</v>
@@ -10607,7 +10599,7 @@
         <v>0</v>
       </c>
       <c r="L247" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M247" t="n">
         <v>1</v>
@@ -10619,9 +10611,7 @@
           <t>藥品代理銷售及通路</t>
         </is>
       </c>
-      <c r="B248" t="n">
-        <v>0</v>
-      </c>
+      <c r="B248" t="inlineStr"/>
       <c r="C248" t="n">
         <v>0</v>
       </c>
@@ -10638,22 +10628,22 @@
         <v>0</v>
       </c>
       <c r="H248" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I248" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J248" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K248" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L248" t="n">
         <v>0</v>
       </c>
       <c r="M248" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="249">
@@ -10726,10 +10716,10 @@
         <v>0</v>
       </c>
       <c r="J250" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K250" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L250" t="n">
         <v>0</v>
@@ -10744,7 +10734,9 @@
           <t>螺絲螺帽</t>
         </is>
       </c>
-      <c r="B251" t="inlineStr"/>
+      <c r="B251" t="n">
+        <v>0</v>
+      </c>
       <c r="C251" t="n">
         <v>0</v>
       </c>
@@ -10799,16 +10791,16 @@
         <v>0</v>
       </c>
       <c r="G252" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H252" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I252" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J252" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K252" t="n">
         <v>0</v>
@@ -10910,7 +10902,7 @@
       </c>
       <c r="B255" t="inlineStr"/>
       <c r="C255" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D255" t="n">
         <v>0</v>
@@ -10963,16 +10955,16 @@
         <v>0</v>
       </c>
       <c r="G256" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H256" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I256" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J256" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K256" t="n">
         <v>0</v>
@@ -11174,10 +11166,10 @@
         <v>0</v>
       </c>
       <c r="I261" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J261" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K261" t="n">
         <v>0</v>
@@ -11197,34 +11189,34 @@
       </c>
       <c r="B262" t="inlineStr"/>
       <c r="C262" t="n">
+        <v>0</v>
+      </c>
+      <c r="D262" t="n">
+        <v>0</v>
+      </c>
+      <c r="E262" t="n">
+        <v>0</v>
+      </c>
+      <c r="F262" t="n">
+        <v>0</v>
+      </c>
+      <c r="G262" t="n">
+        <v>0</v>
+      </c>
+      <c r="H262" t="n">
+        <v>1</v>
+      </c>
+      <c r="I262" t="n">
+        <v>1</v>
+      </c>
+      <c r="J262" t="n">
         <v>2</v>
       </c>
-      <c r="D262" t="n">
-        <v>0</v>
-      </c>
-      <c r="E262" t="n">
-        <v>0</v>
-      </c>
-      <c r="F262" t="n">
-        <v>0</v>
-      </c>
-      <c r="G262" t="n">
-        <v>0</v>
-      </c>
-      <c r="H262" t="n">
-        <v>0</v>
-      </c>
-      <c r="I262" t="n">
-        <v>1</v>
-      </c>
-      <c r="J262" t="n">
-        <v>1</v>
-      </c>
       <c r="K262" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L262" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M262" t="n">
         <v>0</v>
@@ -11241,13 +11233,13 @@
         <v>0</v>
       </c>
       <c r="D263" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E263" t="n">
         <v>1</v>
       </c>
       <c r="F263" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G263" t="n">
         <v>0</v>
@@ -11259,10 +11251,10 @@
         <v>0</v>
       </c>
       <c r="J263" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K263" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L263" t="n">
         <v>0</v>
@@ -11285,25 +11277,25 @@
         <v>0</v>
       </c>
       <c r="E264" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F264" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G264" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H264" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I264" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J264" t="n">
         <v>1</v>
       </c>
       <c r="K264" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L264" t="n">
         <v>0</v>
@@ -11405,10 +11397,10 @@
         <v>0</v>
       </c>
       <c r="D267" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E267" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F267" t="n">
         <v>0</v>
@@ -11499,13 +11491,13 @@
         <v>0</v>
       </c>
       <c r="H269" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I269" t="n">
         <v>1</v>
       </c>
       <c r="J269" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K269" t="n">
         <v>0</v>
@@ -11514,7 +11506,7 @@
         <v>0</v>
       </c>
       <c r="M269" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="270">
@@ -11523,7 +11515,9 @@
           <t>貿易商、代理商、經銷商</t>
         </is>
       </c>
-      <c r="B270" t="inlineStr"/>
+      <c r="B270" t="n">
+        <v>0</v>
+      </c>
       <c r="C270" t="n">
         <v>0</v>
       </c>
@@ -11531,19 +11525,19 @@
         <v>0</v>
       </c>
       <c r="E270" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F270" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G270" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H270" t="n">
         <v>1</v>
       </c>
       <c r="I270" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J270" t="n">
         <v>0</v>
@@ -11555,7 +11549,7 @@
         <v>0</v>
       </c>
       <c r="M270" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="271">
@@ -11607,7 +11601,7 @@
       </c>
       <c r="B272" t="inlineStr"/>
       <c r="C272" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D272" t="n">
         <v>0</v>
@@ -11619,19 +11613,19 @@
         <v>0</v>
       </c>
       <c r="G272" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H272" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I272" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J272" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K272" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L272" t="n">
         <v>1</v>
@@ -11660,16 +11654,16 @@
         <v>0</v>
       </c>
       <c r="G273" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H273" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I273" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J273" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K273" t="n">
         <v>0</v>
@@ -11689,7 +11683,7 @@
       </c>
       <c r="B274" t="inlineStr"/>
       <c r="C274" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D274" t="n">
         <v>0</v>
@@ -11701,19 +11695,19 @@
         <v>0</v>
       </c>
       <c r="G274" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H274" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I274" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J274" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K274" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L274" t="n">
         <v>1</v>
@@ -11742,19 +11736,19 @@
         <v>0</v>
       </c>
       <c r="G275" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H275" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I275" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J275" t="n">
         <v>1</v>
       </c>
       <c r="K275" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L275" t="n">
         <v>0</v>
@@ -11771,7 +11765,7 @@
       </c>
       <c r="B276" t="inlineStr"/>
       <c r="C276" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D276" t="n">
         <v>0</v>
@@ -11783,19 +11777,19 @@
         <v>0</v>
       </c>
       <c r="G276" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H276" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I276" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J276" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K276" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L276" t="n">
         <v>1</v>
@@ -11865,22 +11859,22 @@
         <v>0</v>
       </c>
       <c r="G278" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H278" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I278" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J278" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K278" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L278" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M278" t="n">
         <v>0</v>
@@ -11915,10 +11909,10 @@
         <v>0</v>
       </c>
       <c r="J279" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K279" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L279" t="n">
         <v>0</v>
@@ -11976,7 +11970,7 @@
       </c>
       <c r="B281" t="inlineStr"/>
       <c r="C281" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D281" t="n">
         <v>0</v>
@@ -11988,19 +11982,19 @@
         <v>0</v>
       </c>
       <c r="G281" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H281" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I281" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J281" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K281" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L281" t="n">
         <v>1</v>
@@ -12035,10 +12029,10 @@
         <v>0</v>
       </c>
       <c r="I282" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J282" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K282" t="n">
         <v>0</v>
@@ -12234,22 +12228,22 @@
         <v>0</v>
       </c>
       <c r="G287" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H287" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I287" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J287" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K287" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L287" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M287" t="n">
         <v>0</v>
@@ -12287,10 +12281,10 @@
         <v>0</v>
       </c>
       <c r="K288" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L288" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M288" t="n">
         <v>0</v>
@@ -12310,10 +12304,10 @@
         <v>0</v>
       </c>
       <c r="E289" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F289" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G289" t="n">
         <v>0</v>
@@ -12530,16 +12524,16 @@
         <v>0</v>
       </c>
       <c r="J294" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K294" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L294" t="n">
         <v>0</v>
       </c>
       <c r="M294" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="295">
@@ -12556,10 +12550,10 @@
         <v>0</v>
       </c>
       <c r="E295" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F295" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G295" t="n">
         <v>0</v>
@@ -12606,19 +12600,19 @@
         <v>0</v>
       </c>
       <c r="H296" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I296" t="n">
         <v>1</v>
       </c>
       <c r="J296" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K296" t="n">
         <v>0</v>
       </c>
       <c r="L296" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M296" t="n">
         <v>1</v>
@@ -12659,10 +12653,10 @@
         <v>0</v>
       </c>
       <c r="L297" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M297" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="298">
@@ -12688,13 +12682,13 @@
         <v>0</v>
       </c>
       <c r="H298" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I298" t="n">
         <v>1</v>
       </c>
       <c r="J298" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K298" t="n">
         <v>0</v>
@@ -12808,16 +12802,16 @@
         <v>0</v>
       </c>
       <c r="G301" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H301" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I301" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J301" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K301" t="n">
         <v>0</v>
@@ -12837,31 +12831,31 @@
       </c>
       <c r="B302" t="inlineStr"/>
       <c r="C302" t="n">
+        <v>0</v>
+      </c>
+      <c r="D302" t="n">
+        <v>0</v>
+      </c>
+      <c r="E302" t="n">
+        <v>1</v>
+      </c>
+      <c r="F302" t="n">
+        <v>0</v>
+      </c>
+      <c r="G302" t="n">
         <v>2</v>
-      </c>
-      <c r="D302" t="n">
-        <v>0</v>
-      </c>
-      <c r="E302" t="n">
-        <v>0</v>
-      </c>
-      <c r="F302" t="n">
-        <v>1</v>
-      </c>
-      <c r="G302" t="n">
-        <v>0</v>
       </c>
       <c r="H302" t="n">
         <v>2</v>
       </c>
       <c r="I302" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J302" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K302" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L302" t="n">
         <v>1</v>
@@ -12878,25 +12872,25 @@
       </c>
       <c r="B303" t="inlineStr"/>
       <c r="C303" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D303" t="n">
         <v>0</v>
       </c>
       <c r="E303" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F303" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G303" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H303" t="n">
         <v>1</v>
       </c>
       <c r="I303" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J303" t="n">
         <v>0</v>
@@ -12908,7 +12902,7 @@
         <v>0</v>
       </c>
       <c r="M303" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="304">
@@ -13048,10 +13042,10 @@
         <v>0</v>
       </c>
       <c r="E307" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F307" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G307" t="n">
         <v>0</v>
@@ -13063,10 +13057,10 @@
         <v>0</v>
       </c>
       <c r="J307" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K307" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L307" t="n">
         <v>0</v>
@@ -13089,10 +13083,10 @@
         <v>0</v>
       </c>
       <c r="E308" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F308" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G308" t="n">
         <v>0</v>
@@ -13101,13 +13095,13 @@
         <v>0</v>
       </c>
       <c r="I308" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J308" t="n">
         <v>1</v>
       </c>
       <c r="K308" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L308" t="n">
         <v>0</v>
@@ -13168,13 +13162,13 @@
         <v>0</v>
       </c>
       <c r="D310" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E310" t="n">
         <v>1</v>
       </c>
       <c r="F310" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G310" t="n">
         <v>0</v>
@@ -13209,10 +13203,10 @@
         <v>0</v>
       </c>
       <c r="D311" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E311" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F311" t="n">
         <v>0</v>
@@ -13268,10 +13262,10 @@
         <v>0</v>
       </c>
       <c r="J312" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K312" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L312" t="n">
         <v>0</v>
@@ -13294,25 +13288,25 @@
         <v>0</v>
       </c>
       <c r="E313" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F313" t="n">
+        <v>1</v>
+      </c>
+      <c r="G313" t="n">
+        <v>0</v>
+      </c>
+      <c r="H313" t="n">
         <v>2</v>
       </c>
-      <c r="G313" t="n">
-        <v>1</v>
-      </c>
-      <c r="H313" t="n">
-        <v>0</v>
-      </c>
       <c r="I313" t="n">
+        <v>0</v>
+      </c>
+      <c r="J313" t="n">
         <v>2</v>
       </c>
-      <c r="J313" t="n">
-        <v>0</v>
-      </c>
       <c r="K313" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L313" t="n">
         <v>0</v>
@@ -13329,31 +13323,31 @@
       </c>
       <c r="B314" t="inlineStr"/>
       <c r="C314" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D314" t="n">
         <v>0</v>
       </c>
       <c r="E314" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F314" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G314" t="n">
         <v>0</v>
       </c>
       <c r="H314" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I314" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J314" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K314" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L314" t="n">
         <v>0</v>
@@ -13385,10 +13379,10 @@
         <v>0</v>
       </c>
       <c r="H315" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I315" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J315" t="n">
         <v>0</v>
@@ -13423,10 +13417,10 @@
         <v>0</v>
       </c>
       <c r="G316" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H316" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I316" t="n">
         <v>0</v>
@@ -13470,10 +13464,10 @@
         <v>0</v>
       </c>
       <c r="I317" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J317" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K317" t="n">
         <v>0</v>
@@ -13482,7 +13476,7 @@
         <v>0</v>
       </c>
       <c r="M317" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="318">
@@ -13493,7 +13487,7 @@
       </c>
       <c r="B318" t="inlineStr"/>
       <c r="C318" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D318" t="n">
         <v>0</v>
@@ -13511,19 +13505,19 @@
         <v>0</v>
       </c>
       <c r="I318" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J318" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K318" t="n">
         <v>0</v>
       </c>
       <c r="L318" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M318" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="319">
@@ -13716,10 +13710,10 @@
         <v>0</v>
       </c>
       <c r="I323" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J323" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K323" t="n">
         <v>0</v>
@@ -13763,10 +13757,10 @@
         <v>0</v>
       </c>
       <c r="K324" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L324" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M324" t="n">
         <v>0</v>
@@ -13786,10 +13780,10 @@
         <v>0</v>
       </c>
       <c r="E325" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F325" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G325" t="n">
         <v>0</v>
@@ -13801,10 +13795,10 @@
         <v>0</v>
       </c>
       <c r="J325" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K325" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L325" t="n">
         <v>0</v>
@@ -13827,31 +13821,31 @@
         <v>0</v>
       </c>
       <c r="E326" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F326" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G326" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H326" t="n">
+        <v>4</v>
+      </c>
+      <c r="I326" t="n">
+        <v>0</v>
+      </c>
+      <c r="J326" t="n">
+        <v>3</v>
+      </c>
+      <c r="K326" t="n">
+        <v>1</v>
+      </c>
+      <c r="L326" t="n">
+        <v>0</v>
+      </c>
+      <c r="M326" t="n">
         <v>2</v>
-      </c>
-      <c r="I326" t="n">
-        <v>4</v>
-      </c>
-      <c r="J326" t="n">
-        <v>0</v>
-      </c>
-      <c r="K326" t="n">
-        <v>3</v>
-      </c>
-      <c r="L326" t="n">
-        <v>1</v>
-      </c>
-      <c r="M326" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="327">
@@ -13942,18 +13936,20 @@
           <t>鋰電池材料</t>
         </is>
       </c>
-      <c r="B329" t="inlineStr"/>
+      <c r="B329" t="n">
+        <v>0</v>
+      </c>
       <c r="C329" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D329" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E329" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F329" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G329" t="n">
         <v>0</v>
@@ -14149,7 +14145,7 @@
       </c>
       <c r="B334" t="inlineStr"/>
       <c r="C334" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D334" t="n">
         <v>0</v>
@@ -14287,22 +14283,22 @@
         <v>0</v>
       </c>
       <c r="H337" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I337" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J337" t="n">
         <v>0</v>
       </c>
       <c r="K337" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L337" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M337" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="338">
@@ -14334,10 +14330,10 @@
         <v>0</v>
       </c>
       <c r="J338" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K338" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L338" t="n">
         <v>0</v>
@@ -14354,7 +14350,7 @@
       </c>
       <c r="B339" t="inlineStr"/>
       <c r="C339" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D339" t="n">
         <v>0</v>
@@ -14366,22 +14362,22 @@
         <v>0</v>
       </c>
       <c r="G339" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H339" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I339" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J339" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K339" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L339" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M339" t="n">
         <v>1</v>
@@ -14407,19 +14403,19 @@
         <v>0</v>
       </c>
       <c r="G340" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H340" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I340" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J340" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K340" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L340" t="n">
         <v>0</v>
@@ -14442,25 +14438,25 @@
         <v>0</v>
       </c>
       <c r="E341" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F341" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G341" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H341" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I341" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J341" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K341" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L341" t="n">
         <v>0</v>
@@ -14477,22 +14473,22 @@
       </c>
       <c r="B342" t="inlineStr"/>
       <c r="C342" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D342" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E342" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F342" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G342" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H342" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I342" t="n">
         <v>0</v>
@@ -14504,10 +14500,10 @@
         <v>0</v>
       </c>
       <c r="L342" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M342" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="343">
@@ -14524,19 +14520,19 @@
         <v>0</v>
       </c>
       <c r="E343" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F343" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G343" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H343" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I343" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J343" t="n">
         <v>0</v>
@@ -14548,7 +14544,7 @@
         <v>0</v>
       </c>
       <c r="M343" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="344">
@@ -14598,20 +14594,18 @@
           <t>電力系統</t>
         </is>
       </c>
-      <c r="B345" t="n">
-        <v>0</v>
-      </c>
+      <c r="B345" t="inlineStr"/>
       <c r="C345" t="n">
         <v>0</v>
       </c>
       <c r="D345" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E345" t="n">
         <v>1</v>
       </c>
       <c r="F345" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G345" t="n">
         <v>0</v>
@@ -14646,13 +14640,13 @@
         <v>0</v>
       </c>
       <c r="D346" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E346" t="n">
         <v>1</v>
       </c>
       <c r="F346" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G346" t="n">
         <v>0</v>
@@ -14661,7 +14655,7 @@
         <v>0</v>
       </c>
       <c r="I346" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J346" t="n">
         <v>1</v>
@@ -14670,7 +14664,7 @@
         <v>1</v>
       </c>
       <c r="L346" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M346" t="n">
         <v>0</v>
@@ -14702,10 +14696,10 @@
         <v>0</v>
       </c>
       <c r="I347" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J347" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K347" t="n">
         <v>0</v>
@@ -14731,10 +14725,10 @@
         <v>0</v>
       </c>
       <c r="E348" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F348" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G348" t="n">
         <v>0</v>
@@ -14743,10 +14737,10 @@
         <v>0</v>
       </c>
       <c r="I348" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J348" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K348" t="n">
         <v>0</v>
@@ -14772,10 +14766,10 @@
         <v>0</v>
       </c>
       <c r="E349" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F349" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G349" t="n">
         <v>0</v>
@@ -14848,25 +14842,25 @@
       </c>
       <c r="B351" t="inlineStr"/>
       <c r="C351" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D351" t="n">
         <v>0</v>
       </c>
       <c r="E351" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F351" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G351" t="n">
         <v>0</v>
       </c>
       <c r="H351" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I351" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J351" t="n">
         <v>0</v>
@@ -14889,34 +14883,34 @@
       </c>
       <c r="B352" t="inlineStr"/>
       <c r="C352" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D352" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E352" t="n">
         <v>3</v>
       </c>
       <c r="F352" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G352" t="n">
         <v>2</v>
       </c>
       <c r="H352" t="n">
+        <v>1</v>
+      </c>
+      <c r="I352" t="n">
+        <v>0</v>
+      </c>
+      <c r="J352" t="n">
+        <v>3</v>
+      </c>
+      <c r="K352" t="n">
         <v>2</v>
       </c>
-      <c r="I352" t="n">
-        <v>1</v>
-      </c>
-      <c r="J352" t="n">
-        <v>0</v>
-      </c>
-      <c r="K352" t="n">
-        <v>3</v>
-      </c>
       <c r="L352" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M352" t="n">
         <v>0</v>
@@ -14933,10 +14927,10 @@
         <v>0</v>
       </c>
       <c r="D353" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E353" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F353" t="n">
         <v>0</v>
@@ -14954,10 +14948,10 @@
         <v>0</v>
       </c>
       <c r="K353" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L353" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M353" t="n">
         <v>0</v>
@@ -14974,34 +14968,34 @@
         <v>0</v>
       </c>
       <c r="D354" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E354" t="n">
+        <v>1</v>
+      </c>
+      <c r="F354" t="n">
+        <v>0</v>
+      </c>
+      <c r="G354" t="n">
+        <v>0</v>
+      </c>
+      <c r="H354" t="n">
+        <v>0</v>
+      </c>
+      <c r="I354" t="n">
+        <v>0</v>
+      </c>
+      <c r="J354" t="n">
         <v>2</v>
       </c>
-      <c r="F354" t="n">
-        <v>1</v>
-      </c>
-      <c r="G354" t="n">
-        <v>0</v>
-      </c>
-      <c r="H354" t="n">
-        <v>0</v>
-      </c>
-      <c r="I354" t="n">
-        <v>0</v>
-      </c>
-      <c r="J354" t="n">
-        <v>0</v>
-      </c>
       <c r="K354" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L354" t="n">
         <v>0</v>
       </c>
       <c r="M354" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="355">
@@ -15033,10 +15027,10 @@
         <v>0</v>
       </c>
       <c r="J355" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K355" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L355" t="n">
         <v>0</v>
@@ -15051,9 +15045,7 @@
           <t>電控元件</t>
         </is>
       </c>
-      <c r="B356" t="n">
-        <v>0</v>
-      </c>
+      <c r="B356" t="inlineStr"/>
       <c r="C356" t="n">
         <v>0</v>
       </c>
@@ -15061,10 +15053,10 @@
         <v>0</v>
       </c>
       <c r="E356" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F356" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G356" t="n">
         <v>0</v>
@@ -15076,10 +15068,10 @@
         <v>0</v>
       </c>
       <c r="J356" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K356" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L356" t="n">
         <v>0</v>
@@ -15102,10 +15094,10 @@
         <v>0</v>
       </c>
       <c r="E357" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F357" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G357" t="n">
         <v>0</v>
@@ -15114,16 +15106,16 @@
         <v>0</v>
       </c>
       <c r="I357" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J357" t="n">
         <v>1</v>
       </c>
       <c r="K357" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L357" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M357" t="n">
         <v>0</v>
@@ -15137,16 +15129,16 @@
       </c>
       <c r="B358" t="inlineStr"/>
       <c r="C358" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D358" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E358" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F358" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G358" t="n">
         <v>0</v>
@@ -15155,16 +15147,16 @@
         <v>0</v>
       </c>
       <c r="I358" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J358" t="n">
         <v>1</v>
       </c>
       <c r="K358" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L358" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M358" t="n">
         <v>0</v>
@@ -15178,16 +15170,16 @@
       </c>
       <c r="B359" t="inlineStr"/>
       <c r="C359" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D359" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E359" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F359" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G359" t="n">
         <v>0</v>
@@ -15222,22 +15214,22 @@
         <v>0</v>
       </c>
       <c r="D360" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E360" t="n">
         <v>1</v>
       </c>
       <c r="F360" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G360" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H360" t="n">
         <v>2</v>
       </c>
       <c r="I360" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J360" t="n">
         <v>1</v>
@@ -15246,7 +15238,7 @@
         <v>1</v>
       </c>
       <c r="L360" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M360" t="n">
         <v>0</v>
@@ -15263,10 +15255,10 @@
         <v>0</v>
       </c>
       <c r="D361" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E361" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F361" t="n">
         <v>0</v>
@@ -15383,16 +15375,16 @@
       </c>
       <c r="B364" t="inlineStr"/>
       <c r="C364" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D364" t="n">
         <v>0</v>
       </c>
       <c r="E364" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F364" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G364" t="n">
         <v>0</v>
@@ -15407,7 +15399,7 @@
         <v>0</v>
       </c>
       <c r="K364" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L364" t="n">
         <v>1</v>
@@ -15430,28 +15422,28 @@
         <v>0</v>
       </c>
       <c r="E365" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F365" t="n">
+        <v>0</v>
+      </c>
+      <c r="G365" t="n">
+        <v>0</v>
+      </c>
+      <c r="H365" t="n">
+        <v>1</v>
+      </c>
+      <c r="I365" t="n">
+        <v>1</v>
+      </c>
+      <c r="J365" t="n">
         <v>2</v>
       </c>
-      <c r="G365" t="n">
-        <v>0</v>
-      </c>
-      <c r="H365" t="n">
-        <v>0</v>
-      </c>
-      <c r="I365" t="n">
-        <v>1</v>
-      </c>
-      <c r="J365" t="n">
-        <v>1</v>
-      </c>
       <c r="K365" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L365" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M365" t="n">
         <v>0</v>
@@ -15550,13 +15542,13 @@
         <v>0</v>
       </c>
       <c r="D368" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E368" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F368" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G368" t="n">
         <v>0</v>
@@ -15635,10 +15627,10 @@
         <v>0</v>
       </c>
       <c r="E370" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F370" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G370" t="n">
         <v>0</v>
@@ -15752,28 +15744,28 @@
       </c>
       <c r="B373" t="inlineStr"/>
       <c r="C373" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D373" t="n">
         <v>0</v>
       </c>
       <c r="E373" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F373" t="n">
+        <v>1</v>
+      </c>
+      <c r="G373" t="n">
+        <v>1</v>
+      </c>
+      <c r="H373" t="n">
+        <v>1</v>
+      </c>
+      <c r="I373" t="n">
         <v>2</v>
       </c>
-      <c r="G373" t="n">
-        <v>1</v>
-      </c>
-      <c r="H373" t="n">
-        <v>1</v>
-      </c>
-      <c r="I373" t="n">
-        <v>1</v>
-      </c>
       <c r="J373" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K373" t="n">
         <v>1</v>
@@ -15878,28 +15870,28 @@
         <v>0</v>
       </c>
       <c r="D376" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E376" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F376" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G376" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H376" t="n">
+        <v>0</v>
+      </c>
+      <c r="I376" t="n">
         <v>2</v>
-      </c>
-      <c r="I376" t="n">
-        <v>0</v>
       </c>
       <c r="J376" t="n">
         <v>2</v>
       </c>
       <c r="K376" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L376" t="n">
         <v>0</v>
@@ -15969,22 +15961,22 @@
         <v>0</v>
       </c>
       <c r="G378" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H378" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I378" t="n">
         <v>0</v>
       </c>
       <c r="J378" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K378" t="n">
         <v>1</v>
       </c>
       <c r="L378" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M378" t="n">
         <v>0</v>
@@ -16013,13 +16005,13 @@
         <v>0</v>
       </c>
       <c r="H379" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I379" t="n">
         <v>1</v>
       </c>
       <c r="J379" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K379" t="n">
         <v>0</v>
@@ -16098,10 +16090,10 @@
         <v>0</v>
       </c>
       <c r="I381" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J381" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K381" t="n">
         <v>0</v>
@@ -16162,7 +16154,7 @@
       </c>
       <c r="B383" t="inlineStr"/>
       <c r="C383" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D383" t="n">
         <v>0</v>
@@ -16171,19 +16163,19 @@
         <v>0</v>
       </c>
       <c r="F383" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G383" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H383" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I383" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J383" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K383" t="n">
         <v>0</v>
@@ -16192,7 +16184,7 @@
         <v>0</v>
       </c>
       <c r="M383" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="384">
@@ -16247,13 +16239,13 @@
         <v>0</v>
       </c>
       <c r="D385" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E385" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F385" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G385" t="n">
         <v>0</v>

--- a/Result/analyze_3.xlsx
+++ b/Result/analyze_3.xlsx
@@ -441,57 +441,57 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
     </row>
@@ -533,7 +533,7 @@
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -624,7 +624,9 @@
           <t>HMI</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr"/>
+      <c r="B5" t="n">
+        <v>0</v>
+      </c>
       <c r="C5" t="n">
         <v>0</v>
       </c>
@@ -670,13 +672,13 @@
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G6" t="n">
         <v>2</v>
@@ -685,19 +687,19 @@
         <v>2</v>
       </c>
       <c r="I6" t="n">
+        <v>3</v>
+      </c>
+      <c r="J6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K6" t="n">
         <v>2</v>
       </c>
-      <c r="J6" t="n">
+      <c r="L6" t="n">
+        <v>1</v>
+      </c>
+      <c r="M6" t="n">
         <v>3</v>
-      </c>
-      <c r="K6" t="n">
-        <v>1</v>
-      </c>
-      <c r="L6" t="n">
-        <v>2</v>
-      </c>
-      <c r="M6" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -711,34 +713,34 @@
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="n">
         <v>2</v>
       </c>
-      <c r="F7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" t="n">
-        <v>0</v>
-      </c>
       <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
         <v>2</v>
       </c>
-      <c r="I7" t="n">
-        <v>0</v>
-      </c>
       <c r="J7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K7" t="n">
         <v>1</v>
       </c>
       <c r="L7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -752,34 +754,34 @@
         <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="n">
         <v>2</v>
       </c>
-      <c r="F8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" t="n">
-        <v>0</v>
-      </c>
       <c r="H8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I8" t="n">
+        <v>1</v>
+      </c>
+      <c r="J8" t="n">
         <v>2</v>
       </c>
-      <c r="I8" t="n">
-        <v>1</v>
-      </c>
-      <c r="J8" t="n">
-        <v>1</v>
-      </c>
       <c r="K8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -792,37 +794,37 @@
         <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F9" t="n">
         <v>1</v>
       </c>
       <c r="G9" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H9" t="n">
         <v>4</v>
       </c>
       <c r="I9" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L9" t="n">
         <v>2</v>
       </c>
       <c r="M9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10">
@@ -836,34 +838,34 @@
         <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E10" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J10" t="n">
         <v>2</v>
       </c>
       <c r="K10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -877,28 +879,28 @@
         <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -1129,10 +1131,10 @@
         <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -1287,34 +1289,34 @@
         <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G21" t="n">
+        <v>1</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" t="n">
         <v>2</v>
       </c>
-      <c r="H21" t="n">
-        <v>1</v>
-      </c>
-      <c r="I21" t="n">
-        <v>0</v>
-      </c>
       <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
+        <v>1</v>
+      </c>
+      <c r="M21" t="n">
         <v>2</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-      <c r="M21" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -1369,19 +1371,19 @@
         <v>0</v>
       </c>
       <c r="D23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I23" t="n">
         <v>0</v>
@@ -1393,10 +1395,10 @@
         <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -1410,34 +1412,34 @@
         <v>0</v>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E24" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" t="n">
+        <v>1</v>
+      </c>
+      <c r="G24" t="n">
+        <v>3</v>
+      </c>
+      <c r="H24" t="n">
         <v>2</v>
-      </c>
-      <c r="F24" t="n">
-        <v>0</v>
-      </c>
-      <c r="G24" t="n">
-        <v>1</v>
-      </c>
-      <c r="H24" t="n">
-        <v>3</v>
       </c>
       <c r="I24" t="n">
         <v>2</v>
       </c>
       <c r="J24" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="25">
@@ -1460,13 +1462,13 @@
         <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H25" t="n">
         <v>1</v>
       </c>
       <c r="I25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -1545,19 +1547,19 @@
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
         <v>0</v>
@@ -1671,10 +1673,10 @@
         <v>0</v>
       </c>
       <c r="I30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K30" t="n">
         <v>0</v>
@@ -1709,13 +1711,13 @@
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I31" t="n">
         <v>1</v>
       </c>
       <c r="J31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K31" t="n">
         <v>0</v>
@@ -1733,15 +1735,17 @@
           <t>休閒車業</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr"/>
+      <c r="B32" t="n">
+        <v>0</v>
+      </c>
       <c r="C32" t="n">
         <v>0</v>
       </c>
       <c r="D32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F32" t="n">
         <v>0</v>
@@ -1750,10 +1754,10 @@
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I32" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -1791,10 +1795,10 @@
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -1867,7 +1871,7 @@
         <v>0</v>
       </c>
       <c r="F35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G35" t="n">
         <v>1</v>
@@ -1876,10 +1880,10 @@
         <v>1</v>
       </c>
       <c r="I35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K35" t="n">
         <v>0</v>
@@ -1888,7 +1892,7 @@
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="36">
@@ -2031,10 +2035,10 @@
         <v>0</v>
       </c>
       <c r="F39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H39" t="n">
         <v>0</v>
@@ -2107,10 +2111,10 @@
         <v>0</v>
       </c>
       <c r="D41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F41" t="n">
         <v>0</v>
@@ -2148,25 +2152,25 @@
         <v>0</v>
       </c>
       <c r="D42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F42" t="n">
         <v>0</v>
       </c>
       <c r="G42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J42" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K42" t="n">
         <v>0</v>
@@ -2198,10 +2202,10 @@
         <v>0</v>
       </c>
       <c r="G43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I43" t="n">
         <v>0</v>
@@ -2227,19 +2231,19 @@
       </c>
       <c r="B44" t="inlineStr"/>
       <c r="C44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E44" t="n">
         <v>0</v>
       </c>
       <c r="F44" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G44" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H44" t="n">
         <v>0</v>
@@ -2251,10 +2255,10 @@
         <v>0</v>
       </c>
       <c r="K44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
         <v>0</v>
@@ -2280,22 +2284,22 @@
         <v>0</v>
       </c>
       <c r="G45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H45" t="n">
         <v>1</v>
       </c>
       <c r="I45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
       </c>
       <c r="K45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L45" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M45" t="n">
         <v>2</v>
@@ -2362,10 +2366,10 @@
         <v>0</v>
       </c>
       <c r="G47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I47" t="n">
         <v>0</v>
@@ -2374,13 +2378,13 @@
         <v>0</v>
       </c>
       <c r="K47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L47" t="n">
         <v>1</v>
       </c>
       <c r="M47" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="48">
@@ -2432,19 +2436,19 @@
       </c>
       <c r="B49" t="inlineStr"/>
       <c r="C49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D49" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E49" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F49" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G49" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H49" t="n">
         <v>3</v>
@@ -2456,13 +2460,13 @@
         <v>3</v>
       </c>
       <c r="K49" t="n">
+        <v>2</v>
+      </c>
+      <c r="L49" t="n">
+        <v>1</v>
+      </c>
+      <c r="M49" t="n">
         <v>3</v>
-      </c>
-      <c r="L49" t="n">
-        <v>2</v>
-      </c>
-      <c r="M49" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="50">
@@ -2519,34 +2523,34 @@
         <v>1</v>
       </c>
       <c r="D51" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E51" t="n">
+        <v>1</v>
+      </c>
+      <c r="F51" t="n">
         <v>3</v>
       </c>
-      <c r="F51" t="n">
-        <v>1</v>
-      </c>
       <c r="G51" t="n">
+        <v>4</v>
+      </c>
+      <c r="H51" t="n">
+        <v>6</v>
+      </c>
+      <c r="I51" t="n">
+        <v>1</v>
+      </c>
+      <c r="J51" t="n">
+        <v>0</v>
+      </c>
+      <c r="K51" t="n">
+        <v>0</v>
+      </c>
+      <c r="L51" t="n">
         <v>3</v>
       </c>
-      <c r="H51" t="n">
-        <v>4</v>
-      </c>
-      <c r="I51" t="n">
-        <v>6</v>
-      </c>
-      <c r="J51" t="n">
-        <v>1</v>
-      </c>
-      <c r="K51" t="n">
-        <v>0</v>
-      </c>
-      <c r="L51" t="n">
-        <v>0</v>
-      </c>
       <c r="M51" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="52">
@@ -2601,34 +2605,34 @@
         <v>0</v>
       </c>
       <c r="D53" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E53" t="n">
+        <v>0</v>
+      </c>
+      <c r="F53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G53" t="n">
+        <v>0</v>
+      </c>
+      <c r="H53" t="n">
+        <v>1</v>
+      </c>
+      <c r="I53" t="n">
+        <v>0</v>
+      </c>
+      <c r="J53" t="n">
         <v>2</v>
       </c>
-      <c r="F53" t="n">
-        <v>0</v>
-      </c>
-      <c r="G53" t="n">
-        <v>0</v>
-      </c>
-      <c r="H53" t="n">
-        <v>0</v>
-      </c>
-      <c r="I53" t="n">
-        <v>1</v>
-      </c>
-      <c r="J53" t="n">
-        <v>0</v>
-      </c>
       <c r="K53" t="n">
+        <v>1</v>
+      </c>
+      <c r="L53" t="n">
+        <v>1</v>
+      </c>
+      <c r="M53" t="n">
         <v>2</v>
-      </c>
-      <c r="L53" t="n">
-        <v>1</v>
-      </c>
-      <c r="M53" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="54">
@@ -2642,28 +2646,28 @@
         <v>1</v>
       </c>
       <c r="D54" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E54" t="n">
+        <v>0</v>
+      </c>
+      <c r="F54" t="n">
         <v>4</v>
       </c>
-      <c r="F54" t="n">
-        <v>0</v>
-      </c>
       <c r="G54" t="n">
+        <v>5</v>
+      </c>
+      <c r="H54" t="n">
         <v>4</v>
       </c>
-      <c r="H54" t="n">
-        <v>5</v>
-      </c>
       <c r="I54" t="n">
+        <v>1</v>
+      </c>
+      <c r="J54" t="n">
+        <v>7</v>
+      </c>
+      <c r="K54" t="n">
         <v>4</v>
-      </c>
-      <c r="J54" t="n">
-        <v>1</v>
-      </c>
-      <c r="K54" t="n">
-        <v>7</v>
       </c>
       <c r="L54" t="n">
         <v>4</v>
@@ -2680,7 +2684,7 @@
       </c>
       <c r="B55" t="inlineStr"/>
       <c r="C55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D55" t="n">
         <v>1</v>
@@ -2689,25 +2693,25 @@
         <v>1</v>
       </c>
       <c r="F55" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G55" t="n">
+        <v>1</v>
+      </c>
+      <c r="H55" t="n">
         <v>3</v>
       </c>
-      <c r="H55" t="n">
-        <v>1</v>
-      </c>
       <c r="I55" t="n">
+        <v>2</v>
+      </c>
+      <c r="J55" t="n">
         <v>3</v>
       </c>
-      <c r="J55" t="n">
+      <c r="K55" t="n">
         <v>2</v>
       </c>
-      <c r="K55" t="n">
-        <v>3</v>
-      </c>
       <c r="L55" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M55" t="n">
         <v>1</v>
@@ -2724,13 +2728,13 @@
         <v>0</v>
       </c>
       <c r="D56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G56" t="n">
         <v>1</v>
@@ -2745,7 +2749,7 @@
         <v>1</v>
       </c>
       <c r="K56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L56" t="n">
         <v>0</v>
@@ -2803,10 +2807,10 @@
       </c>
       <c r="B58" t="inlineStr"/>
       <c r="C58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E58" t="n">
         <v>0</v>
@@ -2818,19 +2822,19 @@
         <v>0</v>
       </c>
       <c r="H58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
       </c>
       <c r="K58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M58" t="n">
         <v>0</v>
@@ -2844,13 +2848,13 @@
       </c>
       <c r="B59" t="inlineStr"/>
       <c r="C59" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D59" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E59" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F59" t="n">
         <v>0</v>
@@ -2909,10 +2913,10 @@
         <v>0</v>
       </c>
       <c r="K60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M60" t="n">
         <v>0</v>
@@ -2950,10 +2954,10 @@
         <v>0</v>
       </c>
       <c r="K61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M61" t="n">
         <v>0</v>
@@ -3026,10 +3030,10 @@
         <v>0</v>
       </c>
       <c r="I63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K63" t="n">
         <v>0</v>
@@ -3038,7 +3042,7 @@
         <v>0</v>
       </c>
       <c r="M63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="64">
@@ -3184,10 +3188,10 @@
         <v>0</v>
       </c>
       <c r="G67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I67" t="n">
         <v>0</v>
@@ -3202,7 +3206,7 @@
         <v>0</v>
       </c>
       <c r="M67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="68">
@@ -3211,9 +3215,7 @@
           <t>加工食品</t>
         </is>
       </c>
-      <c r="B68" t="n">
-        <v>0</v>
-      </c>
+      <c r="B68" t="inlineStr"/>
       <c r="C68" t="n">
         <v>0</v>
       </c>
@@ -3277,16 +3279,16 @@
         <v>0</v>
       </c>
       <c r="J69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="70">
@@ -3347,28 +3349,28 @@
         <v>0</v>
       </c>
       <c r="F71" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G71" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H71" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
       </c>
       <c r="K71" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L71" t="n">
         <v>1</v>
       </c>
       <c r="M71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="72">
@@ -3382,34 +3384,34 @@
         <v>0</v>
       </c>
       <c r="D72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G72" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H72" t="n">
+        <v>1</v>
+      </c>
+      <c r="I72" t="n">
+        <v>1</v>
+      </c>
+      <c r="J72" t="n">
+        <v>1</v>
+      </c>
+      <c r="K72" t="n">
+        <v>1</v>
+      </c>
+      <c r="L72" t="n">
         <v>2</v>
       </c>
-      <c r="I72" t="n">
-        <v>1</v>
-      </c>
-      <c r="J72" t="n">
-        <v>1</v>
-      </c>
-      <c r="K72" t="n">
-        <v>1</v>
-      </c>
-      <c r="L72" t="n">
-        <v>1</v>
-      </c>
       <c r="M72" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="73">
@@ -3423,10 +3425,10 @@
         <v>0</v>
       </c>
       <c r="D73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E73" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -3438,19 +3440,19 @@
         <v>0</v>
       </c>
       <c r="I73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J73" t="n">
         <v>1</v>
       </c>
       <c r="K73" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M73" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74">
@@ -3555,13 +3557,13 @@
         <v>0</v>
       </c>
       <c r="G76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H76" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I76" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -3596,10 +3598,10 @@
         <v>0</v>
       </c>
       <c r="G77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H77" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I77" t="n">
         <v>0</v>
@@ -3614,7 +3616,7 @@
         <v>0</v>
       </c>
       <c r="M77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="78">
@@ -3625,28 +3627,28 @@
       </c>
       <c r="B78" t="inlineStr"/>
       <c r="C78" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D78" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E78" t="n">
         <v>0</v>
       </c>
       <c r="F78" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G78" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H78" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I78" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J78" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K78" t="n">
         <v>1</v>
@@ -3655,7 +3657,7 @@
         <v>1</v>
       </c>
       <c r="M78" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="79">
@@ -3762,13 +3764,13 @@
         <v>0</v>
       </c>
       <c r="G81" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H81" t="n">
         <v>1</v>
       </c>
       <c r="I81" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -3835,25 +3837,25 @@
         <v>0</v>
       </c>
       <c r="D83" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E83" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F83" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G83" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H83" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I83" t="n">
         <v>1</v>
       </c>
       <c r="J83" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K83" t="n">
         <v>0</v>
@@ -4040,10 +4042,10 @@
         <v>0</v>
       </c>
       <c r="D88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F88" t="n">
         <v>0</v>
@@ -4081,10 +4083,10 @@
         <v>0</v>
       </c>
       <c r="D89" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F89" t="n">
         <v>0</v>
@@ -4093,10 +4095,10 @@
         <v>0</v>
       </c>
       <c r="H89" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -4105,10 +4107,10 @@
         <v>0</v>
       </c>
       <c r="L89" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="90">
@@ -4187,10 +4189,10 @@
         <v>0</v>
       </c>
       <c r="L91" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M91" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="92">
@@ -4204,34 +4206,34 @@
         <v>1</v>
       </c>
       <c r="D92" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E92" t="n">
+        <v>0</v>
+      </c>
+      <c r="F92" t="n">
+        <v>0</v>
+      </c>
+      <c r="G92" t="n">
+        <v>0</v>
+      </c>
+      <c r="H92" t="n">
+        <v>1</v>
+      </c>
+      <c r="I92" t="n">
+        <v>1</v>
+      </c>
+      <c r="J92" t="n">
         <v>2</v>
       </c>
-      <c r="F92" t="n">
-        <v>0</v>
-      </c>
-      <c r="G92" t="n">
-        <v>0</v>
-      </c>
-      <c r="H92" t="n">
-        <v>0</v>
-      </c>
-      <c r="I92" t="n">
-        <v>1</v>
-      </c>
-      <c r="J92" t="n">
-        <v>1</v>
-      </c>
       <c r="K92" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L92" t="n">
         <v>0</v>
       </c>
       <c r="M92" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="93">
@@ -4298,10 +4300,10 @@
         <v>0</v>
       </c>
       <c r="H94" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I94" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -4322,41 +4324,39 @@
           <t>太陽能發電設備/系統及系統工程</t>
         </is>
       </c>
-      <c r="B95" t="n">
-        <v>0</v>
-      </c>
+      <c r="B95" t="inlineStr"/>
       <c r="C95" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D95" t="n">
         <v>1</v>
       </c>
       <c r="E95" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F95" t="n">
         <v>0</v>
       </c>
       <c r="G95" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H95" t="n">
         <v>2</v>
       </c>
       <c r="I95" t="n">
+        <v>0</v>
+      </c>
+      <c r="J95" t="n">
+        <v>1</v>
+      </c>
+      <c r="K95" t="n">
+        <v>0</v>
+      </c>
+      <c r="L95" t="n">
+        <v>0</v>
+      </c>
+      <c r="M95" t="n">
         <v>2</v>
-      </c>
-      <c r="J95" t="n">
-        <v>0</v>
-      </c>
-      <c r="K95" t="n">
-        <v>1</v>
-      </c>
-      <c r="L95" t="n">
-        <v>0</v>
-      </c>
-      <c r="M95" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="96">
@@ -4370,22 +4370,22 @@
         <v>0</v>
       </c>
       <c r="D96" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E96" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F96" t="n">
         <v>0</v>
       </c>
       <c r="G96" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H96" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I96" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -4435,10 +4435,10 @@
         <v>0</v>
       </c>
       <c r="L97" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M97" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="98">
@@ -4464,19 +4464,19 @@
         <v>0</v>
       </c>
       <c r="H98" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I98" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
       </c>
       <c r="K98" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L98" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M98" t="n">
         <v>0</v>
@@ -4496,19 +4496,19 @@
         <v>0</v>
       </c>
       <c r="E99" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G99" t="n">
         <v>0</v>
       </c>
       <c r="H99" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -4581,16 +4581,16 @@
         <v>0</v>
       </c>
       <c r="F101" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G101" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H101" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I101" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -4602,7 +4602,7 @@
         <v>0</v>
       </c>
       <c r="M101" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="102">
@@ -4616,34 +4616,34 @@
         <v>0</v>
       </c>
       <c r="D102" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E102" t="n">
+        <v>1</v>
+      </c>
+      <c r="F102" t="n">
+        <v>0</v>
+      </c>
+      <c r="G102" t="n">
+        <v>0</v>
+      </c>
+      <c r="H102" t="n">
+        <v>1</v>
+      </c>
+      <c r="I102" t="n">
+        <v>3</v>
+      </c>
+      <c r="J102" t="n">
         <v>2</v>
       </c>
-      <c r="F102" t="n">
-        <v>1</v>
-      </c>
-      <c r="G102" t="n">
-        <v>0</v>
-      </c>
-      <c r="H102" t="n">
-        <v>0</v>
-      </c>
-      <c r="I102" t="n">
-        <v>1</v>
-      </c>
-      <c r="J102" t="n">
-        <v>3</v>
-      </c>
       <c r="K102" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L102" t="n">
         <v>1</v>
       </c>
       <c r="M102" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="103">
@@ -4698,34 +4698,34 @@
         <v>0</v>
       </c>
       <c r="D104" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E104" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F104" t="n">
         <v>0</v>
       </c>
       <c r="G104" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H104" t="n">
         <v>1</v>
       </c>
       <c r="I104" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J104" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K104" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L104" t="n">
+        <v>1</v>
+      </c>
+      <c r="M104" t="n">
         <v>2</v>
-      </c>
-      <c r="M104" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="105">
@@ -4739,19 +4739,19 @@
         <v>0</v>
       </c>
       <c r="D105" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E105" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F105" t="n">
         <v>0</v>
       </c>
       <c r="G105" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H105" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I105" t="n">
         <v>0</v>
@@ -4760,13 +4760,13 @@
         <v>0</v>
       </c>
       <c r="K105" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L105" t="n">
         <v>1</v>
       </c>
       <c r="M105" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="106">
@@ -4780,10 +4780,10 @@
         <v>0</v>
       </c>
       <c r="D106" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E106" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F106" t="n">
         <v>0</v>
@@ -4798,10 +4798,10 @@
         <v>0</v>
       </c>
       <c r="J106" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K106" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L106" t="n">
         <v>0</v>
@@ -4889,7 +4889,7 @@
         <v>0</v>
       </c>
       <c r="M108" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="109">
@@ -4944,10 +4944,10 @@
         <v>0</v>
       </c>
       <c r="D110" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E110" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F110" t="n">
         <v>0</v>
@@ -4993,25 +4993,25 @@
         <v>0</v>
       </c>
       <c r="F111" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G111" t="n">
         <v>1</v>
       </c>
       <c r="H111" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I111" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J111" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K111" t="n">
         <v>1</v>
       </c>
       <c r="L111" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M111" t="n">
         <v>0</v>
@@ -5025,10 +5025,10 @@
       </c>
       <c r="B112" t="inlineStr"/>
       <c r="C112" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D112" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E112" t="n">
         <v>0</v>
@@ -5037,19 +5037,19 @@
         <v>0</v>
       </c>
       <c r="G112" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H112" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I112" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J112" t="n">
         <v>1</v>
       </c>
       <c r="K112" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L112" t="n">
         <v>0</v>
@@ -5066,10 +5066,10 @@
       </c>
       <c r="B113" t="inlineStr"/>
       <c r="C113" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D113" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E113" t="n">
         <v>0</v>
@@ -5105,40 +5105,20 @@
           <t>工藝產業</t>
         </is>
       </c>
-      <c r="B114" t="inlineStr"/>
-      <c r="C114" t="n">
-        <v>0</v>
-      </c>
-      <c r="D114" t="n">
-        <v>0</v>
-      </c>
-      <c r="E114" t="n">
-        <v>0</v>
-      </c>
-      <c r="F114" t="n">
-        <v>0</v>
-      </c>
-      <c r="G114" t="n">
-        <v>1</v>
-      </c>
-      <c r="H114" t="n">
-        <v>0</v>
-      </c>
-      <c r="I114" t="n">
-        <v>0</v>
-      </c>
-      <c r="J114" t="n">
-        <v>0</v>
-      </c>
-      <c r="K114" t="n">
-        <v>0</v>
-      </c>
-      <c r="L114" t="n">
-        <v>0</v>
-      </c>
-      <c r="M114" t="n">
-        <v>0</v>
-      </c>
+      <c r="B114" t="n">
+        <v>0</v>
+      </c>
+      <c r="C114" t="inlineStr"/>
+      <c r="D114" t="inlineStr"/>
+      <c r="E114" t="inlineStr"/>
+      <c r="F114" t="inlineStr"/>
+      <c r="G114" t="inlineStr"/>
+      <c r="H114" t="inlineStr"/>
+      <c r="I114" t="inlineStr"/>
+      <c r="J114" t="inlineStr"/>
+      <c r="K114" t="inlineStr"/>
+      <c r="L114" t="inlineStr"/>
+      <c r="M114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" s="1" t="inlineStr">
@@ -5160,10 +5140,10 @@
         <v>0</v>
       </c>
       <c r="G115" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H115" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I115" t="n">
         <v>0</v>
@@ -5178,7 +5158,7 @@
         <v>0</v>
       </c>
       <c r="M115" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="116">
@@ -5201,10 +5181,10 @@
         <v>0</v>
       </c>
       <c r="G116" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H116" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I116" t="n">
         <v>0</v>
@@ -5219,7 +5199,7 @@
         <v>0</v>
       </c>
       <c r="M116" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="117">
@@ -5356,10 +5336,10 @@
         <v>0</v>
       </c>
       <c r="D120" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E120" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F120" t="n">
         <v>0</v>
@@ -5368,16 +5348,16 @@
         <v>0</v>
       </c>
       <c r="H120" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I120" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J120" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K120" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L120" t="n">
         <v>0</v>
@@ -5392,30 +5372,32 @@
           <t>建設業</t>
         </is>
       </c>
-      <c r="B121" t="inlineStr"/>
+      <c r="B121" t="n">
+        <v>0</v>
+      </c>
       <c r="C121" t="n">
         <v>0</v>
       </c>
       <c r="D121" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E121" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F121" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G121" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H121" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I121" t="n">
         <v>1</v>
       </c>
       <c r="J121" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K121" t="n">
         <v>0</v>
@@ -5556,7 +5538,9 @@
           <t>感測器</t>
         </is>
       </c>
-      <c r="B125" t="inlineStr"/>
+      <c r="B125" t="n">
+        <v>0</v>
+      </c>
       <c r="C125" t="n">
         <v>0</v>
       </c>
@@ -5681,13 +5665,13 @@
       </c>
       <c r="B128" t="inlineStr"/>
       <c r="C128" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D128" t="n">
         <v>1</v>
       </c>
       <c r="E128" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F128" t="n">
         <v>0</v>
@@ -5696,10 +5680,10 @@
         <v>0</v>
       </c>
       <c r="H128" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I128" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J128" t="n">
         <v>1</v>
@@ -5740,10 +5724,10 @@
         <v>0</v>
       </c>
       <c r="I129" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J129" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K129" t="n">
         <v>0</v>
@@ -5752,7 +5736,7 @@
         <v>0</v>
       </c>
       <c r="M129" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="130">
@@ -5804,10 +5788,10 @@
       </c>
       <c r="B131" t="inlineStr"/>
       <c r="C131" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D131" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E131" t="n">
         <v>0</v>
@@ -5872,10 +5856,10 @@
         <v>0</v>
       </c>
       <c r="L132" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M132" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="133">
@@ -6007,7 +5991,9 @@
           <t>控制器</t>
         </is>
       </c>
-      <c r="B136" t="inlineStr"/>
+      <c r="B136" t="n">
+        <v>0</v>
+      </c>
       <c r="C136" t="n">
         <v>0</v>
       </c>
@@ -6039,7 +6025,7 @@
         <v>0</v>
       </c>
       <c r="M136" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="137">
@@ -6071,16 +6057,16 @@
         <v>0</v>
       </c>
       <c r="J137" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K137" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L137" t="n">
         <v>0</v>
       </c>
       <c r="M137" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="138">
@@ -6135,28 +6121,28 @@
         <v>0</v>
       </c>
       <c r="D139" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E139" t="n">
+        <v>0</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0</v>
+      </c>
+      <c r="H139" t="n">
+        <v>1</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0</v>
+      </c>
+      <c r="J139" t="n">
         <v>2</v>
       </c>
-      <c r="F139" t="n">
-        <v>0</v>
-      </c>
-      <c r="G139" t="n">
-        <v>0</v>
-      </c>
-      <c r="H139" t="n">
-        <v>0</v>
-      </c>
-      <c r="I139" t="n">
-        <v>1</v>
-      </c>
-      <c r="J139" t="n">
-        <v>0</v>
-      </c>
       <c r="K139" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L139" t="n">
         <v>0</v>
@@ -6191,7 +6177,7 @@
         <v>1</v>
       </c>
       <c r="I140" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -6203,7 +6189,7 @@
         <v>0</v>
       </c>
       <c r="M140" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="141">
@@ -6226,13 +6212,13 @@
         <v>0</v>
       </c>
       <c r="G141" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H141" t="n">
         <v>1</v>
       </c>
       <c r="I141" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -6267,13 +6253,13 @@
         <v>0</v>
       </c>
       <c r="G142" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H142" t="n">
         <v>1</v>
       </c>
       <c r="I142" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -6346,10 +6332,10 @@
         <v>0</v>
       </c>
       <c r="F144" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G144" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H144" t="n">
         <v>0</v>
@@ -6387,16 +6373,16 @@
         <v>0</v>
       </c>
       <c r="F145" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G145" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H145" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I145" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -6469,16 +6455,16 @@
         <v>0</v>
       </c>
       <c r="F147" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G147" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H147" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I147" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -6499,7 +6485,9 @@
           <t>文化印刷業</t>
         </is>
       </c>
-      <c r="B148" t="inlineStr"/>
+      <c r="B148" t="n">
+        <v>0</v>
+      </c>
       <c r="C148" t="n">
         <v>0</v>
       </c>
@@ -6513,16 +6501,16 @@
         <v>0</v>
       </c>
       <c r="G148" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H148" t="n">
         <v>0</v>
       </c>
       <c r="I148" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J148" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K148" t="n">
         <v>0</v>
@@ -6586,10 +6574,10 @@
         <v>0</v>
       </c>
       <c r="D150" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E150" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F150" t="n">
         <v>0</v>
@@ -6624,10 +6612,10 @@
       </c>
       <c r="B151" t="inlineStr"/>
       <c r="C151" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D151" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E151" t="n">
         <v>0</v>
@@ -6639,10 +6627,10 @@
         <v>0</v>
       </c>
       <c r="H151" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I151" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -6709,28 +6697,28 @@
         <v>0</v>
       </c>
       <c r="D153" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E153" t="n">
+        <v>1</v>
+      </c>
+      <c r="F153" t="n">
+        <v>0</v>
+      </c>
+      <c r="G153" t="n">
+        <v>0</v>
+      </c>
+      <c r="H153" t="n">
+        <v>0</v>
+      </c>
+      <c r="I153" t="n">
+        <v>0</v>
+      </c>
+      <c r="J153" t="n">
         <v>2</v>
       </c>
-      <c r="F153" t="n">
-        <v>1</v>
-      </c>
-      <c r="G153" t="n">
-        <v>0</v>
-      </c>
-      <c r="H153" t="n">
-        <v>0</v>
-      </c>
-      <c r="I153" t="n">
-        <v>0</v>
-      </c>
-      <c r="J153" t="n">
-        <v>0</v>
-      </c>
       <c r="K153" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L153" t="n">
         <v>1</v>
@@ -6745,15 +6733,17 @@
           <t>有線通訊設備(如電話機、傳真機)</t>
         </is>
       </c>
-      <c r="B154" t="inlineStr"/>
+      <c r="B154" t="n">
+        <v>0</v>
+      </c>
       <c r="C154" t="n">
         <v>0</v>
       </c>
       <c r="D154" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E154" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F154" t="n">
         <v>0</v>
@@ -6876,22 +6866,22 @@
         <v>0</v>
       </c>
       <c r="E157" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F157" t="n">
         <v>1</v>
       </c>
       <c r="G157" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H157" t="n">
         <v>0</v>
       </c>
       <c r="I157" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J157" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K157" t="n">
         <v>0</v>
@@ -6914,10 +6904,10 @@
         <v>0</v>
       </c>
       <c r="D158" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E158" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F158" t="n">
         <v>0</v>
@@ -6996,10 +6986,10 @@
         <v>0</v>
       </c>
       <c r="D160" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E160" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F160" t="n">
         <v>0</v>
@@ -7078,25 +7068,25 @@
         <v>0</v>
       </c>
       <c r="D162" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E162" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F162" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G162" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H162" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I162" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J162" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K162" t="n">
         <v>1</v>
@@ -7105,7 +7095,7 @@
         <v>1</v>
       </c>
       <c r="M162" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="163">
@@ -7134,10 +7124,10 @@
         <v>0</v>
       </c>
       <c r="I163" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J163" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K163" t="n">
         <v>0</v>
@@ -7172,13 +7162,13 @@
         <v>0</v>
       </c>
       <c r="H164" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I164" t="n">
         <v>1</v>
       </c>
       <c r="J164" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K164" t="n">
         <v>0</v>
@@ -7196,7 +7186,9 @@
           <t>機殼</t>
         </is>
       </c>
-      <c r="B165" t="inlineStr"/>
+      <c r="B165" t="n">
+        <v>0</v>
+      </c>
       <c r="C165" t="n">
         <v>0</v>
       </c>
@@ -7207,22 +7199,22 @@
         <v>0</v>
       </c>
       <c r="F165" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G165" t="n">
         <v>1</v>
       </c>
       <c r="H165" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I165" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J165" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K165" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L165" t="n">
         <v>0</v>
@@ -7239,13 +7231,13 @@
       </c>
       <c r="B166" t="inlineStr"/>
       <c r="C166" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D166" t="n">
         <v>1</v>
       </c>
       <c r="E166" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F166" t="n">
         <v>0</v>
@@ -7280,10 +7272,10 @@
       </c>
       <c r="B167" t="inlineStr"/>
       <c r="C167" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D167" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E167" t="n">
         <v>0</v>
@@ -7335,10 +7327,10 @@
         <v>0</v>
       </c>
       <c r="G168" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H168" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I168" t="n">
         <v>0</v>
@@ -7499,10 +7491,10 @@
         <v>0</v>
       </c>
       <c r="G172" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H172" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I172" t="n">
         <v>0</v>
@@ -7584,7 +7576,7 @@
         <v>0</v>
       </c>
       <c r="H174" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I174" t="n">
         <v>0</v>
@@ -7599,7 +7591,7 @@
         <v>0</v>
       </c>
       <c r="M174" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="175">
@@ -7625,7 +7617,7 @@
         <v>0</v>
       </c>
       <c r="H175" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I175" t="n">
         <v>0</v>
@@ -7640,7 +7632,7 @@
         <v>0</v>
       </c>
       <c r="M175" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="176">
@@ -7695,10 +7687,10 @@
         <v>0</v>
       </c>
       <c r="D177" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E177" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F177" t="n">
         <v>0</v>
@@ -7710,10 +7702,10 @@
         <v>0</v>
       </c>
       <c r="I177" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J177" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K177" t="n">
         <v>0</v>
@@ -7722,7 +7714,7 @@
         <v>0</v>
       </c>
       <c r="M177" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="178">
@@ -7772,21 +7764,23 @@
           <t>無線通訊設備(如行動電話、衛星定位系統、衛星通訊設備、微波通訊設備、數位機上盒)</t>
         </is>
       </c>
-      <c r="B179" t="inlineStr"/>
+      <c r="B179" t="n">
+        <v>0</v>
+      </c>
       <c r="C179" t="n">
         <v>0</v>
       </c>
       <c r="D179" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E179" t="n">
+        <v>1</v>
+      </c>
+      <c r="F179" t="n">
+        <v>4</v>
+      </c>
+      <c r="G179" t="n">
         <v>2</v>
-      </c>
-      <c r="F179" t="n">
-        <v>1</v>
-      </c>
-      <c r="G179" t="n">
-        <v>4</v>
       </c>
       <c r="H179" t="n">
         <v>2</v>
@@ -7795,16 +7789,16 @@
         <v>2</v>
       </c>
       <c r="J179" t="n">
+        <v>3</v>
+      </c>
+      <c r="K179" t="n">
         <v>2</v>
-      </c>
-      <c r="K179" t="n">
-        <v>3</v>
       </c>
       <c r="L179" t="n">
         <v>2</v>
       </c>
       <c r="M179" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="180">
@@ -7854,20 +7848,18 @@
           <t>燈具/應用</t>
         </is>
       </c>
-      <c r="B181" t="n">
-        <v>0</v>
-      </c>
+      <c r="B181" t="inlineStr"/>
       <c r="C181" t="n">
         <v>0</v>
       </c>
       <c r="D181" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E181" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F181" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G181" t="n">
         <v>1</v>
@@ -7876,19 +7868,19 @@
         <v>1</v>
       </c>
       <c r="I181" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J181" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K181" t="n">
         <v>2</v>
       </c>
       <c r="L181" t="n">
+        <v>1</v>
+      </c>
+      <c r="M181" t="n">
         <v>2</v>
-      </c>
-      <c r="M181" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="182">
@@ -7923,10 +7915,10 @@
         <v>0</v>
       </c>
       <c r="K182" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L182" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M182" t="n">
         <v>0</v>
@@ -7990,19 +7982,19 @@
         <v>0</v>
       </c>
       <c r="F184" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G184" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H184" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I184" t="n">
         <v>1</v>
       </c>
       <c r="J184" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K184" t="n">
         <v>0</v>
@@ -8011,7 +8003,7 @@
         <v>0</v>
       </c>
       <c r="M184" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="185">
@@ -8154,19 +8146,19 @@
         <v>0</v>
       </c>
       <c r="F188" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G188" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H188" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I188" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J188" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K188" t="n">
         <v>1</v>
@@ -8175,7 +8167,7 @@
         <v>1</v>
       </c>
       <c r="M188" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="189">
@@ -8184,17 +8176,15 @@
           <t>特殊照明業</t>
         </is>
       </c>
-      <c r="B189" t="n">
-        <v>0</v>
-      </c>
+      <c r="B189" t="inlineStr"/>
       <c r="C189" t="n">
         <v>0</v>
       </c>
       <c r="D189" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E189" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F189" t="n">
         <v>0</v>
@@ -8314,10 +8304,10 @@
         <v>0</v>
       </c>
       <c r="D192" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E192" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F192" t="n">
         <v>0</v>
@@ -8329,19 +8319,19 @@
         <v>0</v>
       </c>
       <c r="I192" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J192" t="n">
+        <v>1</v>
+      </c>
+      <c r="K192" t="n">
+        <v>0</v>
+      </c>
+      <c r="L192" t="n">
         <v>2</v>
       </c>
-      <c r="K192" t="n">
-        <v>1</v>
-      </c>
-      <c r="L192" t="n">
-        <v>0</v>
-      </c>
       <c r="M192" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="193">
@@ -8396,34 +8386,34 @@
         <v>0</v>
       </c>
       <c r="D194" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E194" t="n">
+        <v>0</v>
+      </c>
+      <c r="F194" t="n">
+        <v>1</v>
+      </c>
+      <c r="G194" t="n">
+        <v>1</v>
+      </c>
+      <c r="H194" t="n">
+        <v>1</v>
+      </c>
+      <c r="I194" t="n">
+        <v>1</v>
+      </c>
+      <c r="J194" t="n">
+        <v>1</v>
+      </c>
+      <c r="K194" t="n">
+        <v>1</v>
+      </c>
+      <c r="L194" t="n">
         <v>2</v>
       </c>
-      <c r="F194" t="n">
-        <v>0</v>
-      </c>
-      <c r="G194" t="n">
-        <v>1</v>
-      </c>
-      <c r="H194" t="n">
-        <v>1</v>
-      </c>
-      <c r="I194" t="n">
-        <v>1</v>
-      </c>
-      <c r="J194" t="n">
-        <v>1</v>
-      </c>
-      <c r="K194" t="n">
-        <v>1</v>
-      </c>
-      <c r="L194" t="n">
-        <v>1</v>
-      </c>
       <c r="M194" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="195">
@@ -8446,7 +8436,7 @@
         <v>0</v>
       </c>
       <c r="G195" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H195" t="n">
         <v>1</v>
@@ -8455,16 +8445,16 @@
         <v>1</v>
       </c>
       <c r="J195" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K195" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L195" t="n">
         <v>1</v>
       </c>
       <c r="M195" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="196">
@@ -8475,37 +8465,37 @@
       </c>
       <c r="B196" t="inlineStr"/>
       <c r="C196" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D196" t="n">
         <v>1</v>
       </c>
       <c r="E196" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F196" t="n">
         <v>0</v>
       </c>
       <c r="G196" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H196" t="n">
+        <v>0</v>
+      </c>
+      <c r="I196" t="n">
+        <v>0</v>
+      </c>
+      <c r="J196" t="n">
+        <v>1</v>
+      </c>
+      <c r="K196" t="n">
+        <v>1</v>
+      </c>
+      <c r="L196" t="n">
+        <v>1</v>
+      </c>
+      <c r="M196" t="n">
         <v>3</v>
-      </c>
-      <c r="I196" t="n">
-        <v>0</v>
-      </c>
-      <c r="J196" t="n">
-        <v>0</v>
-      </c>
-      <c r="K196" t="n">
-        <v>1</v>
-      </c>
-      <c r="L196" t="n">
-        <v>1</v>
-      </c>
-      <c r="M196" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="197">
@@ -8516,37 +8506,37 @@
       </c>
       <c r="B197" t="inlineStr"/>
       <c r="C197" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D197" t="n">
+        <v>8</v>
+      </c>
+      <c r="E197" t="n">
+        <v>0</v>
+      </c>
+      <c r="F197" t="n">
+        <v>5</v>
+      </c>
+      <c r="G197" t="n">
+        <v>10</v>
+      </c>
+      <c r="H197" t="n">
+        <v>4</v>
+      </c>
+      <c r="I197" t="n">
+        <v>1</v>
+      </c>
+      <c r="J197" t="n">
+        <v>14</v>
+      </c>
+      <c r="K197" t="n">
+        <v>6</v>
+      </c>
+      <c r="L197" t="n">
+        <v>2</v>
+      </c>
+      <c r="M197" t="n">
         <v>3</v>
-      </c>
-      <c r="E197" t="n">
-        <v>8</v>
-      </c>
-      <c r="F197" t="n">
-        <v>0</v>
-      </c>
-      <c r="G197" t="n">
-        <v>5</v>
-      </c>
-      <c r="H197" t="n">
-        <v>10</v>
-      </c>
-      <c r="I197" t="n">
-        <v>4</v>
-      </c>
-      <c r="J197" t="n">
-        <v>1</v>
-      </c>
-      <c r="K197" t="n">
-        <v>14</v>
-      </c>
-      <c r="L197" t="n">
-        <v>6</v>
-      </c>
-      <c r="M197" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="198">
@@ -8572,10 +8562,10 @@
         <v>0</v>
       </c>
       <c r="H198" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I198" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J198" t="n">
         <v>0</v>
@@ -8642,10 +8632,10 @@
         <v>0</v>
       </c>
       <c r="D200" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E200" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F200" t="n">
         <v>0</v>
@@ -8780,10 +8770,10 @@
         <v>0</v>
       </c>
       <c r="I203" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J203" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K203" t="n">
         <v>0</v>
@@ -8803,37 +8793,37 @@
       </c>
       <c r="B204" t="inlineStr"/>
       <c r="C204" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D204" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E204" t="n">
         <v>0</v>
       </c>
       <c r="F204" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G204" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H204" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I204" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J204" t="n">
         <v>0</v>
       </c>
       <c r="K204" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L204" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M204" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="205">
@@ -8862,10 +8852,10 @@
         <v>0</v>
       </c>
       <c r="I205" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J205" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K205" t="n">
         <v>0</v>
@@ -8967,37 +8957,37 @@
       </c>
       <c r="B208" t="inlineStr"/>
       <c r="C208" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D208" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="E208" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="F208" t="n">
         <v>0</v>
       </c>
       <c r="G208" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H208" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="I208" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J208" t="n">
+        <v>1</v>
+      </c>
+      <c r="K208" t="n">
         <v>2</v>
       </c>
-      <c r="K208" t="n">
-        <v>1</v>
-      </c>
       <c r="L208" t="n">
+        <v>3</v>
+      </c>
+      <c r="M208" t="n">
         <v>2</v>
-      </c>
-      <c r="M208" t="n">
-        <v>3</v>
       </c>
     </row>
     <row r="209">
@@ -9108,10 +9098,10 @@
         <v>0</v>
       </c>
       <c r="I211" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J211" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K211" t="n">
         <v>0</v>
@@ -9345,19 +9335,19 @@
         <v>0</v>
       </c>
       <c r="F217" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G217" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H217" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I217" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J217" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K217" t="n">
         <v>1</v>
@@ -9366,7 +9356,7 @@
         <v>1</v>
       </c>
       <c r="M217" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="218">
@@ -9380,10 +9370,10 @@
         <v>0</v>
       </c>
       <c r="D218" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E218" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F218" t="n">
         <v>0</v>
@@ -9421,10 +9411,10 @@
         <v>0</v>
       </c>
       <c r="D219" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E219" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F219" t="n">
         <v>0</v>
@@ -9459,37 +9449,37 @@
       </c>
       <c r="B220" t="inlineStr"/>
       <c r="C220" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D220" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E220" t="n">
+        <v>0</v>
+      </c>
+      <c r="F220" t="n">
+        <v>2</v>
+      </c>
+      <c r="G220" t="n">
+        <v>1</v>
+      </c>
+      <c r="H220" t="n">
         <v>3</v>
       </c>
-      <c r="F220" t="n">
-        <v>0</v>
-      </c>
-      <c r="G220" t="n">
-        <v>2</v>
-      </c>
-      <c r="H220" t="n">
-        <v>1</v>
-      </c>
       <c r="I220" t="n">
+        <v>5</v>
+      </c>
+      <c r="J220" t="n">
+        <v>1</v>
+      </c>
+      <c r="K220" t="n">
+        <v>1</v>
+      </c>
+      <c r="L220" t="n">
+        <v>1</v>
+      </c>
+      <c r="M220" t="n">
         <v>3</v>
-      </c>
-      <c r="J220" t="n">
-        <v>5</v>
-      </c>
-      <c r="K220" t="n">
-        <v>1</v>
-      </c>
-      <c r="L220" t="n">
-        <v>1</v>
-      </c>
-      <c r="M220" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="221">
@@ -9498,32 +9488,30 @@
           <t>系統整合服務</t>
         </is>
       </c>
-      <c r="B221" t="n">
-        <v>0</v>
-      </c>
+      <c r="B221" t="inlineStr"/>
       <c r="C221" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D221" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E221" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F221" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G221" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H221" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I221" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J221" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K221" t="n">
         <v>2</v>
@@ -9532,7 +9520,7 @@
         <v>2</v>
       </c>
       <c r="M221" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="222">
@@ -9564,10 +9552,10 @@
         <v>0</v>
       </c>
       <c r="J222" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K222" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L222" t="n">
         <v>0</v>
@@ -9599,10 +9587,10 @@
         <v>0</v>
       </c>
       <c r="H223" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I223" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J223" t="n">
         <v>0</v>
@@ -9637,13 +9625,13 @@
         <v>0</v>
       </c>
       <c r="G224" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H224" t="n">
         <v>1</v>
       </c>
       <c r="I224" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J224" t="n">
         <v>0</v>
@@ -9798,7 +9786,7 @@
         <v>0</v>
       </c>
       <c r="F228" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G228" t="n">
         <v>1</v>
@@ -9839,19 +9827,19 @@
         <v>0</v>
       </c>
       <c r="F229" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G229" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H229" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I229" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J229" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K229" t="n">
         <v>1</v>
@@ -9860,7 +9848,7 @@
         <v>1</v>
       </c>
       <c r="M229" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="230">
@@ -9876,31 +9864,31 @@
         <v>0</v>
       </c>
       <c r="D230" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E230" t="n">
+        <v>1</v>
+      </c>
+      <c r="F230" t="n">
         <v>3</v>
       </c>
-      <c r="F230" t="n">
-        <v>1</v>
-      </c>
       <c r="G230" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H230" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I230" t="n">
         <v>2</v>
       </c>
       <c r="J230" t="n">
+        <v>4</v>
+      </c>
+      <c r="K230" t="n">
         <v>2</v>
       </c>
-      <c r="K230" t="n">
-        <v>4</v>
-      </c>
       <c r="L230" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M230" t="n">
         <v>1</v>
@@ -9923,28 +9911,28 @@
         <v>0</v>
       </c>
       <c r="F231" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G231" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H231" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I231" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J231" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K231" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L231" t="n">
         <v>1</v>
       </c>
       <c r="M231" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="232">
@@ -9953,11 +9941,9 @@
           <t>線上遊戲業</t>
         </is>
       </c>
-      <c r="B232" t="n">
-        <v>0</v>
-      </c>
+      <c r="B232" t="inlineStr"/>
       <c r="C232" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D232" t="n">
         <v>0</v>
@@ -9966,10 +9952,10 @@
         <v>0</v>
       </c>
       <c r="F232" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G232" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H232" t="n">
         <v>0</v>
@@ -9987,7 +9973,7 @@
         <v>0</v>
       </c>
       <c r="M232" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="233">
@@ -10001,16 +9987,16 @@
         <v>0</v>
       </c>
       <c r="D233" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E233" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F233" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G233" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H233" t="n">
         <v>0</v>
@@ -10089,16 +10075,16 @@
         <v>0</v>
       </c>
       <c r="F235" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G235" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H235" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I235" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J235" t="n">
         <v>0</v>
@@ -10133,25 +10119,25 @@
         <v>0</v>
       </c>
       <c r="G236" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H236" t="n">
         <v>1</v>
       </c>
       <c r="I236" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J236" t="n">
         <v>0</v>
       </c>
       <c r="K236" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L236" t="n">
         <v>1</v>
       </c>
       <c r="M236" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="237">
@@ -10174,13 +10160,13 @@
         <v>0</v>
       </c>
       <c r="G237" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H237" t="n">
         <v>1</v>
       </c>
       <c r="I237" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J237" t="n">
         <v>0</v>
@@ -10218,10 +10204,10 @@
         <v>0</v>
       </c>
       <c r="H238" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I238" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J238" t="n">
         <v>0</v>
@@ -10247,10 +10233,10 @@
         <v>0</v>
       </c>
       <c r="D239" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E239" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F239" t="n">
         <v>0</v>
@@ -10259,13 +10245,13 @@
         <v>0</v>
       </c>
       <c r="H239" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I239" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J239" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K239" t="n">
         <v>1</v>
@@ -10274,7 +10260,7 @@
         <v>1</v>
       </c>
       <c r="M239" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="240">
@@ -10297,25 +10283,25 @@
         <v>0</v>
       </c>
       <c r="G240" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H240" t="n">
         <v>1</v>
       </c>
       <c r="I240" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J240" t="n">
         <v>0</v>
       </c>
       <c r="K240" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L240" t="n">
         <v>1</v>
       </c>
       <c r="M240" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="241">
@@ -10338,10 +10324,10 @@
         <v>0</v>
       </c>
       <c r="G241" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H241" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I241" t="n">
         <v>0</v>
@@ -10356,7 +10342,7 @@
         <v>0</v>
       </c>
       <c r="M241" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="242">
@@ -10365,39 +10351,41 @@
           <t>自動化機台</t>
         </is>
       </c>
-      <c r="B242" t="inlineStr"/>
+      <c r="B242" t="n">
+        <v>0</v>
+      </c>
       <c r="C242" t="n">
         <v>0</v>
       </c>
       <c r="D242" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E242" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F242" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G242" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H242" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I242" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J242" t="n">
         <v>0</v>
       </c>
       <c r="K242" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L242" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M242" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="243">
@@ -10423,10 +10411,10 @@
         <v>0</v>
       </c>
       <c r="H243" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I243" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J243" t="n">
         <v>0</v>
@@ -10499,10 +10487,10 @@
         <v>0</v>
       </c>
       <c r="F245" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G245" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H245" t="n">
         <v>0</v>
@@ -10540,16 +10528,16 @@
         <v>0</v>
       </c>
       <c r="F246" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G246" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H246" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I246" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J246" t="n">
         <v>0</v>
@@ -10584,10 +10572,10 @@
         <v>0</v>
       </c>
       <c r="G247" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H247" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I247" t="n">
         <v>0</v>
@@ -10596,7 +10584,7 @@
         <v>0</v>
       </c>
       <c r="K247" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L247" t="n">
         <v>1</v>
@@ -10625,22 +10613,22 @@
         <v>0</v>
       </c>
       <c r="G248" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H248" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I248" t="n">
         <v>0</v>
       </c>
       <c r="J248" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K248" t="n">
         <v>0</v>
       </c>
       <c r="L248" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M248" t="n">
         <v>1</v>
@@ -10713,10 +10701,10 @@
         <v>0</v>
       </c>
       <c r="I250" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J250" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K250" t="n">
         <v>0</v>
@@ -10725,7 +10713,7 @@
         <v>0</v>
       </c>
       <c r="M250" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="251">
@@ -10734,9 +10722,7 @@
           <t>螺絲螺帽</t>
         </is>
       </c>
-      <c r="B251" t="n">
-        <v>0</v>
-      </c>
+      <c r="B251" t="inlineStr"/>
       <c r="C251" t="n">
         <v>0</v>
       </c>
@@ -10788,16 +10774,16 @@
         <v>0</v>
       </c>
       <c r="F252" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G252" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H252" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I252" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J252" t="n">
         <v>0</v>
@@ -10952,16 +10938,16 @@
         <v>0</v>
       </c>
       <c r="F256" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G256" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H256" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I256" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J256" t="n">
         <v>0</v>
@@ -11146,7 +11132,9 @@
           <t>觸控面板</t>
         </is>
       </c>
-      <c r="B261" t="inlineStr"/>
+      <c r="B261" t="n">
+        <v>0</v>
+      </c>
       <c r="C261" t="n">
         <v>0</v>
       </c>
@@ -11163,10 +11151,10 @@
         <v>0</v>
       </c>
       <c r="H261" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I261" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J261" t="n">
         <v>0</v>
@@ -11201,19 +11189,19 @@
         <v>0</v>
       </c>
       <c r="G262" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H262" t="n">
         <v>1</v>
       </c>
       <c r="I262" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J262" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K262" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L262" t="n">
         <v>0</v>
@@ -11230,13 +11218,13 @@
       </c>
       <c r="B263" t="inlineStr"/>
       <c r="C263" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D263" t="n">
         <v>1</v>
       </c>
       <c r="E263" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F263" t="n">
         <v>0</v>
@@ -11248,10 +11236,10 @@
         <v>0</v>
       </c>
       <c r="I263" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J263" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K263" t="n">
         <v>0</v>
@@ -11260,7 +11248,7 @@
         <v>0</v>
       </c>
       <c r="M263" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="264">
@@ -11274,25 +11262,25 @@
         <v>0</v>
       </c>
       <c r="D264" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E264" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F264" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G264" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H264" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I264" t="n">
         <v>1</v>
       </c>
       <c r="J264" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K264" t="n">
         <v>0</v>
@@ -11301,7 +11289,7 @@
         <v>0</v>
       </c>
       <c r="M264" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="265">
@@ -11351,7 +11339,9 @@
           <t>證券業</t>
         </is>
       </c>
-      <c r="B266" t="inlineStr"/>
+      <c r="B266" t="n">
+        <v>0</v>
+      </c>
       <c r="C266" t="n">
         <v>0</v>
       </c>
@@ -11394,10 +11384,10 @@
       </c>
       <c r="B267" t="inlineStr"/>
       <c r="C267" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D267" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E267" t="n">
         <v>0</v>
@@ -11494,7 +11484,7 @@
         <v>1</v>
       </c>
       <c r="I269" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J269" t="n">
         <v>0</v>
@@ -11506,7 +11496,7 @@
         <v>0</v>
       </c>
       <c r="M269" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="270">
@@ -11515,26 +11505,24 @@
           <t>貿易商、代理商、經銷商</t>
         </is>
       </c>
-      <c r="B270" t="n">
-        <v>0</v>
-      </c>
+      <c r="B270" t="inlineStr"/>
       <c r="C270" t="n">
         <v>0</v>
       </c>
       <c r="D270" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E270" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F270" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G270" t="n">
         <v>1</v>
       </c>
       <c r="H270" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I270" t="n">
         <v>0</v>
@@ -11546,7 +11534,7 @@
         <v>0</v>
       </c>
       <c r="L270" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M270" t="n">
         <v>1</v>
@@ -11610,19 +11598,19 @@
         <v>0</v>
       </c>
       <c r="F272" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G272" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H272" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I272" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J272" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K272" t="n">
         <v>1</v>
@@ -11631,7 +11619,7 @@
         <v>1</v>
       </c>
       <c r="M272" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="273">
@@ -11651,16 +11639,16 @@
         <v>0</v>
       </c>
       <c r="F273" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G273" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H273" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I273" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J273" t="n">
         <v>0</v>
@@ -11692,19 +11680,19 @@
         <v>0</v>
       </c>
       <c r="F274" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G274" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H274" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I274" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J274" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K274" t="n">
         <v>1</v>
@@ -11713,7 +11701,7 @@
         <v>1</v>
       </c>
       <c r="M274" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="275">
@@ -11733,19 +11721,19 @@
         <v>0</v>
       </c>
       <c r="F275" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G275" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H275" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I275" t="n">
         <v>1</v>
       </c>
       <c r="J275" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K275" t="n">
         <v>0</v>
@@ -11774,19 +11762,19 @@
         <v>0</v>
       </c>
       <c r="F276" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G276" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H276" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I276" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J276" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K276" t="n">
         <v>1</v>
@@ -11795,7 +11783,7 @@
         <v>1</v>
       </c>
       <c r="M276" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="277">
@@ -11856,22 +11844,22 @@
         <v>0</v>
       </c>
       <c r="F278" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G278" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H278" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I278" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J278" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K278" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L278" t="n">
         <v>0</v>
@@ -11906,10 +11894,10 @@
         <v>0</v>
       </c>
       <c r="I279" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J279" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K279" t="n">
         <v>0</v>
@@ -11918,7 +11906,7 @@
         <v>0</v>
       </c>
       <c r="M279" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="280">
@@ -11979,19 +11967,19 @@
         <v>0</v>
       </c>
       <c r="F281" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G281" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H281" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I281" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J281" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K281" t="n">
         <v>1</v>
@@ -12000,7 +11988,7 @@
         <v>1</v>
       </c>
       <c r="M281" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="282">
@@ -12026,10 +12014,10 @@
         <v>0</v>
       </c>
       <c r="H282" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I282" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J282" t="n">
         <v>0</v>
@@ -12225,22 +12213,22 @@
         <v>0</v>
       </c>
       <c r="F287" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G287" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H287" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I287" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J287" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K287" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L287" t="n">
         <v>0</v>
@@ -12278,16 +12266,16 @@
         <v>0</v>
       </c>
       <c r="J288" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K288" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L288" t="n">
         <v>0</v>
       </c>
       <c r="M288" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="289">
@@ -12301,10 +12289,10 @@
         <v>0</v>
       </c>
       <c r="D289" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E289" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F289" t="n">
         <v>0</v>
@@ -12460,7 +12448,9 @@
           <t>輪胎</t>
         </is>
       </c>
-      <c r="B293" t="inlineStr"/>
+      <c r="B293" t="n">
+        <v>0</v>
+      </c>
       <c r="C293" t="n">
         <v>0</v>
       </c>
@@ -12521,19 +12511,19 @@
         <v>0</v>
       </c>
       <c r="I294" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J294" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K294" t="n">
         <v>0</v>
       </c>
       <c r="L294" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M294" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="295">
@@ -12547,10 +12537,10 @@
         <v>0</v>
       </c>
       <c r="D295" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E295" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F295" t="n">
         <v>0</v>
@@ -12597,25 +12587,25 @@
         <v>0</v>
       </c>
       <c r="G296" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H296" t="n">
         <v>1</v>
       </c>
       <c r="I296" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J296" t="n">
         <v>0</v>
       </c>
       <c r="K296" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L296" t="n">
         <v>1</v>
       </c>
       <c r="M296" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="297">
@@ -12650,10 +12640,10 @@
         <v>0</v>
       </c>
       <c r="K297" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L297" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M297" t="n">
         <v>0</v>
@@ -12679,13 +12669,13 @@
         <v>0</v>
       </c>
       <c r="G298" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H298" t="n">
         <v>1</v>
       </c>
       <c r="I298" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J298" t="n">
         <v>0</v>
@@ -12799,16 +12789,16 @@
         <v>0</v>
       </c>
       <c r="F301" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G301" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H301" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I301" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J301" t="n">
         <v>0</v>
@@ -12834,25 +12824,25 @@
         <v>0</v>
       </c>
       <c r="D302" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E302" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F302" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G302" t="n">
         <v>2</v>
       </c>
       <c r="H302" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I302" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J302" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K302" t="n">
         <v>1</v>
@@ -12861,7 +12851,7 @@
         <v>1</v>
       </c>
       <c r="M302" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="303">
@@ -12875,19 +12865,19 @@
         <v>0</v>
       </c>
       <c r="D303" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E303" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F303" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G303" t="n">
         <v>1</v>
       </c>
       <c r="H303" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I303" t="n">
         <v>0</v>
@@ -12899,10 +12889,10 @@
         <v>0</v>
       </c>
       <c r="L303" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M303" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
   